--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>17536080</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>11.96399974823</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>11.5559997558594</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>11.9499998092651</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>11.6300001144409</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>21175857</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>11.9079999923706</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>11.5319995880127</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>11.8079996109009</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>5967498</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>11.8940000534058</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>11.7659997940063</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>11.8579998016357</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>11.7919998168945</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>9177625</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>11.9499998092651</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>11.8179998397827</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>11.8579998016357</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>11.9499998092651</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>6417196</v>
+        <v>3715291</v>
       </c>
       <c r="C2715" t="n">
-        <v>11.6660003662109</v>
+        <v>11.6319999694824</v>
       </c>
       <c r="D2715" t="n">
-        <v>11.5279998779297</v>
+        <v>11.5139999389648</v>
       </c>
       <c r="E2715" t="n">
-        <v>11.5699996948242</v>
+        <v>11.6199998855591</v>
       </c>
       <c r="F2715" t="n">
-        <v>11.6459999084473</v>
+        <v>11.6079998016357</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>9379609</v>
+        <v>6417196</v>
       </c>
       <c r="C2716" t="n">
-        <v>11.6339998245239</v>
+        <v>11.6660003662109</v>
       </c>
       <c r="D2716" t="n">
-        <v>11.4139995574951</v>
+        <v>11.5279998779297</v>
       </c>
       <c r="E2716" t="n">
         <v>11.5699996948242</v>
       </c>
       <c r="F2716" t="n">
-        <v>11.6260004043579</v>
+        <v>11.6459999084473</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>7811318</v>
+        <v>9379609</v>
       </c>
       <c r="C2717" t="n">
-        <v>11.7379999160767</v>
+        <v>11.6339998245239</v>
       </c>
       <c r="D2717" t="n">
-        <v>11.5860004425049</v>
+        <v>11.4139995574951</v>
       </c>
       <c r="E2717" t="n">
-        <v>11.6800003051758</v>
+        <v>11.5699996948242</v>
       </c>
       <c r="F2717" t="n">
-        <v>11.6899995803833</v>
+        <v>11.6260004043579</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>12472816</v>
+        <v>7811318</v>
       </c>
       <c r="C2718" t="n">
-        <v>12.003999710083</v>
+        <v>11.7379999160767</v>
       </c>
       <c r="D2718" t="n">
-        <v>11.7299995422363</v>
+        <v>11.5860004425049</v>
       </c>
       <c r="E2718" t="n">
-        <v>11.75</v>
+        <v>11.6800003051758</v>
       </c>
       <c r="F2718" t="n">
-        <v>11.9779996871948</v>
+        <v>11.6899995803833</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>17536080</v>
+        <v>12472816</v>
       </c>
       <c r="C2719" t="n">
-        <v>11.96399974823</v>
+        <v>12.003999710083</v>
       </c>
       <c r="D2719" t="n">
-        <v>11.5559997558594</v>
+        <v>11.7299995422363</v>
       </c>
       <c r="E2719" t="n">
-        <v>11.9499998092651</v>
+        <v>11.75</v>
       </c>
       <c r="F2719" t="n">
-        <v>11.6300001144409</v>
+        <v>11.9779996871948</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>21175857</v>
+        <v>17536080</v>
       </c>
       <c r="C2720" t="n">
-        <v>11.9079999923706</v>
+        <v>11.96399974823</v>
       </c>
       <c r="D2720" t="n">
-        <v>11.3400001525879</v>
+        <v>11.5559997558594</v>
       </c>
       <c r="E2720" t="n">
-        <v>11.5319995880127</v>
+        <v>11.9499998092651</v>
       </c>
       <c r="F2720" t="n">
-        <v>11.8079996109009</v>
+        <v>11.6300001144409</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>5967498</v>
+        <v>21175857</v>
       </c>
       <c r="C2721" t="n">
-        <v>11.8940000534058</v>
+        <v>11.9079999923706</v>
       </c>
       <c r="D2721" t="n">
-        <v>11.7659997940063</v>
+        <v>11.3400001525879</v>
       </c>
       <c r="E2721" t="n">
-        <v>11.8579998016357</v>
+        <v>11.5319995880127</v>
       </c>
       <c r="F2721" t="n">
-        <v>11.7919998168945</v>
+        <v>11.8079996109009</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>9177625</v>
+        <v>5967498</v>
       </c>
       <c r="C2722" t="n">
-        <v>11.9499998092651</v>
+        <v>11.8940000534058</v>
       </c>
       <c r="D2722" t="n">
-        <v>11.8179998397827</v>
+        <v>11.7659997940063</v>
       </c>
       <c r="E2722" t="n">
         <v>11.8579998016357</v>
       </c>
       <c r="F2722" t="n">
-        <v>11.9499998092651</v>
+        <v>11.7919998168945</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>13380944</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>11.9720001220703</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>11.706000328064</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>11.9300003051758</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>11.7639999389648</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>7595567</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>11.8339996337891</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>11.9879999160767</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73571777344</v>
+        <v>1765.73583984375</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.04797363281</v>
+        <v>1491.0478515625</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26940917969</v>
+        <v>1523.26928710938</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1365.86657714844</v>
       </c>
       <c r="G13" t="n">
-        <v>1056.05822753906</v>
+        <v>1056.05810546875</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1062.68798828125</v>
       </c>
       <c r="G14" t="n">
-        <v>821.647094726562</v>
+        <v>821.647155761719</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1364.82470703125</v>
       </c>
       <c r="G20" t="n">
-        <v>1055.25268554688</v>
+        <v>1055.25256347656</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.311462402344</v>
+        <v>918.3115234375</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.532897949219</v>
+        <v>950.533020019531</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1119.98974609375</v>
       </c>
       <c r="G29" t="n">
-        <v>865.951599121094</v>
+        <v>865.95166015625</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.422912597656</v>
+        <v>905.4228515625</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366882324219</v>
+        <v>926.366760253906</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1066.85534667969</v>
       </c>
       <c r="G36" t="n">
-        <v>824.869262695312</v>
+        <v>824.869323730469</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1115.82238769531</v>
       </c>
       <c r="G37" t="n">
-        <v>862.7294921875</v>
+        <v>862.729553222656</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1024.7646484375</v>
       </c>
       <c r="G42" t="n">
-        <v>792.32568359375</v>
+        <v>792.325622558594</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1167.91491699219</v>
       </c>
       <c r="G46" t="n">
-        <v>903.006286621094</v>
+        <v>903.00634765625</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977966308594</v>
+        <v>927.977905273438</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03125</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810485839844</v>
+        <v>961.810363769531</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254089355469</v>
+        <v>997.254211425781</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1121.03161621094</v>
       </c>
       <c r="G61" t="n">
-        <v>866.757141113281</v>
+        <v>866.757202148438</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813171386719</v>
+        <v>845.813232421875</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1048.10205078125</v>
       </c>
       <c r="G63" t="n">
-        <v>810.36962890625</v>
+        <v>810.369567871094</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>962.670288085938</v>
       </c>
       <c r="G66" t="n">
-        <v>744.315673828125</v>
+        <v>744.315612792969</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1227.30041503906</v>
       </c>
       <c r="G73" t="n">
-        <v>948.921813964844</v>
+        <v>948.921875</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.197265625</v>
+        <v>1047.19738769531</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03125</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1441.92175292969</v>
       </c>
       <c r="G78" t="n">
-        <v>1114.86242675781</v>
+        <v>1114.8623046875</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80908203125</v>
+        <v>1019.80902099609</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1153.32897949219</v>
       </c>
       <c r="G93" t="n">
-        <v>891.728820800781</v>
+        <v>891.728759765625</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1168.95678710938</v>
       </c>
       <c r="G94" t="n">
-        <v>903.811889648438</v>
+        <v>903.811950683594</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1156.45458984375</v>
       </c>
       <c r="G96" t="n">
-        <v>894.1455078125</v>
+        <v>894.145446777344</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839538574219</v>
+        <v>907.839477539062</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.142578125</v>
+        <v>1010.14263916016</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17028808594</v>
+        <v>1014.17034912109</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.143920898438</v>
+        <v>952.14404296875</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1151.24523925781</v>
       </c>
       <c r="G114" t="n">
-        <v>890.117614746094</v>
+        <v>890.11767578125</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1038.10021972656</v>
       </c>
       <c r="G117" t="n">
-        <v>802.636413574219</v>
+        <v>802.636474609375</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368286132812</v>
+        <v>868.368225097656</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749328613281</v>
+        <v>731.749267578125</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118225097656</v>
+        <v>634.118286132812</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194732666016</v>
+        <v>453.194763183594</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549591064453</v>
+        <v>481.549652099609</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259460449219</v>
+        <v>538.259399414062</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710113525391</v>
+        <v>510.710052490234</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532653808594</v>
+        <v>496.532592773438</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>541.970886230469</v>
       </c>
       <c r="G151" t="n">
-        <v>419.0400390625</v>
+        <v>419.040069580078</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>551.764282226562</v>
       </c>
       <c r="G152" t="n">
-        <v>426.612091064453</v>
+        <v>426.612121582031</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384918212891</v>
+        <v>399.384948730469</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.5126953125</v>
+        <v>400.512725830078</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G162" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>503.630737304688</v>
       </c>
       <c r="G170" t="n">
-        <v>389.396270751953</v>
+        <v>389.396301269531</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724212646484</v>
+        <v>384.724182128906</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G175" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>509.465118408203</v>
       </c>
       <c r="G177" t="n">
-        <v>393.907287597656</v>
+        <v>393.907318115234</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436737060547</v>
+        <v>325.436706542969</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003753662109</v>
+        <v>309.003784179688</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>404.86328125</v>
       </c>
       <c r="G190" t="n">
-        <v>313.031433105469</v>
+        <v>313.031463623047</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742614746094</v>
+        <v>311.742584228516</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281982421875</v>
+        <v>291.281951904297</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843322753906</v>
+        <v>279.843353271484</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499145507812</v>
+        <v>270.499114990234</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>563.641357421875</v>
       </c>
       <c r="G208" t="n">
-        <v>435.795196533203</v>
+        <v>435.795166015625</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>723.044555664062</v>
       </c>
       <c r="G209" t="n">
-        <v>559.042297363281</v>
+        <v>559.042236328125</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266448974609</v>
+        <v>475.266510009766</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184143066406</v>
+        <v>434.184112548828</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906585693359</v>
+        <v>422.906616210938</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>484.0439453125</v>
       </c>
       <c r="G217" t="n">
-        <v>374.252197265625</v>
+        <v>374.252227783203</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>537.178344726562</v>
       </c>
       <c r="G219" t="n">
-        <v>415.334594726562</v>
+        <v>415.334564208984</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>558.015380859375</v>
       </c>
       <c r="G220" t="n">
-        <v>431.4453125</v>
+        <v>431.445281982422</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>537.595092773438</v>
       </c>
       <c r="G222" t="n">
-        <v>415.656799316406</v>
+        <v>415.656768798828</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>583.228149414062</v>
       </c>
       <c r="G224" t="n">
-        <v>450.939239501953</v>
+        <v>450.939270019531</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>454.246978759766</v>
       </c>
       <c r="G242" t="n">
-        <v>351.213836669922</v>
+        <v>351.2138671875</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>94.8084259033203</v>
       </c>
       <c r="G466" t="n">
-        <v>73.3038101196289</v>
+        <v>73.3038024902344</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.1715087890625</v>
+        <v>76.171516418457</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003921508789</v>
+        <v>76.3003997802734</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>97.3505477905273</v>
       </c>
       <c r="G469" t="n">
-        <v>75.2693176269531</v>
+        <v>75.2693099975586</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426254272461</v>
+        <v>76.0426330566406</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>95.4335403442383</v>
       </c>
       <c r="G473" t="n">
-        <v>73.7871246337891</v>
+        <v>73.7871322631836</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064865112305</v>
+        <v>53.9064903259277</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>85.6401443481445</v>
       </c>
       <c r="G484" t="n">
-        <v>66.215087890625</v>
+        <v>66.2150955200195</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.1540451049805</v>
+        <v>63.154052734375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906616210938</v>
+        <v>64.9906692504883</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>83.9731826782227</v>
       </c>
       <c r="G491" t="n">
-        <v>64.9262313842773</v>
+        <v>64.9262390136719</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539855957031</v>
+        <v>66.0539779663086</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.1540451049805</v>
+        <v>63.154052734375</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618530273438</v>
+        <v>61.9618606567383</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.156322479248</v>
+        <v>61.1563148498535</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>81.5977630615234</v>
       </c>
       <c r="G514" t="n">
-        <v>63.0896034240723</v>
+        <v>63.0896110534668</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695938110352</v>
+        <v>63.6695861816406</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184867858887</v>
+        <v>63.2184944152832</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397117614746</v>
+        <v>58.7397079467773</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>75.1591186523438</v>
       </c>
       <c r="G536" t="n">
-        <v>58.1113929748535</v>
+        <v>58.111385345459</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.0607833862305</v>
+        <v>60.060791015625</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.836368560791</v>
+        <v>58.8363761901855</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.46923828125</v>
+        <v>55.4692344665527</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.9536895751953</v>
+        <v>54.953685760498</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>69.4706192016602</v>
       </c>
       <c r="G548" t="n">
-        <v>53.7131652832031</v>
+        <v>53.7131614685059</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.005428314209</v>
+        <v>52.0054321289062</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832160949707</v>
+        <v>51.6832122802734</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184745788574</v>
+        <v>40.5184783935547</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>53.1969032287598</v>
       </c>
       <c r="G576" t="n">
-        <v>41.1306838989258</v>
+        <v>41.130687713623</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>61.0524597167969</v>
       </c>
       <c r="G578" t="n">
-        <v>47.2044296264648</v>
+        <v>47.2044258117676</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>58.9687576293945</v>
       </c>
       <c r="G579" t="n">
-        <v>45.5933570861816</v>
+        <v>45.5933532714844</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.175609588623</v>
+        <v>44.1756134033203</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>56.5933380126953</v>
       </c>
       <c r="G588" t="n">
-        <v>43.7567367553711</v>
+        <v>43.7567329406738</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>56.1974334716797</v>
       </c>
       <c r="G589" t="n">
-        <v>43.4506301879883</v>
+        <v>43.450626373291</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>54.780517578125</v>
       </c>
       <c r="G597" t="n">
-        <v>42.3550987243652</v>
+        <v>42.3551025390625</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.8211784362793</v>
+        <v>43.821174621582</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431777954102</v>
+        <v>52.8431816101074</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>58.7603874206543</v>
       </c>
       <c r="G607" t="n">
-        <v>45.4322471618652</v>
+        <v>45.4322509765625</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>59.0312690734863</v>
       </c>
       <c r="G608" t="n">
-        <v>45.6416893005371</v>
+        <v>45.6416854858398</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194770812988</v>
+        <v>45.3194732666016</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250747680664</v>
+        <v>43.2250785827637</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>57.9269065856934</v>
       </c>
       <c r="G623" t="n">
-        <v>44.7878189086914</v>
+        <v>44.7878227233887</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>56.6975250244141</v>
       </c>
       <c r="G630" t="n">
-        <v>43.837287902832</v>
+        <v>43.8372917175293</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>53.1135559082031</v>
       </c>
       <c r="G634" t="n">
-        <v>41.0662422180176</v>
+        <v>41.0662460327148</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.3734817504883</v>
+        <v>40.373477935791</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.5679397583008</v>
+        <v>39.567943572998</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062690734863</v>
+        <v>39.9062728881836</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>51.0715293884277</v>
       </c>
       <c r="G642" t="n">
-        <v>39.4873924255371</v>
+        <v>39.4873886108398</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>51.1965522766113</v>
       </c>
       <c r="G644" t="n">
-        <v>39.584056854248</v>
+        <v>39.5840606689453</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>51.5299453735352</v>
       </c>
       <c r="G661" t="n">
-        <v>39.8418273925781</v>
+        <v>39.8418312072754</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>49.5921020507812</v>
       </c>
       <c r="G666" t="n">
-        <v>38.3435325622559</v>
+        <v>38.3435287475586</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>46.3415260314941</v>
       </c>
       <c r="G668" t="n">
-        <v>35.8302574157715</v>
+        <v>35.8302536010742</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>45.570556640625</v>
       </c>
       <c r="G675" t="n">
-        <v>35.2341575622559</v>
+        <v>35.2341613769531</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580749511719</v>
+        <v>34.0580787658691</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>47.1958427429199</v>
       </c>
       <c r="G690" t="n">
-        <v>36.490795135498</v>
+        <v>36.4907989501953</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057678222656</v>
+        <v>37.5057716369629</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563026428223</v>
+        <v>38.4563064575195</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>37.0377998352051</v>
       </c>
       <c r="G710" t="n">
-        <v>28.6368198394775</v>
+        <v>28.6368179321289</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884838104248</v>
+        <v>28.5884857177734</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>36.089714050293</v>
       </c>
       <c r="G713" t="n">
-        <v>27.9037780761719</v>
+        <v>27.9037799835205</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532432556152</v>
+        <v>26.9532451629639</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241111755371</v>
+        <v>25.6241130828857</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>28.5467128753662</v>
       </c>
       <c r="G719" t="n">
-        <v>22.0716953277588</v>
+        <v>22.0716972351074</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>29.2864265441895</v>
       </c>
       <c r="G720" t="n">
-        <v>22.6436252593994</v>
+        <v>22.6436233520508</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5260524749756</v>
       </c>
       <c r="G721" t="n">
-        <v>22.8288993835449</v>
+        <v>22.8288974761963</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177558898926</v>
+        <v>24.1177577972412</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>28.8071765899658</v>
       </c>
       <c r="G740" t="n">
-        <v>22.273078918457</v>
+        <v>22.2730808258057</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G742" t="n">
-        <v>24.8105182647705</v>
+        <v>24.8105163574219</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>36.7564964294434</v>
       </c>
       <c r="G747" t="n">
-        <v>28.4193210601807</v>
+        <v>28.419319152832</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782283782959</v>
+        <v>27.6782302856445</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363185882568</v>
+        <v>26.2363166809082</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193939208984</v>
+        <v>25.5193920135498</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G756" t="n">
-        <v>24.8105182647705</v>
+        <v>24.8105163574219</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983127593994</v>
+        <v>24.1983108520508</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399700164795</v>
+        <v>24.4399719238281</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058681488037</v>
+        <v>21.8058700561523</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>25.4107418060303</v>
       </c>
       <c r="G777" t="n">
-        <v>19.6470317840576</v>
+        <v>19.647029876709</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>25.598274230957</v>
       </c>
       <c r="G780" t="n">
-        <v>19.7920265197754</v>
+        <v>19.792028427124</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189617156982</v>
+        <v>20.2189598083496</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>24.9523277282715</v>
       </c>
       <c r="G787" t="n">
-        <v>19.292594909668</v>
+        <v>19.2925930023193</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136722564697</v>
+        <v>20.6136741638184</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G839" t="n">
-        <v>22.4583530426025</v>
+        <v>22.4583549499512</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>27.671558380127</v>
       </c>
       <c r="G842" t="n">
-        <v>21.3950443267822</v>
+        <v>21.3950462341309</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150596618652</v>
+        <v>20.8150577545166</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.4003238677979</v>
       </c>
       <c r="G852" t="n">
-        <v>19.6389751434326</v>
+        <v>19.6389770507812</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G856" t="n">
-        <v>18.6723327636719</v>
+        <v>18.6723308563232</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G860" t="n">
-        <v>18.4145584106445</v>
+        <v>18.4145603179932</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G861" t="n">
-        <v>18.1245670318604</v>
+        <v>18.124568939209</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G864" t="n">
-        <v>17.7701320648193</v>
+        <v>17.770133972168</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G866" t="n">
-        <v>17.1418132781982</v>
+        <v>17.1418113708496</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>21.7538452148438</v>
       </c>
       <c r="G868" t="n">
-        <v>16.8195991516113</v>
+        <v>16.8195972442627</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>21.6079864501953</v>
       </c>
       <c r="G870" t="n">
-        <v>16.706823348999</v>
+        <v>16.7068252563477</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907119750977</v>
+        <v>16.6907138824463</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134963989258</v>
+        <v>16.5134944915771</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.110725402832</v>
+        <v>16.1107273101807</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.9205417633057</v>
       </c>
       <c r="G884" t="n">
-        <v>16.9484844207764</v>
+        <v>16.9484825134277</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290374755859</v>
+        <v>17.0290393829346</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406784057617</v>
+        <v>18.1406764984131</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493412017822</v>
+        <v>27.5493431091309</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321659088135</v>
+        <v>25.6321678161621</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>34.4435882568359</v>
       </c>
       <c r="G900" t="n">
-        <v>26.6310291290283</v>
+        <v>26.631031036377</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G906" t="n">
-        <v>23.8922080993652</v>
+        <v>23.8922061920166</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.9105892181396</v>
+        <v>21.910587310791</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.5838356018066</v>
+        <v>25.583833694458</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516128540039</v>
+        <v>25.5516109466553</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416080474854</v>
+        <v>25.8416061401367</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>33.4850845336914</v>
       </c>
       <c r="G939" t="n">
-        <v>25.8899364471436</v>
+        <v>25.8899345397949</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>34.0268478393555</v>
       </c>
       <c r="G942" t="n">
-        <v>26.3088150024414</v>
+        <v>26.30881690979</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G948" t="n">
-        <v>25.0360698699951</v>
+        <v>25.0360717773438</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G950" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G951" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5262298583984</v>
       </c>
       <c r="G956" t="n">
-        <v>23.6022148132324</v>
+        <v>23.6022129058838</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727630615234</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G962" t="n">
-        <v>23.8922080993652</v>
+        <v>23.8922061920166</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>30.8596210479736</v>
       </c>
       <c r="G964" t="n">
-        <v>23.8599853515625</v>
+        <v>23.8599834442139</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>31.9431476593018</v>
       </c>
       <c r="G968" t="n">
-        <v>24.6977424621582</v>
+        <v>24.6977443695068</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G973" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.312219619751</v>
+        <v>23.3122215270996</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G980" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>30.4428825378418</v>
       </c>
       <c r="G989" t="n">
-        <v>23.5377731323242</v>
+        <v>23.5377712249756</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727630615234</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G996" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544490814209</v>
+        <v>23.0544509887695</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G999" t="n">
-        <v>22.7483444213867</v>
+        <v>22.7483463287354</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1005" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1007" t="n">
-        <v>22.7966785430908</v>
+        <v>22.7966766357422</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1009" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844711303711</v>
+        <v>22.1844692230225</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G1016" t="n">
-        <v>22.7483444213867</v>
+        <v>22.7483463287354</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G1017" t="n">
-        <v>22.4583530426025</v>
+        <v>22.4583549499512</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1020" t="n">
-        <v>22.7966785430908</v>
+        <v>22.7966766357422</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.7104473114014</v>
+        <v>27.71044921875</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493412017822</v>
+        <v>27.5493431091309</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821304321289</v>
+        <v>27.0821323394775</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>35.7146453857422</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.6137828826904</v>
+        <v>27.6137847900391</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.627628326416</v>
+        <v>29.6276245117188</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326614379883</v>
+        <v>28.0326633453369</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>37.1940765380859</v>
       </c>
       <c r="G1040" t="n">
-        <v>28.7576484680176</v>
+        <v>28.7576465606689</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737560272217</v>
+        <v>28.7737598419189</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936332702637</v>
+        <v>33.9936370849609</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>42.5075149536133</v>
       </c>
       <c r="G1052" t="n">
-        <v>32.8658790588379</v>
+        <v>32.8658828735352</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820652008057</v>
+        <v>29.9820613861084</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770225524902</v>
+        <v>31.5770263671875</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571472167969</v>
+        <v>26.3571491241455</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610492706299</v>
+        <v>25.7610511779785</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3787784576416</v>
       </c>
       <c r="G1071" t="n">
-        <v>16.5296039581299</v>
+        <v>16.5296058654785</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.7953433990479</v>
       </c>
       <c r="G1072" t="n">
-        <v>16.0785045623779</v>
+        <v>16.0785064697266</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.8023529052734</v>
+        <v>17.8023548126221</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>22.3164443969727</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.2545890808105</v>
+        <v>17.2545871734619</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.1245670318604</v>
+        <v>18.124568939209</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1102" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G1106" t="n">
-        <v>17.7701320648193</v>
+        <v>17.770133972168</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1115" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683616638184</v>
+        <v>22.1683597564697</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G1124" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G1125" t="n">
-        <v>25.0360698699951</v>
+        <v>25.0360717773438</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021457672119</v>
+        <v>26.5021438598633</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.229398727417</v>
+        <v>25.2293968200684</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.03493309021</v>
+        <v>26.0349349975586</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460746765137</v>
+        <v>24.7460765838623</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31.8597984313965</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.63330078125</v>
+        <v>24.6332988739014</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>32.7974662780762</v>
       </c>
       <c r="G1153" t="n">
-        <v>25.358283996582</v>
+        <v>25.3582859039307</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>37.5066299438477</v>
       </c>
       <c r="G1155" t="n">
-        <v>28.9993076324463</v>
+        <v>28.9993057250977</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303916931152</v>
+        <v>30.0303955078125</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>36.4856185913086</v>
       </c>
       <c r="G1159" t="n">
-        <v>28.2098827362061</v>
+        <v>28.2098846435547</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049129486084</v>
+        <v>26.9049110412598</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>34.7353096008301</v>
       </c>
       <c r="G1161" t="n">
-        <v>26.8565826416016</v>
+        <v>26.8565807342529</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655216217041</v>
+        <v>24.6655197143555</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>30.3386974334717</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.457218170166</v>
+        <v>23.4572200775146</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>31.2555255889893</v>
       </c>
       <c r="G1171" t="n">
-        <v>24.1660919189453</v>
+        <v>24.1660900115967</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>29.3801937103271</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7161235809326</v>
+        <v>22.7161254882812</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094543457031</v>
+        <v>22.9094524383545</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416751861572</v>
+        <v>22.9416732788086</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039161682129</v>
+        <v>22.1039180755615</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672920227051</v>
+        <v>20.2672939300537</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.6584911346436</v>
+        <v>16.6584892272949</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>22.7748603820801</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.6090259552002</v>
+        <v>17.6090240478516</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1240" t="n">
-        <v>19.2684288024902</v>
+        <v>19.2684268951416</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.7839698791504</v>
+        <v>19.783971786499</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>21.962215423584</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.9807052612305</v>
+        <v>16.9807033538818</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6584911346436</v>
+        <v>16.6584892272949</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934791564941</v>
+        <v>17.0934810638428</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801406860352</v>
+        <v>17.4801387786865</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.6723327636719</v>
+        <v>18.6723308563232</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>26.5255222320557</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.5089550018311</v>
+        <v>20.5089530944824</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>25.9629230499268</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.0739631652832</v>
+        <v>20.0739650726318</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>24.8793983459473</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.2362079620361</v>
+        <v>19.2362060546875</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395435333252</v>
+        <v>19.1395416259766</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750980377197</v>
+        <v>19.0750999450684</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1330" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.6078910827637</v>
+        <v>18.607889175415</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153793334961</v>
+        <v>19.1153774261475</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.8334407806396</v>
+        <v>18.833438873291</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353908538818</v>
+        <v>18.5353927612305</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864940643311</v>
+        <v>18.9864921569824</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1345" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112266540527</v>
+        <v>18.5112247467041</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1354" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>24.2959613800049</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.7851047515869</v>
+        <v>18.7851066589355</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.2684288024902</v>
+        <v>19.2684268951416</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531345367432</v>
+        <v>19.9531364440918</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397941589355</v>
+        <v>20.3397922515869</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598056793213</v>
+        <v>19.7598075866699</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>23.1707630157471</v>
       </c>
       <c r="G1402" t="n">
-        <v>17.9151287078857</v>
+        <v>17.9151268005371</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>21.9830532073975</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.9968166351318</v>
+        <v>16.9968185424805</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G1410" t="n">
-        <v>17.1418132781982</v>
+        <v>17.1418113708496</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1416" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.4103889465332</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.1004009246826</v>
+        <v>18.1004028320312</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428771972656</v>
+        <v>19.0428791046143</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>23.9208946228027</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.4951133728027</v>
+        <v>18.4951114654541</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742847442627</v>
+        <v>18.3742828369141</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292861938477</v>
+        <v>18.2292881011963</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1434" t="n">
-        <v>18.0923442840576</v>
+        <v>18.0923461914062</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>23.4520626068115</v>
       </c>
       <c r="G1440" t="n">
-        <v>18.1326217651367</v>
+        <v>18.1326236724854</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1444" t="n">
-        <v>18.0923442840576</v>
+        <v>18.0923461914062</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392929077148</v>
+        <v>17.9392948150635</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>22.5977458953857</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.4720821380615</v>
+        <v>17.4720840454102</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>23.2645282745361</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.9876270294189</v>
+        <v>17.9876251220703</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8023529052734</v>
+        <v>17.8023548126221</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>21.3475246429443</v>
       </c>
       <c r="G1485" t="n">
-        <v>16.5054397583008</v>
+        <v>16.5054378509521</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1489" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765544891357</v>
+        <v>16.3765525817871</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.9753942489624</v>
+        <v>15.975396156311</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668664932251</v>
+        <v>14.9668645858765</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9325141906738</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.6382064819336</v>
+        <v>14.6382083892822</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867658615112</v>
+        <v>14.4867668151855</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.293436050415</v>
+        <v>14.2934370040894</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013570785522</v>
+        <v>13.0013580322266</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379812240601</v>
+        <v>14.8379793167114</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.654314994812</v>
+        <v>14.6543169021606</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.6253175735474</v>
+        <v>14.625316619873</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.518988609314</v>
+        <v>14.5189876556396</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287672042847</v>
+        <v>14.4287662506104</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>18.5866184234619</v>
       </c>
       <c r="G1526" t="n">
-        <v>14.3707675933838</v>
+        <v>14.3707666397095</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958639144897</v>
+        <v>14.9958648681641</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024209976196</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316484451294</v>
+        <v>14.7316465377808</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154230117798</v>
+        <v>14.8154249191284</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.3365745544434</v>
       </c>
       <c r="G1543" t="n">
-        <v>14.1774396896362</v>
+        <v>14.1774387359619</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.7116413116455</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.467432975769</v>
+        <v>14.4674320220947</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994276046753</v>
+        <v>14.6994256973267</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5867958068848</v>
       </c>
       <c r="G1549" t="n">
-        <v>15.1440830230713</v>
+        <v>15.1440811157227</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024209976196</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.6435136795044</v>
+        <v>15.643515586853</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>21.6496601104736</v>
       </c>
       <c r="G1558" t="n">
-        <v>16.7390441894531</v>
+        <v>16.7390460968018</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147443771362</v>
+        <v>15.4147424697876</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.1325492858887</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.7928686141968</v>
+        <v>14.7928705215454</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.3654584884644</v>
+        <v>13.36545753479</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>18.1573753356934</v>
       </c>
       <c r="G1566" t="n">
-        <v>14.0388870239258</v>
+        <v>14.0388860702515</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.88649559021</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.8294477462769</v>
+        <v>13.8294486999512</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781192779541</v>
+        <v>13.5781202316284</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584480285645</v>
+        <v>13.8584470748901</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151958465576</v>
+        <v>15.0151977539062</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>20.0952186584473</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5371837615967</v>
+        <v>15.537184715271</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>20.1202239990234</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.5565176010132</v>
+        <v>15.5565195083618</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8304004669189</v>
+        <v>15.8303985595703</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.0699729919434</v>
+        <v>15.069974899292</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199178695679</v>
+        <v>15.1199159622192</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>18.6178741455078</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.3949337005615</v>
+        <v>14.3949346542358</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660474777222</v>
+        <v>14.2660484313965</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585592269897</v>
+        <v>13.7585582733154</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116125106812</v>
+        <v>13.9116115570068</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>17.8573226928711</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8068914413452</v>
+        <v>13.8068923950195</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722211837769</v>
+        <v>11.6722221374512</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519580841064</v>
+        <v>11.0519590377808</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.3902835845947</v>
+        <v>11.390284538269</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3902835845947</v>
+        <v>11.390284538269</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433340072632</v>
+        <v>11.5433349609375</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.970269203186</v>
+        <v>11.9702701568604</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5860891342163</v>
       </c>
       <c r="G1628" t="n">
-        <v>12.0508232116699</v>
+        <v>12.0508241653442</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.1903629302979</v>
       </c>
       <c r="G1630" t="n">
-        <v>12.5180349349976</v>
+        <v>12.5180358886719</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.0445022583008</v>
       </c>
       <c r="G1631" t="n">
-        <v>12.4052591323853</v>
+        <v>12.4052581787109</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805246353149</v>
+        <v>12.8805255889893</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.253342628479</v>
+        <v>11.2533416748047</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439023971558</v>
+        <v>11.0439033508301</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136325836182</v>
+        <v>10.7136335372925</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535598754883</v>
+        <v>8.34535694122314</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971380233765</v>
+        <v>7.34971284866333</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>8.91824340820312</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.89539098739624</v>
+        <v>6.8953914642334</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>9.3766565322876</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.24982595443726</v>
+        <v>7.2498254776001</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316919326782</v>
+        <v>6.86316871643066</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539722442627</v>
+        <v>6.60539770126343</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>8.8223934173584</v>
       </c>
       <c r="G1676" t="n">
-        <v>6.82128143310547</v>
+        <v>6.82128190994263</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927337646484</v>
+        <v>7.16927289962769</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.74072790145874</v>
+        <v>6.7407283782959</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973346710205</v>
+        <v>6.47973394393921</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>7.91806602478027</v>
       </c>
       <c r="G1689" t="n">
-        <v>6.1220760345459</v>
+        <v>6.12207555770874</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799428939819</v>
+        <v>4.88799476623535</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>6.05523681640625</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.68177700042725</v>
+        <v>4.68177652359009</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555204391479</v>
+        <v>4.76555252075195</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.91699314117432</v>
+        <v>4.91699361801147</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.91699314117432</v>
+        <v>4.91699361801147</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>6.2302680015564</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.81710720062256</v>
+        <v>4.8171067237854</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179761886597</v>
+        <v>3.81179785728455</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.68311882019043</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.62088489532471</v>
+        <v>3.62088513374329</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.55331492424011</v>
+        <v>1.5533150434494</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089272975922</v>
+        <v>1.53089284896851</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393748760223</v>
+        <v>1.37393760681152</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006953716278</v>
+        <v>1.46006965637207</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.88339996337891</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.45620369911194</v>
+        <v>1.45620381832123</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537925720215</v>
+        <v>1.44537937641144</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903848648071</v>
+        <v>1.46903860569</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.52161467075348</v>
+        <v>1.52161455154419</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.50213050842285</v>
+        <v>1.50213062763214</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.06299996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.5950665473938</v>
+        <v>1.59506642818451</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490919589996</v>
+        <v>1.71490931510925</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702329158783</v>
+        <v>1.67702341079712</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.6031848192215</v>
+        <v>1.60318493843079</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259310245514</v>
+        <v>1.56259298324585</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.65305495262146</v>
+        <v>1.65305483341217</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.10450005531311</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.62715351581573</v>
+        <v>1.62715339660645</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.79377329349518</v>
+        <v>1.79377341270447</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552491664886</v>
+        <v>1.83552515506744</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.63949990272522</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.04080367088318</v>
+        <v>2.04080390930176</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.0338454246521</v>
+        <v>2.03384518623352</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198758125305</v>
+        <v>2.12198734283447</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.90665745735168</v>
+        <v>1.9066573381424</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305159091949</v>
+        <v>1.80305147171021</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.13649988174438</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.65189504623413</v>
+        <v>1.65189492702484</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46208000183105</v>
+        <v>1.46207988262177</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.51759397983551</v>
+        <v>1.5175940990448</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222691059113</v>
+        <v>1.79222702980042</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666093826294</v>
+        <v>1.75666081905365</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630158901215</v>
+        <v>1.68630146980286</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831318378448</v>
+        <v>1.6283130645752</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.64686954021454</v>
+        <v>1.64686965942383</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.73501169681549</v>
+        <v>1.73501181602478</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.68939423561096</v>
+        <v>1.68939435482025</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.6205815076828</v>
+        <v>1.62058138847351</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006492614746</v>
+        <v>1.67006480693817</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.73037266731262</v>
+        <v>1.73037254810333</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.75820708274841</v>
+        <v>1.7582072019577</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011617660522</v>
+        <v>1.68011629581451</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65769398212433</v>
+        <v>1.65769410133362</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.7659387588501</v>
+        <v>1.76593887805939</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.80073201656342</v>
+        <v>1.80073189735413</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82701992988586</v>
+        <v>1.82702016830444</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.74583613872528</v>
+        <v>1.74583625793457</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645557880402</v>
+        <v>1.71645545959473</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985284328461</v>
+        <v>1.92985260486603</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309947967529</v>
+        <v>1.96309924125671</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918191432953</v>
+        <v>1.94918215274811</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562405586243</v>
+        <v>2.00562429428101</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959251403809</v>
+        <v>2.02959275245667</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025948524475</v>
+        <v>2.16025972366333</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.02263402938843</v>
+        <v>2.02263379096985</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.954594373703</v>
+        <v>1.95459449291229</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309947967529</v>
+        <v>1.96309924125671</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763913154602</v>
+        <v>1.79763925075531</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.7497022151947</v>
+        <v>1.74970209598541</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310272216797</v>
+        <v>1.81310284137726</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645197868347</v>
+        <v>1.86645221710205</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866893291473</v>
+        <v>1.84866917133331</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737927913666</v>
+        <v>1.89737904071808</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639724731445</v>
+        <v>2.00639748573303</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.90124535560608</v>
+        <v>1.9012451171875</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397505283356</v>
+        <v>1.98397529125214</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.85872030258179</v>
+        <v>1.85872042179108</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062591552734</v>
+        <v>1.93062567710876</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237753868103</v>
+        <v>1.97237777709961</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964376449585</v>
+        <v>2.03964400291443</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.0868079662323</v>
+        <v>2.08680772781372</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443690299988</v>
+        <v>2.07443714141846</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>3.06100010871887</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.36669826507568</v>
+        <v>2.36669850349426</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654775619507</v>
+        <v>2.18654799461365</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716347694397</v>
+        <v>2.30716371536255</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071797370911</v>
+        <v>2.40071821212769</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921983718872</v>
+        <v>2.55921959877014</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.35742044448853</v>
+        <v>2.35742020606995</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876158714294</v>
+        <v>2.31876134872437</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061571121216</v>
+        <v>2.38061547279358</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.3643786907196</v>
+        <v>2.36437892913818</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37442994117737</v>
+        <v>2.37443017959595</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.38757419586182</v>
+        <v>2.3875744342804</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.5777759552002</v>
+        <v>2.57777619361877</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334228515625</v>
+        <v>2.61334252357483</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597308158875</v>
+        <v>2.52597284317017</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.5252001285553</v>
+        <v>2.52519989013672</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710898399353</v>
+        <v>2.44710874557495</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.49891209602356</v>
+        <v>2.49891185760498</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.49659252166748</v>
+        <v>2.4965922832489</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>3.38899993896484</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.62030076980591</v>
+        <v>2.62030053138733</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983927726746</v>
+        <v>2.52983903884888</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792622566223</v>
+        <v>2.75792646408081</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467970848083</v>
+        <v>2.72467994689941</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452595710754</v>
+        <v>2.69452571868896</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.83137845993042</v>
+        <v>2.83137822151184</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2087" t="n">
-        <v>3.14219617843628</v>
+        <v>3.14219641685486</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188447952271</v>
+        <v>3.23188471794128</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.36487150192261</v>
+        <v>3.36487126350403</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>4.20900011062622</v>
       </c>
       <c r="G2096" t="n">
-        <v>3.25430703163147</v>
+        <v>3.25430679321289</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343133926392</v>
+        <v>3.23343110084534</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693434715271</v>
+        <v>3.31693458557129</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739607810974</v>
+        <v>3.40739631652832</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471426963806</v>
+        <v>3.48471403121948</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G2119" t="n">
-        <v>3.47466254234314</v>
+        <v>3.47466278076172</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2120" t="n">
-        <v>3.51796054840088</v>
+        <v>3.51796078681946</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811105728149</v>
+        <v>3.69811153411865</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409482955933</v>
+        <v>3.51409506797791</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667041778564</v>
+        <v>3.56667065620422</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.62002015113831</v>
+        <v>3.62002038955688</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145683288574</v>
+        <v>3.9014573097229</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>11.8940000534058</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>8219347</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>11.960000038147</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>11.8039999008179</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>11.8100004196167</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>11.8159999847412</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>11.8159999847412</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -499,7 +499,7 @@
         <v>2208.72412109375</v>
       </c>
       <c r="G5" t="n">
-        <v>1707.73718261719</v>
+        <v>1707.7373046875</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1933.67529296875</v>
       </c>
       <c r="G8" t="n">
-        <v>1495.07556152344</v>
+        <v>1495.07543945312</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26928710938</v>
+        <v>1523.26940917969</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2005.56311035156</v>
       </c>
       <c r="G10" t="n">
-        <v>1550.65771484375</v>
+        <v>1550.65759277344</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1595.07385253906</v>
       </c>
       <c r="G12" t="n">
-        <v>1233.27624511719</v>
+        <v>1233.2763671875</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1365.86657714844</v>
       </c>
       <c r="G13" t="n">
-        <v>1056.05810546875</v>
+        <v>1056.05822753906</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1481.51208496094</v>
       </c>
       <c r="G19" t="n">
-        <v>1145.47290039062</v>
+        <v>1145.47277832031</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14123535156</v>
+        <v>1068.14135742188</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1082.48315429688</v>
       </c>
       <c r="G27" t="n">
-        <v>836.952331542969</v>
+        <v>836.952392578125</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1009.34521484375</v>
       </c>
       <c r="G30" t="n">
-        <v>780.403625488281</v>
+        <v>780.403686523438</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>956.8359375</v>
       </c>
       <c r="G31" t="n">
-        <v>739.804626464844</v>
+        <v>739.8046875</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1044.97644042969</v>
       </c>
       <c r="G32" t="n">
-        <v>807.952941894531</v>
+        <v>807.953002929688</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366760253906</v>
+        <v>926.366882324219</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1077.27392578125</v>
       </c>
       <c r="G35" t="n">
-        <v>832.924682617188</v>
+        <v>832.924621582031</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1115.82238769531</v>
       </c>
       <c r="G37" t="n">
-        <v>862.729553222656</v>
+        <v>862.7294921875</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1073.1064453125</v>
       </c>
       <c r="G39" t="n">
-        <v>829.702453613281</v>
+        <v>829.702514648438</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1079.35754394531</v>
       </c>
       <c r="G40" t="n">
-        <v>834.535705566406</v>
+        <v>834.53564453125</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1167.91491699219</v>
       </c>
       <c r="G46" t="n">
-        <v>903.00634765625</v>
+        <v>903.006286621094</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G49" t="n">
-        <v>853.868591308594</v>
+        <v>853.86865234375</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G50" t="n">
-        <v>853.868591308594</v>
+        <v>853.86865234375</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03125</v>
+        <v>1023.03131103516</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810363769531</v>
+        <v>961.810424804688</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1245.01184082031</v>
       </c>
       <c r="G54" t="n">
-        <v>962.615966796875</v>
+        <v>962.616027832031</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1193.96118164062</v>
       </c>
       <c r="G55" t="n">
-        <v>923.144714355469</v>
+        <v>923.144775390625</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1240.84448242188</v>
       </c>
       <c r="G56" t="n">
-        <v>959.393920898438</v>
+        <v>959.393859863281</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254211425781</v>
+        <v>997.254028320312</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199462890625</v>
+        <v>960.199340820312</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1177.29162597656</v>
       </c>
       <c r="G60" t="n">
-        <v>910.256164550781</v>
+        <v>910.256225585938</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1121.03161621094</v>
       </c>
       <c r="G61" t="n">
-        <v>866.757202148438</v>
+        <v>866.757141113281</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1048.10205078125</v>
       </c>
       <c r="G63" t="n">
-        <v>810.369567871094</v>
+        <v>810.36962890625</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1040.18395996094</v>
       </c>
       <c r="G64" t="n">
-        <v>804.247497558594</v>
+        <v>804.24755859375</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1000.80200195312</v>
       </c>
       <c r="G65" t="n">
-        <v>773.798217773438</v>
+        <v>773.798278808594</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>962.670288085938</v>
       </c>
       <c r="G66" t="n">
-        <v>744.315612792969</v>
+        <v>744.315673828125</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>908.702392578125</v>
       </c>
       <c r="G68" t="n">
-        <v>702.588806152344</v>
+        <v>702.5888671875</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>980.381713867188</v>
       </c>
       <c r="G69" t="n">
-        <v>758.009765625</v>
+        <v>758.009704589844</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1088.73425292969</v>
       </c>
       <c r="G71" t="n">
-        <v>841.785522460938</v>
+        <v>841.785583496094</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1227.30041503906</v>
       </c>
       <c r="G73" t="n">
-        <v>948.921875</v>
+        <v>948.921813964844</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1251.26293945312</v>
       </c>
       <c r="G74" t="n">
-        <v>967.44921875</v>
+        <v>967.449157714844</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03125</v>
+        <v>1023.03131103516</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86303710938</v>
+        <v>1085.86291503906</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1441.92175292969</v>
       </c>
       <c r="G78" t="n">
-        <v>1114.8623046875</v>
+        <v>1114.86242675781</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1379.41064453125</v>
       </c>
       <c r="G80" t="n">
-        <v>1066.53015136719</v>
+        <v>1066.5302734375</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1390.87097167969</v>
       </c>
       <c r="G85" t="n">
-        <v>1075.39099121094</v>
+        <v>1075.39111328125</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1267.9326171875</v>
       </c>
       <c r="G87" t="n">
-        <v>980.337768554688</v>
+        <v>980.337829589844</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80902099609</v>
+        <v>1019.80908203125</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G90" t="n">
-        <v>965.032653808594</v>
+        <v>965.032592773438</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1208.54711914062</v>
       </c>
       <c r="G91" t="n">
-        <v>934.422302246094</v>
+        <v>934.422241210938</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1168.95678710938</v>
       </c>
       <c r="G94" t="n">
-        <v>903.811950683594</v>
+        <v>903.811889648438</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1163.74755859375</v>
       </c>
       <c r="G95" t="n">
-        <v>899.784240722656</v>
+        <v>899.7841796875</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839477539062</v>
+        <v>907.839538574219</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1159.580078125</v>
       </c>
       <c r="G100" t="n">
-        <v>896.56201171875</v>
+        <v>896.561950683594</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809814453125</v>
+        <v>990.809753417969</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47625732422</v>
+        <v>1000.47613525391</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.14263916016</v>
+        <v>1010.14270019531</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.6982421875</v>
+        <v>1003.69830322266</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G107" t="n">
-        <v>965.032653808594</v>
+        <v>965.032592773438</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1274.18371582031</v>
       </c>
       <c r="G108" t="n">
-        <v>985.170959472656</v>
+        <v>985.171020507812</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1214.79821777344</v>
       </c>
       <c r="G109" t="n">
-        <v>939.255493164062</v>
+        <v>939.255432128906</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809814453125</v>
+        <v>990.809753417969</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.14404296875</v>
+        <v>952.143981933594</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1151.24523925781</v>
       </c>
       <c r="G114" t="n">
-        <v>890.11767578125</v>
+        <v>890.117614746094</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1046.01831054688</v>
       </c>
       <c r="G115" t="n">
-        <v>808.758544921875</v>
+        <v>808.758483886719</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1038.10021972656</v>
       </c>
       <c r="G117" t="n">
-        <v>802.636474609375</v>
+        <v>802.636413574219</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1003.30242919922</v>
       </c>
       <c r="G118" t="n">
-        <v>775.731567382812</v>
+        <v>775.731506347656</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>809.934936523438</v>
       </c>
       <c r="G127" t="n">
-        <v>626.223999023438</v>
+        <v>626.223937988281</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>685.537902832031</v>
       </c>
       <c r="G130" t="n">
-        <v>530.042907714844</v>
+        <v>530.04296875</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>552.597717285156</v>
       </c>
       <c r="G131" t="n">
-        <v>427.256500244141</v>
+        <v>427.256469726562</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194763183594</v>
+        <v>453.194793701172</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>552.181030273438</v>
       </c>
       <c r="G133" t="n">
-        <v>426.934295654297</v>
+        <v>426.934326171875</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>680.745422363281</v>
       </c>
       <c r="G137" t="n">
-        <v>526.337463378906</v>
+        <v>526.337524414062</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.537658691406</v>
+        <v>520.53759765625</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710052490234</v>
+        <v>510.710083007812</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>650.114990234375</v>
       </c>
       <c r="G144" t="n">
-        <v>502.654693603516</v>
+        <v>502.654754638672</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>595.313598632812</v>
       </c>
       <c r="G145" t="n">
-        <v>460.283447265625</v>
+        <v>460.283477783203</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>604.273559570312</v>
       </c>
       <c r="G148" t="n">
-        <v>467.211151123047</v>
+        <v>467.211120605469</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>551.764282226562</v>
       </c>
       <c r="G152" t="n">
-        <v>426.612121582031</v>
+        <v>426.612091064453</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>539.678771972656</v>
       </c>
       <c r="G153" t="n">
-        <v>417.267852783203</v>
+        <v>417.267822265625</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>531.135620117188</v>
       </c>
       <c r="G154" t="n">
-        <v>410.662475585938</v>
+        <v>410.662445068359</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>523.009155273438</v>
       </c>
       <c r="G159" t="n">
-        <v>404.379272460938</v>
+        <v>404.379241943359</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.512725830078</v>
+        <v>400.5126953125</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>477.58447265625</v>
       </c>
       <c r="G164" t="n">
-        <v>369.257904052734</v>
+        <v>369.257873535156</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>494.879211425781</v>
       </c>
       <c r="G165" t="n">
-        <v>382.629791259766</v>
+        <v>382.629821777344</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>503.630737304688</v>
       </c>
       <c r="G170" t="n">
-        <v>389.396301269531</v>
+        <v>389.396270751953</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>476.125885009766</v>
       </c>
       <c r="G180" t="n">
-        <v>368.130126953125</v>
+        <v>368.130157470703</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>392.569427490234</v>
       </c>
       <c r="G188" t="n">
-        <v>303.526092529297</v>
+        <v>303.526123046875</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281951904297</v>
+        <v>291.281982421875</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>354.229309082031</v>
       </c>
       <c r="G198" t="n">
-        <v>273.882354736328</v>
+        <v>273.882385253906</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>355.896270751953</v>
       </c>
       <c r="G202" t="n">
-        <v>275.171234130859</v>
+        <v>275.171203613281</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>360.897155761719</v>
       </c>
       <c r="G204" t="n">
-        <v>279.037780761719</v>
+        <v>279.037811279297</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>497.379638671875</v>
       </c>
       <c r="G207" t="n">
-        <v>384.563079833984</v>
+        <v>384.563049316406</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>563.641357421875</v>
       </c>
       <c r="G208" t="n">
-        <v>435.795166015625</v>
+        <v>435.795196533203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>723.044555664062</v>
       </c>
       <c r="G209" t="n">
-        <v>559.042236328125</v>
+        <v>559.042297363281</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>506.547943115234</v>
       </c>
       <c r="G214" t="n">
-        <v>391.651824951172</v>
+        <v>391.651794433594</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>484.0439453125</v>
       </c>
       <c r="G217" t="n">
-        <v>374.252227783203</v>
+        <v>374.252197265625</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>439.661102294922</v>
       </c>
       <c r="G218" t="n">
-        <v>339.936340332031</v>
+        <v>339.936370849609</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>537.595092773438</v>
       </c>
       <c r="G222" t="n">
-        <v>415.656768798828</v>
+        <v>415.656799316406</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829254150391</v>
+        <v>405.829284667969</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>495.712677001953</v>
       </c>
       <c r="G227" t="n">
-        <v>383.274230957031</v>
+        <v>383.274200439453</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>464.040405273438</v>
       </c>
       <c r="G231" t="n">
-        <v>358.785888671875</v>
+        <v>358.785919189453</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>454.246978759766</v>
       </c>
       <c r="G242" t="n">
-        <v>351.2138671875</v>
+        <v>351.213836669922</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>436.118774414062</v>
       </c>
       <c r="G248" t="n">
-        <v>337.197540283203</v>
+        <v>337.197509765625</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>387.985260009766</v>
       </c>
       <c r="G249" t="n">
-        <v>299.981750488281</v>
+        <v>299.981719970703</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>339.643371582031</v>
       </c>
       <c r="G251" t="n">
-        <v>262.604858398438</v>
+        <v>262.604827880859</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>97.3505477905273</v>
       </c>
       <c r="G469" t="n">
-        <v>75.2693099975586</v>
+        <v>75.2693176269531</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426330566406</v>
+        <v>76.0426254272461</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>97.0588302612305</v>
       </c>
       <c r="G472" t="n">
-        <v>75.0437698364258</v>
+        <v>75.0437622070312</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>93.6832275390625</v>
       </c>
       <c r="G475" t="n">
-        <v>72.4338226318359</v>
+        <v>72.4338302612305</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>85.4734420776367</v>
       </c>
       <c r="G478" t="n">
-        <v>66.0861968994141</v>
+        <v>66.0862045288086</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.1218338012695</v>
+        <v>63.1218299865723</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264366149902</v>
+        <v>56.2264404296875</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>85.6401443481445</v>
       </c>
       <c r="G484" t="n">
-        <v>66.2150955200195</v>
+        <v>66.215087890625</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.154052734375</v>
+        <v>63.1540451049805</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>82.0978469848633</v>
       </c>
       <c r="G487" t="n">
-        <v>63.476261138916</v>
+        <v>63.4762649536133</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>83.306396484375</v>
       </c>
       <c r="G488" t="n">
-        <v>64.4106903076172</v>
+        <v>64.4106826782227</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>84.1815490722656</v>
       </c>
       <c r="G489" t="n">
-        <v>65.0873336791992</v>
+        <v>65.0873413085938</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>83.9731826782227</v>
       </c>
       <c r="G491" t="n">
-        <v>64.9262390136719</v>
+        <v>64.9262313842773</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.154052734375</v>
+        <v>63.1540451049805</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G496" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>80.4725646972656</v>
       </c>
       <c r="G497" t="n">
-        <v>62.2196273803711</v>
+        <v>62.2196311950684</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>80.4308853149414</v>
       </c>
       <c r="G499" t="n">
-        <v>62.1874046325684</v>
+        <v>62.1874084472656</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618606567383</v>
+        <v>61.9618530273438</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563148498535</v>
+        <v>61.1563186645508</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>78.430534362793</v>
       </c>
       <c r="G502" t="n">
-        <v>60.6407814025879</v>
+        <v>60.6407737731934</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>77.5137023925781</v>
       </c>
       <c r="G503" t="n">
-        <v>59.9319000244141</v>
+        <v>59.9319038391113</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G506" t="n">
-        <v>62.5096206665039</v>
+        <v>62.5096168518066</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>79.7640991210938</v>
       </c>
       <c r="G508" t="n">
-        <v>61.6718559265137</v>
+        <v>61.6718597412109</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>81.93115234375</v>
       </c>
       <c r="G510" t="n">
-        <v>63.3473777770996</v>
+        <v>63.3473739624023</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573844909668</v>
+        <v>63.0573806762695</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.4129524230957</v>
+        <v>62.4129600524902</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>81.5977630615234</v>
       </c>
       <c r="G514" t="n">
-        <v>63.0896110534668</v>
+        <v>63.0896034240723</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G516" t="n">
-        <v>62.5096206665039</v>
+        <v>62.5096168518066</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G518" t="n">
-        <v>63.927360534668</v>
+        <v>63.9273643493652</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>83.7231369018555</v>
       </c>
       <c r="G520" t="n">
-        <v>64.7328948974609</v>
+        <v>64.7329025268555</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695861816406</v>
+        <v>63.6695938110352</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G523" t="n">
-        <v>63.927360534668</v>
+        <v>63.9273643493652</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G524" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G528" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>81.0143203735352</v>
       </c>
       <c r="G529" t="n">
-        <v>62.6385040283203</v>
+        <v>62.6385078430176</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>80.555908203125</v>
       </c>
       <c r="G531" t="n">
-        <v>62.2840690612793</v>
+        <v>62.2840728759766</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>78.8055953979492</v>
       </c>
       <c r="G532" t="n">
-        <v>60.9307632446289</v>
+        <v>60.9307670593262</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>77.9721221923828</v>
       </c>
       <c r="G534" t="n">
-        <v>60.2863426208496</v>
+        <v>60.2863464355469</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397079467773</v>
+        <v>58.7397041320801</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>75.1591186523438</v>
       </c>
       <c r="G536" t="n">
-        <v>58.111385345459</v>
+        <v>58.1113929748535</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.060791015625</v>
+        <v>60.0607872009277</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>78.1388168334961</v>
       </c>
       <c r="G538" t="n">
-        <v>60.4152297973633</v>
+        <v>60.4152221679688</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>74.8048934936523</v>
       </c>
       <c r="G541" t="n">
-        <v>57.8375091552734</v>
+        <v>57.8375129699707</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>70.8458557128906</v>
       </c>
       <c r="G542" t="n">
-        <v>54.7764663696289</v>
+        <v>54.7764701843262</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>71.8877105712891</v>
       </c>
       <c r="G544" t="n">
-        <v>55.5820045471191</v>
+        <v>55.5820121765137</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.4692344665527</v>
+        <v>55.4692306518555</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.953685760498</v>
+        <v>54.9536895751953</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>69.4706192016602</v>
       </c>
       <c r="G548" t="n">
-        <v>53.7131614685059</v>
+        <v>53.7131652832031</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>67.0951995849609</v>
       </c>
       <c r="G549" t="n">
-        <v>51.8765449523926</v>
+        <v>51.8765411376953</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>66.9910125732422</v>
       </c>
       <c r="G553" t="n">
-        <v>51.7959899902344</v>
+        <v>51.7959861755371</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G557" t="n">
-        <v>51.2321166992188</v>
+        <v>51.2321128845215</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G558" t="n">
-        <v>51.2321166992188</v>
+        <v>51.2321128845215</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>65.4282302856445</v>
       </c>
       <c r="G560" t="n">
-        <v>50.5876808166504</v>
+        <v>50.5876770019531</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>65.0114974975586</v>
       </c>
       <c r="G561" t="n">
-        <v>50.2654685974121</v>
+        <v>50.2654724121094</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>63.6987609863281</v>
       </c>
       <c r="G563" t="n">
-        <v>49.2504920959473</v>
+        <v>49.25048828125</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>63.8237838745117</v>
       </c>
       <c r="G564" t="n">
-        <v>49.3471565246582</v>
+        <v>49.3471527099609</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>56.0099029541016</v>
       </c>
       <c r="G570" t="n">
-        <v>43.3056335449219</v>
+        <v>43.3056373596191</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>54.3221054077148</v>
       </c>
       <c r="G571" t="n">
-        <v>42.0006675720215</v>
+        <v>42.0006637573242</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>52.9051856994629</v>
       </c>
       <c r="G572" t="n">
-        <v>40.9051322937012</v>
+        <v>40.9051361083984</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367866516113</v>
+        <v>41.4367904663086</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>57.8435592651367</v>
       </c>
       <c r="G577" t="n">
-        <v>44.7233772277832</v>
+        <v>44.7233734130859</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>61.0524597167969</v>
       </c>
       <c r="G578" t="n">
-        <v>47.2044258117676</v>
+        <v>47.2044296264648</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>58.9687576293945</v>
       </c>
       <c r="G579" t="n">
-        <v>45.5933532714844</v>
+        <v>45.5933570861816</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.1756134033203</v>
+        <v>44.175609588623</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>55.5723266601562</v>
       </c>
       <c r="G581" t="n">
-        <v>42.9673080444336</v>
+        <v>42.9673118591309</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G584" t="n">
-        <v>42.9511985778809</v>
+        <v>42.9511947631836</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>55.5306510925293</v>
       </c>
       <c r="G585" t="n">
-        <v>42.9350891113281</v>
+        <v>42.9350852966309</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>56.8850555419922</v>
       </c>
       <c r="G586" t="n">
-        <v>43.9822807312012</v>
+        <v>43.9822845458984</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>56.5933380126953</v>
       </c>
       <c r="G588" t="n">
-        <v>43.7567329406738</v>
+        <v>43.7567367553711</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>55.4889755249023</v>
       </c>
       <c r="G593" t="n">
-        <v>42.9028625488281</v>
+        <v>42.9028663635254</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>56.2599449157715</v>
       </c>
       <c r="G596" t="n">
-        <v>43.4989624023438</v>
+        <v>43.4989585876465</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>57.3017959594727</v>
       </c>
       <c r="G600" t="n">
-        <v>44.3044967651367</v>
+        <v>44.304500579834</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>60.9066009521484</v>
       </c>
       <c r="G606" t="n">
-        <v>47.0916519165039</v>
+        <v>47.0916557312012</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>59.0312690734863</v>
       </c>
       <c r="G608" t="n">
-        <v>45.6416854858398</v>
+        <v>45.6416893005371</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G611" t="n">
-        <v>44.3206100463867</v>
+        <v>44.3206062316895</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>52.2800750732422</v>
       </c>
       <c r="G614" t="n">
-        <v>40.4218139648438</v>
+        <v>40.4218101501465</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G618" t="n">
-        <v>42.9511985778809</v>
+        <v>42.9511947631836</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>57.1976127624512</v>
       </c>
       <c r="G621" t="n">
-        <v>44.2239456176758</v>
+        <v>44.2239418029785</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>57.9269065856934</v>
       </c>
       <c r="G623" t="n">
-        <v>44.7878227233887</v>
+        <v>44.7878189086914</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G624" t="n">
-        <v>44.3206100463867</v>
+        <v>44.3206062316895</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>58.5520172119141</v>
       </c>
       <c r="G625" t="n">
-        <v>45.2711410522461</v>
+        <v>45.2711372375488</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>56.6975250244141</v>
       </c>
       <c r="G630" t="n">
-        <v>43.8372917175293</v>
+        <v>43.837287902832</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>53.1135559082031</v>
       </c>
       <c r="G634" t="n">
-        <v>41.0662460327148</v>
+        <v>41.0662422180176</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>51.0715293884277</v>
       </c>
       <c r="G642" t="n">
-        <v>39.4873886108398</v>
+        <v>39.4873924255371</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>51.1965522766113</v>
       </c>
       <c r="G644" t="n">
-        <v>39.5840606689453</v>
+        <v>39.584056854248</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.0374298095703</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.0213165283203</v>
+        <v>38.021312713623</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>49.3628921508789</v>
       </c>
       <c r="G663" t="n">
-        <v>38.1663131713867</v>
+        <v>38.1663093566895</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>49.5921020507812</v>
       </c>
       <c r="G666" t="n">
-        <v>38.3435287475586</v>
+        <v>38.3435325622559</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>46.3415260314941</v>
       </c>
       <c r="G668" t="n">
-        <v>35.8302536010742</v>
+        <v>35.8302574157715</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G669" t="n">
-        <v>35.4435958862305</v>
+        <v>35.4435997009277</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G671" t="n">
-        <v>35.4435958862305</v>
+        <v>35.4435997009277</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G672" t="n">
-        <v>35.3952674865723</v>
+        <v>35.395263671875</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>45.9247856140137</v>
       </c>
       <c r="G674" t="n">
-        <v>35.5080375671387</v>
+        <v>35.5080413818359</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>45.570556640625</v>
       </c>
       <c r="G675" t="n">
-        <v>35.2341613769531</v>
+        <v>35.2341575622559</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>45.4038581848145</v>
       </c>
       <c r="G679" t="n">
-        <v>35.1052703857422</v>
+        <v>35.1052742004395</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580787658691</v>
+        <v>34.0580749511719</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>43.132625579834</v>
       </c>
       <c r="G681" t="n">
-        <v>33.3492050170898</v>
+        <v>33.3492012023926</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>46.3206901550293</v>
       </c>
       <c r="G685" t="n">
-        <v>35.8141441345215</v>
+        <v>35.8141479492188</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G686" t="n">
-        <v>35.3952674865723</v>
+        <v>35.395263671875</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G687" t="n">
-        <v>38.3113098144531</v>
+        <v>38.3113059997559</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.0374298095703</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>47.695930480957</v>
       </c>
       <c r="G689" t="n">
-        <v>36.8774528503418</v>
+        <v>36.8774490356445</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>47.1958427429199</v>
       </c>
       <c r="G690" t="n">
-        <v>36.4907989501953</v>
+        <v>36.490795135498</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057716369629</v>
+        <v>37.5057754516602</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G697" t="n">
-        <v>38.3113098144531</v>
+        <v>38.3113059997559</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>50.175537109375</v>
       </c>
       <c r="G699" t="n">
-        <v>38.7946281433105</v>
+        <v>38.7946319580078</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.0213165283203</v>
+        <v>38.021312713623</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>42.9242553710938</v>
       </c>
       <c r="G703" t="n">
-        <v>33.1880950927734</v>
+        <v>33.1880989074707</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>42.861743927002</v>
       </c>
       <c r="G704" t="n">
-        <v>33.139762878418</v>
+        <v>33.1397666931152</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>38.5068092346191</v>
       </c>
       <c r="G709" t="n">
-        <v>29.7726249694824</v>
+        <v>29.7726230621338</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>35.7875785827637</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6701755523682</v>
+        <v>27.6701736450195</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241130828857</v>
+        <v>25.6241111755371</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>31.3805484771729</v>
       </c>
       <c r="G717" t="n">
-        <v>24.2627563476562</v>
+        <v>24.2627544403076</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>28.5467128753662</v>
       </c>
       <c r="G719" t="n">
-        <v>22.0716972351074</v>
+        <v>22.0716953277588</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>29.2864265441895</v>
       </c>
       <c r="G720" t="n">
-        <v>22.6436233520508</v>
+        <v>22.6436252593994</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5260524749756</v>
       </c>
       <c r="G721" t="n">
-        <v>22.8288974761963</v>
+        <v>22.8288993835449</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480266571045</v>
+        <v>24.4480247497559</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>30.7137622833252</v>
       </c>
       <c r="G729" t="n">
-        <v>23.7472095489502</v>
+        <v>23.7472114562988</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>29.411449432373</v>
       </c>
       <c r="G735" t="n">
-        <v>22.7402896881104</v>
+        <v>22.740291595459</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>28.7863388061523</v>
       </c>
       <c r="G739" t="n">
-        <v>22.2569675445557</v>
+        <v>22.2569694519043</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>28.8071765899658</v>
       </c>
       <c r="G740" t="n">
-        <v>22.2730808258057</v>
+        <v>22.273078918457</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>29.7031688690186</v>
       </c>
       <c r="G741" t="n">
-        <v>22.965841293335</v>
+        <v>22.9658432006836</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G742" t="n">
-        <v>24.8105163574219</v>
+        <v>24.8105182647705</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>36.7564964294434</v>
       </c>
       <c r="G747" t="n">
-        <v>28.419319152832</v>
+        <v>28.4193210601807</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715572357178</v>
+        <v>27.8715534210205</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>33.3809013366699</v>
       </c>
       <c r="G750" t="n">
-        <v>25.8093852996826</v>
+        <v>25.809383392334</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>31.8285446166992</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6091346740723</v>
+        <v>24.6091365814209</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>32.9329071044922</v>
       </c>
       <c r="G755" t="n">
-        <v>25.463005065918</v>
+        <v>25.4630031585693</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G756" t="n">
-        <v>24.8105163574219</v>
+        <v>24.8105182647705</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983108520508</v>
+        <v>24.1983089447021</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>31.2451076507568</v>
       </c>
       <c r="G760" t="n">
-        <v>24.1580333709717</v>
+        <v>24.1580352783203</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G764" t="n">
-        <v>24.6494121551514</v>
+        <v>24.6494102478027</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399719238281</v>
+        <v>24.4399738311768</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G767" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>31.6618461608887</v>
       </c>
       <c r="G769" t="n">
-        <v>24.4802494049072</v>
+        <v>24.4802474975586</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>31.8181247711182</v>
       </c>
       <c r="G770" t="n">
-        <v>24.6010780334473</v>
+        <v>24.6010799407959</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>31.4013843536377</v>
       </c>
       <c r="G771" t="n">
-        <v>24.2788639068604</v>
+        <v>24.278865814209</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G773" t="n">
-        <v>20.13840675354</v>
+        <v>20.1384086608887</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>25.5774383544922</v>
       </c>
       <c r="G776" t="n">
-        <v>19.7759170532227</v>
+        <v>19.775915145874</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>25.4107418060303</v>
       </c>
       <c r="G777" t="n">
-        <v>19.647029876709</v>
+        <v>19.6470317840576</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>25.5461826324463</v>
       </c>
       <c r="G779" t="n">
-        <v>19.7517490386963</v>
+        <v>19.7517509460449</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>25.598274230957</v>
       </c>
       <c r="G780" t="n">
-        <v>19.792028427124</v>
+        <v>19.7920265197754</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>25.8795757293701</v>
       </c>
       <c r="G781" t="n">
-        <v>20.009521484375</v>
+        <v>20.0095233917236</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189598083496</v>
+        <v>20.2189617156982</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>24.9523277282715</v>
       </c>
       <c r="G787" t="n">
-        <v>19.2925930023193</v>
+        <v>19.292594909668</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>25.7962265014648</v>
       </c>
       <c r="G789" t="n">
-        <v>19.9450778961182</v>
+        <v>19.9450798034668</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G794" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.7653255462646</v>
       </c>
       <c r="G795" t="n">
-        <v>21.4675445556641</v>
+        <v>21.4675426483154</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083866119385</v>
+        <v>21.0083885192871</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G799" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>28.3695983886719</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9347534179688</v>
+        <v>21.9347553253174</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>28.213321685791</v>
       </c>
       <c r="G809" t="n">
-        <v>21.8139247894287</v>
+        <v>21.8139228820801</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G811" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G814" t="n">
-        <v>20.2109069824219</v>
+        <v>20.2109050750732</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>26.4109191894531</v>
       </c>
       <c r="G816" t="n">
-        <v>20.4203453063965</v>
+        <v>20.4203472137451</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908916473389</v>
+        <v>20.7908935546875</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G819" t="n">
-        <v>21.4917106628418</v>
+        <v>21.4917087554932</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G820" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5009002685547</v>
+        <v>20.5008983612061</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G823" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>25.9837608337402</v>
       </c>
       <c r="G824" t="n">
-        <v>20.0900764465332</v>
+        <v>20.0900783538818</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G825" t="n">
-        <v>20.13840675354</v>
+        <v>20.1384086608887</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G828" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G829" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G830" t="n">
-        <v>20.4284000396729</v>
+        <v>20.4284019470215</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G832" t="n">
-        <v>20.4284000396729</v>
+        <v>20.4284019470215</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>26.3171520233154</v>
       </c>
       <c r="G833" t="n">
-        <v>20.3478469848633</v>
+        <v>20.3478450775146</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G834" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G839" t="n">
-        <v>22.4583549499512</v>
+        <v>22.4583530426025</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G841" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>27.671558380127</v>
       </c>
       <c r="G842" t="n">
-        <v>21.3950462341309</v>
+        <v>21.3950443267822</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G843" t="n">
-        <v>21.1856060028076</v>
+        <v>21.185604095459</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.3800163269043</v>
       </c>
       <c r="G848" t="n">
-        <v>21.9428100585938</v>
+        <v>21.9428081512451</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150577545166</v>
+        <v>20.8150615692139</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.4003238677979</v>
       </c>
       <c r="G852" t="n">
-        <v>19.6389770507812</v>
+        <v>19.6389751434326</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G856" t="n">
-        <v>18.6723308563232</v>
+        <v>18.6723327636719</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G861" t="n">
-        <v>18.124568939209</v>
+        <v>18.1245670318604</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G863" t="n">
-        <v>17.8667964935303</v>
+        <v>17.8667945861816</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G864" t="n">
-        <v>17.770133972168</v>
+        <v>17.7701320648193</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G866" t="n">
-        <v>17.1418113708496</v>
+        <v>17.1418132781982</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>21.8580303192139</v>
       </c>
       <c r="G867" t="n">
-        <v>16.9001522064209</v>
+        <v>16.9001502990723</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>21.7538452148438</v>
       </c>
       <c r="G868" t="n">
-        <v>16.8195972442627</v>
+        <v>16.8195991516113</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>21.6079864501953</v>
       </c>
       <c r="G870" t="n">
-        <v>16.7068252563477</v>
+        <v>16.706823348999</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>21.1704082489014</v>
       </c>
       <c r="G871" t="n">
-        <v>16.3684959411621</v>
+        <v>16.3684978485107</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>20.9828758239746</v>
       </c>
       <c r="G872" t="n">
-        <v>16.223503112793</v>
+        <v>16.2235012054443</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>21.0662231445312</v>
       </c>
       <c r="G878" t="n">
-        <v>16.2879447937012</v>
+        <v>16.2879428863525</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.1107273101807</v>
+        <v>16.110725402832</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290393829346</v>
+        <v>17.0290374755859</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>22.4623031616211</v>
       </c>
       <c r="G888" t="n">
-        <v>17.3673610687256</v>
+        <v>17.3673629760742</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406764984131</v>
+        <v>18.1406784057617</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G891" t="n">
-        <v>19.1878757476807</v>
+        <v>19.187873840332</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493431091309</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>34.4435882568359</v>
       </c>
       <c r="G900" t="n">
-        <v>26.631031036377</v>
+        <v>26.6310291290283</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G901" t="n">
-        <v>26.1154880523682</v>
+        <v>26.1154899597168</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>33.4642486572266</v>
       </c>
       <c r="G902" t="n">
-        <v>25.8738269805908</v>
+        <v>25.8738250732422</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G906" t="n">
-        <v>23.8922061920166</v>
+        <v>23.8922080993652</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>29.4427051544189</v>
       </c>
       <c r="G909" t="n">
-        <v>22.7644557952881</v>
+        <v>22.7644577026367</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G910" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>27.1923065185547</v>
       </c>
       <c r="G913" t="n">
-        <v>21.0244979858398</v>
+        <v>21.0244960784912</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G917" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.7752132415771</v>
       </c>
       <c r="G918" t="n">
-        <v>19.1556549072266</v>
+        <v>19.1556529998779</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>25.0877685546875</v>
       </c>
       <c r="G919" t="n">
-        <v>19.3973140716553</v>
+        <v>19.3973159790039</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>26.9005889892578</v>
       </c>
       <c r="G920" t="n">
-        <v>20.7989482879639</v>
+        <v>20.7989463806152</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G921" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.6850395202637</v>
+        <v>21.685037612915</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>30.2136745452881</v>
       </c>
       <c r="G932" t="n">
-        <v>23.3605537414551</v>
+        <v>23.3605518341064</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.583833694458</v>
+        <v>25.5838356018066</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516109466553</v>
+        <v>25.5516128540039</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>33.4850845336914</v>
       </c>
       <c r="G939" t="n">
-        <v>25.8899345397949</v>
+        <v>25.8899364471436</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>34.0268478393555</v>
       </c>
       <c r="G942" t="n">
-        <v>26.30881690979</v>
+        <v>26.3088150024414</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G944" t="n">
-        <v>26.1154880523682</v>
+        <v>26.1154899597168</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>33.7976417541504</v>
       </c>
       <c r="G945" t="n">
-        <v>26.1315994262695</v>
+        <v>26.1315975189209</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G948" t="n">
-        <v>25.0360717773438</v>
+        <v>25.0360698699951</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G949" t="n">
-        <v>25.1327342987061</v>
+        <v>25.1327362060547</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G950" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G951" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G953" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>30.3178596496582</v>
       </c>
       <c r="G955" t="n">
-        <v>23.4411067962646</v>
+        <v>23.4411087036133</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5262298583984</v>
       </c>
       <c r="G956" t="n">
-        <v>23.6022129058838</v>
+        <v>23.6022148132324</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727630615234</v>
+        <v>23.9727592468262</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5887413024902</v>
       </c>
       <c r="G961" t="n">
-        <v>23.6505470275879</v>
+        <v>23.6505451202393</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G962" t="n">
-        <v>23.8922061920166</v>
+        <v>23.8922080993652</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>30.8596210479736</v>
       </c>
       <c r="G964" t="n">
-        <v>23.8599834442139</v>
+        <v>23.8599853515625</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>31.3388748168945</v>
       </c>
       <c r="G965" t="n">
-        <v>24.2305355072021</v>
+        <v>24.2305335998535</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>31.9431476593018</v>
       </c>
       <c r="G968" t="n">
-        <v>24.6977443695068</v>
+        <v>24.6977424621582</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G972" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G973" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.3122215270996</v>
+        <v>23.312219619751</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>31.2346897125244</v>
       </c>
       <c r="G978" t="n">
-        <v>24.1499805450439</v>
+        <v>24.1499786376953</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G980" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G983" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>30.7971115112305</v>
       </c>
       <c r="G986" t="n">
-        <v>23.8116550445557</v>
+        <v>23.811653137207</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G988" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G993" t="n">
-        <v>23.5861034393311</v>
+        <v>23.5861015319824</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727630615234</v>
+        <v>23.9727592468262</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G996" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544509887695</v>
+        <v>23.0544490814209</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G999" t="n">
-        <v>22.7483463287354</v>
+        <v>22.7483444213867</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1001" t="n">
-        <v>22.5227966308594</v>
+        <v>22.5227947235107</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1002" t="n">
-        <v>22.635570526123</v>
+        <v>22.6355686187744</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1003" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1006" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1007" t="n">
-        <v>22.7966766357422</v>
+        <v>22.7966785430908</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>29.2968463897705</v>
       </c>
       <c r="G1008" t="n">
-        <v>22.6516819000244</v>
+        <v>22.651683807373</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1010" t="n">
-        <v>21.9911403656006</v>
+        <v>21.9911422729492</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1013" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1014" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1015" t="n">
-        <v>22.5227966308594</v>
+        <v>22.5227947235107</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G1016" t="n">
-        <v>22.7483463287354</v>
+        <v>22.7483444213867</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G1017" t="n">
-        <v>22.4583549499512</v>
+        <v>22.4583530426025</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1020" t="n">
-        <v>22.7966766357422</v>
+        <v>22.7966785430908</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.71044921875</v>
+        <v>27.7104473114014</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493431091309</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1026" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>39.069408416748</v>
       </c>
       <c r="G1029" t="n">
-        <v>30.2076148986816</v>
+        <v>30.2076110839844</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>38.9652214050293</v>
       </c>
       <c r="G1030" t="n">
-        <v>30.1270580291748</v>
+        <v>30.1270599365234</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>37.9650459289551</v>
       </c>
       <c r="G1031" t="n">
-        <v>29.3537425994873</v>
+        <v>29.3537464141846</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.6276245117188</v>
+        <v>29.627628326416</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>37.73583984375</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1765270233154</v>
+        <v>29.1765289306641</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326633453369</v>
+        <v>28.0326614379883</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1037" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1038" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>37.2774238586426</v>
       </c>
       <c r="G1039" t="n">
-        <v>28.8220901489258</v>
+        <v>28.8220882415771</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>37.9233703613281</v>
       </c>
       <c r="G1041" t="n">
-        <v>29.3215217590332</v>
+        <v>29.3215198516846</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>36.1105499267578</v>
       </c>
       <c r="G1043" t="n">
-        <v>27.9198894500732</v>
+        <v>27.9198875427246</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737598419189</v>
+        <v>28.7737560272217</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>37.5274696350098</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.0154190063477</v>
+        <v>29.0154209136963</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>39.4444732666016</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.4976062774658</v>
+        <v>30.4976043701172</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936370849609</v>
+        <v>33.9936332702637</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770263671875</v>
+        <v>31.5770225524902</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>36.1313896179199</v>
       </c>
       <c r="G1058" t="n">
-        <v>27.9360027313232</v>
+        <v>27.9360008239746</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571491241455</v>
+        <v>26.3571472167969</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610511779785</v>
+        <v>25.7610492706299</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>24.6085166931152</v>
       </c>
       <c r="G1064" t="n">
-        <v>19.0267677307129</v>
+        <v>19.0267696380615</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>20.8578548431396</v>
       </c>
       <c r="G1066" t="n">
-        <v>16.126838684082</v>
+        <v>16.1268367767334</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.0453872680664</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.2718334197998</v>
+        <v>16.2718353271484</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3787784576416</v>
       </c>
       <c r="G1071" t="n">
-        <v>16.5296058654785</v>
+        <v>16.5296039581299</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1073" t="n">
-        <v>16.5618267059326</v>
+        <v>16.561824798584</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.8023548126221</v>
+        <v>17.8023529052734</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1078" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1079" t="n">
-        <v>18.2534523010254</v>
+        <v>18.253454208374</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>23.6708507537842</v>
       </c>
       <c r="G1081" t="n">
-        <v>18.3017845153809</v>
+        <v>18.3017864227295</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>24.5251693725586</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.9623260498047</v>
+        <v>18.9623241424561</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1094" t="n">
-        <v>17.6734676361084</v>
+        <v>17.6734657287598</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1096" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.124568939209</v>
+        <v>18.1245670318604</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1100" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1104" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1105" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G1106" t="n">
-        <v>17.770133972168</v>
+        <v>17.7701320648193</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1108" t="n">
-        <v>17.9634609222412</v>
+        <v>17.9634590148926</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G1110" t="n">
-        <v>17.8667964935303</v>
+        <v>17.8667945861816</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.5618267059326</v>
+        <v>16.561824798584</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>21.3371047973633</v>
       </c>
       <c r="G1114" t="n">
-        <v>16.4973831176758</v>
+        <v>16.4973850250244</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G1119" t="n">
-        <v>21.1856060028076</v>
+        <v>21.185604095459</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.635570526123</v>
+        <v>22.6355686187744</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G1124" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G1125" t="n">
-        <v>25.0360717773438</v>
+        <v>25.0360698699951</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1129" t="n">
-        <v>22.861120223999</v>
+        <v>22.8611183166504</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>29.2134971618652</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.5872383117676</v>
+        <v>22.5872364044189</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>31.0263175964355</v>
       </c>
       <c r="G1133" t="n">
-        <v>23.9888706207275</v>
+        <v>23.9888725280762</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021438598633</v>
+        <v>26.5021476745605</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.0349349975586</v>
+        <v>26.03493309021</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>32.859977722168</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.4066162109375</v>
+        <v>25.4066181182861</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460765838623</v>
+        <v>24.7460746765137</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>32.8808135986328</v>
       </c>
       <c r="G1145" t="n">
-        <v>25.4227275848389</v>
+        <v>25.4227256774902</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>31.5889186859131</v>
       </c>
       <c r="G1147" t="n">
-        <v>24.4238624572754</v>
+        <v>24.4238605499268</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G1148" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G1149" t="n">
-        <v>25.1327342987061</v>
+        <v>25.1327362060547</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31.8597984313965</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.6332988739014</v>
+        <v>24.63330078125</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>37.5066299438477</v>
       </c>
       <c r="G1155" t="n">
-        <v>28.9993057250977</v>
+        <v>28.9993076324463</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>37.6524887084961</v>
       </c>
       <c r="G1156" t="n">
-        <v>29.1120834350586</v>
+        <v>29.11208152771</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>40.2154426574707</v>
       </c>
       <c r="G1157" t="n">
-        <v>31.0937023162842</v>
+        <v>31.0937042236328</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303955078125</v>
+        <v>30.0303936004639</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>36.4856185913086</v>
       </c>
       <c r="G1159" t="n">
-        <v>28.2098846435547</v>
+        <v>28.2098827362061</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>34.7353096008301</v>
       </c>
       <c r="G1161" t="n">
-        <v>26.8565807342529</v>
+        <v>26.8565826416016</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>33.4017372131348</v>
       </c>
       <c r="G1162" t="n">
-        <v>25.8254928588867</v>
+        <v>25.8254947662354</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G1163" t="n">
-        <v>24.6494121551514</v>
+        <v>24.6494102478027</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655197143555</v>
+        <v>24.6655235290527</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>32.4432373046875</v>
       </c>
       <c r="G1168" t="n">
-        <v>25.0844020843506</v>
+        <v>25.0844039916992</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>30.3386974334717</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.4572200775146</v>
+        <v>23.457218170166</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>31.2555255889893</v>
       </c>
       <c r="G1171" t="n">
-        <v>24.1660900115967</v>
+        <v>24.1660919189453</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>30.2970237731934</v>
       </c>
       <c r="G1178" t="n">
-        <v>23.4249973297119</v>
+        <v>23.4249954223633</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G1179" t="n">
-        <v>23.5861034393311</v>
+        <v>23.5861015319824</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.2316703796387</v>
+        <v>23.23166847229</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>30.6720886230469</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.7149887084961</v>
+        <v>23.7149906158447</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>29.9011192321777</v>
       </c>
       <c r="G1186" t="n">
-        <v>23.1188907623291</v>
+        <v>23.1188926696777</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.861120223999</v>
+        <v>22.8611183166504</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1195" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1198" t="n">
-        <v>21.9911403656006</v>
+        <v>21.9911422729492</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>28.0049514770508</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.6528167724609</v>
+        <v>21.6528186798096</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G1203" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>28.5258750915527</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.0555820465088</v>
+        <v>22.0555839538574</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>28.4008541107178</v>
       </c>
       <c r="G1205" t="n">
-        <v>21.9589195251465</v>
+        <v>21.9589214324951</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.4917106628418</v>
+        <v>21.4917087554932</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.2758312225342</v>
       </c>
       <c r="G1209" t="n">
-        <v>21.8622550964355</v>
+        <v>21.8622531890869</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.9842910766602</v>
       </c>
       <c r="G1211" t="n">
-        <v>22.4100208282471</v>
+        <v>22.4100189208984</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>27.7757434844971</v>
       </c>
       <c r="G1212" t="n">
-        <v>21.4755992889404</v>
+        <v>21.4755973815918</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1216" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>24.2334518432617</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.7367763519287</v>
+        <v>18.7367744445801</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1227" t="n">
-        <v>16.4651622772217</v>
+        <v>16.4651641845703</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.6584892272949</v>
+        <v>16.6584911346436</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>22.7748603820801</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.6090240478516</v>
+        <v>17.6090259552002</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1238" t="n">
-        <v>18.3662261962891</v>
+        <v>18.3662281036377</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1240" t="n">
-        <v>19.2684268951416</v>
+        <v>19.2684288024902</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1245" t="n">
-        <v>20.0417423248291</v>
+        <v>20.0417442321777</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G1246" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1256" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1258" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1259" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.4318046569824</v>
+        <v>17.4318065643311</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>21.962215423584</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.9807033538818</v>
+        <v>16.9807052612305</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>21.7330093383789</v>
       </c>
       <c r="G1270" t="n">
-        <v>16.80348777771</v>
+        <v>16.8034896850586</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6584892272949</v>
+        <v>16.6584911346436</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.6734676361084</v>
+        <v>17.6734657287598</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.3662261962891</v>
+        <v>18.3662281036377</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>22.3997936248779</v>
       </c>
       <c r="G1280" t="n">
-        <v>17.3190326690674</v>
+        <v>17.3190307617188</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.4318046569824</v>
+        <v>17.4318065643311</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>22.4414672851562</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.3512535095215</v>
+        <v>17.3512516021729</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1287" t="n">
-        <v>17.1901454925537</v>
+        <v>17.1901473999023</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1294" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.6723308563232</v>
+        <v>18.6723327636719</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>26.5255222320557</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.5089530944824</v>
+        <v>20.5089550018311</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.5895080566406</v>
+        <v>20.5895099639893</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.5895080566406</v>
+        <v>20.5895099639893</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>26.6088714599609</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5733985900879</v>
+        <v>20.5733966827393</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>25.9629230499268</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.0739650726318</v>
+        <v>20.0739631652832</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>25.0460948944092</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.3650932312012</v>
+        <v>19.3650951385498</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>25.504508972168</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.7195281982422</v>
+        <v>19.7195301055908</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395416259766</v>
+        <v>19.1395435333252</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1326" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>24.0250816345215</v>
       </c>
       <c r="G1329" t="n">
-        <v>18.5756702423096</v>
+        <v>18.5756683349609</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1330" t="n">
-        <v>18.5273342132568</v>
+        <v>18.5273361206055</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>23.8375473022461</v>
       </c>
       <c r="G1333" t="n">
-        <v>18.4306697845459</v>
+        <v>18.4306716918945</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153774261475</v>
+        <v>19.1153793334961</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353927612305</v>
+        <v>18.5353889465332</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1338" t="n">
-        <v>18.4870586395264</v>
+        <v>18.4870567321777</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>24.4418201446533</v>
       </c>
       <c r="G1343" t="n">
-        <v>18.8978824615479</v>
+        <v>18.8978805541992</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864921569824</v>
+        <v>18.9864902496338</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1345" t="n">
-        <v>18.5273342132568</v>
+        <v>18.5273361206055</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112247467041</v>
+        <v>18.5112228393555</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.5273342132568</v>
+        <v>18.5273361206055</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1350" t="n">
-        <v>18.5434474945068</v>
+        <v>18.5434455871582</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>23.5875034332275</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.2373428344727</v>
+        <v>18.237340927124</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187149047852</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.2684268951416</v>
+        <v>19.2684288024902</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>24.5043315887451</v>
       </c>
       <c r="G1360" t="n">
-        <v>18.9462127685547</v>
+        <v>18.9462146759033</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>24.806468963623</v>
       </c>
       <c r="G1364" t="n">
-        <v>19.1798210144043</v>
+        <v>19.1798191070557</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>26.4525928497314</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.4525661468506</v>
+        <v>20.4525680541992</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>25.8483200073242</v>
       </c>
       <c r="G1373" t="n">
-        <v>19.9853572845459</v>
+        <v>19.9853553771973</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G1378" t="n">
-        <v>20.2109069824219</v>
+        <v>20.2109050750732</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397922515869</v>
+        <v>20.3397941589355</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>26.2858963012695</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.3236808776855</v>
+        <v>20.3236789703369</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>25.8379001617432</v>
       </c>
       <c r="G1382" t="n">
-        <v>19.9772987365723</v>
+        <v>19.9773006439209</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.0417423248291</v>
+        <v>20.0417442321777</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598075866699</v>
+        <v>19.7598056793213</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>25.0565128326416</v>
       </c>
       <c r="G1386" t="n">
-        <v>19.3731498718262</v>
+        <v>19.3731479644775</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G1387" t="n">
-        <v>19.1878757476807</v>
+        <v>19.187873840332</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187149047852</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>24.2021942138672</v>
       </c>
       <c r="G1394" t="n">
-        <v>18.7126083374023</v>
+        <v>18.7126064300537</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1399" t="n">
-        <v>18.4870586395264</v>
+        <v>18.4870567321777</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>23.6187591552734</v>
       </c>
       <c r="G1400" t="n">
-        <v>18.2615089416504</v>
+        <v>18.2615070343018</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1401" t="n">
-        <v>18.108455657959</v>
+        <v>18.1084575653076</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>23.1707630157471</v>
       </c>
       <c r="G1402" t="n">
-        <v>17.9151268005371</v>
+        <v>17.9151287078857</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>23.472900390625</v>
       </c>
       <c r="G1404" t="n">
-        <v>18.1487350463867</v>
+        <v>18.1487331390381</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>21.9830532073975</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.9968185424805</v>
+        <v>16.9968166351318</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G1410" t="n">
-        <v>17.1418113708496</v>
+        <v>17.1418132781982</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>23.5562477111816</v>
       </c>
       <c r="G1415" t="n">
-        <v>18.2131767272949</v>
+        <v>18.2131748199463</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1417" t="n">
-        <v>18.2534523010254</v>
+        <v>18.253454208374</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1419" t="n">
-        <v>18.5434474945068</v>
+        <v>18.5434455871582</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.4103889465332</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.1004028320312</v>
+        <v>18.1004009246826</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>24.3897285461426</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.8576068878174</v>
+        <v>18.8576049804688</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>24.2230319976807</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.7287197113037</v>
+        <v>18.7287216186523</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>23.9208946228027</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.4951114654541</v>
+        <v>18.4951133728027</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1434" t="n">
-        <v>18.0923461914062</v>
+        <v>18.0923442840576</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1435" t="n">
-        <v>17.9634609222412</v>
+        <v>17.9634590148926</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>23.5354118347168</v>
       </c>
       <c r="G1436" t="n">
-        <v>18.1970653533936</v>
+        <v>18.1970672607422</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>23.2853660583496</v>
       </c>
       <c r="G1438" t="n">
-        <v>18.0037364959717</v>
+        <v>18.0037384033203</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1443" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1444" t="n">
-        <v>18.0923461914062</v>
+        <v>18.0923442840576</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>23.160343170166</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.9070701599121</v>
+        <v>17.9070720672607</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>23.3166217803955</v>
       </c>
       <c r="G1447" t="n">
-        <v>18.0279026031494</v>
+        <v>18.027904510498</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392948150635</v>
+        <v>17.9392929077148</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>23.0978336334229</v>
       </c>
       <c r="G1452" t="n">
-        <v>17.8587398529053</v>
+        <v>17.8587417602539</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1456" t="n">
-        <v>17.1901454925537</v>
+        <v>17.1901473999023</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1459" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>22.6706733703613</v>
       </c>
       <c r="G1464" t="n">
-        <v>17.5284690856934</v>
+        <v>17.528470993042</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.108455657959</v>
+        <v>18.1084575653076</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8023548126221</v>
+        <v>17.8023529052734</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>22.3789558410645</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.3029193878174</v>
+        <v>17.302921295166</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>22.1289119720459</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.1095905303955</v>
+        <v>17.1095924377441</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>21.3475246429443</v>
       </c>
       <c r="G1485" t="n">
-        <v>16.5054378509521</v>
+        <v>16.5054397583008</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>21.0766429901123</v>
       </c>
       <c r="G1486" t="n">
-        <v>16.2959995269775</v>
+        <v>16.2960014343262</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1487" t="n">
-        <v>16.4651622772217</v>
+        <v>16.4651641845703</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>20.2244091033936</v>
       </c>
       <c r="G1497" t="n">
-        <v>15.6370716094971</v>
+        <v>15.6370706558228</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.3367519378662</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.9507541656494</v>
+        <v>14.9507551193237</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9325141906738</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.6382083892822</v>
+        <v>14.6382064819336</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867668151855</v>
+        <v>14.4867658615112</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.2934370040894</v>
+        <v>14.2934350967407</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.690803527832</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.4513206481934</v>
+        <v>14.4513216018677</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379793167114</v>
+        <v>14.8379802703857</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.6543169021606</v>
+        <v>14.6543159484863</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>19.1658878326416</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8186464309692</v>
+        <v>14.8186454772949</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>19.2950782775879</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.9185333251953</v>
+        <v>14.918532371521</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>19.3200817108154</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.9378662109375</v>
+        <v>14.9378652572632</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.625316619873</v>
+        <v>14.6253175735474</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189876556396</v>
+        <v>14.5189867019653</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>18.5866184234619</v>
       </c>
       <c r="G1526" t="n">
-        <v>14.3707666397095</v>
+        <v>14.3707675933838</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>18.9200115203857</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.6285400390625</v>
+        <v>14.6285409927368</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>19.307580947876</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.9281997680664</v>
+        <v>14.9282007217407</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>19.1075439453125</v>
       </c>
       <c r="G1532" t="n">
-        <v>14.7735357284546</v>
+        <v>14.7735347747803</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024209976196</v>
+        <v>14.9024229049683</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>19.2867431640625</v>
       </c>
       <c r="G1534" t="n">
-        <v>14.9120874404907</v>
+        <v>14.912088394165</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316465377808</v>
+        <v>14.7316474914551</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>18.8116588592529</v>
       </c>
       <c r="G1536" t="n">
-        <v>14.5447635650635</v>
+        <v>14.5447645187378</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154249191284</v>
+        <v>14.8154239654541</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>18.9658527374268</v>
       </c>
       <c r="G1538" t="n">
-        <v>14.6639833450317</v>
+        <v>14.6639842987061</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>18.9116764068604</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.6220941543579</v>
+        <v>14.6220960617065</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>18.9241790771484</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.6317625045776</v>
+        <v>14.6317615509033</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1542" t="n">
-        <v>14.0002222061157</v>
+        <v>14.0002212524414</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.3365745544434</v>
       </c>
       <c r="G1543" t="n">
-        <v>14.1774387359619</v>
+        <v>14.1774396896362</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>18.5241088867188</v>
       </c>
       <c r="G1544" t="n">
-        <v>14.3224363327026</v>
+        <v>14.3224353790283</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>18.8283271789551</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.5576505661011</v>
+        <v>14.5576515197754</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994256973267</v>
+        <v>14.699426651001</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.1950607299805</v>
       </c>
       <c r="G1548" t="n">
-        <v>14.8412017822266</v>
+        <v>14.8412008285522</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5867958068848</v>
       </c>
       <c r="G1549" t="n">
-        <v>15.1440811157227</v>
+        <v>15.1440830230713</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>19.7618274688721</v>
       </c>
       <c r="G1550" t="n">
-        <v>15.2794141769409</v>
+        <v>15.2794122695923</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024209976196</v>
+        <v>14.9024229049683</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>19.3784255981445</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.9829750061035</v>
+        <v>14.9829759597778</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>20.6703205108643</v>
       </c>
       <c r="G1553" t="n">
-        <v>15.981840133667</v>
+        <v>15.9818410873413</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.643515586853</v>
+        <v>15.6435146331787</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>21.6496601104736</v>
       </c>
       <c r="G1558" t="n">
-        <v>16.7390460968018</v>
+        <v>16.7390441894531</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>20.6244792938232</v>
       </c>
       <c r="G1559" t="n">
-        <v>15.9463977813721</v>
+        <v>15.9463987350464</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>19.5784606933594</v>
       </c>
       <c r="G1561" t="n">
-        <v>15.1376390457153</v>
+        <v>15.137638092041</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.1325492858887</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.7928705215454</v>
+        <v>14.7928686141968</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.36545753479</v>
+        <v>13.3654584884644</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.88649559021</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.8294486999512</v>
+        <v>13.8294477462769</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781202316284</v>
+        <v>13.5781192779541</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>15.940318107605</v>
       </c>
       <c r="G1571" t="n">
-        <v>12.3247060775757</v>
+        <v>12.3247051239014</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.9196586608887</v>
       </c>
       <c r="G1572" t="n">
-        <v>13.0819110870361</v>
+        <v>13.0819101333618</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.807315826416</v>
       </c>
       <c r="G1574" t="n">
-        <v>13.7682285308838</v>
+        <v>13.7682275772095</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>18.1865482330322</v>
       </c>
       <c r="G1576" t="n">
-        <v>14.0614423751831</v>
+        <v>14.0614414215088</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151977539062</v>
+        <v>15.0151968002319</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>20.2119064331055</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.627405166626</v>
+        <v>15.6274042129517</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>20.3661003112793</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.7466239929199</v>
+        <v>15.7466249465942</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1583" t="n">
-        <v>15.9496192932129</v>
+        <v>15.9496183395386</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.9496192932129</v>
+        <v>15.9496183395386</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>20.1077213287354</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.5468511581421</v>
+        <v>15.5468521118164</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>20.0952186584473</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.537184715271</v>
+        <v>15.5371837615967</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>20.1202239990234</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.5565195083618</v>
+        <v>15.5565176010132</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8303985595703</v>
+        <v>15.8303995132446</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>19.9493598937988</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.424409866333</v>
+        <v>15.4244089126587</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.069974899292</v>
+        <v>15.0699739456177</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199159622192</v>
+        <v>15.1199169158936</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>18.9616851806641</v>
       </c>
       <c r="G1592" t="n">
-        <v>14.6607608795166</v>
+        <v>14.6607599258423</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>18.6178741455078</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.3949346542358</v>
+        <v>14.3949337005615</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>18.024019241333</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.9357786178589</v>
+        <v>13.9357767105103</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.0002222061157</v>
+        <v>14.0002212524414</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>18.1177864074707</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0082769393921</v>
+        <v>14.0082778930664</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585582733154</v>
+        <v>13.7585601806641</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>17.8469047546387</v>
       </c>
       <c r="G1600" t="n">
-        <v>13.7988367080688</v>
+        <v>13.7988357543945</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>17.9719276428223</v>
       </c>
       <c r="G1602" t="n">
-        <v>13.8955011367798</v>
+        <v>13.8955030441284</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>17.8469047546387</v>
       </c>
       <c r="G1604" t="n">
-        <v>13.7988367080688</v>
+        <v>13.7988357543945</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>18.3678302764893</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.2016048431396</v>
+        <v>14.201605796814</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1609" t="n">
-        <v>12.9691362380981</v>
+        <v>12.9691352844238</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1610" t="n">
-        <v>12.9691362380981</v>
+        <v>12.9691352844238</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>15.8986444473267</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.2924852371216</v>
+        <v>12.2924842834473</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.390284538269</v>
+        <v>11.3902835845947</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>14.6484231948853</v>
       </c>
       <c r="G1619" t="n">
-        <v>11.3258409500122</v>
+        <v>11.3258419036865</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.390284538269</v>
+        <v>11.3902835845947</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433349609375</v>
+        <v>11.5433340072632</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>15.0130710601807</v>
       </c>
       <c r="G1625" t="n">
-        <v>11.6077785491943</v>
+        <v>11.6077795028687</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>15.5131587982178</v>
       </c>
       <c r="G1626" t="n">
-        <v>11.9944353103638</v>
+        <v>11.9944362640381</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>15.5235767364502</v>
       </c>
       <c r="G1629" t="n">
-        <v>12.0024909973145</v>
+        <v>12.0024900436401</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.1903629302979</v>
       </c>
       <c r="G1630" t="n">
-        <v>12.5180358886719</v>
+        <v>12.5180349349976</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.0445022583008</v>
       </c>
       <c r="G1631" t="n">
-        <v>12.4052581787109</v>
+        <v>12.4052591323853</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.0236663818359</v>
       </c>
       <c r="G1632" t="n">
-        <v>12.3891487121582</v>
+        <v>12.3891496658325</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>16.429988861084</v>
       </c>
       <c r="G1634" t="n">
-        <v>12.7033081054688</v>
+        <v>12.7033090591431</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805255889893</v>
+        <v>12.8805246353149</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>16.2632923126221</v>
       </c>
       <c r="G1637" t="n">
-        <v>12.5744228363037</v>
+        <v>12.5744218826294</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.7213516235352</v>
       </c>
       <c r="G1640" t="n">
-        <v>11.3822269439697</v>
+        <v>11.382227897644</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>14.7734451293945</v>
       </c>
       <c r="G1642" t="n">
-        <v>11.4225063323975</v>
+        <v>11.4225053787231</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>14.5650749206543</v>
       </c>
       <c r="G1643" t="n">
-        <v>11.2613983154297</v>
+        <v>11.2613973617554</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439033508301</v>
+        <v>11.0439023971558</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>14.0441493988037</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.8586301803589</v>
+        <v>10.8586292266846</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>11.6166372299194</v>
       </c>
       <c r="G1652" t="n">
-        <v>8.98173046112061</v>
+        <v>8.98172950744629</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>11.2728261947632</v>
       </c>
       <c r="G1653" t="n">
-        <v>8.71590232849121</v>
+        <v>8.71590328216553</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>9.64753913879395</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.45926666259766</v>
+        <v>7.4592661857605</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>10.010103225708</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.73959350585938</v>
+        <v>7.73959255218506</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>11.1894779205322</v>
       </c>
       <c r="G1659" t="n">
-        <v>8.65145969390869</v>
+        <v>8.65146064758301</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>10.5331115722656</v>
       </c>
       <c r="G1660" t="n">
-        <v>8.14397239685059</v>
+        <v>8.14397144317627</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392208099365</v>
+        <v>7.90392160415649</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971284866333</v>
+        <v>7.34971332550049</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>9.20162582397461</v>
       </c>
       <c r="G1665" t="n">
-        <v>7.11449575424194</v>
+        <v>7.11449670791626</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>9.54335308074951</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.37871170043945</v>
+        <v>7.37871217727661</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>9.3766565322876</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.2498254776001</v>
+        <v>7.24982595443726</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316871643066</v>
+        <v>6.86316919326782</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>8.75154685974121</v>
       </c>
       <c r="G1669" t="n">
-        <v>6.76650476455688</v>
+        <v>6.76650524139404</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795209884644</v>
+        <v>6.62795162200928</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>8.99325561523438</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.95338869094849</v>
+        <v>6.95338916778564</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>8.8223934173584</v>
       </c>
       <c r="G1676" t="n">
-        <v>6.82128190994263</v>
+        <v>6.82128143310547</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>9.01409339904785</v>
       </c>
       <c r="G1677" t="n">
-        <v>6.96950006484985</v>
+        <v>6.96950054168701</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927289962769</v>
+        <v>7.16927337646484</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>8.73487663269043</v>
       </c>
       <c r="G1680" t="n">
-        <v>6.7536153793335</v>
+        <v>6.75361585617065</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>8.95158195495605</v>
       </c>
       <c r="G1684" t="n">
-        <v>6.92116785049438</v>
+        <v>6.92116737365723</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>7.91806602478027</v>
       </c>
       <c r="G1689" t="n">
-        <v>6.12207555770874</v>
+        <v>6.1220760345459</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107583999634</v>
+        <v>6.15107488632202</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>7.97640991210938</v>
       </c>
       <c r="G1691" t="n">
-        <v>6.16718626022339</v>
+        <v>6.16718578338623</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>7.7680401802063</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.00607872009277</v>
+        <v>6.00607919692993</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032199859619</v>
+        <v>5.11032152175903</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>6.05523681640625</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.68177652359009</v>
+        <v>4.68177700042725</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>6.27194213867188</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.84932851791382</v>
+        <v>4.84932899475098</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.91699361801147</v>
+        <v>4.91699314117432</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.91699361801147</v>
+        <v>4.91699314117432</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>6.2302680015564</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.8171067237854</v>
+        <v>4.81710720062256</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>5.1717472076416</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.99868178367615</v>
+        <v>3.99868226051331</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.99671602249146</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.86335134506226</v>
+        <v>3.86335182189941</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.5533150434494</v>
+        <v>1.55331492424011</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089284896851</v>
+        <v>1.53089272975922</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>1.93019998073578</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.49238836765289</v>
+        <v>1.49238848686218</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.90980005264282</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.47661578655243</v>
+        <v>1.47661566734314</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.39945244789124</v>
+        <v>1.39945232868195</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>1.81560003757477</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.4037823677063</v>
+        <v>1.40378224849701</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.76339995861053</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.36342227458954</v>
+        <v>1.36342239379883</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>1.81239998340607</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.40130805969238</v>
+        <v>1.40130817890167</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.391566157341</v>
+        <v>1.39156603813171</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.41615307331085</v>
+        <v>1.41615319252014</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.80859994888306</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.39837002754211</v>
+        <v>1.39836990833282</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.88960003852844</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.46099746227264</v>
+        <v>1.46099758148193</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>1.88919997215271</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.46068823337555</v>
+        <v>1.46068811416626</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.5192950963974</v>
+        <v>1.51929497718811</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>1.87360000610352</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.4486266374588</v>
+        <v>1.44862651824951</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537937641144</v>
+        <v>1.44537925720215</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.94640004634857</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.50491392612457</v>
+        <v>1.50491404533386</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.45125532150269</v>
+        <v>1.45125544071198</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903860569</v>
+        <v>1.46903848648071</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.57689690589905</v>
+        <v>1.57689678668976</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.52161455154419</v>
+        <v>1.52161467075348</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.48805868625641</v>
+        <v>1.48805856704712</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.58501517772675</v>
+        <v>1.58501529693604</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.06299996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.59506642818451</v>
+        <v>1.5950665473938</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.98660004138947</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.53599572181702</v>
+        <v>1.53599584102631</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490931510925</v>
+        <v>1.71490919589996</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.70176517963409</v>
+        <v>1.7017650604248</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.65537452697754</v>
+        <v>1.65537440776825</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.60318493843079</v>
+        <v>1.6031848192215</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.65305483341217</v>
+        <v>1.65305495262146</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.10450005531311</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.62715339660645</v>
+        <v>1.62715351581573</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.6847550868988</v>
+        <v>1.68475520610809</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428663253784</v>
+        <v>1.89428651332855</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.87186431884766</v>
+        <v>1.87186419963837</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482697963715</v>
+        <v>1.92482709884644</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.37350010871887</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.83513855934143</v>
+        <v>1.83513844013214</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.84789597988129</v>
+        <v>1.847895860672</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.31550002098083</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.79029405117035</v>
+        <v>1.79029417037964</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.01026296615601</v>
+        <v>2.01026320457458</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.90201842784882</v>
+        <v>1.90201818943024</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552515506744</v>
+        <v>1.83552503585815</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.91052317619324</v>
+        <v>1.91052305698395</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.63949990272522</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.04080390930176</v>
+        <v>2.04080367088318</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.03809762001038</v>
+        <v>2.0380973815918</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.03384518623352</v>
+        <v>2.03384494781494</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.52349996566772</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.95111525058746</v>
+        <v>1.95111513137817</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.9066573381424</v>
+        <v>1.90665745735168</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.39050006866455</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.84828245639801</v>
+        <v>1.8482825756073</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.46099996566772</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.90279138088226</v>
+        <v>1.90279150009155</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428663253784</v>
+        <v>1.89428651332855</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305147171021</v>
+        <v>1.80305135250092</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.13649988174438</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.65189492702484</v>
+        <v>1.65189504623413</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.48805868625641</v>
+        <v>1.48805856704712</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.48450195789337</v>
+        <v>1.48450207710266</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46207988262177</v>
+        <v>1.46208000183105</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.99520003795624</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.54264497756958</v>
+        <v>1.54264509677887</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.49532651901245</v>
+        <v>1.49532663822174</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.91349995136261</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.47947633266449</v>
+        <v>1.47947645187378</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.99950003623962</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.54596972465515</v>
+        <v>1.54596984386444</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.58501517772675</v>
+        <v>1.58501529693604</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630146980286</v>
+        <v>1.68630158901215</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.61516916751862</v>
+        <v>1.61516928672791</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.58037602901459</v>
+        <v>1.58037614822388</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.67315757274628</v>
+        <v>1.67315769195557</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.6283130645752</v>
+        <v>1.62831330299377</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.64686965942383</v>
+        <v>1.64686954021454</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.68939435482025</v>
+        <v>1.68939423561096</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.65537452697754</v>
+        <v>1.65537440776825</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.77444386482239</v>
+        <v>1.77444410324097</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.6484158039093</v>
+        <v>1.64841592311859</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.59738612174988</v>
+        <v>1.59738600254059</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.62985956668854</v>
+        <v>1.62985968589783</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.73037254810333</v>
+        <v>1.73037266731262</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.7582072019577</v>
+        <v>1.75820708274841</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011629581451</v>
+        <v>1.68011617660522</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65769410133362</v>
+        <v>1.65769398212433</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.68552851676941</v>
+        <v>1.68552839756012</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.76593887805939</v>
+        <v>1.76593899726868</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.76748526096344</v>
+        <v>1.76748538017273</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.32100009918213</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.7945464849472</v>
+        <v>1.79454660415649</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82702016830444</v>
+        <v>1.82701992988586</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.79068064689636</v>
+        <v>1.79068052768707</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645545959473</v>
+        <v>1.71645569801331</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.77367055416107</v>
+        <v>1.77367067337036</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.77985620498657</v>
+        <v>1.77985608577728</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.77444386482239</v>
+        <v>1.77444410324097</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>2.30699992179871</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.78372192382812</v>
+        <v>1.78372204303741</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.77057802677155</v>
+        <v>1.77057790756226</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.80150508880615</v>
+        <v>1.80150496959686</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985260486603</v>
+        <v>1.92985272407532</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309924125671</v>
+        <v>1.963099360466</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.96000671386719</v>
+        <v>1.9600065946579</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.97624337673187</v>
+        <v>1.97624325752258</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.97160422801971</v>
+        <v>1.97160446643829</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.95923340320587</v>
+        <v>1.95923328399658</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382106304169</v>
+        <v>1.95382130146027</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.97160422801971</v>
+        <v>1.97160446643829</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918215274811</v>
+        <v>1.94918203353882</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>2.61700010299683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.02340745925903</v>
+        <v>2.02340722084045</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.96077990531921</v>
+        <v>1.96077978610992</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.90356469154358</v>
+        <v>1.90356457233429</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.9097501039505</v>
+        <v>1.90974998474121</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.03191208839417</v>
+        <v>2.03191232681274</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025972366333</v>
+        <v>2.16025996208191</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.02263379096985</v>
+        <v>2.02263402938843</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.97624337673187</v>
+        <v>1.97624325752258</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309924125671</v>
+        <v>1.963099360466</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.9940265417099</v>
+        <v>1.99402642250061</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.98088252544403</v>
+        <v>1.98088228702545</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.96000671386719</v>
+        <v>1.9600065946579</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.90511095523834</v>
+        <v>1.90511107444763</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763925075531</v>
+        <v>1.7976393699646</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.74970209598541</v>
+        <v>1.7497022151947</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310284137726</v>
+        <v>1.81310272216797</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645221710205</v>
+        <v>1.86645209789276</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.9267600774765</v>
+        <v>1.92676019668579</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.10768389701843</v>
+        <v>2.10768365859985</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.73900008201599</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.1177351474762</v>
+        <v>2.11773490905762</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866917133331</v>
+        <v>1.84866905212402</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.86181282997131</v>
+        <v>1.8618129491806</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.8672251701355</v>
+        <v>1.86722528934479</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737904071808</v>
+        <v>1.89737927913666</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.91748178005219</v>
+        <v>1.91748189926147</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639748573303</v>
+        <v>2.00639724731445</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.96077990531921</v>
+        <v>1.96077978610992</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>2.60899996757507</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.01722192764282</v>
+        <v>2.01722168922424</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.89119386672974</v>
+        <v>1.89119374752045</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.98552143573761</v>
+        <v>1.98552167415619</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397529125214</v>
+        <v>1.98397517204285</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.95614063739777</v>
+        <v>1.95614075660706</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.91052317619324</v>
+        <v>1.91052305698395</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.83475160598755</v>
+        <v>1.83475172519684</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.85949349403381</v>
+        <v>1.85949337482452</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.85408115386963</v>
+        <v>1.85408139228821</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.81155633926392</v>
+        <v>1.81155622005463</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.85872042179108</v>
+        <v>1.85872030258179</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>2.42899990081787</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.87804973125458</v>
+        <v>1.87804961204529</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062567710876</v>
+        <v>1.93062579631805</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237777709961</v>
+        <v>1.97237765789032</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866545200348</v>
+        <v>1.99866557121277</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1999" t="n">
-        <v>2.03191208839417</v>
+        <v>2.03191232681274</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>3.06100010871887</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.36669850349426</v>
+        <v>2.36669826507568</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G2007" t="n">
-        <v>2.35973978042603</v>
+        <v>2.3597400188446</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>2.92899990081787</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.26463890075684</v>
+        <v>2.26463866233826</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.42777943611145</v>
+        <v>2.42777967453003</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921959877014</v>
+        <v>2.55921983718872</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.53447818756104</v>
+        <v>2.53447794914246</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.35742020606995</v>
+        <v>2.35742044448853</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061547279358</v>
+        <v>2.38061571121216</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.36437892913818</v>
+        <v>2.3643786907196</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.35046172142029</v>
+        <v>2.35046148300171</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>3.11899995803833</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.41154289245605</v>
+        <v>2.41154265403748</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.3875744342804</v>
+        <v>2.38757419586182</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.35510087013245</v>
+        <v>2.35510063171387</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334252357483</v>
+        <v>2.61334204673767</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597284317017</v>
+        <v>2.52597308158875</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.52519989013672</v>
+        <v>2.5252001285553</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710874557495</v>
+        <v>2.44710898399353</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.49891185760498</v>
+        <v>2.49891209602356</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.4965922832489</v>
+        <v>2.49659252166748</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>3.38899993896484</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.62030053138733</v>
+        <v>2.62030076980591</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.59169340133667</v>
+        <v>2.59169316291809</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>3.19099998474121</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.46721148490906</v>
+        <v>2.46721172332764</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.53602433204651</v>
+        <v>2.53602457046509</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983903884888</v>
+        <v>2.5298388004303</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>3.53900003433228</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.73627781867981</v>
+        <v>2.73627758026123</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.74323606491089</v>
+        <v>2.74323630332947</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>3.6489999294281</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.82132697105408</v>
+        <v>2.82132720947266</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.75019454956055</v>
+        <v>2.75019478797913</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.83137822151184</v>
+        <v>2.83137845993042</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.89245939254761</v>
+        <v>2.89245963096619</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.88859367370605</v>
+        <v>2.88859343528748</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2078" t="n">
-        <v>2.89245939254761</v>
+        <v>2.89245963096619</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.04632210731506</v>
+        <v>3.04632186889648</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2087" t="n">
-        <v>3.14219641685486</v>
+        <v>3.14219617843628</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2088" t="n">
-        <v>3.17003035545349</v>
+        <v>3.17003059387207</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188471794128</v>
+        <v>3.23188447952271</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.36487126350403</v>
+        <v>3.36487150192261</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.21564793586731</v>
+        <v>3.21564769744873</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>4.20900011062622</v>
       </c>
       <c r="G2096" t="n">
-        <v>3.25430679321289</v>
+        <v>3.25430703163147</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>4.1710000038147</v>
       </c>
       <c r="G2101" t="n">
-        <v>3.22492599487305</v>
+        <v>3.22492623329163</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343110084534</v>
+        <v>3.23343133926392</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.15843272209167</v>
+        <v>3.15843296051025</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.07338333129883</v>
+        <v>3.07338309288025</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972237586975</v>
+        <v>3.10972261428833</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>4.16300010681152</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.21874094009399</v>
+        <v>3.21874070167542</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693458557129</v>
+        <v>3.31693434715271</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811153411865</v>
+        <v>3.69811129570007</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409506797791</v>
+        <v>3.51409482955933</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667065620422</v>
+        <v>3.5666708946228</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2124" t="n">
-        <v>3.6030101776123</v>
+        <v>3.60300993919373</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>4.64900016784668</v>
       </c>
       <c r="G2125" t="n">
-        <v>3.59450531005859</v>
+        <v>3.59450507164001</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.62002038955688</v>
+        <v>3.62002015113831</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G2129" t="n">
-        <v>3.76769733428955</v>
+        <v>3.76769709587097</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.9014573097229</v>
+        <v>3.90145707130432</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.98186755180359</v>
+        <v>3.98186731338501</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G2132" t="n">
-        <v>4.09320545196533</v>
+        <v>4.09320497512817</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>4.98099994659424</v>
       </c>
       <c r="G2134" t="n">
-        <v>4.04208087921143</v>
+        <v>4.04208040237427</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2141" t="n">
-        <v>3.99257922172546</v>
+        <v>3.99257898330688</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G2143" t="n">
-        <v>3.99907112121582</v>
+        <v>3.9990713596344</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2149" t="n">
-        <v>3.75724411010742</v>
+        <v>3.757244348526</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56269,7 +56269,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2150" t="n">
-        <v>3.78970408439636</v>
+        <v>3.78970456123352</v>
       </c>
       <c r="H2150" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G2151" t="n">
-        <v>3.6420111656189</v>
+        <v>3.64201140403748</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G2154" t="n">
-        <v>3.67771744728088</v>
+        <v>3.6777172088623</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>4.56699991226196</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.70611977577209</v>
+        <v>3.70611953735352</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2158" t="n">
-        <v>3.7499406337738</v>
+        <v>3.74994039535522</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56529,7 +56529,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2160" t="n">
-        <v>3.6030592918396</v>
+        <v>3.60305953025818</v>
       </c>
       <c r="H2160" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G2163" t="n">
-        <v>3.79700756072998</v>
+        <v>3.79700779914856</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56633,7 +56633,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2164" t="n">
-        <v>3.7499406337738</v>
+        <v>3.74994039535522</v>
       </c>
       <c r="H2164" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G2165" t="n">
-        <v>3.96417689323425</v>
+        <v>3.96417713165283</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G2167" t="n">
-        <v>3.9252245426178</v>
+        <v>3.92522478103638</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G2175" t="n">
-        <v>3.99501371383667</v>
+        <v>3.99501347541809</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.99420213699341</v>
+        <v>3.99420237541199</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2186" t="n">
-        <v>3.81404900550842</v>
+        <v>3.814049243927</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57231,7 +57231,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G2187" t="n">
-        <v>3.63470768928528</v>
+        <v>3.63470792770386</v>
       </c>
       <c r="H2187" t="s">
         <v>8</v>
@@ -57257,7 +57257,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G2188" t="n">
-        <v>3.52028608322144</v>
+        <v>3.52028632164001</v>
       </c>
       <c r="H2188" t="s">
         <v>8</v>
@@ -57335,7 +57335,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G2191" t="n">
-        <v>4.07859802246094</v>
+        <v>4.0785984992981</v>
       </c>
       <c r="H2191" t="s">
         <v>8</v>
@@ -57517,7 +57517,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2198" t="n">
-        <v>4.22629117965698</v>
+        <v>4.22629165649414</v>
       </c>
       <c r="H2198" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G2199" t="n">
-        <v>4.23440647125244</v>
+        <v>4.23440599441528</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G2202" t="n">
-        <v>4.24089813232422</v>
+        <v>4.24089765548706</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2203" t="n">
-        <v>4.24414396286011</v>
+        <v>4.24414443969727</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G2205" t="n">
-        <v>4.23278284072876</v>
+        <v>4.23278331756592</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G2207" t="n">
-        <v>4.21006107330322</v>
+        <v>4.21006155014038</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57829,7 +57829,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2210" t="n">
-        <v>4.09807395935059</v>
+        <v>4.09807443618774</v>
       </c>
       <c r="H2210" t="s">
         <v>8</v>
@@ -57855,7 +57855,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.98608756065369</v>
+        <v>3.98608732223511</v>
       </c>
       <c r="H2211" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.96904540061951</v>
+        <v>3.96904563903809</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -58037,7 +58037,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G2218" t="n">
-        <v>3.99582529067993</v>
+        <v>3.99582505226135</v>
       </c>
       <c r="H2218" t="s">
         <v>8</v>
@@ -58089,7 +58089,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2220" t="n">
-        <v>4.0558762550354</v>
+        <v>4.05587673187256</v>
       </c>
       <c r="H2220" t="s">
         <v>8</v>
@@ -58115,7 +58115,7 @@
         <v>4.97100019454956</v>
       </c>
       <c r="G2221" t="n">
-        <v>4.03396558761597</v>
+        <v>4.03396606445312</v>
       </c>
       <c r="H2221" t="s">
         <v>8</v>
@@ -58167,7 +58167,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G2223" t="n">
-        <v>4.06074571609497</v>
+        <v>4.06074523925781</v>
       </c>
       <c r="H2223" t="s">
         <v>8</v>
@@ -58271,7 +58271,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G2227" t="n">
-        <v>4.20519208908081</v>
+        <v>4.20519256591797</v>
       </c>
       <c r="H2227" t="s">
         <v>8</v>
@@ -58349,7 +58349,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.88870716094971</v>
+        <v>3.88870739936829</v>
       </c>
       <c r="H2230" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2232" t="n">
-        <v>4.0558762550354</v>
+        <v>4.05587673187256</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58427,7 +58427,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G2233" t="n">
-        <v>4.1532564163208</v>
+        <v>4.15325593948364</v>
       </c>
       <c r="H2233" t="s">
         <v>8</v>
@@ -58453,7 +58453,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G2234" t="n">
-        <v>4.16137075424194</v>
+        <v>4.1613712310791</v>
       </c>
       <c r="H2234" t="s">
         <v>8</v>
@@ -58557,7 +58557,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G2238" t="n">
-        <v>4.25712823867798</v>
+        <v>4.25712776184082</v>
       </c>
       <c r="H2238" t="s">
         <v>8</v>
@@ -58687,7 +58687,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G2243" t="n">
-        <v>4.2587513923645</v>
+        <v>4.25875091552734</v>
       </c>
       <c r="H2243" t="s">
         <v>8</v>
@@ -58713,7 +58713,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G2244" t="n">
-        <v>4.12566566467285</v>
+        <v>4.12566518783569</v>
       </c>
       <c r="H2244" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G2246" t="n">
-        <v>4.09645080566406</v>
+        <v>4.09645128250122</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58817,7 +58817,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G2248" t="n">
-        <v>4.14838743209839</v>
+        <v>4.14838695526123</v>
       </c>
       <c r="H2248" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G2252" t="n">
-        <v>4.13702630996704</v>
+        <v>4.13702583312988</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58999,7 +58999,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2255" t="n">
-        <v>4.22629117965698</v>
+        <v>4.22629165649414</v>
       </c>
       <c r="H2255" t="s">
         <v>8</v>
@@ -59103,7 +59103,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G2259" t="n">
-        <v>4.47623252868652</v>
+        <v>4.47623300552368</v>
       </c>
       <c r="H2259" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>6.01800012588501</v>
       </c>
       <c r="G2261" t="n">
-        <v>4.88360643386841</v>
+        <v>4.88360595703125</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59285,7 +59285,7 @@
         <v>5.93200016021729</v>
       </c>
       <c r="G2266" t="n">
-        <v>4.81381750106812</v>
+        <v>4.81381702423096</v>
       </c>
       <c r="H2266" t="s">
         <v>8</v>
@@ -59545,7 +59545,7 @@
         <v>6.37200021743774</v>
       </c>
       <c r="G2276" t="n">
-        <v>5.17087745666504</v>
+        <v>5.17087697982788</v>
       </c>
       <c r="H2276" t="s">
         <v>8</v>
@@ -59571,7 +59571,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2277" t="n">
-        <v>5.1286792755127</v>
+        <v>5.12867879867554</v>
       </c>
       <c r="H2277" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>6.65199995040894</v>
       </c>
       <c r="G2288" t="n">
-        <v>5.39809703826904</v>
+        <v>5.39809656143188</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59909,7 +59909,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2290" t="n">
-        <v>5.44516372680664</v>
+        <v>5.4451642036438</v>
       </c>
       <c r="H2290" t="s">
         <v>8</v>
@@ -59961,7 +59961,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2292" t="n">
-        <v>5.52631425857544</v>
+        <v>5.52631378173828</v>
       </c>
       <c r="H2292" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2295" t="n">
-        <v>5.71133613586426</v>
+        <v>5.7113356590271</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60117,7 +60117,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2298" t="n">
-        <v>5.71133613586426</v>
+        <v>5.7113356590271</v>
       </c>
       <c r="H2298" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2299" t="n">
-        <v>5.7421727180481</v>
+        <v>5.74217319488525</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2300" t="n">
-        <v>5.7421727180481</v>
+        <v>5.74217319488525</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60195,7 +60195,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G2301" t="n">
-        <v>5.7194504737854</v>
+        <v>5.71945095062256</v>
       </c>
       <c r="H2301" t="s">
         <v>8</v>
@@ -60351,7 +60351,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G2307" t="n">
-        <v>5.16276168823242</v>
+        <v>5.16276216506958</v>
       </c>
       <c r="H2307" t="s">
         <v>8</v>
@@ -60429,7 +60429,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G2310" t="n">
-        <v>5.05402088165283</v>
+        <v>5.05402135848999</v>
       </c>
       <c r="H2310" t="s">
         <v>8</v>
@@ -60481,7 +60481,7 @@
         <v>6.30200004577637</v>
       </c>
       <c r="G2312" t="n">
-        <v>5.1140718460083</v>
+        <v>5.11407232284546</v>
       </c>
       <c r="H2312" t="s">
         <v>8</v>
@@ -60663,7 +60663,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2319" t="n">
-        <v>5.1286792755127</v>
+        <v>5.12867879867554</v>
       </c>
       <c r="H2319" t="s">
         <v>8</v>
@@ -60871,7 +60871,7 @@
         <v>6.60799980163574</v>
       </c>
       <c r="G2327" t="n">
-        <v>5.36239051818848</v>
+        <v>5.36239099502563</v>
       </c>
       <c r="H2327" t="s">
         <v>8</v>
@@ -60923,7 +60923,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G2329" t="n">
-        <v>5.69835138320923</v>
+        <v>5.69835186004639</v>
       </c>
       <c r="H2329" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G2330" t="n">
-        <v>5.69348239898682</v>
+        <v>5.69348287582397</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61001,7 +61001,7 @@
         <v>7.11800003051758</v>
       </c>
       <c r="G2332" t="n">
-        <v>5.77625608444214</v>
+        <v>5.77625560760498</v>
       </c>
       <c r="H2332" t="s">
         <v>8</v>
@@ -61131,7 +61131,7 @@
         <v>6.88800001144409</v>
       </c>
       <c r="G2337" t="n">
-        <v>5.5896110534668</v>
+        <v>5.58961057662964</v>
       </c>
       <c r="H2337" t="s">
         <v>8</v>
@@ -61209,7 +61209,7 @@
         <v>7.09600019454956</v>
       </c>
       <c r="G2340" t="n">
-        <v>5.75840282440186</v>
+        <v>5.75840330123901</v>
       </c>
       <c r="H2340" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2344" t="n">
-        <v>6.34592866897583</v>
+        <v>6.34592914581299</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61365,7 +61365,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G2346" t="n">
-        <v>6.17064523696899</v>
+        <v>6.17064476013184</v>
       </c>
       <c r="H2346" t="s">
         <v>8</v>
@@ -61703,7 +61703,7 @@
         <v>5.89300012588501</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.7821683883667</v>
+        <v>4.78216886520386</v>
       </c>
       <c r="H2359" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G2360" t="n">
-        <v>5.01019954681396</v>
+        <v>5.01020002365112</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61807,7 +61807,7 @@
         <v>6.67799997329712</v>
       </c>
       <c r="G2363" t="n">
-        <v>5.41919612884521</v>
+        <v>5.41919565200806</v>
       </c>
       <c r="H2363" t="s">
         <v>8</v>
@@ -61859,7 +61859,7 @@
         <v>6.53200006484985</v>
       </c>
       <c r="G2365" t="n">
-        <v>5.30071687698364</v>
+        <v>5.3007173538208</v>
       </c>
       <c r="H2365" t="s">
         <v>8</v>
@@ -61885,7 +61885,7 @@
         <v>6.50899982452393</v>
       </c>
       <c r="G2366" t="n">
-        <v>5.28205251693726</v>
+        <v>5.2820520401001</v>
       </c>
       <c r="H2366" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>7.48899984359741</v>
       </c>
       <c r="G2376" t="n">
-        <v>6.07732200622559</v>
+        <v>6.07732248306274</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62171,7 +62171,7 @@
         <v>7.68400001525879</v>
       </c>
       <c r="G2377" t="n">
-        <v>6.23556518554688</v>
+        <v>6.23556470870972</v>
       </c>
       <c r="H2377" t="s">
         <v>8</v>
@@ -62275,7 +62275,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2381" t="n">
-        <v>6.72733402252197</v>
+        <v>6.72733354568481</v>
       </c>
       <c r="H2381" t="s">
         <v>8</v>
@@ -62301,7 +62301,7 @@
         <v>8.14200019836426</v>
       </c>
       <c r="G2382" t="n">
-        <v>6.60723161697388</v>
+        <v>6.60723209381104</v>
       </c>
       <c r="H2382" t="s">
         <v>8</v>
@@ -62327,7 +62327,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G2383" t="n">
-        <v>6.55286121368408</v>
+        <v>6.55286073684692</v>
       </c>
       <c r="H2383" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>11.8159999847412</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>10157022</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>12.0260000228882</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>11.9099998474121</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>11.9399995803833</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>11.9659996032715</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>11.9659996032715</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73583984375</v>
+        <v>1765.73571777344</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.0478515625</v>
+        <v>1491.04797363281</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26928710938</v>
+        <v>1523.26940917969</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1365.86657714844</v>
       </c>
       <c r="G13" t="n">
-        <v>1056.05810546875</v>
+        <v>1056.05822753906</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1062.68798828125</v>
       </c>
       <c r="G14" t="n">
-        <v>821.647155761719</v>
+        <v>821.647094726562</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1364.82470703125</v>
       </c>
       <c r="G20" t="n">
-        <v>1055.25256347656</v>
+        <v>1055.25268554688</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.3115234375</v>
+        <v>918.311462402344</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.533020019531</v>
+        <v>950.532897949219</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1119.98974609375</v>
       </c>
       <c r="G29" t="n">
-        <v>865.95166015625</v>
+        <v>865.951599121094</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.4228515625</v>
+        <v>905.422912597656</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366760253906</v>
+        <v>926.366882324219</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1066.85534667969</v>
       </c>
       <c r="G36" t="n">
-        <v>824.869323730469</v>
+        <v>824.869262695312</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1115.82238769531</v>
       </c>
       <c r="G37" t="n">
-        <v>862.729553222656</v>
+        <v>862.7294921875</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1024.7646484375</v>
       </c>
       <c r="G42" t="n">
-        <v>792.325622558594</v>
+        <v>792.32568359375</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1167.91491699219</v>
       </c>
       <c r="G46" t="n">
-        <v>903.00634765625</v>
+        <v>903.006286621094</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977905273438</v>
+        <v>927.977966308594</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03125</v>
+        <v>1023.03137207031</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810363769531</v>
+        <v>961.810485839844</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254211425781</v>
+        <v>997.254089355469</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1121.03161621094</v>
       </c>
       <c r="G61" t="n">
-        <v>866.757202148438</v>
+        <v>866.757141113281</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813232421875</v>
+        <v>845.813171386719</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1048.10205078125</v>
       </c>
       <c r="G63" t="n">
-        <v>810.369567871094</v>
+        <v>810.36962890625</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>962.670288085938</v>
       </c>
       <c r="G66" t="n">
-        <v>744.315612792969</v>
+        <v>744.315673828125</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1227.30041503906</v>
       </c>
       <c r="G73" t="n">
-        <v>948.921875</v>
+        <v>948.921813964844</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.19738769531</v>
+        <v>1047.197265625</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03125</v>
+        <v>1023.03137207031</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1441.92175292969</v>
       </c>
       <c r="G78" t="n">
-        <v>1114.8623046875</v>
+        <v>1114.86242675781</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80902099609</v>
+        <v>1019.80908203125</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1153.32897949219</v>
       </c>
       <c r="G93" t="n">
-        <v>891.728759765625</v>
+        <v>891.728820800781</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1168.95678710938</v>
       </c>
       <c r="G94" t="n">
-        <v>903.811950683594</v>
+        <v>903.811889648438</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1156.45458984375</v>
       </c>
       <c r="G96" t="n">
-        <v>894.145446777344</v>
+        <v>894.1455078125</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839477539062</v>
+        <v>907.839538574219</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.14263916016</v>
+        <v>1010.142578125</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17034912109</v>
+        <v>1014.17028808594</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.14404296875</v>
+        <v>952.143920898438</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1151.24523925781</v>
       </c>
       <c r="G114" t="n">
-        <v>890.11767578125</v>
+        <v>890.117614746094</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1038.10021972656</v>
       </c>
       <c r="G117" t="n">
-        <v>802.636474609375</v>
+        <v>802.636413574219</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368225097656</v>
+        <v>868.368286132812</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749267578125</v>
+        <v>731.749328613281</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118286132812</v>
+        <v>634.118225097656</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194763183594</v>
+        <v>453.194732666016</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549652099609</v>
+        <v>481.549591064453</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259399414062</v>
+        <v>538.259460449219</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710052490234</v>
+        <v>510.710113525391</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532592773438</v>
+        <v>496.532653808594</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>541.970886230469</v>
       </c>
       <c r="G151" t="n">
-        <v>419.040069580078</v>
+        <v>419.0400390625</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>551.764282226562</v>
       </c>
       <c r="G152" t="n">
-        <v>426.612121582031</v>
+        <v>426.612091064453</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384948730469</v>
+        <v>399.384918212891</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.512725830078</v>
+        <v>400.5126953125</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G162" t="n">
-        <v>378.602111816406</v>
+        <v>378.602081298828</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>503.630737304688</v>
       </c>
       <c r="G170" t="n">
-        <v>389.396301269531</v>
+        <v>389.396270751953</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724182128906</v>
+        <v>384.724212646484</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G175" t="n">
-        <v>378.602111816406</v>
+        <v>378.602081298828</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>509.465118408203</v>
       </c>
       <c r="G177" t="n">
-        <v>393.907318115234</v>
+        <v>393.907287597656</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436706542969</v>
+        <v>325.436737060547</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214569091797</v>
+        <v>322.214538574219</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003784179688</v>
+        <v>309.003753662109</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>404.86328125</v>
       </c>
       <c r="G190" t="n">
-        <v>313.031463623047</v>
+        <v>313.031433105469</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742584228516</v>
+        <v>311.742614746094</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281951904297</v>
+        <v>291.281982421875</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843353271484</v>
+        <v>279.843322753906</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499114990234</v>
+        <v>270.499145507812</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>563.641357421875</v>
       </c>
       <c r="G208" t="n">
-        <v>435.795166015625</v>
+        <v>435.795196533203</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>723.044555664062</v>
       </c>
       <c r="G209" t="n">
-        <v>559.042236328125</v>
+        <v>559.042297363281</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266510009766</v>
+        <v>475.266448974609</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184112548828</v>
+        <v>434.184143066406</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906616210938</v>
+        <v>422.906585693359</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>484.0439453125</v>
       </c>
       <c r="G217" t="n">
-        <v>374.252227783203</v>
+        <v>374.252197265625</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>537.178344726562</v>
       </c>
       <c r="G219" t="n">
-        <v>415.334564208984</v>
+        <v>415.334594726562</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>558.015380859375</v>
       </c>
       <c r="G220" t="n">
-        <v>431.445281982422</v>
+        <v>431.4453125</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>537.595092773438</v>
       </c>
       <c r="G222" t="n">
-        <v>415.656768798828</v>
+        <v>415.656799316406</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>583.228149414062</v>
       </c>
       <c r="G224" t="n">
-        <v>450.939270019531</v>
+        <v>450.939239501953</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214569091797</v>
+        <v>322.214538574219</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>454.246978759766</v>
       </c>
       <c r="G242" t="n">
-        <v>351.2138671875</v>
+        <v>351.213836669922</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>94.8084259033203</v>
       </c>
       <c r="G466" t="n">
-        <v>73.3038024902344</v>
+        <v>73.3038101196289</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.171516418457</v>
+        <v>76.1715087890625</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003997802734</v>
+        <v>76.3003921508789</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>97.3505477905273</v>
       </c>
       <c r="G469" t="n">
-        <v>75.2693099975586</v>
+        <v>75.2693176269531</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426330566406</v>
+        <v>76.0426254272461</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>95.4335403442383</v>
       </c>
       <c r="G473" t="n">
-        <v>73.7871322631836</v>
+        <v>73.7871246337891</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064903259277</v>
+        <v>53.9064865112305</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>85.6401443481445</v>
       </c>
       <c r="G484" t="n">
-        <v>66.2150955200195</v>
+        <v>66.215087890625</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.154052734375</v>
+        <v>63.1540451049805</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906692504883</v>
+        <v>64.9906616210938</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>83.9731826782227</v>
       </c>
       <c r="G491" t="n">
-        <v>64.9262390136719</v>
+        <v>64.9262313842773</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539779663086</v>
+        <v>66.0539855957031</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.154052734375</v>
+        <v>63.1540451049805</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618606567383</v>
+        <v>61.9618530273438</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563148498535</v>
+        <v>61.156322479248</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>81.5977630615234</v>
       </c>
       <c r="G514" t="n">
-        <v>63.0896110534668</v>
+        <v>63.0896034240723</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695861816406</v>
+        <v>63.6695938110352</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184944152832</v>
+        <v>63.2184867858887</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397079467773</v>
+        <v>58.7397117614746</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>75.1591186523438</v>
       </c>
       <c r="G536" t="n">
-        <v>58.111385345459</v>
+        <v>58.1113929748535</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.060791015625</v>
+        <v>60.0607833862305</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.8363761901855</v>
+        <v>58.836368560791</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.4692344665527</v>
+        <v>55.46923828125</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.953685760498</v>
+        <v>54.9536895751953</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>69.4706192016602</v>
       </c>
       <c r="G548" t="n">
-        <v>53.7131614685059</v>
+        <v>53.7131652832031</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.0054321289062</v>
+        <v>52.005428314209</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832122802734</v>
+        <v>51.6832160949707</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184783935547</v>
+        <v>40.5184745788574</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>53.1969032287598</v>
       </c>
       <c r="G576" t="n">
-        <v>41.130687713623</v>
+        <v>41.1306838989258</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>61.0524597167969</v>
       </c>
       <c r="G578" t="n">
-        <v>47.2044258117676</v>
+        <v>47.2044296264648</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>58.9687576293945</v>
       </c>
       <c r="G579" t="n">
-        <v>45.5933532714844</v>
+        <v>45.5933570861816</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.1756134033203</v>
+        <v>44.175609588623</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>56.5933380126953</v>
       </c>
       <c r="G588" t="n">
-        <v>43.7567329406738</v>
+        <v>43.7567367553711</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>56.1974334716797</v>
       </c>
       <c r="G589" t="n">
-        <v>43.450626373291</v>
+        <v>43.4506301879883</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>54.780517578125</v>
       </c>
       <c r="G597" t="n">
-        <v>42.3551025390625</v>
+        <v>42.3550987243652</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.821174621582</v>
+        <v>43.8211784362793</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431816101074</v>
+        <v>52.8431777954102</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>58.7603874206543</v>
       </c>
       <c r="G607" t="n">
-        <v>45.4322509765625</v>
+        <v>45.4322471618652</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>59.0312690734863</v>
       </c>
       <c r="G608" t="n">
-        <v>45.6416854858398</v>
+        <v>45.6416893005371</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194732666016</v>
+        <v>45.3194770812988</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250785827637</v>
+        <v>43.2250747680664</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>57.9269065856934</v>
       </c>
       <c r="G623" t="n">
-        <v>44.7878227233887</v>
+        <v>44.7878189086914</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>56.6975250244141</v>
       </c>
       <c r="G630" t="n">
-        <v>43.8372917175293</v>
+        <v>43.837287902832</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>53.1135559082031</v>
       </c>
       <c r="G634" t="n">
-        <v>41.0662460327148</v>
+        <v>41.0662422180176</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.373477935791</v>
+        <v>40.3734817504883</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.567943572998</v>
+        <v>39.5679397583008</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062728881836</v>
+        <v>39.9062690734863</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>51.0715293884277</v>
       </c>
       <c r="G642" t="n">
-        <v>39.4873886108398</v>
+        <v>39.4873924255371</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>51.1965522766113</v>
       </c>
       <c r="G644" t="n">
-        <v>39.5840606689453</v>
+        <v>39.584056854248</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.0213165283203</v>
+        <v>38.021312713623</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>51.5299453735352</v>
       </c>
       <c r="G661" t="n">
-        <v>39.8418312072754</v>
+        <v>39.8418273925781</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>49.5921020507812</v>
       </c>
       <c r="G666" t="n">
-        <v>38.3435287475586</v>
+        <v>38.3435325622559</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>46.3415260314941</v>
       </c>
       <c r="G668" t="n">
-        <v>35.8302536010742</v>
+        <v>35.8302574157715</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>45.570556640625</v>
       </c>
       <c r="G675" t="n">
-        <v>35.2341613769531</v>
+        <v>35.2341575622559</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580787658691</v>
+        <v>34.0580749511719</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>47.1958427429199</v>
       </c>
       <c r="G690" t="n">
-        <v>36.4907989501953</v>
+        <v>36.490795135498</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057716369629</v>
+        <v>37.5057678222656</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563064575195</v>
+        <v>38.4563026428223</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.0213165283203</v>
+        <v>38.021312713623</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>37.0377998352051</v>
       </c>
       <c r="G710" t="n">
-        <v>28.6368179321289</v>
+        <v>28.6368198394775</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884857177734</v>
+        <v>28.5884838104248</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>36.089714050293</v>
       </c>
       <c r="G713" t="n">
-        <v>27.9037799835205</v>
+        <v>27.9037780761719</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532451629639</v>
+        <v>26.9532432556152</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241130828857</v>
+        <v>25.6241111755371</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766651153564</v>
+        <v>23.3766632080078</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>28.5467128753662</v>
       </c>
       <c r="G719" t="n">
-        <v>22.0716972351074</v>
+        <v>22.0716953277588</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>29.2864265441895</v>
       </c>
       <c r="G720" t="n">
-        <v>22.6436233520508</v>
+        <v>22.6436252593994</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5260524749756</v>
       </c>
       <c r="G721" t="n">
-        <v>22.8288974761963</v>
+        <v>22.8288993835449</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177577972412</v>
+        <v>24.1177558898926</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005805969238</v>
+        <v>22.2005825042725</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>28.8071765899658</v>
       </c>
       <c r="G740" t="n">
-        <v>22.2730808258057</v>
+        <v>22.273078918457</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G742" t="n">
-        <v>24.8105163574219</v>
+        <v>24.8105182647705</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>36.7564964294434</v>
       </c>
       <c r="G747" t="n">
-        <v>28.419319152832</v>
+        <v>28.4193210601807</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782302856445</v>
+        <v>27.6782283782959</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363166809082</v>
+        <v>26.2363185882568</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193920135498</v>
+        <v>25.5193939208984</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G756" t="n">
-        <v>24.8105163574219</v>
+        <v>24.8105182647705</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077491760254</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983108520508</v>
+        <v>24.1983127593994</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399719238281</v>
+        <v>24.4399700164795</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058700561523</v>
+        <v>21.8058681488037</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>25.4107418060303</v>
       </c>
       <c r="G777" t="n">
-        <v>19.647029876709</v>
+        <v>19.6470317840576</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>25.598274230957</v>
       </c>
       <c r="G780" t="n">
-        <v>19.792028427124</v>
+        <v>19.7920265197754</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189598083496</v>
+        <v>20.2189617156982</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>24.9523277282715</v>
       </c>
       <c r="G787" t="n">
-        <v>19.2925930023193</v>
+        <v>19.292594909668</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136741638184</v>
+        <v>20.6136722564697</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G839" t="n">
-        <v>22.4583549499512</v>
+        <v>22.4583530426025</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>27.671558380127</v>
       </c>
       <c r="G842" t="n">
-        <v>21.3950462341309</v>
+        <v>21.3950443267822</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150577545166</v>
+        <v>20.8150596618652</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.4003238677979</v>
       </c>
       <c r="G852" t="n">
-        <v>19.6389770507812</v>
+        <v>19.6389751434326</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G856" t="n">
-        <v>18.6723308563232</v>
+        <v>18.6723327636719</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G860" t="n">
-        <v>18.4145603179932</v>
+        <v>18.4145584106445</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G861" t="n">
-        <v>18.124568939209</v>
+        <v>18.1245670318604</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G864" t="n">
-        <v>17.770133972168</v>
+        <v>17.7701320648193</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G866" t="n">
-        <v>17.1418113708496</v>
+        <v>17.1418132781982</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>21.7538452148438</v>
       </c>
       <c r="G868" t="n">
-        <v>16.8195972442627</v>
+        <v>16.8195991516113</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>21.6079864501953</v>
       </c>
       <c r="G870" t="n">
-        <v>16.7068252563477</v>
+        <v>16.706823348999</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907138824463</v>
+        <v>16.6907119750977</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134944915771</v>
+        <v>16.5134963989258</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.1107273101807</v>
+        <v>16.110725402832</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.9205417633057</v>
       </c>
       <c r="G884" t="n">
-        <v>16.9484825134277</v>
+        <v>16.9484844207764</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290393829346</v>
+        <v>17.0290374755859</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406764984131</v>
+        <v>18.1406784057617</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493431091309</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321678161621</v>
+        <v>25.6321659088135</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>34.4435882568359</v>
       </c>
       <c r="G900" t="n">
-        <v>26.631031036377</v>
+        <v>26.6310291290283</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G906" t="n">
-        <v>23.8922061920166</v>
+        <v>23.8922080993652</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.910587310791</v>
+        <v>21.9105892181396</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005805969238</v>
+        <v>22.2005825042725</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.583833694458</v>
+        <v>25.5838356018066</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516109466553</v>
+        <v>25.5516128540039</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416061401367</v>
+        <v>25.8416080474854</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>33.4850845336914</v>
       </c>
       <c r="G939" t="n">
-        <v>25.8899345397949</v>
+        <v>25.8899364471436</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>34.0268478393555</v>
       </c>
       <c r="G942" t="n">
-        <v>26.30881690979</v>
+        <v>26.3088150024414</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G948" t="n">
-        <v>25.0360717773438</v>
+        <v>25.0360698699951</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G950" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G951" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5262298583984</v>
       </c>
       <c r="G956" t="n">
-        <v>23.6022129058838</v>
+        <v>23.6022148132324</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727630615234</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G962" t="n">
-        <v>23.8922061920166</v>
+        <v>23.8922080993652</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>30.8596210479736</v>
       </c>
       <c r="G964" t="n">
-        <v>23.8599834442139</v>
+        <v>23.8599853515625</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>31.9431476593018</v>
       </c>
       <c r="G968" t="n">
-        <v>24.6977443695068</v>
+        <v>24.6977424621582</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G973" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.3122215270996</v>
+        <v>23.312219619751</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G980" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077491760254</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>30.4428825378418</v>
       </c>
       <c r="G989" t="n">
-        <v>23.5377712249756</v>
+        <v>23.5377731323242</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727630615234</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G996" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544509887695</v>
+        <v>23.0544490814209</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G999" t="n">
-        <v>22.7483463287354</v>
+        <v>22.7483444213867</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1005" t="n">
-        <v>22.4744625091553</v>
+        <v>22.4744644165039</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1007" t="n">
-        <v>22.7966766357422</v>
+        <v>22.7966785430908</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1009" t="n">
-        <v>22.4744625091553</v>
+        <v>22.4744644165039</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844692230225</v>
+        <v>22.1844711303711</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G1016" t="n">
-        <v>22.7483463287354</v>
+        <v>22.7483444213867</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G1017" t="n">
-        <v>22.4583549499512</v>
+        <v>22.4583530426025</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1020" t="n">
-        <v>22.7966766357422</v>
+        <v>22.7966785430908</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.71044921875</v>
+        <v>27.7104473114014</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493431091309</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821323394775</v>
+        <v>27.0821304321289</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>35.7146453857422</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.6137847900391</v>
+        <v>27.6137828826904</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.6276245117188</v>
+        <v>29.627628326416</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326633453369</v>
+        <v>28.0326614379883</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>37.1940765380859</v>
       </c>
       <c r="G1040" t="n">
-        <v>28.7576465606689</v>
+        <v>28.7576484680176</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737598419189</v>
+        <v>28.7737560272217</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936370849609</v>
+        <v>33.9936332702637</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>42.5075149536133</v>
       </c>
       <c r="G1052" t="n">
-        <v>32.8658828735352</v>
+        <v>32.8658790588379</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820613861084</v>
+        <v>29.9820652008057</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770263671875</v>
+        <v>31.5770225524902</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571491241455</v>
+        <v>26.3571472167969</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610511779785</v>
+        <v>25.7610492706299</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728973388672</v>
+        <v>18.1728992462158</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3787784576416</v>
       </c>
       <c r="G1071" t="n">
-        <v>16.5296058654785</v>
+        <v>16.5296039581299</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.7953433990479</v>
       </c>
       <c r="G1072" t="n">
-        <v>16.0785064697266</v>
+        <v>16.0785045623779</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445804595947</v>
+        <v>17.5445823669434</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.8023548126221</v>
+        <v>17.8023529052734</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>22.3164443969727</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.2545871734619</v>
+        <v>17.2545890808105</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.124568939209</v>
+        <v>18.1245670318604</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1102" t="n">
-        <v>17.5123596191406</v>
+        <v>17.5123615264893</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G1106" t="n">
-        <v>17.770133972168</v>
+        <v>17.7701320648193</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1115" t="n">
-        <v>16.4329414367676</v>
+        <v>16.4329395294189</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683597564697</v>
+        <v>22.1683616638184</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G1124" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G1125" t="n">
-        <v>25.0360717773438</v>
+        <v>25.0360698699951</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021438598633</v>
+        <v>26.5021457672119</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.2293968200684</v>
+        <v>25.229398727417</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.0349349975586</v>
+        <v>26.03493309021</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460765838623</v>
+        <v>24.7460746765137</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31.8597984313965</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.6332988739014</v>
+        <v>24.63330078125</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>32.7974662780762</v>
       </c>
       <c r="G1153" t="n">
-        <v>25.3582859039307</v>
+        <v>25.358283996582</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>37.5066299438477</v>
       </c>
       <c r="G1155" t="n">
-        <v>28.9993057250977</v>
+        <v>28.9993076324463</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303955078125</v>
+        <v>30.0303916931152</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>36.4856185913086</v>
       </c>
       <c r="G1159" t="n">
-        <v>28.2098846435547</v>
+        <v>28.2098827362061</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049110412598</v>
+        <v>26.9049129486084</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>34.7353096008301</v>
       </c>
       <c r="G1161" t="n">
-        <v>26.8565807342529</v>
+        <v>26.8565826416016</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655197143555</v>
+        <v>24.6655216217041</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>30.3386974334717</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.4572200775146</v>
+        <v>23.457218170166</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>31.2555255889893</v>
       </c>
       <c r="G1171" t="n">
-        <v>24.1660900115967</v>
+        <v>24.1660919189453</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>29.3801937103271</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7161254882812</v>
+        <v>22.7161235809326</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766651153564</v>
+        <v>23.3766632080078</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094524383545</v>
+        <v>22.9094543457031</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416732788086</v>
+        <v>22.9416751861572</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039180755615</v>
+        <v>22.1039161682129</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672939300537</v>
+        <v>20.2672920227051</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.6584892272949</v>
+        <v>16.6584911346436</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>22.7748603820801</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.6090240478516</v>
+        <v>17.6090259552002</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1240" t="n">
-        <v>19.2684268951416</v>
+        <v>19.2684288024902</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.783971786499</v>
+        <v>19.7839698791504</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728973388672</v>
+        <v>18.1728992462158</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206649780273</v>
+        <v>18.7206630706787</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206649780273</v>
+        <v>18.7206630706787</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445804595947</v>
+        <v>17.5445823669434</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862415313721</v>
+        <v>17.7862396240234</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.5123596191406</v>
+        <v>17.5123615264893</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>21.962215423584</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.9807033538818</v>
+        <v>16.9807052612305</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6584892272949</v>
+        <v>16.6584911346436</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934810638428</v>
+        <v>17.0934791564941</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357086181641</v>
+        <v>16.8357105255127</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801387786865</v>
+        <v>17.4801406860352</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.6723308563232</v>
+        <v>18.6723327636719</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>26.5255222320557</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.5089530944824</v>
+        <v>20.5089550018311</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>25.9629230499268</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.0739650726318</v>
+        <v>20.0739631652832</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>24.8793983459473</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.2362060546875</v>
+        <v>19.2362079620361</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395416259766</v>
+        <v>19.1395435333252</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750999450684</v>
+        <v>19.0750980377197</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1330" t="n">
-        <v>18.5273342132568</v>
+        <v>18.5273361206055</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.607889175415</v>
+        <v>18.6078910827637</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153774261475</v>
+        <v>19.1153793334961</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.833438873291</v>
+        <v>18.8334407806396</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353927612305</v>
+        <v>18.5353908538818</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864921569824</v>
+        <v>18.9864940643311</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1345" t="n">
-        <v>18.5273342132568</v>
+        <v>18.5273361206055</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112247467041</v>
+        <v>18.5112266540527</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.5273342132568</v>
+        <v>18.5273361206055</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1354" t="n">
-        <v>18.3259506225586</v>
+        <v>18.3259525299072</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>24.2959613800049</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.7851066589355</v>
+        <v>18.7851047515869</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.2684268951416</v>
+        <v>19.2684288024902</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531364440918</v>
+        <v>19.9531345367432</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397922515869</v>
+        <v>20.3397941589355</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598075866699</v>
+        <v>19.7598056793213</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>23.1707630157471</v>
       </c>
       <c r="G1402" t="n">
-        <v>17.9151268005371</v>
+        <v>17.9151287078857</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>21.9830532073975</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.9968185424805</v>
+        <v>16.9968166351318</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G1410" t="n">
-        <v>17.1418113708496</v>
+        <v>17.1418132781982</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1416" t="n">
-        <v>18.3259506225586</v>
+        <v>18.3259525299072</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.4103889465332</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.1004028320312</v>
+        <v>18.1004009246826</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428791046143</v>
+        <v>19.0428771972656</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>23.9208946228027</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.4951114654541</v>
+        <v>18.4951133728027</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742828369141</v>
+        <v>18.3742847442627</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292881011963</v>
+        <v>18.2292861938477</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1434" t="n">
-        <v>18.0923461914062</v>
+        <v>18.0923442840576</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>23.4520626068115</v>
       </c>
       <c r="G1440" t="n">
-        <v>18.1326236724854</v>
+        <v>18.1326217651367</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1444" t="n">
-        <v>18.0923461914062</v>
+        <v>18.0923442840576</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392948150635</v>
+        <v>17.9392929077148</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>22.5977458953857</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.4720840454102</v>
+        <v>17.4720821380615</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>23.2645282745361</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.9876251220703</v>
+        <v>17.9876270294189</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862415313721</v>
+        <v>17.7862396240234</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8023548126221</v>
+        <v>17.8023529052734</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>21.3475246429443</v>
       </c>
       <c r="G1485" t="n">
-        <v>16.5054378509521</v>
+        <v>16.5054397583008</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1489" t="n">
-        <v>16.4329414367676</v>
+        <v>16.4329395294189</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765525817871</v>
+        <v>16.3765544891357</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.975396156311</v>
+        <v>15.9753942489624</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668645858765</v>
+        <v>14.9668664932251</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9325141906738</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.6382083892822</v>
+        <v>14.6382064819336</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867668151855</v>
+        <v>14.4867658615112</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.2934370040894</v>
+        <v>14.293436050415</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780061721802</v>
+        <v>13.6780052185059</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013580322266</v>
+        <v>13.0013570785522</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379793167114</v>
+        <v>14.8379812240601</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.6543169021606</v>
+        <v>14.654314994812</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.625316619873</v>
+        <v>14.6253175735474</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189876556396</v>
+        <v>14.518988609314</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287662506104</v>
+        <v>14.4287672042847</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>18.5866184234619</v>
       </c>
       <c r="G1526" t="n">
-        <v>14.3707666397095</v>
+        <v>14.3707675933838</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958648681641</v>
+        <v>14.9958639144897</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024209976196</v>
+        <v>14.9024229049683</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316465377808</v>
+        <v>14.7316484451294</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154249191284</v>
+        <v>14.8154230117798</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.3365745544434</v>
       </c>
       <c r="G1543" t="n">
-        <v>14.1774387359619</v>
+        <v>14.1774396896362</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.7116413116455</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.4674320220947</v>
+        <v>14.467432975769</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994256973267</v>
+        <v>14.6994276046753</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5867958068848</v>
       </c>
       <c r="G1549" t="n">
-        <v>15.1440811157227</v>
+        <v>15.1440830230713</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024209976196</v>
+        <v>14.9024229049683</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.643515586853</v>
+        <v>15.6435136795044</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357086181641</v>
+        <v>16.8357105255127</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>21.6496601104736</v>
       </c>
       <c r="G1558" t="n">
-        <v>16.7390460968018</v>
+        <v>16.7390441894531</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147424697876</v>
+        <v>15.4147443771362</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.1325492858887</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.7928705215454</v>
+        <v>14.7928686141968</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.36545753479</v>
+        <v>13.3654584884644</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>18.1573753356934</v>
       </c>
       <c r="G1566" t="n">
-        <v>14.0388860702515</v>
+        <v>14.0388870239258</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.88649559021</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.8294486999512</v>
+        <v>13.8294477462769</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781202316284</v>
+        <v>13.5781192779541</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584470748901</v>
+        <v>13.8584480285645</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151977539062</v>
+        <v>15.0151958465576</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>20.0952186584473</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.537184715271</v>
+        <v>15.5371837615967</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>20.1202239990234</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.5565195083618</v>
+        <v>15.5565176010132</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8303985595703</v>
+        <v>15.8304004669189</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.069974899292</v>
+        <v>15.0699729919434</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199159622192</v>
+        <v>15.1199178695679</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>18.6178741455078</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.3949346542358</v>
+        <v>14.3949337005615</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660484313965</v>
+        <v>14.2660474777222</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585582733154</v>
+        <v>13.7585592269897</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116115570068</v>
+        <v>13.9116125106812</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780061721802</v>
+        <v>13.6780052185059</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>17.8573226928711</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8068923950195</v>
+        <v>13.8068914413452</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722221374512</v>
+        <v>11.6722211837769</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519590377808</v>
+        <v>11.0519580841064</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.390284538269</v>
+        <v>11.3902835845947</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.390284538269</v>
+        <v>11.3902835845947</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433349609375</v>
+        <v>11.5433340072632</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.9702701568604</v>
+        <v>11.970269203186</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5860891342163</v>
       </c>
       <c r="G1628" t="n">
-        <v>12.0508241653442</v>
+        <v>12.0508232116699</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.1903629302979</v>
       </c>
       <c r="G1630" t="n">
-        <v>12.5180358886719</v>
+        <v>12.5180349349976</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.0445022583008</v>
       </c>
       <c r="G1631" t="n">
-        <v>12.4052581787109</v>
+        <v>12.4052591323853</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805255889893</v>
+        <v>12.8805246353149</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.2533416748047</v>
+        <v>11.253342628479</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439033508301</v>
+        <v>11.0439023971558</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136335372925</v>
+        <v>10.7136325836182</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535694122314</v>
+        <v>8.34535598754883</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971284866333</v>
+        <v>7.34971380233765</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>8.91824340820312</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.8953914642334</v>
+        <v>6.89539098739624</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>9.3766565322876</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.2498254776001</v>
+        <v>7.24982595443726</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316871643066</v>
+        <v>6.86316919326782</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539770126343</v>
+        <v>6.60539722442627</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>8.8223934173584</v>
       </c>
       <c r="G1676" t="n">
-        <v>6.82128190994263</v>
+        <v>6.82128143310547</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927289962769</v>
+        <v>7.16927337646484</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.7407283782959</v>
+        <v>6.74072790145874</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973394393921</v>
+        <v>6.47973346710205</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>7.91806602478027</v>
       </c>
       <c r="G1689" t="n">
-        <v>6.12207555770874</v>
+        <v>6.1220760345459</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799476623535</v>
+        <v>4.88799428939819</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>6.05523681640625</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.68177652359009</v>
+        <v>4.68177700042725</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555252075195</v>
+        <v>4.76555204391479</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.91699361801147</v>
+        <v>4.91699314117432</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.91699361801147</v>
+        <v>4.91699314117432</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>6.2302680015564</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.8171067237854</v>
+        <v>4.81710720062256</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179785728455</v>
+        <v>3.81179761886597</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.68311882019043</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.62088513374329</v>
+        <v>3.62088489532471</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.5533150434494</v>
+        <v>1.55331492424011</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089284896851</v>
+        <v>1.53089272975922</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393760681152</v>
+        <v>1.37393748760223</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006965637207</v>
+        <v>1.46006953716278</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.88339996337891</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.45620381832123</v>
+        <v>1.45620369911194</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537937641144</v>
+        <v>1.44537925720215</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903860569</v>
+        <v>1.46903848648071</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.52161455154419</v>
+        <v>1.52161467075348</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.50213062763214</v>
+        <v>1.50213050842285</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.06299996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.59506642818451</v>
+        <v>1.5950665473938</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490931510925</v>
+        <v>1.71490919589996</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702341079712</v>
+        <v>1.67702329158783</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.60318493843079</v>
+        <v>1.6031848192215</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259298324585</v>
+        <v>1.56259310245514</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.65305483341217</v>
+        <v>1.65305495262146</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681817054749</v>
+        <v>1.63681828975677</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.10450005531311</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.62715339660645</v>
+        <v>1.62715351581573</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.79377341270447</v>
+        <v>1.79377329349518</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428663253784</v>
+        <v>1.89428651332855</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552515506744</v>
+        <v>1.83552491664886</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.63949990272522</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.04080390930176</v>
+        <v>2.04080367088318</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.03384518623352</v>
+        <v>2.0338454246521</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198734283447</v>
+        <v>2.12198758125305</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.9066573381424</v>
+        <v>1.90665745735168</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428663253784</v>
+        <v>1.89428651332855</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305147171021</v>
+        <v>1.80305159091949</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.13649988174438</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.65189492702484</v>
+        <v>1.65189504623413</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46207988262177</v>
+        <v>1.46208000183105</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.5175940990448</v>
+        <v>1.51759397983551</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.6344987154007</v>
+        <v>1.63449859619141</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.6344987154007</v>
+        <v>1.63449859619141</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222702980042</v>
+        <v>1.79222691059113</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666081905365</v>
+        <v>1.75666093826294</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630146980286</v>
+        <v>1.68630158901215</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681817054749</v>
+        <v>1.63681828975677</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.6283130645752</v>
+        <v>1.62831318378448</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.64686965942383</v>
+        <v>1.64686954021454</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.73501181602478</v>
+        <v>1.73501169681549</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.68939435482025</v>
+        <v>1.68939423561096</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.62058138847351</v>
+        <v>1.6205815076828</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006480693817</v>
+        <v>1.67006492614746</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.73037254810333</v>
+        <v>1.73037266731262</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.7582072019577</v>
+        <v>1.75820708274841</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011629581451</v>
+        <v>1.68011617660522</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65769410133362</v>
+        <v>1.65769398212433</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.76593887805939</v>
+        <v>1.7659387588501</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.80073189735413</v>
+        <v>1.80073201656342</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82702016830444</v>
+        <v>1.82701992988586</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.74583625793457</v>
+        <v>1.74583613872528</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645545959473</v>
+        <v>1.71645557880402</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985260486603</v>
+        <v>1.92985284328461</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309924125671</v>
+        <v>1.96309947967529</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918215274811</v>
+        <v>1.94918191432953</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562429428101</v>
+        <v>2.00562405586243</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959275245667</v>
+        <v>2.02959251403809</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025972366333</v>
+        <v>2.16025948524475</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.02263379096985</v>
+        <v>2.02263402938843</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.95459449291229</v>
+        <v>1.954594373703</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309924125671</v>
+        <v>1.96309947967529</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763925075531</v>
+        <v>1.79763913154602</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.74970209598541</v>
+        <v>1.7497022151947</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310284137726</v>
+        <v>1.81310272216797</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645221710205</v>
+        <v>1.86645197868347</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866917133331</v>
+        <v>1.84866893291473</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737904071808</v>
+        <v>1.89737927913666</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639748573303</v>
+        <v>2.00639724731445</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.9012451171875</v>
+        <v>1.90124535560608</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397529125214</v>
+        <v>1.98397505283356</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.85872042179108</v>
+        <v>1.85872030258179</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062567710876</v>
+        <v>1.93062591552734</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237777709961</v>
+        <v>1.97237753868103</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964400291443</v>
+        <v>2.03964376449585</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.08680772781372</v>
+        <v>2.0868079662323</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443714141846</v>
+        <v>2.07443690299988</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>3.06100010871887</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.36669850349426</v>
+        <v>2.36669826507568</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654799461365</v>
+        <v>2.18654775619507</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716371536255</v>
+        <v>2.30716347694397</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071821212769</v>
+        <v>2.40071797370911</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921959877014</v>
+        <v>2.55921983718872</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.35742020606995</v>
+        <v>2.35742044448853</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876134872437</v>
+        <v>2.31876158714294</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061547279358</v>
+        <v>2.38061571121216</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.36437892913818</v>
+        <v>2.3643786907196</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37443017959595</v>
+        <v>2.37442994117737</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.3875744342804</v>
+        <v>2.38757419586182</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.57777619361877</v>
+        <v>2.5777759552002</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334252357483</v>
+        <v>2.61334228515625</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597284317017</v>
+        <v>2.52597308158875</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.52519989013672</v>
+        <v>2.5252001285553</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710874557495</v>
+        <v>2.44710898399353</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.49891185760498</v>
+        <v>2.49891209602356</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.4965922832489</v>
+        <v>2.49659252166748</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>3.38899993896484</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.62030053138733</v>
+        <v>2.62030076980591</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983903884888</v>
+        <v>2.52983927726746</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792646408081</v>
+        <v>2.75792622566223</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467994689941</v>
+        <v>2.72467970848083</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452571868896</v>
+        <v>2.69452595710754</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.83137822151184</v>
+        <v>2.83137845993042</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2087" t="n">
-        <v>3.14219641685486</v>
+        <v>3.14219617843628</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188471794128</v>
+        <v>3.23188447952271</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.36487126350403</v>
+        <v>3.36487150192261</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>4.20900011062622</v>
       </c>
       <c r="G2096" t="n">
-        <v>3.25430679321289</v>
+        <v>3.25430703163147</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343110084534</v>
+        <v>3.23343133926392</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693458557129</v>
+        <v>3.31693434715271</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739631652832</v>
+        <v>3.40739607810974</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471403121948</v>
+        <v>3.48471426963806</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G2119" t="n">
-        <v>3.47466278076172</v>
+        <v>3.47466254234314</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2120" t="n">
-        <v>3.51796078681946</v>
+        <v>3.51796054840088</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811153411865</v>
+        <v>3.69811105728149</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409506797791</v>
+        <v>3.51409482955933</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667065620422</v>
+        <v>3.56667041778564</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.62002038955688</v>
+        <v>3.62002015113831</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.9014573097229</v>
+        <v>3.90145683288574</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>11.9160003662109</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>12616443</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>12.0179996490479</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>11.7519998550415</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>11.9180002212524</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>11.7519998550415</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>11.7519998550415</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>11.2700004577637</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>11.3680000305176</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>14272300</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>11.6339998245239</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>11.4479999542236</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>11.4540004730225</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>11.4540004730225</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>11.6339998245239</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>17815563</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>11.1379995346069</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>11.6800003051758</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>11.1820001602173</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>19784451</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>11.0179996490479</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>10.8199996948242</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>10.8599996566772</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>10580606</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>11.0459995269775</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>10.9099998474121</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>6956868</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>11.1960000991821</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>11.0780000686646</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>11.0799999237061</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2435.84741210938</v>
       </c>
       <c r="G2" t="n">
-        <v>1883.34399414062</v>
+        <v>1883.34411621094</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73583984375</v>
+        <v>1765.73571777344</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2208.72412109375</v>
       </c>
       <c r="G5" t="n">
-        <v>1707.7373046875</v>
+        <v>1707.73718261719</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.0478515625</v>
+        <v>1491.04797363281</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2005.56311035156</v>
       </c>
       <c r="G10" t="n">
-        <v>1550.65759277344</v>
+        <v>1550.65771484375</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1481.51208496094</v>
       </c>
       <c r="G19" t="n">
-        <v>1145.47277832031</v>
+        <v>1145.47290039062</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14135742188</v>
+        <v>1068.14123535156</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1218.96557617188</v>
       </c>
       <c r="G23" t="n">
-        <v>942.4775390625</v>
+        <v>942.477478027344</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.532958984375</v>
+        <v>950.532897949219</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>956.8359375</v>
       </c>
       <c r="G31" t="n">
-        <v>739.8046875</v>
+        <v>739.804626464844</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1044.97644042969</v>
       </c>
       <c r="G32" t="n">
-        <v>807.953002929688</v>
+        <v>807.952941894531</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.4228515625</v>
+        <v>905.422912597656</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366821289062</v>
+        <v>926.366882324219</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1077.27392578125</v>
       </c>
       <c r="G35" t="n">
-        <v>832.924621582031</v>
+        <v>832.924682617188</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1079.35754394531</v>
       </c>
       <c r="G40" t="n">
-        <v>834.53564453125</v>
+        <v>834.535705566406</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G49" t="n">
-        <v>853.86865234375</v>
+        <v>853.868591308594</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G50" t="n">
-        <v>853.86865234375</v>
+        <v>853.868591308594</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03131103516</v>
+        <v>1023.03137207031</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810424804688</v>
+        <v>961.810485839844</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1193.96118164062</v>
       </c>
       <c r="G55" t="n">
-        <v>923.144775390625</v>
+        <v>923.144714355469</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1240.84448242188</v>
       </c>
       <c r="G56" t="n">
-        <v>959.393859863281</v>
+        <v>959.393920898438</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254150390625</v>
+        <v>997.254089355469</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199401855469</v>
+        <v>960.199462890625</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813232421875</v>
+        <v>845.813171386719</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1040.18395996094</v>
       </c>
       <c r="G64" t="n">
-        <v>804.24755859375</v>
+        <v>804.247497558594</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1000.80200195312</v>
       </c>
       <c r="G65" t="n">
-        <v>773.798278808594</v>
+        <v>773.798217773438</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1088.73425292969</v>
       </c>
       <c r="G71" t="n">
-        <v>841.785583496094</v>
+        <v>841.785522460938</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1251.26293945312</v>
       </c>
       <c r="G74" t="n">
-        <v>967.449157714844</v>
+        <v>967.44921875</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.19738769531</v>
+        <v>1047.197265625</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03131103516</v>
+        <v>1023.03137207031</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1267.9326171875</v>
       </c>
       <c r="G87" t="n">
-        <v>980.337829589844</v>
+        <v>980.337768554688</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G90" t="n">
-        <v>965.032592773438</v>
+        <v>965.032653808594</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839477539062</v>
+        <v>907.839538574219</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809875488281</v>
+        <v>990.809814453125</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47613525391</v>
+        <v>1000.47625732422</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17022705078</v>
+        <v>1014.17028808594</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.69830322266</v>
+        <v>1003.6982421875</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G107" t="n">
-        <v>965.032592773438</v>
+        <v>965.032653808594</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1274.18371582031</v>
       </c>
       <c r="G108" t="n">
-        <v>985.171020507812</v>
+        <v>985.170959472656</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1214.79821777344</v>
       </c>
       <c r="G109" t="n">
-        <v>939.255432128906</v>
+        <v>939.255493164062</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1217.92370605469</v>
       </c>
       <c r="G110" t="n">
-        <v>941.671997070312</v>
+        <v>941.672058105469</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809875488281</v>
+        <v>990.809814453125</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.143981933594</v>
+        <v>952.143920898438</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1046.01831054688</v>
       </c>
       <c r="G115" t="n">
-        <v>808.758483886719</v>
+        <v>808.758544921875</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1067.89721679688</v>
       </c>
       <c r="G119" t="n">
-        <v>825.674865722656</v>
+        <v>825.6748046875</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368225097656</v>
+        <v>868.368286132812</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118286132812</v>
+        <v>634.118225097656</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>685.537902832031</v>
       </c>
       <c r="G130" t="n">
-        <v>530.04296875</v>
+        <v>530.042907714844</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>552.597717285156</v>
       </c>
       <c r="G131" t="n">
-        <v>427.256469726562</v>
+        <v>427.256500244141</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194763183594</v>
+        <v>453.194732666016</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>552.181030273438</v>
       </c>
       <c r="G133" t="n">
-        <v>426.934326171875</v>
+        <v>426.934295654297</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>582.394653320312</v>
       </c>
       <c r="G134" t="n">
-        <v>450.294860839844</v>
+        <v>450.294830322266</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549621582031</v>
+        <v>481.549591064453</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>680.745422363281</v>
       </c>
       <c r="G137" t="n">
-        <v>526.337524414062</v>
+        <v>526.337463378906</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259399414062</v>
+        <v>538.259460449219</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.53759765625</v>
+        <v>520.537658691406</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710083007812</v>
+        <v>510.710113525391</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>672.202209472656</v>
       </c>
       <c r="G143" t="n">
-        <v>519.732116699219</v>
+        <v>519.732055664062</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532623291016</v>
+        <v>496.532653808594</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>539.678771972656</v>
       </c>
       <c r="G153" t="n">
-        <v>417.267822265625</v>
+        <v>417.267852783203</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>523.009155273438</v>
       </c>
       <c r="G159" t="n">
-        <v>404.379241943359</v>
+        <v>404.379272460938</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>477.58447265625</v>
       </c>
       <c r="G164" t="n">
-        <v>369.257873535156</v>
+        <v>369.257904052734</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724182128906</v>
+        <v>384.724212646484</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>498.213134765625</v>
       </c>
       <c r="G178" t="n">
-        <v>385.207489013672</v>
+        <v>385.20751953125</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>464.248779296875</v>
       </c>
       <c r="G182" t="n">
-        <v>358.946990966797</v>
+        <v>358.947021484375</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436706542969</v>
+        <v>325.436737060547</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214569091797</v>
+        <v>322.214538574219</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003784179688</v>
+        <v>309.003753662109</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>392.569427490234</v>
       </c>
       <c r="G188" t="n">
-        <v>303.526123046875</v>
+        <v>303.526092529297</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742584228516</v>
+        <v>311.742614746094</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>392.361053466797</v>
       </c>
       <c r="G192" t="n">
-        <v>303.365020751953</v>
+        <v>303.364990234375</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499114990234</v>
+        <v>270.499145507812</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>354.229309082031</v>
       </c>
       <c r="G198" t="n">
-        <v>273.882385253906</v>
+        <v>273.882354736328</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>355.062805175781</v>
       </c>
       <c r="G199" t="n">
-        <v>274.526794433594</v>
+        <v>274.526824951172</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>355.062805175781</v>
       </c>
       <c r="G200" t="n">
-        <v>274.526794433594</v>
+        <v>274.526824951172</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>360.897155761719</v>
       </c>
       <c r="G204" t="n">
-        <v>279.037811279297</v>
+        <v>279.037780761719</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266479492188</v>
+        <v>475.266448974609</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184112548828</v>
+        <v>434.184143066406</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906616210938</v>
+        <v>422.906585693359</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>506.547943115234</v>
       </c>
       <c r="G214" t="n">
-        <v>391.651794433594</v>
+        <v>391.651824951172</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>439.661102294922</v>
       </c>
       <c r="G218" t="n">
-        <v>339.936370849609</v>
+        <v>339.936340332031</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>495.712677001953</v>
       </c>
       <c r="G227" t="n">
-        <v>383.274200439453</v>
+        <v>383.274230957031</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214569091797</v>
+        <v>322.214538574219</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>387.985260009766</v>
       </c>
       <c r="G249" t="n">
-        <v>299.981719970703</v>
+        <v>299.981750488281</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>386.318298339844</v>
       </c>
       <c r="G250" t="n">
-        <v>298.692901611328</v>
+        <v>298.69287109375</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>339.643371582031</v>
       </c>
       <c r="G251" t="n">
-        <v>262.604827880859</v>
+        <v>262.604858398438</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.171516418457</v>
+        <v>76.1715087890625</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003997802734</v>
+        <v>76.3003921508789</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>97.0588302612305</v>
       </c>
       <c r="G472" t="n">
-        <v>75.0437622070312</v>
+        <v>75.0437698364258</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>93.6832275390625</v>
       </c>
       <c r="G475" t="n">
-        <v>72.4338302612305</v>
+        <v>72.4338226318359</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>89.2241058349609</v>
       </c>
       <c r="G476" t="n">
-        <v>68.9861221313477</v>
+        <v>68.9861297607422</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>85.4734420776367</v>
       </c>
       <c r="G478" t="n">
-        <v>66.0862045288086</v>
+        <v>66.0861968994141</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.1218299865723</v>
+        <v>63.1218338012695</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264404296875</v>
+        <v>56.2264366149902</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>82.0978469848633</v>
       </c>
       <c r="G487" t="n">
-        <v>63.4762649536133</v>
+        <v>63.476261138916</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>83.306396484375</v>
       </c>
       <c r="G488" t="n">
-        <v>64.4106826782227</v>
+        <v>64.4106903076172</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906692504883</v>
+        <v>64.9906616210938</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539779663086</v>
+        <v>66.0539855957031</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>83.8064804077148</v>
       </c>
       <c r="G493" t="n">
-        <v>64.7973480224609</v>
+        <v>64.7973403930664</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G496" t="n">
-        <v>62.8318367004395</v>
+        <v>62.8318290710449</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>80.4725646972656</v>
       </c>
       <c r="G497" t="n">
-        <v>62.2196311950684</v>
+        <v>62.2196273803711</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>80.4308853149414</v>
       </c>
       <c r="G499" t="n">
-        <v>62.1874084472656</v>
+        <v>62.1874046325684</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563186645508</v>
+        <v>61.156322479248</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>78.430534362793</v>
       </c>
       <c r="G502" t="n">
-        <v>60.6407775878906</v>
+        <v>60.6407814025879</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G506" t="n">
-        <v>62.5096168518066</v>
+        <v>62.5096206665039</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>79.7640991210938</v>
       </c>
       <c r="G508" t="n">
-        <v>61.6718597412109</v>
+        <v>61.6718559265137</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>81.93115234375</v>
       </c>
       <c r="G510" t="n">
-        <v>63.3473739624023</v>
+        <v>63.3473777770996</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573806762695</v>
+        <v>63.0573844909668</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G516" t="n">
-        <v>62.5096168518066</v>
+        <v>62.5096206665039</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G518" t="n">
-        <v>63.9273643493652</v>
+        <v>63.927360534668</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G523" t="n">
-        <v>63.9273643493652</v>
+        <v>63.927360534668</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G524" t="n">
-        <v>62.8318367004395</v>
+        <v>62.8318290710449</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184944152832</v>
+        <v>63.2184867858887</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G528" t="n">
-        <v>62.8318367004395</v>
+        <v>62.8318290710449</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>81.0143203735352</v>
       </c>
       <c r="G529" t="n">
-        <v>62.6385078430176</v>
+        <v>62.6385040283203</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>80.555908203125</v>
       </c>
       <c r="G531" t="n">
-        <v>62.2840728759766</v>
+        <v>62.2840690612793</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>78.1388168334961</v>
       </c>
       <c r="G538" t="n">
-        <v>60.415225982666</v>
+        <v>60.4152297973633</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>74.8048934936523</v>
       </c>
       <c r="G541" t="n">
-        <v>57.8375053405762</v>
+        <v>57.8375091552734</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.953685760498</v>
+        <v>54.9536895751953</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>67.0951995849609</v>
       </c>
       <c r="G549" t="n">
-        <v>51.8765411376953</v>
+        <v>51.8765449523926</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832122802734</v>
+        <v>51.6832160949707</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G557" t="n">
-        <v>51.2321128845215</v>
+        <v>51.2321166992188</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G558" t="n">
-        <v>51.2321128845215</v>
+        <v>51.2321166992188</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>65.0114974975586</v>
       </c>
       <c r="G561" t="n">
-        <v>50.2654724121094</v>
+        <v>50.2654685974121</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>63.6987609863281</v>
       </c>
       <c r="G563" t="n">
-        <v>49.25048828125</v>
+        <v>49.2504920959473</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>60.0731201171875</v>
       </c>
       <c r="G567" t="n">
-        <v>46.4472274780273</v>
+        <v>46.4472236633301</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>55.0097236633301</v>
       </c>
       <c r="G569" t="n">
-        <v>42.5323143005371</v>
+        <v>42.5323181152344</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>56.0099029541016</v>
       </c>
       <c r="G570" t="n">
-        <v>43.3056373596191</v>
+        <v>43.3056335449219</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367904663086</v>
+        <v>41.4367866516113</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184783935547</v>
+        <v>40.5184745788574</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>57.8435592651367</v>
       </c>
       <c r="G577" t="n">
-        <v>44.7233734130859</v>
+        <v>44.7233772277832</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>55.5723266601562</v>
       </c>
       <c r="G581" t="n">
-        <v>42.9673118591309</v>
+        <v>42.9673080444336</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>55.5306510925293</v>
       </c>
       <c r="G585" t="n">
-        <v>42.9350852966309</v>
+        <v>42.9350891113281</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>56.3641319274902</v>
       </c>
       <c r="G587" t="n">
-        <v>43.5795135498047</v>
+        <v>43.579517364502</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.821174621582</v>
+        <v>43.8211784362793</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431816101074</v>
+        <v>52.8431777954102</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>60.9066009521484</v>
       </c>
       <c r="G606" t="n">
-        <v>47.0916557312012</v>
+        <v>47.0916519165039</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194732666016</v>
+        <v>45.3194770812988</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>57.1976127624512</v>
       </c>
       <c r="G621" t="n">
-        <v>44.2239418029785</v>
+        <v>44.2239456176758</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250785827637</v>
+        <v>43.2250747680664</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.567943572998</v>
+        <v>39.5679397583008</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>50.3839073181152</v>
       </c>
       <c r="G650" t="n">
-        <v>38.9557342529297</v>
+        <v>38.955738067627</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374298095703</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>55.3847923278809</v>
       </c>
       <c r="G659" t="n">
-        <v>42.8223152160645</v>
+        <v>42.8223114013672</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>49.3628921508789</v>
       </c>
       <c r="G663" t="n">
-        <v>38.1663093566895</v>
+        <v>38.1663131713867</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>50.3839073181152</v>
       </c>
       <c r="G665" t="n">
-        <v>38.9557342529297</v>
+        <v>38.955738067627</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>45.9247856140137</v>
       </c>
       <c r="G674" t="n">
-        <v>35.5080413818359</v>
+        <v>35.5080375671387</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>43.132625579834</v>
       </c>
       <c r="G681" t="n">
-        <v>33.3492012023926</v>
+        <v>33.3492050170898</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>46.3206901550293</v>
       </c>
       <c r="G685" t="n">
-        <v>35.8141479492188</v>
+        <v>35.8141441345215</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G687" t="n">
-        <v>38.3113059997559</v>
+        <v>38.3113098144531</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374298095703</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>47.695930480957</v>
       </c>
       <c r="G689" t="n">
-        <v>36.8774490356445</v>
+        <v>36.8774528503418</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057716369629</v>
+        <v>37.5057678222656</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G697" t="n">
-        <v>38.3113059997559</v>
+        <v>38.3113098144531</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563064575195</v>
+        <v>38.4563026428223</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>50.175537109375</v>
       </c>
       <c r="G699" t="n">
-        <v>38.7946319580078</v>
+        <v>38.7946281433105</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>44.8412628173828</v>
       </c>
       <c r="G702" t="n">
-        <v>34.6702880859375</v>
+        <v>34.6702842712402</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>42.861743927002</v>
       </c>
       <c r="G704" t="n">
-        <v>33.1397666931152</v>
+        <v>33.139762878418</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>43.4243431091309</v>
       </c>
       <c r="G705" t="n">
-        <v>33.5747566223145</v>
+        <v>33.5747528076172</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884857177734</v>
+        <v>28.5884838104248</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>35.7875785827637</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6701736450195</v>
+        <v>27.6701755523682</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241130828857</v>
+        <v>25.6241111755371</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>30.7137622833252</v>
       </c>
       <c r="G729" t="n">
-        <v>23.7472114562988</v>
+        <v>23.7472095489502</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177577972412</v>
+        <v>24.1177558898926</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>30.5574855804443</v>
       </c>
       <c r="G734" t="n">
-        <v>23.6263790130615</v>
+        <v>23.6263809204102</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005805969238</v>
+        <v>22.2005825042725</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>28.7863388061523</v>
       </c>
       <c r="G739" t="n">
-        <v>22.2569694519043</v>
+        <v>22.2569675445557</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715553283691</v>
+        <v>27.8715572357178</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>33.3809013366699</v>
       </c>
       <c r="G750" t="n">
-        <v>25.809383392334</v>
+        <v>25.8093852996826</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>31.8285446166992</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6091365814209</v>
+        <v>24.6091346740723</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193920135498</v>
+        <v>25.5193939208984</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077491760254</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983108520508</v>
+        <v>24.1983127593994</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>31.2451076507568</v>
       </c>
       <c r="G760" t="n">
-        <v>24.1580352783203</v>
+        <v>24.1580333709717</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>30.9325523376465</v>
       </c>
       <c r="G762" t="n">
-        <v>23.9163761138916</v>
+        <v>23.916374206543</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399719238281</v>
+        <v>24.4399700164795</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G767" t="n">
-        <v>24.6171894073486</v>
+        <v>24.6171913146973</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058700561523</v>
+        <v>21.8058681488037</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>25.2336273193359</v>
       </c>
       <c r="G778" t="n">
-        <v>19.5100879669189</v>
+        <v>19.5100898742676</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>25.7962265014648</v>
       </c>
       <c r="G789" t="n">
-        <v>19.9450798034668</v>
+        <v>19.9450778961182</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G794" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>27.7653255462646</v>
       </c>
       <c r="G795" t="n">
-        <v>21.4675426483154</v>
+        <v>21.4675445556641</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083885192871</v>
+        <v>21.0083866119385</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136741638184</v>
+        <v>20.6136722564697</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>27.0256118774414</v>
       </c>
       <c r="G803" t="n">
-        <v>20.8956108093262</v>
+        <v>20.8956127166748</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>28.3695983886719</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9347553253174</v>
+        <v>21.9347534179688</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>27.9841136932373</v>
       </c>
       <c r="G806" t="n">
-        <v>21.6367073059082</v>
+        <v>21.6367053985596</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>27.1297950744629</v>
       </c>
       <c r="G812" t="n">
-        <v>20.9761638641357</v>
+        <v>20.9761657714844</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>26.4630126953125</v>
       </c>
       <c r="G815" t="n">
-        <v>20.4606246948242</v>
+        <v>20.4606227874756</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>26.4109191894531</v>
       </c>
       <c r="G816" t="n">
-        <v>20.4203472137451</v>
+        <v>20.4203453063965</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G819" t="n">
-        <v>21.4917087554932</v>
+        <v>21.4917106628418</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G820" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G830" t="n">
-        <v>20.4284019470215</v>
+        <v>20.4284000396729</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G832" t="n">
-        <v>20.4284019470215</v>
+        <v>20.4284000396729</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>29.0884761810303</v>
       </c>
       <c r="G840" t="n">
-        <v>22.4905738830566</v>
+        <v>22.4905757904053</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>27.9841136932373</v>
       </c>
       <c r="G847" t="n">
-        <v>21.6367073059082</v>
+        <v>21.6367053985596</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.3800163269043</v>
       </c>
       <c r="G848" t="n">
-        <v>21.9428081512451</v>
+        <v>21.9428100585938</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>24.400146484375</v>
       </c>
       <c r="G857" t="n">
-        <v>18.8656597137451</v>
+        <v>18.8656616210938</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G863" t="n">
-        <v>17.8667945861816</v>
+        <v>17.8667964935303</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>22.2747707366943</v>
       </c>
       <c r="G865" t="n">
-        <v>17.2223644256592</v>
+        <v>17.2223663330078</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>21.8580303192139</v>
       </c>
       <c r="G867" t="n">
-        <v>16.9001502990723</v>
+        <v>16.9001522064209</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>21.1704082489014</v>
       </c>
       <c r="G871" t="n">
-        <v>16.3684978485107</v>
+        <v>16.3684959411621</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907138824463</v>
+        <v>16.6907119750977</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134944915771</v>
+        <v>16.5134963989258</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>21.7121715545654</v>
       </c>
       <c r="G881" t="n">
-        <v>16.7873783111572</v>
+        <v>16.7873764038086</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>22.4623031616211</v>
       </c>
       <c r="G888" t="n">
-        <v>17.3673629760742</v>
+        <v>17.3673610687256</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406764984131</v>
+        <v>18.1406784057617</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G891" t="n">
-        <v>19.187873840332</v>
+        <v>19.1878757476807</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>32.547420501709</v>
       </c>
       <c r="G893" t="n">
-        <v>25.1649532318115</v>
+        <v>25.1649551391602</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493392944336</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321678161621</v>
+        <v>25.6321659088135</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G901" t="n">
-        <v>26.1154899597168</v>
+        <v>26.1154880523682</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>26.7547302246094</v>
       </c>
       <c r="G915" t="n">
-        <v>20.6861743927002</v>
+        <v>20.6861724853516</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>26.4630126953125</v>
       </c>
       <c r="G916" t="n">
-        <v>20.4606246948242</v>
+        <v>20.4606227874756</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G917" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.7752132415771</v>
       </c>
       <c r="G918" t="n">
-        <v>19.1556529998779</v>
+        <v>19.1556549072266</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>25.0877685546875</v>
       </c>
       <c r="G919" t="n">
-        <v>19.3973159790039</v>
+        <v>19.3973140716553</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>26.9005889892578</v>
       </c>
       <c r="G920" t="n">
-        <v>20.7989463806152</v>
+        <v>20.7989482879639</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.910587310791</v>
+        <v>21.9105892181396</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005805969238</v>
+        <v>22.2005825042725</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>31.7556133270264</v>
       </c>
       <c r="G931" t="n">
-        <v>24.5527458190918</v>
+        <v>24.5527477264404</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416061401367</v>
+        <v>25.8416080474854</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G944" t="n">
-        <v>26.1154899597168</v>
+        <v>26.1154880523682</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>33.7976417541504</v>
       </c>
       <c r="G945" t="n">
-        <v>26.1315975189209</v>
+        <v>26.1315994262695</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G949" t="n">
-        <v>25.1327362060547</v>
+        <v>25.1327342987061</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G953" t="n">
-        <v>24.6171894073486</v>
+        <v>24.6171913146973</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>30.3178596496582</v>
       </c>
       <c r="G955" t="n">
-        <v>23.4411087036133</v>
+        <v>23.4411067962646</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727592468262</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>30.38037109375</v>
       </c>
       <c r="G959" t="n">
-        <v>23.4894390106201</v>
+        <v>23.4894409179688</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>30.5887413024902</v>
       </c>
       <c r="G961" t="n">
-        <v>23.6505451202393</v>
+        <v>23.6505470275879</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>31.3388748168945</v>
       </c>
       <c r="G965" t="n">
-        <v>24.2305335998535</v>
+        <v>24.2305355072021</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>31.2346897125244</v>
       </c>
       <c r="G978" t="n">
-        <v>24.1499786376953</v>
+        <v>24.1499805450439</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077491760254</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>30.7971115112305</v>
       </c>
       <c r="G986" t="n">
-        <v>23.811653137207</v>
+        <v>23.8116550445557</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727592468262</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>29.3593578338623</v>
       </c>
       <c r="G1000" t="n">
-        <v>22.7000160217285</v>
+        <v>22.7000141143799</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1001" t="n">
-        <v>22.5227947235107</v>
+        <v>22.5227966308594</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1003" t="n">
-        <v>23.0061168670654</v>
+        <v>23.0061187744141</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1006" t="n">
-        <v>23.0061168670654</v>
+        <v>23.0061187744141</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844692230225</v>
+        <v>22.1844711303711</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1013" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1014" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1015" t="n">
-        <v>22.5227947235107</v>
+        <v>22.5227966308594</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493392944336</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821323394775</v>
+        <v>27.0821304321289</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>39.069408416748</v>
       </c>
       <c r="G1029" t="n">
-        <v>30.207612991333</v>
+        <v>30.2076148986816</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>38.9652214050293</v>
       </c>
       <c r="G1030" t="n">
-        <v>30.1270599365234</v>
+        <v>30.1270580291748</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>37.9650459289551</v>
       </c>
       <c r="G1031" t="n">
-        <v>29.3537445068359</v>
+        <v>29.3537425994873</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>37.73583984375</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1765289306641</v>
+        <v>29.1765270233154</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>38.0275573730469</v>
       </c>
       <c r="G1045" t="n">
-        <v>29.4020767211914</v>
+        <v>29.40207862854</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>39.4444732666016</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.4976081848145</v>
+        <v>30.4976062774658</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936294555664</v>
+        <v>33.9936332702637</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820613861084</v>
+        <v>29.9820652008057</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>38.0275573730469</v>
       </c>
       <c r="G1057" t="n">
-        <v>29.4020767211914</v>
+        <v>29.40207862854</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445804595947</v>
+        <v>17.5445823669434</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1078" t="n">
-        <v>17.754020690918</v>
+        <v>17.7540187835693</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.754020690918</v>
+        <v>17.7540187835693</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1096" t="n">
-        <v>17.6412448883057</v>
+        <v>17.6412467956543</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0601253509521</v>
+        <v>18.0601234436035</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1100" t="n">
-        <v>17.6412448883057</v>
+        <v>17.6412467956543</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1108" t="n">
-        <v>17.9634590148926</v>
+        <v>17.9634609222412</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G1110" t="n">
-        <v>17.8667945861816</v>
+        <v>17.8667964935303</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>21.7121715545654</v>
       </c>
       <c r="G1111" t="n">
-        <v>16.7873783111572</v>
+        <v>16.7873764038086</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683597564697</v>
+        <v>22.1683616638184</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>29.2134971618652</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.5872364044189</v>
+        <v>22.5872383117676</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>31.0263175964355</v>
       </c>
       <c r="G1133" t="n">
-        <v>23.9888725280762</v>
+        <v>23.9888706207275</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>32.859977722168</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.4066181182861</v>
+        <v>25.4066162109375</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>32.5890960693359</v>
       </c>
       <c r="G1144" t="n">
-        <v>25.1971759796143</v>
+        <v>25.1971778869629</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G1148" t="n">
-        <v>24.6171894073486</v>
+        <v>24.6171913146973</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G1149" t="n">
-        <v>25.1327362060547</v>
+        <v>25.1327342987061</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>40.2154426574707</v>
       </c>
       <c r="G1157" t="n">
-        <v>31.0937042236328</v>
+        <v>31.0937023162842</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049110412598</v>
+        <v>26.9049129486084</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655235290527</v>
+        <v>24.6655216217041</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>32.5890960693359</v>
       </c>
       <c r="G1166" t="n">
-        <v>25.1971759796143</v>
+        <v>25.1971778869629</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>32.4432373046875</v>
       </c>
       <c r="G1168" t="n">
-        <v>25.0844039916992</v>
+        <v>25.0844020843506</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>30.8804588317871</v>
       </c>
       <c r="G1172" t="n">
-        <v>23.8760948181152</v>
+        <v>23.8760967254639</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>30.6095771789551</v>
       </c>
       <c r="G1177" t="n">
-        <v>23.6666584014893</v>
+        <v>23.6666564941406</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.23166847229</v>
+        <v>23.2316703796387</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>29.9011192321777</v>
       </c>
       <c r="G1186" t="n">
-        <v>23.1188926696777</v>
+        <v>23.1188907623291</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094524383545</v>
+        <v>22.9094543457031</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1195" t="n">
-        <v>23.0061168670654</v>
+        <v>23.0061187744141</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>28.0049514770508</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.6528186798096</v>
+        <v>21.6528167724609</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>28.5258750915527</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.0555839538574</v>
+        <v>22.0555820465088</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>28.4008541107178</v>
       </c>
       <c r="G1205" t="n">
-        <v>21.9589214324951</v>
+        <v>21.9589195251465</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.4917087554932</v>
+        <v>21.4917106628418</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.2758312225342</v>
       </c>
       <c r="G1209" t="n">
-        <v>21.8622531890869</v>
+        <v>21.8622550964355</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672939300537</v>
+        <v>20.2672920227051</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1216" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>23.3791332244873</v>
       </c>
       <c r="G1225" t="n">
-        <v>18.0762367248535</v>
+        <v>18.0762348175049</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>22.1914234161377</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.157922744751</v>
+        <v>17.1579246520996</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.783971786499</v>
+        <v>19.7839698791504</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1245" t="n">
-        <v>20.0417442321777</v>
+        <v>20.0417423248291</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206649780273</v>
+        <v>18.7206630706787</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206649780273</v>
+        <v>18.7206630706787</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.6412448883057</v>
+        <v>17.6412467956543</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1259" t="n">
-        <v>17.754020690918</v>
+        <v>17.7540187835693</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445804595947</v>
+        <v>17.5445823669434</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862415313721</v>
+        <v>17.7862396240234</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.4318065643311</v>
+        <v>17.4318046569824</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.0601253509521</v>
+        <v>18.0601234436035</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>22.3997936248779</v>
       </c>
       <c r="G1280" t="n">
-        <v>17.3190307617188</v>
+        <v>17.3190326690674</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.4318065643311</v>
+        <v>17.4318046569824</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>22.1914234161377</v>
       </c>
       <c r="G1286" t="n">
-        <v>17.157922744751</v>
+        <v>17.1579246520996</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934810638428</v>
+        <v>17.0934791564941</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357086181641</v>
+        <v>16.8357105255127</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801387786865</v>
+        <v>17.4801406860352</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1294" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.5895099639893</v>
+        <v>20.5895080566406</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.5895099639893</v>
+        <v>20.5895080566406</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>26.6088714599609</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5733966827393</v>
+        <v>20.5733985900879</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>25.0460948944092</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.3650951385498</v>
+        <v>19.3650932312012</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>25.504508972168</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.7195301055908</v>
+        <v>19.7195281982422</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>25.3794860839844</v>
       </c>
       <c r="G1317" t="n">
-        <v>19.6228656768799</v>
+        <v>19.6228637695312</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750999450684</v>
+        <v>19.0750980377197</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1326" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.607889175415</v>
+        <v>18.6078910827637</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>23.8375473022461</v>
       </c>
       <c r="G1333" t="n">
-        <v>18.4306716918945</v>
+        <v>18.4306697845459</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153774261475</v>
+        <v>19.1153793334961</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.833438873291</v>
+        <v>18.8334407806396</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353889465332</v>
+        <v>18.5353908538818</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>24.3167991638184</v>
       </c>
       <c r="G1340" t="n">
-        <v>18.8012199401855</v>
+        <v>18.8012180328369</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864921569824</v>
+        <v>18.9864940643311</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112247467041</v>
+        <v>18.5112266540527</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1350" t="n">
-        <v>18.5434455871582</v>
+        <v>18.5434474945068</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>24.3167991638184</v>
       </c>
       <c r="G1355" t="n">
-        <v>18.8012199401855</v>
+        <v>18.8012180328369</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187129974365</v>
+        <v>19.0187149047852</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>24.806468963623</v>
       </c>
       <c r="G1364" t="n">
-        <v>19.1798191070557</v>
+        <v>19.1798210144043</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>25.4628353118896</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.6873092651367</v>
+        <v>19.6873073577881</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>25.1919536590576</v>
       </c>
       <c r="G1370" t="n">
-        <v>19.4778671264648</v>
+        <v>19.4778690338135</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>25.0148391723633</v>
       </c>
       <c r="G1372" t="n">
-        <v>19.3409271240234</v>
+        <v>19.3409290313721</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>25.8483200073242</v>
       </c>
       <c r="G1373" t="n">
-        <v>19.9853553771973</v>
+        <v>19.9853572845459</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>26.2858963012695</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.3236789703369</v>
+        <v>20.3236808776855</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.0417442321777</v>
+        <v>20.0417423248291</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598037719727</v>
+        <v>19.7598056793213</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G1387" t="n">
-        <v>19.187873840332</v>
+        <v>19.1878757476807</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187129974365</v>
+        <v>19.0187149047852</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>24.1813583374023</v>
       </c>
       <c r="G1395" t="n">
-        <v>18.696496963501</v>
+        <v>18.6964988708496</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1401" t="n">
-        <v>18.1084575653076</v>
+        <v>18.108455657959</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>21.9830532073975</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.9968147277832</v>
+        <v>16.9968166351318</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>23.5562477111816</v>
       </c>
       <c r="G1415" t="n">
-        <v>18.2131748199463</v>
+        <v>18.2131767272949</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>24.400146484375</v>
       </c>
       <c r="G1418" t="n">
-        <v>18.8656597137451</v>
+        <v>18.8656616210938</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1419" t="n">
-        <v>18.5434455871582</v>
+        <v>18.5434474945068</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>24.3897285461426</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.8576049804688</v>
+        <v>18.8576068878174</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428791046143</v>
+        <v>19.0428771972656</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742828369141</v>
+        <v>18.3742847442627</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292881011963</v>
+        <v>18.2292861938477</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1435" t="n">
-        <v>17.9634590148926</v>
+        <v>17.9634609222412</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1443" t="n">
-        <v>18.0601253509521</v>
+        <v>18.0601234436035</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>23.160343170166</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.9070720672607</v>
+        <v>17.9070701599121</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>23.2436923980713</v>
       </c>
       <c r="G1451" t="n">
-        <v>17.9715137481689</v>
+        <v>17.9715156555176</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>23.0978336334229</v>
       </c>
       <c r="G1452" t="n">
-        <v>17.8587417602539</v>
+        <v>17.8587398529053</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.1084575653076</v>
+        <v>18.108455657959</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862415313721</v>
+        <v>17.7862396240234</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>21.8059387207031</v>
       </c>
       <c r="G1479" t="n">
-        <v>16.8598766326904</v>
+        <v>16.8598747253418</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>22.1289119720459</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.1095924377441</v>
+        <v>17.1095905303955</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>21.7121715545654</v>
       </c>
       <c r="G1482" t="n">
-        <v>16.7873783111572</v>
+        <v>16.7873764038086</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>21.0766429901123</v>
       </c>
       <c r="G1486" t="n">
-        <v>16.2960014343262</v>
+        <v>16.2959995269775</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.9753952026367</v>
+        <v>15.9753942489624</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>20.2244091033936</v>
       </c>
       <c r="G1497" t="n">
-        <v>15.6370725631714</v>
+        <v>15.6370716094971</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.2934350967407</v>
+        <v>14.293436050415</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>19.0783729553223</v>
       </c>
       <c r="G1507" t="n">
-        <v>14.7509803771973</v>
+        <v>14.7509813308716</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>18.507438659668</v>
       </c>
       <c r="G1508" t="n">
-        <v>14.3095474243164</v>
+        <v>14.3095483779907</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379802703857</v>
+        <v>14.8379812240601</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157651901245</v>
+        <v>14.5157642364502</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>18.8908386230469</v>
       </c>
       <c r="G1514" t="n">
-        <v>14.6059846878052</v>
+        <v>14.6059837341309</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.6543159484863</v>
+        <v>14.654314994812</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>19.1658878326416</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8186454772949</v>
+        <v>14.8186464309692</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>19.3200817108154</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.9378652572632</v>
+        <v>14.9378662109375</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157651901245</v>
+        <v>14.5157642364502</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.6253185272217</v>
+        <v>14.6253175735474</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189876556396</v>
+        <v>14.518988609314</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287662506104</v>
+        <v>14.4287672042847</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>19.307580947876</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.9282007217407</v>
+        <v>14.9281997680664</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>19.1075439453125</v>
       </c>
       <c r="G1532" t="n">
-        <v>14.7735366821289</v>
+        <v>14.7735357284546</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>18.8116588592529</v>
       </c>
       <c r="G1536" t="n">
-        <v>14.5447645187378</v>
+        <v>14.5447635650635</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>18.9116764068604</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.6220951080322</v>
+        <v>14.6220941543579</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>18.9241790771484</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.6317615509033</v>
+        <v>14.6317625045776</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>18.8283271789551</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.5576515197754</v>
+        <v>14.5576505661011</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.699426651001</v>
+        <v>14.6994276046753</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5867958068848</v>
       </c>
       <c r="G1549" t="n">
-        <v>15.144082069397</v>
+        <v>15.1440830230713</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>20.6703205108643</v>
       </c>
       <c r="G1553" t="n">
-        <v>15.9818410873413</v>
+        <v>15.981840133667</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.6435146331787</v>
+        <v>15.6435136795044</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357086181641</v>
+        <v>16.8357105255127</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>20.6244792938232</v>
       </c>
       <c r="G1559" t="n">
-        <v>15.9463987350464</v>
+        <v>15.9463977813721</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147424697876</v>
+        <v>15.4147443771362</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.0366992950439</v>
       </c>
       <c r="G1563" t="n">
-        <v>14.7187595367432</v>
+        <v>14.7187604904175</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157651901245</v>
+        <v>14.5157642364502</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.88649559021</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.8294486999512</v>
+        <v>13.8294477462769</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>17.1113586425781</v>
       </c>
       <c r="G1568" t="n">
-        <v>13.2301292419434</v>
+        <v>13.230128288269</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.9196586608887</v>
       </c>
       <c r="G1572" t="n">
-        <v>13.0819101333618</v>
+        <v>13.0819110870361</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.807315826416</v>
       </c>
       <c r="G1574" t="n">
-        <v>13.7682275772095</v>
+        <v>13.7682285308838</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584470748901</v>
+        <v>13.8584480285645</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>20.2119064331055</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.6274042129517</v>
+        <v>15.627405166626</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>20.3661003112793</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.7466249465942</v>
+        <v>15.7466239929199</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1583" t="n">
-        <v>15.9496183395386</v>
+        <v>15.9496192932129</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.9496183395386</v>
+        <v>15.9496192932129</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>20.1077213287354</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.5468521118164</v>
+        <v>15.5468511581421</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8303995132446</v>
+        <v>15.8304004669189</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>19.9493598937988</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.4244108200073</v>
+        <v>15.424409866333</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.0699739456177</v>
+        <v>15.0699729919434</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199169158936</v>
+        <v>15.1199178695679</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>18.6178741455078</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.3949327468872</v>
+        <v>14.3949337005615</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>18.024019241333</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.9357776641846</v>
+        <v>13.9357786178589</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116115570068</v>
+        <v>13.9116125106812</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1609" t="n">
-        <v>12.9691352844238</v>
+        <v>12.9691362380981</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1610" t="n">
-        <v>12.9691352844238</v>
+        <v>12.9691362380981</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722221374512</v>
+        <v>11.6722211837769</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>14.3983793258667</v>
       </c>
       <c r="G1616" t="n">
-        <v>11.1325120925903</v>
+        <v>11.1325130462646</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>14.5442380905151</v>
       </c>
       <c r="G1620" t="n">
-        <v>11.2452869415283</v>
+        <v>11.2452878952026</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433349609375</v>
+        <v>11.5433340072632</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>15.5131587982178</v>
       </c>
       <c r="G1626" t="n">
-        <v>11.9944362640381</v>
+        <v>11.9944353103638</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>16.429988861084</v>
       </c>
       <c r="G1634" t="n">
-        <v>12.7033090591431</v>
+        <v>12.7033081054688</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>15.2318592071533</v>
       </c>
       <c r="G1639" t="n">
-        <v>11.7769403457642</v>
+        <v>11.7769412994385</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>14.7213516235352</v>
       </c>
       <c r="G1640" t="n">
-        <v>11.382227897644</v>
+        <v>11.3822269439697</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>14.7734451293945</v>
       </c>
       <c r="G1642" t="n">
-        <v>11.4225053787231</v>
+        <v>11.4225063323975</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>14.5650749206543</v>
       </c>
       <c r="G1643" t="n">
-        <v>11.2613973617554</v>
+        <v>11.2613983154297</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.2533416748047</v>
+        <v>11.253342628479</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>11.6166372299194</v>
       </c>
       <c r="G1652" t="n">
-        <v>8.98172950744629</v>
+        <v>8.98173046112061</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>11.2728261947632</v>
       </c>
       <c r="G1653" t="n">
-        <v>8.71590328216553</v>
+        <v>8.71590232849121</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535694122314</v>
+        <v>8.34535598754883</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392255783081</v>
+        <v>7.90392208099365</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971332550049</v>
+        <v>7.34971380233765</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>9.54335308074951</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.37871217727661</v>
+        <v>7.37871170043945</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316871643066</v>
+        <v>6.86316919326782</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795162200928</v>
+        <v>6.62795209884644</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539770126343</v>
+        <v>6.60539722442627</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>8.62235736846924</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.66661787033081</v>
+        <v>6.66661834716797</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>8.73487663269043</v>
       </c>
       <c r="G1680" t="n">
-        <v>6.75361585617065</v>
+        <v>6.7536153793335</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>8.62235736846924</v>
       </c>
       <c r="G1683" t="n">
-        <v>6.66661787033081</v>
+        <v>6.66661834716797</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.7407283782959</v>
+        <v>6.74072790145874</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973394393921</v>
+        <v>6.47973346710205</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107536315918</v>
+        <v>6.15107583999634</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>7.7680401802063</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.00607919692993</v>
+        <v>6.00607872009277</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>7.54300022125244</v>
       </c>
       <c r="G1693" t="n">
-        <v>5.83208274841309</v>
+        <v>5.83208322525024</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032152175903</v>
+        <v>5.11032199859619</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>6.32611799240112</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.89121675491333</v>
+        <v>4.89121627807617</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>7.65135192871094</v>
       </c>
       <c r="G1707" t="n">
-        <v>5.91585874557495</v>
+        <v>5.91585826873779</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>6.27194213867188</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.84932899475098</v>
+        <v>4.84932851791382</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555252075195</v>
+        <v>4.76555204391479</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.98942279815674</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.85771226882935</v>
+        <v>3.8577127456665</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179738044739</v>
+        <v>3.81179761886597</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.74562978744507</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.66921758651733</v>
+        <v>3.66921734809875</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.84252214431763</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.74413251876831</v>
+        <v>3.74413228034973</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>3.56354594230652</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.75525569915771</v>
+        <v>2.75525593757629</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.00300002098083</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.54867601394653</v>
+        <v>1.54867589473724</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.53862464427948</v>
+        <v>1.53862452507019</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.90980005264282</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.47661566734314</v>
+        <v>1.47661578655243</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.00250005722046</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.54828917980194</v>
+        <v>1.54828929901123</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.39945232868195</v>
+        <v>1.39945244789124</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>1.81560003757477</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.40378224849701</v>
+        <v>1.4037823677063</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.39156603813171</v>
+        <v>1.391566157341</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.41615319252014</v>
+        <v>1.41615307331085</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393760681152</v>
+        <v>1.37393748760223</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.80859994888306</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.39836990833282</v>
+        <v>1.39837002754211</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006965637207</v>
+        <v>1.46006953716278</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>1.88919997215271</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.46068811416626</v>
+        <v>1.46068823337555</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>1.80820000171661</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.39806067943573</v>
+        <v>1.39806079864502</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.94640004634857</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.50491404533386</v>
+        <v>1.50491392612457</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903860569</v>
+        <v>1.46903848648071</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>1.94780004024506</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.50599634647369</v>
+        <v>1.50599646568298</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.90659999847412</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.4741415977478</v>
+        <v>1.47414147853851</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.48805856704712</v>
+        <v>1.48805868625641</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.98660004138947</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.53599584102631</v>
+        <v>1.53599572181702</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490907669067</v>
+        <v>1.71490919589996</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.7017650604248</v>
+        <v>1.70176517963409</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259298324585</v>
+        <v>1.56259310245514</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681817054749</v>
+        <v>1.63681828975677</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>2.4614999294281</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.90317809581757</v>
+        <v>1.90317797660828</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482709884644</v>
+        <v>1.92482697963715</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.847895860672</v>
+        <v>1.84789597988129</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.01026320457458</v>
+        <v>2.01026296615601</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.90201830863953</v>
+        <v>1.90201842784882</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.88191568851471</v>
+        <v>1.88191556930542</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552503585815</v>
+        <v>1.83552491664886</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.91052305698395</v>
+        <v>1.91052317619324</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.14170336723328</v>
+        <v>2.14170360565186</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.03384518623352</v>
+        <v>2.0338454246521</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198734283447</v>
+        <v>2.12198758125305</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.52349996566772</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.95111513137817</v>
+        <v>1.95111525058746</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.39050006866455</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.8482825756073</v>
+        <v>1.84828245639801</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>2.36700010299683</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.83011281490326</v>
+        <v>1.83011269569397</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305147171021</v>
+        <v>1.80305159091949</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.48805856704712</v>
+        <v>1.48805868625641</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.5175940990448</v>
+        <v>1.51759397983551</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.99520003795624</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.54264509677887</v>
+        <v>1.54264497756958</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.91349995136261</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.47947645187378</v>
+        <v>1.47947633266449</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.99950003623962</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.54596984386444</v>
+        <v>1.54596972465515</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.03099989891052</v>
       </c>
       <c r="G1853" t="n">
-        <v>1.57032489776611</v>
+        <v>1.57032477855682</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.6344987154007</v>
+        <v>1.63449859619141</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.6344987154007</v>
+        <v>1.63449859619141</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222702980042</v>
+        <v>1.79222691059113</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.58037614822388</v>
+        <v>1.58037602901459</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681817054749</v>
+        <v>1.63681828975677</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831330299377</v>
+        <v>1.62831318378448</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.62058138847351</v>
+        <v>1.6205815076828</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.62985968589783</v>
+        <v>1.62985956668854</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006480693817</v>
+        <v>1.67006492614746</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.75820696353912</v>
+        <v>1.75820708274841</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.84634935855865</v>
+        <v>1.84634947776794</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.86954462528229</v>
+        <v>1.86954474449158</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.68552839756012</v>
+        <v>1.68552851676941</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.76593887805939</v>
+        <v>1.7659387588501</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.76748538017273</v>
+        <v>1.76748526096344</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.32100009918213</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.79454660415649</v>
+        <v>1.7945464849472</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.72727990150452</v>
+        <v>1.72728002071381</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.77057790756226</v>
+        <v>1.77057802677155</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.80150496959686</v>
+        <v>1.80150508880615</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985272407532</v>
+        <v>1.92985284328461</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.963099360466</v>
+        <v>1.96309947967529</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.9600065946579</v>
+        <v>1.96000671386719</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.97624349594116</v>
+        <v>1.97624337673187</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.95923328399658</v>
+        <v>1.95923340320587</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382130146027</v>
+        <v>1.95382106304169</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918203353882</v>
+        <v>1.94918191432953</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>2.61700010299683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.02340722084045</v>
+        <v>2.02340745925903</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959275245667</v>
+        <v>2.02959251403809</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.96077978610992</v>
+        <v>1.96077990531921</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>2.52900004386902</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.95536780357361</v>
+        <v>1.95536756515503</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.14170336723328</v>
+        <v>2.14170360565186</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.90974998474121</v>
+        <v>1.9097501039505</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025972366333</v>
+        <v>2.16025948524475</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.12160062789917</v>
+        <v>2.12160086631775</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.97624349594116</v>
+        <v>1.97624337673187</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.95459449291229</v>
+        <v>1.954594373703</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.963099360466</v>
+        <v>1.96309947967529</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.99402642250061</v>
+        <v>1.9940265417099</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.9600065946579</v>
+        <v>1.96000671386719</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.88810110092163</v>
+        <v>1.88810098171234</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763925075531</v>
+        <v>1.79763913154602</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.31100010871887</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.78681468963623</v>
+        <v>1.78681480884552</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.82933962345123</v>
+        <v>1.82933950424194</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645209789276</v>
+        <v>1.86645197868347</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.92676019668579</v>
+        <v>1.9267600774765</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.10768365859985</v>
+        <v>2.10768389701843</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.8618129491806</v>
+        <v>1.86181282997131</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.86722540855408</v>
+        <v>1.8672251701355</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737915992737</v>
+        <v>1.89737927913666</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.91748189926147</v>
+        <v>1.91748178005219</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.96077978610992</v>
+        <v>1.96077990531921</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.90124523639679</v>
+        <v>1.90124535560608</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>2.59899997711182</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.00949025154114</v>
+        <v>2.00949001312256</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.98552167415619</v>
+        <v>1.98552143573761</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397517204285</v>
+        <v>1.98397505283356</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.95614075660706</v>
+        <v>1.95614063739777</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.91052305698395</v>
+        <v>1.91052317619324</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.83475172519684</v>
+        <v>1.83475160598755</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062579631805</v>
+        <v>1.93062591552734</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237741947174</v>
+        <v>1.97237753868103</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866557121277</v>
+        <v>1.99866545200348</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964400291443</v>
+        <v>2.03964376449585</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.0551073551178</v>
+        <v>2.05510759353638</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.08680772781372</v>
+        <v>2.0868079662323</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443714141846</v>
+        <v>2.07443690299988</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>3.06100010871887</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.36669850349426</v>
+        <v>2.36669826507568</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G2007" t="n">
-        <v>2.3597400188446</v>
+        <v>2.35973978042603</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654799461365</v>
+        <v>2.18654775619507</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.28551483154297</v>
+        <v>2.28551459312439</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071821212769</v>
+        <v>2.40071797370911</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G2022" t="n">
-        <v>2.55458045005798</v>
+        <v>2.55458068847656</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.53447794914246</v>
+        <v>2.53447818756104</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876134872437</v>
+        <v>2.31876158714294</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.35046148300171</v>
+        <v>2.35046172142029</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37443017959595</v>
+        <v>2.37442994117737</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.35510063171387</v>
+        <v>2.35510087013245</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.52519989013672</v>
+        <v>2.5252001285553</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.53602457046509</v>
+        <v>2.53602433204651</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983903884888</v>
+        <v>2.52983927726746</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>3.53900003433228</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.73627758026123</v>
+        <v>2.73627781867981</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792646408081</v>
+        <v>2.75792622566223</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452571868896</v>
+        <v>2.69452595710754</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.75019478797913</v>
+        <v>2.75019454956055</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.99374604225159</v>
+        <v>2.99374580383301</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>3.93899989128113</v>
       </c>
       <c r="G2083" t="n">
-        <v>3.04554891586304</v>
+        <v>3.04554867744446</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G2094" t="n">
-        <v>3.308429479599</v>
+        <v>3.30842924118042</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G2100" t="n">
-        <v>3.19554543495178</v>
+        <v>3.1955451965332</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>4.1710000038147</v>
       </c>
       <c r="G2101" t="n">
-        <v>3.22492623329163</v>
+        <v>3.22492599487305</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.07338309288025</v>
+        <v>3.07338333129883</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972261428833</v>
+        <v>3.10972237586975</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>4.16300010681152</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.21874070167542</v>
+        <v>3.21874094009399</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693410873413</v>
+        <v>3.31693434715271</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739631652832</v>
+        <v>3.40739607810974</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471403121948</v>
+        <v>3.48471426963806</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667065620422</v>
+        <v>3.56667041778564</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2124" t="n">
-        <v>3.60300993919373</v>
+        <v>3.6030101776123</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.66022562980652</v>
+        <v>3.66022539138794</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G2129" t="n">
-        <v>3.76769709587097</v>
+        <v>3.76769733428955</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145707130432</v>
+        <v>3.90145683288574</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.98186731338501</v>
+        <v>3.98186755180359</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G2132" t="n">
-        <v>4.09320497512817</v>
+        <v>4.09320545196533</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>11.1660003662109</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>7772627</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>11.246000289917</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>11.0100002288818</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>11.0699996948242</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>11.0600004196167</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>11.0600004196167</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73571777344</v>
+        <v>1765.73583984375</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.04797363281</v>
+        <v>1491.0478515625</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26940917969</v>
+        <v>1523.26928710938</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1365.86657714844</v>
       </c>
       <c r="G13" t="n">
-        <v>1056.05822753906</v>
+        <v>1056.05810546875</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1062.68798828125</v>
       </c>
       <c r="G14" t="n">
-        <v>821.647094726562</v>
+        <v>821.647155761719</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1364.82470703125</v>
       </c>
       <c r="G20" t="n">
-        <v>1055.25268554688</v>
+        <v>1055.25256347656</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.311462402344</v>
+        <v>918.3115234375</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.532897949219</v>
+        <v>950.533020019531</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1119.98974609375</v>
       </c>
       <c r="G29" t="n">
-        <v>865.951599121094</v>
+        <v>865.95166015625</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.422912597656</v>
+        <v>905.4228515625</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366882324219</v>
+        <v>926.366760253906</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1066.85534667969</v>
       </c>
       <c r="G36" t="n">
-        <v>824.869262695312</v>
+        <v>824.869323730469</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1115.82238769531</v>
       </c>
       <c r="G37" t="n">
-        <v>862.7294921875</v>
+        <v>862.729553222656</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1024.7646484375</v>
       </c>
       <c r="G42" t="n">
-        <v>792.32568359375</v>
+        <v>792.325622558594</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1167.91491699219</v>
       </c>
       <c r="G46" t="n">
-        <v>903.006286621094</v>
+        <v>903.00634765625</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977966308594</v>
+        <v>927.977905273438</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03125</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810485839844</v>
+        <v>961.810363769531</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254089355469</v>
+        <v>997.254211425781</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1121.03161621094</v>
       </c>
       <c r="G61" t="n">
-        <v>866.757141113281</v>
+        <v>866.757202148438</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813171386719</v>
+        <v>845.813232421875</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1048.10205078125</v>
       </c>
       <c r="G63" t="n">
-        <v>810.36962890625</v>
+        <v>810.369567871094</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>962.670288085938</v>
       </c>
       <c r="G66" t="n">
-        <v>744.315673828125</v>
+        <v>744.315612792969</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1227.30041503906</v>
       </c>
       <c r="G73" t="n">
-        <v>948.921813964844</v>
+        <v>948.921875</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.197265625</v>
+        <v>1047.19738769531</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03125</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1441.92175292969</v>
       </c>
       <c r="G78" t="n">
-        <v>1114.86242675781</v>
+        <v>1114.8623046875</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80908203125</v>
+        <v>1019.80902099609</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1153.32897949219</v>
       </c>
       <c r="G93" t="n">
-        <v>891.728820800781</v>
+        <v>891.728759765625</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1168.95678710938</v>
       </c>
       <c r="G94" t="n">
-        <v>903.811889648438</v>
+        <v>903.811950683594</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1156.45458984375</v>
       </c>
       <c r="G96" t="n">
-        <v>894.1455078125</v>
+        <v>894.145446777344</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839538574219</v>
+        <v>907.839477539062</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.142578125</v>
+        <v>1010.14263916016</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17028808594</v>
+        <v>1014.17034912109</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.143920898438</v>
+        <v>952.14404296875</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1151.24523925781</v>
       </c>
       <c r="G114" t="n">
-        <v>890.117614746094</v>
+        <v>890.11767578125</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1038.10021972656</v>
       </c>
       <c r="G117" t="n">
-        <v>802.636413574219</v>
+        <v>802.636474609375</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368286132812</v>
+        <v>868.368225097656</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749328613281</v>
+        <v>731.749267578125</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118225097656</v>
+        <v>634.118286132812</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194732666016</v>
+        <v>453.194763183594</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549591064453</v>
+        <v>481.549652099609</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259460449219</v>
+        <v>538.259399414062</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710113525391</v>
+        <v>510.710052490234</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532653808594</v>
+        <v>496.532592773438</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>541.970886230469</v>
       </c>
       <c r="G151" t="n">
-        <v>419.0400390625</v>
+        <v>419.040069580078</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>551.764282226562</v>
       </c>
       <c r="G152" t="n">
-        <v>426.612091064453</v>
+        <v>426.612121582031</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384918212891</v>
+        <v>399.384948730469</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.5126953125</v>
+        <v>400.512725830078</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G162" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>503.630737304688</v>
       </c>
       <c r="G170" t="n">
-        <v>389.396270751953</v>
+        <v>389.396301269531</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724212646484</v>
+        <v>384.724182128906</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G175" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>509.465118408203</v>
       </c>
       <c r="G177" t="n">
-        <v>393.907287597656</v>
+        <v>393.907318115234</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436737060547</v>
+        <v>325.436706542969</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003753662109</v>
+        <v>309.003784179688</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>404.86328125</v>
       </c>
       <c r="G190" t="n">
-        <v>313.031433105469</v>
+        <v>313.031463623047</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742614746094</v>
+        <v>311.742584228516</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281982421875</v>
+        <v>291.281951904297</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843322753906</v>
+        <v>279.843353271484</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499145507812</v>
+        <v>270.499114990234</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>563.641357421875</v>
       </c>
       <c r="G208" t="n">
-        <v>435.795196533203</v>
+        <v>435.795166015625</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>723.044555664062</v>
       </c>
       <c r="G209" t="n">
-        <v>559.042297363281</v>
+        <v>559.042236328125</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266448974609</v>
+        <v>475.266510009766</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184143066406</v>
+        <v>434.184112548828</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906585693359</v>
+        <v>422.906616210938</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>484.0439453125</v>
       </c>
       <c r="G217" t="n">
-        <v>374.252197265625</v>
+        <v>374.252227783203</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>537.178344726562</v>
       </c>
       <c r="G219" t="n">
-        <v>415.334594726562</v>
+        <v>415.334564208984</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>558.015380859375</v>
       </c>
       <c r="G220" t="n">
-        <v>431.4453125</v>
+        <v>431.445281982422</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>537.595092773438</v>
       </c>
       <c r="G222" t="n">
-        <v>415.656799316406</v>
+        <v>415.656768798828</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>583.228149414062</v>
       </c>
       <c r="G224" t="n">
-        <v>450.939239501953</v>
+        <v>450.939270019531</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>454.246978759766</v>
       </c>
       <c r="G242" t="n">
-        <v>351.213836669922</v>
+        <v>351.2138671875</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>94.8084259033203</v>
       </c>
       <c r="G466" t="n">
-        <v>73.3038101196289</v>
+        <v>73.3038024902344</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.1715087890625</v>
+        <v>76.171516418457</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003921508789</v>
+        <v>76.3003997802734</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>97.3505477905273</v>
       </c>
       <c r="G469" t="n">
-        <v>75.2693176269531</v>
+        <v>75.2693099975586</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426254272461</v>
+        <v>76.0426330566406</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>95.4335403442383</v>
       </c>
       <c r="G473" t="n">
-        <v>73.7871246337891</v>
+        <v>73.7871322631836</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064865112305</v>
+        <v>53.9064903259277</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>85.6401443481445</v>
       </c>
       <c r="G484" t="n">
-        <v>66.215087890625</v>
+        <v>66.2150955200195</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.1540451049805</v>
+        <v>63.154052734375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906616210938</v>
+        <v>64.9906692504883</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>83.9731826782227</v>
       </c>
       <c r="G491" t="n">
-        <v>64.9262313842773</v>
+        <v>64.9262390136719</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539855957031</v>
+        <v>66.0539779663086</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.1540451049805</v>
+        <v>63.154052734375</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618530273438</v>
+        <v>61.9618606567383</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.156322479248</v>
+        <v>61.1563148498535</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>81.5977630615234</v>
       </c>
       <c r="G514" t="n">
-        <v>63.0896034240723</v>
+        <v>63.0896110534668</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695938110352</v>
+        <v>63.6695861816406</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184867858887</v>
+        <v>63.2184944152832</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397117614746</v>
+        <v>58.7397079467773</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>75.1591186523438</v>
       </c>
       <c r="G536" t="n">
-        <v>58.1113929748535</v>
+        <v>58.111385345459</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.0607833862305</v>
+        <v>60.060791015625</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.836368560791</v>
+        <v>58.8363761901855</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.46923828125</v>
+        <v>55.4692344665527</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.9536895751953</v>
+        <v>54.953685760498</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>69.4706192016602</v>
       </c>
       <c r="G548" t="n">
-        <v>53.7131652832031</v>
+        <v>53.7131614685059</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.005428314209</v>
+        <v>52.0054321289062</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832160949707</v>
+        <v>51.6832122802734</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184745788574</v>
+        <v>40.5184783935547</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>53.1969032287598</v>
       </c>
       <c r="G576" t="n">
-        <v>41.1306838989258</v>
+        <v>41.130687713623</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>61.0524597167969</v>
       </c>
       <c r="G578" t="n">
-        <v>47.2044296264648</v>
+        <v>47.2044258117676</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>58.9687576293945</v>
       </c>
       <c r="G579" t="n">
-        <v>45.5933570861816</v>
+        <v>45.5933532714844</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.175609588623</v>
+        <v>44.1756134033203</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>56.5933380126953</v>
       </c>
       <c r="G588" t="n">
-        <v>43.7567367553711</v>
+        <v>43.7567329406738</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>56.1974334716797</v>
       </c>
       <c r="G589" t="n">
-        <v>43.4506301879883</v>
+        <v>43.450626373291</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>54.780517578125</v>
       </c>
       <c r="G597" t="n">
-        <v>42.3550987243652</v>
+        <v>42.3551025390625</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.8211784362793</v>
+        <v>43.821174621582</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431777954102</v>
+        <v>52.8431816101074</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>58.7603874206543</v>
       </c>
       <c r="G607" t="n">
-        <v>45.4322471618652</v>
+        <v>45.4322509765625</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>59.0312690734863</v>
       </c>
       <c r="G608" t="n">
-        <v>45.6416893005371</v>
+        <v>45.6416854858398</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194770812988</v>
+        <v>45.3194732666016</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250747680664</v>
+        <v>43.2250785827637</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>57.9269065856934</v>
       </c>
       <c r="G623" t="n">
-        <v>44.7878189086914</v>
+        <v>44.7878227233887</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>56.6975250244141</v>
       </c>
       <c r="G630" t="n">
-        <v>43.837287902832</v>
+        <v>43.8372917175293</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>53.1135559082031</v>
       </c>
       <c r="G634" t="n">
-        <v>41.0662422180176</v>
+        <v>41.0662460327148</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.3734817504883</v>
+        <v>40.373477935791</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.5679397583008</v>
+        <v>39.567943572998</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062690734863</v>
+        <v>39.9062728881836</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>51.0715293884277</v>
       </c>
       <c r="G642" t="n">
-        <v>39.4873924255371</v>
+        <v>39.4873886108398</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>51.1965522766113</v>
       </c>
       <c r="G644" t="n">
-        <v>39.584056854248</v>
+        <v>39.5840606689453</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>51.5299453735352</v>
       </c>
       <c r="G661" t="n">
-        <v>39.8418273925781</v>
+        <v>39.8418312072754</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>49.5921020507812</v>
       </c>
       <c r="G666" t="n">
-        <v>38.3435325622559</v>
+        <v>38.3435287475586</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>46.3415260314941</v>
       </c>
       <c r="G668" t="n">
-        <v>35.8302574157715</v>
+        <v>35.8302536010742</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>45.570556640625</v>
       </c>
       <c r="G675" t="n">
-        <v>35.2341575622559</v>
+        <v>35.2341613769531</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580749511719</v>
+        <v>34.0580787658691</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>47.1958427429199</v>
       </c>
       <c r="G690" t="n">
-        <v>36.490795135498</v>
+        <v>36.4907989501953</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057678222656</v>
+        <v>37.5057716369629</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563026428223</v>
+        <v>38.4563064575195</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>37.0377998352051</v>
       </c>
       <c r="G710" t="n">
-        <v>28.6368198394775</v>
+        <v>28.6368179321289</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884838104248</v>
+        <v>28.5884857177734</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>36.089714050293</v>
       </c>
       <c r="G713" t="n">
-        <v>27.9037780761719</v>
+        <v>27.9037799835205</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532432556152</v>
+        <v>26.9532451629639</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241111755371</v>
+        <v>25.6241130828857</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>28.5467128753662</v>
       </c>
       <c r="G719" t="n">
-        <v>22.0716953277588</v>
+        <v>22.0716972351074</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>29.2864265441895</v>
       </c>
       <c r="G720" t="n">
-        <v>22.6436252593994</v>
+        <v>22.6436233520508</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.5260524749756</v>
       </c>
       <c r="G721" t="n">
-        <v>22.8288993835449</v>
+        <v>22.8288974761963</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177558898926</v>
+        <v>24.1177577972412</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>28.8071765899658</v>
       </c>
       <c r="G740" t="n">
-        <v>22.273078918457</v>
+        <v>22.2730808258057</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G742" t="n">
-        <v>24.8105182647705</v>
+        <v>24.8105163574219</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>36.7564964294434</v>
       </c>
       <c r="G747" t="n">
-        <v>28.4193210601807</v>
+        <v>28.419319152832</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782283782959</v>
+        <v>27.6782302856445</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363185882568</v>
+        <v>26.2363166809082</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193939208984</v>
+        <v>25.5193920135498</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G756" t="n">
-        <v>24.8105182647705</v>
+        <v>24.8105163574219</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983127593994</v>
+        <v>24.1983108520508</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399700164795</v>
+        <v>24.4399719238281</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058681488037</v>
+        <v>21.8058700561523</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>25.4107418060303</v>
       </c>
       <c r="G777" t="n">
-        <v>19.6470317840576</v>
+        <v>19.647029876709</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>25.598274230957</v>
       </c>
       <c r="G780" t="n">
-        <v>19.7920265197754</v>
+        <v>19.792028427124</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189617156982</v>
+        <v>20.2189598083496</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>24.9523277282715</v>
       </c>
       <c r="G787" t="n">
-        <v>19.292594909668</v>
+        <v>19.2925930023193</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136722564697</v>
+        <v>20.6136741638184</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G839" t="n">
-        <v>22.4583530426025</v>
+        <v>22.4583549499512</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>27.671558380127</v>
       </c>
       <c r="G842" t="n">
-        <v>21.3950443267822</v>
+        <v>21.3950462341309</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150596618652</v>
+        <v>20.8150577545166</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.4003238677979</v>
       </c>
       <c r="G852" t="n">
-        <v>19.6389751434326</v>
+        <v>19.6389770507812</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G856" t="n">
-        <v>18.6723327636719</v>
+        <v>18.6723308563232</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G860" t="n">
-        <v>18.4145584106445</v>
+        <v>18.4145603179932</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G861" t="n">
-        <v>18.1245670318604</v>
+        <v>18.124568939209</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G864" t="n">
-        <v>17.7701320648193</v>
+        <v>17.770133972168</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G866" t="n">
-        <v>17.1418132781982</v>
+        <v>17.1418113708496</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>21.7538452148438</v>
       </c>
       <c r="G868" t="n">
-        <v>16.8195991516113</v>
+        <v>16.8195972442627</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>21.6079864501953</v>
       </c>
       <c r="G870" t="n">
-        <v>16.706823348999</v>
+        <v>16.7068252563477</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907119750977</v>
+        <v>16.6907138824463</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134963989258</v>
+        <v>16.5134944915771</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.110725402832</v>
+        <v>16.1107273101807</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>21.9205417633057</v>
       </c>
       <c r="G884" t="n">
-        <v>16.9484844207764</v>
+        <v>16.9484825134277</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290374755859</v>
+        <v>17.0290393829346</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406784057617</v>
+        <v>18.1406764984131</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493412017822</v>
+        <v>27.5493431091309</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321659088135</v>
+        <v>25.6321678161621</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>34.4435882568359</v>
       </c>
       <c r="G900" t="n">
-        <v>26.6310291290283</v>
+        <v>26.631031036377</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G906" t="n">
-        <v>23.8922080993652</v>
+        <v>23.8922061920166</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.9105892181396</v>
+        <v>21.910587310791</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.5838356018066</v>
+        <v>25.583833694458</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516128540039</v>
+        <v>25.5516109466553</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416080474854</v>
+        <v>25.8416061401367</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>33.4850845336914</v>
       </c>
       <c r="G939" t="n">
-        <v>25.8899364471436</v>
+        <v>25.8899345397949</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>34.0268478393555</v>
       </c>
       <c r="G942" t="n">
-        <v>26.3088150024414</v>
+        <v>26.30881690979</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G948" t="n">
-        <v>25.0360698699951</v>
+        <v>25.0360717773438</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G950" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G951" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>30.5262298583984</v>
       </c>
       <c r="G956" t="n">
-        <v>23.6022148132324</v>
+        <v>23.6022129058838</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727630615234</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G962" t="n">
-        <v>23.8922080993652</v>
+        <v>23.8922061920166</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>30.8596210479736</v>
       </c>
       <c r="G964" t="n">
-        <v>23.8599853515625</v>
+        <v>23.8599834442139</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>31.9431476593018</v>
       </c>
       <c r="G968" t="n">
-        <v>24.6977424621582</v>
+        <v>24.6977443695068</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G973" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.312219619751</v>
+        <v>23.3122215270996</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G980" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>30.4428825378418</v>
       </c>
       <c r="G989" t="n">
-        <v>23.5377731323242</v>
+        <v>23.5377712249756</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727630615234</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G996" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544490814209</v>
+        <v>23.0544509887695</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G999" t="n">
-        <v>22.7483444213867</v>
+        <v>22.7483463287354</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1005" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1007" t="n">
-        <v>22.7966785430908</v>
+        <v>22.7966766357422</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1009" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844711303711</v>
+        <v>22.1844692230225</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G1016" t="n">
-        <v>22.7483444213867</v>
+        <v>22.7483463287354</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G1017" t="n">
-        <v>22.4583530426025</v>
+        <v>22.4583549499512</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1020" t="n">
-        <v>22.7966785430908</v>
+        <v>22.7966766357422</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.7104473114014</v>
+        <v>27.71044921875</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493412017822</v>
+        <v>27.5493431091309</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821304321289</v>
+        <v>27.0821323394775</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>35.7146453857422</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.6137828826904</v>
+        <v>27.6137847900391</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.627628326416</v>
+        <v>29.6276245117188</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326614379883</v>
+        <v>28.0326633453369</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>37.1940765380859</v>
       </c>
       <c r="G1040" t="n">
-        <v>28.7576484680176</v>
+        <v>28.7576465606689</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737560272217</v>
+        <v>28.7737598419189</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936332702637</v>
+        <v>33.9936370849609</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>42.5075149536133</v>
       </c>
       <c r="G1052" t="n">
-        <v>32.8658790588379</v>
+        <v>32.8658828735352</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820652008057</v>
+        <v>29.9820613861084</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770225524902</v>
+        <v>31.5770263671875</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571472167969</v>
+        <v>26.3571491241455</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610492706299</v>
+        <v>25.7610511779785</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3787784576416</v>
       </c>
       <c r="G1071" t="n">
-        <v>16.5296039581299</v>
+        <v>16.5296058654785</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.7953433990479</v>
       </c>
       <c r="G1072" t="n">
-        <v>16.0785045623779</v>
+        <v>16.0785064697266</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.8023529052734</v>
+        <v>17.8023548126221</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>22.3164443969727</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.2545890808105</v>
+        <v>17.2545871734619</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.1245670318604</v>
+        <v>18.124568939209</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1102" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G1106" t="n">
-        <v>17.7701320648193</v>
+        <v>17.770133972168</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1115" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683616638184</v>
+        <v>22.1683597564697</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G1124" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G1125" t="n">
-        <v>25.0360698699951</v>
+        <v>25.0360717773438</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021457672119</v>
+        <v>26.5021438598633</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.229398727417</v>
+        <v>25.2293968200684</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.03493309021</v>
+        <v>26.0349349975586</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460746765137</v>
+        <v>24.7460765838623</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>31.8597984313965</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.63330078125</v>
+        <v>24.6332988739014</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>32.7974662780762</v>
       </c>
       <c r="G1153" t="n">
-        <v>25.358283996582</v>
+        <v>25.3582859039307</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>37.5066299438477</v>
       </c>
       <c r="G1155" t="n">
-        <v>28.9993076324463</v>
+        <v>28.9993057250977</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303916931152</v>
+        <v>30.0303955078125</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>36.4856185913086</v>
       </c>
       <c r="G1159" t="n">
-        <v>28.2098827362061</v>
+        <v>28.2098846435547</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049129486084</v>
+        <v>26.9049110412598</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>34.7353096008301</v>
       </c>
       <c r="G1161" t="n">
-        <v>26.8565826416016</v>
+        <v>26.8565807342529</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655216217041</v>
+        <v>24.6655197143555</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>30.3386974334717</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.457218170166</v>
+        <v>23.4572200775146</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>31.2555255889893</v>
       </c>
       <c r="G1171" t="n">
-        <v>24.1660919189453</v>
+        <v>24.1660900115967</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>29.3801937103271</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7161235809326</v>
+        <v>22.7161254882812</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094543457031</v>
+        <v>22.9094524383545</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416751861572</v>
+        <v>22.9416732788086</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039161682129</v>
+        <v>22.1039180755615</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672920227051</v>
+        <v>20.2672939300537</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.6584911346436</v>
+        <v>16.6584892272949</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>22.7748603820801</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.6090259552002</v>
+        <v>17.6090240478516</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1240" t="n">
-        <v>19.2684288024902</v>
+        <v>19.2684268951416</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.7839698791504</v>
+        <v>19.783971786499</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>21.962215423584</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.9807052612305</v>
+        <v>16.9807033538818</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6584911346436</v>
+        <v>16.6584892272949</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934791564941</v>
+        <v>17.0934810638428</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801406860352</v>
+        <v>17.4801387786865</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.6723327636719</v>
+        <v>18.6723308563232</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>26.5255222320557</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.5089550018311</v>
+        <v>20.5089530944824</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>25.9629230499268</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.0739631652832</v>
+        <v>20.0739650726318</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>24.8793983459473</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.2362079620361</v>
+        <v>19.2362060546875</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395435333252</v>
+        <v>19.1395416259766</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750980377197</v>
+        <v>19.0750999450684</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1330" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.6078910827637</v>
+        <v>18.607889175415</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153793334961</v>
+        <v>19.1153774261475</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.8334407806396</v>
+        <v>18.833438873291</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353908538818</v>
+        <v>18.5353927612305</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864940643311</v>
+        <v>18.9864921569824</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1345" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112266540527</v>
+        <v>18.5112247467041</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1354" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>24.2959613800049</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.7851047515869</v>
+        <v>18.7851066589355</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.2684288024902</v>
+        <v>19.2684268951416</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531345367432</v>
+        <v>19.9531364440918</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397941589355</v>
+        <v>20.3397922515869</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598056793213</v>
+        <v>19.7598075866699</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>23.1707630157471</v>
       </c>
       <c r="G1402" t="n">
-        <v>17.9151287078857</v>
+        <v>17.9151268005371</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>21.9830532073975</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.9968166351318</v>
+        <v>16.9968185424805</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G1410" t="n">
-        <v>17.1418132781982</v>
+        <v>17.1418113708496</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1416" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.4103889465332</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.1004009246826</v>
+        <v>18.1004028320312</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428771972656</v>
+        <v>19.0428791046143</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>23.9208946228027</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.4951133728027</v>
+        <v>18.4951114654541</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742847442627</v>
+        <v>18.3742828369141</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292861938477</v>
+        <v>18.2292881011963</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1434" t="n">
-        <v>18.0923442840576</v>
+        <v>18.0923461914062</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>23.4520626068115</v>
       </c>
       <c r="G1440" t="n">
-        <v>18.1326217651367</v>
+        <v>18.1326236724854</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1444" t="n">
-        <v>18.0923442840576</v>
+        <v>18.0923461914062</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392929077148</v>
+        <v>17.9392948150635</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>22.5977458953857</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.4720821380615</v>
+        <v>17.4720840454102</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>23.2645282745361</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.9876270294189</v>
+        <v>17.9876251220703</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8023529052734</v>
+        <v>17.8023548126221</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>21.3475246429443</v>
       </c>
       <c r="G1485" t="n">
-        <v>16.5054397583008</v>
+        <v>16.5054378509521</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1489" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765544891357</v>
+        <v>16.3765525817871</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.9753942489624</v>
+        <v>15.975396156311</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668664932251</v>
+        <v>14.9668645858765</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9325141906738</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.6382064819336</v>
+        <v>14.6382083892822</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867658615112</v>
+        <v>14.4867668151855</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.293436050415</v>
+        <v>14.2934370040894</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013570785522</v>
+        <v>13.0013580322266</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379812240601</v>
+        <v>14.8379793167114</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.654314994812</v>
+        <v>14.6543169021606</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.6253175735474</v>
+        <v>14.625316619873</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.518988609314</v>
+        <v>14.5189876556396</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287672042847</v>
+        <v>14.4287662506104</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>18.5866184234619</v>
       </c>
       <c r="G1526" t="n">
-        <v>14.3707675933838</v>
+        <v>14.3707666397095</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958639144897</v>
+        <v>14.9958648681641</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024209976196</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316484451294</v>
+        <v>14.7316465377808</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154230117798</v>
+        <v>14.8154249191284</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>18.3365745544434</v>
       </c>
       <c r="G1543" t="n">
-        <v>14.1774396896362</v>
+        <v>14.1774387359619</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.7116413116455</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.467432975769</v>
+        <v>14.4674320220947</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994276046753</v>
+        <v>14.6994256973267</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.5867958068848</v>
       </c>
       <c r="G1549" t="n">
-        <v>15.1440830230713</v>
+        <v>15.1440811157227</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024209976196</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.6435136795044</v>
+        <v>15.643515586853</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>21.6496601104736</v>
       </c>
       <c r="G1558" t="n">
-        <v>16.7390441894531</v>
+        <v>16.7390460968018</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147443771362</v>
+        <v>15.4147424697876</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>19.1325492858887</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.7928686141968</v>
+        <v>14.7928705215454</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.3654584884644</v>
+        <v>13.36545753479</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>18.1573753356934</v>
       </c>
       <c r="G1566" t="n">
-        <v>14.0388870239258</v>
+        <v>14.0388860702515</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.88649559021</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.8294477462769</v>
+        <v>13.8294486999512</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781192779541</v>
+        <v>13.5781202316284</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584480285645</v>
+        <v>13.8584470748901</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151958465576</v>
+        <v>15.0151977539062</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>20.0952186584473</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5371837615967</v>
+        <v>15.537184715271</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>20.1202239990234</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.5565176010132</v>
+        <v>15.5565195083618</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8304004669189</v>
+        <v>15.8303985595703</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.0699729919434</v>
+        <v>15.069974899292</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199178695679</v>
+        <v>15.1199159622192</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>18.6178741455078</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.3949337005615</v>
+        <v>14.3949346542358</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660474777222</v>
+        <v>14.2660484313965</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585592269897</v>
+        <v>13.7585582733154</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116125106812</v>
+        <v>13.9116115570068</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>17.8573226928711</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8068914413452</v>
+        <v>13.8068923950195</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722211837769</v>
+        <v>11.6722221374512</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519580841064</v>
+        <v>11.0519590377808</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.3902835845947</v>
+        <v>11.390284538269</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3902835845947</v>
+        <v>11.390284538269</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433340072632</v>
+        <v>11.5433349609375</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.970269203186</v>
+        <v>11.9702701568604</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>15.5860891342163</v>
       </c>
       <c r="G1628" t="n">
-        <v>12.0508232116699</v>
+        <v>12.0508241653442</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.1903629302979</v>
       </c>
       <c r="G1630" t="n">
-        <v>12.5180349349976</v>
+        <v>12.5180358886719</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.0445022583008</v>
       </c>
       <c r="G1631" t="n">
-        <v>12.4052591323853</v>
+        <v>12.4052581787109</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805246353149</v>
+        <v>12.8805255889893</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.253342628479</v>
+        <v>11.2533416748047</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439023971558</v>
+        <v>11.0439033508301</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136325836182</v>
+        <v>10.7136335372925</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535598754883</v>
+        <v>8.34535694122314</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971380233765</v>
+        <v>7.34971284866333</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>8.91824340820312</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.89539098739624</v>
+        <v>6.8953914642334</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>9.3766565322876</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.24982595443726</v>
+        <v>7.2498254776001</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316919326782</v>
+        <v>6.86316871643066</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539722442627</v>
+        <v>6.60539770126343</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>8.8223934173584</v>
       </c>
       <c r="G1676" t="n">
-        <v>6.82128143310547</v>
+        <v>6.82128190994263</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927337646484</v>
+        <v>7.16927289962769</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.74072790145874</v>
+        <v>6.7407283782959</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973346710205</v>
+        <v>6.47973394393921</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>7.91806602478027</v>
       </c>
       <c r="G1689" t="n">
-        <v>6.1220760345459</v>
+        <v>6.12207555770874</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799428939819</v>
+        <v>4.88799476623535</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>6.05523681640625</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.68177700042725</v>
+        <v>4.68177652359009</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555204391479</v>
+        <v>4.76555252075195</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.91699314117432</v>
+        <v>4.91699361801147</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.91699314117432</v>
+        <v>4.91699361801147</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>6.2302680015564</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.81710720062256</v>
+        <v>4.8171067237854</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179761886597</v>
+        <v>3.81179785728455</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.68311882019043</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.62088489532471</v>
+        <v>3.62088513374329</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.55331492424011</v>
+        <v>1.5533150434494</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089272975922</v>
+        <v>1.53089284896851</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393748760223</v>
+        <v>1.37393760681152</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006953716278</v>
+        <v>1.46006965637207</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.88339996337891</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.45620369911194</v>
+        <v>1.45620381832123</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537925720215</v>
+        <v>1.44537937641144</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903848648071</v>
+        <v>1.46903860569</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.52161467075348</v>
+        <v>1.52161455154419</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.50213050842285</v>
+        <v>1.50213062763214</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.06299996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.5950665473938</v>
+        <v>1.59506642818451</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490919589996</v>
+        <v>1.71490931510925</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702329158783</v>
+        <v>1.67702341079712</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.6031848192215</v>
+        <v>1.60318493843079</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259310245514</v>
+        <v>1.56259298324585</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.65305495262146</v>
+        <v>1.65305483341217</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>2.10450005531311</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.62715351581573</v>
+        <v>1.62715339660645</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.79377329349518</v>
+        <v>1.79377341270447</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552491664886</v>
+        <v>1.83552515506744</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>2.63949990272522</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.04080367088318</v>
+        <v>2.04080390930176</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.0338454246521</v>
+        <v>2.03384518623352</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198758125305</v>
+        <v>2.12198734283447</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.90665745735168</v>
+        <v>1.9066573381424</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305159091949</v>
+        <v>1.80305147171021</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.13649988174438</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.65189504623413</v>
+        <v>1.65189492702484</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46208000183105</v>
+        <v>1.46207988262177</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.51759397983551</v>
+        <v>1.5175940990448</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222691059113</v>
+        <v>1.79222702980042</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666093826294</v>
+        <v>1.75666081905365</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630158901215</v>
+        <v>1.68630146980286</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831318378448</v>
+        <v>1.6283130645752</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.64686954021454</v>
+        <v>1.64686965942383</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.73501169681549</v>
+        <v>1.73501181602478</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.68939423561096</v>
+        <v>1.68939435482025</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.6205815076828</v>
+        <v>1.62058138847351</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006492614746</v>
+        <v>1.67006480693817</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.73037266731262</v>
+        <v>1.73037254810333</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.75820708274841</v>
+        <v>1.7582072019577</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011617660522</v>
+        <v>1.68011629581451</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65769398212433</v>
+        <v>1.65769410133362</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.7659387588501</v>
+        <v>1.76593887805939</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.80073201656342</v>
+        <v>1.80073189735413</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82701992988586</v>
+        <v>1.82702016830444</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.74583613872528</v>
+        <v>1.74583625793457</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645557880402</v>
+        <v>1.71645545959473</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985284328461</v>
+        <v>1.92985260486603</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309947967529</v>
+        <v>1.96309924125671</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918191432953</v>
+        <v>1.94918215274811</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562405586243</v>
+        <v>2.00562429428101</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959251403809</v>
+        <v>2.02959275245667</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025948524475</v>
+        <v>2.16025972366333</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.02263402938843</v>
+        <v>2.02263379096985</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.954594373703</v>
+        <v>1.95459449291229</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309947967529</v>
+        <v>1.96309924125671</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763913154602</v>
+        <v>1.79763925075531</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.7497022151947</v>
+        <v>1.74970209598541</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310272216797</v>
+        <v>1.81310284137726</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645197868347</v>
+        <v>1.86645221710205</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866893291473</v>
+        <v>1.84866917133331</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737927913666</v>
+        <v>1.89737904071808</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639724731445</v>
+        <v>2.00639748573303</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.90124535560608</v>
+        <v>1.9012451171875</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397505283356</v>
+        <v>1.98397529125214</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.85872030258179</v>
+        <v>1.85872042179108</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062591552734</v>
+        <v>1.93062567710876</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237753868103</v>
+        <v>1.97237777709961</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964376449585</v>
+        <v>2.03964400291443</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.0868079662323</v>
+        <v>2.08680772781372</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443690299988</v>
+        <v>2.07443714141846</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>3.06100010871887</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.36669826507568</v>
+        <v>2.36669850349426</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654775619507</v>
+        <v>2.18654799461365</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716347694397</v>
+        <v>2.30716371536255</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071797370911</v>
+        <v>2.40071821212769</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921983718872</v>
+        <v>2.55921959877014</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.35742044448853</v>
+        <v>2.35742020606995</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876158714294</v>
+        <v>2.31876134872437</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061571121216</v>
+        <v>2.38061547279358</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.3643786907196</v>
+        <v>2.36437892913818</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37442994117737</v>
+        <v>2.37443017959595</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.38757419586182</v>
+        <v>2.3875744342804</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.5777759552002</v>
+        <v>2.57777619361877</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334228515625</v>
+        <v>2.61334252357483</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597308158875</v>
+        <v>2.52597284317017</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.5252001285553</v>
+        <v>2.52519989013672</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710898399353</v>
+        <v>2.44710874557495</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.49891209602356</v>
+        <v>2.49891185760498</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.49659252166748</v>
+        <v>2.4965922832489</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>3.38899993896484</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.62030076980591</v>
+        <v>2.62030053138733</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983927726746</v>
+        <v>2.52983903884888</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792622566223</v>
+        <v>2.75792646408081</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467970848083</v>
+        <v>2.72467994689941</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452595710754</v>
+        <v>2.69452571868896</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.83137845993042</v>
+        <v>2.83137822151184</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2087" t="n">
-        <v>3.14219617843628</v>
+        <v>3.14219641685486</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188447952271</v>
+        <v>3.23188471794128</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.36487150192261</v>
+        <v>3.36487126350403</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>4.20900011062622</v>
       </c>
       <c r="G2096" t="n">
-        <v>3.25430703163147</v>
+        <v>3.25430679321289</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343133926392</v>
+        <v>3.23343110084534</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693434715271</v>
+        <v>3.31693458557129</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739607810974</v>
+        <v>3.40739631652832</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471426963806</v>
+        <v>3.48471403121948</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G2119" t="n">
-        <v>3.47466254234314</v>
+        <v>3.47466278076172</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2120" t="n">
-        <v>3.51796054840088</v>
+        <v>3.51796078681946</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811105728149</v>
+        <v>3.69811153411865</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409482955933</v>
+        <v>3.51409506797791</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667041778564</v>
+        <v>3.56667065620422</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.62002015113831</v>
+        <v>3.62002038955688</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145683288574</v>
+        <v>3.9014573097229</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>11.0600004196167</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>7332430</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>11.2740001678467</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>11.1560001373291</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>11.1879997253418</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>11.1879997253418</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73571777344</v>
+        <v>1765.73583984375</v>
       </c>
       <c r="H4" t="n">
         <v>22853</v>
@@ -514,7 +514,7 @@
         <v>2208.72412109375</v>
       </c>
       <c r="G5" t="n">
-        <v>1707.73718261719</v>
+        <v>1707.7373046875</v>
       </c>
       <c r="H5" t="n">
         <v>38406</v>
@@ -572,7 +572,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.04797363281</v>
+        <v>1491.0478515625</v>
       </c>
       <c r="H7" t="n">
         <v>58243</v>
@@ -601,7 +601,7 @@
         <v>1933.67529296875</v>
       </c>
       <c r="G8" t="n">
-        <v>1495.07556152344</v>
+        <v>1495.07543945312</v>
       </c>
       <c r="H8" t="n">
         <v>53763</v>
@@ -659,7 +659,7 @@
         <v>2005.56311035156</v>
       </c>
       <c r="G10" t="n">
-        <v>1550.65771484375</v>
+        <v>1550.65759277344</v>
       </c>
       <c r="H10" t="n">
         <v>43759</v>
@@ -717,7 +717,7 @@
         <v>1595.07385253906</v>
       </c>
       <c r="G12" t="n">
-        <v>1233.27624511719</v>
+        <v>1233.2763671875</v>
       </c>
       <c r="H12" t="n">
         <v>58224</v>
@@ -775,7 +775,7 @@
         <v>1062.68798828125</v>
       </c>
       <c r="G14" t="n">
-        <v>821.647094726562</v>
+        <v>821.647155761719</v>
       </c>
       <c r="H14" t="n">
         <v>36638</v>
@@ -920,7 +920,7 @@
         <v>1481.51208496094</v>
       </c>
       <c r="G19" t="n">
-        <v>1145.47290039062</v>
+        <v>1145.47277832031</v>
       </c>
       <c r="H19" t="n">
         <v>52360</v>
@@ -949,7 +949,7 @@
         <v>1364.82470703125</v>
       </c>
       <c r="G20" t="n">
-        <v>1055.25268554688</v>
+        <v>1055.25256347656</v>
       </c>
       <c r="H20" t="n">
         <v>48851</v>
@@ -978,7 +978,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14123535156</v>
+        <v>1068.14135742188</v>
       </c>
       <c r="H21" t="n">
         <v>67666</v>
@@ -1094,7 +1094,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.311462402344</v>
+        <v>918.3115234375</v>
       </c>
       <c r="H25" t="n">
         <v>64565</v>
@@ -1123,7 +1123,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.532897949219</v>
+        <v>950.533020019531</v>
       </c>
       <c r="H26" t="n">
         <v>64029</v>
@@ -1152,7 +1152,7 @@
         <v>1082.48315429688</v>
       </c>
       <c r="G27" t="n">
-        <v>836.952331542969</v>
+        <v>836.952392578125</v>
       </c>
       <c r="H27" t="n">
         <v>42864</v>
@@ -1210,7 +1210,7 @@
         <v>1119.98974609375</v>
       </c>
       <c r="G29" t="n">
-        <v>865.951599121094</v>
+        <v>865.95166015625</v>
       </c>
       <c r="H29" t="n">
         <v>60147</v>
@@ -1239,7 +1239,7 @@
         <v>1009.34521484375</v>
       </c>
       <c r="G30" t="n">
-        <v>780.403625488281</v>
+        <v>780.403686523438</v>
       </c>
       <c r="H30" t="n">
         <v>46957</v>
@@ -1268,7 +1268,7 @@
         <v>956.8359375</v>
       </c>
       <c r="G31" t="n">
-        <v>739.804626464844</v>
+        <v>739.8046875</v>
       </c>
       <c r="H31" t="n">
         <v>71729</v>
@@ -1297,7 +1297,7 @@
         <v>1044.97644042969</v>
       </c>
       <c r="G32" t="n">
-        <v>807.952941894531</v>
+        <v>807.953002929688</v>
       </c>
       <c r="H32" t="n">
         <v>67475</v>
@@ -1326,7 +1326,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.422912597656</v>
+        <v>905.4228515625</v>
       </c>
       <c r="H33" t="n">
         <v>78116</v>
@@ -1384,7 +1384,7 @@
         <v>1077.27392578125</v>
       </c>
       <c r="G35" t="n">
-        <v>832.924682617188</v>
+        <v>832.924621582031</v>
       </c>
       <c r="H35" t="n">
         <v>48406</v>
@@ -1413,7 +1413,7 @@
         <v>1066.85534667969</v>
       </c>
       <c r="G36" t="n">
-        <v>824.869262695312</v>
+        <v>824.869323730469</v>
       </c>
       <c r="H36" t="n">
         <v>40227</v>
@@ -1500,7 +1500,7 @@
         <v>1073.1064453125</v>
       </c>
       <c r="G39" t="n">
-        <v>829.702453613281</v>
+        <v>829.702514648438</v>
       </c>
       <c r="H39" t="n">
         <v>36745</v>
@@ -1529,7 +1529,7 @@
         <v>1079.35754394531</v>
       </c>
       <c r="G40" t="n">
-        <v>834.535705566406</v>
+        <v>834.53564453125</v>
       </c>
       <c r="H40" t="n">
         <v>38826</v>
@@ -1587,7 +1587,7 @@
         <v>1024.7646484375</v>
       </c>
       <c r="G42" t="n">
-        <v>792.32568359375</v>
+        <v>792.325622558594</v>
       </c>
       <c r="H42" t="n">
         <v>166009</v>
@@ -1790,7 +1790,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G49" t="n">
-        <v>853.868591308594</v>
+        <v>853.86865234375</v>
       </c>
       <c r="H49" t="n">
         <v>45335</v>
@@ -1819,7 +1819,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G50" t="n">
-        <v>853.868591308594</v>
+        <v>853.86865234375</v>
       </c>
       <c r="H50" t="n">
         <v>70901</v>
@@ -1848,7 +1848,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977966308594</v>
+        <v>927.977905273438</v>
       </c>
       <c r="H51" t="n">
         <v>78651</v>
@@ -1877,7 +1877,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03131103516</v>
       </c>
       <c r="H52" t="n">
         <v>99090</v>
@@ -1906,7 +1906,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810485839844</v>
+        <v>961.810424804688</v>
       </c>
       <c r="H53" t="n">
         <v>82251</v>
@@ -1935,7 +1935,7 @@
         <v>1245.01184082031</v>
       </c>
       <c r="G54" t="n">
-        <v>962.615966796875</v>
+        <v>962.616027832031</v>
       </c>
       <c r="H54" t="n">
         <v>47448</v>
@@ -1964,7 +1964,7 @@
         <v>1193.96118164062</v>
       </c>
       <c r="G55" t="n">
-        <v>923.144714355469</v>
+        <v>923.144775390625</v>
       </c>
       <c r="H55" t="n">
         <v>43553</v>
@@ -1993,7 +1993,7 @@
         <v>1240.84448242188</v>
       </c>
       <c r="G56" t="n">
-        <v>959.393920898438</v>
+        <v>959.393859863281</v>
       </c>
       <c r="H56" t="n">
         <v>50887</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254089355469</v>
+        <v>997.254028320312</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2080,7 +2080,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199462890625</v>
+        <v>960.199340820312</v>
       </c>
       <c r="H59" t="n">
         <v>31218</v>
@@ -2109,7 +2109,7 @@
         <v>1177.29162597656</v>
       </c>
       <c r="G60" t="n">
-        <v>910.256164550781</v>
+        <v>910.256225585938</v>
       </c>
       <c r="H60" t="n">
         <v>37028</v>
@@ -2167,7 +2167,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813171386719</v>
+        <v>845.813232421875</v>
       </c>
       <c r="H62" t="n">
         <v>30190</v>
@@ -2225,7 +2225,7 @@
         <v>1040.18395996094</v>
       </c>
       <c r="G64" t="n">
-        <v>804.247497558594</v>
+        <v>804.24755859375</v>
       </c>
       <c r="H64" t="n">
         <v>34669</v>
@@ -2254,7 +2254,7 @@
         <v>1000.80200195312</v>
       </c>
       <c r="G65" t="n">
-        <v>773.798217773438</v>
+        <v>773.798278808594</v>
       </c>
       <c r="H65" t="n">
         <v>36991</v>
@@ -2341,7 +2341,7 @@
         <v>908.702392578125</v>
       </c>
       <c r="G68" t="n">
-        <v>702.588806152344</v>
+        <v>702.5888671875</v>
       </c>
       <c r="H68" t="n">
         <v>37316</v>
@@ -2370,7 +2370,7 @@
         <v>980.381713867188</v>
       </c>
       <c r="G69" t="n">
-        <v>758.009765625</v>
+        <v>758.009704589844</v>
       </c>
       <c r="H69" t="n">
         <v>52413</v>
@@ -2428,7 +2428,7 @@
         <v>1088.73425292969</v>
       </c>
       <c r="G71" t="n">
-        <v>841.785522460938</v>
+        <v>841.785583496094</v>
       </c>
       <c r="H71" t="n">
         <v>71518</v>
@@ -2515,7 +2515,7 @@
         <v>1251.26293945312</v>
       </c>
       <c r="G74" t="n">
-        <v>967.44921875</v>
+        <v>967.449157714844</v>
       </c>
       <c r="H74" t="n">
         <v>42225</v>
@@ -2544,7 +2544,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.197265625</v>
+        <v>1047.19738769531</v>
       </c>
       <c r="H75" t="n">
         <v>71166</v>
@@ -2573,7 +2573,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03131103516</v>
       </c>
       <c r="H76" t="n">
         <v>87970</v>
@@ -2602,7 +2602,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86303710938</v>
+        <v>1085.86291503906</v>
       </c>
       <c r="H77" t="n">
         <v>60062</v>
@@ -2689,7 +2689,7 @@
         <v>1379.41064453125</v>
       </c>
       <c r="G80" t="n">
-        <v>1066.53015136719</v>
+        <v>1066.5302734375</v>
       </c>
       <c r="H80" t="n">
         <v>19070</v>
@@ -2834,7 +2834,7 @@
         <v>1390.87097167969</v>
       </c>
       <c r="G85" t="n">
-        <v>1075.39099121094</v>
+        <v>1075.39111328125</v>
       </c>
       <c r="H85" t="n">
         <v>43075</v>
@@ -2892,7 +2892,7 @@
         <v>1267.9326171875</v>
       </c>
       <c r="G87" t="n">
-        <v>980.337768554688</v>
+        <v>980.337829589844</v>
       </c>
       <c r="H87" t="n">
         <v>37678</v>
@@ -2979,7 +2979,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G90" t="n">
-        <v>965.032653808594</v>
+        <v>965.032592773438</v>
       </c>
       <c r="H90" t="n">
         <v>33396</v>
@@ -3008,7 +3008,7 @@
         <v>1208.54711914062</v>
       </c>
       <c r="G91" t="n">
-        <v>934.422302246094</v>
+        <v>934.422241210938</v>
       </c>
       <c r="H91" t="n">
         <v>37385</v>
@@ -3066,7 +3066,7 @@
         <v>1153.32897949219</v>
       </c>
       <c r="G93" t="n">
-        <v>891.728820800781</v>
+        <v>891.728759765625</v>
       </c>
       <c r="H93" t="n">
         <v>32662</v>
@@ -3124,7 +3124,7 @@
         <v>1163.74755859375</v>
       </c>
       <c r="G95" t="n">
-        <v>899.784240722656</v>
+        <v>899.7841796875</v>
       </c>
       <c r="H95" t="n">
         <v>21832</v>
@@ -3153,7 +3153,7 @@
         <v>1156.45458984375</v>
       </c>
       <c r="G96" t="n">
-        <v>894.1455078125</v>
+        <v>894.145446777344</v>
       </c>
       <c r="H96" t="n">
         <v>29015</v>
@@ -3269,7 +3269,7 @@
         <v>1159.580078125</v>
       </c>
       <c r="G100" t="n">
-        <v>896.56201171875</v>
+        <v>896.561950683594</v>
       </c>
       <c r="H100" t="n">
         <v>16345</v>
@@ -3298,7 +3298,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809814453125</v>
+        <v>990.809753417969</v>
       </c>
       <c r="H101" t="n">
         <v>46314</v>
@@ -3327,7 +3327,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47625732422</v>
+        <v>1000.47613525391</v>
       </c>
       <c r="H102" t="n">
         <v>46119</v>
@@ -3356,7 +3356,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.142578125</v>
+        <v>1010.14270019531</v>
       </c>
       <c r="H103" t="n">
         <v>21794</v>
@@ -3385,7 +3385,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17028808594</v>
+        <v>1014.17034912109</v>
       </c>
       <c r="H104" t="n">
         <v>14276</v>
@@ -3443,7 +3443,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.6982421875</v>
+        <v>1003.69830322266</v>
       </c>
       <c r="H106" t="n">
         <v>20322</v>
@@ -3472,7 +3472,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G107" t="n">
-        <v>965.032653808594</v>
+        <v>965.032592773438</v>
       </c>
       <c r="H107" t="n">
         <v>26277</v>
@@ -3501,7 +3501,7 @@
         <v>1274.18371582031</v>
       </c>
       <c r="G108" t="n">
-        <v>985.170959472656</v>
+        <v>985.171020507812</v>
       </c>
       <c r="H108" t="n">
         <v>32082</v>
@@ -3530,7 +3530,7 @@
         <v>1214.79821777344</v>
       </c>
       <c r="G109" t="n">
-        <v>939.255493164062</v>
+        <v>939.255432128906</v>
       </c>
       <c r="H109" t="n">
         <v>27462</v>
@@ -3588,7 +3588,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809814453125</v>
+        <v>990.809753417969</v>
       </c>
       <c r="H111" t="n">
         <v>28141</v>
@@ -3646,7 +3646,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.143920898438</v>
+        <v>952.143981933594</v>
       </c>
       <c r="H113" t="n">
         <v>14885</v>
@@ -3704,7 +3704,7 @@
         <v>1046.01831054688</v>
       </c>
       <c r="G115" t="n">
-        <v>808.758544921875</v>
+        <v>808.758483886719</v>
       </c>
       <c r="H115" t="n">
         <v>39052</v>
@@ -3791,7 +3791,7 @@
         <v>1003.30242919922</v>
       </c>
       <c r="G118" t="n">
-        <v>775.731567382812</v>
+        <v>775.731506347656</v>
       </c>
       <c r="H118" t="n">
         <v>34176</v>
@@ -3849,7 +3849,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368286132812</v>
+        <v>868.368225097656</v>
       </c>
       <c r="H120" t="n">
         <v>32561</v>
@@ -3965,7 +3965,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749328613281</v>
+        <v>731.749267578125</v>
       </c>
       <c r="H124" t="n">
         <v>64325</v>
@@ -3994,7 +3994,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118225097656</v>
+        <v>634.118286132812</v>
       </c>
       <c r="H125" t="n">
         <v>71078</v>
@@ -4052,7 +4052,7 @@
         <v>809.934936523438</v>
       </c>
       <c r="G127" t="n">
-        <v>626.223999023438</v>
+        <v>626.223937988281</v>
       </c>
       <c r="H127" t="n">
         <v>44209</v>
@@ -4139,7 +4139,7 @@
         <v>685.537902832031</v>
       </c>
       <c r="G130" t="n">
-        <v>530.042907714844</v>
+        <v>530.04296875</v>
       </c>
       <c r="H130" t="n">
         <v>79855</v>
@@ -4168,7 +4168,7 @@
         <v>552.597717285156</v>
       </c>
       <c r="G131" t="n">
-        <v>427.256500244141</v>
+        <v>427.256469726562</v>
       </c>
       <c r="H131" t="n">
         <v>109680</v>
@@ -4197,7 +4197,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194732666016</v>
+        <v>453.194793701172</v>
       </c>
       <c r="H132" t="n">
         <v>69237</v>
@@ -4226,7 +4226,7 @@
         <v>552.181030273438</v>
       </c>
       <c r="G133" t="n">
-        <v>426.934295654297</v>
+        <v>426.934326171875</v>
       </c>
       <c r="H133" t="n">
         <v>49476</v>
@@ -4284,7 +4284,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549591064453</v>
+        <v>481.549652099609</v>
       </c>
       <c r="H135" t="n">
         <v>39529</v>
@@ -4342,7 +4342,7 @@
         <v>680.745422363281</v>
       </c>
       <c r="G137" t="n">
-        <v>526.337463378906</v>
+        <v>526.337524414062</v>
       </c>
       <c r="H137" t="n">
         <v>93205</v>
@@ -4429,7 +4429,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259460449219</v>
+        <v>538.259399414062</v>
       </c>
       <c r="H140" t="n">
         <v>34135</v>
@@ -4458,7 +4458,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.537658691406</v>
+        <v>520.53759765625</v>
       </c>
       <c r="H141" t="n">
         <v>36777</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710113525391</v>
+        <v>510.710083007812</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4545,7 +4545,7 @@
         <v>650.114990234375</v>
       </c>
       <c r="G144" t="n">
-        <v>502.654693603516</v>
+        <v>502.654754638672</v>
       </c>
       <c r="H144" t="n">
         <v>26528</v>
@@ -4574,7 +4574,7 @@
         <v>595.313598632812</v>
       </c>
       <c r="G145" t="n">
-        <v>460.283447265625</v>
+        <v>460.283477783203</v>
       </c>
       <c r="H145" t="n">
         <v>58255</v>
@@ -4661,7 +4661,7 @@
         <v>604.273559570312</v>
       </c>
       <c r="G148" t="n">
-        <v>467.211151123047</v>
+        <v>467.211120605469</v>
       </c>
       <c r="H148" t="n">
         <v>26200</v>
@@ -4690,7 +4690,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532653808594</v>
+        <v>496.532592773438</v>
       </c>
       <c r="H149" t="n">
         <v>46906</v>
@@ -4748,7 +4748,7 @@
         <v>541.970886230469</v>
       </c>
       <c r="G151" t="n">
-        <v>419.0400390625</v>
+        <v>419.040069580078</v>
       </c>
       <c r="H151" t="n">
         <v>45660</v>
@@ -4806,7 +4806,7 @@
         <v>539.678771972656</v>
       </c>
       <c r="G153" t="n">
-        <v>417.267852783203</v>
+        <v>417.267822265625</v>
       </c>
       <c r="H153" t="n">
         <v>31277</v>
@@ -4835,7 +4835,7 @@
         <v>531.135620117188</v>
       </c>
       <c r="G154" t="n">
-        <v>410.662475585938</v>
+        <v>410.662445068359</v>
       </c>
       <c r="H154" t="n">
         <v>36401</v>
@@ -4951,7 +4951,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384918212891</v>
+        <v>399.384948730469</v>
       </c>
       <c r="H158" t="n">
         <v>11284</v>
@@ -4980,7 +4980,7 @@
         <v>523.009155273438</v>
       </c>
       <c r="G159" t="n">
-        <v>404.379272460938</v>
+        <v>404.379241943359</v>
       </c>
       <c r="H159" t="n">
         <v>21609</v>
@@ -5067,7 +5067,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G162" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H162" t="n">
         <v>24713</v>
@@ -5125,7 +5125,7 @@
         <v>477.58447265625</v>
       </c>
       <c r="G164" t="n">
-        <v>369.257904052734</v>
+        <v>369.257873535156</v>
       </c>
       <c r="H164" t="n">
         <v>11396</v>
@@ -5154,7 +5154,7 @@
         <v>494.879211425781</v>
       </c>
       <c r="G165" t="n">
-        <v>382.629791259766</v>
+        <v>382.629821777344</v>
       </c>
       <c r="H165" t="n">
         <v>15915</v>
@@ -5415,7 +5415,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724212646484</v>
+        <v>384.724182128906</v>
       </c>
       <c r="H174" t="n">
         <v>11728</v>
@@ -5444,7 +5444,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G175" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H175" t="n">
         <v>11244</v>
@@ -5502,7 +5502,7 @@
         <v>509.465118408203</v>
       </c>
       <c r="G177" t="n">
-        <v>393.907287597656</v>
+        <v>393.907318115234</v>
       </c>
       <c r="H177" t="n">
         <v>26337</v>
@@ -5589,7 +5589,7 @@
         <v>476.125885009766</v>
       </c>
       <c r="G180" t="n">
-        <v>368.130126953125</v>
+        <v>368.130157470703</v>
       </c>
       <c r="H180" t="n">
         <v>18405</v>
@@ -5676,7 +5676,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436737060547</v>
+        <v>325.436706542969</v>
       </c>
       <c r="H183" t="n">
         <v>78778</v>
@@ -5705,7 +5705,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H184" t="n">
         <v>24033</v>
@@ -5763,7 +5763,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003753662109</v>
+        <v>309.003784179688</v>
       </c>
       <c r="H186" t="n">
         <v>27102</v>
@@ -5821,7 +5821,7 @@
         <v>392.569427490234</v>
       </c>
       <c r="G188" t="n">
-        <v>303.526092529297</v>
+        <v>303.526123046875</v>
       </c>
       <c r="H188" t="n">
         <v>15965</v>
@@ -5879,7 +5879,7 @@
         <v>404.86328125</v>
       </c>
       <c r="G190" t="n">
-        <v>313.031433105469</v>
+        <v>313.031463623047</v>
       </c>
       <c r="H190" t="n">
         <v>26142</v>
@@ -5908,7 +5908,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742614746094</v>
+        <v>311.742584228516</v>
       </c>
       <c r="H191" t="n">
         <v>13716</v>
@@ -6053,7 +6053,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843322753906</v>
+        <v>279.843353271484</v>
       </c>
       <c r="H196" t="n">
         <v>54804</v>
@@ -6082,7 +6082,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499145507812</v>
+        <v>270.499114990234</v>
       </c>
       <c r="H197" t="n">
         <v>45392</v>
@@ -6111,7 +6111,7 @@
         <v>354.229309082031</v>
       </c>
       <c r="G198" t="n">
-        <v>273.882354736328</v>
+        <v>273.882385253906</v>
       </c>
       <c r="H198" t="n">
         <v>39961</v>
@@ -6227,7 +6227,7 @@
         <v>355.896270751953</v>
       </c>
       <c r="G202" t="n">
-        <v>275.171234130859</v>
+        <v>275.171203613281</v>
       </c>
       <c r="H202" t="n">
         <v>17732</v>
@@ -6285,7 +6285,7 @@
         <v>360.897155761719</v>
       </c>
       <c r="G204" t="n">
-        <v>279.037780761719</v>
+        <v>279.037811279297</v>
       </c>
       <c r="H204" t="n">
         <v>13463</v>
@@ -6372,7 +6372,7 @@
         <v>497.379638671875</v>
       </c>
       <c r="G207" t="n">
-        <v>384.563079833984</v>
+        <v>384.563049316406</v>
       </c>
       <c r="H207" t="n">
         <v>111579</v>
@@ -6459,7 +6459,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266448974609</v>
+        <v>475.266510009766</v>
       </c>
       <c r="H210" t="n">
         <v>166520</v>
@@ -6488,7 +6488,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184143066406</v>
+        <v>434.184112548828</v>
       </c>
       <c r="H211" t="n">
         <v>136414</v>
@@ -6546,7 +6546,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906585693359</v>
+        <v>422.906616210938</v>
       </c>
       <c r="H213" t="n">
         <v>68253</v>
@@ -6575,7 +6575,7 @@
         <v>506.547943115234</v>
       </c>
       <c r="G214" t="n">
-        <v>391.651824951172</v>
+        <v>391.651794433594</v>
       </c>
       <c r="H214" t="n">
         <v>68364</v>
@@ -6691,7 +6691,7 @@
         <v>439.661102294922</v>
       </c>
       <c r="G218" t="n">
-        <v>339.936340332031</v>
+        <v>339.936370849609</v>
       </c>
       <c r="H218" t="n">
         <v>64785</v>
@@ -6720,7 +6720,7 @@
         <v>537.178344726562</v>
       </c>
       <c r="G219" t="n">
-        <v>415.334594726562</v>
+        <v>415.334564208984</v>
       </c>
       <c r="H219" t="n">
         <v>97389</v>
@@ -6749,7 +6749,7 @@
         <v>558.015380859375</v>
       </c>
       <c r="G220" t="n">
-        <v>431.4453125</v>
+        <v>431.445281982422</v>
       </c>
       <c r="H220" t="n">
         <v>158097</v>
@@ -6865,7 +6865,7 @@
         <v>583.228149414062</v>
       </c>
       <c r="G224" t="n">
-        <v>450.939239501953</v>
+        <v>450.939270019531</v>
       </c>
       <c r="H224" t="n">
         <v>123957</v>
@@ -6894,7 +6894,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829254150391</v>
+        <v>405.829284667969</v>
       </c>
       <c r="H225" t="n">
         <v>74636</v>
@@ -6952,7 +6952,7 @@
         <v>495.712677001953</v>
       </c>
       <c r="G227" t="n">
-        <v>383.274230957031</v>
+        <v>383.274200439453</v>
       </c>
       <c r="H227" t="n">
         <v>36344</v>
@@ -7068,7 +7068,7 @@
         <v>464.040405273438</v>
       </c>
       <c r="G231" t="n">
-        <v>358.785888671875</v>
+        <v>358.785919189453</v>
       </c>
       <c r="H231" t="n">
         <v>44014</v>
@@ -7126,7 +7126,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H233" t="n">
         <v>63341</v>
@@ -7271,7 +7271,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H238" t="n">
         <v>56464</v>
@@ -7416,7 +7416,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H243" t="n">
         <v>108228</v>
@@ -7561,7 +7561,7 @@
         <v>436.118774414062</v>
       </c>
       <c r="G248" t="n">
-        <v>337.197540283203</v>
+        <v>337.197509765625</v>
       </c>
       <c r="H248" t="n">
         <v>78353</v>
@@ -7590,7 +7590,7 @@
         <v>387.985260009766</v>
       </c>
       <c r="G249" t="n">
-        <v>299.981750488281</v>
+        <v>299.981719970703</v>
       </c>
       <c r="H249" t="n">
         <v>107400</v>
@@ -7648,7 +7648,7 @@
         <v>339.643371582031</v>
       </c>
       <c r="G251" t="n">
-        <v>262.604858398438</v>
+        <v>262.604827880859</v>
       </c>
       <c r="H251" t="n">
         <v>159767</v>
@@ -13883,7 +13883,7 @@
         <v>94.8084259033203</v>
       </c>
       <c r="G466" t="n">
-        <v>73.3038101196289</v>
+        <v>73.3038024902344</v>
       </c>
       <c r="H466" t="n">
         <v>2488563</v>
@@ -13912,7 +13912,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.1715087890625</v>
+        <v>76.171516418457</v>
       </c>
       <c r="H467" t="n">
         <v>616657</v>
@@ -13941,7 +13941,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003921508789</v>
+        <v>76.3003997802734</v>
       </c>
       <c r="H468" t="n">
         <v>232423</v>
@@ -14057,7 +14057,7 @@
         <v>97.0588302612305</v>
       </c>
       <c r="G472" t="n">
-        <v>75.0437698364258</v>
+        <v>75.0437622070312</v>
       </c>
       <c r="H472" t="n">
         <v>68056</v>
@@ -14086,7 +14086,7 @@
         <v>95.4335403442383</v>
       </c>
       <c r="G473" t="n">
-        <v>73.7871246337891</v>
+        <v>73.7871322631836</v>
       </c>
       <c r="H473" t="n">
         <v>87104</v>
@@ -14144,7 +14144,7 @@
         <v>93.6832275390625</v>
       </c>
       <c r="G475" t="n">
-        <v>72.4338226318359</v>
+        <v>72.4338302612305</v>
       </c>
       <c r="H475" t="n">
         <v>148288</v>
@@ -14231,7 +14231,7 @@
         <v>85.4734420776367</v>
       </c>
       <c r="G478" t="n">
-        <v>66.0861968994141</v>
+        <v>66.0862045288086</v>
       </c>
       <c r="H478" t="n">
         <v>120033</v>
@@ -14260,7 +14260,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.1218338012695</v>
+        <v>63.1218299865723</v>
       </c>
       <c r="H479" t="n">
         <v>202691</v>
@@ -14318,7 +14318,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264366149902</v>
+        <v>56.2264404296875</v>
       </c>
       <c r="H481" t="n">
         <v>308433</v>
@@ -14347,7 +14347,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064865112305</v>
+        <v>53.9064903259277</v>
       </c>
       <c r="H482" t="n">
         <v>255815</v>
@@ -14492,7 +14492,7 @@
         <v>82.0978469848633</v>
       </c>
       <c r="G487" t="n">
-        <v>63.476261138916</v>
+        <v>63.4762649536133</v>
       </c>
       <c r="H487" t="n">
         <v>63428</v>
@@ -14521,7 +14521,7 @@
         <v>83.306396484375</v>
       </c>
       <c r="G488" t="n">
-        <v>64.4106903076172</v>
+        <v>64.4106826782227</v>
       </c>
       <c r="H488" t="n">
         <v>91362</v>
@@ -14550,7 +14550,7 @@
         <v>84.1815490722656</v>
       </c>
       <c r="G489" t="n">
-        <v>65.0873336791992</v>
+        <v>65.0873413085938</v>
       </c>
       <c r="H489" t="n">
         <v>130214</v>
@@ -14579,7 +14579,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906616210938</v>
+        <v>64.9906692504883</v>
       </c>
       <c r="H490" t="n">
         <v>123807</v>
@@ -14637,7 +14637,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539855957031</v>
+        <v>66.0539779663086</v>
       </c>
       <c r="H492" t="n">
         <v>305053</v>
@@ -14753,7 +14753,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G496" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H496" t="n">
         <v>50947</v>
@@ -14782,7 +14782,7 @@
         <v>80.4725646972656</v>
       </c>
       <c r="G497" t="n">
-        <v>62.2196273803711</v>
+        <v>62.2196311950684</v>
       </c>
       <c r="H497" t="n">
         <v>56838</v>
@@ -14840,7 +14840,7 @@
         <v>80.4308853149414</v>
       </c>
       <c r="G499" t="n">
-        <v>62.1874046325684</v>
+        <v>62.1874084472656</v>
       </c>
       <c r="H499" t="n">
         <v>32132</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.156322479248</v>
+        <v>61.1563186645508</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -14927,7 +14927,7 @@
         <v>78.430534362793</v>
       </c>
       <c r="G502" t="n">
-        <v>60.6407814025879</v>
+        <v>60.6407737731934</v>
       </c>
       <c r="H502" t="n">
         <v>45614</v>
@@ -14956,7 +14956,7 @@
         <v>77.5137023925781</v>
       </c>
       <c r="G503" t="n">
-        <v>59.9319000244141</v>
+        <v>59.9319038391113</v>
       </c>
       <c r="H503" t="n">
         <v>48461</v>
@@ -15014,7 +15014,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H505" t="n">
         <v>57550</v>
@@ -15043,7 +15043,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G506" t="n">
-        <v>62.5096206665039</v>
+        <v>62.5096168518066</v>
       </c>
       <c r="H506" t="n">
         <v>88056</v>
@@ -15101,7 +15101,7 @@
         <v>79.7640991210938</v>
       </c>
       <c r="G508" t="n">
-        <v>61.6718559265137</v>
+        <v>61.6718597412109</v>
       </c>
       <c r="H508" t="n">
         <v>34426</v>
@@ -15159,7 +15159,7 @@
         <v>81.93115234375</v>
       </c>
       <c r="G510" t="n">
-        <v>63.3473777770996</v>
+        <v>63.3473739624023</v>
       </c>
       <c r="H510" t="n">
         <v>35391</v>
@@ -15188,7 +15188,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573844909668</v>
+        <v>63.0573806762695</v>
       </c>
       <c r="H511" t="n">
         <v>34562</v>
@@ -15217,7 +15217,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H512" t="n">
         <v>22428</v>
@@ -15246,7 +15246,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.4129524230957</v>
+        <v>62.4129600524902</v>
       </c>
       <c r="H513" t="n">
         <v>27484</v>
@@ -15304,7 +15304,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H515" t="n">
         <v>30486</v>
@@ -15333,7 +15333,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G516" t="n">
-        <v>62.5096206665039</v>
+        <v>62.5096168518066</v>
       </c>
       <c r="H516" t="n">
         <v>30537</v>
@@ -15391,7 +15391,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G518" t="n">
-        <v>63.927360534668</v>
+        <v>63.9273643493652</v>
       </c>
       <c r="H518" t="n">
         <v>298961</v>
@@ -15449,7 +15449,7 @@
         <v>83.7231369018555</v>
       </c>
       <c r="G520" t="n">
-        <v>64.7328948974609</v>
+        <v>64.7329025268555</v>
       </c>
       <c r="H520" t="n">
         <v>131635</v>
@@ -15536,7 +15536,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G523" t="n">
-        <v>63.927360534668</v>
+        <v>63.9273643493652</v>
       </c>
       <c r="H523" t="n">
         <v>45681</v>
@@ -15565,7 +15565,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G524" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H524" t="n">
         <v>49745</v>
@@ -15594,7 +15594,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H525" t="n">
         <v>40067</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184867858887</v>
+        <v>63.2184944152832</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15652,7 +15652,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.6707344055176</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H527" t="n">
         <v>45359</v>
@@ -15681,7 +15681,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G528" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H528" t="n">
         <v>57552</v>
@@ -15710,7 +15710,7 @@
         <v>81.0143203735352</v>
       </c>
       <c r="G529" t="n">
-        <v>62.6385040283203</v>
+        <v>62.6385078430176</v>
       </c>
       <c r="H529" t="n">
         <v>50236</v>
@@ -15768,7 +15768,7 @@
         <v>80.555908203125</v>
       </c>
       <c r="G531" t="n">
-        <v>62.2840690612793</v>
+        <v>62.2840728759766</v>
       </c>
       <c r="H531" t="n">
         <v>74076</v>
@@ -15797,7 +15797,7 @@
         <v>78.8055953979492</v>
       </c>
       <c r="G532" t="n">
-        <v>60.9307632446289</v>
+        <v>60.9307670593262</v>
       </c>
       <c r="H532" t="n">
         <v>101055</v>
@@ -15855,7 +15855,7 @@
         <v>77.9721221923828</v>
       </c>
       <c r="G534" t="n">
-        <v>60.2863426208496</v>
+        <v>60.2863464355469</v>
       </c>
       <c r="H534" t="n">
         <v>68146</v>
@@ -15884,7 +15884,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397117614746</v>
+        <v>58.7397041320801</v>
       </c>
       <c r="H535" t="n">
         <v>102598</v>
@@ -15942,7 +15942,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.0607833862305</v>
+        <v>60.0607872009277</v>
       </c>
       <c r="H537" t="n">
         <v>142371</v>
@@ -15971,7 +15971,7 @@
         <v>78.1388168334961</v>
       </c>
       <c r="G538" t="n">
-        <v>60.4152297973633</v>
+        <v>60.4152221679688</v>
       </c>
       <c r="H538" t="n">
         <v>64920</v>
@@ -16000,7 +16000,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.836368560791</v>
+        <v>58.8363761901855</v>
       </c>
       <c r="H539" t="n">
         <v>77063</v>
@@ -16058,7 +16058,7 @@
         <v>74.8048934936523</v>
       </c>
       <c r="G541" t="n">
-        <v>57.8375091552734</v>
+        <v>57.8375129699707</v>
       </c>
       <c r="H541" t="n">
         <v>169917</v>
@@ -16087,7 +16087,7 @@
         <v>70.8458557128906</v>
       </c>
       <c r="G542" t="n">
-        <v>54.7764663696289</v>
+        <v>54.7764701843262</v>
       </c>
       <c r="H542" t="n">
         <v>196506</v>
@@ -16145,7 +16145,7 @@
         <v>71.8877105712891</v>
       </c>
       <c r="G544" t="n">
-        <v>55.5820045471191</v>
+        <v>55.5820121765137</v>
       </c>
       <c r="H544" t="n">
         <v>70492</v>
@@ -16203,7 +16203,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.46923828125</v>
+        <v>55.4692306518555</v>
       </c>
       <c r="H546" t="n">
         <v>24192</v>
@@ -16290,7 +16290,7 @@
         <v>67.0951995849609</v>
       </c>
       <c r="G549" t="n">
-        <v>51.8765449523926</v>
+        <v>51.8765411376953</v>
       </c>
       <c r="H549" t="n">
         <v>124037</v>
@@ -16348,7 +16348,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.005428314209</v>
+        <v>52.0054321289062</v>
       </c>
       <c r="H551" t="n">
         <v>83287</v>
@@ -16406,7 +16406,7 @@
         <v>66.9910125732422</v>
       </c>
       <c r="G553" t="n">
-        <v>51.7959899902344</v>
+        <v>51.7959861755371</v>
       </c>
       <c r="H553" t="n">
         <v>50170</v>
@@ -16435,7 +16435,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832160949707</v>
+        <v>51.6832122802734</v>
       </c>
       <c r="H554" t="n">
         <v>49117</v>
@@ -16522,7 +16522,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G557" t="n">
-        <v>51.2321166992188</v>
+        <v>51.2321128845215</v>
       </c>
       <c r="H557" t="n">
         <v>73571</v>
@@ -16551,7 +16551,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G558" t="n">
-        <v>51.2321166992188</v>
+        <v>51.2321128845215</v>
       </c>
       <c r="H558" t="n">
         <v>20722</v>
@@ -16609,7 +16609,7 @@
         <v>65.4282302856445</v>
       </c>
       <c r="G560" t="n">
-        <v>50.5876808166504</v>
+        <v>50.5876770019531</v>
       </c>
       <c r="H560" t="n">
         <v>38087</v>
@@ -16638,7 +16638,7 @@
         <v>65.0114974975586</v>
       </c>
       <c r="G561" t="n">
-        <v>50.2654685974121</v>
+        <v>50.2654724121094</v>
       </c>
       <c r="H561" t="n">
         <v>34140</v>
@@ -16696,7 +16696,7 @@
         <v>63.6987609863281</v>
       </c>
       <c r="G563" t="n">
-        <v>49.2504920959473</v>
+        <v>49.25048828125</v>
       </c>
       <c r="H563" t="n">
         <v>49204</v>
@@ -16725,7 +16725,7 @@
         <v>63.8237838745117</v>
       </c>
       <c r="G564" t="n">
-        <v>49.3471565246582</v>
+        <v>49.3471527099609</v>
       </c>
       <c r="H564" t="n">
         <v>41188</v>
@@ -16899,7 +16899,7 @@
         <v>56.0099029541016</v>
       </c>
       <c r="G570" t="n">
-        <v>43.3056335449219</v>
+        <v>43.3056373596191</v>
       </c>
       <c r="H570" t="n">
         <v>225410</v>
@@ -16928,7 +16928,7 @@
         <v>54.3221054077148</v>
       </c>
       <c r="G571" t="n">
-        <v>42.0006675720215</v>
+        <v>42.0006637573242</v>
       </c>
       <c r="H571" t="n">
         <v>114062</v>
@@ -16957,7 +16957,7 @@
         <v>52.9051856994629</v>
       </c>
       <c r="G572" t="n">
-        <v>40.9051322937012</v>
+        <v>40.9051361083984</v>
       </c>
       <c r="H572" t="n">
         <v>130898</v>
@@ -17015,7 +17015,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367866516113</v>
+        <v>41.4367904663086</v>
       </c>
       <c r="H574" t="n">
         <v>153152</v>
@@ -17044,7 +17044,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184745788574</v>
+        <v>40.5184783935547</v>
       </c>
       <c r="H575" t="n">
         <v>92688</v>
@@ -17073,7 +17073,7 @@
         <v>53.1969032287598</v>
       </c>
       <c r="G576" t="n">
-        <v>41.1306838989258</v>
+        <v>41.130687713623</v>
       </c>
       <c r="H576" t="n">
         <v>90811</v>
@@ -17102,7 +17102,7 @@
         <v>57.8435592651367</v>
       </c>
       <c r="G577" t="n">
-        <v>44.7233772277832</v>
+        <v>44.7233734130859</v>
       </c>
       <c r="H577" t="n">
         <v>304629</v>
@@ -17218,7 +17218,7 @@
         <v>55.5723266601562</v>
       </c>
       <c r="G581" t="n">
-        <v>42.9673080444336</v>
+        <v>42.9673118591309</v>
       </c>
       <c r="H581" t="n">
         <v>116018</v>
@@ -17276,7 +17276,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H583" t="n">
         <v>160680</v>
@@ -17305,7 +17305,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G584" t="n">
-        <v>42.9511985778809</v>
+        <v>42.9511947631836</v>
       </c>
       <c r="H584" t="n">
         <v>78005</v>
@@ -17334,7 +17334,7 @@
         <v>55.5306510925293</v>
       </c>
       <c r="G585" t="n">
-        <v>42.9350891113281</v>
+        <v>42.9350852966309</v>
       </c>
       <c r="H585" t="n">
         <v>117880</v>
@@ -17363,7 +17363,7 @@
         <v>56.8850555419922</v>
       </c>
       <c r="G586" t="n">
-        <v>43.9822807312012</v>
+        <v>43.9822845458984</v>
       </c>
       <c r="H586" t="n">
         <v>88984</v>
@@ -17450,7 +17450,7 @@
         <v>56.1974334716797</v>
       </c>
       <c r="G589" t="n">
-        <v>43.4506301879883</v>
+        <v>43.450626373291</v>
       </c>
       <c r="H589" t="n">
         <v>63710</v>
@@ -17566,7 +17566,7 @@
         <v>55.4889755249023</v>
       </c>
       <c r="G593" t="n">
-        <v>42.9028625488281</v>
+        <v>42.9028663635254</v>
       </c>
       <c r="H593" t="n">
         <v>40012</v>
@@ -17653,7 +17653,7 @@
         <v>56.2599449157715</v>
       </c>
       <c r="G596" t="n">
-        <v>43.4989624023438</v>
+        <v>43.4989585876465</v>
       </c>
       <c r="H596" t="n">
         <v>59156</v>
@@ -17682,7 +17682,7 @@
         <v>54.780517578125</v>
       </c>
       <c r="G597" t="n">
-        <v>42.3550987243652</v>
+        <v>42.3551025390625</v>
       </c>
       <c r="H597" t="n">
         <v>77570</v>
@@ -17769,7 +17769,7 @@
         <v>57.3017959594727</v>
       </c>
       <c r="G600" t="n">
-        <v>44.3044967651367</v>
+        <v>44.304500579834</v>
       </c>
       <c r="H600" t="n">
         <v>186430</v>
@@ -17798,7 +17798,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.8211784362793</v>
+        <v>43.821174621582</v>
       </c>
       <c r="H601" t="n">
         <v>72323</v>
@@ -17856,7 +17856,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431777954102</v>
+        <v>52.8431816101074</v>
       </c>
       <c r="H603" t="n">
         <v>634116</v>
@@ -17943,7 +17943,7 @@
         <v>60.9066009521484</v>
       </c>
       <c r="G606" t="n">
-        <v>47.0916519165039</v>
+        <v>47.0916557312012</v>
       </c>
       <c r="H606" t="n">
         <v>628237</v>
@@ -17972,7 +17972,7 @@
         <v>58.7603874206543</v>
       </c>
       <c r="G607" t="n">
-        <v>45.4322471618652</v>
+        <v>45.4322509765625</v>
       </c>
       <c r="H607" t="n">
         <v>352792</v>
@@ -18030,7 +18030,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194770812988</v>
+        <v>45.3194732666016</v>
       </c>
       <c r="H609" t="n">
         <v>202532</v>
@@ -18088,7 +18088,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G611" t="n">
-        <v>44.3206100463867</v>
+        <v>44.3206062316895</v>
       </c>
       <c r="H611" t="n">
         <v>142469</v>
@@ -18175,7 +18175,7 @@
         <v>52.2800750732422</v>
       </c>
       <c r="G614" t="n">
-        <v>40.4218139648438</v>
+        <v>40.4218101501465</v>
       </c>
       <c r="H614" t="n">
         <v>255740</v>
@@ -18233,7 +18233,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H616" t="n">
         <v>281053</v>
@@ -18291,7 +18291,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G618" t="n">
-        <v>42.9511985778809</v>
+        <v>42.9511947631836</v>
       </c>
       <c r="H618" t="n">
         <v>69954</v>
@@ -18378,7 +18378,7 @@
         <v>57.1976127624512</v>
       </c>
       <c r="G621" t="n">
-        <v>44.2239456176758</v>
+        <v>44.2239418029785</v>
       </c>
       <c r="H621" t="n">
         <v>99660</v>
@@ -18407,7 +18407,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250747680664</v>
+        <v>43.2250785827637</v>
       </c>
       <c r="H622" t="n">
         <v>51718</v>
@@ -18465,7 +18465,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G624" t="n">
-        <v>44.3206100463867</v>
+        <v>44.3206062316895</v>
       </c>
       <c r="H624" t="n">
         <v>48032</v>
@@ -18494,7 +18494,7 @@
         <v>58.5520172119141</v>
       </c>
       <c r="G625" t="n">
-        <v>45.2711410522461</v>
+        <v>45.2711372375488</v>
       </c>
       <c r="H625" t="n">
         <v>62650</v>
@@ -18668,7 +18668,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H631" t="n">
         <v>46391</v>
@@ -18813,7 +18813,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.3734817504883</v>
+        <v>40.373477935791</v>
       </c>
       <c r="H636" t="n">
         <v>90143</v>
@@ -18929,7 +18929,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.5679397583008</v>
+        <v>39.567943572998</v>
       </c>
       <c r="H640" t="n">
         <v>70245</v>
@@ -18958,7 +18958,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062690734863</v>
+        <v>39.9062728881836</v>
       </c>
       <c r="H641" t="n">
         <v>47114</v>
@@ -19364,7 +19364,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.0374298095703</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H655" t="n">
         <v>34543</v>
@@ -19538,7 +19538,7 @@
         <v>51.5299453735352</v>
       </c>
       <c r="G661" t="n">
-        <v>39.8418273925781</v>
+        <v>39.8418312072754</v>
       </c>
       <c r="H661" t="n">
         <v>115915</v>
@@ -19596,7 +19596,7 @@
         <v>49.3628921508789</v>
       </c>
       <c r="G663" t="n">
-        <v>38.1663131713867</v>
+        <v>38.1663093566895</v>
       </c>
       <c r="H663" t="n">
         <v>91978</v>
@@ -19770,7 +19770,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G669" t="n">
-        <v>35.4435958862305</v>
+        <v>35.4435997009277</v>
       </c>
       <c r="H669" t="n">
         <v>39954</v>
@@ -19828,7 +19828,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G671" t="n">
-        <v>35.4435958862305</v>
+        <v>35.4435997009277</v>
       </c>
       <c r="H671" t="n">
         <v>76441</v>
@@ -19857,7 +19857,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G672" t="n">
-        <v>35.3952674865723</v>
+        <v>35.395263671875</v>
       </c>
       <c r="H672" t="n">
         <v>39171</v>
@@ -19915,7 +19915,7 @@
         <v>45.9247856140137</v>
       </c>
       <c r="G674" t="n">
-        <v>35.5080375671387</v>
+        <v>35.5080413818359</v>
       </c>
       <c r="H674" t="n">
         <v>38417</v>
@@ -20060,7 +20060,7 @@
         <v>45.4038581848145</v>
       </c>
       <c r="G679" t="n">
-        <v>35.1052703857422</v>
+        <v>35.1052742004395</v>
       </c>
       <c r="H679" t="n">
         <v>107371</v>
@@ -20118,7 +20118,7 @@
         <v>43.132625579834</v>
       </c>
       <c r="G681" t="n">
-        <v>33.3492050170898</v>
+        <v>33.3492012023926</v>
       </c>
       <c r="H681" t="n">
         <v>52451</v>
@@ -20234,7 +20234,7 @@
         <v>46.3206901550293</v>
       </c>
       <c r="G685" t="n">
-        <v>35.8141441345215</v>
+        <v>35.8141479492188</v>
       </c>
       <c r="H685" t="n">
         <v>78485</v>
@@ -20263,7 +20263,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G686" t="n">
-        <v>35.3952674865723</v>
+        <v>35.395263671875</v>
       </c>
       <c r="H686" t="n">
         <v>55186</v>
@@ -20292,7 +20292,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G687" t="n">
-        <v>38.3113098144531</v>
+        <v>38.3113059997559</v>
       </c>
       <c r="H687" t="n">
         <v>246032</v>
@@ -20321,7 +20321,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.0374298095703</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H688" t="n">
         <v>118566</v>
@@ -20350,7 +20350,7 @@
         <v>47.695930480957</v>
       </c>
       <c r="G689" t="n">
-        <v>36.8774528503418</v>
+        <v>36.8774490356445</v>
       </c>
       <c r="H689" t="n">
         <v>132939</v>
@@ -20437,7 +20437,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057678222656</v>
+        <v>37.5057754516602</v>
       </c>
       <c r="H692" t="n">
         <v>93100</v>
@@ -20582,7 +20582,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G697" t="n">
-        <v>38.3113098144531</v>
+        <v>38.3113059997559</v>
       </c>
       <c r="H697" t="n">
         <v>47583</v>
@@ -20611,7 +20611,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563026428223</v>
+        <v>38.4563064575195</v>
       </c>
       <c r="H698" t="n">
         <v>127098</v>
@@ -20640,7 +20640,7 @@
         <v>50.175537109375</v>
       </c>
       <c r="G699" t="n">
-        <v>38.7946281433105</v>
+        <v>38.7946319580078</v>
       </c>
       <c r="H699" t="n">
         <v>37785</v>
@@ -20756,7 +20756,7 @@
         <v>42.9242553710938</v>
       </c>
       <c r="G703" t="n">
-        <v>33.1880950927734</v>
+        <v>33.1880989074707</v>
       </c>
       <c r="H703" t="n">
         <v>149650</v>
@@ -20785,7 +20785,7 @@
         <v>42.861743927002</v>
       </c>
       <c r="G704" t="n">
-        <v>33.139762878418</v>
+        <v>33.1397666931152</v>
       </c>
       <c r="H704" t="n">
         <v>60234</v>
@@ -20930,7 +20930,7 @@
         <v>38.5068092346191</v>
       </c>
       <c r="G709" t="n">
-        <v>29.7726249694824</v>
+        <v>29.7726230621338</v>
       </c>
       <c r="H709" t="n">
         <v>137943</v>
@@ -20959,7 +20959,7 @@
         <v>37.0377998352051</v>
       </c>
       <c r="G710" t="n">
-        <v>28.6368198394775</v>
+        <v>28.6368179321289</v>
       </c>
       <c r="H710" t="n">
         <v>115092</v>
@@ -21017,7 +21017,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884838104248</v>
+        <v>28.5884857177734</v>
       </c>
       <c r="H712" t="n">
         <v>79946</v>
@@ -21046,7 +21046,7 @@
         <v>36.089714050293</v>
       </c>
       <c r="G713" t="n">
-        <v>27.9037780761719</v>
+        <v>27.9037799835205</v>
       </c>
       <c r="H713" t="n">
         <v>152219</v>
@@ -21075,7 +21075,7 @@
         <v>35.7875785827637</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6701755523682</v>
+        <v>27.6701736450195</v>
       </c>
       <c r="H714" t="n">
         <v>86668</v>
@@ -21104,7 +21104,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532432556152</v>
+        <v>26.9532451629639</v>
       </c>
       <c r="H715" t="n">
         <v>100245</v>
@@ -21162,7 +21162,7 @@
         <v>31.3805484771729</v>
       </c>
       <c r="G717" t="n">
-        <v>24.2627563476562</v>
+        <v>24.2627544403076</v>
       </c>
       <c r="H717" t="n">
         <v>177943</v>
@@ -21191,7 +21191,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H718" t="n">
         <v>180004</v>
@@ -21481,7 +21481,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480266571045</v>
+        <v>24.4480247497559</v>
       </c>
       <c r="H728" t="n">
         <v>59503</v>
@@ -21510,7 +21510,7 @@
         <v>30.7137622833252</v>
       </c>
       <c r="G729" t="n">
-        <v>23.7472095489502</v>
+        <v>23.7472114562988</v>
       </c>
       <c r="H729" t="n">
         <v>111085</v>
@@ -21597,7 +21597,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177558898926</v>
+        <v>24.1177577972412</v>
       </c>
       <c r="H732" t="n">
         <v>82427</v>
@@ -21684,7 +21684,7 @@
         <v>29.411449432373</v>
       </c>
       <c r="G735" t="n">
-        <v>22.7402896881104</v>
+        <v>22.740291595459</v>
       </c>
       <c r="H735" t="n">
         <v>76940</v>
@@ -21713,7 +21713,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H736" t="n">
         <v>72375</v>
@@ -21800,7 +21800,7 @@
         <v>28.7863388061523</v>
       </c>
       <c r="G739" t="n">
-        <v>22.2569675445557</v>
+        <v>22.2569694519043</v>
       </c>
       <c r="H739" t="n">
         <v>68543</v>
@@ -21858,7 +21858,7 @@
         <v>29.7031688690186</v>
       </c>
       <c r="G741" t="n">
-        <v>22.965841293335</v>
+        <v>22.9658432006836</v>
       </c>
       <c r="H741" t="n">
         <v>64021</v>
@@ -22061,7 +22061,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715572357178</v>
+        <v>27.8715534210205</v>
       </c>
       <c r="H748" t="n">
         <v>89948</v>
@@ -22090,7 +22090,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782283782959</v>
+        <v>27.6782302856445</v>
       </c>
       <c r="H749" t="n">
         <v>99834</v>
@@ -22119,7 +22119,7 @@
         <v>33.3809013366699</v>
       </c>
       <c r="G750" t="n">
-        <v>25.8093852996826</v>
+        <v>25.809383392334</v>
       </c>
       <c r="H750" t="n">
         <v>76706</v>
@@ -22148,7 +22148,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363185882568</v>
+        <v>26.2363166809082</v>
       </c>
       <c r="H751" t="n">
         <v>69130</v>
@@ -22206,7 +22206,7 @@
         <v>31.8285446166992</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6091346740723</v>
+        <v>24.6091365814209</v>
       </c>
       <c r="H753" t="n">
         <v>76863</v>
@@ -22235,7 +22235,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193939208984</v>
+        <v>25.5193920135498</v>
       </c>
       <c r="H754" t="n">
         <v>87590</v>
@@ -22264,7 +22264,7 @@
         <v>32.9329071044922</v>
       </c>
       <c r="G755" t="n">
-        <v>25.463005065918</v>
+        <v>25.4630031585693</v>
       </c>
       <c r="H755" t="n">
         <v>93592</v>
@@ -22322,7 +22322,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H757" t="n">
         <v>41825</v>
@@ -22351,7 +22351,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983127593994</v>
+        <v>24.1983089447021</v>
       </c>
       <c r="H758" t="n">
         <v>28653</v>
@@ -22409,7 +22409,7 @@
         <v>31.2451076507568</v>
       </c>
       <c r="G760" t="n">
-        <v>24.1580333709717</v>
+        <v>24.1580352783203</v>
       </c>
       <c r="H760" t="n">
         <v>71582</v>
@@ -22438,7 +22438,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H761" t="n">
         <v>113781</v>
@@ -22525,7 +22525,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G764" t="n">
-        <v>24.6494121551514</v>
+        <v>24.6494102478027</v>
       </c>
       <c r="H764" t="n">
         <v>57921</v>
@@ -22583,7 +22583,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399700164795</v>
+        <v>24.4399738311768</v>
       </c>
       <c r="H766" t="n">
         <v>84803</v>
@@ -22612,7 +22612,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G767" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H767" t="n">
         <v>49945</v>
@@ -22670,7 +22670,7 @@
         <v>31.6618461608887</v>
       </c>
       <c r="G769" t="n">
-        <v>24.4802494049072</v>
+        <v>24.4802474975586</v>
       </c>
       <c r="H769" t="n">
         <v>65021</v>
@@ -22699,7 +22699,7 @@
         <v>31.8181247711182</v>
       </c>
       <c r="G770" t="n">
-        <v>24.6010780334473</v>
+        <v>24.6010799407959</v>
       </c>
       <c r="H770" t="n">
         <v>51778</v>
@@ -22728,7 +22728,7 @@
         <v>31.4013843536377</v>
       </c>
       <c r="G771" t="n">
-        <v>24.2788639068604</v>
+        <v>24.278865814209</v>
       </c>
       <c r="H771" t="n">
         <v>59036</v>
@@ -22757,7 +22757,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058681488037</v>
+        <v>21.8058700561523</v>
       </c>
       <c r="H772" t="n">
         <v>398596</v>
@@ -22786,7 +22786,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G773" t="n">
-        <v>20.13840675354</v>
+        <v>20.1384086608887</v>
       </c>
       <c r="H773" t="n">
         <v>541685</v>
@@ -22873,7 +22873,7 @@
         <v>25.5774383544922</v>
       </c>
       <c r="G776" t="n">
-        <v>19.7759170532227</v>
+        <v>19.775915145874</v>
       </c>
       <c r="H776" t="n">
         <v>194733</v>
@@ -22960,7 +22960,7 @@
         <v>25.5461826324463</v>
       </c>
       <c r="G779" t="n">
-        <v>19.7517490386963</v>
+        <v>19.7517509460449</v>
       </c>
       <c r="H779" t="n">
         <v>108228</v>
@@ -23018,7 +23018,7 @@
         <v>25.8795757293701</v>
       </c>
       <c r="G781" t="n">
-        <v>20.009521484375</v>
+        <v>20.0095233917236</v>
       </c>
       <c r="H781" t="n">
         <v>68304</v>
@@ -23250,7 +23250,7 @@
         <v>25.7962265014648</v>
       </c>
       <c r="G789" t="n">
-        <v>19.9450778961182</v>
+        <v>19.9450798034668</v>
       </c>
       <c r="H789" t="n">
         <v>147656</v>
@@ -23366,7 +23366,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H793" t="n">
         <v>765447</v>
@@ -23395,7 +23395,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G794" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H794" t="n">
         <v>554437</v>
@@ -23424,7 +23424,7 @@
         <v>27.7653255462646</v>
       </c>
       <c r="G795" t="n">
-        <v>21.4675445556641</v>
+        <v>21.4675426483154</v>
       </c>
       <c r="H795" t="n">
         <v>207446</v>
@@ -23511,7 +23511,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083866119385</v>
+        <v>21.0083885192871</v>
       </c>
       <c r="H798" t="n">
         <v>100025</v>
@@ -23540,7 +23540,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G799" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H799" t="n">
         <v>101229</v>
@@ -23598,7 +23598,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136722564697</v>
+        <v>20.6136741638184</v>
       </c>
       <c r="H801" t="n">
         <v>58055</v>
@@ -23714,7 +23714,7 @@
         <v>28.3695983886719</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9347534179688</v>
+        <v>21.9347553253174</v>
       </c>
       <c r="H805" t="n">
         <v>225218</v>
@@ -23801,7 +23801,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H808" t="n">
         <v>86623</v>
@@ -23830,7 +23830,7 @@
         <v>28.213321685791</v>
       </c>
       <c r="G809" t="n">
-        <v>21.8139247894287</v>
+        <v>21.8139228820801</v>
       </c>
       <c r="H809" t="n">
         <v>93205</v>
@@ -23888,7 +23888,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G811" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H811" t="n">
         <v>85007</v>
@@ -23975,7 +23975,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G814" t="n">
-        <v>20.2109069824219</v>
+        <v>20.2109050750732</v>
       </c>
       <c r="H814" t="n">
         <v>72125</v>
@@ -24033,7 +24033,7 @@
         <v>26.4109191894531</v>
       </c>
       <c r="G816" t="n">
-        <v>20.4203453063965</v>
+        <v>20.4203472137451</v>
       </c>
       <c r="H816" t="n">
         <v>121401</v>
@@ -24062,7 +24062,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908916473389</v>
+        <v>20.7908935546875</v>
       </c>
       <c r="H817" t="n">
         <v>135708</v>
@@ -24091,7 +24091,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H818" t="n">
         <v>142172</v>
@@ -24120,7 +24120,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G819" t="n">
-        <v>21.4917106628418</v>
+        <v>21.4917087554932</v>
       </c>
       <c r="H819" t="n">
         <v>111493</v>
@@ -24149,7 +24149,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G820" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H820" t="n">
         <v>116471</v>
@@ -24178,7 +24178,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5009002685547</v>
+        <v>20.5008983612061</v>
       </c>
       <c r="H821" t="n">
         <v>75021</v>
@@ -24207,7 +24207,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H822" t="n">
         <v>72133</v>
@@ -24236,7 +24236,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G823" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H823" t="n">
         <v>50892</v>
@@ -24265,7 +24265,7 @@
         <v>25.9837608337402</v>
       </c>
       <c r="G824" t="n">
-        <v>20.0900764465332</v>
+        <v>20.0900783538818</v>
       </c>
       <c r="H824" t="n">
         <v>122105</v>
@@ -24294,7 +24294,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G825" t="n">
-        <v>20.13840675354</v>
+        <v>20.1384086608887</v>
       </c>
       <c r="H825" t="n">
         <v>67600</v>
@@ -24381,7 +24381,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G828" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H828" t="n">
         <v>55529</v>
@@ -24410,7 +24410,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G829" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H829" t="n">
         <v>73545</v>
@@ -24439,7 +24439,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G830" t="n">
-        <v>20.4284000396729</v>
+        <v>20.4284019470215</v>
       </c>
       <c r="H830" t="n">
         <v>56424</v>
@@ -24497,7 +24497,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G832" t="n">
-        <v>20.4284000396729</v>
+        <v>20.4284019470215</v>
       </c>
       <c r="H832" t="n">
         <v>33693</v>
@@ -24526,7 +24526,7 @@
         <v>26.3171520233154</v>
       </c>
       <c r="G833" t="n">
-        <v>20.3478469848633</v>
+        <v>20.3478450775146</v>
       </c>
       <c r="H833" t="n">
         <v>51548</v>
@@ -24555,7 +24555,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G834" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H834" t="n">
         <v>86286</v>
@@ -24613,7 +24613,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H836" t="n">
         <v>263799</v>
@@ -24758,7 +24758,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G841" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H841" t="n">
         <v>67797</v>
@@ -24816,7 +24816,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G843" t="n">
-        <v>21.1856060028076</v>
+        <v>21.185604095459</v>
       </c>
       <c r="H843" t="n">
         <v>56383</v>
@@ -24961,7 +24961,7 @@
         <v>28.3800163269043</v>
       </c>
       <c r="G848" t="n">
-        <v>21.9428100585938</v>
+        <v>21.9428081512451</v>
       </c>
       <c r="H848" t="n">
         <v>228370</v>
@@ -25019,7 +25019,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150596618652</v>
+        <v>20.8150615692139</v>
       </c>
       <c r="H850" t="n">
         <v>79359</v>
@@ -25309,7 +25309,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G860" t="n">
-        <v>18.4145584106445</v>
+        <v>18.4145603179932</v>
       </c>
       <c r="H860" t="n">
         <v>61245</v>
@@ -25367,7 +25367,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H862" t="n">
         <v>131429</v>
@@ -25396,7 +25396,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G863" t="n">
-        <v>17.8667964935303</v>
+        <v>17.8667945861816</v>
       </c>
       <c r="H863" t="n">
         <v>69191</v>
@@ -25512,7 +25512,7 @@
         <v>21.8580303192139</v>
       </c>
       <c r="G867" t="n">
-        <v>16.9001522064209</v>
+        <v>16.9001502990723</v>
       </c>
       <c r="H867" t="n">
         <v>72401</v>
@@ -25628,7 +25628,7 @@
         <v>21.1704082489014</v>
       </c>
       <c r="G871" t="n">
-        <v>16.3684959411621</v>
+        <v>16.3684978485107</v>
       </c>
       <c r="H871" t="n">
         <v>85174</v>
@@ -25657,7 +25657,7 @@
         <v>20.9828758239746</v>
       </c>
       <c r="G872" t="n">
-        <v>16.223503112793</v>
+        <v>16.2235012054443</v>
       </c>
       <c r="H872" t="n">
         <v>64631</v>
@@ -25744,7 +25744,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907119750977</v>
+        <v>16.6907138824463</v>
       </c>
       <c r="H875" t="n">
         <v>61152</v>
@@ -25802,7 +25802,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134963989258</v>
+        <v>16.5134944915771</v>
       </c>
       <c r="H877" t="n">
         <v>48820</v>
@@ -25831,7 +25831,7 @@
         <v>21.0662231445312</v>
       </c>
       <c r="G878" t="n">
-        <v>16.2879447937012</v>
+        <v>16.2879428863525</v>
       </c>
       <c r="H878" t="n">
         <v>56625</v>
@@ -26005,7 +26005,7 @@
         <v>21.9205417633057</v>
       </c>
       <c r="G884" t="n">
-        <v>16.9484844207764</v>
+        <v>16.9484825134277</v>
       </c>
       <c r="H884" t="n">
         <v>58458</v>
@@ -26121,7 +26121,7 @@
         <v>22.4623031616211</v>
       </c>
       <c r="G888" t="n">
-        <v>17.3673610687256</v>
+        <v>17.3673629760742</v>
       </c>
       <c r="H888" t="n">
         <v>52523</v>
@@ -26208,7 +26208,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G891" t="n">
-        <v>19.1878757476807</v>
+        <v>19.187873840332</v>
       </c>
       <c r="H891" t="n">
         <v>189581</v>
@@ -26295,7 +26295,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H894" t="n">
         <v>1152937</v>
@@ -26440,7 +26440,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321659088135</v>
+        <v>25.6321678161621</v>
       </c>
       <c r="H899" t="n">
         <v>451580</v>
@@ -26498,7 +26498,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G901" t="n">
-        <v>26.1154880523682</v>
+        <v>26.1154899597168</v>
       </c>
       <c r="H901" t="n">
         <v>172580</v>
@@ -26527,7 +26527,7 @@
         <v>33.4642486572266</v>
       </c>
       <c r="G902" t="n">
-        <v>25.8738269805908</v>
+        <v>25.8738250732422</v>
       </c>
       <c r="H902" t="n">
         <v>95164</v>
@@ -26614,7 +26614,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H905" t="n">
         <v>121784</v>
@@ -26730,7 +26730,7 @@
         <v>29.4427051544189</v>
       </c>
       <c r="G909" t="n">
-        <v>22.7644557952881</v>
+        <v>22.7644577026367</v>
       </c>
       <c r="H909" t="n">
         <v>66556</v>
@@ -26759,7 +26759,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G910" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H910" t="n">
         <v>231966</v>
@@ -26788,7 +26788,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H911" t="n">
         <v>124106</v>
@@ -26846,7 +26846,7 @@
         <v>27.1923065185547</v>
       </c>
       <c r="G913" t="n">
-        <v>21.0244979858398</v>
+        <v>21.0244960784912</v>
       </c>
       <c r="H913" t="n">
         <v>226257</v>
@@ -26962,7 +26962,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G917" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H917" t="n">
         <v>101465</v>
@@ -26991,7 +26991,7 @@
         <v>24.7752132415771</v>
       </c>
       <c r="G918" t="n">
-        <v>19.1556549072266</v>
+        <v>19.1556529998779</v>
       </c>
       <c r="H918" t="n">
         <v>269232</v>
@@ -27020,7 +27020,7 @@
         <v>25.0877685546875</v>
       </c>
       <c r="G919" t="n">
-        <v>19.3973140716553</v>
+        <v>19.3973159790039</v>
       </c>
       <c r="H919" t="n">
         <v>122716</v>
@@ -27049,7 +27049,7 @@
         <v>26.9005889892578</v>
       </c>
       <c r="G920" t="n">
-        <v>20.7989482879639</v>
+        <v>20.7989463806152</v>
       </c>
       <c r="H920" t="n">
         <v>193491</v>
@@ -27078,7 +27078,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G921" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H921" t="n">
         <v>265131</v>
@@ -27107,7 +27107,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.9105892181396</v>
+        <v>21.910587310791</v>
       </c>
       <c r="H922" t="n">
         <v>183228</v>
@@ -27136,7 +27136,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H923" t="n">
         <v>187583</v>
@@ -27310,7 +27310,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.6850395202637</v>
+        <v>21.685037612915</v>
       </c>
       <c r="H929" t="n">
         <v>97800</v>
@@ -27397,7 +27397,7 @@
         <v>30.2136745452881</v>
       </c>
       <c r="G932" t="n">
-        <v>23.3605537414551</v>
+        <v>23.3605518341064</v>
       </c>
       <c r="H932" t="n">
         <v>674039</v>
@@ -27513,7 +27513,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H936" t="n">
         <v>340303</v>
@@ -27571,7 +27571,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416080474854</v>
+        <v>25.8416061401367</v>
       </c>
       <c r="H938" t="n">
         <v>128698</v>
@@ -27745,7 +27745,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G944" t="n">
-        <v>26.1154880523682</v>
+        <v>26.1154899597168</v>
       </c>
       <c r="H944" t="n">
         <v>380608</v>
@@ -27774,7 +27774,7 @@
         <v>33.7976417541504</v>
       </c>
       <c r="G945" t="n">
-        <v>26.1315994262695</v>
+        <v>26.1315975189209</v>
       </c>
       <c r="H945" t="n">
         <v>97707</v>
@@ -27803,7 +27803,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H946" t="n">
         <v>289611</v>
@@ -27832,7 +27832,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H947" t="n">
         <v>135438</v>
@@ -27890,7 +27890,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G949" t="n">
-        <v>25.1327342987061</v>
+        <v>25.1327362060547</v>
       </c>
       <c r="H949" t="n">
         <v>164909</v>
@@ -28006,7 +28006,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G953" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H953" t="n">
         <v>64598</v>
@@ -28064,7 +28064,7 @@
         <v>30.3178596496582</v>
       </c>
       <c r="G955" t="n">
-        <v>23.4411067962646</v>
+        <v>23.4411087036133</v>
       </c>
       <c r="H955" t="n">
         <v>170866</v>
@@ -28151,7 +28151,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727592468262</v>
       </c>
       <c r="H958" t="n">
         <v>106089</v>
@@ -28238,7 +28238,7 @@
         <v>30.5887413024902</v>
       </c>
       <c r="G961" t="n">
-        <v>23.6505470275879</v>
+        <v>23.6505451202393</v>
       </c>
       <c r="H961" t="n">
         <v>140338</v>
@@ -28354,7 +28354,7 @@
         <v>31.3388748168945</v>
       </c>
       <c r="G965" t="n">
-        <v>24.2305355072021</v>
+        <v>24.2305335998535</v>
       </c>
       <c r="H965" t="n">
         <v>256042</v>
@@ -28557,7 +28557,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G972" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H972" t="n">
         <v>39949</v>
@@ -28731,7 +28731,7 @@
         <v>31.2346897125244</v>
       </c>
       <c r="G978" t="n">
-        <v>24.1499805450439</v>
+        <v>24.1499786376953</v>
       </c>
       <c r="H978" t="n">
         <v>163262</v>
@@ -28818,7 +28818,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H981" t="n">
         <v>162326</v>
@@ -28876,7 +28876,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G983" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H983" t="n">
         <v>59846</v>
@@ -28963,7 +28963,7 @@
         <v>30.7971115112305</v>
       </c>
       <c r="G986" t="n">
-        <v>23.8116550445557</v>
+        <v>23.811653137207</v>
       </c>
       <c r="H986" t="n">
         <v>68207</v>
@@ -28992,7 +28992,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H987" t="n">
         <v>52930</v>
@@ -29021,7 +29021,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G988" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H988" t="n">
         <v>68067</v>
@@ -29050,7 +29050,7 @@
         <v>30.4428825378418</v>
       </c>
       <c r="G989" t="n">
-        <v>23.5377731323242</v>
+        <v>23.5377712249756</v>
       </c>
       <c r="H989" t="n">
         <v>96270</v>
@@ -29108,7 +29108,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H991" t="n">
         <v>68666</v>
@@ -29166,7 +29166,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G993" t="n">
-        <v>23.5861034393311</v>
+        <v>23.5861015319824</v>
       </c>
       <c r="H993" t="n">
         <v>46714</v>
@@ -29224,7 +29224,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727592468262</v>
       </c>
       <c r="H995" t="n">
         <v>242944</v>
@@ -29282,7 +29282,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H997" t="n">
         <v>75104</v>
@@ -29398,7 +29398,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1001" t="n">
-        <v>22.5227966308594</v>
+        <v>22.5227947235107</v>
       </c>
       <c r="H1001" t="n">
         <v>101377</v>
@@ -29427,7 +29427,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1002" t="n">
-        <v>22.635570526123</v>
+        <v>22.6355686187744</v>
       </c>
       <c r="H1002" t="n">
         <v>70616</v>
@@ -29456,7 +29456,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1003" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1003" t="n">
         <v>96029</v>
@@ -29514,7 +29514,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1005" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1005" t="n">
         <v>82787</v>
@@ -29543,7 +29543,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1006" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1006" t="n">
         <v>86215</v>
@@ -29601,7 +29601,7 @@
         <v>29.2968463897705</v>
       </c>
       <c r="G1008" t="n">
-        <v>22.6516819000244</v>
+        <v>22.651683807373</v>
       </c>
       <c r="H1008" t="n">
         <v>46369</v>
@@ -29630,7 +29630,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1009" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1009" t="n">
         <v>71916</v>
@@ -29659,7 +29659,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1010" t="n">
-        <v>21.9911403656006</v>
+        <v>21.9911422729492</v>
       </c>
       <c r="H1010" t="n">
         <v>116651</v>
@@ -29688,7 +29688,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844711303711</v>
+        <v>22.1844692230225</v>
       </c>
       <c r="H1011" t="n">
         <v>138206</v>
@@ -29746,7 +29746,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1013" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1013" t="n">
         <v>50162</v>
@@ -29775,7 +29775,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1014" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1014" t="n">
         <v>48803</v>
@@ -29804,7 +29804,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1015" t="n">
-        <v>22.5227966308594</v>
+        <v>22.5227947235107</v>
       </c>
       <c r="H1015" t="n">
         <v>63776</v>
@@ -30094,7 +30094,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821304321289</v>
+        <v>27.0821323394775</v>
       </c>
       <c r="H1025" t="n">
         <v>329331</v>
@@ -30123,7 +30123,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1026" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1026" t="n">
         <v>378731</v>
@@ -30181,7 +30181,7 @@
         <v>35.7146453857422</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.6137828826904</v>
+        <v>27.6137847900391</v>
       </c>
       <c r="H1028" t="n">
         <v>133385</v>
@@ -30210,7 +30210,7 @@
         <v>39.069408416748</v>
       </c>
       <c r="G1029" t="n">
-        <v>30.2076148986816</v>
+        <v>30.2076110839844</v>
       </c>
       <c r="H1029" t="n">
         <v>1179620</v>
@@ -30239,7 +30239,7 @@
         <v>38.9652214050293</v>
       </c>
       <c r="G1030" t="n">
-        <v>30.1270580291748</v>
+        <v>30.1270599365234</v>
       </c>
       <c r="H1030" t="n">
         <v>657786</v>
@@ -30268,7 +30268,7 @@
         <v>37.9650459289551</v>
       </c>
       <c r="G1031" t="n">
-        <v>29.3537425994873</v>
+        <v>29.3537464141846</v>
       </c>
       <c r="H1031" t="n">
         <v>257810</v>
@@ -30384,7 +30384,7 @@
         <v>37.73583984375</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1765270233154</v>
+        <v>29.1765289306641</v>
       </c>
       <c r="H1035" t="n">
         <v>228495</v>
@@ -30442,7 +30442,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1037" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1037" t="n">
         <v>256721</v>
@@ -30471,7 +30471,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1038" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1038" t="n">
         <v>147337</v>
@@ -30500,7 +30500,7 @@
         <v>37.2774238586426</v>
       </c>
       <c r="G1039" t="n">
-        <v>28.8220901489258</v>
+        <v>28.8220882415771</v>
       </c>
       <c r="H1039" t="n">
         <v>439132</v>
@@ -30529,7 +30529,7 @@
         <v>37.1940765380859</v>
       </c>
       <c r="G1040" t="n">
-        <v>28.7576484680176</v>
+        <v>28.7576465606689</v>
       </c>
       <c r="H1040" t="n">
         <v>194824</v>
@@ -30558,7 +30558,7 @@
         <v>37.9233703613281</v>
       </c>
       <c r="G1041" t="n">
-        <v>29.3215217590332</v>
+        <v>29.3215198516846</v>
       </c>
       <c r="H1041" t="n">
         <v>364128</v>
@@ -30616,7 +30616,7 @@
         <v>36.1105499267578</v>
       </c>
       <c r="G1043" t="n">
-        <v>27.9198894500732</v>
+        <v>27.9198875427246</v>
       </c>
       <c r="H1043" t="n">
         <v>263584</v>
@@ -30761,7 +30761,7 @@
         <v>37.5274696350098</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.0154190063477</v>
+        <v>29.0154209136963</v>
       </c>
       <c r="H1048" t="n">
         <v>161694</v>
@@ -30790,7 +30790,7 @@
         <v>39.4444732666016</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.4976062774658</v>
+        <v>30.4976043701172</v>
       </c>
       <c r="H1049" t="n">
         <v>881669</v>
@@ -30877,7 +30877,7 @@
         <v>42.5075149536133</v>
       </c>
       <c r="G1052" t="n">
-        <v>32.8658790588379</v>
+        <v>32.8658828735352</v>
       </c>
       <c r="H1052" t="n">
         <v>937883</v>
@@ -30935,7 +30935,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820652008057</v>
+        <v>29.9820613861084</v>
       </c>
       <c r="H1054" t="n">
         <v>787822</v>
@@ -31051,7 +31051,7 @@
         <v>36.1313896179199</v>
       </c>
       <c r="G1058" t="n">
-        <v>27.9360027313232</v>
+        <v>27.9360008239746</v>
       </c>
       <c r="H1058" t="n">
         <v>542723</v>
@@ -31196,7 +31196,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H1063" t="n">
         <v>342146</v>
@@ -31225,7 +31225,7 @@
         <v>24.6085166931152</v>
       </c>
       <c r="G1064" t="n">
-        <v>19.0267677307129</v>
+        <v>19.0267696380615</v>
       </c>
       <c r="H1064" t="n">
         <v>440901</v>
@@ -31283,7 +31283,7 @@
         <v>20.8578548431396</v>
       </c>
       <c r="G1066" t="n">
-        <v>16.126838684082</v>
+        <v>16.1268367767334</v>
       </c>
       <c r="H1066" t="n">
         <v>607780</v>
@@ -31312,7 +31312,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1067" t="n">
         <v>602051</v>
@@ -31341,7 +31341,7 @@
         <v>21.0453872680664</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.2718334197998</v>
+        <v>16.2718353271484</v>
       </c>
       <c r="H1068" t="n">
         <v>439578</v>
@@ -31457,7 +31457,7 @@
         <v>20.7953433990479</v>
       </c>
       <c r="G1072" t="n">
-        <v>16.0785045623779</v>
+        <v>16.0785064697266</v>
       </c>
       <c r="H1072" t="n">
         <v>293641</v>
@@ -31486,7 +31486,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1073" t="n">
-        <v>16.5618267059326</v>
+        <v>16.561824798584</v>
       </c>
       <c r="H1073" t="n">
         <v>191571</v>
@@ -31515,7 +31515,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1074" t="n">
         <v>278986</v>
@@ -31631,7 +31631,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1078" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1078" t="n">
         <v>133373</v>
@@ -31660,7 +31660,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1079" t="n">
-        <v>18.2534523010254</v>
+        <v>18.253454208374</v>
       </c>
       <c r="H1079" t="n">
         <v>119826</v>
@@ -31718,7 +31718,7 @@
         <v>23.6708507537842</v>
       </c>
       <c r="G1081" t="n">
-        <v>18.3017845153809</v>
+        <v>18.3017864227295</v>
       </c>
       <c r="H1081" t="n">
         <v>80116</v>
@@ -31747,7 +31747,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1082" t="n">
         <v>65084</v>
@@ -31834,7 +31834,7 @@
         <v>24.5251693725586</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.9623260498047</v>
+        <v>18.9623241424561</v>
       </c>
       <c r="H1085" t="n">
         <v>121224</v>
@@ -31950,7 +31950,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1089" t="n">
         <v>85682</v>
@@ -32008,7 +32008,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1091" t="n">
         <v>40526</v>
@@ -32095,7 +32095,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1094" t="n">
-        <v>17.6734676361084</v>
+        <v>17.6734657287598</v>
       </c>
       <c r="H1094" t="n">
         <v>86867</v>
@@ -32124,7 +32124,7 @@
         <v>22.3164443969727</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.2545890808105</v>
+        <v>17.2545871734619</v>
       </c>
       <c r="H1095" t="n">
         <v>75023</v>
@@ -32153,7 +32153,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1096" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1096" t="n">
         <v>91309</v>
@@ -32182,7 +32182,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1097" t="n">
         <v>181346</v>
@@ -32269,7 +32269,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1100" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1100" t="n">
         <v>53003</v>
@@ -32298,7 +32298,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1101" t="n">
         <v>70876</v>
@@ -32327,7 +32327,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1102" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1102" t="n">
         <v>32012</v>
@@ -32385,7 +32385,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1104" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1104" t="n">
         <v>60478</v>
@@ -32414,7 +32414,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1105" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1105" t="n">
         <v>47186</v>
@@ -32501,7 +32501,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1108" t="n">
-        <v>17.9634609222412</v>
+        <v>17.9634590148926</v>
       </c>
       <c r="H1108" t="n">
         <v>76222</v>
@@ -32559,7 +32559,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G1110" t="n">
-        <v>17.8667964935303</v>
+        <v>17.8667945861816</v>
       </c>
       <c r="H1110" t="n">
         <v>49897</v>
@@ -32617,7 +32617,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.5618267059326</v>
+        <v>16.561824798584</v>
       </c>
       <c r="H1112" t="n">
         <v>116319</v>
@@ -32675,7 +32675,7 @@
         <v>21.3371047973633</v>
       </c>
       <c r="G1114" t="n">
-        <v>16.4973831176758</v>
+        <v>16.4973850250244</v>
       </c>
       <c r="H1114" t="n">
         <v>115150</v>
@@ -32704,7 +32704,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1115" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1115" t="n">
         <v>101008</v>
@@ -32820,7 +32820,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G1119" t="n">
-        <v>21.1856060028076</v>
+        <v>21.185604095459</v>
       </c>
       <c r="H1119" t="n">
         <v>1322864</v>
@@ -32878,7 +32878,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1121" t="n">
         <v>244265</v>
@@ -32907,7 +32907,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683616638184</v>
+        <v>22.1683597564697</v>
       </c>
       <c r="H1122" t="n">
         <v>393290</v>
@@ -32936,7 +32936,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.635570526123</v>
+        <v>22.6355686187744</v>
       </c>
       <c r="H1123" t="n">
         <v>408833</v>
@@ -33023,7 +33023,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1126" t="n">
         <v>401649</v>
@@ -33110,7 +33110,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1129" t="n">
-        <v>22.861120223999</v>
+        <v>22.8611183166504</v>
       </c>
       <c r="H1129" t="n">
         <v>230255</v>
@@ -33139,7 +33139,7 @@
         <v>29.2134971618652</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.5872383117676</v>
+        <v>22.5872364044189</v>
       </c>
       <c r="H1130" t="n">
         <v>133679</v>
@@ -33197,7 +33197,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1132" t="n">
         <v>117120</v>
@@ -33226,7 +33226,7 @@
         <v>31.0263175964355</v>
       </c>
       <c r="G1133" t="n">
-        <v>23.9888706207275</v>
+        <v>23.9888725280762</v>
       </c>
       <c r="H1133" t="n">
         <v>120603</v>
@@ -33371,7 +33371,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021457672119</v>
+        <v>26.5021476745605</v>
       </c>
       <c r="H1138" t="n">
         <v>299299</v>
@@ -33400,7 +33400,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.229398727417</v>
+        <v>25.2293968200684</v>
       </c>
       <c r="H1139" t="n">
         <v>249320</v>
@@ -33458,7 +33458,7 @@
         <v>32.859977722168</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.4066162109375</v>
+        <v>25.4066181182861</v>
       </c>
       <c r="H1141" t="n">
         <v>424729</v>
@@ -33574,7 +33574,7 @@
         <v>32.8808135986328</v>
       </c>
       <c r="G1145" t="n">
-        <v>25.4227275848389</v>
+        <v>25.4227256774902</v>
       </c>
       <c r="H1145" t="n">
         <v>211348</v>
@@ -33603,7 +33603,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1146" t="n">
         <v>101636</v>
@@ -33632,7 +33632,7 @@
         <v>31.5889186859131</v>
       </c>
       <c r="G1147" t="n">
-        <v>24.4238624572754</v>
+        <v>24.4238605499268</v>
       </c>
       <c r="H1147" t="n">
         <v>65647</v>
@@ -33661,7 +33661,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G1148" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H1148" t="n">
         <v>124950</v>
@@ -33690,7 +33690,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G1149" t="n">
-        <v>25.1327342987061</v>
+        <v>25.1327362060547</v>
       </c>
       <c r="H1149" t="n">
         <v>67331</v>
@@ -33719,7 +33719,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1150" t="n">
         <v>90180</v>
@@ -33806,7 +33806,7 @@
         <v>32.7974662780762</v>
       </c>
       <c r="G1153" t="n">
-        <v>25.358283996582</v>
+        <v>25.3582859039307</v>
       </c>
       <c r="H1153" t="n">
         <v>172785</v>
@@ -33893,7 +33893,7 @@
         <v>37.6524887084961</v>
       </c>
       <c r="G1156" t="n">
-        <v>29.1120834350586</v>
+        <v>29.11208152771</v>
       </c>
       <c r="H1156" t="n">
         <v>1160270</v>
@@ -33922,7 +33922,7 @@
         <v>40.2154426574707</v>
       </c>
       <c r="G1157" t="n">
-        <v>31.0937023162842</v>
+        <v>31.0937042236328</v>
       </c>
       <c r="H1157" t="n">
         <v>1079270</v>
@@ -33951,7 +33951,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303916931152</v>
+        <v>30.0303936004639</v>
       </c>
       <c r="H1158" t="n">
         <v>499559</v>
@@ -34009,7 +34009,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049129486084</v>
+        <v>26.9049110412598</v>
       </c>
       <c r="H1160" t="n">
         <v>710323</v>
@@ -34067,7 +34067,7 @@
         <v>33.4017372131348</v>
       </c>
       <c r="G1162" t="n">
-        <v>25.8254928588867</v>
+        <v>25.8254947662354</v>
       </c>
       <c r="H1162" t="n">
         <v>201608</v>
@@ -34096,7 +34096,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G1163" t="n">
-        <v>24.6494121551514</v>
+        <v>24.6494102478027</v>
       </c>
       <c r="H1163" t="n">
         <v>167963</v>
@@ -34125,7 +34125,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655216217041</v>
+        <v>24.6655235290527</v>
       </c>
       <c r="H1164" t="n">
         <v>153075</v>
@@ -34241,7 +34241,7 @@
         <v>32.4432373046875</v>
       </c>
       <c r="G1168" t="n">
-        <v>25.0844020843506</v>
+        <v>25.0844039916992</v>
       </c>
       <c r="H1168" t="n">
         <v>285284</v>
@@ -34444,7 +34444,7 @@
         <v>29.3801937103271</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7161235809326</v>
+        <v>22.7161254882812</v>
       </c>
       <c r="H1175" t="n">
         <v>84856</v>
@@ -34531,7 +34531,7 @@
         <v>30.2970237731934</v>
       </c>
       <c r="G1178" t="n">
-        <v>23.4249973297119</v>
+        <v>23.4249954223633</v>
       </c>
       <c r="H1178" t="n">
         <v>90363</v>
@@ -34560,7 +34560,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G1179" t="n">
-        <v>23.5861034393311</v>
+        <v>23.5861015319824</v>
       </c>
       <c r="H1179" t="n">
         <v>120513</v>
@@ -34618,7 +34618,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H1181" t="n">
         <v>179328</v>
@@ -34647,7 +34647,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.2316703796387</v>
+        <v>23.23166847229</v>
       </c>
       <c r="H1182" t="n">
         <v>79634</v>
@@ -34705,7 +34705,7 @@
         <v>30.6720886230469</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.7149887084961</v>
+        <v>23.7149906158447</v>
       </c>
       <c r="H1184" t="n">
         <v>210874</v>
@@ -34763,7 +34763,7 @@
         <v>29.9011192321777</v>
       </c>
       <c r="G1186" t="n">
-        <v>23.1188907623291</v>
+        <v>23.1188926696777</v>
       </c>
       <c r="H1186" t="n">
         <v>142772</v>
@@ -34821,7 +34821,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.861120223999</v>
+        <v>22.8611183166504</v>
       </c>
       <c r="H1188" t="n">
         <v>181360</v>
@@ -34879,7 +34879,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094543457031</v>
+        <v>22.9094524383545</v>
       </c>
       <c r="H1190" t="n">
         <v>71944</v>
@@ -34995,7 +34995,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416751861572</v>
+        <v>22.9416732788086</v>
       </c>
       <c r="H1194" t="n">
         <v>35197</v>
@@ -35024,7 +35024,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1195" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1195" t="n">
         <v>37758</v>
@@ -35082,7 +35082,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1197" t="n">
         <v>53084</v>
@@ -35111,7 +35111,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1198" t="n">
-        <v>21.9911403656006</v>
+        <v>21.9911422729492</v>
       </c>
       <c r="H1198" t="n">
         <v>75589</v>
@@ -35140,7 +35140,7 @@
         <v>28.0049514770508</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.6528167724609</v>
+        <v>21.6528186798096</v>
       </c>
       <c r="H1199" t="n">
         <v>87498</v>
@@ -35198,7 +35198,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1201" t="n">
         <v>213623</v>
@@ -35256,7 +35256,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G1203" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H1203" t="n">
         <v>72630</v>
@@ -35285,7 +35285,7 @@
         <v>28.5258750915527</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.0555820465088</v>
+        <v>22.0555839538574</v>
       </c>
       <c r="H1204" t="n">
         <v>90794</v>
@@ -35314,7 +35314,7 @@
         <v>28.4008541107178</v>
       </c>
       <c r="G1205" t="n">
-        <v>21.9589195251465</v>
+        <v>21.9589214324951</v>
       </c>
       <c r="H1205" t="n">
         <v>82873</v>
@@ -35372,7 +35372,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1207" t="n">
         <v>83126</v>
@@ -35401,7 +35401,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.4917106628418</v>
+        <v>21.4917087554932</v>
       </c>
       <c r="H1208" t="n">
         <v>131767</v>
@@ -35430,7 +35430,7 @@
         <v>28.2758312225342</v>
       </c>
       <c r="G1209" t="n">
-        <v>21.8622550964355</v>
+        <v>21.8622531890869</v>
       </c>
       <c r="H1209" t="n">
         <v>84042</v>
@@ -35459,7 +35459,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039161682129</v>
+        <v>22.1039180755615</v>
       </c>
       <c r="H1210" t="n">
         <v>66037</v>
@@ -35488,7 +35488,7 @@
         <v>28.9842910766602</v>
       </c>
       <c r="G1211" t="n">
-        <v>22.4100208282471</v>
+        <v>22.4100189208984</v>
       </c>
       <c r="H1211" t="n">
         <v>95686</v>
@@ -35517,7 +35517,7 @@
         <v>27.7757434844971</v>
       </c>
       <c r="G1212" t="n">
-        <v>21.4755992889404</v>
+        <v>21.4755973815918</v>
       </c>
       <c r="H1212" t="n">
         <v>157370</v>
@@ -35546,7 +35546,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H1213" t="n">
         <v>153694</v>
@@ -35575,7 +35575,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672920227051</v>
+        <v>20.2672939300537</v>
       </c>
       <c r="H1214" t="n">
         <v>217939</v>
@@ -35633,7 +35633,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1216" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H1216" t="n">
         <v>408334</v>
@@ -35720,7 +35720,7 @@
         <v>24.2334518432617</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.7367763519287</v>
+        <v>18.7367744445801</v>
       </c>
       <c r="H1219" t="n">
         <v>241385</v>
@@ -35807,7 +35807,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1222" t="n">
         <v>166257</v>
@@ -35952,7 +35952,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1227" t="n">
-        <v>16.4651622772217</v>
+        <v>16.4651641845703</v>
       </c>
       <c r="H1227" t="n">
         <v>140219</v>
@@ -36271,7 +36271,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1238" t="n">
-        <v>18.3662261962891</v>
+        <v>18.3662281036377</v>
       </c>
       <c r="H1238" t="n">
         <v>189606</v>
@@ -36445,7 +36445,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.7839698791504</v>
+        <v>19.783971786499</v>
       </c>
       <c r="H1244" t="n">
         <v>193590</v>
@@ -36474,7 +36474,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1245" t="n">
-        <v>20.0417423248291</v>
+        <v>20.0417442321777</v>
       </c>
       <c r="H1245" t="n">
         <v>379252</v>
@@ -36503,7 +36503,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G1246" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H1246" t="n">
         <v>327050</v>
@@ -36590,7 +36590,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1249" t="n">
         <v>265701</v>
@@ -36619,7 +36619,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1250" t="n">
         <v>489077</v>
@@ -36735,7 +36735,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1254" t="n">
         <v>171179</v>
@@ -36793,7 +36793,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1256" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1256" t="n">
         <v>220502</v>
@@ -36822,7 +36822,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1257" t="n">
         <v>258497</v>
@@ -36851,7 +36851,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1258" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1258" t="n">
         <v>197297</v>
@@ -36880,7 +36880,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1259" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1259" t="n">
         <v>142502</v>
@@ -36909,7 +36909,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1260" t="n">
         <v>115703</v>
@@ -36938,7 +36938,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1261" t="n">
         <v>101768</v>
@@ -36967,7 +36967,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1262" t="n">
         <v>79845</v>
@@ -36996,7 +36996,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1263" t="n">
         <v>100240</v>
@@ -37025,7 +37025,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.4318046569824</v>
+        <v>17.4318065643311</v>
       </c>
       <c r="H1264" t="n">
         <v>328679</v>
@@ -37199,7 +37199,7 @@
         <v>21.7330093383789</v>
       </c>
       <c r="G1270" t="n">
-        <v>16.80348777771</v>
+        <v>16.8034896850586</v>
       </c>
       <c r="H1270" t="n">
         <v>111326</v>
@@ -37257,7 +37257,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.6734676361084</v>
+        <v>17.6734657287598</v>
       </c>
       <c r="H1272" t="n">
         <v>374152</v>
@@ -37344,7 +37344,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.3662261962891</v>
+        <v>18.3662281036377</v>
       </c>
       <c r="H1275" t="n">
         <v>170011</v>
@@ -37402,7 +37402,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1277" t="n">
         <v>133192</v>
@@ -37489,7 +37489,7 @@
         <v>22.3997936248779</v>
       </c>
       <c r="G1280" t="n">
-        <v>17.3190326690674</v>
+        <v>17.3190307617188</v>
       </c>
       <c r="H1280" t="n">
         <v>107216</v>
@@ -37518,7 +37518,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.4318046569824</v>
+        <v>17.4318065643311</v>
       </c>
       <c r="H1281" t="n">
         <v>82476</v>
@@ -37576,7 +37576,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1283" t="n">
         <v>188315</v>
@@ -37634,7 +37634,7 @@
         <v>22.4414672851562</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.3512535095215</v>
+        <v>17.3512516021729</v>
       </c>
       <c r="H1285" t="n">
         <v>118092</v>
@@ -37692,7 +37692,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1287" t="n">
-        <v>17.1901454925537</v>
+        <v>17.1901473999023</v>
       </c>
       <c r="H1287" t="n">
         <v>74707</v>
@@ -37721,7 +37721,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934791564941</v>
+        <v>17.0934810638428</v>
       </c>
       <c r="H1288" t="n">
         <v>71228</v>
@@ -37808,7 +37808,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1291" t="n">
         <v>77029</v>
@@ -37866,7 +37866,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801406860352</v>
+        <v>17.4801387786865</v>
       </c>
       <c r="H1293" t="n">
         <v>213107</v>
@@ -37895,7 +37895,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1294" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1294" t="n">
         <v>170814</v>
@@ -38011,7 +38011,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H1298" t="n">
         <v>910482</v>
@@ -38098,7 +38098,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.5895080566406</v>
+        <v>20.5895099639893</v>
       </c>
       <c r="H1301" t="n">
         <v>361172</v>
@@ -38156,7 +38156,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.5895080566406</v>
+        <v>20.5895099639893</v>
       </c>
       <c r="H1303" t="n">
         <v>234506</v>
@@ -38185,7 +38185,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H1304" t="n">
         <v>141753</v>
@@ -38214,7 +38214,7 @@
         <v>26.6088714599609</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5733985900879</v>
+        <v>20.5733966827393</v>
       </c>
       <c r="H1305" t="n">
         <v>187199</v>
@@ -38475,7 +38475,7 @@
         <v>24.8793983459473</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.2362079620361</v>
+        <v>19.2362060546875</v>
       </c>
       <c r="H1314" t="n">
         <v>83220</v>
@@ -38504,7 +38504,7 @@
         <v>25.0460948944092</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.3650932312012</v>
+        <v>19.3650951385498</v>
       </c>
       <c r="H1315" t="n">
         <v>145650</v>
@@ -38533,7 +38533,7 @@
         <v>25.504508972168</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.7195281982422</v>
+        <v>19.7195301055908</v>
       </c>
       <c r="H1316" t="n">
         <v>192020</v>
@@ -38649,7 +38649,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1320" t="n">
         <v>181732</v>
@@ -38678,7 +38678,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1321" t="n">
         <v>147765</v>
@@ -38736,7 +38736,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750980377197</v>
+        <v>19.0750999450684</v>
       </c>
       <c r="H1323" t="n">
         <v>120557</v>
@@ -38823,7 +38823,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1326" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1326" t="n">
         <v>76196</v>
@@ -38910,7 +38910,7 @@
         <v>24.0250816345215</v>
       </c>
       <c r="G1329" t="n">
-        <v>18.5756702423096</v>
+        <v>18.5756683349609</v>
       </c>
       <c r="H1329" t="n">
         <v>59340</v>
@@ -38997,7 +38997,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.6078910827637</v>
+        <v>18.607889175415</v>
       </c>
       <c r="H1332" t="n">
         <v>53943</v>
@@ -39026,7 +39026,7 @@
         <v>23.8375473022461</v>
       </c>
       <c r="G1333" t="n">
-        <v>18.4306697845459</v>
+        <v>18.4306716918945</v>
       </c>
       <c r="H1333" t="n">
         <v>62096</v>
@@ -39113,7 +39113,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.8334407806396</v>
+        <v>18.833438873291</v>
       </c>
       <c r="H1336" t="n">
         <v>97937</v>
@@ -39142,7 +39142,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353908538818</v>
+        <v>18.5353889465332</v>
       </c>
       <c r="H1337" t="n">
         <v>143301</v>
@@ -39171,7 +39171,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1338" t="n">
-        <v>18.4870586395264</v>
+        <v>18.4870567321777</v>
       </c>
       <c r="H1338" t="n">
         <v>70075</v>
@@ -39316,7 +39316,7 @@
         <v>24.4418201446533</v>
       </c>
       <c r="G1343" t="n">
-        <v>18.8978824615479</v>
+        <v>18.8978805541992</v>
       </c>
       <c r="H1343" t="n">
         <v>117770</v>
@@ -39345,7 +39345,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864940643311</v>
+        <v>18.9864902496338</v>
       </c>
       <c r="H1344" t="n">
         <v>82258</v>
@@ -39403,7 +39403,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112266540527</v>
+        <v>18.5112228393555</v>
       </c>
       <c r="H1346" t="n">
         <v>91238</v>
@@ -39519,7 +39519,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1350" t="n">
-        <v>18.5434474945068</v>
+        <v>18.5434455871582</v>
       </c>
       <c r="H1350" t="n">
         <v>31645</v>
@@ -39577,7 +39577,7 @@
         <v>23.5875034332275</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.2373428344727</v>
+        <v>18.237340927124</v>
       </c>
       <c r="H1352" t="n">
         <v>119737</v>
@@ -39635,7 +39635,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1354" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1354" t="n">
         <v>116974</v>
@@ -39693,7 +39693,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187149047852</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1356" t="n">
         <v>228828</v>
@@ -39722,7 +39722,7 @@
         <v>24.2959613800049</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.7851047515869</v>
+        <v>18.7851066589355</v>
       </c>
       <c r="H1357" t="n">
         <v>232305</v>
@@ -39809,7 +39809,7 @@
         <v>24.5043315887451</v>
       </c>
       <c r="G1360" t="n">
-        <v>18.9462127685547</v>
+        <v>18.9462146759033</v>
       </c>
       <c r="H1360" t="n">
         <v>123870</v>
@@ -39838,7 +39838,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1361" t="n">
         <v>157303</v>
@@ -39925,7 +39925,7 @@
         <v>24.806468963623</v>
       </c>
       <c r="G1364" t="n">
-        <v>19.1798210144043</v>
+        <v>19.1798191070557</v>
       </c>
       <c r="H1364" t="n">
         <v>128975</v>
@@ -39954,7 +39954,7 @@
         <v>26.4525928497314</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.4525661468506</v>
+        <v>20.4525680541992</v>
       </c>
       <c r="H1365" t="n">
         <v>970320</v>
@@ -40128,7 +40128,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1371" t="n">
         <v>230606</v>
@@ -40186,7 +40186,7 @@
         <v>25.8483200073242</v>
       </c>
       <c r="G1373" t="n">
-        <v>19.9853572845459</v>
+        <v>19.9853553771973</v>
       </c>
       <c r="H1373" t="n">
         <v>1023932</v>
@@ -40302,7 +40302,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531345367432</v>
+        <v>19.9531364440918</v>
       </c>
       <c r="H1377" t="n">
         <v>173483</v>
@@ -40331,7 +40331,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G1378" t="n">
-        <v>20.2109069824219</v>
+        <v>20.2109050750732</v>
       </c>
       <c r="H1378" t="n">
         <v>358719</v>
@@ -40389,7 +40389,7 @@
         <v>26.2858963012695</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.3236808776855</v>
+        <v>20.3236789703369</v>
       </c>
       <c r="H1380" t="n">
         <v>657639</v>
@@ -40447,7 +40447,7 @@
         <v>25.8379001617432</v>
       </c>
       <c r="G1382" t="n">
-        <v>19.9772987365723</v>
+        <v>19.9773006439209</v>
       </c>
       <c r="H1382" t="n">
         <v>272090</v>
@@ -40476,7 +40476,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.0417423248291</v>
+        <v>20.0417442321777</v>
       </c>
       <c r="H1383" t="n">
         <v>242252</v>
@@ -40563,7 +40563,7 @@
         <v>25.0565128326416</v>
       </c>
       <c r="G1386" t="n">
-        <v>19.3731498718262</v>
+        <v>19.3731479644775</v>
       </c>
       <c r="H1386" t="n">
         <v>256812</v>
@@ -40592,7 +40592,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G1387" t="n">
-        <v>19.1878757476807</v>
+        <v>19.187873840332</v>
       </c>
       <c r="H1387" t="n">
         <v>247944</v>
@@ -40650,7 +40650,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187149047852</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1389" t="n">
         <v>201477</v>
@@ -40795,7 +40795,7 @@
         <v>24.2021942138672</v>
       </c>
       <c r="G1394" t="n">
-        <v>18.7126083374023</v>
+        <v>18.7126064300537</v>
       </c>
       <c r="H1394" t="n">
         <v>201948</v>
@@ -40940,7 +40940,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1399" t="n">
-        <v>18.4870586395264</v>
+        <v>18.4870567321777</v>
       </c>
       <c r="H1399" t="n">
         <v>189206</v>
@@ -40969,7 +40969,7 @@
         <v>23.6187591552734</v>
       </c>
       <c r="G1400" t="n">
-        <v>18.2615089416504</v>
+        <v>18.2615070343018</v>
       </c>
       <c r="H1400" t="n">
         <v>207750</v>
@@ -40998,7 +40998,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1401" t="n">
-        <v>18.108455657959</v>
+        <v>18.1084575653076</v>
       </c>
       <c r="H1401" t="n">
         <v>352284</v>
@@ -41085,7 +41085,7 @@
         <v>23.472900390625</v>
       </c>
       <c r="G1404" t="n">
-        <v>18.1487350463867</v>
+        <v>18.1487331390381</v>
       </c>
       <c r="H1404" t="n">
         <v>251573</v>
@@ -41346,7 +41346,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1413" t="n">
         <v>387357</v>
@@ -41375,7 +41375,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1414" t="n">
         <v>234798</v>
@@ -41404,7 +41404,7 @@
         <v>23.5562477111816</v>
       </c>
       <c r="G1415" t="n">
-        <v>18.2131767272949</v>
+        <v>18.2131748199463</v>
       </c>
       <c r="H1415" t="n">
         <v>138909</v>
@@ -41433,7 +41433,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1416" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1416" t="n">
         <v>113622</v>
@@ -41462,7 +41462,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1417" t="n">
-        <v>18.2534523010254</v>
+        <v>18.253454208374</v>
       </c>
       <c r="H1417" t="n">
         <v>115441</v>
@@ -41520,7 +41520,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1419" t="n">
-        <v>18.5434474945068</v>
+        <v>18.5434455871582</v>
       </c>
       <c r="H1419" t="n">
         <v>305385</v>
@@ -41665,7 +41665,7 @@
         <v>24.3897285461426</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.8576068878174</v>
+        <v>18.8576049804688</v>
       </c>
       <c r="H1424" t="n">
         <v>537633</v>
@@ -41723,7 +41723,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428771972656</v>
+        <v>19.0428791046143</v>
       </c>
       <c r="H1426" t="n">
         <v>251332</v>
@@ -41752,7 +41752,7 @@
         <v>24.2230319976807</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.7287197113037</v>
+        <v>18.7287216186523</v>
       </c>
       <c r="H1427" t="n">
         <v>215889</v>
@@ -41839,7 +41839,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742847442627</v>
+        <v>18.3742828369141</v>
       </c>
       <c r="H1430" t="n">
         <v>93708</v>
@@ -41897,7 +41897,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292861938477</v>
+        <v>18.2292881011963</v>
       </c>
       <c r="H1432" t="n">
         <v>168351</v>
@@ -41984,7 +41984,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1435" t="n">
-        <v>17.9634609222412</v>
+        <v>17.9634590148926</v>
       </c>
       <c r="H1435" t="n">
         <v>76206</v>
@@ -42013,7 +42013,7 @@
         <v>23.5354118347168</v>
       </c>
       <c r="G1436" t="n">
-        <v>18.1970653533936</v>
+        <v>18.1970672607422</v>
       </c>
       <c r="H1436" t="n">
         <v>361330</v>
@@ -42071,7 +42071,7 @@
         <v>23.2853660583496</v>
       </c>
       <c r="G1438" t="n">
-        <v>18.0037364959717</v>
+        <v>18.0037384033203</v>
       </c>
       <c r="H1438" t="n">
         <v>138869</v>
@@ -42129,7 +42129,7 @@
         <v>23.4520626068115</v>
       </c>
       <c r="G1440" t="n">
-        <v>18.1326217651367</v>
+        <v>18.1326236724854</v>
       </c>
       <c r="H1440" t="n">
         <v>97025</v>
@@ -42216,7 +42216,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1443" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1443" t="n">
         <v>129448</v>
@@ -42274,7 +42274,7 @@
         <v>23.160343170166</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.9070701599121</v>
+        <v>17.9070720672607</v>
       </c>
       <c r="H1445" t="n">
         <v>118808</v>
@@ -42332,7 +42332,7 @@
         <v>23.3166217803955</v>
       </c>
       <c r="G1447" t="n">
-        <v>18.0279026031494</v>
+        <v>18.027904510498</v>
       </c>
       <c r="H1447" t="n">
         <v>122725</v>
@@ -42477,7 +42477,7 @@
         <v>23.0978336334229</v>
       </c>
       <c r="G1452" t="n">
-        <v>17.8587398529053</v>
+        <v>17.8587417602539</v>
       </c>
       <c r="H1452" t="n">
         <v>274366</v>
@@ -42593,7 +42593,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1456" t="n">
-        <v>17.1901454925537</v>
+        <v>17.1901473999023</v>
       </c>
       <c r="H1456" t="n">
         <v>147195</v>
@@ -42651,7 +42651,7 @@
         <v>22.5977458953857</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.4720821380615</v>
+        <v>17.4720840454102</v>
       </c>
       <c r="H1458" t="n">
         <v>246340</v>
@@ -42680,7 +42680,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1459" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1459" t="n">
         <v>176935</v>
@@ -42709,7 +42709,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1460" t="n">
         <v>158955</v>
@@ -42767,7 +42767,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1462" t="n">
         <v>81655</v>
@@ -42825,7 +42825,7 @@
         <v>22.6706733703613</v>
       </c>
       <c r="G1464" t="n">
-        <v>17.5284690856934</v>
+        <v>17.528470993042</v>
       </c>
       <c r="H1464" t="n">
         <v>280896</v>
@@ -42854,7 +42854,7 @@
         <v>23.2645282745361</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.9876270294189</v>
+        <v>17.9876251220703</v>
       </c>
       <c r="H1465" t="n">
         <v>247043</v>
@@ -42883,7 +42883,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.108455657959</v>
+        <v>18.1084575653076</v>
       </c>
       <c r="H1466" t="n">
         <v>183896</v>
@@ -42912,7 +42912,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1467" t="n">
         <v>172242</v>
@@ -43057,7 +43057,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1472" t="n">
         <v>130410</v>
@@ -43173,7 +43173,7 @@
         <v>22.3789558410645</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.3029193878174</v>
+        <v>17.302921295166</v>
       </c>
       <c r="H1476" t="n">
         <v>79029</v>
@@ -43289,7 +43289,7 @@
         <v>22.1289119720459</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.1095905303955</v>
+        <v>17.1095924377441</v>
       </c>
       <c r="H1480" t="n">
         <v>114206</v>
@@ -43463,7 +43463,7 @@
         <v>21.0766429901123</v>
       </c>
       <c r="G1486" t="n">
-        <v>16.2959995269775</v>
+        <v>16.2960014343262</v>
       </c>
       <c r="H1486" t="n">
         <v>123202</v>
@@ -43492,7 +43492,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1487" t="n">
-        <v>16.4651622772217</v>
+        <v>16.4651641845703</v>
       </c>
       <c r="H1487" t="n">
         <v>60560</v>
@@ -43550,7 +43550,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1489" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1489" t="n">
         <v>110218</v>
@@ -43608,7 +43608,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765544891357</v>
+        <v>16.3765525817871</v>
       </c>
       <c r="H1491" t="n">
         <v>136046</v>
@@ -43753,7 +43753,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.9753942489624</v>
+        <v>15.975396156311</v>
       </c>
       <c r="H1496" t="n">
         <v>142969</v>
@@ -43782,7 +43782,7 @@
         <v>20.2244091033936</v>
       </c>
       <c r="G1497" t="n">
-        <v>15.6370716094971</v>
+        <v>15.6370706558228</v>
       </c>
       <c r="H1497" t="n">
         <v>157081</v>
@@ -43811,7 +43811,7 @@
         <v>19.3367519378662</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.9507541656494</v>
+        <v>14.9507551193237</v>
       </c>
       <c r="H1498" t="n">
         <v>306456</v>
@@ -43840,7 +43840,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668664932251</v>
+        <v>14.9668645858765</v>
       </c>
       <c r="H1499" t="n">
         <v>131664</v>
@@ -43927,7 +43927,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.293436050415</v>
+        <v>14.2934350967407</v>
       </c>
       <c r="H1502" t="n">
         <v>112108</v>
@@ -43956,7 +43956,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1503" t="n">
         <v>269832</v>
@@ -44014,7 +44014,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013570785522</v>
+        <v>13.0013580322266</v>
       </c>
       <c r="H1505" t="n">
         <v>156575</v>
@@ -44130,7 +44130,7 @@
         <v>18.690803527832</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.4513206481934</v>
+        <v>14.4513216018677</v>
       </c>
       <c r="H1509" t="n">
         <v>189210</v>
@@ -44217,7 +44217,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379812240601</v>
+        <v>14.8379802703857</v>
       </c>
       <c r="H1512" t="n">
         <v>518691</v>
@@ -44246,7 +44246,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1513" t="n">
         <v>165517</v>
@@ -44304,7 +44304,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.654314994812</v>
+        <v>14.6543159484863</v>
       </c>
       <c r="H1515" t="n">
         <v>168456</v>
@@ -44333,7 +44333,7 @@
         <v>19.1658878326416</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8186464309692</v>
+        <v>14.8186454772949</v>
       </c>
       <c r="H1516" t="n">
         <v>177163</v>
@@ -44362,7 +44362,7 @@
         <v>19.2950782775879</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.9185333251953</v>
+        <v>14.918532371521</v>
       </c>
       <c r="H1517" t="n">
         <v>167619</v>
@@ -44391,7 +44391,7 @@
         <v>19.3200817108154</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.9378662109375</v>
+        <v>14.9378652572632</v>
       </c>
       <c r="H1518" t="n">
         <v>167937</v>
@@ -44420,7 +44420,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1519" t="n">
         <v>157517</v>
@@ -44507,7 +44507,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.518988609314</v>
+        <v>14.5189867019653</v>
       </c>
       <c r="H1522" t="n">
         <v>83491</v>
@@ -44594,7 +44594,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287672042847</v>
+        <v>14.4287662506104</v>
       </c>
       <c r="H1525" t="n">
         <v>203931</v>
@@ -44652,7 +44652,7 @@
         <v>18.9200115203857</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.6285400390625</v>
+        <v>14.6285409927368</v>
       </c>
       <c r="H1527" t="n">
         <v>97123</v>
@@ -44681,7 +44681,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958639144897</v>
+        <v>14.9958648681641</v>
       </c>
       <c r="H1528" t="n">
         <v>508333</v>
@@ -44768,7 +44768,7 @@
         <v>19.307580947876</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.9281997680664</v>
+        <v>14.9282007217407</v>
       </c>
       <c r="H1531" t="n">
         <v>93839</v>
@@ -44797,7 +44797,7 @@
         <v>19.1075439453125</v>
       </c>
       <c r="G1532" t="n">
-        <v>14.7735357284546</v>
+        <v>14.7735347747803</v>
       </c>
       <c r="H1532" t="n">
         <v>109512</v>
@@ -44855,7 +44855,7 @@
         <v>19.2867431640625</v>
       </c>
       <c r="G1534" t="n">
-        <v>14.9120874404907</v>
+        <v>14.912088394165</v>
       </c>
       <c r="H1534" t="n">
         <v>132919</v>
@@ -44884,7 +44884,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316484451294</v>
+        <v>14.7316474914551</v>
       </c>
       <c r="H1535" t="n">
         <v>124218</v>
@@ -44913,7 +44913,7 @@
         <v>18.8116588592529</v>
       </c>
       <c r="G1536" t="n">
-        <v>14.5447635650635</v>
+        <v>14.5447645187378</v>
       </c>
       <c r="H1536" t="n">
         <v>106444</v>
@@ -44942,7 +44942,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154230117798</v>
+        <v>14.8154239654541</v>
       </c>
       <c r="H1537" t="n">
         <v>73886</v>
@@ -44971,7 +44971,7 @@
         <v>18.9658527374268</v>
       </c>
       <c r="G1538" t="n">
-        <v>14.6639833450317</v>
+        <v>14.6639842987061</v>
       </c>
       <c r="H1538" t="n">
         <v>115175</v>
@@ -45000,7 +45000,7 @@
         <v>18.9116764068604</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.6220941543579</v>
+        <v>14.6220960617065</v>
       </c>
       <c r="H1539" t="n">
         <v>34303</v>
@@ -45029,7 +45029,7 @@
         <v>18.9241790771484</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.6317625045776</v>
+        <v>14.6317615509033</v>
       </c>
       <c r="H1540" t="n">
         <v>58627</v>
@@ -45087,7 +45087,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1542" t="n">
-        <v>14.0002222061157</v>
+        <v>14.0002212524414</v>
       </c>
       <c r="H1542" t="n">
         <v>149427</v>
@@ -45145,7 +45145,7 @@
         <v>18.5241088867188</v>
       </c>
       <c r="G1544" t="n">
-        <v>14.3224363327026</v>
+        <v>14.3224353790283</v>
       </c>
       <c r="H1544" t="n">
         <v>44397</v>
@@ -45174,7 +45174,7 @@
         <v>18.8283271789551</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.5576505661011</v>
+        <v>14.5576515197754</v>
       </c>
       <c r="H1545" t="n">
         <v>72837</v>
@@ -45203,7 +45203,7 @@
         <v>18.7116413116455</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.467432975769</v>
+        <v>14.4674320220947</v>
       </c>
       <c r="H1546" t="n">
         <v>228021</v>
@@ -45232,7 +45232,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994276046753</v>
+        <v>14.699426651001</v>
       </c>
       <c r="H1547" t="n">
         <v>198643</v>
@@ -45261,7 +45261,7 @@
         <v>19.1950607299805</v>
       </c>
       <c r="G1548" t="n">
-        <v>14.8412017822266</v>
+        <v>14.8412008285522</v>
       </c>
       <c r="H1548" t="n">
         <v>148931</v>
@@ -45319,7 +45319,7 @@
         <v>19.7618274688721</v>
       </c>
       <c r="G1550" t="n">
-        <v>15.2794141769409</v>
+        <v>15.2794122695923</v>
       </c>
       <c r="H1550" t="n">
         <v>232939</v>
@@ -45377,7 +45377,7 @@
         <v>19.3784255981445</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.9829750061035</v>
+        <v>14.9829759597778</v>
       </c>
       <c r="H1552" t="n">
         <v>194072</v>
@@ -45406,7 +45406,7 @@
         <v>20.6703205108643</v>
       </c>
       <c r="G1553" t="n">
-        <v>15.981840133667</v>
+        <v>15.9818410873413</v>
       </c>
       <c r="H1553" t="n">
         <v>660001</v>
@@ -45464,7 +45464,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.6435136795044</v>
+        <v>15.6435146331787</v>
       </c>
       <c r="H1555" t="n">
         <v>151091</v>
@@ -45493,7 +45493,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1556" t="n">
         <v>411312</v>
@@ -45580,7 +45580,7 @@
         <v>20.6244792938232</v>
       </c>
       <c r="G1559" t="n">
-        <v>15.9463977813721</v>
+        <v>15.9463987350464</v>
       </c>
       <c r="H1559" t="n">
         <v>435045</v>
@@ -45609,7 +45609,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147443771362</v>
+        <v>15.4147424697876</v>
       </c>
       <c r="H1560" t="n">
         <v>254459</v>
@@ -45638,7 +45638,7 @@
         <v>19.5784606933594</v>
       </c>
       <c r="G1561" t="n">
-        <v>15.1376390457153</v>
+        <v>15.137638092041</v>
       </c>
       <c r="H1561" t="n">
         <v>134574</v>
@@ -45725,7 +45725,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1564" t="n">
         <v>315453</v>
@@ -45783,7 +45783,7 @@
         <v>18.1573753356934</v>
       </c>
       <c r="G1566" t="n">
-        <v>14.0388870239258</v>
+        <v>14.0388860702515</v>
       </c>
       <c r="H1566" t="n">
         <v>543373</v>
@@ -45928,7 +45928,7 @@
         <v>15.940318107605</v>
       </c>
       <c r="G1571" t="n">
-        <v>12.3247060775757</v>
+        <v>12.3247051239014</v>
       </c>
       <c r="H1571" t="n">
         <v>242452</v>
@@ -45957,7 +45957,7 @@
         <v>16.9196586608887</v>
       </c>
       <c r="G1572" t="n">
-        <v>13.0819110870361</v>
+        <v>13.0819101333618</v>
       </c>
       <c r="H1572" t="n">
         <v>407858</v>
@@ -46015,7 +46015,7 @@
         <v>17.807315826416</v>
       </c>
       <c r="G1574" t="n">
-        <v>13.7682285308838</v>
+        <v>13.7682275772095</v>
       </c>
       <c r="H1574" t="n">
         <v>308404</v>
@@ -46044,7 +46044,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584480285645</v>
+        <v>13.8584470748901</v>
       </c>
       <c r="H1575" t="n">
         <v>588208</v>
@@ -46073,7 +46073,7 @@
         <v>18.1865482330322</v>
       </c>
       <c r="G1576" t="n">
-        <v>14.0614423751831</v>
+        <v>14.0614414215088</v>
       </c>
       <c r="H1576" t="n">
         <v>334948</v>
@@ -46102,7 +46102,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151958465576</v>
+        <v>15.0151968002319</v>
       </c>
       <c r="H1577" t="n">
         <v>400947</v>
@@ -46160,7 +46160,7 @@
         <v>20.2119064331055</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.627405166626</v>
+        <v>15.6274042129517</v>
       </c>
       <c r="H1579" t="n">
         <v>454220</v>
@@ -46218,7 +46218,7 @@
         <v>20.3661003112793</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.7466239929199</v>
+        <v>15.7466249465942</v>
       </c>
       <c r="H1581" t="n">
         <v>349520</v>
@@ -46276,7 +46276,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1583" t="n">
-        <v>15.9496192932129</v>
+        <v>15.9496183395386</v>
       </c>
       <c r="H1583" t="n">
         <v>228335</v>
@@ -46305,7 +46305,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.9496192932129</v>
+        <v>15.9496183395386</v>
       </c>
       <c r="H1584" t="n">
         <v>108428</v>
@@ -46334,7 +46334,7 @@
         <v>20.1077213287354</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.5468511581421</v>
+        <v>15.5468521118164</v>
       </c>
       <c r="H1585" t="n">
         <v>177619</v>
@@ -46421,7 +46421,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8304004669189</v>
+        <v>15.8303995132446</v>
       </c>
       <c r="H1588" t="n">
         <v>187148</v>
@@ -46450,7 +46450,7 @@
         <v>19.9493598937988</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.424409866333</v>
+        <v>15.4244089126587</v>
       </c>
       <c r="H1589" t="n">
         <v>222730</v>
@@ -46479,7 +46479,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.0699729919434</v>
+        <v>15.0699739456177</v>
       </c>
       <c r="H1590" t="n">
         <v>151523</v>
@@ -46508,7 +46508,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199178695679</v>
+        <v>15.1199169158936</v>
       </c>
       <c r="H1591" t="n">
         <v>163415</v>
@@ -46537,7 +46537,7 @@
         <v>18.9616851806641</v>
       </c>
       <c r="G1592" t="n">
-        <v>14.6607608795166</v>
+        <v>14.6607599258423</v>
       </c>
       <c r="H1592" t="n">
         <v>276239</v>
@@ -46595,7 +46595,7 @@
         <v>18.024019241333</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.9357786178589</v>
+        <v>13.9357767105103</v>
       </c>
       <c r="H1594" t="n">
         <v>185388</v>
@@ -46624,7 +46624,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.0002222061157</v>
+        <v>14.0002212524414</v>
       </c>
       <c r="H1595" t="n">
         <v>171574</v>
@@ -46653,7 +46653,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660474777222</v>
+        <v>14.2660484313965</v>
       </c>
       <c r="H1596" t="n">
         <v>137521</v>
@@ -46682,7 +46682,7 @@
         <v>18.1177864074707</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0082769393921</v>
+        <v>14.0082778930664</v>
       </c>
       <c r="H1597" t="n">
         <v>193042</v>
@@ -46711,7 +46711,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585592269897</v>
+        <v>13.7585601806641</v>
       </c>
       <c r="H1598" t="n">
         <v>171526</v>
@@ -46740,7 +46740,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116125106812</v>
+        <v>13.9116115570068</v>
       </c>
       <c r="H1599" t="n">
         <v>156203</v>
@@ -46769,7 +46769,7 @@
         <v>17.8469047546387</v>
       </c>
       <c r="G1600" t="n">
-        <v>13.7988367080688</v>
+        <v>13.7988357543945</v>
       </c>
       <c r="H1600" t="n">
         <v>70442</v>
@@ -46798,7 +46798,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1601" t="n">
         <v>280445</v>
@@ -46827,7 +46827,7 @@
         <v>17.9719276428223</v>
       </c>
       <c r="G1602" t="n">
-        <v>13.8955011367798</v>
+        <v>13.8955030441284</v>
       </c>
       <c r="H1602" t="n">
         <v>168613</v>
@@ -46885,7 +46885,7 @@
         <v>17.8469047546387</v>
       </c>
       <c r="G1604" t="n">
-        <v>13.7988367080688</v>
+        <v>13.7988357543945</v>
       </c>
       <c r="H1604" t="n">
         <v>282454</v>
@@ -46943,7 +46943,7 @@
         <v>18.3678302764893</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.2016048431396</v>
+        <v>14.201605796814</v>
       </c>
       <c r="H1606" t="n">
         <v>655478</v>
@@ -46972,7 +46972,7 @@
         <v>17.8573226928711</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8068914413452</v>
+        <v>13.8068923950195</v>
       </c>
       <c r="H1607" t="n">
         <v>594069</v>
@@ -47030,7 +47030,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1609" t="n">
-        <v>12.9691362380981</v>
+        <v>12.9691352844238</v>
       </c>
       <c r="H1609" t="n">
         <v>243613</v>
@@ -47059,7 +47059,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1610" t="n">
-        <v>12.9691362380981</v>
+        <v>12.9691352844238</v>
       </c>
       <c r="H1610" t="n">
         <v>466473</v>
@@ -47146,7 +47146,7 @@
         <v>15.8986444473267</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.2924852371216</v>
+        <v>12.2924842834473</v>
       </c>
       <c r="H1613" t="n">
         <v>194884</v>
@@ -47175,7 +47175,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722211837769</v>
+        <v>11.6722221374512</v>
       </c>
       <c r="H1614" t="n">
         <v>366805</v>
@@ -47204,7 +47204,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519580841064</v>
+        <v>11.0519590377808</v>
       </c>
       <c r="H1615" t="n">
         <v>230061</v>
@@ -47320,7 +47320,7 @@
         <v>14.6484231948853</v>
       </c>
       <c r="G1619" t="n">
-        <v>11.3258409500122</v>
+        <v>11.3258419036865</v>
       </c>
       <c r="H1619" t="n">
         <v>113034</v>
@@ -47494,7 +47494,7 @@
         <v>15.0130710601807</v>
       </c>
       <c r="G1625" t="n">
-        <v>11.6077785491943</v>
+        <v>11.6077795028687</v>
       </c>
       <c r="H1625" t="n">
         <v>59931</v>
@@ -47523,7 +47523,7 @@
         <v>15.5131587982178</v>
       </c>
       <c r="G1626" t="n">
-        <v>11.9944353103638</v>
+        <v>11.9944362640381</v>
       </c>
       <c r="H1626" t="n">
         <v>418987</v>
@@ -47552,7 +47552,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.970269203186</v>
+        <v>11.9702701568604</v>
       </c>
       <c r="H1627" t="n">
         <v>161789</v>
@@ -47581,7 +47581,7 @@
         <v>15.5860891342163</v>
       </c>
       <c r="G1628" t="n">
-        <v>12.0508232116699</v>
+        <v>12.0508241653442</v>
       </c>
       <c r="H1628" t="n">
         <v>106888</v>
@@ -47610,7 +47610,7 @@
         <v>15.5235767364502</v>
       </c>
       <c r="G1629" t="n">
-        <v>12.0024909973145</v>
+        <v>12.0024900436401</v>
       </c>
       <c r="H1629" t="n">
         <v>65253</v>
@@ -47697,7 +47697,7 @@
         <v>16.0236663818359</v>
       </c>
       <c r="G1632" t="n">
-        <v>12.3891487121582</v>
+        <v>12.3891496658325</v>
       </c>
       <c r="H1632" t="n">
         <v>63823</v>
@@ -47755,7 +47755,7 @@
         <v>16.429988861084</v>
       </c>
       <c r="G1634" t="n">
-        <v>12.7033081054688</v>
+        <v>12.7033090591431</v>
       </c>
       <c r="H1634" t="n">
         <v>81533</v>
@@ -47842,7 +47842,7 @@
         <v>16.2632923126221</v>
       </c>
       <c r="G1637" t="n">
-        <v>12.5744228363037</v>
+        <v>12.5744218826294</v>
       </c>
       <c r="H1637" t="n">
         <v>89530</v>
@@ -47929,7 +47929,7 @@
         <v>14.7213516235352</v>
       </c>
       <c r="G1640" t="n">
-        <v>11.3822269439697</v>
+        <v>11.382227897644</v>
       </c>
       <c r="H1640" t="n">
         <v>200632</v>
@@ -47987,7 +47987,7 @@
         <v>14.7734451293945</v>
       </c>
       <c r="G1642" t="n">
-        <v>11.4225063323975</v>
+        <v>11.4225053787231</v>
       </c>
       <c r="H1642" t="n">
         <v>170224</v>
@@ -48016,7 +48016,7 @@
         <v>14.5650749206543</v>
       </c>
       <c r="G1643" t="n">
-        <v>11.2613983154297</v>
+        <v>11.2613973617554</v>
       </c>
       <c r="H1643" t="n">
         <v>60975</v>
@@ -48045,7 +48045,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.253342628479</v>
+        <v>11.2533416748047</v>
       </c>
       <c r="H1644" t="n">
         <v>145140</v>
@@ -48161,7 +48161,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136325836182</v>
+        <v>10.7136335372925</v>
       </c>
       <c r="H1648" t="n">
         <v>160860</v>
@@ -48190,7 +48190,7 @@
         <v>14.0441493988037</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.8586301803589</v>
+        <v>10.8586292266846</v>
       </c>
       <c r="H1649" t="n">
         <v>111558</v>
@@ -48277,7 +48277,7 @@
         <v>11.6166372299194</v>
       </c>
       <c r="G1652" t="n">
-        <v>8.98173046112061</v>
+        <v>8.98172950744629</v>
       </c>
       <c r="H1652" t="n">
         <v>1035045</v>
@@ -48306,7 +48306,7 @@
         <v>11.2728261947632</v>
       </c>
       <c r="G1653" t="n">
-        <v>8.71590232849121</v>
+        <v>8.71590328216553</v>
       </c>
       <c r="H1653" t="n">
         <v>358963</v>
@@ -48335,7 +48335,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535598754883</v>
+        <v>8.34535694122314</v>
       </c>
       <c r="H1654" t="n">
         <v>225381</v>
@@ -48422,7 +48422,7 @@
         <v>9.64753913879395</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.45926666259766</v>
+        <v>7.4592661857605</v>
       </c>
       <c r="H1657" t="n">
         <v>314217</v>
@@ -48451,7 +48451,7 @@
         <v>10.010103225708</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.73959350585938</v>
+        <v>7.73959255218506</v>
       </c>
       <c r="H1658" t="n">
         <v>359843</v>
@@ -48480,7 +48480,7 @@
         <v>11.1894779205322</v>
       </c>
       <c r="G1659" t="n">
-        <v>8.65145969390869</v>
+        <v>8.65146064758301</v>
       </c>
       <c r="H1659" t="n">
         <v>479547</v>
@@ -48509,7 +48509,7 @@
         <v>10.5331115722656</v>
       </c>
       <c r="G1660" t="n">
-        <v>8.14397239685059</v>
+        <v>8.14397144317627</v>
       </c>
       <c r="H1660" t="n">
         <v>318695</v>
@@ -48567,7 +48567,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392208099365</v>
+        <v>7.90392160415649</v>
       </c>
       <c r="H1662" t="n">
         <v>148424</v>
@@ -48596,7 +48596,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971380233765</v>
+        <v>7.34971332550049</v>
       </c>
       <c r="H1663" t="n">
         <v>388404</v>
@@ -48625,7 +48625,7 @@
         <v>8.91824340820312</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.89539098739624</v>
+        <v>6.8953914642334</v>
       </c>
       <c r="H1664" t="n">
         <v>278474</v>
@@ -48654,7 +48654,7 @@
         <v>9.20162582397461</v>
       </c>
       <c r="G1665" t="n">
-        <v>7.11449575424194</v>
+        <v>7.11449670791626</v>
       </c>
       <c r="H1665" t="n">
         <v>236205</v>
@@ -48683,7 +48683,7 @@
         <v>9.54335308074951</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.37871170043945</v>
+        <v>7.37871217727661</v>
       </c>
       <c r="H1666" t="n">
         <v>148370</v>
@@ -48770,7 +48770,7 @@
         <v>8.75154685974121</v>
       </c>
       <c r="G1669" t="n">
-        <v>6.76650476455688</v>
+        <v>6.76650524139404</v>
       </c>
       <c r="H1669" t="n">
         <v>299096</v>
@@ -48828,7 +48828,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795209884644</v>
+        <v>6.62795162200928</v>
       </c>
       <c r="H1671" t="n">
         <v>134394</v>
@@ -48857,7 +48857,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539722442627</v>
+        <v>6.60539770126343</v>
       </c>
       <c r="H1672" t="n">
         <v>149384</v>
@@ -48944,7 +48944,7 @@
         <v>8.99325561523438</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.95338869094849</v>
+        <v>6.95338916778564</v>
       </c>
       <c r="H1675" t="n">
         <v>183001</v>
@@ -49002,7 +49002,7 @@
         <v>9.01409339904785</v>
       </c>
       <c r="G1677" t="n">
-        <v>6.96950006484985</v>
+        <v>6.96950054168701</v>
       </c>
       <c r="H1677" t="n">
         <v>218588</v>
@@ -49089,7 +49089,7 @@
         <v>8.73487663269043</v>
       </c>
       <c r="G1680" t="n">
-        <v>6.7536153793335</v>
+        <v>6.75361585617065</v>
       </c>
       <c r="H1680" t="n">
         <v>210660</v>
@@ -49205,7 +49205,7 @@
         <v>8.95158195495605</v>
       </c>
       <c r="G1684" t="n">
-        <v>6.92116785049438</v>
+        <v>6.92116737365723</v>
       </c>
       <c r="H1684" t="n">
         <v>262827</v>
@@ -49234,7 +49234,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.74072790145874</v>
+        <v>6.7407283782959</v>
       </c>
       <c r="H1685" t="n">
         <v>219529</v>
@@ -49321,7 +49321,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973346710205</v>
+        <v>6.47973394393921</v>
       </c>
       <c r="H1688" t="n">
         <v>211830</v>
@@ -49379,7 +49379,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107583999634</v>
+        <v>6.15107488632202</v>
       </c>
       <c r="H1690" t="n">
         <v>346128</v>
@@ -49408,7 +49408,7 @@
         <v>7.97640991210938</v>
       </c>
       <c r="G1691" t="n">
-        <v>6.16718626022339</v>
+        <v>6.16718578338623</v>
       </c>
       <c r="H1691" t="n">
         <v>184846</v>
@@ -49437,7 +49437,7 @@
         <v>7.7680401802063</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.00607872009277</v>
+        <v>6.00607919692993</v>
       </c>
       <c r="H1692" t="n">
         <v>226862</v>
@@ -49553,7 +49553,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032199859619</v>
+        <v>5.11032152175903</v>
       </c>
       <c r="H1696" t="n">
         <v>868645</v>
@@ -49640,7 +49640,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799428939819</v>
+        <v>4.88799476623535</v>
       </c>
       <c r="H1699" t="n">
         <v>228803</v>
@@ -49959,7 +49959,7 @@
         <v>6.27194213867188</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.84932851791382</v>
+        <v>4.84932899475098</v>
       </c>
       <c r="H1710" t="n">
         <v>660674</v>
@@ -50017,7 +50017,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555204391479</v>
+        <v>4.76555252075195</v>
       </c>
       <c r="H1712" t="n">
         <v>627926</v>
@@ -50220,7 +50220,7 @@
         <v>5.1717472076416</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.99868178367615</v>
+        <v>3.99868226051331</v>
       </c>
       <c r="H1719" t="n">
         <v>801083</v>
@@ -50249,7 +50249,7 @@
         <v>4.99671602249146</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.86335134506226</v>
+        <v>3.86335182189941</v>
       </c>
       <c r="H1720" t="n">
         <v>478249</v>
@@ -50278,7 +50278,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179761886597</v>
+        <v>3.81179785728455</v>
       </c>
       <c r="H1721" t="n">
         <v>554124</v>
@@ -50365,7 +50365,7 @@
         <v>4.68311882019043</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.62088489532471</v>
+        <v>3.62088513374329</v>
       </c>
       <c r="H1724" t="n">
         <v>677198</v>
@@ -50771,7 +50771,7 @@
         <v>1.93019998073578</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.49238836765289</v>
+        <v>1.49238848686218</v>
       </c>
       <c r="H1738" t="n">
         <v>977946</v>
@@ -50800,7 +50800,7 @@
         <v>1.90980005264282</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.47661578655243</v>
+        <v>1.47661566734314</v>
       </c>
       <c r="H1739" t="n">
         <v>1929525</v>
@@ -50945,7 +50945,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.39945244789124</v>
+        <v>1.39945232868195</v>
       </c>
       <c r="H1744" t="n">
         <v>10215715</v>
@@ -51119,7 +51119,7 @@
         <v>1.81560003757477</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.4037823677063</v>
+        <v>1.40378224849701</v>
       </c>
       <c r="H1750" t="n">
         <v>4722464</v>
@@ -51148,7 +51148,7 @@
         <v>1.76339995861053</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.36342227458954</v>
+        <v>1.36342239379883</v>
       </c>
       <c r="H1751" t="n">
         <v>3047867</v>
@@ -51177,7 +51177,7 @@
         <v>1.81239998340607</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.40130805969238</v>
+        <v>1.40130817890167</v>
       </c>
       <c r="H1752" t="n">
         <v>3775318</v>
@@ -51235,7 +51235,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.391566157341</v>
+        <v>1.39156603813171</v>
       </c>
       <c r="H1754" t="n">
         <v>2641302</v>
@@ -51293,7 +51293,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.41615307331085</v>
+        <v>1.41615319252014</v>
       </c>
       <c r="H1756" t="n">
         <v>9845377</v>
@@ -51351,7 +51351,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393748760223</v>
+        <v>1.37393760681152</v>
       </c>
       <c r="H1758" t="n">
         <v>3847795</v>
@@ -51380,7 +51380,7 @@
         <v>1.80859994888306</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.39837002754211</v>
+        <v>1.39836990833282</v>
       </c>
       <c r="H1759" t="n">
         <v>3782624</v>
@@ -51409,7 +51409,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006953716278</v>
+        <v>1.46006965637207</v>
       </c>
       <c r="H1760" t="n">
         <v>10216109</v>
@@ -51438,7 +51438,7 @@
         <v>1.88339996337891</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.45620369911194</v>
+        <v>1.45620381832123</v>
       </c>
       <c r="H1761" t="n">
         <v>12545701</v>
@@ -51467,7 +51467,7 @@
         <v>1.88960003852844</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.46099746227264</v>
+        <v>1.46099758148193</v>
       </c>
       <c r="H1762" t="n">
         <v>18263848</v>
@@ -51496,7 +51496,7 @@
         <v>1.88919997215271</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.46068823337555</v>
+        <v>1.46068811416626</v>
       </c>
       <c r="H1763" t="n">
         <v>3524769</v>
@@ -51525,7 +51525,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.5192950963974</v>
+        <v>1.51929497718811</v>
       </c>
       <c r="H1764" t="n">
         <v>6153718</v>
@@ -51554,7 +51554,7 @@
         <v>1.87360000610352</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.4486266374588</v>
+        <v>1.44862651824951</v>
       </c>
       <c r="H1765" t="n">
         <v>9888369</v>
@@ -51699,7 +51699,7 @@
         <v>1.94640004634857</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.50491392612457</v>
+        <v>1.50491404533386</v>
       </c>
       <c r="H1770" t="n">
         <v>8428502</v>
@@ -51815,7 +51815,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.45125532150269</v>
+        <v>1.45125544071198</v>
       </c>
       <c r="H1774" t="n">
         <v>7152049</v>
@@ -51902,7 +51902,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.57689690589905</v>
+        <v>1.57689678668976</v>
       </c>
       <c r="H1777" t="n">
         <v>14755833</v>
@@ -52018,7 +52018,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.50213050842285</v>
+        <v>1.50213062763214</v>
       </c>
       <c r="H1781" t="n">
         <v>3033681</v>
@@ -52047,7 +52047,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.48805868625641</v>
+        <v>1.48805856704712</v>
       </c>
       <c r="H1782" t="n">
         <v>2159725</v>
@@ -52076,7 +52076,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.58501517772675</v>
+        <v>1.58501529693604</v>
       </c>
       <c r="H1783" t="n">
         <v>13921292</v>
@@ -52163,7 +52163,7 @@
         <v>1.98660004138947</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.53599572181702</v>
+        <v>1.53599584102631</v>
       </c>
       <c r="H1786" t="n">
         <v>9824828</v>
@@ -52279,7 +52279,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702329158783</v>
+        <v>1.67702341079712</v>
       </c>
       <c r="H1790" t="n">
         <v>8965001</v>
@@ -52308,7 +52308,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.70176517963409</v>
+        <v>1.7017650604248</v>
       </c>
       <c r="H1791" t="n">
         <v>8676097</v>
@@ -52366,7 +52366,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.65537452697754</v>
+        <v>1.65537440776825</v>
       </c>
       <c r="H1793" t="n">
         <v>21373665</v>
@@ -52453,7 +52453,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259310245514</v>
+        <v>1.56259298324585</v>
       </c>
       <c r="H1796" t="n">
         <v>7220763</v>
@@ -52540,7 +52540,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1799" t="n">
         <v>5974419</v>
@@ -52598,7 +52598,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.6847550868988</v>
+        <v>1.68475520610809</v>
       </c>
       <c r="H1801" t="n">
         <v>14097011</v>
@@ -52656,7 +52656,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.79377329349518</v>
+        <v>1.79377341270447</v>
       </c>
       <c r="H1803" t="n">
         <v>18893517</v>
@@ -52743,7 +52743,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.87186431884766</v>
+        <v>1.87186419963837</v>
       </c>
       <c r="H1806" t="n">
         <v>12148200</v>
@@ -52772,7 +52772,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482697963715</v>
+        <v>1.92482709884644</v>
       </c>
       <c r="H1807" t="n">
         <v>14549250</v>
@@ -52801,7 +52801,7 @@
         <v>2.37350010871887</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.83513855934143</v>
+        <v>1.83513844013214</v>
       </c>
       <c r="H1808" t="n">
         <v>19340207</v>
@@ -52830,7 +52830,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.84789597988129</v>
+        <v>1.847895860672</v>
       </c>
       <c r="H1809" t="n">
         <v>9933747</v>
@@ -52859,7 +52859,7 @@
         <v>2.31550002098083</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.79029405117035</v>
+        <v>1.79029417037964</v>
       </c>
       <c r="H1810" t="n">
         <v>25899848</v>
@@ -52888,7 +52888,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.01026296615601</v>
+        <v>2.01026320457458</v>
       </c>
       <c r="H1811" t="n">
         <v>45207296</v>
@@ -52917,7 +52917,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.90201842784882</v>
+        <v>1.90201818943024</v>
       </c>
       <c r="H1812" t="n">
         <v>16282025</v>
@@ -53004,7 +53004,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552491664886</v>
+        <v>1.83552503585815</v>
       </c>
       <c r="H1815" t="n">
         <v>8871781</v>
@@ -53033,7 +53033,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.91052317619324</v>
+        <v>1.91052305698395</v>
       </c>
       <c r="H1816" t="n">
         <v>14267354</v>
@@ -53149,7 +53149,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.03809762001038</v>
+        <v>2.0380973815918</v>
       </c>
       <c r="H1820" t="n">
         <v>13501447</v>
@@ -53178,7 +53178,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.0338454246521</v>
+        <v>2.03384494781494</v>
       </c>
       <c r="H1821" t="n">
         <v>13235723</v>
@@ -53236,7 +53236,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198758125305</v>
+        <v>2.12198734283447</v>
       </c>
       <c r="H1823" t="n">
         <v>9639295</v>
@@ -53265,7 +53265,7 @@
         <v>2.52349996566772</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.95111525058746</v>
+        <v>1.95111513137817</v>
       </c>
       <c r="H1824" t="n">
         <v>54311078</v>
@@ -53323,7 +53323,7 @@
         <v>2.39050006866455</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.84828245639801</v>
+        <v>1.8482825756073</v>
       </c>
       <c r="H1826" t="n">
         <v>13530053</v>
@@ -53352,7 +53352,7 @@
         <v>2.46099996566772</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.90279138088226</v>
+        <v>1.90279150009155</v>
       </c>
       <c r="H1827" t="n">
         <v>7484611</v>
@@ -53468,7 +53468,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305159091949</v>
+        <v>1.80305135250092</v>
       </c>
       <c r="H1831" t="n">
         <v>6664209</v>
@@ -53584,7 +53584,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.48805868625641</v>
+        <v>1.48805856704712</v>
       </c>
       <c r="H1835" t="n">
         <v>21201799</v>
@@ -53613,7 +53613,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.48450195789337</v>
+        <v>1.48450207710266</v>
       </c>
       <c r="H1836" t="n">
         <v>20305784</v>
@@ -53729,7 +53729,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.51759397983551</v>
+        <v>1.5175940990448</v>
       </c>
       <c r="H1840" t="n">
         <v>7183811</v>
@@ -53903,7 +53903,7 @@
         <v>1.99520003795624</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.54264497756958</v>
+        <v>1.54264509677887</v>
       </c>
       <c r="H1846" t="n">
         <v>10952973</v>
@@ -53990,7 +53990,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.49532651901245</v>
+        <v>1.49532663822174</v>
       </c>
       <c r="H1849" t="n">
         <v>5122410</v>
@@ -54019,7 +54019,7 @@
         <v>1.91349995136261</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.47947633266449</v>
+        <v>1.47947645187378</v>
       </c>
       <c r="H1850" t="n">
         <v>4817935</v>
@@ -54077,7 +54077,7 @@
         <v>1.99950003623962</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.54596972465515</v>
+        <v>1.54596984386444</v>
       </c>
       <c r="H1852" t="n">
         <v>6684358</v>
@@ -54135,7 +54135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.58501517772675</v>
+        <v>1.58501529693604</v>
       </c>
       <c r="H1854" t="n">
         <v>4279847</v>
@@ -54164,7 +54164,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1855" t="n">
         <v>7814956</v>
@@ -54193,7 +54193,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1856" t="n">
         <v>6891203</v>
@@ -54222,7 +54222,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1857" t="n">
         <v>11220865</v>
@@ -54251,7 +54251,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222691059113</v>
+        <v>1.79222702980042</v>
       </c>
       <c r="H1858" t="n">
         <v>11711966</v>
@@ -54309,7 +54309,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666093826294</v>
+        <v>1.75666081905365</v>
       </c>
       <c r="H1860" t="n">
         <v>8508624</v>
@@ -54454,7 +54454,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.61516916751862</v>
+        <v>1.61516928672791</v>
       </c>
       <c r="H1865" t="n">
         <v>6994580</v>
@@ -54483,7 +54483,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.58037602901459</v>
+        <v>1.58037614822388</v>
       </c>
       <c r="H1866" t="n">
         <v>6951613</v>
@@ -54599,7 +54599,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.67315757274628</v>
+        <v>1.67315769195557</v>
       </c>
       <c r="H1870" t="n">
         <v>10635223</v>
@@ -54628,7 +54628,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1871" t="n">
         <v>17872031</v>
@@ -54686,7 +54686,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831318378448</v>
+        <v>1.62831330299377</v>
       </c>
       <c r="H1873" t="n">
         <v>6917707</v>
@@ -54802,7 +54802,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.73501169681549</v>
+        <v>1.73501181602478</v>
       </c>
       <c r="H1877" t="n">
         <v>5397862</v>
@@ -54860,7 +54860,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.65537452697754</v>
+        <v>1.65537440776825</v>
       </c>
       <c r="H1879" t="n">
         <v>7813573</v>
@@ -54918,7 +54918,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.77444386482239</v>
+        <v>1.77444410324097</v>
       </c>
       <c r="H1881" t="n">
         <v>14803240</v>
@@ -54947,7 +54947,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.6484158039093</v>
+        <v>1.64841592311859</v>
       </c>
       <c r="H1882" t="n">
         <v>29583047</v>
@@ -55005,7 +55005,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.6205815076828</v>
+        <v>1.62058138847351</v>
       </c>
       <c r="H1884" t="n">
         <v>14947292</v>
@@ -55034,7 +55034,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.59738612174988</v>
+        <v>1.59738600254059</v>
       </c>
       <c r="H1885" t="n">
         <v>18251323</v>
@@ -55092,7 +55092,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.62985956668854</v>
+        <v>1.62985968589783</v>
       </c>
       <c r="H1887" t="n">
         <v>15958032</v>
@@ -55121,7 +55121,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006492614746</v>
+        <v>1.67006480693817</v>
       </c>
       <c r="H1888" t="n">
         <v>9732271</v>
@@ -55353,7 +55353,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.68552851676941</v>
+        <v>1.68552839756012</v>
       </c>
       <c r="H1896" t="n">
         <v>10826926</v>
@@ -55382,7 +55382,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1897" t="n">
         <v>13177383</v>
@@ -55411,7 +55411,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.7659387588501</v>
+        <v>1.76593899726868</v>
       </c>
       <c r="H1898" t="n">
         <v>9180042</v>
@@ -55440,7 +55440,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.76748526096344</v>
+        <v>1.76748538017273</v>
       </c>
       <c r="H1899" t="n">
         <v>12029873</v>
@@ -55469,7 +55469,7 @@
         <v>2.32100009918213</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.7945464849472</v>
+        <v>1.79454660415649</v>
       </c>
       <c r="H1900" t="n">
         <v>9000879</v>
@@ -55498,7 +55498,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.80073201656342</v>
+        <v>1.80073189735413</v>
       </c>
       <c r="H1901" t="n">
         <v>7297805</v>
@@ -55556,7 +55556,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.79068064689636</v>
+        <v>1.79068052768707</v>
       </c>
       <c r="H1903" t="n">
         <v>9401467</v>
@@ -55585,7 +55585,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.74583613872528</v>
+        <v>1.74583625793457</v>
       </c>
       <c r="H1904" t="n">
         <v>7115446</v>
@@ -55614,7 +55614,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645557880402</v>
+        <v>1.71645569801331</v>
       </c>
       <c r="H1905" t="n">
         <v>7081375</v>
@@ -55701,7 +55701,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.77367055416107</v>
+        <v>1.77367067337036</v>
       </c>
       <c r="H1908" t="n">
         <v>7446800</v>
@@ -55730,7 +55730,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.77985620498657</v>
+        <v>1.77985608577728</v>
       </c>
       <c r="H1909" t="n">
         <v>7154278</v>
@@ -55759,7 +55759,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1910" t="n">
         <v>7777212</v>
@@ -55788,7 +55788,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.77444386482239</v>
+        <v>1.77444410324097</v>
       </c>
       <c r="H1911" t="n">
         <v>8748249</v>
@@ -55817,7 +55817,7 @@
         <v>2.30699992179871</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.78372192382812</v>
+        <v>1.78372204303741</v>
       </c>
       <c r="H1912" t="n">
         <v>6290363</v>
@@ -55875,7 +55875,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.77057802677155</v>
+        <v>1.77057790756226</v>
       </c>
       <c r="H1914" t="n">
         <v>6184037</v>
@@ -55904,7 +55904,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.80150508880615</v>
+        <v>1.80150496959686</v>
       </c>
       <c r="H1915" t="n">
         <v>7696382</v>
@@ -55933,7 +55933,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1916" t="n">
         <v>11063863</v>
@@ -55991,7 +55991,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985284328461</v>
+        <v>1.92985272407532</v>
       </c>
       <c r="H1918" t="n">
         <v>16178743</v>
@@ -56020,7 +56020,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309947967529</v>
+        <v>1.963099360466</v>
       </c>
       <c r="H1919" t="n">
         <v>16639251</v>
@@ -56049,7 +56049,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.96000671386719</v>
+        <v>1.9600065946579</v>
       </c>
       <c r="H1920" t="n">
         <v>11600649</v>
@@ -56078,7 +56078,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.97624337673187</v>
+        <v>1.97624325752258</v>
       </c>
       <c r="H1921" t="n">
         <v>6898571</v>
@@ -56107,7 +56107,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.97160422801971</v>
+        <v>1.97160446643829</v>
       </c>
       <c r="H1922" t="n">
         <v>5995361</v>
@@ -56136,7 +56136,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.95923340320587</v>
+        <v>1.95923328399658</v>
       </c>
       <c r="H1923" t="n">
         <v>6467525</v>
@@ -56165,7 +56165,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382106304169</v>
+        <v>1.95382130146027</v>
       </c>
       <c r="H1924" t="n">
         <v>4430041</v>
@@ -56194,7 +56194,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.97160422801971</v>
+        <v>1.97160446643829</v>
       </c>
       <c r="H1925" t="n">
         <v>5300597</v>
@@ -56223,7 +56223,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918191432953</v>
+        <v>1.94918203353882</v>
       </c>
       <c r="H1926" t="n">
         <v>5834369</v>
@@ -56252,7 +56252,7 @@
         <v>2.61700010299683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.02340745925903</v>
+        <v>2.02340722084045</v>
       </c>
       <c r="H1927" t="n">
         <v>20029327</v>
@@ -56310,7 +56310,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562405586243</v>
+        <v>2.00562429428101</v>
       </c>
       <c r="H1929" t="n">
         <v>10963576</v>
@@ -56339,7 +56339,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959251403809</v>
+        <v>2.02959275245667</v>
       </c>
       <c r="H1930" t="n">
         <v>11993677</v>
@@ -56368,7 +56368,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.96077990531921</v>
+        <v>1.96077978610992</v>
       </c>
       <c r="H1931" t="n">
         <v>9783275</v>
@@ -56426,7 +56426,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.90356469154358</v>
+        <v>1.90356457233429</v>
       </c>
       <c r="H1933" t="n">
         <v>13404200</v>
@@ -56513,7 +56513,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.9097501039505</v>
+        <v>1.90974998474121</v>
       </c>
       <c r="H1936" t="n">
         <v>39674896</v>
@@ -56600,7 +56600,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.03191208839417</v>
+        <v>2.03191232681274</v>
       </c>
       <c r="H1939" t="n">
         <v>13224837</v>
@@ -56629,7 +56629,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025948524475</v>
+        <v>2.16025996208191</v>
       </c>
       <c r="H1940" t="n">
         <v>21527670</v>
@@ -56803,7 +56803,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.97624337673187</v>
+        <v>1.97624325752258</v>
       </c>
       <c r="H1946" t="n">
         <v>12028860</v>
@@ -56832,7 +56832,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.954594373703</v>
+        <v>1.95459449291229</v>
       </c>
       <c r="H1947" t="n">
         <v>11144521</v>
@@ -56890,7 +56890,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309947967529</v>
+        <v>1.963099360466</v>
       </c>
       <c r="H1949" t="n">
         <v>5429828</v>
@@ -56919,7 +56919,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.9940265417099</v>
+        <v>1.99402642250061</v>
       </c>
       <c r="H1950" t="n">
         <v>6249034</v>
@@ -56977,7 +56977,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.98088252544403</v>
+        <v>1.98088228702545</v>
       </c>
       <c r="H1952" t="n">
         <v>14258681</v>
@@ -57006,7 +57006,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.96000671386719</v>
+        <v>1.9600065946579</v>
       </c>
       <c r="H1953" t="n">
         <v>6716319</v>
@@ -57064,7 +57064,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.90511095523834</v>
+        <v>1.90511107444763</v>
       </c>
       <c r="H1955" t="n">
         <v>11937121</v>
@@ -57093,7 +57093,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763913154602</v>
+        <v>1.7976393699646</v>
       </c>
       <c r="H1956" t="n">
         <v>22749670</v>
@@ -57238,7 +57238,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645197868347</v>
+        <v>1.86645209789276</v>
       </c>
       <c r="H1961" t="n">
         <v>10420578</v>
@@ -57296,7 +57296,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.9267600774765</v>
+        <v>1.92676019668579</v>
       </c>
       <c r="H1963" t="n">
         <v>13390725</v>
@@ -57383,7 +57383,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.10768389701843</v>
+        <v>2.10768365859985</v>
       </c>
       <c r="H1966" t="n">
         <v>26715391</v>
@@ -57412,7 +57412,7 @@
         <v>2.73900008201599</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.1177351474762</v>
+        <v>2.11773490905762</v>
       </c>
       <c r="H1967" t="n">
         <v>25132081</v>
@@ -57528,7 +57528,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866893291473</v>
+        <v>1.84866905212402</v>
       </c>
       <c r="H1971" t="n">
         <v>32386618</v>
@@ -57557,7 +57557,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.86181282997131</v>
+        <v>1.8618129491806</v>
       </c>
       <c r="H1972" t="n">
         <v>18377109</v>
@@ -57586,7 +57586,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.8672251701355</v>
+        <v>1.86722528934479</v>
       </c>
       <c r="H1973" t="n">
         <v>10855064</v>
@@ -57644,7 +57644,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.91748178005219</v>
+        <v>1.91748189926147</v>
       </c>
       <c r="H1975" t="n">
         <v>17294006</v>
@@ -57702,7 +57702,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.96077990531921</v>
+        <v>1.96077978610992</v>
       </c>
       <c r="H1977" t="n">
         <v>19720359</v>
@@ -57731,7 +57731,7 @@
         <v>2.60899996757507</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.01722192764282</v>
+        <v>2.01722168922424</v>
       </c>
       <c r="H1978" t="n">
         <v>16862561</v>
@@ -57760,7 +57760,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.89119386672974</v>
+        <v>1.89119374752045</v>
       </c>
       <c r="H1979" t="n">
         <v>28800121</v>
@@ -57789,7 +57789,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.90124535560608</v>
+        <v>1.9012451171875</v>
       </c>
       <c r="H1980" t="n">
         <v>37059275</v>
@@ -57847,7 +57847,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.98552143573761</v>
+        <v>1.98552167415619</v>
       </c>
       <c r="H1982" t="n">
         <v>29807799</v>
@@ -57934,7 +57934,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397505283356</v>
+        <v>1.98397517204285</v>
       </c>
       <c r="H1985" t="n">
         <v>20639388</v>
@@ -57963,7 +57963,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.95614063739777</v>
+        <v>1.95614075660706</v>
       </c>
       <c r="H1986" t="n">
         <v>18660240</v>
@@ -57992,7 +57992,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.91052317619324</v>
+        <v>1.91052305698395</v>
       </c>
       <c r="H1987" t="n">
         <v>16615036</v>
@@ -58021,7 +58021,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.83475160598755</v>
+        <v>1.83475172519684</v>
       </c>
       <c r="H1988" t="n">
         <v>16787583</v>
@@ -58050,7 +58050,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.85949349403381</v>
+        <v>1.85949337482452</v>
       </c>
       <c r="H1989" t="n">
         <v>32110096</v>
@@ -58079,7 +58079,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.85408115386963</v>
+        <v>1.85408139228821</v>
       </c>
       <c r="H1990" t="n">
         <v>14799249</v>
@@ -58108,7 +58108,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.81155633926392</v>
+        <v>1.81155622005463</v>
       </c>
       <c r="H1991" t="n">
         <v>6593039</v>
@@ -58166,7 +58166,7 @@
         <v>2.42899990081787</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.87804973125458</v>
+        <v>1.87804961204529</v>
       </c>
       <c r="H1993" t="n">
         <v>10692244</v>
@@ -58195,7 +58195,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062591552734</v>
+        <v>1.93062579631805</v>
       </c>
       <c r="H1994" t="n">
         <v>10863078</v>
@@ -58224,7 +58224,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237753868103</v>
+        <v>1.97237765789032</v>
       </c>
       <c r="H1995" t="n">
         <v>14164042</v>
@@ -58253,7 +58253,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866545200348</v>
+        <v>1.99866557121277</v>
       </c>
       <c r="H1996" t="n">
         <v>13386081</v>
@@ -58282,7 +58282,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964376449585</v>
+        <v>2.03964400291443</v>
       </c>
       <c r="H1997" t="n">
         <v>18265540</v>
@@ -58340,7 +58340,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1999" t="n">
-        <v>2.03191208839417</v>
+        <v>2.03191232681274</v>
       </c>
       <c r="H1999" t="n">
         <v>11141976</v>
@@ -58427,7 +58427,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.0868079662323</v>
+        <v>2.08680772781372</v>
       </c>
       <c r="H2002" t="n">
         <v>18452495</v>
@@ -58456,7 +58456,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443690299988</v>
+        <v>2.07443714141846</v>
       </c>
       <c r="H2003" t="n">
         <v>11980891</v>
@@ -58572,7 +58572,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G2007" t="n">
-        <v>2.35973978042603</v>
+        <v>2.3597400188446</v>
       </c>
       <c r="H2007" t="n">
         <v>16760666</v>
@@ -58659,7 +58659,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654775619507</v>
+        <v>2.18654799461365</v>
       </c>
       <c r="H2010" t="n">
         <v>100072608</v>
@@ -58717,7 +58717,7 @@
         <v>2.92899990081787</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.26463890075684</v>
+        <v>2.26463866233826</v>
       </c>
       <c r="H2012" t="n">
         <v>40936353</v>
@@ -58746,7 +58746,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716347694397</v>
+        <v>2.30716371536255</v>
       </c>
       <c r="H2013" t="n">
         <v>31624933</v>
@@ -58833,7 +58833,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071797370911</v>
+        <v>2.40071821212769</v>
       </c>
       <c r="H2016" t="n">
         <v>54965782</v>
@@ -58891,7 +58891,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.42777943611145</v>
+        <v>2.42777967453003</v>
       </c>
       <c r="H2018" t="n">
         <v>25023304</v>
@@ -59094,7 +59094,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.53447818756104</v>
+        <v>2.53447794914246</v>
       </c>
       <c r="H2025" t="n">
         <v>37969241</v>
@@ -59210,7 +59210,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876158714294</v>
+        <v>2.31876134872437</v>
       </c>
       <c r="H2029" t="n">
         <v>17461139</v>
@@ -59297,7 +59297,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.35046172142029</v>
+        <v>2.35046148300171</v>
       </c>
       <c r="H2032" t="n">
         <v>11232080</v>
@@ -59326,7 +59326,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37442994117737</v>
+        <v>2.37443017959595</v>
       </c>
       <c r="H2033" t="n">
         <v>6292252</v>
@@ -59355,7 +59355,7 @@
         <v>3.11899995803833</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.41154289245605</v>
+        <v>2.41154265403748</v>
       </c>
       <c r="H2034" t="n">
         <v>8906628</v>
@@ -59413,7 +59413,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.35510087013245</v>
+        <v>2.35510063171387</v>
       </c>
       <c r="H2036" t="n">
         <v>10336670</v>
@@ -59529,7 +59529,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.5777759552002</v>
+        <v>2.57777619361877</v>
       </c>
       <c r="H2040" t="n">
         <v>21608685</v>
@@ -59558,7 +59558,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334228515625</v>
+        <v>2.61334204673767</v>
       </c>
       <c r="H2041" t="n">
         <v>21815059</v>
@@ -59935,7 +59935,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.59169340133667</v>
+        <v>2.59169316291809</v>
       </c>
       <c r="H2054" t="n">
         <v>26331357</v>
@@ -59993,7 +59993,7 @@
         <v>3.19099998474121</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.46721148490906</v>
+        <v>2.46721172332764</v>
       </c>
       <c r="H2056" t="n">
         <v>19021872</v>
@@ -60022,7 +60022,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.53602433204651</v>
+        <v>2.53602457046509</v>
       </c>
       <c r="H2057" t="n">
         <v>20653870</v>
@@ -60051,7 +60051,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983927726746</v>
+        <v>2.5298388004303</v>
       </c>
       <c r="H2058" t="n">
         <v>17041685</v>
@@ -60283,7 +60283,7 @@
         <v>3.53900003433228</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.73627781867981</v>
+        <v>2.73627758026123</v>
       </c>
       <c r="H2066" t="n">
         <v>30033671</v>
@@ -60312,7 +60312,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.74323606491089</v>
+        <v>2.74323630332947</v>
       </c>
       <c r="H2067" t="n">
         <v>44075315</v>
@@ -60341,7 +60341,7 @@
         <v>3.6489999294281</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.82132697105408</v>
+        <v>2.82132720947266</v>
       </c>
       <c r="H2068" t="n">
         <v>26692588</v>
@@ -60370,7 +60370,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792622566223</v>
+        <v>2.75792646408081</v>
       </c>
       <c r="H2069" t="n">
         <v>27477458</v>
@@ -60399,7 +60399,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467970848083</v>
+        <v>2.72467994689941</v>
       </c>
       <c r="H2070" t="n">
         <v>14759944</v>
@@ -60428,7 +60428,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452595710754</v>
+        <v>2.69452571868896</v>
       </c>
       <c r="H2071" t="n">
         <v>16175878</v>
@@ -60486,7 +60486,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.75019454956055</v>
+        <v>2.75019478797913</v>
       </c>
       <c r="H2073" t="n">
         <v>39123998</v>
@@ -60544,7 +60544,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.89245939254761</v>
+        <v>2.89245963096619</v>
       </c>
       <c r="H2075" t="n">
         <v>28364901</v>
@@ -60573,7 +60573,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.88859367370605</v>
+        <v>2.88859343528748</v>
       </c>
       <c r="H2076" t="n">
         <v>26425626</v>
@@ -60631,7 +60631,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2078" t="n">
-        <v>2.89245939254761</v>
+        <v>2.89245963096619</v>
       </c>
       <c r="H2078" t="n">
         <v>15255947</v>
@@ -60718,7 +60718,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.04632210731506</v>
+        <v>3.04632186889648</v>
       </c>
       <c r="H2081" t="n">
         <v>24628211</v>
@@ -60921,7 +60921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2088" t="n">
-        <v>3.17003035545349</v>
+        <v>3.17003059387207</v>
       </c>
       <c r="H2088" t="n">
         <v>24484756</v>
@@ -61124,7 +61124,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.21564793586731</v>
+        <v>3.21564769744873</v>
       </c>
       <c r="H2095" t="n">
         <v>22065801</v>
@@ -61298,7 +61298,7 @@
         <v>4.1710000038147</v>
       </c>
       <c r="G2101" t="n">
-        <v>3.22492599487305</v>
+        <v>3.22492623329163</v>
       </c>
       <c r="H2101" t="n">
         <v>15860905</v>
@@ -61385,7 +61385,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.15843272209167</v>
+        <v>3.15843296051025</v>
       </c>
       <c r="H2104" t="n">
         <v>12108834</v>
@@ -61414,7 +61414,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.07338333129883</v>
+        <v>3.07338309288025</v>
       </c>
       <c r="H2105" t="n">
         <v>15454340</v>
@@ -61472,7 +61472,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972237586975</v>
+        <v>3.10972261428833</v>
       </c>
       <c r="H2107" t="n">
         <v>24633782</v>
@@ -61646,7 +61646,7 @@
         <v>4.16300010681152</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.21874094009399</v>
+        <v>3.21874070167542</v>
       </c>
       <c r="H2113" t="n">
         <v>18257227</v>
@@ -61704,7 +61704,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739607810974</v>
+        <v>3.40739631652832</v>
       </c>
       <c r="H2115" t="n">
         <v>25716222</v>
@@ -61791,7 +61791,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471426963806</v>
+        <v>3.48471403121948</v>
       </c>
       <c r="H2118" t="n">
         <v>28093096</v>
@@ -61820,7 +61820,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G2119" t="n">
-        <v>3.47466254234314</v>
+        <v>3.47466278076172</v>
       </c>
       <c r="H2119" t="n">
         <v>18482624</v>
@@ -61849,7 +61849,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2120" t="n">
-        <v>3.51796054840088</v>
+        <v>3.51796078681946</v>
       </c>
       <c r="H2120" t="n">
         <v>24621349</v>
@@ -61878,7 +61878,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811105728149</v>
+        <v>3.69811129570007</v>
       </c>
       <c r="H2121" t="n">
         <v>32155461</v>
@@ -61936,7 +61936,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667041778564</v>
+        <v>3.5666708946228</v>
       </c>
       <c r="H2123" t="n">
         <v>15663428</v>
@@ -61965,7 +61965,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2124" t="n">
-        <v>3.6030101776123</v>
+        <v>3.60300993919373</v>
       </c>
       <c r="H2124" t="n">
         <v>34298846</v>
@@ -61994,7 +61994,7 @@
         <v>4.64900016784668</v>
       </c>
       <c r="G2125" t="n">
-        <v>3.59450531005859</v>
+        <v>3.59450507164001</v>
       </c>
       <c r="H2125" t="n">
         <v>25660150</v>
@@ -62110,7 +62110,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G2129" t="n">
-        <v>3.76769733428955</v>
+        <v>3.76769709587097</v>
       </c>
       <c r="H2129" t="n">
         <v>26746590</v>
@@ -62139,7 +62139,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145683288574</v>
+        <v>3.90145707130432</v>
       </c>
       <c r="H2130" t="n">
         <v>31985059</v>
@@ -62168,7 +62168,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.98186755180359</v>
+        <v>3.98186731338501</v>
       </c>
       <c r="H2131" t="n">
         <v>28979314</v>
@@ -62197,7 +62197,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G2132" t="n">
-        <v>4.09320545196533</v>
+        <v>4.09320497512817</v>
       </c>
       <c r="H2132" t="n">
         <v>33248614</v>
@@ -62255,7 +62255,7 @@
         <v>4.98099994659424</v>
       </c>
       <c r="G2134" t="n">
-        <v>4.04208087921143</v>
+        <v>4.04208040237427</v>
       </c>
       <c r="H2134" t="n">
         <v>12971734</v>
@@ -62458,7 +62458,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2141" t="n">
-        <v>3.99257922172546</v>
+        <v>3.99257898330688</v>
       </c>
       <c r="H2141" t="n">
         <v>26160718</v>
@@ -62516,7 +62516,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G2143" t="n">
-        <v>3.99907112121582</v>
+        <v>3.9990713596344</v>
       </c>
       <c r="H2143" t="n">
         <v>11607781</v>
@@ -62690,7 +62690,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2149" t="n">
-        <v>3.75724411010742</v>
+        <v>3.757244348526</v>
       </c>
       <c r="H2149" t="n">
         <v>21711731</v>
@@ -62719,7 +62719,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2150" t="n">
-        <v>3.78970408439636</v>
+        <v>3.78970456123352</v>
       </c>
       <c r="H2150" t="n">
         <v>15083376</v>
@@ -62748,7 +62748,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G2151" t="n">
-        <v>3.6420111656189</v>
+        <v>3.64201140403748</v>
       </c>
       <c r="H2151" t="n">
         <v>19374406</v>
@@ -62835,7 +62835,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G2154" t="n">
-        <v>3.67771744728088</v>
+        <v>3.6777172088623</v>
       </c>
       <c r="H2154" t="n">
         <v>20881847</v>
@@ -62864,7 +62864,7 @@
         <v>4.56699991226196</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.70611977577209</v>
+        <v>3.70611953735352</v>
       </c>
       <c r="H2155" t="n">
         <v>13574114</v>
@@ -62951,7 +62951,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2158" t="n">
-        <v>3.7499406337738</v>
+        <v>3.74994039535522</v>
       </c>
       <c r="H2158" t="n">
         <v>19858583</v>
@@ -63009,7 +63009,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2160" t="n">
-        <v>3.6030592918396</v>
+        <v>3.60305953025818</v>
       </c>
       <c r="H2160" t="n">
         <v>12604005</v>
@@ -63096,7 +63096,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G2163" t="n">
-        <v>3.79700756072998</v>
+        <v>3.79700779914856</v>
       </c>
       <c r="H2163" t="n">
         <v>21436986</v>
@@ -63125,7 +63125,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2164" t="n">
-        <v>3.7499406337738</v>
+        <v>3.74994039535522</v>
       </c>
       <c r="H2164" t="n">
         <v>10077225</v>
@@ -63154,7 +63154,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G2165" t="n">
-        <v>3.96417689323425</v>
+        <v>3.96417713165283</v>
       </c>
       <c r="H2165" t="n">
         <v>30567140</v>
@@ -63212,7 +63212,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G2167" t="n">
-        <v>3.9252245426178</v>
+        <v>3.92522478103638</v>
       </c>
       <c r="H2167" t="n">
         <v>13060115</v>
@@ -63444,7 +63444,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G2175" t="n">
-        <v>3.99501371383667</v>
+        <v>3.99501347541809</v>
       </c>
       <c r="H2175" t="n">
         <v>11662675</v>
@@ -63676,7 +63676,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.99420213699341</v>
+        <v>3.99420237541199</v>
       </c>
       <c r="H2183" t="n">
         <v>8046997</v>
@@ -63763,7 +63763,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2186" t="n">
-        <v>3.81404900550842</v>
+        <v>3.814049243927</v>
       </c>
       <c r="H2186" t="n">
         <v>21749998</v>
@@ -63792,7 +63792,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G2187" t="n">
-        <v>3.63470768928528</v>
+        <v>3.63470792770386</v>
       </c>
       <c r="H2187" t="n">
         <v>19583127</v>
@@ -63821,7 +63821,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G2188" t="n">
-        <v>3.52028608322144</v>
+        <v>3.52028632164001</v>
       </c>
       <c r="H2188" t="n">
         <v>25013968</v>
@@ -63908,7 +63908,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G2191" t="n">
-        <v>4.07859802246094</v>
+        <v>4.0785984992981</v>
       </c>
       <c r="H2191" t="n">
         <v>19208194</v>
@@ -64111,7 +64111,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2198" t="n">
-        <v>4.22629117965698</v>
+        <v>4.22629165649414</v>
       </c>
       <c r="H2198" t="n">
         <v>10355970</v>
@@ -64140,7 +64140,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G2199" t="n">
-        <v>4.23440647125244</v>
+        <v>4.23440599441528</v>
       </c>
       <c r="H2199" t="n">
         <v>8128461</v>
@@ -64227,7 +64227,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G2202" t="n">
-        <v>4.24089813232422</v>
+        <v>4.24089765548706</v>
       </c>
       <c r="H2202" t="n">
         <v>3987011</v>
@@ -64256,7 +64256,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2203" t="n">
-        <v>4.24414396286011</v>
+        <v>4.24414443969727</v>
       </c>
       <c r="H2203" t="n">
         <v>5969529</v>
@@ -64314,7 +64314,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G2205" t="n">
-        <v>4.23278284072876</v>
+        <v>4.23278331756592</v>
       </c>
       <c r="H2205" t="n">
         <v>7947589</v>
@@ -64372,7 +64372,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G2207" t="n">
-        <v>4.21006107330322</v>
+        <v>4.21006155014038</v>
       </c>
       <c r="H2207" t="n">
         <v>10026352</v>
@@ -64459,7 +64459,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2210" t="n">
-        <v>4.09807395935059</v>
+        <v>4.09807443618774</v>
       </c>
       <c r="H2210" t="n">
         <v>9610643</v>
@@ -64488,7 +64488,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.98608756065369</v>
+        <v>3.98608732223511</v>
       </c>
       <c r="H2211" t="n">
         <v>13196853</v>
@@ -64575,7 +64575,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.96904540061951</v>
+        <v>3.96904563903809</v>
       </c>
       <c r="H2214" t="n">
         <v>12020355</v>
@@ -64691,7 +64691,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G2218" t="n">
-        <v>3.99582529067993</v>
+        <v>3.99582505226135</v>
       </c>
       <c r="H2218" t="n">
         <v>10120832</v>
@@ -64749,7 +64749,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2220" t="n">
-        <v>4.0558762550354</v>
+        <v>4.05587673187256</v>
       </c>
       <c r="H2220" t="n">
         <v>12990332</v>
@@ -64778,7 +64778,7 @@
         <v>4.97100019454956</v>
       </c>
       <c r="G2221" t="n">
-        <v>4.03396558761597</v>
+        <v>4.03396606445312</v>
       </c>
       <c r="H2221" t="n">
         <v>14888759</v>
@@ -64836,7 +64836,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G2223" t="n">
-        <v>4.06074571609497</v>
+        <v>4.06074523925781</v>
       </c>
       <c r="H2223" t="n">
         <v>11996497</v>
@@ -64952,7 +64952,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G2227" t="n">
-        <v>4.20519208908081</v>
+        <v>4.20519256591797</v>
       </c>
       <c r="H2227" t="n">
         <v>12886962</v>
@@ -65039,7 +65039,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.88870716094971</v>
+        <v>3.88870739936829</v>
       </c>
       <c r="H2230" t="n">
         <v>16144924</v>
@@ -65097,7 +65097,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2232" t="n">
-        <v>4.0558762550354</v>
+        <v>4.05587673187256</v>
       </c>
       <c r="H2232" t="n">
         <v>10452631</v>
@@ -65126,7 +65126,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G2233" t="n">
-        <v>4.1532564163208</v>
+        <v>4.15325593948364</v>
       </c>
       <c r="H2233" t="n">
         <v>16873513</v>
@@ -65155,7 +65155,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G2234" t="n">
-        <v>4.16137075424194</v>
+        <v>4.1613712310791</v>
       </c>
       <c r="H2234" t="n">
         <v>7535202</v>
@@ -65271,7 +65271,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G2238" t="n">
-        <v>4.25712823867798</v>
+        <v>4.25712776184082</v>
       </c>
       <c r="H2238" t="n">
         <v>12216723</v>
@@ -65416,7 +65416,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G2243" t="n">
-        <v>4.2587513923645</v>
+        <v>4.25875091552734</v>
       </c>
       <c r="H2243" t="n">
         <v>8824041</v>
@@ -65445,7 +65445,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G2244" t="n">
-        <v>4.12566566467285</v>
+        <v>4.12566518783569</v>
       </c>
       <c r="H2244" t="n">
         <v>14098523</v>
@@ -65503,7 +65503,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G2246" t="n">
-        <v>4.09645080566406</v>
+        <v>4.09645128250122</v>
       </c>
       <c r="H2246" t="n">
         <v>9115898</v>
@@ -65561,7 +65561,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G2248" t="n">
-        <v>4.14838743209839</v>
+        <v>4.14838695526123</v>
       </c>
       <c r="H2248" t="n">
         <v>9089883</v>
@@ -65677,7 +65677,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G2252" t="n">
-        <v>4.13702630996704</v>
+        <v>4.13702583312988</v>
       </c>
       <c r="H2252" t="n">
         <v>8443415</v>
@@ -65764,7 +65764,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2255" t="n">
-        <v>4.22629117965698</v>
+        <v>4.22629165649414</v>
       </c>
       <c r="H2255" t="n">
         <v>19992634</v>
@@ -65880,7 +65880,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G2259" t="n">
-        <v>4.47623252868652</v>
+        <v>4.47623300552368</v>
       </c>
       <c r="H2259" t="n">
         <v>24618281</v>
@@ -65938,7 +65938,7 @@
         <v>6.01800012588501</v>
       </c>
       <c r="G2261" t="n">
-        <v>4.88360643386841</v>
+        <v>4.88360595703125</v>
       </c>
       <c r="H2261" t="n">
         <v>15163406</v>
@@ -66083,7 +66083,7 @@
         <v>5.93200016021729</v>
       </c>
       <c r="G2266" t="n">
-        <v>4.81381750106812</v>
+        <v>4.81381702423096</v>
       </c>
       <c r="H2266" t="n">
         <v>14209848</v>
@@ -66373,7 +66373,7 @@
         <v>6.37200021743774</v>
       </c>
       <c r="G2276" t="n">
-        <v>5.17087745666504</v>
+        <v>5.17087697982788</v>
       </c>
       <c r="H2276" t="n">
         <v>8697069</v>
@@ -66402,7 +66402,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2277" t="n">
-        <v>5.1286792755127</v>
+        <v>5.12867879867554</v>
       </c>
       <c r="H2277" t="n">
         <v>9776574</v>
@@ -66721,7 +66721,7 @@
         <v>6.65199995040894</v>
       </c>
       <c r="G2288" t="n">
-        <v>5.39809703826904</v>
+        <v>5.39809656143188</v>
       </c>
       <c r="H2288" t="n">
         <v>5442007</v>
@@ -66779,7 +66779,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2290" t="n">
-        <v>5.44516372680664</v>
+        <v>5.4451642036438</v>
       </c>
       <c r="H2290" t="n">
         <v>13302467</v>
@@ -66837,7 +66837,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2292" t="n">
-        <v>5.52631425857544</v>
+        <v>5.52631378173828</v>
       </c>
       <c r="H2292" t="n">
         <v>8534256</v>
@@ -66924,7 +66924,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2295" t="n">
-        <v>5.71133613586426</v>
+        <v>5.7113356590271</v>
       </c>
       <c r="H2295" t="n">
         <v>13899191</v>
@@ -67011,7 +67011,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2298" t="n">
-        <v>5.71133613586426</v>
+        <v>5.7113356590271</v>
       </c>
       <c r="H2298" t="n">
         <v>10737504</v>
@@ -67040,7 +67040,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2299" t="n">
-        <v>5.7421727180481</v>
+        <v>5.74217319488525</v>
       </c>
       <c r="H2299" t="n">
         <v>12020301</v>
@@ -67069,7 +67069,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2300" t="n">
-        <v>5.7421727180481</v>
+        <v>5.74217319488525</v>
       </c>
       <c r="H2300" t="n">
         <v>10188937</v>
@@ -67098,7 +67098,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G2301" t="n">
-        <v>5.7194504737854</v>
+        <v>5.71945095062256</v>
       </c>
       <c r="H2301" t="n">
         <v>9495869</v>
@@ -67272,7 +67272,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G2307" t="n">
-        <v>5.16276168823242</v>
+        <v>5.16276216506958</v>
       </c>
       <c r="H2307" t="n">
         <v>34036799</v>
@@ -67359,7 +67359,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G2310" t="n">
-        <v>5.05402088165283</v>
+        <v>5.05402135848999</v>
       </c>
       <c r="H2310" t="n">
         <v>20549379</v>
@@ -67417,7 +67417,7 @@
         <v>6.30200004577637</v>
       </c>
       <c r="G2312" t="n">
-        <v>5.1140718460083</v>
+        <v>5.11407232284546</v>
       </c>
       <c r="H2312" t="n">
         <v>15019935</v>
@@ -67620,7 +67620,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2319" t="n">
-        <v>5.1286792755127</v>
+        <v>5.12867879867554</v>
       </c>
       <c r="H2319" t="n">
         <v>15133688</v>
@@ -67852,7 +67852,7 @@
         <v>6.60799980163574</v>
       </c>
       <c r="G2327" t="n">
-        <v>5.36239051818848</v>
+        <v>5.36239099502563</v>
       </c>
       <c r="H2327" t="n">
         <v>26555901</v>
@@ -67910,7 +67910,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G2329" t="n">
-        <v>5.69835138320923</v>
+        <v>5.69835186004639</v>
       </c>
       <c r="H2329" t="n">
         <v>30197117</v>
@@ -67939,7 +67939,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G2330" t="n">
-        <v>5.69348239898682</v>
+        <v>5.69348287582397</v>
       </c>
       <c r="H2330" t="n">
         <v>20333854</v>
@@ -67997,7 +67997,7 @@
         <v>7.11800003051758</v>
       </c>
       <c r="G2332" t="n">
-        <v>5.77625608444214</v>
+        <v>5.77625560760498</v>
       </c>
       <c r="H2332" t="n">
         <v>25105102</v>
@@ -68142,7 +68142,7 @@
         <v>6.88800001144409</v>
       </c>
       <c r="G2337" t="n">
-        <v>5.5896110534668</v>
+        <v>5.58961057662964</v>
       </c>
       <c r="H2337" t="n">
         <v>31043675</v>
@@ -68229,7 +68229,7 @@
         <v>7.09600019454956</v>
       </c>
       <c r="G2340" t="n">
-        <v>5.75840282440186</v>
+        <v>5.75840330123901</v>
       </c>
       <c r="H2340" t="n">
         <v>18107631</v>
@@ -68345,7 +68345,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2344" t="n">
-        <v>6.34592866897583</v>
+        <v>6.34592914581299</v>
       </c>
       <c r="H2344" t="n">
         <v>26774763</v>
@@ -68403,7 +68403,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G2346" t="n">
-        <v>6.17064523696899</v>
+        <v>6.17064476013184</v>
       </c>
       <c r="H2346" t="n">
         <v>35553613</v>
@@ -68780,7 +68780,7 @@
         <v>5.89300012588501</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.7821683883667</v>
+        <v>4.78216886520386</v>
       </c>
       <c r="H2359" t="n">
         <v>19388932</v>
@@ -68809,7 +68809,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G2360" t="n">
-        <v>5.01019954681396</v>
+        <v>5.01020002365112</v>
       </c>
       <c r="H2360" t="n">
         <v>25575508</v>
@@ -68896,7 +68896,7 @@
         <v>6.67799997329712</v>
       </c>
       <c r="G2363" t="n">
-        <v>5.41919612884521</v>
+        <v>5.41919565200806</v>
       </c>
       <c r="H2363" t="n">
         <v>16423481</v>
@@ -68954,7 +68954,7 @@
         <v>6.53200006484985</v>
       </c>
       <c r="G2365" t="n">
-        <v>5.30071687698364</v>
+        <v>5.3007173538208</v>
       </c>
       <c r="H2365" t="n">
         <v>10138487</v>
@@ -68983,7 +68983,7 @@
         <v>6.50899982452393</v>
       </c>
       <c r="G2366" t="n">
-        <v>5.28205251693726</v>
+        <v>5.2820520401001</v>
       </c>
       <c r="H2366" t="n">
         <v>11026759</v>
@@ -69273,7 +69273,7 @@
         <v>7.48899984359741</v>
       </c>
       <c r="G2376" t="n">
-        <v>6.07732200622559</v>
+        <v>6.07732248306274</v>
       </c>
       <c r="H2376" t="n">
         <v>12569452</v>
@@ -69302,7 +69302,7 @@
         <v>7.68400001525879</v>
       </c>
       <c r="G2377" t="n">
-        <v>6.23556518554688</v>
+        <v>6.23556470870972</v>
       </c>
       <c r="H2377" t="n">
         <v>20468675</v>
@@ -69418,7 +69418,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2381" t="n">
-        <v>6.72733402252197</v>
+        <v>6.72733354568481</v>
       </c>
       <c r="H2381" t="n">
         <v>21907312</v>
@@ -69447,7 +69447,7 @@
         <v>8.14200019836426</v>
       </c>
       <c r="G2382" t="n">
-        <v>6.60723161697388</v>
+        <v>6.60723209381104</v>
       </c>
       <c r="H2382" t="n">
         <v>27889420</v>
@@ -69476,7 +69476,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G2383" t="n">
-        <v>6.55286121368408</v>
+        <v>6.55286073684692</v>
       </c>
       <c r="H2383" t="n">
         <v>25770231</v>
@@ -79980,6 +79980,35 @@
         <v>8796469</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>11.0860004425049</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>10.7559995651245</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>10412561</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2369.1689453125</v>
       </c>
       <c r="G3" t="n">
-        <v>1831.78967285156</v>
+        <v>1831.78979492188</v>
       </c>
       <c r="H3" t="n">
         <v>30489</v>
@@ -630,7 +630,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26940917969</v>
+        <v>1523.26928710938</v>
       </c>
       <c r="H9" t="n">
         <v>41776</v>
@@ -717,7 +717,7 @@
         <v>1595.07385253906</v>
       </c>
       <c r="G12" t="n">
-        <v>1233.2763671875</v>
+        <v>1233.27624511719</v>
       </c>
       <c r="H12" t="n">
         <v>58224</v>
@@ -891,7 +891,7 @@
         <v>1464.84240722656</v>
       </c>
       <c r="G18" t="n">
-        <v>1132.58410644531</v>
+        <v>1132.58422851562</v>
       </c>
       <c r="H18" t="n">
         <v>55490</v>
@@ -978,7 +978,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14135742188</v>
+        <v>1068.14123535156</v>
       </c>
       <c r="H21" t="n">
         <v>67666</v>
@@ -1036,7 +1036,7 @@
         <v>1218.96557617188</v>
       </c>
       <c r="G23" t="n">
-        <v>942.477478027344</v>
+        <v>942.4775390625</v>
       </c>
       <c r="H23" t="n">
         <v>56261</v>
@@ -1094,7 +1094,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.3115234375</v>
+        <v>918.311462402344</v>
       </c>
       <c r="H25" t="n">
         <v>64565</v>
@@ -1152,7 +1152,7 @@
         <v>1082.48315429688</v>
       </c>
       <c r="G27" t="n">
-        <v>836.952392578125</v>
+        <v>836.952331542969</v>
       </c>
       <c r="H27" t="n">
         <v>42864</v>
@@ -1268,7 +1268,7 @@
         <v>956.8359375</v>
       </c>
       <c r="G31" t="n">
-        <v>739.8046875</v>
+        <v>739.804626464844</v>
       </c>
       <c r="H31" t="n">
         <v>71729</v>
@@ -1616,7 +1616,7 @@
         <v>1076.23205566406</v>
       </c>
       <c r="G43" t="n">
-        <v>832.119079589844</v>
+        <v>832.119140625</v>
       </c>
       <c r="H43" t="n">
         <v>62505</v>
@@ -1848,7 +1848,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977905273438</v>
+        <v>927.977966308594</v>
       </c>
       <c r="H51" t="n">
         <v>78651</v>
@@ -1877,7 +1877,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03131103516</v>
+        <v>1023.03125</v>
       </c>
       <c r="H52" t="n">
         <v>99090</v>
@@ -1906,7 +1906,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810424804688</v>
+        <v>961.810363769531</v>
       </c>
       <c r="H53" t="n">
         <v>82251</v>
@@ -1935,7 +1935,7 @@
         <v>1245.01184082031</v>
       </c>
       <c r="G54" t="n">
-        <v>962.616027832031</v>
+        <v>962.615966796875</v>
       </c>
       <c r="H54" t="n">
         <v>47448</v>
@@ -1993,7 +1993,7 @@
         <v>1240.84448242188</v>
       </c>
       <c r="G56" t="n">
-        <v>959.393859863281</v>
+        <v>959.393920898438</v>
       </c>
       <c r="H56" t="n">
         <v>50887</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254028320312</v>
+        <v>997.254089355469</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2051,7 +2051,7 @@
         <v>1259.59777832031</v>
       </c>
       <c r="G58" t="n">
-        <v>973.893493652344</v>
+        <v>973.8935546875</v>
       </c>
       <c r="H58" t="n">
         <v>36967</v>
@@ -2080,7 +2080,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199340820312</v>
+        <v>960.199401855469</v>
       </c>
       <c r="H59" t="n">
         <v>31218</v>
@@ -2399,7 +2399,7 @@
         <v>1076.23205566406</v>
       </c>
       <c r="G70" t="n">
-        <v>832.119079589844</v>
+        <v>832.119140625</v>
       </c>
       <c r="H70" t="n">
         <v>65174</v>
@@ -2573,7 +2573,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03131103516</v>
+        <v>1023.03125</v>
       </c>
       <c r="H76" t="n">
         <v>87970</v>
@@ -2602,7 +2602,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86291503906</v>
+        <v>1085.86303710938</v>
       </c>
       <c r="H77" t="n">
         <v>60062</v>
@@ -2660,7 +2660,7 @@
         <v>1421.08471679688</v>
       </c>
       <c r="G79" t="n">
-        <v>1098.75158691406</v>
+        <v>1098.75170898438</v>
       </c>
       <c r="H79" t="n">
         <v>33838</v>
@@ -2689,7 +2689,7 @@
         <v>1379.41064453125</v>
       </c>
       <c r="G80" t="n">
-        <v>1066.5302734375</v>
+        <v>1066.53015136719</v>
       </c>
       <c r="H80" t="n">
         <v>19070</v>
@@ -2747,7 +2747,7 @@
         <v>1470.05163574219</v>
       </c>
       <c r="G82" t="n">
-        <v>1136.61181640625</v>
+        <v>1136.61193847656</v>
       </c>
       <c r="H82" t="n">
         <v>43127</v>
@@ -2863,7 +2863,7 @@
         <v>1285.64404296875</v>
       </c>
       <c r="G86" t="n">
-        <v>994.031921386719</v>
+        <v>994.031799316406</v>
       </c>
       <c r="H86" t="n">
         <v>50926</v>
@@ -2921,7 +2921,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80908203125</v>
+        <v>1019.80902099609</v>
       </c>
       <c r="H88" t="n">
         <v>45362</v>
@@ -3298,7 +3298,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809753417969</v>
+        <v>990.809692382812</v>
       </c>
       <c r="H101" t="n">
         <v>46314</v>
@@ -3327,7 +3327,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47613525391</v>
+        <v>1000.47619628906</v>
       </c>
       <c r="H102" t="n">
         <v>46119</v>
@@ -3356,7 +3356,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.14270019531</v>
+        <v>1010.14263916016</v>
       </c>
       <c r="H103" t="n">
         <v>21794</v>
@@ -3443,7 +3443,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.69830322266</v>
+        <v>1003.69836425781</v>
       </c>
       <c r="H106" t="n">
         <v>20322</v>
@@ -3588,7 +3588,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809753417969</v>
+        <v>990.809692382812</v>
       </c>
       <c r="H111" t="n">
         <v>28141</v>
@@ -3617,7 +3617,7 @@
         <v>1256.47229003906</v>
       </c>
       <c r="G112" t="n">
-        <v>971.476928710938</v>
+        <v>971.476989746094</v>
       </c>
       <c r="H112" t="n">
         <v>17386</v>
@@ -3704,7 +3704,7 @@
         <v>1046.01831054688</v>
       </c>
       <c r="G115" t="n">
-        <v>808.758483886719</v>
+        <v>808.758544921875</v>
       </c>
       <c r="H115" t="n">
         <v>39052</v>
@@ -3849,7 +3849,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368225097656</v>
+        <v>868.368286132812</v>
       </c>
       <c r="H120" t="n">
         <v>32561</v>
@@ -3994,7 +3994,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118286132812</v>
+        <v>634.118225097656</v>
       </c>
       <c r="H125" t="n">
         <v>71078</v>
@@ -4052,7 +4052,7 @@
         <v>809.934936523438</v>
       </c>
       <c r="G127" t="n">
-        <v>626.223937988281</v>
+        <v>626.223999023438</v>
       </c>
       <c r="H127" t="n">
         <v>44209</v>
@@ -4284,7 +4284,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549652099609</v>
+        <v>481.549682617188</v>
       </c>
       <c r="H135" t="n">
         <v>39529</v>
@@ -4342,7 +4342,7 @@
         <v>680.745422363281</v>
       </c>
       <c r="G137" t="n">
-        <v>526.337524414062</v>
+        <v>526.337463378906</v>
       </c>
       <c r="H137" t="n">
         <v>93205</v>
@@ -4458,7 +4458,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.53759765625</v>
+        <v>520.537658691406</v>
       </c>
       <c r="H141" t="n">
         <v>36777</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710083007812</v>
+        <v>510.710052490234</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4545,7 +4545,7 @@
         <v>650.114990234375</v>
       </c>
       <c r="G144" t="n">
-        <v>502.654754638672</v>
+        <v>502.654693603516</v>
       </c>
       <c r="H144" t="n">
         <v>26528</v>
@@ -4574,7 +4574,7 @@
         <v>595.313598632812</v>
       </c>
       <c r="G145" t="n">
-        <v>460.283477783203</v>
+        <v>460.283447265625</v>
       </c>
       <c r="H145" t="n">
         <v>58255</v>
@@ -4690,7 +4690,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532592773438</v>
+        <v>496.532623291016</v>
       </c>
       <c r="H149" t="n">
         <v>46906</v>
@@ -4893,7 +4893,7 @@
         <v>512.799011230469</v>
       </c>
       <c r="G156" t="n">
-        <v>396.485015869141</v>
+        <v>396.484985351562</v>
       </c>
       <c r="H156" t="n">
         <v>51516</v>
@@ -4951,7 +4951,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384948730469</v>
+        <v>399.384918212891</v>
       </c>
       <c r="H158" t="n">
         <v>11284</v>
@@ -4980,7 +4980,7 @@
         <v>523.009155273438</v>
       </c>
       <c r="G159" t="n">
-        <v>404.379241943359</v>
+        <v>404.379272460938</v>
       </c>
       <c r="H159" t="n">
         <v>21609</v>
@@ -5009,7 +5009,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.5126953125</v>
+        <v>400.512725830078</v>
       </c>
       <c r="H160" t="n">
         <v>10381</v>
@@ -5212,7 +5212,7 @@
         <v>490.50341796875</v>
       </c>
       <c r="G167" t="n">
-        <v>379.246551513672</v>
+        <v>379.246520996094</v>
       </c>
       <c r="H167" t="n">
         <v>15313</v>
@@ -5357,7 +5357,7 @@
         <v>498.629852294922</v>
       </c>
       <c r="G172" t="n">
-        <v>385.529724121094</v>
+        <v>385.529693603516</v>
       </c>
       <c r="H172" t="n">
         <v>21623</v>
@@ -5415,7 +5415,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724182128906</v>
+        <v>384.724212646484</v>
       </c>
       <c r="H174" t="n">
         <v>11728</v>
@@ -5618,7 +5618,7 @@
         <v>466.749237060547</v>
       </c>
       <c r="G181" t="n">
-        <v>360.880310058594</v>
+        <v>360.880340576172</v>
       </c>
       <c r="H181" t="n">
         <v>25529</v>
@@ -5647,7 +5647,7 @@
         <v>464.248779296875</v>
       </c>
       <c r="G182" t="n">
-        <v>358.947021484375</v>
+        <v>358.947052001953</v>
       </c>
       <c r="H182" t="n">
         <v>28648</v>
@@ -5763,7 +5763,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003784179688</v>
+        <v>309.003753662109</v>
       </c>
       <c r="H186" t="n">
         <v>27102</v>
@@ -5908,7 +5908,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742584228516</v>
+        <v>311.742614746094</v>
       </c>
       <c r="H191" t="n">
         <v>13716</v>
@@ -5995,7 +5995,7 @@
         <v>381.942565917969</v>
       </c>
       <c r="G194" t="n">
-        <v>295.309631347656</v>
+        <v>295.309661865234</v>
       </c>
       <c r="H194" t="n">
         <v>11584</v>
@@ -6024,7 +6024,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281982421875</v>
+        <v>291.281951904297</v>
       </c>
       <c r="H195" t="n">
         <v>13255</v>
@@ -6111,7 +6111,7 @@
         <v>354.229309082031</v>
       </c>
       <c r="G198" t="n">
-        <v>273.882385253906</v>
+        <v>273.882354736328</v>
       </c>
       <c r="H198" t="n">
         <v>39961</v>
@@ -6227,7 +6227,7 @@
         <v>355.896270751953</v>
       </c>
       <c r="G202" t="n">
-        <v>275.171203613281</v>
+        <v>275.171234130859</v>
       </c>
       <c r="H202" t="n">
         <v>17732</v>
@@ -6372,7 +6372,7 @@
         <v>497.379638671875</v>
       </c>
       <c r="G207" t="n">
-        <v>384.563049316406</v>
+        <v>384.563079833984</v>
       </c>
       <c r="H207" t="n">
         <v>111579</v>
@@ -6488,7 +6488,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184112548828</v>
+        <v>434.184143066406</v>
       </c>
       <c r="H211" t="n">
         <v>136414</v>
@@ -6894,7 +6894,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829284667969</v>
+        <v>405.829254150391</v>
       </c>
       <c r="H225" t="n">
         <v>74636</v>
@@ -7010,7 +7010,7 @@
         <v>469.666412353516</v>
       </c>
       <c r="G229" t="n">
-        <v>363.135803222656</v>
+        <v>363.135833740234</v>
       </c>
       <c r="H229" t="n">
         <v>34267</v>
@@ -7184,7 +7184,7 @@
         <v>421.949615478516</v>
       </c>
       <c r="G235" t="n">
-        <v>326.242218017578</v>
+        <v>326.242248535156</v>
       </c>
       <c r="H235" t="n">
         <v>85324</v>
@@ -7271,7 +7271,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H238" t="n">
         <v>56464</v>
@@ -7300,7 +7300,7 @@
         <v>389.235473632812</v>
       </c>
       <c r="G239" t="n">
-        <v>300.948364257812</v>
+        <v>300.948394775391</v>
       </c>
       <c r="H239" t="n">
         <v>60863</v>
@@ -7416,7 +7416,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H243" t="n">
         <v>108228</v>
@@ -7474,7 +7474,7 @@
         <v>426.742126464844</v>
       </c>
       <c r="G245" t="n">
-        <v>329.947692871094</v>
+        <v>329.947723388672</v>
       </c>
       <c r="H245" t="n">
         <v>45235</v>
@@ -7532,7 +7532,7 @@
         <v>430.492767333984</v>
       </c>
       <c r="G247" t="n">
-        <v>332.847625732422</v>
+        <v>332.847595214844</v>
       </c>
       <c r="H247" t="n">
         <v>82950</v>
@@ -7677,7 +7677,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G252" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H252" t="n">
         <v>181498</v>
@@ -7706,7 +7706,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G253" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G254" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G255" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G256" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G257" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G258" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G259" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G260" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G261" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G262" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G263" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G264" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G265" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G266" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G267" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G268" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G269" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G270" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G271" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G272" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G273" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G274" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G275" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G276" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G277" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G278" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G279" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G280" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G281" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G282" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G283" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G284" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G285" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G286" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G287" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G288" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G289" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G290" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G291" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G292" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G293" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G294" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G295" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G296" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G297" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G298" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G299" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G300" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G301" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G302" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G303" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G304" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G305" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G306" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G307" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G308" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G309" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G310" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G311" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G312" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G313" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G314" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G315" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G316" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G317" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G318" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G319" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G320" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G321" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G322" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G323" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G324" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G325" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G326" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G327" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G328" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G329" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G330" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G331" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G332" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G333" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G334" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G335" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G336" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G337" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G338" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G339" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G340" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G341" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G342" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G343" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G344" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G345" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G346" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G347" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G348" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G349" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G350" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G351" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G352" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G353" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G354" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G355" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G356" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G357" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G358" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G359" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G360" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G361" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G362" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G363" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G364" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G365" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G366" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G367" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G368" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G369" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G370" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G371" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G372" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G373" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G374" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G375" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G376" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G377" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G378" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G379" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G380" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G381" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G382" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G383" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G384" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G385" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G386" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G387" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G388" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G389" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G390" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G391" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G392" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G393" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G394" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G395" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G396" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G397" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G398" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G399" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G400" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G401" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G402" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G403" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G404" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G405" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G406" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G407" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G408" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G409" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G410" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G411" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G412" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G413" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G414" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G415" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G416" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G417" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G418" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G419" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G420" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G421" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G422" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G423" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G424" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G425" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G426" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G427" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G428" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G429" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G430" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G431" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G432" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G433" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G434" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G435" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G436" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G437" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G438" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G439" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G440" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G441" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G442" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G443" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G444" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G445" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G446" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G447" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G448" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G449" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G450" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G451" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G452" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G453" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G454" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G455" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G456" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G457" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G458" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G459" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G460" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G461" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G462" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G463" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G464" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G465" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003997802734</v>
+        <v>76.300407409668</v>
       </c>
       <c r="H468" t="n">
         <v>232423</v>
@@ -13999,7 +13999,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426254272461</v>
+        <v>76.0426330566406</v>
       </c>
       <c r="H470" t="n">
         <v>149896</v>
@@ -14260,7 +14260,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.1218299865723</v>
+        <v>63.121826171875</v>
       </c>
       <c r="H479" t="n">
         <v>202691</v>
@@ -14318,7 +14318,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264404296875</v>
+        <v>56.2264366149902</v>
       </c>
       <c r="H481" t="n">
         <v>308433</v>
@@ -14434,7 +14434,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.1540451049805</v>
+        <v>63.1540489196777</v>
       </c>
       <c r="H485" t="n">
         <v>461818</v>
@@ -14492,7 +14492,7 @@
         <v>82.0978469848633</v>
       </c>
       <c r="G487" t="n">
-        <v>63.4762649536133</v>
+        <v>63.476261138916</v>
       </c>
       <c r="H487" t="n">
         <v>63428</v>
@@ -14521,7 +14521,7 @@
         <v>83.306396484375</v>
       </c>
       <c r="G488" t="n">
-        <v>64.4106826782227</v>
+        <v>64.4106903076172</v>
       </c>
       <c r="H488" t="n">
         <v>91362</v>
@@ -14550,7 +14550,7 @@
         <v>84.1815490722656</v>
       </c>
       <c r="G489" t="n">
-        <v>65.0873413085938</v>
+        <v>65.0873336791992</v>
       </c>
       <c r="H489" t="n">
         <v>130214</v>
@@ -14695,7 +14695,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.1540451049805</v>
+        <v>63.1540489196777</v>
       </c>
       <c r="H494" t="n">
         <v>82320</v>
@@ -14724,7 +14724,7 @@
         <v>82.3062210083008</v>
       </c>
       <c r="G495" t="n">
-        <v>63.6373748779297</v>
+        <v>63.637378692627</v>
       </c>
       <c r="H495" t="n">
         <v>41220</v>
@@ -14811,7 +14811,7 @@
         <v>80.6392593383789</v>
       </c>
       <c r="G498" t="n">
-        <v>62.3485107421875</v>
+        <v>62.3485145568848</v>
       </c>
       <c r="H498" t="n">
         <v>58360</v>
@@ -14869,7 +14869,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618530273438</v>
+        <v>61.961856842041</v>
       </c>
       <c r="H500" t="n">
         <v>52866</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563186645508</v>
+        <v>61.156322479248</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -14956,7 +14956,7 @@
         <v>77.5137023925781</v>
       </c>
       <c r="G503" t="n">
-        <v>59.9319038391113</v>
+        <v>59.9319000244141</v>
       </c>
       <c r="H503" t="n">
         <v>48461</v>
@@ -14985,7 +14985,7 @@
         <v>80.0974960327148</v>
       </c>
       <c r="G504" t="n">
-        <v>61.9296379089355</v>
+        <v>61.9296340942383</v>
       </c>
       <c r="H504" t="n">
         <v>38478</v>
@@ -15014,7 +15014,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.6707305908203</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H505" t="n">
         <v>57550</v>
@@ -15043,7 +15043,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G506" t="n">
-        <v>62.5096168518066</v>
+        <v>62.5096206665039</v>
       </c>
       <c r="H506" t="n">
         <v>88056</v>
@@ -15101,7 +15101,7 @@
         <v>79.7640991210938</v>
       </c>
       <c r="G508" t="n">
-        <v>61.6718597412109</v>
+        <v>61.6718559265137</v>
       </c>
       <c r="H508" t="n">
         <v>34426</v>
@@ -15159,7 +15159,7 @@
         <v>81.93115234375</v>
       </c>
       <c r="G510" t="n">
-        <v>63.3473739624023</v>
+        <v>63.3473777770996</v>
       </c>
       <c r="H510" t="n">
         <v>35391</v>
@@ -15188,7 +15188,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573806762695</v>
+        <v>63.0573883056641</v>
       </c>
       <c r="H511" t="n">
         <v>34562</v>
@@ -15217,7 +15217,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.6707305908203</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H512" t="n">
         <v>22428</v>
@@ -15246,7 +15246,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.4129600524902</v>
+        <v>62.412956237793</v>
       </c>
       <c r="H513" t="n">
         <v>27484</v>
@@ -15304,7 +15304,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.6707305908203</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H515" t="n">
         <v>30486</v>
@@ -15333,7 +15333,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G516" t="n">
-        <v>62.5096168518066</v>
+        <v>62.5096206665039</v>
       </c>
       <c r="H516" t="n">
         <v>30537</v>
@@ -15391,7 +15391,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G518" t="n">
-        <v>63.9273643493652</v>
+        <v>63.927360534668</v>
       </c>
       <c r="H518" t="n">
         <v>298961</v>
@@ -15420,7 +15420,7 @@
         <v>81.8894805908203</v>
       </c>
       <c r="G519" t="n">
-        <v>63.3151588439941</v>
+        <v>63.3151512145996</v>
       </c>
       <c r="H519" t="n">
         <v>98758</v>
@@ -15507,7 +15507,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695938110352</v>
+        <v>63.6695899963379</v>
       </c>
       <c r="H522" t="n">
         <v>52551</v>
@@ -15536,7 +15536,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G523" t="n">
-        <v>63.9273643493652</v>
+        <v>63.927360534668</v>
       </c>
       <c r="H523" t="n">
         <v>45681</v>
@@ -15594,7 +15594,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.6707305908203</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H525" t="n">
         <v>40067</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184944152832</v>
+        <v>63.2184906005859</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15652,7 +15652,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.6707305908203</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H527" t="n">
         <v>45359</v>
@@ -15710,7 +15710,7 @@
         <v>81.0143203735352</v>
       </c>
       <c r="G529" t="n">
-        <v>62.6385078430176</v>
+        <v>62.6385040283203</v>
       </c>
       <c r="H529" t="n">
         <v>50236</v>
@@ -15768,7 +15768,7 @@
         <v>80.555908203125</v>
       </c>
       <c r="G531" t="n">
-        <v>62.2840728759766</v>
+        <v>62.2840690612793</v>
       </c>
       <c r="H531" t="n">
         <v>74076</v>
@@ -15826,7 +15826,7 @@
         <v>78.7639236450195</v>
       </c>
       <c r="G533" t="n">
-        <v>60.8985481262207</v>
+        <v>60.8985443115234</v>
       </c>
       <c r="H533" t="n">
         <v>102976</v>
@@ -15855,7 +15855,7 @@
         <v>77.9721221923828</v>
       </c>
       <c r="G534" t="n">
-        <v>60.2863464355469</v>
+        <v>60.2863426208496</v>
       </c>
       <c r="H534" t="n">
         <v>68146</v>
@@ -16000,7 +16000,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.8363761901855</v>
+        <v>58.8363800048828</v>
       </c>
       <c r="H539" t="n">
         <v>77063</v>
@@ -16029,7 +16029,7 @@
         <v>78.7639236450195</v>
       </c>
       <c r="G540" t="n">
-        <v>60.8985481262207</v>
+        <v>60.8985443115234</v>
       </c>
       <c r="H540" t="n">
         <v>63710</v>
@@ -16290,7 +16290,7 @@
         <v>67.0951995849609</v>
       </c>
       <c r="G549" t="n">
-        <v>51.8765411376953</v>
+        <v>51.8765449523926</v>
       </c>
       <c r="H549" t="n">
         <v>124037</v>
@@ -16348,7 +16348,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.0054321289062</v>
+        <v>52.005428314209</v>
       </c>
       <c r="H551" t="n">
         <v>83287</v>
@@ -16493,7 +16493,7 @@
         <v>63.5529022216797</v>
       </c>
       <c r="G556" t="n">
-        <v>49.1377143859863</v>
+        <v>49.1377182006836</v>
       </c>
       <c r="H556" t="n">
         <v>55076</v>
@@ -16696,7 +16696,7 @@
         <v>63.6987609863281</v>
       </c>
       <c r="G563" t="n">
-        <v>49.25048828125</v>
+        <v>49.2504920959473</v>
       </c>
       <c r="H563" t="n">
         <v>49204</v>
@@ -16899,7 +16899,7 @@
         <v>56.0099029541016</v>
       </c>
       <c r="G570" t="n">
-        <v>43.3056373596191</v>
+        <v>43.3056335449219</v>
       </c>
       <c r="H570" t="n">
         <v>225410</v>
@@ -16928,7 +16928,7 @@
         <v>54.3221054077148</v>
       </c>
       <c r="G571" t="n">
-        <v>42.0006637573242</v>
+        <v>42.0006675720215</v>
       </c>
       <c r="H571" t="n">
         <v>114062</v>
@@ -16957,7 +16957,7 @@
         <v>52.9051856994629</v>
       </c>
       <c r="G572" t="n">
-        <v>40.9051361083984</v>
+        <v>40.9051322937012</v>
       </c>
       <c r="H572" t="n">
         <v>130898</v>
@@ -16986,7 +16986,7 @@
         <v>51.6758041381836</v>
       </c>
       <c r="G573" t="n">
-        <v>39.9546012878418</v>
+        <v>39.9546051025391</v>
       </c>
       <c r="H573" t="n">
         <v>230355</v>
@@ -17015,7 +17015,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367904663086</v>
+        <v>41.4367866516113</v>
       </c>
       <c r="H574" t="n">
         <v>153152</v>
@@ -17189,7 +17189,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.175609588623</v>
+        <v>44.1756134033203</v>
       </c>
       <c r="H580" t="n">
         <v>158204</v>
@@ -17218,7 +17218,7 @@
         <v>55.5723266601562</v>
       </c>
       <c r="G581" t="n">
-        <v>42.9673118591309</v>
+        <v>42.9673080444336</v>
       </c>
       <c r="H581" t="n">
         <v>116018</v>
@@ -17305,7 +17305,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G584" t="n">
-        <v>42.9511947631836</v>
+        <v>42.9511985778809</v>
       </c>
       <c r="H584" t="n">
         <v>78005</v>
@@ -17479,7 +17479,7 @@
         <v>56.4683151245117</v>
       </c>
       <c r="G590" t="n">
-        <v>43.6600685119629</v>
+        <v>43.6600646972656</v>
       </c>
       <c r="H590" t="n">
         <v>38834</v>
@@ -17566,7 +17566,7 @@
         <v>55.4889755249023</v>
       </c>
       <c r="G593" t="n">
-        <v>42.9028663635254</v>
+        <v>42.9028625488281</v>
       </c>
       <c r="H593" t="n">
         <v>40012</v>
@@ -17624,7 +17624,7 @@
         <v>55.6348342895508</v>
       </c>
       <c r="G595" t="n">
-        <v>43.0156402587891</v>
+        <v>43.0156364440918</v>
       </c>
       <c r="H595" t="n">
         <v>43278</v>
@@ -17769,7 +17769,7 @@
         <v>57.3017959594727</v>
       </c>
       <c r="G600" t="n">
-        <v>44.304500579834</v>
+        <v>44.3044967651367</v>
       </c>
       <c r="H600" t="n">
         <v>186430</v>
@@ -18059,7 +18059,7 @@
         <v>59.1771278381348</v>
       </c>
       <c r="G610" t="n">
-        <v>45.754467010498</v>
+        <v>45.7544631958008</v>
       </c>
       <c r="H610" t="n">
         <v>95657</v>
@@ -18088,7 +18088,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G611" t="n">
-        <v>44.3206062316895</v>
+        <v>44.3206100463867</v>
       </c>
       <c r="H611" t="n">
         <v>142469</v>
@@ -18175,7 +18175,7 @@
         <v>52.2800750732422</v>
       </c>
       <c r="G614" t="n">
-        <v>40.4218101501465</v>
+        <v>40.4218139648438</v>
       </c>
       <c r="H614" t="n">
         <v>255740</v>
@@ -18262,7 +18262,7 @@
         <v>55.6348342895508</v>
       </c>
       <c r="G617" t="n">
-        <v>43.0156402587891</v>
+        <v>43.0156364440918</v>
       </c>
       <c r="H617" t="n">
         <v>190893</v>
@@ -18291,7 +18291,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G618" t="n">
-        <v>42.9511947631836</v>
+        <v>42.9511985778809</v>
       </c>
       <c r="H618" t="n">
         <v>69954</v>
@@ -18349,7 +18349,7 @@
         <v>59.1771278381348</v>
       </c>
       <c r="G620" t="n">
-        <v>45.754467010498</v>
+        <v>45.7544631958008</v>
       </c>
       <c r="H620" t="n">
         <v>121797</v>
@@ -18378,7 +18378,7 @@
         <v>57.1976127624512</v>
       </c>
       <c r="G621" t="n">
-        <v>44.2239418029785</v>
+        <v>44.2239456176758</v>
       </c>
       <c r="H621" t="n">
         <v>99660</v>
@@ -18465,7 +18465,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G624" t="n">
-        <v>44.3206062316895</v>
+        <v>44.3206100463867</v>
       </c>
       <c r="H624" t="n">
         <v>48032</v>
@@ -18494,7 +18494,7 @@
         <v>58.5520172119141</v>
       </c>
       <c r="G625" t="n">
-        <v>45.2711372375488</v>
+        <v>45.2711410522461</v>
       </c>
       <c r="H625" t="n">
         <v>62650</v>
@@ -18813,7 +18813,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.373477935791</v>
+        <v>40.3734817504883</v>
       </c>
       <c r="H636" t="n">
         <v>90143</v>
@@ -18900,7 +18900,7 @@
         <v>51.6758041381836</v>
       </c>
       <c r="G639" t="n">
-        <v>39.9546012878418</v>
+        <v>39.9546051025391</v>
       </c>
       <c r="H639" t="n">
         <v>54533</v>
@@ -18958,7 +18958,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062728881836</v>
+        <v>39.9062690734863</v>
       </c>
       <c r="H641" t="n">
         <v>47114</v>
@@ -19016,7 +19016,7 @@
         <v>51.4465942382812</v>
       </c>
       <c r="G643" t="n">
-        <v>39.7773818969727</v>
+        <v>39.7773857116699</v>
       </c>
       <c r="H643" t="n">
         <v>34432</v>
@@ -19074,7 +19074,7 @@
         <v>50.6339530944824</v>
       </c>
       <c r="G645" t="n">
-        <v>39.1490669250488</v>
+        <v>39.1490631103516</v>
       </c>
       <c r="H645" t="n">
         <v>34642</v>
@@ -19132,7 +19132,7 @@
         <v>50.4255828857422</v>
       </c>
       <c r="G647" t="n">
-        <v>38.9879608154297</v>
+        <v>38.9879570007324</v>
       </c>
       <c r="H647" t="n">
         <v>33718</v>
@@ -19277,7 +19277,7 @@
         <v>50.0088424682617</v>
       </c>
       <c r="G652" t="n">
-        <v>38.6657447814941</v>
+        <v>38.6657485961914</v>
       </c>
       <c r="H652" t="n">
         <v>24569</v>
@@ -19306,7 +19306,7 @@
         <v>49.4879150390625</v>
       </c>
       <c r="G653" t="n">
-        <v>38.2629737854004</v>
+        <v>38.2629776000977</v>
       </c>
       <c r="H653" t="n">
         <v>58634</v>
@@ -19335,7 +19335,7 @@
         <v>50.0088424682617</v>
       </c>
       <c r="G654" t="n">
-        <v>38.6657447814941</v>
+        <v>38.6657485961914</v>
       </c>
       <c r="H654" t="n">
         <v>54520</v>
@@ -19364,7 +19364,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374221801758</v>
       </c>
       <c r="H655" t="n">
         <v>34543</v>
@@ -19393,7 +19393,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H656" t="n">
         <v>39162</v>
@@ -19509,7 +19509,7 @@
         <v>54.1762466430664</v>
       </c>
       <c r="G660" t="n">
-        <v>41.8878898620605</v>
+        <v>41.8878936767578</v>
       </c>
       <c r="H660" t="n">
         <v>68284</v>
@@ -19567,7 +19567,7 @@
         <v>50.6339530944824</v>
       </c>
       <c r="G662" t="n">
-        <v>39.1490669250488</v>
+        <v>39.1490631103516</v>
       </c>
       <c r="H662" t="n">
         <v>400900</v>
@@ -19625,7 +19625,7 @@
         <v>50.4255828857422</v>
       </c>
       <c r="G664" t="n">
-        <v>38.9879608154297</v>
+        <v>38.9879570007324</v>
       </c>
       <c r="H664" t="n">
         <v>60973</v>
@@ -19857,7 +19857,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G672" t="n">
-        <v>35.395263671875</v>
+        <v>35.3952674865723</v>
       </c>
       <c r="H672" t="n">
         <v>39171</v>
@@ -19973,7 +19973,7 @@
         <v>45.5288848876953</v>
       </c>
       <c r="G676" t="n">
-        <v>35.2019386291504</v>
+        <v>35.2019424438477</v>
       </c>
       <c r="H676" t="n">
         <v>28978</v>
@@ -20089,7 +20089,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580749511719</v>
+        <v>34.0580711364746</v>
       </c>
       <c r="H680" t="n">
         <v>49600</v>
@@ -20147,7 +20147,7 @@
         <v>44.507869720459</v>
       </c>
       <c r="G682" t="n">
-        <v>34.4125137329102</v>
+        <v>34.4125099182129</v>
       </c>
       <c r="H682" t="n">
         <v>55885</v>
@@ -20234,7 +20234,7 @@
         <v>46.3206901550293</v>
       </c>
       <c r="G685" t="n">
-        <v>35.8141479492188</v>
+        <v>35.8141441345215</v>
       </c>
       <c r="H685" t="n">
         <v>78485</v>
@@ -20263,7 +20263,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G686" t="n">
-        <v>35.395263671875</v>
+        <v>35.3952674865723</v>
       </c>
       <c r="H686" t="n">
         <v>55186</v>
@@ -20292,7 +20292,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G687" t="n">
-        <v>38.3113059997559</v>
+        <v>38.3113098144531</v>
       </c>
       <c r="H687" t="n">
         <v>246032</v>
@@ -20321,7 +20321,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374221801758</v>
       </c>
       <c r="H688" t="n">
         <v>118566</v>
@@ -20350,7 +20350,7 @@
         <v>47.695930480957</v>
       </c>
       <c r="G689" t="n">
-        <v>36.8774490356445</v>
+        <v>36.8774528503418</v>
       </c>
       <c r="H689" t="n">
         <v>132939</v>
@@ -20408,7 +20408,7 @@
         <v>46.6124076843262</v>
       </c>
       <c r="G691" t="n">
-        <v>36.0396957397461</v>
+        <v>36.0396995544434</v>
       </c>
       <c r="H691" t="n">
         <v>87887</v>
@@ -20437,7 +20437,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057754516602</v>
+        <v>37.5057716369629</v>
       </c>
       <c r="H692" t="n">
         <v>93100</v>
@@ -20582,7 +20582,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G697" t="n">
-        <v>38.3113059997559</v>
+        <v>38.3113098144531</v>
       </c>
       <c r="H697" t="n">
         <v>47583</v>
@@ -20640,7 +20640,7 @@
         <v>50.175537109375</v>
       </c>
       <c r="G699" t="n">
-        <v>38.7946319580078</v>
+        <v>38.7946281433105</v>
       </c>
       <c r="H699" t="n">
         <v>37785</v>
@@ -20669,7 +20669,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H700" t="n">
         <v>69415</v>
@@ -20756,7 +20756,7 @@
         <v>42.9242553710938</v>
       </c>
       <c r="G703" t="n">
-        <v>33.1880989074707</v>
+        <v>33.1880950927734</v>
       </c>
       <c r="H703" t="n">
         <v>149650</v>
@@ -20785,7 +20785,7 @@
         <v>42.861743927002</v>
       </c>
       <c r="G704" t="n">
-        <v>33.1397666931152</v>
+        <v>33.139762878418</v>
       </c>
       <c r="H704" t="n">
         <v>60234</v>
@@ -20872,7 +20872,7 @@
         <v>40.1008377075195</v>
       </c>
       <c r="G707" t="n">
-        <v>31.0050926208496</v>
+        <v>31.0050945281982</v>
       </c>
       <c r="H707" t="n">
         <v>128220</v>
@@ -20901,7 +20901,7 @@
         <v>39.3715438842773</v>
       </c>
       <c r="G708" t="n">
-        <v>30.441219329834</v>
+        <v>30.4412174224854</v>
       </c>
       <c r="H708" t="n">
         <v>153302</v>
@@ -20930,7 +20930,7 @@
         <v>38.5068092346191</v>
       </c>
       <c r="G709" t="n">
-        <v>29.7726230621338</v>
+        <v>29.7726249694824</v>
       </c>
       <c r="H709" t="n">
         <v>137943</v>
@@ -21307,7 +21307,7 @@
         <v>31.7764511108398</v>
       </c>
       <c r="G722" t="n">
-        <v>24.5688571929932</v>
+        <v>24.5688591003418</v>
       </c>
       <c r="H722" t="n">
         <v>227745</v>
@@ -21394,7 +21394,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G725" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H725" t="n">
         <v>79264</v>
@@ -21481,7 +21481,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480247497559</v>
+        <v>24.4480266571045</v>
       </c>
       <c r="H728" t="n">
         <v>59503</v>
@@ -21568,7 +21568,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G731" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H731" t="n">
         <v>152132</v>
@@ -21597,7 +21597,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177577972412</v>
+        <v>24.1177558898926</v>
       </c>
       <c r="H732" t="n">
         <v>82427</v>
@@ -21684,7 +21684,7 @@
         <v>29.411449432373</v>
       </c>
       <c r="G735" t="n">
-        <v>22.740291595459</v>
+        <v>22.7402896881104</v>
       </c>
       <c r="H735" t="n">
         <v>76940</v>
@@ -21771,7 +21771,7 @@
         <v>27.8174171447754</v>
       </c>
       <c r="G738" t="n">
-        <v>21.5078201293945</v>
+        <v>21.5078182220459</v>
       </c>
       <c r="H738" t="n">
         <v>74571</v>
@@ -22061,7 +22061,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715534210205</v>
+        <v>27.8715553283691</v>
       </c>
       <c r="H748" t="n">
         <v>89948</v>
@@ -22148,7 +22148,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363166809082</v>
+        <v>26.2363185882568</v>
       </c>
       <c r="H751" t="n">
         <v>69130</v>
@@ -22206,7 +22206,7 @@
         <v>31.8285446166992</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6091365814209</v>
+        <v>24.6091346740723</v>
       </c>
       <c r="H753" t="n">
         <v>76863</v>
@@ -22264,7 +22264,7 @@
         <v>32.9329071044922</v>
       </c>
       <c r="G755" t="n">
-        <v>25.4630031585693</v>
+        <v>25.463005065918</v>
       </c>
       <c r="H755" t="n">
         <v>93592</v>
@@ -22351,7 +22351,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983089447021</v>
+        <v>24.1983108520508</v>
       </c>
       <c r="H758" t="n">
         <v>28653</v>
@@ -22467,7 +22467,7 @@
         <v>30.9325523376465</v>
       </c>
       <c r="G762" t="n">
-        <v>23.916374206543</v>
+        <v>23.9163722991943</v>
       </c>
       <c r="H762" t="n">
         <v>60399</v>
@@ -22496,7 +22496,7 @@
         <v>31.1617584228516</v>
       </c>
       <c r="G763" t="n">
-        <v>24.0935916900635</v>
+        <v>24.0935897827148</v>
       </c>
       <c r="H763" t="n">
         <v>61156</v>
@@ -22583,7 +22583,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399738311768</v>
+        <v>24.4399719238281</v>
       </c>
       <c r="H766" t="n">
         <v>84803</v>
@@ -22641,7 +22641,7 @@
         <v>31.9744033813477</v>
       </c>
       <c r="G768" t="n">
-        <v>24.7219104766846</v>
+        <v>24.7219123840332</v>
       </c>
       <c r="H768" t="n">
         <v>89969</v>
@@ -22757,7 +22757,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058700561523</v>
+        <v>21.8058681488037</v>
       </c>
       <c r="H772" t="n">
         <v>398596</v>
@@ -22786,7 +22786,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G773" t="n">
-        <v>20.1384086608887</v>
+        <v>20.13840675354</v>
       </c>
       <c r="H773" t="n">
         <v>541685</v>
@@ -22873,7 +22873,7 @@
         <v>25.5774383544922</v>
       </c>
       <c r="G776" t="n">
-        <v>19.775915145874</v>
+        <v>19.7759170532227</v>
       </c>
       <c r="H776" t="n">
         <v>194733</v>
@@ -22931,7 +22931,7 @@
         <v>25.2336273193359</v>
       </c>
       <c r="G778" t="n">
-        <v>19.5100898742676</v>
+        <v>19.5100917816162</v>
       </c>
       <c r="H778" t="n">
         <v>81516</v>
@@ -23047,7 +23047,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189617156982</v>
+        <v>20.2189598083496</v>
       </c>
       <c r="H782" t="n">
         <v>91503</v>
@@ -23134,7 +23134,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H785" t="n">
         <v>94288</v>
@@ -23221,7 +23221,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G788" t="n">
-        <v>19.3328704833984</v>
+        <v>19.3328723907471</v>
       </c>
       <c r="H788" t="n">
         <v>72501</v>
@@ -23511,7 +23511,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083885192871</v>
+        <v>21.0083866119385</v>
       </c>
       <c r="H798" t="n">
         <v>100025</v>
@@ -23830,7 +23830,7 @@
         <v>28.213321685791</v>
       </c>
       <c r="G809" t="n">
-        <v>21.8139228820801</v>
+        <v>21.8139247894287</v>
       </c>
       <c r="H809" t="n">
         <v>93205</v>
@@ -23975,7 +23975,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G814" t="n">
-        <v>20.2109050750732</v>
+        <v>20.2109069824219</v>
       </c>
       <c r="H814" t="n">
         <v>72125</v>
@@ -24062,7 +24062,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908935546875</v>
+        <v>20.7908916473389</v>
       </c>
       <c r="H817" t="n">
         <v>135708</v>
@@ -24149,7 +24149,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G820" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H820" t="n">
         <v>116471</v>
@@ -24178,7 +24178,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5008983612061</v>
+        <v>20.5009002685547</v>
       </c>
       <c r="H821" t="n">
         <v>75021</v>
@@ -24207,7 +24207,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H822" t="n">
         <v>72133</v>
@@ -24236,7 +24236,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G823" t="n">
-        <v>20.2995128631592</v>
+        <v>20.2995147705078</v>
       </c>
       <c r="H823" t="n">
         <v>50892</v>
@@ -24265,7 +24265,7 @@
         <v>25.9837608337402</v>
       </c>
       <c r="G824" t="n">
-        <v>20.0900783538818</v>
+        <v>20.0900764465332</v>
       </c>
       <c r="H824" t="n">
         <v>122105</v>
@@ -24294,7 +24294,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G825" t="n">
-        <v>20.1384086608887</v>
+        <v>20.13840675354</v>
       </c>
       <c r="H825" t="n">
         <v>67600</v>
@@ -24381,7 +24381,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G828" t="n">
-        <v>20.1706314086914</v>
+        <v>20.1706295013428</v>
       </c>
       <c r="H828" t="n">
         <v>55529</v>
@@ -24410,7 +24410,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G829" t="n">
-        <v>20.2995128631592</v>
+        <v>20.2995147705078</v>
       </c>
       <c r="H829" t="n">
         <v>73545</v>
@@ -24468,7 +24468,7 @@
         <v>26.5671977996826</v>
       </c>
       <c r="G831" t="n">
-        <v>20.5411777496338</v>
+        <v>20.5411758422852</v>
       </c>
       <c r="H831" t="n">
         <v>63160</v>
@@ -24526,7 +24526,7 @@
         <v>26.3171520233154</v>
       </c>
       <c r="G833" t="n">
-        <v>20.3478450775146</v>
+        <v>20.3478469848633</v>
       </c>
       <c r="H833" t="n">
         <v>51548</v>
@@ -24555,7 +24555,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G834" t="n">
-        <v>20.1706314086914</v>
+        <v>20.1706295013428</v>
       </c>
       <c r="H834" t="n">
         <v>86286</v>
@@ -24874,7 +24874,7 @@
         <v>28.2341575622559</v>
       </c>
       <c r="G845" t="n">
-        <v>21.8300342559814</v>
+        <v>21.8300323486328</v>
       </c>
       <c r="H845" t="n">
         <v>92713</v>
@@ -24990,7 +24990,7 @@
         <v>27.5882110595703</v>
       </c>
       <c r="G849" t="n">
-        <v>21.330602645874</v>
+        <v>21.3306007385254</v>
       </c>
       <c r="H849" t="n">
         <v>65057</v>
@@ -25019,7 +25019,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150615692139</v>
+        <v>20.8150596618652</v>
       </c>
       <c r="H850" t="n">
         <v>79359</v>
@@ -25048,7 +25048,7 @@
         <v>26.5671977996826</v>
       </c>
       <c r="G851" t="n">
-        <v>20.5411777496338</v>
+        <v>20.5411758422852</v>
       </c>
       <c r="H851" t="n">
         <v>87555</v>
@@ -25106,7 +25106,7 @@
         <v>25.3169765472412</v>
       </c>
       <c r="G853" t="n">
-        <v>19.5745334625244</v>
+        <v>19.5745315551758</v>
       </c>
       <c r="H853" t="n">
         <v>88528</v>
@@ -25251,7 +25251,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H858" t="n">
         <v>84494</v>
@@ -25367,7 +25367,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H862" t="n">
         <v>131429</v>
@@ -25454,7 +25454,7 @@
         <v>22.2747707366943</v>
       </c>
       <c r="G865" t="n">
-        <v>17.2223663330078</v>
+        <v>17.2223682403564</v>
       </c>
       <c r="H865" t="n">
         <v>109629</v>
@@ -25512,7 +25512,7 @@
         <v>21.8580303192139</v>
       </c>
       <c r="G867" t="n">
-        <v>16.9001502990723</v>
+        <v>16.9001522064209</v>
       </c>
       <c r="H867" t="n">
         <v>72401</v>
@@ -25831,7 +25831,7 @@
         <v>21.0662231445312</v>
       </c>
       <c r="G878" t="n">
-        <v>16.2879428863525</v>
+        <v>16.2879447937012</v>
       </c>
       <c r="H878" t="n">
         <v>56625</v>
@@ -25860,7 +25860,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.110725402832</v>
+        <v>16.1107273101807</v>
       </c>
       <c r="H879" t="n">
         <v>44522</v>
@@ -25947,7 +25947,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G882" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H882" t="n">
         <v>129721</v>
@@ -25976,7 +25976,7 @@
         <v>22.2539348602295</v>
       </c>
       <c r="G883" t="n">
-        <v>17.2062568664551</v>
+        <v>17.2062549591064</v>
       </c>
       <c r="H883" t="n">
         <v>82411</v>
@@ -26063,7 +26063,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290374755859</v>
+        <v>17.0290355682373</v>
       </c>
       <c r="H886" t="n">
         <v>60342</v>
@@ -26121,7 +26121,7 @@
         <v>22.4623031616211</v>
       </c>
       <c r="G888" t="n">
-        <v>17.3673629760742</v>
+        <v>17.3673610687256</v>
       </c>
       <c r="H888" t="n">
         <v>52523</v>
@@ -26179,7 +26179,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H890" t="n">
         <v>95871</v>
@@ -26208,7 +26208,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G891" t="n">
-        <v>19.187873840332</v>
+        <v>19.1878757476807</v>
       </c>
       <c r="H891" t="n">
         <v>189581</v>
@@ -26411,7 +26411,7 @@
         <v>35.4854393005371</v>
       </c>
       <c r="G898" t="n">
-        <v>27.4365673065186</v>
+        <v>27.4365653991699</v>
       </c>
       <c r="H898" t="n">
         <v>324224</v>
@@ -26730,7 +26730,7 @@
         <v>29.4427051544189</v>
       </c>
       <c r="G909" t="n">
-        <v>22.7644577026367</v>
+        <v>22.7644557952881</v>
       </c>
       <c r="H909" t="n">
         <v>66556</v>
@@ -26846,7 +26846,7 @@
         <v>27.1923065185547</v>
       </c>
       <c r="G913" t="n">
-        <v>21.0244960784912</v>
+        <v>21.0244979858398</v>
       </c>
       <c r="H913" t="n">
         <v>226257</v>
@@ -26962,7 +26962,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G917" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H917" t="n">
         <v>101465</v>
@@ -26991,7 +26991,7 @@
         <v>24.7752132415771</v>
       </c>
       <c r="G918" t="n">
-        <v>19.1556529998779</v>
+        <v>19.1556549072266</v>
       </c>
       <c r="H918" t="n">
         <v>269232</v>
@@ -27020,7 +27020,7 @@
         <v>25.0877685546875</v>
       </c>
       <c r="G919" t="n">
-        <v>19.3973159790039</v>
+        <v>19.3973140716553</v>
       </c>
       <c r="H919" t="n">
         <v>122716</v>
@@ -27049,7 +27049,7 @@
         <v>26.9005889892578</v>
       </c>
       <c r="G920" t="n">
-        <v>20.7989463806152</v>
+        <v>20.7989482879639</v>
       </c>
       <c r="H920" t="n">
         <v>193491</v>
@@ -27194,7 +27194,7 @@
         <v>27.5882110595703</v>
       </c>
       <c r="G925" t="n">
-        <v>21.330602645874</v>
+        <v>21.3306007385254</v>
       </c>
       <c r="H925" t="n">
         <v>85266</v>
@@ -27310,7 +27310,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.685037612915</v>
+        <v>21.6850357055664</v>
       </c>
       <c r="H929" t="n">
         <v>97800</v>
@@ -27339,7 +27339,7 @@
         <v>28.0674629211426</v>
       </c>
       <c r="G930" t="n">
-        <v>21.7011489868164</v>
+        <v>21.701150894165</v>
       </c>
       <c r="H930" t="n">
         <v>138426</v>
@@ -27368,7 +27368,7 @@
         <v>31.7556133270264</v>
       </c>
       <c r="G931" t="n">
-        <v>24.5527477264404</v>
+        <v>24.5527458190918</v>
       </c>
       <c r="H931" t="n">
         <v>595323</v>
@@ -27455,7 +27455,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.5838356018066</v>
+        <v>25.583833694458</v>
       </c>
       <c r="H934" t="n">
         <v>517926</v>
@@ -27542,7 +27542,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516128540039</v>
+        <v>25.5516109466553</v>
       </c>
       <c r="H937" t="n">
         <v>279125</v>
@@ -27629,7 +27629,7 @@
         <v>33.4434127807617</v>
       </c>
       <c r="G940" t="n">
-        <v>25.8577156066895</v>
+        <v>25.8577175140381</v>
       </c>
       <c r="H940" t="n">
         <v>218952</v>
@@ -27774,7 +27774,7 @@
         <v>33.7976417541504</v>
       </c>
       <c r="G945" t="n">
-        <v>26.1315975189209</v>
+        <v>26.1315994262695</v>
       </c>
       <c r="H945" t="n">
         <v>97707</v>
@@ -27977,7 +27977,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G952" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H952" t="n">
         <v>91792</v>
@@ -28064,7 +28064,7 @@
         <v>30.3178596496582</v>
       </c>
       <c r="G955" t="n">
-        <v>23.4411087036133</v>
+        <v>23.4411067962646</v>
       </c>
       <c r="H955" t="n">
         <v>170866</v>
@@ -28122,7 +28122,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G957" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H957" t="n">
         <v>141695</v>
@@ -28151,7 +28151,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727592468262</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H958" t="n">
         <v>106089</v>
@@ -28238,7 +28238,7 @@
         <v>30.5887413024902</v>
       </c>
       <c r="G961" t="n">
-        <v>23.6505451202393</v>
+        <v>23.6505470275879</v>
       </c>
       <c r="H961" t="n">
         <v>140338</v>
@@ -28557,7 +28557,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G972" t="n">
-        <v>23.9244270324707</v>
+        <v>23.9244289398193</v>
       </c>
       <c r="H972" t="n">
         <v>39949</v>
@@ -28615,7 +28615,7 @@
         <v>30.5470676422119</v>
       </c>
       <c r="G974" t="n">
-        <v>23.6183261871338</v>
+        <v>23.6183242797852</v>
       </c>
       <c r="H974" t="n">
         <v>118306</v>
@@ -28644,7 +28644,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.312219619751</v>
+        <v>23.3122215270996</v>
       </c>
       <c r="H975" t="n">
         <v>121812</v>
@@ -28731,7 +28731,7 @@
         <v>31.2346897125244</v>
       </c>
       <c r="G978" t="n">
-        <v>24.1499786376953</v>
+        <v>24.1499805450439</v>
       </c>
       <c r="H978" t="n">
         <v>163262</v>
@@ -28876,7 +28876,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G983" t="n">
-        <v>23.9244270324707</v>
+        <v>23.9244289398193</v>
       </c>
       <c r="H983" t="n">
         <v>59846</v>
@@ -28963,7 +28963,7 @@
         <v>30.7971115112305</v>
       </c>
       <c r="G986" t="n">
-        <v>23.811653137207</v>
+        <v>23.8116550445557</v>
       </c>
       <c r="H986" t="n">
         <v>68207</v>
@@ -28992,7 +28992,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H987" t="n">
         <v>52930</v>
@@ -29021,7 +29021,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G988" t="n">
-        <v>23.9244270324707</v>
+        <v>23.9244289398193</v>
       </c>
       <c r="H988" t="n">
         <v>68067</v>
@@ -29108,7 +29108,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H991" t="n">
         <v>68666</v>
@@ -29195,7 +29195,7 @@
         <v>30.776273727417</v>
       </c>
       <c r="G994" t="n">
-        <v>23.7955436706543</v>
+        <v>23.7955417633057</v>
       </c>
       <c r="H994" t="n">
         <v>129866</v>
@@ -29224,7 +29224,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727592468262</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H995" t="n">
         <v>242944</v>
@@ -29282,7 +29282,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H997" t="n">
         <v>75104</v>
@@ -29311,7 +29311,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544490814209</v>
+        <v>23.0544509887695</v>
       </c>
       <c r="H998" t="n">
         <v>173291</v>
@@ -29427,7 +29427,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1002" t="n">
-        <v>22.6355686187744</v>
+        <v>22.635570526123</v>
       </c>
       <c r="H1002" t="n">
         <v>70616</v>
@@ -29485,7 +29485,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1004" t="n">
-        <v>23.086669921875</v>
+        <v>23.0866718292236</v>
       </c>
       <c r="H1004" t="n">
         <v>49988</v>
@@ -29601,7 +29601,7 @@
         <v>29.2968463897705</v>
       </c>
       <c r="G1008" t="n">
-        <v>22.651683807373</v>
+        <v>22.6516819000244</v>
       </c>
       <c r="H1008" t="n">
         <v>46369</v>
@@ -29920,7 +29920,7 @@
         <v>28.609224319458</v>
       </c>
       <c r="G1019" t="n">
-        <v>22.1200275421143</v>
+        <v>22.1200294494629</v>
       </c>
       <c r="H1019" t="n">
         <v>72155</v>
@@ -30007,7 +30007,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.7104473114014</v>
+        <v>27.71044921875</v>
       </c>
       <c r="H1022" t="n">
         <v>1331456</v>
@@ -30036,7 +30036,7 @@
         <v>33.9643363952637</v>
       </c>
       <c r="G1023" t="n">
-        <v>26.2604827880859</v>
+        <v>26.2604846954346</v>
       </c>
       <c r="H1023" t="n">
         <v>837731</v>
@@ -30297,7 +30297,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1032" t="n">
         <v>254966</v>
@@ -30326,7 +30326,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.627628326416</v>
+        <v>29.6276264190674</v>
       </c>
       <c r="H1033" t="n">
         <v>422202</v>
@@ -30413,7 +30413,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326614379883</v>
+        <v>28.0326633453369</v>
       </c>
       <c r="H1036" t="n">
         <v>264193</v>
@@ -30500,7 +30500,7 @@
         <v>37.2774238586426</v>
       </c>
       <c r="G1039" t="n">
-        <v>28.8220882415771</v>
+        <v>28.8220901489258</v>
       </c>
       <c r="H1039" t="n">
         <v>439132</v>
@@ -30587,7 +30587,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1042" t="n">
         <v>912645</v>
@@ -30616,7 +30616,7 @@
         <v>36.1105499267578</v>
       </c>
       <c r="G1043" t="n">
-        <v>27.9198875427246</v>
+        <v>27.919885635376</v>
       </c>
       <c r="H1043" t="n">
         <v>263584</v>
@@ -30645,7 +30645,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1044" t="n">
         <v>248431</v>
@@ -30732,7 +30732,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737560272217</v>
+        <v>28.7737579345703</v>
       </c>
       <c r="H1047" t="n">
         <v>145626</v>
@@ -30761,7 +30761,7 @@
         <v>37.5274696350098</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.0154209136963</v>
+        <v>29.0154190063477</v>
       </c>
       <c r="H1048" t="n">
         <v>161694</v>
@@ -30906,7 +30906,7 @@
         <v>37.7566757202148</v>
       </c>
       <c r="G1053" t="n">
-        <v>29.1926383972168</v>
+        <v>29.1926364898682</v>
       </c>
       <c r="H1053" t="n">
         <v>774052</v>
@@ -30935,7 +30935,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820613861084</v>
+        <v>29.982063293457</v>
       </c>
       <c r="H1054" t="n">
         <v>787822</v>
@@ -30964,7 +30964,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770225524902</v>
+        <v>31.5770244598389</v>
       </c>
       <c r="H1055" t="n">
         <v>622084</v>
@@ -30993,7 +30993,7 @@
         <v>39.3819618225098</v>
       </c>
       <c r="G1056" t="n">
-        <v>30.4492740631104</v>
+        <v>30.4492721557617</v>
       </c>
       <c r="H1056" t="n">
         <v>399174</v>
@@ -31080,7 +31080,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571472167969</v>
+        <v>26.3571491241455</v>
       </c>
       <c r="H1059" t="n">
         <v>364508</v>
@@ -31109,7 +31109,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610492706299</v>
+        <v>25.7610511779785</v>
       </c>
       <c r="H1060" t="n">
         <v>600964</v>
@@ -31167,7 +31167,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1062" t="n">
-        <v>23.0383396148682</v>
+        <v>23.0383377075195</v>
       </c>
       <c r="H1062" t="n">
         <v>516650</v>
@@ -31196,7 +31196,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.2995128631592</v>
+        <v>20.2995147705078</v>
       </c>
       <c r="H1063" t="n">
         <v>342146</v>
@@ -31225,7 +31225,7 @@
         <v>24.6085166931152</v>
       </c>
       <c r="G1064" t="n">
-        <v>19.0267696380615</v>
+        <v>19.0267677307129</v>
       </c>
       <c r="H1064" t="n">
         <v>440901</v>
@@ -31283,7 +31283,7 @@
         <v>20.8578548431396</v>
       </c>
       <c r="G1066" t="n">
-        <v>16.1268367767334</v>
+        <v>16.126838684082</v>
       </c>
       <c r="H1066" t="n">
         <v>607780</v>
@@ -31341,7 +31341,7 @@
         <v>21.0453872680664</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.2718353271484</v>
+        <v>16.2718334197998</v>
       </c>
       <c r="H1068" t="n">
         <v>439578</v>
@@ -31370,7 +31370,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1069" t="n">
-        <v>17.0773696899414</v>
+        <v>17.07737159729</v>
       </c>
       <c r="H1069" t="n">
         <v>307976</v>
@@ -31573,7 +31573,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1076" t="n">
         <v>255584</v>
@@ -31718,7 +31718,7 @@
         <v>23.6708507537842</v>
       </c>
       <c r="G1081" t="n">
-        <v>18.3017864227295</v>
+        <v>18.3017845153809</v>
       </c>
       <c r="H1081" t="n">
         <v>80116</v>
@@ -31747,7 +31747,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1082" t="n">
         <v>65084</v>
@@ -31805,7 +31805,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1084" t="n">
         <v>220735</v>
@@ -31863,7 +31863,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1086" t="n">
         <v>126056</v>
@@ -31950,7 +31950,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1089" t="n">
         <v>85682</v>
@@ -32037,7 +32037,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1092" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1092" t="n">
         <v>95086</v>
@@ -32298,7 +32298,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1101" t="n">
         <v>70876</v>
@@ -32733,7 +32733,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1116" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H1116" t="n">
         <v>88021</v>
@@ -32762,7 +32762,7 @@
         <v>22.8790454864502</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.6895771026611</v>
+        <v>17.6895790100098</v>
       </c>
       <c r="H1117" t="n">
         <v>312068</v>
@@ -32849,7 +32849,7 @@
         <v>27.8174171447754</v>
       </c>
       <c r="G1120" t="n">
-        <v>21.5078201293945</v>
+        <v>21.5078182220459</v>
       </c>
       <c r="H1120" t="n">
         <v>741547</v>
@@ -32936,7 +32936,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.6355686187744</v>
+        <v>22.635570526123</v>
       </c>
       <c r="H1123" t="n">
         <v>408833</v>
@@ -33023,7 +33023,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1126" t="n">
         <v>401649</v>
@@ -33081,7 +33081,7 @@
         <v>28.4633655548096</v>
       </c>
       <c r="G1128" t="n">
-        <v>22.0072536468506</v>
+        <v>22.007251739502</v>
       </c>
       <c r="H1128" t="n">
         <v>243052</v>
@@ -33139,7 +33139,7 @@
         <v>29.2134971618652</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.5872364044189</v>
+        <v>22.5872383117676</v>
       </c>
       <c r="H1130" t="n">
         <v>133679</v>
@@ -33168,7 +33168,7 @@
         <v>30.5470676422119</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.6183261871338</v>
+        <v>23.6183242797852</v>
       </c>
       <c r="H1131" t="n">
         <v>259143</v>
@@ -33197,7 +33197,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1132" t="n">
         <v>117120</v>
@@ -33371,7 +33371,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021476745605</v>
+        <v>26.5021457672119</v>
       </c>
       <c r="H1138" t="n">
         <v>299299</v>
@@ -33400,7 +33400,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.2293968200684</v>
+        <v>25.2293949127197</v>
       </c>
       <c r="H1139" t="n">
         <v>249320</v>
@@ -33429,7 +33429,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.03493309021</v>
+        <v>26.0349349975586</v>
       </c>
       <c r="H1140" t="n">
         <v>192736</v>
@@ -33458,7 +33458,7 @@
         <v>32.859977722168</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.4066181182861</v>
+        <v>25.4066162109375</v>
       </c>
       <c r="H1141" t="n">
         <v>424729</v>
@@ -33487,7 +33487,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460746765137</v>
+        <v>24.7460765838623</v>
       </c>
       <c r="H1142" t="n">
         <v>259051</v>
@@ -33574,7 +33574,7 @@
         <v>32.8808135986328</v>
       </c>
       <c r="G1145" t="n">
-        <v>25.4227256774902</v>
+        <v>25.4227275848389</v>
       </c>
       <c r="H1145" t="n">
         <v>211348</v>
@@ -33632,7 +33632,7 @@
         <v>31.5889186859131</v>
       </c>
       <c r="G1147" t="n">
-        <v>24.4238605499268</v>
+        <v>24.4238624572754</v>
       </c>
       <c r="H1147" t="n">
         <v>65647</v>
@@ -33748,7 +33748,7 @@
         <v>31.7764511108398</v>
       </c>
       <c r="G1151" t="n">
-        <v>24.5688571929932</v>
+        <v>24.5688591003418</v>
       </c>
       <c r="H1151" t="n">
         <v>53540</v>
@@ -34067,7 +34067,7 @@
         <v>33.4017372131348</v>
       </c>
       <c r="G1162" t="n">
-        <v>25.8254947662354</v>
+        <v>25.8254928588867</v>
       </c>
       <c r="H1162" t="n">
         <v>201608</v>
@@ -34415,7 +34415,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1174" t="n">
-        <v>23.0383396148682</v>
+        <v>23.0383377075195</v>
       </c>
       <c r="H1174" t="n">
         <v>198986</v>
@@ -34473,7 +34473,7 @@
         <v>28.88010597229</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.3294677734375</v>
+        <v>22.3294658660889</v>
       </c>
       <c r="H1176" t="n">
         <v>108064</v>
@@ -34531,7 +34531,7 @@
         <v>30.2970237731934</v>
       </c>
       <c r="G1178" t="n">
-        <v>23.4249954223633</v>
+        <v>23.4249973297119</v>
       </c>
       <c r="H1178" t="n">
         <v>90363</v>
@@ -34647,7 +34647,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.23166847229</v>
+        <v>23.2316703796387</v>
       </c>
       <c r="H1182" t="n">
         <v>79634</v>
@@ -34676,7 +34676,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.086669921875</v>
+        <v>23.0866718292236</v>
       </c>
       <c r="H1183" t="n">
         <v>53322</v>
@@ -34705,7 +34705,7 @@
         <v>30.6720886230469</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.7149906158447</v>
+        <v>23.7149887084961</v>
       </c>
       <c r="H1184" t="n">
         <v>210874</v>
@@ -34734,7 +34734,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.086669921875</v>
+        <v>23.0866718292236</v>
       </c>
       <c r="H1185" t="n">
         <v>108022</v>
@@ -34763,7 +34763,7 @@
         <v>29.9011192321777</v>
       </c>
       <c r="G1186" t="n">
-        <v>23.1188926696777</v>
+        <v>23.1188907623291</v>
       </c>
       <c r="H1186" t="n">
         <v>142772</v>
@@ -34792,7 +34792,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1187" t="n">
-        <v>23.0383396148682</v>
+        <v>23.0383377075195</v>
       </c>
       <c r="H1187" t="n">
         <v>68126</v>
@@ -34879,7 +34879,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094524383545</v>
+        <v>22.9094543457031</v>
       </c>
       <c r="H1190" t="n">
         <v>71944</v>
@@ -34937,7 +34937,7 @@
         <v>29.4010314941406</v>
       </c>
       <c r="G1192" t="n">
-        <v>22.732234954834</v>
+        <v>22.7322368621826</v>
       </c>
       <c r="H1192" t="n">
         <v>80247</v>
@@ -34995,7 +34995,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416732788086</v>
+        <v>22.94167137146</v>
       </c>
       <c r="H1194" t="n">
         <v>35197</v>
@@ -35140,7 +35140,7 @@
         <v>28.0049514770508</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.6528186798096</v>
+        <v>21.6528167724609</v>
       </c>
       <c r="H1199" t="n">
         <v>87498</v>
@@ -35430,7 +35430,7 @@
         <v>28.2758312225342</v>
       </c>
       <c r="G1209" t="n">
-        <v>21.8622531890869</v>
+        <v>21.8622550964355</v>
       </c>
       <c r="H1209" t="n">
         <v>84042</v>
@@ -35459,7 +35459,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039180755615</v>
+        <v>22.1039161682129</v>
       </c>
       <c r="H1210" t="n">
         <v>66037</v>
@@ -35488,7 +35488,7 @@
         <v>28.9842910766602</v>
       </c>
       <c r="G1211" t="n">
-        <v>22.4100189208984</v>
+        <v>22.4100208282471</v>
       </c>
       <c r="H1211" t="n">
         <v>95686</v>
@@ -35517,7 +35517,7 @@
         <v>27.7757434844971</v>
       </c>
       <c r="G1212" t="n">
-        <v>21.4755973815918</v>
+        <v>21.4755992889404</v>
       </c>
       <c r="H1212" t="n">
         <v>157370</v>
@@ -35633,7 +35633,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1216" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H1216" t="n">
         <v>408334</v>
@@ -35720,7 +35720,7 @@
         <v>24.2334518432617</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.7367744445801</v>
+        <v>18.7367763519287</v>
       </c>
       <c r="H1219" t="n">
         <v>241385</v>
@@ -35807,7 +35807,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784355163574</v>
       </c>
       <c r="H1222" t="n">
         <v>166257</v>
@@ -35836,7 +35836,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1223" t="n">
         <v>87232</v>
@@ -35894,7 +35894,7 @@
         <v>23.3791332244873</v>
       </c>
       <c r="G1225" t="n">
-        <v>18.0762348175049</v>
+        <v>18.0762367248535</v>
       </c>
       <c r="H1225" t="n">
         <v>105717</v>
@@ -36126,7 +36126,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1233" t="n">
         <v>394163</v>
@@ -36213,7 +36213,7 @@
         <v>23.6500148773193</v>
       </c>
       <c r="G1236" t="n">
-        <v>18.2856750488281</v>
+        <v>18.2856731414795</v>
       </c>
       <c r="H1236" t="n">
         <v>245630</v>
@@ -36387,7 +36387,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1242" t="n">
         <v>245897</v>
@@ -36416,7 +36416,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1243" t="n">
         <v>239601</v>
@@ -36503,7 +36503,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G1246" t="n">
-        <v>20.1706314086914</v>
+        <v>20.1706295013428</v>
       </c>
       <c r="H1246" t="n">
         <v>327050</v>
@@ -36532,7 +36532,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G1247" t="n">
-        <v>19.3328704833984</v>
+        <v>19.3328723907471</v>
       </c>
       <c r="H1247" t="n">
         <v>451275</v>
@@ -36561,7 +36561,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1248" t="n">
         <v>312209</v>
@@ -36648,7 +36648,7 @@
         <v>25.1086044311523</v>
       </c>
       <c r="G1251" t="n">
-        <v>19.413423538208</v>
+        <v>19.4134254455566</v>
       </c>
       <c r="H1251" t="n">
         <v>488244</v>
@@ -36967,7 +36967,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1262" t="n">
         <v>79845</v>
@@ -37083,7 +37083,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1266" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H1266" t="n">
         <v>116876</v>
@@ -37112,7 +37112,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1267" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H1267" t="n">
         <v>88925</v>
@@ -37315,7 +37315,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1274" t="n">
         <v>234349</v>
@@ -37576,7 +37576,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1283" t="n">
         <v>188315</v>
@@ -37605,7 +37605,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1284" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1284" t="n">
         <v>99256</v>
@@ -37692,7 +37692,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1287" t="n">
-        <v>17.1901473999023</v>
+        <v>17.1901454925537</v>
       </c>
       <c r="H1287" t="n">
         <v>74707</v>
@@ -37721,7 +37721,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934810638428</v>
+        <v>17.0934791564941</v>
       </c>
       <c r="H1288" t="n">
         <v>71228</v>
@@ -37750,7 +37750,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1289" t="n">
-        <v>17.0773696899414</v>
+        <v>17.07737159729</v>
       </c>
       <c r="H1289" t="n">
         <v>72279</v>
@@ -37779,7 +37779,7 @@
         <v>21.5038013458252</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.6262683868408</v>
+        <v>16.6262702941895</v>
       </c>
       <c r="H1290" t="n">
         <v>126746</v>
@@ -37895,7 +37895,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1294" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1294" t="n">
         <v>170814</v>
@@ -38011,7 +38011,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H1298" t="n">
         <v>910482</v>
@@ -38098,7 +38098,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.5895099639893</v>
+        <v>20.5895080566406</v>
       </c>
       <c r="H1301" t="n">
         <v>361172</v>
@@ -38156,7 +38156,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.5895099639893</v>
+        <v>20.5895080566406</v>
       </c>
       <c r="H1303" t="n">
         <v>234506</v>
@@ -38185,7 +38185,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H1304" t="n">
         <v>141753</v>
@@ -38446,7 +38446,7 @@
         <v>25.1086044311523</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.413423538208</v>
+        <v>19.4134254455566</v>
       </c>
       <c r="H1313" t="n">
         <v>127568</v>
@@ -38533,7 +38533,7 @@
         <v>25.504508972168</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.7195301055908</v>
+        <v>19.7195281982422</v>
       </c>
       <c r="H1316" t="n">
         <v>192020</v>
@@ -38620,7 +38620,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1319" t="n">
         <v>101081</v>
@@ -38649,7 +38649,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784355163574</v>
       </c>
       <c r="H1320" t="n">
         <v>181732</v>
@@ -38678,7 +38678,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784355163574</v>
       </c>
       <c r="H1321" t="n">
         <v>147765</v>
@@ -38707,7 +38707,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395435333252</v>
+        <v>19.1395416259766</v>
       </c>
       <c r="H1322" t="n">
         <v>105576</v>
@@ -38736,7 +38736,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750999450684</v>
+        <v>19.075101852417</v>
       </c>
       <c r="H1323" t="n">
         <v>120557</v>
@@ -38794,7 +38794,7 @@
         <v>24.4834957122803</v>
       </c>
       <c r="G1325" t="n">
-        <v>18.9301052093506</v>
+        <v>18.930103302002</v>
       </c>
       <c r="H1325" t="n">
         <v>183528</v>
@@ -38823,7 +38823,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1326" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784355163574</v>
       </c>
       <c r="H1326" t="n">
         <v>76196</v>
@@ -38852,7 +38852,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1327" t="n">
         <v>104855</v>
@@ -38910,7 +38910,7 @@
         <v>24.0250816345215</v>
       </c>
       <c r="G1329" t="n">
-        <v>18.5756683349609</v>
+        <v>18.5756702423096</v>
       </c>
       <c r="H1329" t="n">
         <v>59340</v>
@@ -39084,7 +39084,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153793334961</v>
+        <v>19.1153774261475</v>
       </c>
       <c r="H1335" t="n">
         <v>175794</v>
@@ -39113,7 +39113,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.833438873291</v>
+        <v>18.8334407806396</v>
       </c>
       <c r="H1336" t="n">
         <v>97937</v>
@@ -39142,7 +39142,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353889465332</v>
+        <v>18.5353908538818</v>
       </c>
       <c r="H1337" t="n">
         <v>143301</v>
@@ -39171,7 +39171,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1338" t="n">
-        <v>18.4870567321777</v>
+        <v>18.4870586395264</v>
       </c>
       <c r="H1338" t="n">
         <v>70075</v>
@@ -39200,7 +39200,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1339" t="n">
         <v>83809</v>
@@ -39258,7 +39258,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.3328704833984</v>
+        <v>19.3328723907471</v>
       </c>
       <c r="H1341" t="n">
         <v>461267</v>
@@ -39316,7 +39316,7 @@
         <v>24.4418201446533</v>
       </c>
       <c r="G1343" t="n">
-        <v>18.8978805541992</v>
+        <v>18.8978824615479</v>
       </c>
       <c r="H1343" t="n">
         <v>117770</v>
@@ -39345,7 +39345,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864902496338</v>
+        <v>18.9864921569824</v>
       </c>
       <c r="H1344" t="n">
         <v>82258</v>
@@ -39403,7 +39403,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112228393555</v>
+        <v>18.5112247467041</v>
       </c>
       <c r="H1346" t="n">
         <v>91238</v>
@@ -39577,7 +39577,7 @@
         <v>23.5875034332275</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.237340927124</v>
+        <v>18.2373428344727</v>
       </c>
       <c r="H1352" t="n">
         <v>119737</v>
@@ -39693,7 +39693,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187129974365</v>
+        <v>19.0187110900879</v>
       </c>
       <c r="H1356" t="n">
         <v>228828</v>
@@ -39838,7 +39838,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1361" t="n">
         <v>157303</v>
@@ -39954,7 +39954,7 @@
         <v>26.4525928497314</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.4525680541992</v>
+        <v>20.4525661468506</v>
       </c>
       <c r="H1365" t="n">
         <v>970320</v>
@@ -39983,7 +39983,7 @@
         <v>25.4628353118896</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.6873073577881</v>
+        <v>19.6873092651367</v>
       </c>
       <c r="H1366" t="n">
         <v>576263</v>
@@ -40012,7 +40012,7 @@
         <v>25.3169765472412</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.5745334625244</v>
+        <v>19.5745315551758</v>
       </c>
       <c r="H1367" t="n">
         <v>278725</v>
@@ -40041,7 +40041,7 @@
         <v>25.2127914428711</v>
       </c>
       <c r="G1368" t="n">
-        <v>19.4939804077148</v>
+        <v>19.4939785003662</v>
       </c>
       <c r="H1368" t="n">
         <v>211758</v>
@@ -40128,7 +40128,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1371" t="n">
         <v>230606</v>
@@ -40157,7 +40157,7 @@
         <v>25.0148391723633</v>
       </c>
       <c r="G1372" t="n">
-        <v>19.3409290313721</v>
+        <v>19.3409271240234</v>
       </c>
       <c r="H1372" t="n">
         <v>175588</v>
@@ -40244,7 +40244,7 @@
         <v>25.6295318603516</v>
       </c>
       <c r="G1375" t="n">
-        <v>19.8161945343018</v>
+        <v>19.8161926269531</v>
       </c>
       <c r="H1375" t="n">
         <v>312050</v>
@@ -40302,7 +40302,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531364440918</v>
+        <v>19.9531345367432</v>
       </c>
       <c r="H1377" t="n">
         <v>173483</v>
@@ -40331,7 +40331,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G1378" t="n">
-        <v>20.2109050750732</v>
+        <v>20.2109069824219</v>
       </c>
       <c r="H1378" t="n">
         <v>358719</v>
@@ -40360,7 +40360,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397941589355</v>
+        <v>20.3397922515869</v>
       </c>
       <c r="H1379" t="n">
         <v>314666</v>
@@ -40389,7 +40389,7 @@
         <v>26.2858963012695</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.3236789703369</v>
+        <v>20.3236808776855</v>
       </c>
       <c r="H1380" t="n">
         <v>657639</v>
@@ -40592,7 +40592,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G1387" t="n">
-        <v>19.187873840332</v>
+        <v>19.1878757476807</v>
       </c>
       <c r="H1387" t="n">
         <v>247944</v>
@@ -40650,7 +40650,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187129974365</v>
+        <v>19.0187110900879</v>
       </c>
       <c r="H1389" t="n">
         <v>201477</v>
@@ -40737,7 +40737,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1392" t="n">
         <v>83268</v>
@@ -40795,7 +40795,7 @@
         <v>24.2021942138672</v>
       </c>
       <c r="G1394" t="n">
-        <v>18.7126064300537</v>
+        <v>18.7126083374023</v>
       </c>
       <c r="H1394" t="n">
         <v>201948</v>
@@ -40940,7 +40940,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1399" t="n">
-        <v>18.4870567321777</v>
+        <v>18.4870586395264</v>
       </c>
       <c r="H1399" t="n">
         <v>189206</v>
@@ -41201,7 +41201,7 @@
         <v>22.6602554321289</v>
       </c>
       <c r="G1408" t="n">
-        <v>17.520414352417</v>
+        <v>17.5204162597656</v>
       </c>
       <c r="H1408" t="n">
         <v>224491</v>
@@ -41317,7 +41317,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1412" t="n">
         <v>692896</v>
@@ -41346,7 +41346,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1413" t="n">
         <v>387357</v>
@@ -41375,7 +41375,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1414" t="n">
         <v>234798</v>
@@ -41404,7 +41404,7 @@
         <v>23.5562477111816</v>
       </c>
       <c r="G1415" t="n">
-        <v>18.2131748199463</v>
+        <v>18.2131767272949</v>
       </c>
       <c r="H1415" t="n">
         <v>138909</v>
@@ -41578,7 +41578,7 @@
         <v>23.6500148773193</v>
       </c>
       <c r="G1421" t="n">
-        <v>18.2856750488281</v>
+        <v>18.2856731414795</v>
       </c>
       <c r="H1421" t="n">
         <v>152809</v>
@@ -41694,7 +41694,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1425" t="n">
         <v>269832</v>
@@ -41752,7 +41752,7 @@
         <v>24.2230319976807</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.7287216186523</v>
+        <v>18.7287197113037</v>
       </c>
       <c r="H1427" t="n">
         <v>215889</v>
@@ -41781,7 +41781,7 @@
         <v>24.1917762756348</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.704553604126</v>
+        <v>18.7045516967773</v>
       </c>
       <c r="H1428" t="n">
         <v>192377</v>
@@ -41897,7 +41897,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292881011963</v>
+        <v>18.2292861938477</v>
       </c>
       <c r="H1432" t="n">
         <v>168351</v>
@@ -42071,7 +42071,7 @@
         <v>23.2853660583496</v>
       </c>
       <c r="G1438" t="n">
-        <v>18.0037384033203</v>
+        <v>18.0037364959717</v>
       </c>
       <c r="H1438" t="n">
         <v>138869</v>
@@ -42100,7 +42100,7 @@
         <v>23.3895511627197</v>
       </c>
       <c r="G1439" t="n">
-        <v>18.0842914581299</v>
+        <v>18.0842895507812</v>
       </c>
       <c r="H1439" t="n">
         <v>177402</v>
@@ -42158,7 +42158,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1441" t="n">
         <v>161224</v>
@@ -42187,7 +42187,7 @@
         <v>23.3895511627197</v>
       </c>
       <c r="G1442" t="n">
-        <v>18.0842914581299</v>
+        <v>18.0842895507812</v>
       </c>
       <c r="H1442" t="n">
         <v>315746</v>
@@ -42274,7 +42274,7 @@
         <v>23.160343170166</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.9070720672607</v>
+        <v>17.9070701599121</v>
       </c>
       <c r="H1445" t="n">
         <v>118808</v>
@@ -42332,7 +42332,7 @@
         <v>23.3166217803955</v>
       </c>
       <c r="G1447" t="n">
-        <v>18.027904510498</v>
+        <v>18.0279026031494</v>
       </c>
       <c r="H1447" t="n">
         <v>122725</v>
@@ -42361,7 +42361,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392929077148</v>
+        <v>17.9392948150635</v>
       </c>
       <c r="H1448" t="n">
         <v>194792</v>
@@ -42506,7 +42506,7 @@
         <v>22.899881362915</v>
       </c>
       <c r="G1453" t="n">
-        <v>17.7056884765625</v>
+        <v>17.7056865692139</v>
       </c>
       <c r="H1453" t="n">
         <v>292793</v>
@@ -42564,7 +42564,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1455" t="n">
-        <v>17.0773696899414</v>
+        <v>17.07737159729</v>
       </c>
       <c r="H1455" t="n">
         <v>103335</v>
@@ -42593,7 +42593,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1456" t="n">
-        <v>17.1901473999023</v>
+        <v>17.1901454925537</v>
       </c>
       <c r="H1456" t="n">
         <v>147195</v>
@@ -42622,7 +42622,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1457" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1457" t="n">
         <v>107698</v>
@@ -42709,7 +42709,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1460" t="n">
         <v>158955</v>
@@ -42767,7 +42767,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1462" t="n">
         <v>81655</v>
@@ -42825,7 +42825,7 @@
         <v>22.6706733703613</v>
       </c>
       <c r="G1464" t="n">
-        <v>17.528470993042</v>
+        <v>17.5284690856934</v>
       </c>
       <c r="H1464" t="n">
         <v>280896</v>
@@ -43028,7 +43028,7 @@
         <v>22.899881362915</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.7056884765625</v>
+        <v>17.7056865692139</v>
       </c>
       <c r="H1471" t="n">
         <v>144340</v>
@@ -43202,7 +43202,7 @@
         <v>22.6602554321289</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.520414352417</v>
+        <v>17.5204162597656</v>
       </c>
       <c r="H1477" t="n">
         <v>102803</v>
@@ -43463,7 +43463,7 @@
         <v>21.0766429901123</v>
       </c>
       <c r="G1486" t="n">
-        <v>16.2960014343262</v>
+        <v>16.2959995269775</v>
       </c>
       <c r="H1486" t="n">
         <v>123202</v>
@@ -43608,7 +43608,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765525817871</v>
+        <v>16.3765544891357</v>
       </c>
       <c r="H1491" t="n">
         <v>136046</v>
@@ -43811,7 +43811,7 @@
         <v>19.3367519378662</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.9507551193237</v>
+        <v>14.9507541656494</v>
       </c>
       <c r="H1498" t="n">
         <v>306456</v>
@@ -43840,7 +43840,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668645858765</v>
+        <v>14.9668655395508</v>
       </c>
       <c r="H1499" t="n">
         <v>131664</v>
@@ -43898,7 +43898,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867658615112</v>
+        <v>14.4867668151855</v>
       </c>
       <c r="H1501" t="n">
         <v>287038</v>
@@ -43956,7 +43956,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780061721802</v>
+        <v>13.6780071258545</v>
       </c>
       <c r="H1503" t="n">
         <v>269832</v>
@@ -44014,7 +44014,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013580322266</v>
+        <v>13.0013570785522</v>
       </c>
       <c r="H1505" t="n">
         <v>156575</v>
@@ -44043,7 +44043,7 @@
         <v>19.6284694671631</v>
       </c>
       <c r="G1506" t="n">
-        <v>15.1763038635254</v>
+        <v>15.1763048171997</v>
       </c>
       <c r="H1506" t="n">
         <v>979944</v>
@@ -44072,7 +44072,7 @@
         <v>19.0783729553223</v>
       </c>
       <c r="G1507" t="n">
-        <v>14.7509813308716</v>
+        <v>14.7509803771973</v>
       </c>
       <c r="H1507" t="n">
         <v>512576</v>
@@ -44130,7 +44130,7 @@
         <v>18.690803527832</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.4513216018677</v>
+        <v>14.4513206481934</v>
       </c>
       <c r="H1509" t="n">
         <v>189210</v>
@@ -44217,7 +44217,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379802703857</v>
+        <v>14.8379793167114</v>
       </c>
       <c r="H1512" t="n">
         <v>518691</v>
@@ -44246,7 +44246,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157661437988</v>
+        <v>14.5157651901245</v>
       </c>
       <c r="H1513" t="n">
         <v>165517</v>
@@ -44275,7 +44275,7 @@
         <v>18.8908386230469</v>
       </c>
       <c r="G1514" t="n">
-        <v>14.6059837341309</v>
+        <v>14.6059827804565</v>
       </c>
       <c r="H1514" t="n">
         <v>149007</v>
@@ -44333,7 +44333,7 @@
         <v>19.1658878326416</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8186454772949</v>
+        <v>14.8186445236206</v>
       </c>
       <c r="H1516" t="n">
         <v>177163</v>
@@ -44420,7 +44420,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157661437988</v>
+        <v>14.5157651901245</v>
       </c>
       <c r="H1519" t="n">
         <v>157517</v>
@@ -44478,7 +44478,7 @@
         <v>19.1575527191162</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.8122005462646</v>
+        <v>14.812201499939</v>
       </c>
       <c r="H1521" t="n">
         <v>111135</v>
@@ -44507,7 +44507,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189867019653</v>
+        <v>14.5189876556396</v>
       </c>
       <c r="H1522" t="n">
         <v>83491</v>
@@ -44594,7 +44594,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287662506104</v>
+        <v>14.428765296936</v>
       </c>
       <c r="H1525" t="n">
         <v>203931</v>
@@ -44652,7 +44652,7 @@
         <v>18.9200115203857</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.6285409927368</v>
+        <v>14.6285400390625</v>
       </c>
       <c r="H1527" t="n">
         <v>97123</v>
@@ -44681,7 +44681,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958648681641</v>
+        <v>14.9958639144897</v>
       </c>
       <c r="H1528" t="n">
         <v>508333</v>
@@ -44826,7 +44826,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024219512939</v>
       </c>
       <c r="H1533" t="n">
         <v>79836</v>
@@ -44884,7 +44884,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316474914551</v>
+        <v>14.7316484451294</v>
       </c>
       <c r="H1535" t="n">
         <v>124218</v>
@@ -45029,7 +45029,7 @@
         <v>18.9241790771484</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.6317615509033</v>
+        <v>14.6317625045776</v>
       </c>
       <c r="H1540" t="n">
         <v>58627</v>
@@ -45087,7 +45087,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1542" t="n">
-        <v>14.0002212524414</v>
+        <v>14.0002222061157</v>
       </c>
       <c r="H1542" t="n">
         <v>149427</v>
@@ -45145,7 +45145,7 @@
         <v>18.5241088867188</v>
       </c>
       <c r="G1544" t="n">
-        <v>14.3224353790283</v>
+        <v>14.3224363327026</v>
       </c>
       <c r="H1544" t="n">
         <v>44397</v>
@@ -45261,7 +45261,7 @@
         <v>19.1950607299805</v>
       </c>
       <c r="G1548" t="n">
-        <v>14.8412008285522</v>
+        <v>14.8412017822266</v>
       </c>
       <c r="H1548" t="n">
         <v>148931</v>
@@ -45319,7 +45319,7 @@
         <v>19.7618274688721</v>
       </c>
       <c r="G1550" t="n">
-        <v>15.2794122695923</v>
+        <v>15.2794132232666</v>
       </c>
       <c r="H1550" t="n">
         <v>232939</v>
@@ -45348,7 +45348,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024219512939</v>
       </c>
       <c r="H1551" t="n">
         <v>264963</v>
@@ -45377,7 +45377,7 @@
         <v>19.3784255981445</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.9829759597778</v>
+        <v>14.9829750061035</v>
       </c>
       <c r="H1552" t="n">
         <v>194072</v>
@@ -45406,7 +45406,7 @@
         <v>20.6703205108643</v>
       </c>
       <c r="G1553" t="n">
-        <v>15.9818410873413</v>
+        <v>15.981840133667</v>
       </c>
       <c r="H1553" t="n">
         <v>660001</v>
@@ -45435,7 +45435,7 @@
         <v>20.0243721008301</v>
       </c>
       <c r="G1554" t="n">
-        <v>15.4824075698853</v>
+        <v>15.4824066162109</v>
       </c>
       <c r="H1554" t="n">
         <v>487112</v>
@@ -45580,7 +45580,7 @@
         <v>20.6244792938232</v>
       </c>
       <c r="G1559" t="n">
-        <v>15.9463987350464</v>
+        <v>15.9463977813721</v>
       </c>
       <c r="H1559" t="n">
         <v>435045</v>
@@ -45696,7 +45696,7 @@
         <v>19.0366992950439</v>
       </c>
       <c r="G1563" t="n">
-        <v>14.7187604904175</v>
+        <v>14.7187595367432</v>
       </c>
       <c r="H1563" t="n">
         <v>364625</v>
@@ -45725,7 +45725,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157661437988</v>
+        <v>14.5157651901245</v>
       </c>
       <c r="H1564" t="n">
         <v>315453</v>
@@ -45754,7 +45754,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.3654584884644</v>
+        <v>13.36545753479</v>
       </c>
       <c r="H1565" t="n">
         <v>596953</v>
@@ -45870,7 +45870,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781192779541</v>
+        <v>13.5781202316284</v>
       </c>
       <c r="H1569" t="n">
         <v>306814</v>
@@ -46131,7 +46131,7 @@
         <v>19.7534923553467</v>
       </c>
       <c r="G1578" t="n">
-        <v>15.2729682922363</v>
+        <v>15.272967338562</v>
       </c>
       <c r="H1578" t="n">
         <v>326853</v>
@@ -46160,7 +46160,7 @@
         <v>20.2119064331055</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.6274042129517</v>
+        <v>15.627405166626</v>
       </c>
       <c r="H1579" t="n">
         <v>454220</v>
@@ -46421,7 +46421,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8303995132446</v>
+        <v>15.8304004669189</v>
       </c>
       <c r="H1588" t="n">
         <v>187148</v>
@@ -46508,7 +46508,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199169158936</v>
+        <v>15.1199178695679</v>
       </c>
       <c r="H1591" t="n">
         <v>163415</v>
@@ -46595,7 +46595,7 @@
         <v>18.024019241333</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.9357767105103</v>
+        <v>13.9357776641846</v>
       </c>
       <c r="H1594" t="n">
         <v>185388</v>
@@ -46624,7 +46624,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.0002212524414</v>
+        <v>14.0002222061157</v>
       </c>
       <c r="H1595" t="n">
         <v>171574</v>
@@ -46682,7 +46682,7 @@
         <v>18.1177864074707</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0082778930664</v>
+        <v>14.0082769393921</v>
       </c>
       <c r="H1597" t="n">
         <v>193042</v>
@@ -46711,7 +46711,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585601806641</v>
+        <v>13.7585592269897</v>
       </c>
       <c r="H1598" t="n">
         <v>171526</v>
@@ -46798,7 +46798,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780061721802</v>
+        <v>13.6780071258545</v>
       </c>
       <c r="H1601" t="n">
         <v>280445</v>
@@ -47001,7 +47001,7 @@
         <v>16.9821681976318</v>
       </c>
       <c r="G1608" t="n">
-        <v>13.130241394043</v>
+        <v>13.1302423477173</v>
       </c>
       <c r="H1608" t="n">
         <v>500248</v>
@@ -47030,7 +47030,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1609" t="n">
-        <v>12.9691352844238</v>
+        <v>12.9691362380981</v>
       </c>
       <c r="H1609" t="n">
         <v>243613</v>
@@ -47059,7 +47059,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1610" t="n">
-        <v>12.9691352844238</v>
+        <v>12.9691362380981</v>
       </c>
       <c r="H1610" t="n">
         <v>466473</v>
@@ -47204,7 +47204,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519590377808</v>
+        <v>11.0519580841064</v>
       </c>
       <c r="H1615" t="n">
         <v>230061</v>
@@ -47291,7 +47291,7 @@
         <v>14.7942819595337</v>
       </c>
       <c r="G1618" t="n">
-        <v>11.4386167526245</v>
+        <v>11.4386157989502</v>
       </c>
       <c r="H1618" t="n">
         <v>110697</v>
@@ -47320,7 +47320,7 @@
         <v>14.6484231948853</v>
       </c>
       <c r="G1619" t="n">
-        <v>11.3258419036865</v>
+        <v>11.3258409500122</v>
       </c>
       <c r="H1619" t="n">
         <v>113034</v>
@@ -47436,7 +47436,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433340072632</v>
+        <v>11.5433349609375</v>
       </c>
       <c r="H1623" t="n">
         <v>121159</v>
@@ -47465,7 +47465,7 @@
         <v>14.700514793396</v>
       </c>
       <c r="G1624" t="n">
-        <v>11.3661165237427</v>
+        <v>11.366117477417</v>
       </c>
       <c r="H1624" t="n">
         <v>91847</v>
@@ -47494,7 +47494,7 @@
         <v>15.0130710601807</v>
       </c>
       <c r="G1625" t="n">
-        <v>11.6077795028687</v>
+        <v>11.6077785491943</v>
       </c>
       <c r="H1625" t="n">
         <v>59931</v>
@@ -47552,7 +47552,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.9702701568604</v>
+        <v>11.970269203186</v>
       </c>
       <c r="H1627" t="n">
         <v>161789</v>
@@ -47755,7 +47755,7 @@
         <v>16.429988861084</v>
       </c>
       <c r="G1634" t="n">
-        <v>12.7033090591431</v>
+        <v>12.7033081054688</v>
       </c>
       <c r="H1634" t="n">
         <v>81533</v>
@@ -47784,7 +47784,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805246353149</v>
+        <v>12.8805255889893</v>
       </c>
       <c r="H1635" t="n">
         <v>140616</v>
@@ -48132,7 +48132,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439023971558</v>
+        <v>11.0439033508301</v>
       </c>
       <c r="H1647" t="n">
         <v>123714</v>
@@ -48161,7 +48161,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136335372925</v>
+        <v>10.7136325836182</v>
       </c>
       <c r="H1648" t="n">
         <v>160860</v>
@@ -48451,7 +48451,7 @@
         <v>10.010103225708</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.73959255218506</v>
+        <v>7.73959302902222</v>
       </c>
       <c r="H1658" t="n">
         <v>359843</v>
@@ -48509,7 +48509,7 @@
         <v>10.5331115722656</v>
       </c>
       <c r="G1660" t="n">
-        <v>8.14397144317627</v>
+        <v>8.14397239685059</v>
       </c>
       <c r="H1660" t="n">
         <v>318695</v>
@@ -48567,7 +48567,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392160415649</v>
+        <v>7.90392255783081</v>
       </c>
       <c r="H1662" t="n">
         <v>148424</v>
@@ -48799,7 +48799,7 @@
         <v>8.75571441650391</v>
       </c>
       <c r="G1670" t="n">
-        <v>6.76972723007202</v>
+        <v>6.76972770690918</v>
       </c>
       <c r="H1670" t="n">
         <v>178963</v>
@@ -48828,7 +48828,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795162200928</v>
+        <v>6.62795209884644</v>
       </c>
       <c r="H1671" t="n">
         <v>134394</v>
@@ -48886,7 +48886,7 @@
         <v>8.40981960296631</v>
       </c>
       <c r="G1673" t="n">
-        <v>6.50228881835938</v>
+        <v>6.50228929519653</v>
       </c>
       <c r="H1673" t="n">
         <v>175627</v>
@@ -48915,7 +48915,7 @@
         <v>8.62235736846924</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.66661834716797</v>
+        <v>6.66661882400513</v>
       </c>
       <c r="H1674" t="n">
         <v>247778</v>
@@ -48944,7 +48944,7 @@
         <v>8.99325561523438</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.95338916778564</v>
+        <v>6.95338869094849</v>
       </c>
       <c r="H1675" t="n">
         <v>183001</v>
@@ -49031,7 +49031,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927337646484</v>
+        <v>7.16927289962769</v>
       </c>
       <c r="H1678" t="n">
         <v>171846</v>
@@ -49176,7 +49176,7 @@
         <v>8.62235736846924</v>
       </c>
       <c r="G1683" t="n">
-        <v>6.66661834716797</v>
+        <v>6.66661882400513</v>
       </c>
       <c r="H1683" t="n">
         <v>289417</v>
@@ -49292,7 +49292,7 @@
         <v>8.46816253662109</v>
       </c>
       <c r="G1687" t="n">
-        <v>6.54739809036255</v>
+        <v>6.54739856719971</v>
       </c>
       <c r="H1687" t="n">
         <v>158208</v>
@@ -49321,7 +49321,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973394393921</v>
+        <v>6.47973346710205</v>
       </c>
       <c r="H1688" t="n">
         <v>211830</v>
@@ -49379,7 +49379,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107488632202</v>
+        <v>6.15107536315918</v>
       </c>
       <c r="H1690" t="n">
         <v>346128</v>
@@ -49524,7 +49524,7 @@
         <v>6.87204790115356</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.31331729888916</v>
+        <v>5.31331777572632</v>
       </c>
       <c r="H1695" t="n">
         <v>342058</v>
@@ -49553,7 +49553,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032152175903</v>
+        <v>5.11032199859619</v>
       </c>
       <c r="H1696" t="n">
         <v>868645</v>
@@ -49582,7 +49582,7 @@
         <v>6.32611799240112</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.89121627807617</v>
+        <v>4.89121675491333</v>
       </c>
       <c r="H1697" t="n">
         <v>323082</v>
@@ -49611,7 +49611,7 @@
         <v>6.63450622558594</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.12965536117554</v>
+        <v>5.12965488433838</v>
       </c>
       <c r="H1698" t="n">
         <v>358770</v>
@@ -49640,7 +49640,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799476623535</v>
+        <v>4.88799428939819</v>
       </c>
       <c r="H1699" t="n">
         <v>228803</v>
@@ -49756,7 +49756,7 @@
         <v>6.3677921295166</v>
       </c>
       <c r="G1703" t="n">
-        <v>4.92343807220459</v>
+        <v>4.92343759536743</v>
       </c>
       <c r="H1703" t="n">
         <v>613489</v>
@@ -49872,7 +49872,7 @@
         <v>7.65135192871094</v>
       </c>
       <c r="G1707" t="n">
-        <v>5.91585826873779</v>
+        <v>5.91585779190063</v>
       </c>
       <c r="H1707" t="n">
         <v>677853</v>
@@ -49901,7 +49901,7 @@
         <v>7.26378393173218</v>
       </c>
       <c r="G1708" t="n">
-        <v>5.61619901657104</v>
+        <v>5.6161994934082</v>
       </c>
       <c r="H1708" t="n">
         <v>487854</v>
@@ -49959,7 +49959,7 @@
         <v>6.27194213867188</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.84932899475098</v>
+        <v>4.84932851791382</v>
       </c>
       <c r="H1710" t="n">
         <v>660674</v>
@@ -50017,7 +50017,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555252075195</v>
+        <v>4.76555204391479</v>
       </c>
       <c r="H1712" t="n">
         <v>627926</v>
@@ -50220,7 +50220,7 @@
         <v>5.1717472076416</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.99868226051331</v>
+        <v>3.99868178367615</v>
       </c>
       <c r="H1719" t="n">
         <v>801083</v>
@@ -50249,7 +50249,7 @@
         <v>4.99671602249146</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.86335182189941</v>
+        <v>3.86335206031799</v>
       </c>
       <c r="H1720" t="n">
         <v>478249</v>
@@ -50307,7 +50307,7 @@
         <v>4.66853284835815</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.6096076965332</v>
+        <v>3.60960745811462</v>
       </c>
       <c r="H1722" t="n">
         <v>526169</v>
@@ -50394,7 +50394,7 @@
         <v>4.84252214431763</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.74413228034973</v>
+        <v>3.74413251876831</v>
       </c>
       <c r="H1725" t="n">
         <v>619872</v>
@@ -50481,7 +50481,7 @@
         <v>2.06286406517029</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.59496140480042</v>
+        <v>1.5949615240097</v>
       </c>
       <c r="H1728" t="n">
         <v>913518</v>
@@ -50684,7 +50684,7 @@
         <v>1.9831999540329</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.53336691856384</v>
+        <v>1.53336679935455</v>
       </c>
       <c r="H1735" t="n">
         <v>1128008</v>
@@ -50713,7 +50713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089272975922</v>
+        <v>1.53089284896851</v>
       </c>
       <c r="H1736" t="n">
         <v>1871837</v>
@@ -50858,7 +50858,7 @@
         <v>1.9456000328064</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.50429546833038</v>
+        <v>1.50429534912109</v>
       </c>
       <c r="H1741" t="n">
         <v>2596034</v>
@@ -50945,7 +50945,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.39945232868195</v>
+        <v>1.39945244789124</v>
       </c>
       <c r="H1744" t="n">
         <v>10215715</v>
@@ -51003,7 +51003,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1746" t="n">
         <v>4299825</v>
@@ -51032,7 +51032,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1747" t="n">
         <v>5687761</v>
@@ -51061,7 +51061,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1748" t="n">
         <v>7070109</v>
@@ -51090,7 +51090,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.38398885726929</v>
+        <v>1.38398897647858</v>
       </c>
       <c r="H1749" t="n">
         <v>7258460</v>
@@ -51177,7 +51177,7 @@
         <v>1.81239998340607</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.40130817890167</v>
+        <v>1.40130805969238</v>
       </c>
       <c r="H1752" t="n">
         <v>3775318</v>
@@ -51206,7 +51206,7 @@
         <v>1.81299996376038</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.40177202224731</v>
+        <v>1.40177190303802</v>
       </c>
       <c r="H1753" t="n">
         <v>5951051</v>
@@ -51235,7 +51235,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.39156603813171</v>
+        <v>1.391566157341</v>
       </c>
       <c r="H1754" t="n">
         <v>2641302</v>
@@ -51380,7 +51380,7 @@
         <v>1.80859994888306</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.39836990833282</v>
+        <v>1.39837002754211</v>
       </c>
       <c r="H1759" t="n">
         <v>3782624</v>
@@ -51467,7 +51467,7 @@
         <v>1.88960003852844</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.46099758148193</v>
+        <v>1.46099746227264</v>
       </c>
       <c r="H1762" t="n">
         <v>18263848</v>
@@ -51496,7 +51496,7 @@
         <v>1.88919997215271</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.46068811416626</v>
+        <v>1.46068823337555</v>
       </c>
       <c r="H1763" t="n">
         <v>3524769</v>
@@ -51554,7 +51554,7 @@
         <v>1.87360000610352</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.44862651824951</v>
+        <v>1.4486266374588</v>
       </c>
       <c r="H1765" t="n">
         <v>9888369</v>
@@ -51583,7 +51583,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537925720215</v>
+        <v>1.44537937641144</v>
       </c>
       <c r="H1766" t="n">
         <v>4191313</v>
@@ -51612,7 +51612,7 @@
         <v>1.80820000171661</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.39806079864502</v>
+        <v>1.39806067943573</v>
       </c>
       <c r="H1767" t="n">
         <v>5834324</v>
@@ -51641,7 +51641,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.409503698349</v>
+        <v>1.40950381755829</v>
       </c>
       <c r="H1768" t="n">
         <v>4615701</v>
@@ -51757,7 +51757,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.50383162498474</v>
+        <v>1.50383150577545</v>
       </c>
       <c r="H1772" t="n">
         <v>6992176</v>
@@ -51815,7 +51815,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.45125544071198</v>
+        <v>1.45125532150269</v>
       </c>
       <c r="H1774" t="n">
         <v>7152049</v>
@@ -51844,7 +51844,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903848648071</v>
+        <v>1.46903836727142</v>
       </c>
       <c r="H1775" t="n">
         <v>3814973</v>
@@ -51902,7 +51902,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.57689678668976</v>
+        <v>1.57689690589905</v>
       </c>
       <c r="H1777" t="n">
         <v>14755833</v>
@@ -52047,7 +52047,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.48805856704712</v>
+        <v>1.48805868625641</v>
       </c>
       <c r="H1782" t="n">
         <v>2159725</v>
@@ -52076,7 +52076,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.58501529693604</v>
+        <v>1.58501517772675</v>
       </c>
       <c r="H1783" t="n">
         <v>13921292</v>
@@ -52163,7 +52163,7 @@
         <v>1.98660004138947</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.53599584102631</v>
+        <v>1.53599572181702</v>
       </c>
       <c r="H1786" t="n">
         <v>9824828</v>
@@ -52366,7 +52366,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.65537440776825</v>
+        <v>1.65537452697754</v>
       </c>
       <c r="H1793" t="n">
         <v>21373665</v>
@@ -52395,7 +52395,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1794" t="n">
         <v>6601746</v>
@@ -52424,7 +52424,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.6031848192215</v>
+        <v>1.60318493843079</v>
       </c>
       <c r="H1795" t="n">
         <v>7563778</v>
@@ -52482,7 +52482,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.56800544261932</v>
+        <v>1.56800532341003</v>
       </c>
       <c r="H1797" t="n">
         <v>6304338</v>
@@ -52598,7 +52598,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.68475520610809</v>
+        <v>1.6847550868988</v>
       </c>
       <c r="H1801" t="n">
         <v>14097011</v>
@@ -52627,7 +52627,7 @@
         <v>2.18449997901917</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.68900775909424</v>
+        <v>1.68900763988495</v>
       </c>
       <c r="H1802" t="n">
         <v>7676085</v>
@@ -52685,7 +52685,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1804" t="n">
         <v>18740837</v>
@@ -52743,7 +52743,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.87186419963837</v>
+        <v>1.87186431884766</v>
       </c>
       <c r="H1806" t="n">
         <v>12148200</v>
@@ -52772,7 +52772,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482709884644</v>
+        <v>1.92482697963715</v>
       </c>
       <c r="H1807" t="n">
         <v>14549250</v>
@@ -52801,7 +52801,7 @@
         <v>2.37350010871887</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.83513844013214</v>
+        <v>1.83513855934143</v>
       </c>
       <c r="H1808" t="n">
         <v>19340207</v>
@@ -52859,7 +52859,7 @@
         <v>2.31550002098083</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.79029417037964</v>
+        <v>1.79029405117035</v>
       </c>
       <c r="H1810" t="n">
         <v>25899848</v>
@@ -52888,7 +52888,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.01026320457458</v>
+        <v>2.01026296615601</v>
       </c>
       <c r="H1811" t="n">
         <v>45207296</v>
@@ -53004,7 +53004,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552503585815</v>
+        <v>1.83552515506744</v>
       </c>
       <c r="H1815" t="n">
         <v>8871781</v>
@@ -53294,7 +53294,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.90665745735168</v>
+        <v>1.90665757656097</v>
       </c>
       <c r="H1825" t="n">
         <v>21554181</v>
@@ -53323,7 +53323,7 @@
         <v>2.39050006866455</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.8482825756073</v>
+        <v>1.84828245639801</v>
       </c>
       <c r="H1826" t="n">
         <v>13530053</v>
@@ -53381,7 +53381,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1828" t="n">
         <v>6331894</v>
@@ -53410,7 +53410,7 @@
         <v>2.36700010299683</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.83011269569397</v>
+        <v>1.83011281490326</v>
       </c>
       <c r="H1829" t="n">
         <v>7991760</v>
@@ -53584,7 +53584,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.48805856704712</v>
+        <v>1.48805868625641</v>
       </c>
       <c r="H1835" t="n">
         <v>21201799</v>
@@ -53642,7 +53642,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46208000183105</v>
+        <v>1.46207988262177</v>
       </c>
       <c r="H1837" t="n">
         <v>27810987</v>
@@ -53787,7 +53787,7 @@
         <v>1.88059997558594</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.4540388584137</v>
+        <v>1.45403873920441</v>
       </c>
       <c r="H1842" t="n">
         <v>11617888</v>
@@ -53816,7 +53816,7 @@
         <v>1.81420004367828</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.40269982814789</v>
+        <v>1.40269994735718</v>
       </c>
       <c r="H1843" t="n">
         <v>8718449</v>
@@ -53845,7 +53845,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.41646242141724</v>
+        <v>1.41646254062653</v>
       </c>
       <c r="H1844" t="n">
         <v>7614292</v>
@@ -54135,7 +54135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.58501529693604</v>
+        <v>1.58501517772675</v>
       </c>
       <c r="H1854" t="n">
         <v>4279847</v>
@@ -54222,7 +54222,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1857" t="n">
         <v>11220865</v>
@@ -54309,7 +54309,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666081905365</v>
+        <v>1.75666093826294</v>
       </c>
       <c r="H1860" t="n">
         <v>8508624</v>
@@ -54396,7 +54396,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1863" t="n">
         <v>7031365</v>
@@ -54425,7 +54425,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630158901215</v>
+        <v>1.68630146980286</v>
       </c>
       <c r="H1864" t="n">
         <v>5899256</v>
@@ -54454,7 +54454,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.61516928672791</v>
+        <v>1.61516916751862</v>
       </c>
       <c r="H1865" t="n">
         <v>6994580</v>
@@ -54657,7 +54657,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.60125207901001</v>
+        <v>1.60125195980072</v>
       </c>
       <c r="H1872" t="n">
         <v>6922251</v>
@@ -54686,7 +54686,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831330299377</v>
+        <v>1.62831318378448</v>
       </c>
       <c r="H1873" t="n">
         <v>6917707</v>
@@ -54773,7 +54773,7 @@
         <v>2.21300005912781</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.71104335784912</v>
+        <v>1.71104323863983</v>
       </c>
       <c r="H1876" t="n">
         <v>15770492</v>
@@ -54860,7 +54860,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.65537440776825</v>
+        <v>1.65537452697754</v>
       </c>
       <c r="H1879" t="n">
         <v>7813573</v>
@@ -54918,7 +54918,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.77444410324097</v>
+        <v>1.77444398403168</v>
       </c>
       <c r="H1881" t="n">
         <v>14803240</v>
@@ -54976,7 +54976,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1883" t="n">
         <v>10738852</v>
@@ -55063,7 +55063,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.60125207901001</v>
+        <v>1.60125195980072</v>
       </c>
       <c r="H1886" t="n">
         <v>6292235</v>
@@ -55092,7 +55092,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.62985968589783</v>
+        <v>1.62985956668854</v>
       </c>
       <c r="H1887" t="n">
         <v>15958032</v>
@@ -55121,7 +55121,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006480693817</v>
+        <v>1.67006492614746</v>
       </c>
       <c r="H1888" t="n">
         <v>9732271</v>
@@ -55179,7 +55179,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.75820708274841</v>
+        <v>1.7582072019577</v>
       </c>
       <c r="H1890" t="n">
         <v>16440004</v>
@@ -55237,7 +55237,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.86954474449158</v>
+        <v>1.86954462528229</v>
       </c>
       <c r="H1892" t="n">
         <v>29342749</v>
@@ -55266,7 +55266,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.88346219062805</v>
+        <v>1.88346207141876</v>
       </c>
       <c r="H1893" t="n">
         <v>15431172</v>
@@ -55295,7 +55295,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011617660522</v>
+        <v>1.68011629581451</v>
       </c>
       <c r="H1894" t="n">
         <v>28227461</v>
@@ -55382,7 +55382,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1897" t="n">
         <v>13177383</v>
@@ -55440,7 +55440,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.76748538017273</v>
+        <v>1.76748526096344</v>
       </c>
       <c r="H1899" t="n">
         <v>12029873</v>
@@ -55469,7 +55469,7 @@
         <v>2.32100009918213</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.79454660415649</v>
+        <v>1.79454672336578</v>
       </c>
       <c r="H1900" t="n">
         <v>9000879</v>
@@ -55527,7 +55527,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82701992988586</v>
+        <v>1.82701981067657</v>
       </c>
       <c r="H1902" t="n">
         <v>11298307</v>
@@ -55614,7 +55614,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645569801331</v>
+        <v>1.71645557880402</v>
       </c>
       <c r="H1905" t="n">
         <v>7081375</v>
@@ -55643,7 +55643,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.73578500747681</v>
+        <v>1.73578488826752</v>
       </c>
       <c r="H1906" t="n">
         <v>5356916</v>
@@ -55701,7 +55701,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.77367067337036</v>
+        <v>1.77367079257965</v>
       </c>
       <c r="H1908" t="n">
         <v>7446800</v>
@@ -55730,7 +55730,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.77985608577728</v>
+        <v>1.77985620498657</v>
       </c>
       <c r="H1909" t="n">
         <v>7154278</v>
@@ -55759,7 +55759,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387615203857</v>
       </c>
       <c r="H1910" t="n">
         <v>7777212</v>
@@ -55788,7 +55788,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.77444410324097</v>
+        <v>1.77444398403168</v>
       </c>
       <c r="H1911" t="n">
         <v>8748249</v>
@@ -55933,7 +55933,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387615203857</v>
       </c>
       <c r="H1916" t="n">
         <v>11063863</v>
@@ -56165,7 +56165,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382130146027</v>
+        <v>1.95382118225098</v>
       </c>
       <c r="H1924" t="n">
         <v>4430041</v>
@@ -56223,7 +56223,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918203353882</v>
+        <v>1.94918215274811</v>
       </c>
       <c r="H1926" t="n">
         <v>5834369</v>
@@ -56252,7 +56252,7 @@
         <v>2.61700010299683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.02340722084045</v>
+        <v>2.02340745925903</v>
       </c>
       <c r="H1927" t="n">
         <v>20029327</v>
@@ -56310,7 +56310,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562429428101</v>
+        <v>2.00562405586243</v>
       </c>
       <c r="H1929" t="n">
         <v>10963576</v>
@@ -56339,7 +56339,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959275245667</v>
+        <v>2.02959251403809</v>
       </c>
       <c r="H1930" t="n">
         <v>11993677</v>
@@ -56368,7 +56368,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.96077978610992</v>
+        <v>1.96077966690063</v>
       </c>
       <c r="H1931" t="n">
         <v>9783275</v>
@@ -56455,7 +56455,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1934" t="n">
-        <v>1.95691382884979</v>
+        <v>1.95691394805908</v>
       </c>
       <c r="H1934" t="n">
         <v>24640061</v>
@@ -56542,7 +56542,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.95691382884979</v>
+        <v>1.95691394805908</v>
       </c>
       <c r="H1937" t="n">
         <v>24480809</v>
@@ -56571,7 +56571,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G1938" t="n">
-        <v>1.97005796432495</v>
+        <v>1.97005784511566</v>
       </c>
       <c r="H1938" t="n">
         <v>9538925</v>
@@ -56629,7 +56629,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025996208191</v>
+        <v>2.16025972366333</v>
       </c>
       <c r="H1940" t="n">
         <v>21527670</v>
@@ -56745,7 +56745,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.03500485420227</v>
+        <v>2.03500509262085</v>
       </c>
       <c r="H1944" t="n">
         <v>9682287</v>
@@ -56919,7 +56919,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.99402642250061</v>
+        <v>1.9940265417099</v>
       </c>
       <c r="H1950" t="n">
         <v>6249034</v>
@@ -56948,7 +56948,7 @@
         <v>2.62899994850159</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.03268551826477</v>
+        <v>2.03268527984619</v>
       </c>
       <c r="H1951" t="n">
         <v>12173491</v>
@@ -56977,7 +56977,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.98088228702545</v>
+        <v>1.98088240623474</v>
       </c>
       <c r="H1952" t="n">
         <v>14258681</v>
@@ -57064,7 +57064,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.90511107444763</v>
+        <v>1.90511095523834</v>
       </c>
       <c r="H1955" t="n">
         <v>11937121</v>
@@ -57093,7 +57093,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.7976393699646</v>
+        <v>1.79763925075531</v>
       </c>
       <c r="H1956" t="n">
         <v>22749670</v>
@@ -57209,7 +57209,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310272216797</v>
+        <v>1.81310260295868</v>
       </c>
       <c r="H1960" t="n">
         <v>6445475</v>
@@ -57267,7 +57267,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.920574426651</v>
+        <v>1.92057454586029</v>
       </c>
       <c r="H1962" t="n">
         <v>17155594</v>
@@ -57296,7 +57296,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.92676019668579</v>
+        <v>1.92675995826721</v>
       </c>
       <c r="H1963" t="n">
         <v>13390725</v>
@@ -57470,7 +57470,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.06825160980225</v>
+        <v>2.06825137138367</v>
       </c>
       <c r="H1969" t="n">
         <v>23723962</v>
@@ -57528,7 +57528,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866905212402</v>
+        <v>1.84866893291473</v>
       </c>
       <c r="H1971" t="n">
         <v>32386618</v>
@@ -57557,7 +57557,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.8618129491806</v>
+        <v>1.86181282997131</v>
       </c>
       <c r="H1972" t="n">
         <v>18377109</v>
@@ -57586,7 +57586,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.86722528934479</v>
+        <v>1.8672251701355</v>
       </c>
       <c r="H1973" t="n">
         <v>10855064</v>
@@ -57615,7 +57615,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737927913666</v>
+        <v>1.89737915992737</v>
       </c>
       <c r="H1974" t="n">
         <v>15191141</v>
@@ -57644,7 +57644,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.91748189926147</v>
+        <v>1.91748178005219</v>
       </c>
       <c r="H1975" t="n">
         <v>17294006</v>
@@ -57673,7 +57673,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639724731445</v>
+        <v>2.00639748573303</v>
       </c>
       <c r="H1976" t="n">
         <v>29570216</v>
@@ -57702,7 +57702,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.96077978610992</v>
+        <v>1.96077966690063</v>
       </c>
       <c r="H1977" t="n">
         <v>19720359</v>
@@ -57876,7 +57876,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.94840896129608</v>
+        <v>1.94840884208679</v>
       </c>
       <c r="H1983" t="n">
         <v>25197954</v>
@@ -57905,7 +57905,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.95691382884979</v>
+        <v>1.95691394805908</v>
       </c>
       <c r="H1984" t="n">
         <v>32448765</v>
@@ -57934,7 +57934,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397517204285</v>
+        <v>1.98397505283356</v>
       </c>
       <c r="H1985" t="n">
         <v>20639388</v>
@@ -57963,7 +57963,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.95614075660706</v>
+        <v>1.95614087581635</v>
       </c>
       <c r="H1986" t="n">
         <v>18660240</v>
@@ -58021,7 +58021,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.83475172519684</v>
+        <v>1.83475184440613</v>
       </c>
       <c r="H1988" t="n">
         <v>16787583</v>
@@ -58079,7 +58079,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.85408139228821</v>
+        <v>1.85408127307892</v>
       </c>
       <c r="H1990" t="n">
         <v>14799249</v>
@@ -58166,7 +58166,7 @@
         <v>2.42899990081787</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.87804961204529</v>
+        <v>1.87804973125458</v>
       </c>
       <c r="H1993" t="n">
         <v>10692244</v>
@@ -58224,7 +58224,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237765789032</v>
+        <v>1.97237777709961</v>
       </c>
       <c r="H1995" t="n">
         <v>14164042</v>
@@ -58253,7 +58253,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866557121277</v>
+        <v>1.99866569042206</v>
       </c>
       <c r="H1996" t="n">
         <v>13386081</v>
@@ -58282,7 +58282,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964400291443</v>
+        <v>2.03964376449585</v>
       </c>
       <c r="H1997" t="n">
         <v>18265540</v>
@@ -58311,7 +58311,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.05510759353638</v>
+        <v>2.0551073551178</v>
       </c>
       <c r="H1998" t="n">
         <v>14855596</v>
@@ -58572,7 +58572,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G2007" t="n">
-        <v>2.3597400188446</v>
+        <v>2.35973978042603</v>
       </c>
       <c r="H2007" t="n">
         <v>16760666</v>
@@ -58630,7 +58630,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G2009" t="n">
-        <v>2.37520337104797</v>
+        <v>2.37520313262939</v>
       </c>
       <c r="H2009" t="n">
         <v>13477044</v>
@@ -58659,7 +58659,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654799461365</v>
+        <v>2.18654775619507</v>
       </c>
       <c r="H2010" t="n">
         <v>100072608</v>
@@ -58775,7 +58775,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.28551459312439</v>
+        <v>2.28551483154297</v>
       </c>
       <c r="H2014" t="n">
         <v>26182103</v>
@@ -58949,7 +58949,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921983718872</v>
+        <v>2.55921959877014</v>
       </c>
       <c r="H2020" t="n">
         <v>36522732</v>
@@ -59065,7 +59065,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.60329103469849</v>
+        <v>2.60329079627991</v>
       </c>
       <c r="H2024" t="n">
         <v>39561081</v>
@@ -59094,7 +59094,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.53447794914246</v>
+        <v>2.53447818756104</v>
       </c>
       <c r="H2025" t="n">
         <v>37969241</v>
@@ -59239,7 +59239,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061571121216</v>
+        <v>2.38061547279358</v>
       </c>
       <c r="H2030" t="n">
         <v>33067746</v>
@@ -59268,7 +59268,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.3643786907196</v>
+        <v>2.36437892913818</v>
       </c>
       <c r="H2031" t="n">
         <v>14604732</v>
@@ -59297,7 +59297,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.35046148300171</v>
+        <v>2.35046172142029</v>
       </c>
       <c r="H2032" t="n">
         <v>11232080</v>
@@ -59558,7 +59558,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334204673767</v>
+        <v>2.61334228515625</v>
       </c>
       <c r="H2041" t="n">
         <v>21815059</v>
@@ -59587,7 +59587,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597308158875</v>
+        <v>2.52597332000732</v>
       </c>
       <c r="H2042" t="n">
         <v>27175102</v>
@@ -59616,7 +59616,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.5252001285553</v>
+        <v>2.52519989013672</v>
       </c>
       <c r="H2043" t="n">
         <v>14675290</v>
@@ -59674,7 +59674,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710898399353</v>
+        <v>2.44710874557495</v>
       </c>
       <c r="H2045" t="n">
         <v>15281373</v>
@@ -59877,7 +59877,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.49659252166748</v>
+        <v>2.4965922832489</v>
       </c>
       <c r="H2052" t="n">
         <v>21135868</v>
@@ -59964,7 +59964,7 @@
         <v>3.2409999370575</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.50587034225464</v>
+        <v>2.50587058067322</v>
       </c>
       <c r="H2055" t="n">
         <v>36516901</v>
@@ -59993,7 +59993,7 @@
         <v>3.19099998474121</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.46721172332764</v>
+        <v>2.46721148490906</v>
       </c>
       <c r="H2056" t="n">
         <v>19021872</v>
@@ -60022,7 +60022,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.53602457046509</v>
+        <v>2.53602433204651</v>
       </c>
       <c r="H2057" t="n">
         <v>20653870</v>
@@ -60051,7 +60051,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.5298388004303</v>
+        <v>2.52983903884888</v>
       </c>
       <c r="H2058" t="n">
         <v>17041685</v>
@@ -60167,7 +60167,7 @@
         <v>3.37299990653992</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.60792970657349</v>
+        <v>2.60792994499207</v>
       </c>
       <c r="H2062" t="n">
         <v>29705979</v>
@@ -60399,7 +60399,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467994689941</v>
+        <v>2.72467970848083</v>
       </c>
       <c r="H2070" t="n">
         <v>14759944</v>
@@ -60486,7 +60486,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.75019478797913</v>
+        <v>2.75019454956055</v>
       </c>
       <c r="H2073" t="n">
         <v>39123998</v>
@@ -60718,7 +60718,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.04632186889648</v>
+        <v>3.04632210731506</v>
       </c>
       <c r="H2081" t="n">
         <v>24628211</v>
@@ -60747,7 +60747,7 @@
         <v>3.93099999427795</v>
       </c>
       <c r="G2082" t="n">
-        <v>3.03936338424683</v>
+        <v>3.03936362266541</v>
       </c>
       <c r="H2082" t="n">
         <v>19979927</v>
@@ -60776,7 +60776,7 @@
         <v>3.93899989128113</v>
       </c>
       <c r="G2083" t="n">
-        <v>3.04554867744446</v>
+        <v>3.04554843902588</v>
       </c>
       <c r="H2083" t="n">
         <v>14348482</v>
@@ -60834,7 +60834,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2085" t="n">
-        <v>2.98292136192322</v>
+        <v>2.9829216003418</v>
       </c>
       <c r="H2085" t="n">
         <v>15537029</v>
@@ -60863,7 +60863,7 @@
         <v>3.87299990653992</v>
       </c>
       <c r="G2086" t="n">
-        <v>2.99451899528503</v>
+        <v>2.99451875686646</v>
       </c>
       <c r="H2086" t="n">
         <v>18280166</v>
@@ -60921,7 +60921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2088" t="n">
-        <v>3.17003059387207</v>
+        <v>3.17003035545349</v>
       </c>
       <c r="H2088" t="n">
         <v>24484756</v>
@@ -60979,7 +60979,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188447952271</v>
+        <v>3.23188471794128</v>
       </c>
       <c r="H2090" t="n">
         <v>36447686</v>
@@ -61240,7 +61240,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2099" t="n">
-        <v>3.24734807014465</v>
+        <v>3.24734830856323</v>
       </c>
       <c r="H2099" t="n">
         <v>35140784</v>
@@ -61327,7 +61327,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343133926392</v>
+        <v>3.23343110084534</v>
       </c>
       <c r="H2102" t="n">
         <v>15820699</v>
@@ -61472,7 +61472,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972261428833</v>
+        <v>3.10972237586975</v>
       </c>
       <c r="H2107" t="n">
         <v>24633782</v>
@@ -61530,7 +61530,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G2109" t="n">
-        <v>3.11126899719238</v>
+        <v>3.11126923561096</v>
       </c>
       <c r="H2109" t="n">
         <v>23566464</v>
@@ -61588,7 +61588,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G2111" t="n">
-        <v>3.14838147163391</v>
+        <v>3.14838171005249</v>
       </c>
       <c r="H2111" t="n">
         <v>22266963</v>
@@ -61617,7 +61617,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2112" t="n">
-        <v>3.24734807014465</v>
+        <v>3.24734830856323</v>
       </c>
       <c r="H2112" t="n">
         <v>29517947</v>
@@ -61646,7 +61646,7 @@
         <v>4.16300010681152</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.21874070167542</v>
+        <v>3.21874094009399</v>
       </c>
       <c r="H2113" t="n">
         <v>18257227</v>
@@ -61878,7 +61878,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811129570007</v>
+        <v>3.69811105728149</v>
       </c>
       <c r="H2121" t="n">
         <v>32155461</v>
@@ -61907,7 +61907,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409482955933</v>
+        <v>3.51409459114075</v>
       </c>
       <c r="H2122" t="n">
         <v>36014819</v>
@@ -62052,7 +62052,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.66022539138794</v>
+        <v>3.66022562980652</v>
       </c>
       <c r="H2127" t="n">
         <v>18548351</v>
@@ -62081,7 +62081,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G2128" t="n">
-        <v>3.66873025894165</v>
+        <v>3.66873002052307</v>
       </c>
       <c r="H2128" t="n">
         <v>13092351</v>
@@ -62139,7 +62139,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145707130432</v>
+        <v>3.90145683288574</v>
       </c>
       <c r="H2130" t="n">
         <v>31985059</v>
@@ -80009,6 +80009,35 @@
         <v>10412561</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>11.0120000839233</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>11.1319999694824</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>10.9580001831055</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>9204201</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>10.8900003433228</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>10.9139995574951</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>10.5679998397827</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>10.5679998397827</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>10.5679998397827</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>12857934</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2369.1689453125</v>
       </c>
       <c r="G3" t="n">
-        <v>1831.78979492188</v>
+        <v>1831.78967285156</v>
       </c>
       <c r="H3" t="n">
         <v>30489</v>
@@ -630,7 +630,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26928710938</v>
+        <v>1523.26940917969</v>
       </c>
       <c r="H9" t="n">
         <v>41776</v>
@@ -717,7 +717,7 @@
         <v>1595.07385253906</v>
       </c>
       <c r="G12" t="n">
-        <v>1233.27624511719</v>
+        <v>1233.2763671875</v>
       </c>
       <c r="H12" t="n">
         <v>58224</v>
@@ -891,7 +891,7 @@
         <v>1464.84240722656</v>
       </c>
       <c r="G18" t="n">
-        <v>1132.58422851562</v>
+        <v>1132.58410644531</v>
       </c>
       <c r="H18" t="n">
         <v>55490</v>
@@ -978,7 +978,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14123535156</v>
+        <v>1068.14135742188</v>
       </c>
       <c r="H21" t="n">
         <v>67666</v>
@@ -1036,7 +1036,7 @@
         <v>1218.96557617188</v>
       </c>
       <c r="G23" t="n">
-        <v>942.4775390625</v>
+        <v>942.477478027344</v>
       </c>
       <c r="H23" t="n">
         <v>56261</v>
@@ -1094,7 +1094,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.311462402344</v>
+        <v>918.3115234375</v>
       </c>
       <c r="H25" t="n">
         <v>64565</v>
@@ -1152,7 +1152,7 @@
         <v>1082.48315429688</v>
       </c>
       <c r="G27" t="n">
-        <v>836.952331542969</v>
+        <v>836.952392578125</v>
       </c>
       <c r="H27" t="n">
         <v>42864</v>
@@ -1268,7 +1268,7 @@
         <v>956.8359375</v>
       </c>
       <c r="G31" t="n">
-        <v>739.804626464844</v>
+        <v>739.8046875</v>
       </c>
       <c r="H31" t="n">
         <v>71729</v>
@@ -1616,7 +1616,7 @@
         <v>1076.23205566406</v>
       </c>
       <c r="G43" t="n">
-        <v>832.119140625</v>
+        <v>832.119079589844</v>
       </c>
       <c r="H43" t="n">
         <v>62505</v>
@@ -1848,7 +1848,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977966308594</v>
+        <v>927.977905273438</v>
       </c>
       <c r="H51" t="n">
         <v>78651</v>
@@ -1877,7 +1877,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03125</v>
+        <v>1023.03131103516</v>
       </c>
       <c r="H52" t="n">
         <v>99090</v>
@@ -1906,7 +1906,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810363769531</v>
+        <v>961.810424804688</v>
       </c>
       <c r="H53" t="n">
         <v>82251</v>
@@ -1935,7 +1935,7 @@
         <v>1245.01184082031</v>
       </c>
       <c r="G54" t="n">
-        <v>962.615966796875</v>
+        <v>962.616027832031</v>
       </c>
       <c r="H54" t="n">
         <v>47448</v>
@@ -1993,7 +1993,7 @@
         <v>1240.84448242188</v>
       </c>
       <c r="G56" t="n">
-        <v>959.393920898438</v>
+        <v>959.393859863281</v>
       </c>
       <c r="H56" t="n">
         <v>50887</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254089355469</v>
+        <v>997.254028320312</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2051,7 +2051,7 @@
         <v>1259.59777832031</v>
       </c>
       <c r="G58" t="n">
-        <v>973.8935546875</v>
+        <v>973.893493652344</v>
       </c>
       <c r="H58" t="n">
         <v>36967</v>
@@ -2080,7 +2080,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199401855469</v>
+        <v>960.199340820312</v>
       </c>
       <c r="H59" t="n">
         <v>31218</v>
@@ -2399,7 +2399,7 @@
         <v>1076.23205566406</v>
       </c>
       <c r="G70" t="n">
-        <v>832.119140625</v>
+        <v>832.119079589844</v>
       </c>
       <c r="H70" t="n">
         <v>65174</v>
@@ -2573,7 +2573,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03125</v>
+        <v>1023.03131103516</v>
       </c>
       <c r="H76" t="n">
         <v>87970</v>
@@ -2602,7 +2602,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86303710938</v>
+        <v>1085.86291503906</v>
       </c>
       <c r="H77" t="n">
         <v>60062</v>
@@ -2660,7 +2660,7 @@
         <v>1421.08471679688</v>
       </c>
       <c r="G79" t="n">
-        <v>1098.75170898438</v>
+        <v>1098.75158691406</v>
       </c>
       <c r="H79" t="n">
         <v>33838</v>
@@ -2689,7 +2689,7 @@
         <v>1379.41064453125</v>
       </c>
       <c r="G80" t="n">
-        <v>1066.53015136719</v>
+        <v>1066.5302734375</v>
       </c>
       <c r="H80" t="n">
         <v>19070</v>
@@ -2747,7 +2747,7 @@
         <v>1470.05163574219</v>
       </c>
       <c r="G82" t="n">
-        <v>1136.61193847656</v>
+        <v>1136.61181640625</v>
       </c>
       <c r="H82" t="n">
         <v>43127</v>
@@ -2863,7 +2863,7 @@
         <v>1285.64404296875</v>
       </c>
       <c r="G86" t="n">
-        <v>994.031799316406</v>
+        <v>994.031921386719</v>
       </c>
       <c r="H86" t="n">
         <v>50926</v>
@@ -2921,7 +2921,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80902099609</v>
+        <v>1019.80908203125</v>
       </c>
       <c r="H88" t="n">
         <v>45362</v>
@@ -3298,7 +3298,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809692382812</v>
+        <v>990.809753417969</v>
       </c>
       <c r="H101" t="n">
         <v>46314</v>
@@ -3327,7 +3327,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47619628906</v>
+        <v>1000.47613525391</v>
       </c>
       <c r="H102" t="n">
         <v>46119</v>
@@ -3356,7 +3356,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.14263916016</v>
+        <v>1010.14270019531</v>
       </c>
       <c r="H103" t="n">
         <v>21794</v>
@@ -3443,7 +3443,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.69836425781</v>
+        <v>1003.69830322266</v>
       </c>
       <c r="H106" t="n">
         <v>20322</v>
@@ -3588,7 +3588,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809692382812</v>
+        <v>990.809753417969</v>
       </c>
       <c r="H111" t="n">
         <v>28141</v>
@@ -3617,7 +3617,7 @@
         <v>1256.47229003906</v>
       </c>
       <c r="G112" t="n">
-        <v>971.476989746094</v>
+        <v>971.476928710938</v>
       </c>
       <c r="H112" t="n">
         <v>17386</v>
@@ -3704,7 +3704,7 @@
         <v>1046.01831054688</v>
       </c>
       <c r="G115" t="n">
-        <v>808.758544921875</v>
+        <v>808.758483886719</v>
       </c>
       <c r="H115" t="n">
         <v>39052</v>
@@ -3849,7 +3849,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368286132812</v>
+        <v>868.368225097656</v>
       </c>
       <c r="H120" t="n">
         <v>32561</v>
@@ -3994,7 +3994,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118225097656</v>
+        <v>634.118286132812</v>
       </c>
       <c r="H125" t="n">
         <v>71078</v>
@@ -4052,7 +4052,7 @@
         <v>809.934936523438</v>
       </c>
       <c r="G127" t="n">
-        <v>626.223999023438</v>
+        <v>626.223937988281</v>
       </c>
       <c r="H127" t="n">
         <v>44209</v>
@@ -4284,7 +4284,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549682617188</v>
+        <v>481.549652099609</v>
       </c>
       <c r="H135" t="n">
         <v>39529</v>
@@ -4342,7 +4342,7 @@
         <v>680.745422363281</v>
       </c>
       <c r="G137" t="n">
-        <v>526.337463378906</v>
+        <v>526.337524414062</v>
       </c>
       <c r="H137" t="n">
         <v>93205</v>
@@ -4458,7 +4458,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.537658691406</v>
+        <v>520.53759765625</v>
       </c>
       <c r="H141" t="n">
         <v>36777</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710052490234</v>
+        <v>510.710083007812</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4545,7 +4545,7 @@
         <v>650.114990234375</v>
       </c>
       <c r="G144" t="n">
-        <v>502.654693603516</v>
+        <v>502.654754638672</v>
       </c>
       <c r="H144" t="n">
         <v>26528</v>
@@ -4574,7 +4574,7 @@
         <v>595.313598632812</v>
       </c>
       <c r="G145" t="n">
-        <v>460.283447265625</v>
+        <v>460.283477783203</v>
       </c>
       <c r="H145" t="n">
         <v>58255</v>
@@ -4690,7 +4690,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532623291016</v>
+        <v>496.532592773438</v>
       </c>
       <c r="H149" t="n">
         <v>46906</v>
@@ -4893,7 +4893,7 @@
         <v>512.799011230469</v>
       </c>
       <c r="G156" t="n">
-        <v>396.484985351562</v>
+        <v>396.485015869141</v>
       </c>
       <c r="H156" t="n">
         <v>51516</v>
@@ -4951,7 +4951,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384918212891</v>
+        <v>399.384948730469</v>
       </c>
       <c r="H158" t="n">
         <v>11284</v>
@@ -4980,7 +4980,7 @@
         <v>523.009155273438</v>
       </c>
       <c r="G159" t="n">
-        <v>404.379272460938</v>
+        <v>404.379241943359</v>
       </c>
       <c r="H159" t="n">
         <v>21609</v>
@@ -5009,7 +5009,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.512725830078</v>
+        <v>400.5126953125</v>
       </c>
       <c r="H160" t="n">
         <v>10381</v>
@@ -5212,7 +5212,7 @@
         <v>490.50341796875</v>
       </c>
       <c r="G167" t="n">
-        <v>379.246520996094</v>
+        <v>379.246551513672</v>
       </c>
       <c r="H167" t="n">
         <v>15313</v>
@@ -5357,7 +5357,7 @@
         <v>498.629852294922</v>
       </c>
       <c r="G172" t="n">
-        <v>385.529693603516</v>
+        <v>385.529724121094</v>
       </c>
       <c r="H172" t="n">
         <v>21623</v>
@@ -5415,7 +5415,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724212646484</v>
+        <v>384.724182128906</v>
       </c>
       <c r="H174" t="n">
         <v>11728</v>
@@ -5618,7 +5618,7 @@
         <v>466.749237060547</v>
       </c>
       <c r="G181" t="n">
-        <v>360.880340576172</v>
+        <v>360.880310058594</v>
       </c>
       <c r="H181" t="n">
         <v>25529</v>
@@ -5647,7 +5647,7 @@
         <v>464.248779296875</v>
       </c>
       <c r="G182" t="n">
-        <v>358.947052001953</v>
+        <v>358.947021484375</v>
       </c>
       <c r="H182" t="n">
         <v>28648</v>
@@ -5763,7 +5763,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003753662109</v>
+        <v>309.003784179688</v>
       </c>
       <c r="H186" t="n">
         <v>27102</v>
@@ -5908,7 +5908,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742614746094</v>
+        <v>311.742584228516</v>
       </c>
       <c r="H191" t="n">
         <v>13716</v>
@@ -5995,7 +5995,7 @@
         <v>381.942565917969</v>
       </c>
       <c r="G194" t="n">
-        <v>295.309661865234</v>
+        <v>295.309631347656</v>
       </c>
       <c r="H194" t="n">
         <v>11584</v>
@@ -6024,7 +6024,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281951904297</v>
+        <v>291.281982421875</v>
       </c>
       <c r="H195" t="n">
         <v>13255</v>
@@ -6111,7 +6111,7 @@
         <v>354.229309082031</v>
       </c>
       <c r="G198" t="n">
-        <v>273.882354736328</v>
+        <v>273.882385253906</v>
       </c>
       <c r="H198" t="n">
         <v>39961</v>
@@ -6227,7 +6227,7 @@
         <v>355.896270751953</v>
       </c>
       <c r="G202" t="n">
-        <v>275.171234130859</v>
+        <v>275.171203613281</v>
       </c>
       <c r="H202" t="n">
         <v>17732</v>
@@ -6372,7 +6372,7 @@
         <v>497.379638671875</v>
       </c>
       <c r="G207" t="n">
-        <v>384.563079833984</v>
+        <v>384.563049316406</v>
       </c>
       <c r="H207" t="n">
         <v>111579</v>
@@ -6488,7 +6488,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184143066406</v>
+        <v>434.184112548828</v>
       </c>
       <c r="H211" t="n">
         <v>136414</v>
@@ -6894,7 +6894,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829254150391</v>
+        <v>405.829284667969</v>
       </c>
       <c r="H225" t="n">
         <v>74636</v>
@@ -7010,7 +7010,7 @@
         <v>469.666412353516</v>
       </c>
       <c r="G229" t="n">
-        <v>363.135833740234</v>
+        <v>363.135803222656</v>
       </c>
       <c r="H229" t="n">
         <v>34267</v>
@@ -7184,7 +7184,7 @@
         <v>421.949615478516</v>
       </c>
       <c r="G235" t="n">
-        <v>326.242248535156</v>
+        <v>326.242218017578</v>
       </c>
       <c r="H235" t="n">
         <v>85324</v>
@@ -7271,7 +7271,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H238" t="n">
         <v>56464</v>
@@ -7300,7 +7300,7 @@
         <v>389.235473632812</v>
       </c>
       <c r="G239" t="n">
-        <v>300.948394775391</v>
+        <v>300.948364257812</v>
       </c>
       <c r="H239" t="n">
         <v>60863</v>
@@ -7416,7 +7416,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H243" t="n">
         <v>108228</v>
@@ -7474,7 +7474,7 @@
         <v>426.742126464844</v>
       </c>
       <c r="G245" t="n">
-        <v>329.947723388672</v>
+        <v>329.947692871094</v>
       </c>
       <c r="H245" t="n">
         <v>45235</v>
@@ -7532,7 +7532,7 @@
         <v>430.492767333984</v>
       </c>
       <c r="G247" t="n">
-        <v>332.847595214844</v>
+        <v>332.847625732422</v>
       </c>
       <c r="H247" t="n">
         <v>82950</v>
@@ -7677,7 +7677,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G252" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H252" t="n">
         <v>181498</v>
@@ -7706,7 +7706,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G253" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G254" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G255" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G256" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G257" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G258" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G259" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G260" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G261" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G262" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G263" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G264" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G265" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G266" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G267" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G268" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G269" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G270" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G271" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G272" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G273" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G274" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G275" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G276" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G277" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G278" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G279" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G280" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G281" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G282" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G283" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G284" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G285" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G286" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G287" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G288" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G289" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G290" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G291" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G292" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G293" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G294" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G295" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G296" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G297" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G298" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G299" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G300" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G301" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G302" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G303" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G304" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G305" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G306" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G307" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G308" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G309" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G310" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G311" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G312" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G313" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G314" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G315" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G316" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G317" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G318" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G319" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G320" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G321" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G322" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G323" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G324" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G325" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G326" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G327" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G328" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G329" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G330" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G331" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G332" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G333" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G334" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G335" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G336" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G337" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G338" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G339" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G340" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G341" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G342" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G343" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G344" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G345" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G346" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G347" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G348" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G349" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G350" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G351" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G352" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G353" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G354" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G355" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G356" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G357" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G358" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G359" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G360" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G361" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G362" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G363" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G364" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G365" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G366" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G367" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G368" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G369" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G370" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G371" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G372" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G373" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G374" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G375" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G376" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G377" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G378" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G379" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G380" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G381" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G382" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G383" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G384" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G385" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G386" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G387" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G388" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G389" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G390" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G391" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G392" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G393" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G394" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G395" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G396" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G397" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G398" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G399" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G400" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G401" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G402" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G403" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G404" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G405" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G406" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G407" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G408" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G409" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G410" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G411" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G412" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G413" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G414" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G415" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G416" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G417" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G418" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G419" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G420" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G421" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G422" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G423" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G424" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G425" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G426" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G427" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G428" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G429" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G430" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G431" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G432" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G433" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G434" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G435" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G436" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G437" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G438" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G439" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G440" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G441" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G442" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G443" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G444" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G445" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G446" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G447" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G448" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G449" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G450" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G451" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G452" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G453" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G454" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G455" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G456" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G457" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G458" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G459" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G460" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G461" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G462" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G463" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G464" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G465" t="n">
-        <v>242.949768066406</v>
+        <v>242.949783325195</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.300407409668</v>
+        <v>76.3003997802734</v>
       </c>
       <c r="H468" t="n">
         <v>232423</v>
@@ -13999,7 +13999,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426330566406</v>
+        <v>76.0426254272461</v>
       </c>
       <c r="H470" t="n">
         <v>149896</v>
@@ -14260,7 +14260,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.121826171875</v>
+        <v>63.1218299865723</v>
       </c>
       <c r="H479" t="n">
         <v>202691</v>
@@ -14318,7 +14318,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264366149902</v>
+        <v>56.2264404296875</v>
       </c>
       <c r="H481" t="n">
         <v>308433</v>
@@ -14434,7 +14434,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.1540489196777</v>
+        <v>63.1540451049805</v>
       </c>
       <c r="H485" t="n">
         <v>461818</v>
@@ -14492,7 +14492,7 @@
         <v>82.0978469848633</v>
       </c>
       <c r="G487" t="n">
-        <v>63.476261138916</v>
+        <v>63.4762649536133</v>
       </c>
       <c r="H487" t="n">
         <v>63428</v>
@@ -14521,7 +14521,7 @@
         <v>83.306396484375</v>
       </c>
       <c r="G488" t="n">
-        <v>64.4106903076172</v>
+        <v>64.4106826782227</v>
       </c>
       <c r="H488" t="n">
         <v>91362</v>
@@ -14550,7 +14550,7 @@
         <v>84.1815490722656</v>
       </c>
       <c r="G489" t="n">
-        <v>65.0873336791992</v>
+        <v>65.0873413085938</v>
       </c>
       <c r="H489" t="n">
         <v>130214</v>
@@ -14695,7 +14695,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.1540489196777</v>
+        <v>63.1540451049805</v>
       </c>
       <c r="H494" t="n">
         <v>82320</v>
@@ -14724,7 +14724,7 @@
         <v>82.3062210083008</v>
       </c>
       <c r="G495" t="n">
-        <v>63.637378692627</v>
+        <v>63.6373748779297</v>
       </c>
       <c r="H495" t="n">
         <v>41220</v>
@@ -14811,7 +14811,7 @@
         <v>80.6392593383789</v>
       </c>
       <c r="G498" t="n">
-        <v>62.3485145568848</v>
+        <v>62.3485107421875</v>
       </c>
       <c r="H498" t="n">
         <v>58360</v>
@@ -14869,7 +14869,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.961856842041</v>
+        <v>61.9618530273438</v>
       </c>
       <c r="H500" t="n">
         <v>52866</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.156322479248</v>
+        <v>61.1563186645508</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -14956,7 +14956,7 @@
         <v>77.5137023925781</v>
       </c>
       <c r="G503" t="n">
-        <v>59.9319000244141</v>
+        <v>59.9319038391113</v>
       </c>
       <c r="H503" t="n">
         <v>48461</v>
@@ -14985,7 +14985,7 @@
         <v>80.0974960327148</v>
       </c>
       <c r="G504" t="n">
-        <v>61.9296340942383</v>
+        <v>61.9296379089355</v>
       </c>
       <c r="H504" t="n">
         <v>38478</v>
@@ -15014,7 +15014,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.670726776123</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H505" t="n">
         <v>57550</v>
@@ -15043,7 +15043,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G506" t="n">
-        <v>62.5096206665039</v>
+        <v>62.5096168518066</v>
       </c>
       <c r="H506" t="n">
         <v>88056</v>
@@ -15101,7 +15101,7 @@
         <v>79.7640991210938</v>
       </c>
       <c r="G508" t="n">
-        <v>61.6718559265137</v>
+        <v>61.6718597412109</v>
       </c>
       <c r="H508" t="n">
         <v>34426</v>
@@ -15159,7 +15159,7 @@
         <v>81.93115234375</v>
       </c>
       <c r="G510" t="n">
-        <v>63.3473777770996</v>
+        <v>63.3473739624023</v>
       </c>
       <c r="H510" t="n">
         <v>35391</v>
@@ -15188,7 +15188,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573883056641</v>
+        <v>63.0573806762695</v>
       </c>
       <c r="H511" t="n">
         <v>34562</v>
@@ -15217,7 +15217,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.670726776123</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H512" t="n">
         <v>22428</v>
@@ -15246,7 +15246,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.412956237793</v>
+        <v>62.4129600524902</v>
       </c>
       <c r="H513" t="n">
         <v>27484</v>
@@ -15304,7 +15304,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.670726776123</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H515" t="n">
         <v>30486</v>
@@ -15333,7 +15333,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G516" t="n">
-        <v>62.5096206665039</v>
+        <v>62.5096168518066</v>
       </c>
       <c r="H516" t="n">
         <v>30537</v>
@@ -15391,7 +15391,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G518" t="n">
-        <v>63.927360534668</v>
+        <v>63.9273643493652</v>
       </c>
       <c r="H518" t="n">
         <v>298961</v>
@@ -15420,7 +15420,7 @@
         <v>81.8894805908203</v>
       </c>
       <c r="G519" t="n">
-        <v>63.3151512145996</v>
+        <v>63.3151588439941</v>
       </c>
       <c r="H519" t="n">
         <v>98758</v>
@@ -15507,7 +15507,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695899963379</v>
+        <v>63.6695938110352</v>
       </c>
       <c r="H522" t="n">
         <v>52551</v>
@@ -15536,7 +15536,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G523" t="n">
-        <v>63.927360534668</v>
+        <v>63.9273643493652</v>
       </c>
       <c r="H523" t="n">
         <v>45681</v>
@@ -15594,7 +15594,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.670726776123</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H525" t="n">
         <v>40067</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184906005859</v>
+        <v>63.2184944152832</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15652,7 +15652,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.670726776123</v>
+        <v>62.6707305908203</v>
       </c>
       <c r="H527" t="n">
         <v>45359</v>
@@ -15710,7 +15710,7 @@
         <v>81.0143203735352</v>
       </c>
       <c r="G529" t="n">
-        <v>62.6385040283203</v>
+        <v>62.6385078430176</v>
       </c>
       <c r="H529" t="n">
         <v>50236</v>
@@ -15768,7 +15768,7 @@
         <v>80.555908203125</v>
       </c>
       <c r="G531" t="n">
-        <v>62.2840690612793</v>
+        <v>62.2840728759766</v>
       </c>
       <c r="H531" t="n">
         <v>74076</v>
@@ -15826,7 +15826,7 @@
         <v>78.7639236450195</v>
       </c>
       <c r="G533" t="n">
-        <v>60.8985443115234</v>
+        <v>60.8985481262207</v>
       </c>
       <c r="H533" t="n">
         <v>102976</v>
@@ -15855,7 +15855,7 @@
         <v>77.9721221923828</v>
       </c>
       <c r="G534" t="n">
-        <v>60.2863426208496</v>
+        <v>60.2863464355469</v>
       </c>
       <c r="H534" t="n">
         <v>68146</v>
@@ -16000,7 +16000,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.8363800048828</v>
+        <v>58.8363761901855</v>
       </c>
       <c r="H539" t="n">
         <v>77063</v>
@@ -16029,7 +16029,7 @@
         <v>78.7639236450195</v>
       </c>
       <c r="G540" t="n">
-        <v>60.8985443115234</v>
+        <v>60.8985481262207</v>
       </c>
       <c r="H540" t="n">
         <v>63710</v>
@@ -16290,7 +16290,7 @@
         <v>67.0951995849609</v>
       </c>
       <c r="G549" t="n">
-        <v>51.8765449523926</v>
+        <v>51.8765411376953</v>
       </c>
       <c r="H549" t="n">
         <v>124037</v>
@@ -16348,7 +16348,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.005428314209</v>
+        <v>52.0054321289062</v>
       </c>
       <c r="H551" t="n">
         <v>83287</v>
@@ -16493,7 +16493,7 @@
         <v>63.5529022216797</v>
       </c>
       <c r="G556" t="n">
-        <v>49.1377182006836</v>
+        <v>49.1377143859863</v>
       </c>
       <c r="H556" t="n">
         <v>55076</v>
@@ -16696,7 +16696,7 @@
         <v>63.6987609863281</v>
       </c>
       <c r="G563" t="n">
-        <v>49.2504920959473</v>
+        <v>49.25048828125</v>
       </c>
       <c r="H563" t="n">
         <v>49204</v>
@@ -16899,7 +16899,7 @@
         <v>56.0099029541016</v>
       </c>
       <c r="G570" t="n">
-        <v>43.3056335449219</v>
+        <v>43.3056373596191</v>
       </c>
       <c r="H570" t="n">
         <v>225410</v>
@@ -16928,7 +16928,7 @@
         <v>54.3221054077148</v>
       </c>
       <c r="G571" t="n">
-        <v>42.0006675720215</v>
+        <v>42.0006637573242</v>
       </c>
       <c r="H571" t="n">
         <v>114062</v>
@@ -16957,7 +16957,7 @@
         <v>52.9051856994629</v>
       </c>
       <c r="G572" t="n">
-        <v>40.9051322937012</v>
+        <v>40.9051361083984</v>
       </c>
       <c r="H572" t="n">
         <v>130898</v>
@@ -16986,7 +16986,7 @@
         <v>51.6758041381836</v>
       </c>
       <c r="G573" t="n">
-        <v>39.9546051025391</v>
+        <v>39.9546012878418</v>
       </c>
       <c r="H573" t="n">
         <v>230355</v>
@@ -17015,7 +17015,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367866516113</v>
+        <v>41.4367904663086</v>
       </c>
       <c r="H574" t="n">
         <v>153152</v>
@@ -17189,7 +17189,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.1756134033203</v>
+        <v>44.175609588623</v>
       </c>
       <c r="H580" t="n">
         <v>158204</v>
@@ -17218,7 +17218,7 @@
         <v>55.5723266601562</v>
       </c>
       <c r="G581" t="n">
-        <v>42.9673080444336</v>
+        <v>42.9673118591309</v>
       </c>
       <c r="H581" t="n">
         <v>116018</v>
@@ -17305,7 +17305,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G584" t="n">
-        <v>42.9511985778809</v>
+        <v>42.9511947631836</v>
       </c>
       <c r="H584" t="n">
         <v>78005</v>
@@ -17479,7 +17479,7 @@
         <v>56.4683151245117</v>
       </c>
       <c r="G590" t="n">
-        <v>43.6600646972656</v>
+        <v>43.6600685119629</v>
       </c>
       <c r="H590" t="n">
         <v>38834</v>
@@ -17566,7 +17566,7 @@
         <v>55.4889755249023</v>
       </c>
       <c r="G593" t="n">
-        <v>42.9028625488281</v>
+        <v>42.9028663635254</v>
       </c>
       <c r="H593" t="n">
         <v>40012</v>
@@ -17624,7 +17624,7 @@
         <v>55.6348342895508</v>
       </c>
       <c r="G595" t="n">
-        <v>43.0156364440918</v>
+        <v>43.0156402587891</v>
       </c>
       <c r="H595" t="n">
         <v>43278</v>
@@ -17769,7 +17769,7 @@
         <v>57.3017959594727</v>
       </c>
       <c r="G600" t="n">
-        <v>44.3044967651367</v>
+        <v>44.304500579834</v>
       </c>
       <c r="H600" t="n">
         <v>186430</v>
@@ -18059,7 +18059,7 @@
         <v>59.1771278381348</v>
       </c>
       <c r="G610" t="n">
-        <v>45.7544631958008</v>
+        <v>45.754467010498</v>
       </c>
       <c r="H610" t="n">
         <v>95657</v>
@@ -18088,7 +18088,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G611" t="n">
-        <v>44.3206100463867</v>
+        <v>44.3206062316895</v>
       </c>
       <c r="H611" t="n">
         <v>142469</v>
@@ -18175,7 +18175,7 @@
         <v>52.2800750732422</v>
       </c>
       <c r="G614" t="n">
-        <v>40.4218139648438</v>
+        <v>40.4218101501465</v>
       </c>
       <c r="H614" t="n">
         <v>255740</v>
@@ -18262,7 +18262,7 @@
         <v>55.6348342895508</v>
       </c>
       <c r="G617" t="n">
-        <v>43.0156364440918</v>
+        <v>43.0156402587891</v>
       </c>
       <c r="H617" t="n">
         <v>190893</v>
@@ -18291,7 +18291,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G618" t="n">
-        <v>42.9511985778809</v>
+        <v>42.9511947631836</v>
       </c>
       <c r="H618" t="n">
         <v>69954</v>
@@ -18349,7 +18349,7 @@
         <v>59.1771278381348</v>
       </c>
       <c r="G620" t="n">
-        <v>45.7544631958008</v>
+        <v>45.754467010498</v>
       </c>
       <c r="H620" t="n">
         <v>121797</v>
@@ -18378,7 +18378,7 @@
         <v>57.1976127624512</v>
       </c>
       <c r="G621" t="n">
-        <v>44.2239456176758</v>
+        <v>44.2239418029785</v>
       </c>
       <c r="H621" t="n">
         <v>99660</v>
@@ -18465,7 +18465,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G624" t="n">
-        <v>44.3206100463867</v>
+        <v>44.3206062316895</v>
       </c>
       <c r="H624" t="n">
         <v>48032</v>
@@ -18494,7 +18494,7 @@
         <v>58.5520172119141</v>
       </c>
       <c r="G625" t="n">
-        <v>45.2711410522461</v>
+        <v>45.2711372375488</v>
       </c>
       <c r="H625" t="n">
         <v>62650</v>
@@ -18813,7 +18813,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.3734817504883</v>
+        <v>40.373477935791</v>
       </c>
       <c r="H636" t="n">
         <v>90143</v>
@@ -18900,7 +18900,7 @@
         <v>51.6758041381836</v>
       </c>
       <c r="G639" t="n">
-        <v>39.9546051025391</v>
+        <v>39.9546012878418</v>
       </c>
       <c r="H639" t="n">
         <v>54533</v>
@@ -18958,7 +18958,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062690734863</v>
+        <v>39.9062728881836</v>
       </c>
       <c r="H641" t="n">
         <v>47114</v>
@@ -19016,7 +19016,7 @@
         <v>51.4465942382812</v>
       </c>
       <c r="G643" t="n">
-        <v>39.7773857116699</v>
+        <v>39.7773818969727</v>
       </c>
       <c r="H643" t="n">
         <v>34432</v>
@@ -19074,7 +19074,7 @@
         <v>50.6339530944824</v>
       </c>
       <c r="G645" t="n">
-        <v>39.1490631103516</v>
+        <v>39.1490669250488</v>
       </c>
       <c r="H645" t="n">
         <v>34642</v>
@@ -19132,7 +19132,7 @@
         <v>50.4255828857422</v>
       </c>
       <c r="G647" t="n">
-        <v>38.9879570007324</v>
+        <v>38.9879608154297</v>
       </c>
       <c r="H647" t="n">
         <v>33718</v>
@@ -19277,7 +19277,7 @@
         <v>50.0088424682617</v>
       </c>
       <c r="G652" t="n">
-        <v>38.6657485961914</v>
+        <v>38.6657447814941</v>
       </c>
       <c r="H652" t="n">
         <v>24569</v>
@@ -19306,7 +19306,7 @@
         <v>49.4879150390625</v>
       </c>
       <c r="G653" t="n">
-        <v>38.2629776000977</v>
+        <v>38.2629737854004</v>
       </c>
       <c r="H653" t="n">
         <v>58634</v>
@@ -19335,7 +19335,7 @@
         <v>50.0088424682617</v>
       </c>
       <c r="G654" t="n">
-        <v>38.6657485961914</v>
+        <v>38.6657447814941</v>
       </c>
       <c r="H654" t="n">
         <v>54520</v>
@@ -19364,7 +19364,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.0374221801758</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H655" t="n">
         <v>34543</v>
@@ -19393,7 +19393,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.0213165283203</v>
+        <v>38.021312713623</v>
       </c>
       <c r="H656" t="n">
         <v>39162</v>
@@ -19509,7 +19509,7 @@
         <v>54.1762466430664</v>
       </c>
       <c r="G660" t="n">
-        <v>41.8878936767578</v>
+        <v>41.8878898620605</v>
       </c>
       <c r="H660" t="n">
         <v>68284</v>
@@ -19567,7 +19567,7 @@
         <v>50.6339530944824</v>
       </c>
       <c r="G662" t="n">
-        <v>39.1490631103516</v>
+        <v>39.1490669250488</v>
       </c>
       <c r="H662" t="n">
         <v>400900</v>
@@ -19625,7 +19625,7 @@
         <v>50.4255828857422</v>
       </c>
       <c r="G664" t="n">
-        <v>38.9879570007324</v>
+        <v>38.9879608154297</v>
       </c>
       <c r="H664" t="n">
         <v>60973</v>
@@ -19857,7 +19857,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G672" t="n">
-        <v>35.3952674865723</v>
+        <v>35.395263671875</v>
       </c>
       <c r="H672" t="n">
         <v>39171</v>
@@ -19973,7 +19973,7 @@
         <v>45.5288848876953</v>
       </c>
       <c r="G676" t="n">
-        <v>35.2019424438477</v>
+        <v>35.2019386291504</v>
       </c>
       <c r="H676" t="n">
         <v>28978</v>
@@ -20089,7 +20089,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580711364746</v>
+        <v>34.0580749511719</v>
       </c>
       <c r="H680" t="n">
         <v>49600</v>
@@ -20147,7 +20147,7 @@
         <v>44.507869720459</v>
       </c>
       <c r="G682" t="n">
-        <v>34.4125099182129</v>
+        <v>34.4125137329102</v>
       </c>
       <c r="H682" t="n">
         <v>55885</v>
@@ -20234,7 +20234,7 @@
         <v>46.3206901550293</v>
       </c>
       <c r="G685" t="n">
-        <v>35.8141441345215</v>
+        <v>35.8141479492188</v>
       </c>
       <c r="H685" t="n">
         <v>78485</v>
@@ -20263,7 +20263,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G686" t="n">
-        <v>35.3952674865723</v>
+        <v>35.395263671875</v>
       </c>
       <c r="H686" t="n">
         <v>55186</v>
@@ -20292,7 +20292,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G687" t="n">
-        <v>38.3113098144531</v>
+        <v>38.3113059997559</v>
       </c>
       <c r="H687" t="n">
         <v>246032</v>
@@ -20321,7 +20321,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.0374221801758</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H688" t="n">
         <v>118566</v>
@@ -20350,7 +20350,7 @@
         <v>47.695930480957</v>
       </c>
       <c r="G689" t="n">
-        <v>36.8774528503418</v>
+        <v>36.8774490356445</v>
       </c>
       <c r="H689" t="n">
         <v>132939</v>
@@ -20408,7 +20408,7 @@
         <v>46.6124076843262</v>
       </c>
       <c r="G691" t="n">
-        <v>36.0396995544434</v>
+        <v>36.0396957397461</v>
       </c>
       <c r="H691" t="n">
         <v>87887</v>
@@ -20437,7 +20437,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057716369629</v>
+        <v>37.5057754516602</v>
       </c>
       <c r="H692" t="n">
         <v>93100</v>
@@ -20582,7 +20582,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G697" t="n">
-        <v>38.3113098144531</v>
+        <v>38.3113059997559</v>
       </c>
       <c r="H697" t="n">
         <v>47583</v>
@@ -20640,7 +20640,7 @@
         <v>50.175537109375</v>
       </c>
       <c r="G699" t="n">
-        <v>38.7946281433105</v>
+        <v>38.7946319580078</v>
       </c>
       <c r="H699" t="n">
         <v>37785</v>
@@ -20669,7 +20669,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.0213165283203</v>
+        <v>38.021312713623</v>
       </c>
       <c r="H700" t="n">
         <v>69415</v>
@@ -20756,7 +20756,7 @@
         <v>42.9242553710938</v>
       </c>
       <c r="G703" t="n">
-        <v>33.1880950927734</v>
+        <v>33.1880989074707</v>
       </c>
       <c r="H703" t="n">
         <v>149650</v>
@@ -20785,7 +20785,7 @@
         <v>42.861743927002</v>
       </c>
       <c r="G704" t="n">
-        <v>33.139762878418</v>
+        <v>33.1397666931152</v>
       </c>
       <c r="H704" t="n">
         <v>60234</v>
@@ -20872,7 +20872,7 @@
         <v>40.1008377075195</v>
       </c>
       <c r="G707" t="n">
-        <v>31.0050945281982</v>
+        <v>31.0050926208496</v>
       </c>
       <c r="H707" t="n">
         <v>128220</v>
@@ -20901,7 +20901,7 @@
         <v>39.3715438842773</v>
       </c>
       <c r="G708" t="n">
-        <v>30.4412174224854</v>
+        <v>30.441219329834</v>
       </c>
       <c r="H708" t="n">
         <v>153302</v>
@@ -20930,7 +20930,7 @@
         <v>38.5068092346191</v>
       </c>
       <c r="G709" t="n">
-        <v>29.7726249694824</v>
+        <v>29.7726230621338</v>
       </c>
       <c r="H709" t="n">
         <v>137943</v>
@@ -21307,7 +21307,7 @@
         <v>31.7764511108398</v>
       </c>
       <c r="G722" t="n">
-        <v>24.5688591003418</v>
+        <v>24.5688571929932</v>
       </c>
       <c r="H722" t="n">
         <v>227745</v>
@@ -21394,7 +21394,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G725" t="n">
-        <v>24.2466449737549</v>
+        <v>24.2466430664062</v>
       </c>
       <c r="H725" t="n">
         <v>79264</v>
@@ -21481,7 +21481,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480266571045</v>
+        <v>24.4480247497559</v>
       </c>
       <c r="H728" t="n">
         <v>59503</v>
@@ -21568,7 +21568,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G731" t="n">
-        <v>24.2466449737549</v>
+        <v>24.2466430664062</v>
       </c>
       <c r="H731" t="n">
         <v>152132</v>
@@ -21597,7 +21597,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177558898926</v>
+        <v>24.1177577972412</v>
       </c>
       <c r="H732" t="n">
         <v>82427</v>
@@ -21684,7 +21684,7 @@
         <v>29.411449432373</v>
       </c>
       <c r="G735" t="n">
-        <v>22.7402896881104</v>
+        <v>22.740291595459</v>
       </c>
       <c r="H735" t="n">
         <v>76940</v>
@@ -21771,7 +21771,7 @@
         <v>27.8174171447754</v>
       </c>
       <c r="G738" t="n">
-        <v>21.5078182220459</v>
+        <v>21.5078201293945</v>
       </c>
       <c r="H738" t="n">
         <v>74571</v>
@@ -22061,7 +22061,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715553283691</v>
+        <v>27.8715534210205</v>
       </c>
       <c r="H748" t="n">
         <v>89948</v>
@@ -22148,7 +22148,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363185882568</v>
+        <v>26.2363166809082</v>
       </c>
       <c r="H751" t="n">
         <v>69130</v>
@@ -22206,7 +22206,7 @@
         <v>31.8285446166992</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6091346740723</v>
+        <v>24.6091365814209</v>
       </c>
       <c r="H753" t="n">
         <v>76863</v>
@@ -22264,7 +22264,7 @@
         <v>32.9329071044922</v>
       </c>
       <c r="G755" t="n">
-        <v>25.463005065918</v>
+        <v>25.4630031585693</v>
       </c>
       <c r="H755" t="n">
         <v>93592</v>
@@ -22351,7 +22351,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983108520508</v>
+        <v>24.1983089447021</v>
       </c>
       <c r="H758" t="n">
         <v>28653</v>
@@ -22467,7 +22467,7 @@
         <v>30.9325523376465</v>
       </c>
       <c r="G762" t="n">
-        <v>23.9163722991943</v>
+        <v>23.916374206543</v>
       </c>
       <c r="H762" t="n">
         <v>60399</v>
@@ -22496,7 +22496,7 @@
         <v>31.1617584228516</v>
       </c>
       <c r="G763" t="n">
-        <v>24.0935897827148</v>
+        <v>24.0935916900635</v>
       </c>
       <c r="H763" t="n">
         <v>61156</v>
@@ -22583,7 +22583,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399719238281</v>
+        <v>24.4399738311768</v>
       </c>
       <c r="H766" t="n">
         <v>84803</v>
@@ -22641,7 +22641,7 @@
         <v>31.9744033813477</v>
       </c>
       <c r="G768" t="n">
-        <v>24.7219123840332</v>
+        <v>24.7219104766846</v>
       </c>
       <c r="H768" t="n">
         <v>89969</v>
@@ -22757,7 +22757,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058681488037</v>
+        <v>21.8058700561523</v>
       </c>
       <c r="H772" t="n">
         <v>398596</v>
@@ -22786,7 +22786,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G773" t="n">
-        <v>20.13840675354</v>
+        <v>20.1384086608887</v>
       </c>
       <c r="H773" t="n">
         <v>541685</v>
@@ -22873,7 +22873,7 @@
         <v>25.5774383544922</v>
       </c>
       <c r="G776" t="n">
-        <v>19.7759170532227</v>
+        <v>19.775915145874</v>
       </c>
       <c r="H776" t="n">
         <v>194733</v>
@@ -22931,7 +22931,7 @@
         <v>25.2336273193359</v>
       </c>
       <c r="G778" t="n">
-        <v>19.5100917816162</v>
+        <v>19.5100898742676</v>
       </c>
       <c r="H778" t="n">
         <v>81516</v>
@@ -23047,7 +23047,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189598083496</v>
+        <v>20.2189617156982</v>
       </c>
       <c r="H782" t="n">
         <v>91503</v>
@@ -23134,7 +23134,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H785" t="n">
         <v>94288</v>
@@ -23221,7 +23221,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G788" t="n">
-        <v>19.3328723907471</v>
+        <v>19.3328704833984</v>
       </c>
       <c r="H788" t="n">
         <v>72501</v>
@@ -23511,7 +23511,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083866119385</v>
+        <v>21.0083885192871</v>
       </c>
       <c r="H798" t="n">
         <v>100025</v>
@@ -23830,7 +23830,7 @@
         <v>28.213321685791</v>
       </c>
       <c r="G809" t="n">
-        <v>21.8139247894287</v>
+        <v>21.8139228820801</v>
       </c>
       <c r="H809" t="n">
         <v>93205</v>
@@ -23975,7 +23975,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G814" t="n">
-        <v>20.2109069824219</v>
+        <v>20.2109050750732</v>
       </c>
       <c r="H814" t="n">
         <v>72125</v>
@@ -24062,7 +24062,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908916473389</v>
+        <v>20.7908935546875</v>
       </c>
       <c r="H817" t="n">
         <v>135708</v>
@@ -24149,7 +24149,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G820" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H820" t="n">
         <v>116471</v>
@@ -24178,7 +24178,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5009002685547</v>
+        <v>20.5008983612061</v>
       </c>
       <c r="H821" t="n">
         <v>75021</v>
@@ -24207,7 +24207,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H822" t="n">
         <v>72133</v>
@@ -24236,7 +24236,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G823" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H823" t="n">
         <v>50892</v>
@@ -24265,7 +24265,7 @@
         <v>25.9837608337402</v>
       </c>
       <c r="G824" t="n">
-        <v>20.0900764465332</v>
+        <v>20.0900783538818</v>
       </c>
       <c r="H824" t="n">
         <v>122105</v>
@@ -24294,7 +24294,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G825" t="n">
-        <v>20.13840675354</v>
+        <v>20.1384086608887</v>
       </c>
       <c r="H825" t="n">
         <v>67600</v>
@@ -24381,7 +24381,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G828" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H828" t="n">
         <v>55529</v>
@@ -24410,7 +24410,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G829" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H829" t="n">
         <v>73545</v>
@@ -24468,7 +24468,7 @@
         <v>26.5671977996826</v>
       </c>
       <c r="G831" t="n">
-        <v>20.5411758422852</v>
+        <v>20.5411777496338</v>
       </c>
       <c r="H831" t="n">
         <v>63160</v>
@@ -24526,7 +24526,7 @@
         <v>26.3171520233154</v>
       </c>
       <c r="G833" t="n">
-        <v>20.3478469848633</v>
+        <v>20.3478450775146</v>
       </c>
       <c r="H833" t="n">
         <v>51548</v>
@@ -24555,7 +24555,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G834" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H834" t="n">
         <v>86286</v>
@@ -24874,7 +24874,7 @@
         <v>28.2341575622559</v>
       </c>
       <c r="G845" t="n">
-        <v>21.8300323486328</v>
+        <v>21.8300342559814</v>
       </c>
       <c r="H845" t="n">
         <v>92713</v>
@@ -24990,7 +24990,7 @@
         <v>27.5882110595703</v>
       </c>
       <c r="G849" t="n">
-        <v>21.3306007385254</v>
+        <v>21.330602645874</v>
       </c>
       <c r="H849" t="n">
         <v>65057</v>
@@ -25019,7 +25019,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150596618652</v>
+        <v>20.8150615692139</v>
       </c>
       <c r="H850" t="n">
         <v>79359</v>
@@ -25048,7 +25048,7 @@
         <v>26.5671977996826</v>
       </c>
       <c r="G851" t="n">
-        <v>20.5411758422852</v>
+        <v>20.5411777496338</v>
       </c>
       <c r="H851" t="n">
         <v>87555</v>
@@ -25106,7 +25106,7 @@
         <v>25.3169765472412</v>
       </c>
       <c r="G853" t="n">
-        <v>19.5745315551758</v>
+        <v>19.5745334625244</v>
       </c>
       <c r="H853" t="n">
         <v>88528</v>
@@ -25251,7 +25251,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H858" t="n">
         <v>84494</v>
@@ -25367,7 +25367,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H862" t="n">
         <v>131429</v>
@@ -25454,7 +25454,7 @@
         <v>22.2747707366943</v>
       </c>
       <c r="G865" t="n">
-        <v>17.2223682403564</v>
+        <v>17.2223663330078</v>
       </c>
       <c r="H865" t="n">
         <v>109629</v>
@@ -25512,7 +25512,7 @@
         <v>21.8580303192139</v>
       </c>
       <c r="G867" t="n">
-        <v>16.9001522064209</v>
+        <v>16.9001502990723</v>
       </c>
       <c r="H867" t="n">
         <v>72401</v>
@@ -25831,7 +25831,7 @@
         <v>21.0662231445312</v>
       </c>
       <c r="G878" t="n">
-        <v>16.2879447937012</v>
+        <v>16.2879428863525</v>
       </c>
       <c r="H878" t="n">
         <v>56625</v>
@@ -25860,7 +25860,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.1107273101807</v>
+        <v>16.110725402832</v>
       </c>
       <c r="H879" t="n">
         <v>44522</v>
@@ -25947,7 +25947,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G882" t="n">
-        <v>16.9162616729736</v>
+        <v>16.9162635803223</v>
       </c>
       <c r="H882" t="n">
         <v>129721</v>
@@ -25976,7 +25976,7 @@
         <v>22.2539348602295</v>
       </c>
       <c r="G883" t="n">
-        <v>17.2062549591064</v>
+        <v>17.2062568664551</v>
       </c>
       <c r="H883" t="n">
         <v>82411</v>
@@ -26063,7 +26063,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290355682373</v>
+        <v>17.0290374755859</v>
       </c>
       <c r="H886" t="n">
         <v>60342</v>
@@ -26121,7 +26121,7 @@
         <v>22.4623031616211</v>
       </c>
       <c r="G888" t="n">
-        <v>17.3673610687256</v>
+        <v>17.3673629760742</v>
       </c>
       <c r="H888" t="n">
         <v>52523</v>
@@ -26179,7 +26179,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H890" t="n">
         <v>95871</v>
@@ -26208,7 +26208,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G891" t="n">
-        <v>19.1878757476807</v>
+        <v>19.187873840332</v>
       </c>
       <c r="H891" t="n">
         <v>189581</v>
@@ -26411,7 +26411,7 @@
         <v>35.4854393005371</v>
       </c>
       <c r="G898" t="n">
-        <v>27.4365653991699</v>
+        <v>27.4365673065186</v>
       </c>
       <c r="H898" t="n">
         <v>324224</v>
@@ -26730,7 +26730,7 @@
         <v>29.4427051544189</v>
       </c>
       <c r="G909" t="n">
-        <v>22.7644557952881</v>
+        <v>22.7644577026367</v>
       </c>
       <c r="H909" t="n">
         <v>66556</v>
@@ -26846,7 +26846,7 @@
         <v>27.1923065185547</v>
       </c>
       <c r="G913" t="n">
-        <v>21.0244979858398</v>
+        <v>21.0244960784912</v>
       </c>
       <c r="H913" t="n">
         <v>226257</v>
@@ -26962,7 +26962,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G917" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H917" t="n">
         <v>101465</v>
@@ -26991,7 +26991,7 @@
         <v>24.7752132415771</v>
       </c>
       <c r="G918" t="n">
-        <v>19.1556549072266</v>
+        <v>19.1556529998779</v>
       </c>
       <c r="H918" t="n">
         <v>269232</v>
@@ -27020,7 +27020,7 @@
         <v>25.0877685546875</v>
       </c>
       <c r="G919" t="n">
-        <v>19.3973140716553</v>
+        <v>19.3973159790039</v>
       </c>
       <c r="H919" t="n">
         <v>122716</v>
@@ -27049,7 +27049,7 @@
         <v>26.9005889892578</v>
       </c>
       <c r="G920" t="n">
-        <v>20.7989482879639</v>
+        <v>20.7989463806152</v>
       </c>
       <c r="H920" t="n">
         <v>193491</v>
@@ -27194,7 +27194,7 @@
         <v>27.5882110595703</v>
       </c>
       <c r="G925" t="n">
-        <v>21.3306007385254</v>
+        <v>21.330602645874</v>
       </c>
       <c r="H925" t="n">
         <v>85266</v>
@@ -27310,7 +27310,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.6850357055664</v>
+        <v>21.685037612915</v>
       </c>
       <c r="H929" t="n">
         <v>97800</v>
@@ -27339,7 +27339,7 @@
         <v>28.0674629211426</v>
       </c>
       <c r="G930" t="n">
-        <v>21.701150894165</v>
+        <v>21.7011489868164</v>
       </c>
       <c r="H930" t="n">
         <v>138426</v>
@@ -27368,7 +27368,7 @@
         <v>31.7556133270264</v>
       </c>
       <c r="G931" t="n">
-        <v>24.5527458190918</v>
+        <v>24.5527477264404</v>
       </c>
       <c r="H931" t="n">
         <v>595323</v>
@@ -27455,7 +27455,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.583833694458</v>
+        <v>25.5838356018066</v>
       </c>
       <c r="H934" t="n">
         <v>517926</v>
@@ -27542,7 +27542,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516109466553</v>
+        <v>25.5516128540039</v>
       </c>
       <c r="H937" t="n">
         <v>279125</v>
@@ -27629,7 +27629,7 @@
         <v>33.4434127807617</v>
       </c>
       <c r="G940" t="n">
-        <v>25.8577175140381</v>
+        <v>25.8577156066895</v>
       </c>
       <c r="H940" t="n">
         <v>218952</v>
@@ -27774,7 +27774,7 @@
         <v>33.7976417541504</v>
       </c>
       <c r="G945" t="n">
-        <v>26.1315994262695</v>
+        <v>26.1315975189209</v>
       </c>
       <c r="H945" t="n">
         <v>97707</v>
@@ -27977,7 +27977,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G952" t="n">
-        <v>24.2466449737549</v>
+        <v>24.2466430664062</v>
       </c>
       <c r="H952" t="n">
         <v>91792</v>
@@ -28064,7 +28064,7 @@
         <v>30.3178596496582</v>
       </c>
       <c r="G955" t="n">
-        <v>23.4411067962646</v>
+        <v>23.4411087036133</v>
       </c>
       <c r="H955" t="n">
         <v>170866</v>
@@ -28122,7 +28122,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G957" t="n">
-        <v>24.2466449737549</v>
+        <v>24.2466430664062</v>
       </c>
       <c r="H957" t="n">
         <v>141695</v>
@@ -28151,7 +28151,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727592468262</v>
       </c>
       <c r="H958" t="n">
         <v>106089</v>
@@ -28238,7 +28238,7 @@
         <v>30.5887413024902</v>
       </c>
       <c r="G961" t="n">
-        <v>23.6505470275879</v>
+        <v>23.6505451202393</v>
       </c>
       <c r="H961" t="n">
         <v>140338</v>
@@ -28557,7 +28557,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G972" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H972" t="n">
         <v>39949</v>
@@ -28615,7 +28615,7 @@
         <v>30.5470676422119</v>
       </c>
       <c r="G974" t="n">
-        <v>23.6183242797852</v>
+        <v>23.6183261871338</v>
       </c>
       <c r="H974" t="n">
         <v>118306</v>
@@ -28644,7 +28644,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.3122215270996</v>
+        <v>23.312219619751</v>
       </c>
       <c r="H975" t="n">
         <v>121812</v>
@@ -28731,7 +28731,7 @@
         <v>31.2346897125244</v>
       </c>
       <c r="G978" t="n">
-        <v>24.1499805450439</v>
+        <v>24.1499786376953</v>
       </c>
       <c r="H978" t="n">
         <v>163262</v>
@@ -28876,7 +28876,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G983" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H983" t="n">
         <v>59846</v>
@@ -28963,7 +28963,7 @@
         <v>30.7971115112305</v>
       </c>
       <c r="G986" t="n">
-        <v>23.8116550445557</v>
+        <v>23.811653137207</v>
       </c>
       <c r="H986" t="n">
         <v>68207</v>
@@ -28992,7 +28992,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H987" t="n">
         <v>52930</v>
@@ -29021,7 +29021,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G988" t="n">
-        <v>23.9244289398193</v>
+        <v>23.9244270324707</v>
       </c>
       <c r="H988" t="n">
         <v>68067</v>
@@ -29108,7 +29108,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H991" t="n">
         <v>68666</v>
@@ -29195,7 +29195,7 @@
         <v>30.776273727417</v>
       </c>
       <c r="G994" t="n">
-        <v>23.7955417633057</v>
+        <v>23.7955436706543</v>
       </c>
       <c r="H994" t="n">
         <v>129866</v>
@@ -29224,7 +29224,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727592468262</v>
       </c>
       <c r="H995" t="n">
         <v>242944</v>
@@ -29282,7 +29282,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H997" t="n">
         <v>75104</v>
@@ -29311,7 +29311,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544509887695</v>
+        <v>23.0544490814209</v>
       </c>
       <c r="H998" t="n">
         <v>173291</v>
@@ -29427,7 +29427,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1002" t="n">
-        <v>22.635570526123</v>
+        <v>22.6355686187744</v>
       </c>
       <c r="H1002" t="n">
         <v>70616</v>
@@ -29485,7 +29485,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1004" t="n">
-        <v>23.0866718292236</v>
+        <v>23.086669921875</v>
       </c>
       <c r="H1004" t="n">
         <v>49988</v>
@@ -29601,7 +29601,7 @@
         <v>29.2968463897705</v>
       </c>
       <c r="G1008" t="n">
-        <v>22.6516819000244</v>
+        <v>22.651683807373</v>
       </c>
       <c r="H1008" t="n">
         <v>46369</v>
@@ -29920,7 +29920,7 @@
         <v>28.609224319458</v>
       </c>
       <c r="G1019" t="n">
-        <v>22.1200294494629</v>
+        <v>22.1200275421143</v>
       </c>
       <c r="H1019" t="n">
         <v>72155</v>
@@ -30007,7 +30007,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.71044921875</v>
+        <v>27.7104473114014</v>
       </c>
       <c r="H1022" t="n">
         <v>1331456</v>
@@ -30036,7 +30036,7 @@
         <v>33.9643363952637</v>
       </c>
       <c r="G1023" t="n">
-        <v>26.2604846954346</v>
+        <v>26.2604827880859</v>
       </c>
       <c r="H1023" t="n">
         <v>837731</v>
@@ -30297,7 +30297,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1032" t="n">
         <v>254966</v>
@@ -30326,7 +30326,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.6276264190674</v>
+        <v>29.627628326416</v>
       </c>
       <c r="H1033" t="n">
         <v>422202</v>
@@ -30413,7 +30413,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326633453369</v>
+        <v>28.0326614379883</v>
       </c>
       <c r="H1036" t="n">
         <v>264193</v>
@@ -30500,7 +30500,7 @@
         <v>37.2774238586426</v>
       </c>
       <c r="G1039" t="n">
-        <v>28.8220901489258</v>
+        <v>28.8220882415771</v>
       </c>
       <c r="H1039" t="n">
         <v>439132</v>
@@ -30587,7 +30587,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1042" t="n">
         <v>912645</v>
@@ -30616,7 +30616,7 @@
         <v>36.1105499267578</v>
       </c>
       <c r="G1043" t="n">
-        <v>27.919885635376</v>
+        <v>27.9198875427246</v>
       </c>
       <c r="H1043" t="n">
         <v>263584</v>
@@ -30645,7 +30645,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8382015228271</v>
+        <v>28.8381996154785</v>
       </c>
       <c r="H1044" t="n">
         <v>248431</v>
@@ -30732,7 +30732,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737579345703</v>
+        <v>28.7737560272217</v>
       </c>
       <c r="H1047" t="n">
         <v>145626</v>
@@ -30761,7 +30761,7 @@
         <v>37.5274696350098</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.0154190063477</v>
+        <v>29.0154209136963</v>
       </c>
       <c r="H1048" t="n">
         <v>161694</v>
@@ -30906,7 +30906,7 @@
         <v>37.7566757202148</v>
       </c>
       <c r="G1053" t="n">
-        <v>29.1926364898682</v>
+        <v>29.1926383972168</v>
       </c>
       <c r="H1053" t="n">
         <v>774052</v>
@@ -30935,7 +30935,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.982063293457</v>
+        <v>29.9820613861084</v>
       </c>
       <c r="H1054" t="n">
         <v>787822</v>
@@ -30964,7 +30964,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770244598389</v>
+        <v>31.5770225524902</v>
       </c>
       <c r="H1055" t="n">
         <v>622084</v>
@@ -30993,7 +30993,7 @@
         <v>39.3819618225098</v>
       </c>
       <c r="G1056" t="n">
-        <v>30.4492721557617</v>
+        <v>30.4492740631104</v>
       </c>
       <c r="H1056" t="n">
         <v>399174</v>
@@ -31080,7 +31080,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571491241455</v>
+        <v>26.3571472167969</v>
       </c>
       <c r="H1059" t="n">
         <v>364508</v>
@@ -31109,7 +31109,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610511779785</v>
+        <v>25.7610492706299</v>
       </c>
       <c r="H1060" t="n">
         <v>600964</v>
@@ -31167,7 +31167,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1062" t="n">
-        <v>23.0383377075195</v>
+        <v>23.0383396148682</v>
       </c>
       <c r="H1062" t="n">
         <v>516650</v>
@@ -31196,7 +31196,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.2995147705078</v>
+        <v>20.2995128631592</v>
       </c>
       <c r="H1063" t="n">
         <v>342146</v>
@@ -31225,7 +31225,7 @@
         <v>24.6085166931152</v>
       </c>
       <c r="G1064" t="n">
-        <v>19.0267677307129</v>
+        <v>19.0267696380615</v>
       </c>
       <c r="H1064" t="n">
         <v>440901</v>
@@ -31283,7 +31283,7 @@
         <v>20.8578548431396</v>
       </c>
       <c r="G1066" t="n">
-        <v>16.126838684082</v>
+        <v>16.1268367767334</v>
       </c>
       <c r="H1066" t="n">
         <v>607780</v>
@@ -31341,7 +31341,7 @@
         <v>21.0453872680664</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.2718334197998</v>
+        <v>16.2718353271484</v>
       </c>
       <c r="H1068" t="n">
         <v>439578</v>
@@ -31370,7 +31370,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1069" t="n">
-        <v>17.07737159729</v>
+        <v>17.0773696899414</v>
       </c>
       <c r="H1069" t="n">
         <v>307976</v>
@@ -31573,7 +31573,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1076" t="n">
         <v>255584</v>
@@ -31718,7 +31718,7 @@
         <v>23.6708507537842</v>
       </c>
       <c r="G1081" t="n">
-        <v>18.3017845153809</v>
+        <v>18.3017864227295</v>
       </c>
       <c r="H1081" t="n">
         <v>80116</v>
@@ -31747,7 +31747,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1082" t="n">
         <v>65084</v>
@@ -31805,7 +31805,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1084" t="n">
         <v>220735</v>
@@ -31863,7 +31863,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1086" t="n">
         <v>126056</v>
@@ -31950,7 +31950,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1089" t="n">
         <v>85682</v>
@@ -32037,7 +32037,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1092" t="n">
-        <v>17.399585723877</v>
+        <v>17.3995838165283</v>
       </c>
       <c r="H1092" t="n">
         <v>95086</v>
@@ -32298,7 +32298,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1101" t="n">
         <v>70876</v>
@@ -32733,7 +32733,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1116" t="n">
-        <v>16.9162616729736</v>
+        <v>16.9162635803223</v>
       </c>
       <c r="H1116" t="n">
         <v>88021</v>
@@ -32762,7 +32762,7 @@
         <v>22.8790454864502</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.6895790100098</v>
+        <v>17.6895771026611</v>
       </c>
       <c r="H1117" t="n">
         <v>312068</v>
@@ -32849,7 +32849,7 @@
         <v>27.8174171447754</v>
       </c>
       <c r="G1120" t="n">
-        <v>21.5078182220459</v>
+        <v>21.5078201293945</v>
       </c>
       <c r="H1120" t="n">
         <v>741547</v>
@@ -32936,7 +32936,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.635570526123</v>
+        <v>22.6355686187744</v>
       </c>
       <c r="H1123" t="n">
         <v>408833</v>
@@ -33023,7 +33023,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1126" t="n">
         <v>401649</v>
@@ -33081,7 +33081,7 @@
         <v>28.4633655548096</v>
       </c>
       <c r="G1128" t="n">
-        <v>22.007251739502</v>
+        <v>22.0072536468506</v>
       </c>
       <c r="H1128" t="n">
         <v>243052</v>
@@ -33139,7 +33139,7 @@
         <v>29.2134971618652</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.5872383117676</v>
+        <v>22.5872364044189</v>
       </c>
       <c r="H1130" t="n">
         <v>133679</v>
@@ -33168,7 +33168,7 @@
         <v>30.5470676422119</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.6183242797852</v>
+        <v>23.6183261871338</v>
       </c>
       <c r="H1131" t="n">
         <v>259143</v>
@@ -33197,7 +33197,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1132" t="n">
         <v>117120</v>
@@ -33371,7 +33371,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021457672119</v>
+        <v>26.5021476745605</v>
       </c>
       <c r="H1138" t="n">
         <v>299299</v>
@@ -33400,7 +33400,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.2293949127197</v>
+        <v>25.2293968200684</v>
       </c>
       <c r="H1139" t="n">
         <v>249320</v>
@@ -33429,7 +33429,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.0349349975586</v>
+        <v>26.03493309021</v>
       </c>
       <c r="H1140" t="n">
         <v>192736</v>
@@ -33458,7 +33458,7 @@
         <v>32.859977722168</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.4066162109375</v>
+        <v>25.4066181182861</v>
       </c>
       <c r="H1141" t="n">
         <v>424729</v>
@@ -33487,7 +33487,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460765838623</v>
+        <v>24.7460746765137</v>
       </c>
       <c r="H1142" t="n">
         <v>259051</v>
@@ -33574,7 +33574,7 @@
         <v>32.8808135986328</v>
       </c>
       <c r="G1145" t="n">
-        <v>25.4227275848389</v>
+        <v>25.4227256774902</v>
       </c>
       <c r="H1145" t="n">
         <v>211348</v>
@@ -33632,7 +33632,7 @@
         <v>31.5889186859131</v>
       </c>
       <c r="G1147" t="n">
-        <v>24.4238624572754</v>
+        <v>24.4238605499268</v>
       </c>
       <c r="H1147" t="n">
         <v>65647</v>
@@ -33748,7 +33748,7 @@
         <v>31.7764511108398</v>
       </c>
       <c r="G1151" t="n">
-        <v>24.5688591003418</v>
+        <v>24.5688571929932</v>
       </c>
       <c r="H1151" t="n">
         <v>53540</v>
@@ -34067,7 +34067,7 @@
         <v>33.4017372131348</v>
       </c>
       <c r="G1162" t="n">
-        <v>25.8254928588867</v>
+        <v>25.8254947662354</v>
       </c>
       <c r="H1162" t="n">
         <v>201608</v>
@@ -34415,7 +34415,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1174" t="n">
-        <v>23.0383377075195</v>
+        <v>23.0383396148682</v>
       </c>
       <c r="H1174" t="n">
         <v>198986</v>
@@ -34473,7 +34473,7 @@
         <v>28.88010597229</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.3294658660889</v>
+        <v>22.3294677734375</v>
       </c>
       <c r="H1176" t="n">
         <v>108064</v>
@@ -34531,7 +34531,7 @@
         <v>30.2970237731934</v>
       </c>
       <c r="G1178" t="n">
-        <v>23.4249973297119</v>
+        <v>23.4249954223633</v>
       </c>
       <c r="H1178" t="n">
         <v>90363</v>
@@ -34647,7 +34647,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.2316703796387</v>
+        <v>23.23166847229</v>
       </c>
       <c r="H1182" t="n">
         <v>79634</v>
@@ -34676,7 +34676,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.0866718292236</v>
+        <v>23.086669921875</v>
       </c>
       <c r="H1183" t="n">
         <v>53322</v>
@@ -34705,7 +34705,7 @@
         <v>30.6720886230469</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.7149887084961</v>
+        <v>23.7149906158447</v>
       </c>
       <c r="H1184" t="n">
         <v>210874</v>
@@ -34734,7 +34734,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.0866718292236</v>
+        <v>23.086669921875</v>
       </c>
       <c r="H1185" t="n">
         <v>108022</v>
@@ -34763,7 +34763,7 @@
         <v>29.9011192321777</v>
       </c>
       <c r="G1186" t="n">
-        <v>23.1188907623291</v>
+        <v>23.1188926696777</v>
       </c>
       <c r="H1186" t="n">
         <v>142772</v>
@@ -34792,7 +34792,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1187" t="n">
-        <v>23.0383377075195</v>
+        <v>23.0383396148682</v>
       </c>
       <c r="H1187" t="n">
         <v>68126</v>
@@ -34879,7 +34879,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094543457031</v>
+        <v>22.9094524383545</v>
       </c>
       <c r="H1190" t="n">
         <v>71944</v>
@@ -34937,7 +34937,7 @@
         <v>29.4010314941406</v>
       </c>
       <c r="G1192" t="n">
-        <v>22.7322368621826</v>
+        <v>22.732234954834</v>
       </c>
       <c r="H1192" t="n">
         <v>80247</v>
@@ -34995,7 +34995,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.94167137146</v>
+        <v>22.9416732788086</v>
       </c>
       <c r="H1194" t="n">
         <v>35197</v>
@@ -35140,7 +35140,7 @@
         <v>28.0049514770508</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.6528167724609</v>
+        <v>21.6528186798096</v>
       </c>
       <c r="H1199" t="n">
         <v>87498</v>
@@ -35430,7 +35430,7 @@
         <v>28.2758312225342</v>
       </c>
       <c r="G1209" t="n">
-        <v>21.8622550964355</v>
+        <v>21.8622531890869</v>
       </c>
       <c r="H1209" t="n">
         <v>84042</v>
@@ -35459,7 +35459,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039161682129</v>
+        <v>22.1039180755615</v>
       </c>
       <c r="H1210" t="n">
         <v>66037</v>
@@ -35488,7 +35488,7 @@
         <v>28.9842910766602</v>
       </c>
       <c r="G1211" t="n">
-        <v>22.4100208282471</v>
+        <v>22.4100189208984</v>
       </c>
       <c r="H1211" t="n">
         <v>95686</v>
@@ -35517,7 +35517,7 @@
         <v>27.7757434844971</v>
       </c>
       <c r="G1212" t="n">
-        <v>21.4755992889404</v>
+        <v>21.4755973815918</v>
       </c>
       <c r="H1212" t="n">
         <v>157370</v>
@@ -35633,7 +35633,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1216" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H1216" t="n">
         <v>408334</v>
@@ -35720,7 +35720,7 @@
         <v>24.2334518432617</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.7367763519287</v>
+        <v>18.7367744445801</v>
       </c>
       <c r="H1219" t="n">
         <v>241385</v>
@@ -35807,7 +35807,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1222" t="n">
         <v>166257</v>
@@ -35836,7 +35836,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1223" t="n">
         <v>87232</v>
@@ -35894,7 +35894,7 @@
         <v>23.3791332244873</v>
       </c>
       <c r="G1225" t="n">
-        <v>18.0762367248535</v>
+        <v>18.0762348175049</v>
       </c>
       <c r="H1225" t="n">
         <v>105717</v>
@@ -36126,7 +36126,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.399585723877</v>
+        <v>17.3995838165283</v>
       </c>
       <c r="H1233" t="n">
         <v>394163</v>
@@ -36213,7 +36213,7 @@
         <v>23.6500148773193</v>
       </c>
       <c r="G1236" t="n">
-        <v>18.2856731414795</v>
+        <v>18.2856750488281</v>
       </c>
       <c r="H1236" t="n">
         <v>245630</v>
@@ -36387,7 +36387,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H1242" t="n">
         <v>245897</v>
@@ -36416,7 +36416,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967456817627</v>
+        <v>19.8967475891113</v>
       </c>
       <c r="H1243" t="n">
         <v>239601</v>
@@ -36503,7 +36503,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G1246" t="n">
-        <v>20.1706295013428</v>
+        <v>20.1706314086914</v>
       </c>
       <c r="H1246" t="n">
         <v>327050</v>
@@ -36532,7 +36532,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G1247" t="n">
-        <v>19.3328723907471</v>
+        <v>19.3328704833984</v>
       </c>
       <c r="H1247" t="n">
         <v>451275</v>
@@ -36561,7 +36561,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884441375732</v>
+        <v>18.6884422302246</v>
       </c>
       <c r="H1248" t="n">
         <v>312209</v>
@@ -36648,7 +36648,7 @@
         <v>25.1086044311523</v>
       </c>
       <c r="G1251" t="n">
-        <v>19.4134254455566</v>
+        <v>19.413423538208</v>
       </c>
       <c r="H1251" t="n">
         <v>488244</v>
@@ -36967,7 +36967,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1262" t="n">
         <v>79845</v>
@@ -37083,7 +37083,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1266" t="n">
-        <v>16.9162616729736</v>
+        <v>16.9162635803223</v>
       </c>
       <c r="H1266" t="n">
         <v>116876</v>
@@ -37112,7 +37112,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1267" t="n">
-        <v>16.9162616729736</v>
+        <v>16.9162635803223</v>
       </c>
       <c r="H1267" t="n">
         <v>88925</v>
@@ -37315,7 +37315,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H1274" t="n">
         <v>234349</v>
@@ -37576,7 +37576,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1283" t="n">
         <v>188315</v>
@@ -37605,7 +37605,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1284" t="n">
-        <v>17.399585723877</v>
+        <v>17.3995838165283</v>
       </c>
       <c r="H1284" t="n">
         <v>99256</v>
@@ -37692,7 +37692,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1287" t="n">
-        <v>17.1901454925537</v>
+        <v>17.1901473999023</v>
       </c>
       <c r="H1287" t="n">
         <v>74707</v>
@@ -37721,7 +37721,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934791564941</v>
+        <v>17.0934810638428</v>
       </c>
       <c r="H1288" t="n">
         <v>71228</v>
@@ -37750,7 +37750,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1289" t="n">
-        <v>17.07737159729</v>
+        <v>17.0773696899414</v>
       </c>
       <c r="H1289" t="n">
         <v>72279</v>
@@ -37779,7 +37779,7 @@
         <v>21.5038013458252</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.6262702941895</v>
+        <v>16.6262683868408</v>
       </c>
       <c r="H1290" t="n">
         <v>126746</v>
@@ -37895,7 +37895,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1294" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1294" t="n">
         <v>170814</v>
@@ -38011,7 +38011,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.9439449310303</v>
+        <v>20.9439430236816</v>
       </c>
       <c r="H1298" t="n">
         <v>910482</v>
@@ -38098,7 +38098,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.5895080566406</v>
+        <v>20.5895099639893</v>
       </c>
       <c r="H1301" t="n">
         <v>361172</v>
@@ -38156,7 +38156,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.5895080566406</v>
+        <v>20.5895099639893</v>
       </c>
       <c r="H1303" t="n">
         <v>234506</v>
@@ -38185,7 +38185,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H1304" t="n">
         <v>141753</v>
@@ -38446,7 +38446,7 @@
         <v>25.1086044311523</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.4134254455566</v>
+        <v>19.413423538208</v>
       </c>
       <c r="H1313" t="n">
         <v>127568</v>
@@ -38533,7 +38533,7 @@
         <v>25.504508972168</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.7195281982422</v>
+        <v>19.7195301055908</v>
       </c>
       <c r="H1316" t="n">
         <v>192020</v>
@@ -38620,7 +38620,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1319" t="n">
         <v>101081</v>
@@ -38649,7 +38649,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1320" t="n">
         <v>181732</v>
@@ -38678,7 +38678,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1321" t="n">
         <v>147765</v>
@@ -38707,7 +38707,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395416259766</v>
+        <v>19.1395435333252</v>
       </c>
       <c r="H1322" t="n">
         <v>105576</v>
@@ -38736,7 +38736,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.075101852417</v>
+        <v>19.0750999450684</v>
       </c>
       <c r="H1323" t="n">
         <v>120557</v>
@@ -38794,7 +38794,7 @@
         <v>24.4834957122803</v>
       </c>
       <c r="G1325" t="n">
-        <v>18.930103302002</v>
+        <v>18.9301052093506</v>
       </c>
       <c r="H1325" t="n">
         <v>183528</v>
@@ -38823,7 +38823,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1326" t="n">
-        <v>18.9784355163574</v>
+        <v>18.9784374237061</v>
       </c>
       <c r="H1326" t="n">
         <v>76196</v>
@@ -38852,7 +38852,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1327" t="n">
         <v>104855</v>
@@ -38910,7 +38910,7 @@
         <v>24.0250816345215</v>
       </c>
       <c r="G1329" t="n">
-        <v>18.5756702423096</v>
+        <v>18.5756683349609</v>
       </c>
       <c r="H1329" t="n">
         <v>59340</v>
@@ -39084,7 +39084,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153774261475</v>
+        <v>19.1153793334961</v>
       </c>
       <c r="H1335" t="n">
         <v>175794</v>
@@ -39113,7 +39113,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.8334407806396</v>
+        <v>18.833438873291</v>
       </c>
       <c r="H1336" t="n">
         <v>97937</v>
@@ -39142,7 +39142,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353908538818</v>
+        <v>18.5353889465332</v>
       </c>
       <c r="H1337" t="n">
         <v>143301</v>
@@ -39171,7 +39171,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1338" t="n">
-        <v>18.4870586395264</v>
+        <v>18.4870567321777</v>
       </c>
       <c r="H1338" t="n">
         <v>70075</v>
@@ -39200,7 +39200,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1339" t="n">
         <v>83809</v>
@@ -39258,7 +39258,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.3328723907471</v>
+        <v>19.3328704833984</v>
       </c>
       <c r="H1341" t="n">
         <v>461267</v>
@@ -39316,7 +39316,7 @@
         <v>24.4418201446533</v>
       </c>
       <c r="G1343" t="n">
-        <v>18.8978824615479</v>
+        <v>18.8978805541992</v>
       </c>
       <c r="H1343" t="n">
         <v>117770</v>
@@ -39345,7 +39345,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864921569824</v>
+        <v>18.9864902496338</v>
       </c>
       <c r="H1344" t="n">
         <v>82258</v>
@@ -39403,7 +39403,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112247467041</v>
+        <v>18.5112228393555</v>
       </c>
       <c r="H1346" t="n">
         <v>91238</v>
@@ -39577,7 +39577,7 @@
         <v>23.5875034332275</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.2373428344727</v>
+        <v>18.237340927124</v>
       </c>
       <c r="H1352" t="n">
         <v>119737</v>
@@ -39693,7 +39693,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187110900879</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1356" t="n">
         <v>228828</v>
@@ -39838,7 +39838,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1361" t="n">
         <v>157303</v>
@@ -39954,7 +39954,7 @@
         <v>26.4525928497314</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.4525661468506</v>
+        <v>20.4525680541992</v>
       </c>
       <c r="H1365" t="n">
         <v>970320</v>
@@ -39983,7 +39983,7 @@
         <v>25.4628353118896</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.6873092651367</v>
+        <v>19.6873073577881</v>
       </c>
       <c r="H1366" t="n">
         <v>576263</v>
@@ -40012,7 +40012,7 @@
         <v>25.3169765472412</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.5745315551758</v>
+        <v>19.5745334625244</v>
       </c>
       <c r="H1367" t="n">
         <v>278725</v>
@@ -40041,7 +40041,7 @@
         <v>25.2127914428711</v>
       </c>
       <c r="G1368" t="n">
-        <v>19.4939785003662</v>
+        <v>19.4939804077148</v>
       </c>
       <c r="H1368" t="n">
         <v>211758</v>
@@ -40128,7 +40128,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1371" t="n">
         <v>230606</v>
@@ -40157,7 +40157,7 @@
         <v>25.0148391723633</v>
       </c>
       <c r="G1372" t="n">
-        <v>19.3409271240234</v>
+        <v>19.3409290313721</v>
       </c>
       <c r="H1372" t="n">
         <v>175588</v>
@@ -40244,7 +40244,7 @@
         <v>25.6295318603516</v>
       </c>
       <c r="G1375" t="n">
-        <v>19.8161926269531</v>
+        <v>19.8161945343018</v>
       </c>
       <c r="H1375" t="n">
         <v>312050</v>
@@ -40302,7 +40302,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531345367432</v>
+        <v>19.9531364440918</v>
       </c>
       <c r="H1377" t="n">
         <v>173483</v>
@@ -40331,7 +40331,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G1378" t="n">
-        <v>20.2109069824219</v>
+        <v>20.2109050750732</v>
       </c>
       <c r="H1378" t="n">
         <v>358719</v>
@@ -40360,7 +40360,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397922515869</v>
+        <v>20.3397941589355</v>
       </c>
       <c r="H1379" t="n">
         <v>314666</v>
@@ -40389,7 +40389,7 @@
         <v>26.2858963012695</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.3236808776855</v>
+        <v>20.3236789703369</v>
       </c>
       <c r="H1380" t="n">
         <v>657639</v>
@@ -40592,7 +40592,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G1387" t="n">
-        <v>19.1878757476807</v>
+        <v>19.187873840332</v>
       </c>
       <c r="H1387" t="n">
         <v>247944</v>
@@ -40650,7 +40650,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187110900879</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1389" t="n">
         <v>201477</v>
@@ -40737,7 +40737,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1392" t="n">
         <v>83268</v>
@@ -40795,7 +40795,7 @@
         <v>24.2021942138672</v>
       </c>
       <c r="G1394" t="n">
-        <v>18.7126083374023</v>
+        <v>18.7126064300537</v>
       </c>
       <c r="H1394" t="n">
         <v>201948</v>
@@ -40940,7 +40940,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1399" t="n">
-        <v>18.4870586395264</v>
+        <v>18.4870567321777</v>
       </c>
       <c r="H1399" t="n">
         <v>189206</v>
@@ -41201,7 +41201,7 @@
         <v>22.6602554321289</v>
       </c>
       <c r="G1408" t="n">
-        <v>17.5204162597656</v>
+        <v>17.520414352417</v>
       </c>
       <c r="H1408" t="n">
         <v>224491</v>
@@ -41317,7 +41317,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401100158691</v>
+        <v>18.6401119232178</v>
       </c>
       <c r="H1412" t="n">
         <v>692896</v>
@@ -41346,7 +41346,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1413" t="n">
         <v>387357</v>
@@ -41375,7 +41375,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1414" t="n">
         <v>234798</v>
@@ -41404,7 +41404,7 @@
         <v>23.5562477111816</v>
       </c>
       <c r="G1415" t="n">
-        <v>18.2131767272949</v>
+        <v>18.2131748199463</v>
       </c>
       <c r="H1415" t="n">
         <v>138909</v>
@@ -41578,7 +41578,7 @@
         <v>23.6500148773193</v>
       </c>
       <c r="G1421" t="n">
-        <v>18.2856731414795</v>
+        <v>18.2856750488281</v>
       </c>
       <c r="H1421" t="n">
         <v>152809</v>
@@ -41694,7 +41694,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106582641602</v>
+        <v>19.0106563568115</v>
       </c>
       <c r="H1425" t="n">
         <v>269832</v>
@@ -41752,7 +41752,7 @@
         <v>24.2230319976807</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.7287197113037</v>
+        <v>18.7287216186523</v>
       </c>
       <c r="H1427" t="n">
         <v>215889</v>
@@ -41781,7 +41781,7 @@
         <v>24.1917762756348</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.7045516967773</v>
+        <v>18.704553604126</v>
       </c>
       <c r="H1428" t="n">
         <v>192377</v>
@@ -41897,7 +41897,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292861938477</v>
+        <v>18.2292881011963</v>
       </c>
       <c r="H1432" t="n">
         <v>168351</v>
@@ -42071,7 +42071,7 @@
         <v>23.2853660583496</v>
       </c>
       <c r="G1438" t="n">
-        <v>18.0037364959717</v>
+        <v>18.0037384033203</v>
       </c>
       <c r="H1438" t="n">
         <v>138869</v>
@@ -42100,7 +42100,7 @@
         <v>23.3895511627197</v>
       </c>
       <c r="G1439" t="n">
-        <v>18.0842895507812</v>
+        <v>18.0842914581299</v>
       </c>
       <c r="H1439" t="n">
         <v>177402</v>
@@ -42158,7 +42158,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051200866699</v>
+        <v>18.2051219940186</v>
       </c>
       <c r="H1441" t="n">
         <v>161224</v>
@@ -42187,7 +42187,7 @@
         <v>23.3895511627197</v>
       </c>
       <c r="G1442" t="n">
-        <v>18.0842895507812</v>
+        <v>18.0842914581299</v>
       </c>
       <c r="H1442" t="n">
         <v>315746</v>
@@ -42274,7 +42274,7 @@
         <v>23.160343170166</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.9070701599121</v>
+        <v>17.9070720672607</v>
       </c>
       <c r="H1445" t="n">
         <v>118808</v>
@@ -42332,7 +42332,7 @@
         <v>23.3166217803955</v>
       </c>
       <c r="G1447" t="n">
-        <v>18.0279026031494</v>
+        <v>18.027904510498</v>
       </c>
       <c r="H1447" t="n">
         <v>122725</v>
@@ -42361,7 +42361,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392948150635</v>
+        <v>17.9392929077148</v>
       </c>
       <c r="H1448" t="n">
         <v>194792</v>
@@ -42506,7 +42506,7 @@
         <v>22.899881362915</v>
       </c>
       <c r="G1453" t="n">
-        <v>17.7056865692139</v>
+        <v>17.7056884765625</v>
       </c>
       <c r="H1453" t="n">
         <v>292793</v>
@@ -42564,7 +42564,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1455" t="n">
-        <v>17.07737159729</v>
+        <v>17.0773696899414</v>
       </c>
       <c r="H1455" t="n">
         <v>103335</v>
@@ -42593,7 +42593,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1456" t="n">
-        <v>17.1901454925537</v>
+        <v>17.1901473999023</v>
       </c>
       <c r="H1456" t="n">
         <v>147195</v>
@@ -42622,7 +42622,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1457" t="n">
-        <v>17.399585723877</v>
+        <v>17.3995838165283</v>
       </c>
       <c r="H1457" t="n">
         <v>107698</v>
@@ -42709,7 +42709,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1460" t="n">
         <v>158955</v>
@@ -42767,7 +42767,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.4156951904297</v>
+        <v>17.4156970977783</v>
       </c>
       <c r="H1462" t="n">
         <v>81655</v>
@@ -42825,7 +42825,7 @@
         <v>22.6706733703613</v>
       </c>
       <c r="G1464" t="n">
-        <v>17.5284690856934</v>
+        <v>17.528470993042</v>
       </c>
       <c r="H1464" t="n">
         <v>280896</v>
@@ -43028,7 +43028,7 @@
         <v>22.899881362915</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.7056865692139</v>
+        <v>17.7056884765625</v>
       </c>
       <c r="H1471" t="n">
         <v>144340</v>
@@ -43202,7 +43202,7 @@
         <v>22.6602554321289</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.5204162597656</v>
+        <v>17.520414352417</v>
       </c>
       <c r="H1477" t="n">
         <v>102803</v>
@@ -43463,7 +43463,7 @@
         <v>21.0766429901123</v>
       </c>
       <c r="G1486" t="n">
-        <v>16.2959995269775</v>
+        <v>16.2960014343262</v>
       </c>
       <c r="H1486" t="n">
         <v>123202</v>
@@ -43608,7 +43608,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765544891357</v>
+        <v>16.3765525817871</v>
       </c>
       <c r="H1491" t="n">
         <v>136046</v>
@@ -43811,7 +43811,7 @@
         <v>19.3367519378662</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.9507541656494</v>
+        <v>14.9507551193237</v>
       </c>
       <c r="H1498" t="n">
         <v>306456</v>
@@ -43840,7 +43840,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668655395508</v>
+        <v>14.9668645858765</v>
       </c>
       <c r="H1499" t="n">
         <v>131664</v>
@@ -43898,7 +43898,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867668151855</v>
+        <v>14.4867658615112</v>
       </c>
       <c r="H1501" t="n">
         <v>287038</v>
@@ -43956,7 +43956,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780071258545</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1503" t="n">
         <v>269832</v>
@@ -44014,7 +44014,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013570785522</v>
+        <v>13.0013580322266</v>
       </c>
       <c r="H1505" t="n">
         <v>156575</v>
@@ -44043,7 +44043,7 @@
         <v>19.6284694671631</v>
       </c>
       <c r="G1506" t="n">
-        <v>15.1763048171997</v>
+        <v>15.1763038635254</v>
       </c>
       <c r="H1506" t="n">
         <v>979944</v>
@@ -44072,7 +44072,7 @@
         <v>19.0783729553223</v>
       </c>
       <c r="G1507" t="n">
-        <v>14.7509803771973</v>
+        <v>14.7509813308716</v>
       </c>
       <c r="H1507" t="n">
         <v>512576</v>
@@ -44130,7 +44130,7 @@
         <v>18.690803527832</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.4513206481934</v>
+        <v>14.4513216018677</v>
       </c>
       <c r="H1509" t="n">
         <v>189210</v>
@@ -44217,7 +44217,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379793167114</v>
+        <v>14.8379802703857</v>
       </c>
       <c r="H1512" t="n">
         <v>518691</v>
@@ -44246,7 +44246,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157651901245</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1513" t="n">
         <v>165517</v>
@@ -44275,7 +44275,7 @@
         <v>18.8908386230469</v>
       </c>
       <c r="G1514" t="n">
-        <v>14.6059827804565</v>
+        <v>14.6059837341309</v>
       </c>
       <c r="H1514" t="n">
         <v>149007</v>
@@ -44333,7 +44333,7 @@
         <v>19.1658878326416</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8186445236206</v>
+        <v>14.8186454772949</v>
       </c>
       <c r="H1516" t="n">
         <v>177163</v>
@@ -44420,7 +44420,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157651901245</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1519" t="n">
         <v>157517</v>
@@ -44478,7 +44478,7 @@
         <v>19.1575527191162</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.812201499939</v>
+        <v>14.8122005462646</v>
       </c>
       <c r="H1521" t="n">
         <v>111135</v>
@@ -44507,7 +44507,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189876556396</v>
+        <v>14.5189867019653</v>
       </c>
       <c r="H1522" t="n">
         <v>83491</v>
@@ -44594,7 +44594,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.428765296936</v>
+        <v>14.4287662506104</v>
       </c>
       <c r="H1525" t="n">
         <v>203931</v>
@@ -44652,7 +44652,7 @@
         <v>18.9200115203857</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.6285400390625</v>
+        <v>14.6285409927368</v>
       </c>
       <c r="H1527" t="n">
         <v>97123</v>
@@ -44681,7 +44681,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958639144897</v>
+        <v>14.9958648681641</v>
       </c>
       <c r="H1528" t="n">
         <v>508333</v>
@@ -44826,7 +44826,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024219512939</v>
+        <v>14.9024229049683</v>
       </c>
       <c r="H1533" t="n">
         <v>79836</v>
@@ -44884,7 +44884,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316484451294</v>
+        <v>14.7316474914551</v>
       </c>
       <c r="H1535" t="n">
         <v>124218</v>
@@ -45029,7 +45029,7 @@
         <v>18.9241790771484</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.6317625045776</v>
+        <v>14.6317615509033</v>
       </c>
       <c r="H1540" t="n">
         <v>58627</v>
@@ -45087,7 +45087,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1542" t="n">
-        <v>14.0002222061157</v>
+        <v>14.0002212524414</v>
       </c>
       <c r="H1542" t="n">
         <v>149427</v>
@@ -45145,7 +45145,7 @@
         <v>18.5241088867188</v>
       </c>
       <c r="G1544" t="n">
-        <v>14.3224363327026</v>
+        <v>14.3224353790283</v>
       </c>
       <c r="H1544" t="n">
         <v>44397</v>
@@ -45261,7 +45261,7 @@
         <v>19.1950607299805</v>
       </c>
       <c r="G1548" t="n">
-        <v>14.8412017822266</v>
+        <v>14.8412008285522</v>
       </c>
       <c r="H1548" t="n">
         <v>148931</v>
@@ -45319,7 +45319,7 @@
         <v>19.7618274688721</v>
       </c>
       <c r="G1550" t="n">
-        <v>15.2794132232666</v>
+        <v>15.2794122695923</v>
       </c>
       <c r="H1550" t="n">
         <v>232939</v>
@@ -45348,7 +45348,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024219512939</v>
+        <v>14.9024229049683</v>
       </c>
       <c r="H1551" t="n">
         <v>264963</v>
@@ -45377,7 +45377,7 @@
         <v>19.3784255981445</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.9829750061035</v>
+        <v>14.9829759597778</v>
       </c>
       <c r="H1552" t="n">
         <v>194072</v>
@@ -45406,7 +45406,7 @@
         <v>20.6703205108643</v>
       </c>
       <c r="G1553" t="n">
-        <v>15.981840133667</v>
+        <v>15.9818410873413</v>
       </c>
       <c r="H1553" t="n">
         <v>660001</v>
@@ -45435,7 +45435,7 @@
         <v>20.0243721008301</v>
       </c>
       <c r="G1554" t="n">
-        <v>15.4824066162109</v>
+        <v>15.4824075698853</v>
       </c>
       <c r="H1554" t="n">
         <v>487112</v>
@@ -45580,7 +45580,7 @@
         <v>20.6244792938232</v>
       </c>
       <c r="G1559" t="n">
-        <v>15.9463977813721</v>
+        <v>15.9463987350464</v>
       </c>
       <c r="H1559" t="n">
         <v>435045</v>
@@ -45696,7 +45696,7 @@
         <v>19.0366992950439</v>
       </c>
       <c r="G1563" t="n">
-        <v>14.7187595367432</v>
+        <v>14.7187604904175</v>
       </c>
       <c r="H1563" t="n">
         <v>364625</v>
@@ -45725,7 +45725,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157651901245</v>
+        <v>14.5157661437988</v>
       </c>
       <c r="H1564" t="n">
         <v>315453</v>
@@ -45754,7 +45754,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.36545753479</v>
+        <v>13.3654584884644</v>
       </c>
       <c r="H1565" t="n">
         <v>596953</v>
@@ -45870,7 +45870,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781202316284</v>
+        <v>13.5781192779541</v>
       </c>
       <c r="H1569" t="n">
         <v>306814</v>
@@ -46131,7 +46131,7 @@
         <v>19.7534923553467</v>
       </c>
       <c r="G1578" t="n">
-        <v>15.272967338562</v>
+        <v>15.2729682922363</v>
       </c>
       <c r="H1578" t="n">
         <v>326853</v>
@@ -46160,7 +46160,7 @@
         <v>20.2119064331055</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.627405166626</v>
+        <v>15.6274042129517</v>
       </c>
       <c r="H1579" t="n">
         <v>454220</v>
@@ -46421,7 +46421,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8304004669189</v>
+        <v>15.8303995132446</v>
       </c>
       <c r="H1588" t="n">
         <v>187148</v>
@@ -46508,7 +46508,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199178695679</v>
+        <v>15.1199169158936</v>
       </c>
       <c r="H1591" t="n">
         <v>163415</v>
@@ -46595,7 +46595,7 @@
         <v>18.024019241333</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.9357776641846</v>
+        <v>13.9357767105103</v>
       </c>
       <c r="H1594" t="n">
         <v>185388</v>
@@ -46624,7 +46624,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.0002222061157</v>
+        <v>14.0002212524414</v>
       </c>
       <c r="H1595" t="n">
         <v>171574</v>
@@ -46682,7 +46682,7 @@
         <v>18.1177864074707</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0082769393921</v>
+        <v>14.0082778930664</v>
       </c>
       <c r="H1597" t="n">
         <v>193042</v>
@@ -46711,7 +46711,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585592269897</v>
+        <v>13.7585601806641</v>
       </c>
       <c r="H1598" t="n">
         <v>171526</v>
@@ -46798,7 +46798,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780071258545</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1601" t="n">
         <v>280445</v>
@@ -47001,7 +47001,7 @@
         <v>16.9821681976318</v>
       </c>
       <c r="G1608" t="n">
-        <v>13.1302423477173</v>
+        <v>13.130241394043</v>
       </c>
       <c r="H1608" t="n">
         <v>500248</v>
@@ -47030,7 +47030,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1609" t="n">
-        <v>12.9691362380981</v>
+        <v>12.9691352844238</v>
       </c>
       <c r="H1609" t="n">
         <v>243613</v>
@@ -47059,7 +47059,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1610" t="n">
-        <v>12.9691362380981</v>
+        <v>12.9691352844238</v>
       </c>
       <c r="H1610" t="n">
         <v>466473</v>
@@ -47204,7 +47204,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519580841064</v>
+        <v>11.0519590377808</v>
       </c>
       <c r="H1615" t="n">
         <v>230061</v>
@@ -47291,7 +47291,7 @@
         <v>14.7942819595337</v>
       </c>
       <c r="G1618" t="n">
-        <v>11.4386157989502</v>
+        <v>11.4386167526245</v>
       </c>
       <c r="H1618" t="n">
         <v>110697</v>
@@ -47320,7 +47320,7 @@
         <v>14.6484231948853</v>
       </c>
       <c r="G1619" t="n">
-        <v>11.3258409500122</v>
+        <v>11.3258419036865</v>
       </c>
       <c r="H1619" t="n">
         <v>113034</v>
@@ -47436,7 +47436,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433349609375</v>
+        <v>11.5433340072632</v>
       </c>
       <c r="H1623" t="n">
         <v>121159</v>
@@ -47465,7 +47465,7 @@
         <v>14.700514793396</v>
       </c>
       <c r="G1624" t="n">
-        <v>11.366117477417</v>
+        <v>11.3661165237427</v>
       </c>
       <c r="H1624" t="n">
         <v>91847</v>
@@ -47494,7 +47494,7 @@
         <v>15.0130710601807</v>
       </c>
       <c r="G1625" t="n">
-        <v>11.6077785491943</v>
+        <v>11.6077795028687</v>
       </c>
       <c r="H1625" t="n">
         <v>59931</v>
@@ -47552,7 +47552,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.970269203186</v>
+        <v>11.9702701568604</v>
       </c>
       <c r="H1627" t="n">
         <v>161789</v>
@@ -47755,7 +47755,7 @@
         <v>16.429988861084</v>
       </c>
       <c r="G1634" t="n">
-        <v>12.7033081054688</v>
+        <v>12.7033090591431</v>
       </c>
       <c r="H1634" t="n">
         <v>81533</v>
@@ -47784,7 +47784,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805255889893</v>
+        <v>12.8805246353149</v>
       </c>
       <c r="H1635" t="n">
         <v>140616</v>
@@ -48132,7 +48132,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439033508301</v>
+        <v>11.0439023971558</v>
       </c>
       <c r="H1647" t="n">
         <v>123714</v>
@@ -48161,7 +48161,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136325836182</v>
+        <v>10.7136335372925</v>
       </c>
       <c r="H1648" t="n">
         <v>160860</v>
@@ -48451,7 +48451,7 @@
         <v>10.010103225708</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.73959302902222</v>
+        <v>7.73959255218506</v>
       </c>
       <c r="H1658" t="n">
         <v>359843</v>
@@ -48509,7 +48509,7 @@
         <v>10.5331115722656</v>
       </c>
       <c r="G1660" t="n">
-        <v>8.14397239685059</v>
+        <v>8.14397144317627</v>
       </c>
       <c r="H1660" t="n">
         <v>318695</v>
@@ -48567,7 +48567,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392255783081</v>
+        <v>7.90392160415649</v>
       </c>
       <c r="H1662" t="n">
         <v>148424</v>
@@ -48799,7 +48799,7 @@
         <v>8.75571441650391</v>
       </c>
       <c r="G1670" t="n">
-        <v>6.76972770690918</v>
+        <v>6.76972723007202</v>
       </c>
       <c r="H1670" t="n">
         <v>178963</v>
@@ -48828,7 +48828,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795209884644</v>
+        <v>6.62795162200928</v>
       </c>
       <c r="H1671" t="n">
         <v>134394</v>
@@ -48886,7 +48886,7 @@
         <v>8.40981960296631</v>
       </c>
       <c r="G1673" t="n">
-        <v>6.50228929519653</v>
+        <v>6.50228881835938</v>
       </c>
       <c r="H1673" t="n">
         <v>175627</v>
@@ -48915,7 +48915,7 @@
         <v>8.62235736846924</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.66661882400513</v>
+        <v>6.66661834716797</v>
       </c>
       <c r="H1674" t="n">
         <v>247778</v>
@@ -48944,7 +48944,7 @@
         <v>8.99325561523438</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.95338869094849</v>
+        <v>6.95338916778564</v>
       </c>
       <c r="H1675" t="n">
         <v>183001</v>
@@ -49031,7 +49031,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927289962769</v>
+        <v>7.16927337646484</v>
       </c>
       <c r="H1678" t="n">
         <v>171846</v>
@@ -49176,7 +49176,7 @@
         <v>8.62235736846924</v>
       </c>
       <c r="G1683" t="n">
-        <v>6.66661882400513</v>
+        <v>6.66661834716797</v>
       </c>
       <c r="H1683" t="n">
         <v>289417</v>
@@ -49292,7 +49292,7 @@
         <v>8.46816253662109</v>
       </c>
       <c r="G1687" t="n">
-        <v>6.54739856719971</v>
+        <v>6.54739809036255</v>
       </c>
       <c r="H1687" t="n">
         <v>158208</v>
@@ -49321,7 +49321,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973346710205</v>
+        <v>6.47973394393921</v>
       </c>
       <c r="H1688" t="n">
         <v>211830</v>
@@ -49379,7 +49379,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107536315918</v>
+        <v>6.15107488632202</v>
       </c>
       <c r="H1690" t="n">
         <v>346128</v>
@@ -49524,7 +49524,7 @@
         <v>6.87204790115356</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.31331777572632</v>
+        <v>5.31331729888916</v>
       </c>
       <c r="H1695" t="n">
         <v>342058</v>
@@ -49553,7 +49553,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032199859619</v>
+        <v>5.11032152175903</v>
       </c>
       <c r="H1696" t="n">
         <v>868645</v>
@@ -49582,7 +49582,7 @@
         <v>6.32611799240112</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.89121675491333</v>
+        <v>4.89121627807617</v>
       </c>
       <c r="H1697" t="n">
         <v>323082</v>
@@ -49611,7 +49611,7 @@
         <v>6.63450622558594</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.12965488433838</v>
+        <v>5.12965536117554</v>
       </c>
       <c r="H1698" t="n">
         <v>358770</v>
@@ -49640,7 +49640,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799428939819</v>
+        <v>4.88799476623535</v>
       </c>
       <c r="H1699" t="n">
         <v>228803</v>
@@ -49756,7 +49756,7 @@
         <v>6.3677921295166</v>
       </c>
       <c r="G1703" t="n">
-        <v>4.92343759536743</v>
+        <v>4.92343807220459</v>
       </c>
       <c r="H1703" t="n">
         <v>613489</v>
@@ -49872,7 +49872,7 @@
         <v>7.65135192871094</v>
       </c>
       <c r="G1707" t="n">
-        <v>5.91585779190063</v>
+        <v>5.91585826873779</v>
       </c>
       <c r="H1707" t="n">
         <v>677853</v>
@@ -49901,7 +49901,7 @@
         <v>7.26378393173218</v>
       </c>
       <c r="G1708" t="n">
-        <v>5.6161994934082</v>
+        <v>5.61619901657104</v>
       </c>
       <c r="H1708" t="n">
         <v>487854</v>
@@ -49959,7 +49959,7 @@
         <v>6.27194213867188</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.84932851791382</v>
+        <v>4.84932899475098</v>
       </c>
       <c r="H1710" t="n">
         <v>660674</v>
@@ -50017,7 +50017,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555204391479</v>
+        <v>4.76555252075195</v>
       </c>
       <c r="H1712" t="n">
         <v>627926</v>
@@ -50220,7 +50220,7 @@
         <v>5.1717472076416</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.99868178367615</v>
+        <v>3.99868226051331</v>
       </c>
       <c r="H1719" t="n">
         <v>801083</v>
@@ -50249,7 +50249,7 @@
         <v>4.99671602249146</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.86335206031799</v>
+        <v>3.86335182189941</v>
       </c>
       <c r="H1720" t="n">
         <v>478249</v>
@@ -50307,7 +50307,7 @@
         <v>4.66853284835815</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.60960745811462</v>
+        <v>3.6096076965332</v>
       </c>
       <c r="H1722" t="n">
         <v>526169</v>
@@ -50394,7 +50394,7 @@
         <v>4.84252214431763</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.74413251876831</v>
+        <v>3.74413228034973</v>
       </c>
       <c r="H1725" t="n">
         <v>619872</v>
@@ -50481,7 +50481,7 @@
         <v>2.06286406517029</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.5949615240097</v>
+        <v>1.59496140480042</v>
       </c>
       <c r="H1728" t="n">
         <v>913518</v>
@@ -50684,7 +50684,7 @@
         <v>1.9831999540329</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.53336679935455</v>
+        <v>1.53336691856384</v>
       </c>
       <c r="H1735" t="n">
         <v>1128008</v>
@@ -50713,7 +50713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089284896851</v>
+        <v>1.53089272975922</v>
       </c>
       <c r="H1736" t="n">
         <v>1871837</v>
@@ -50858,7 +50858,7 @@
         <v>1.9456000328064</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.50429534912109</v>
+        <v>1.50429546833038</v>
       </c>
       <c r="H1741" t="n">
         <v>2596034</v>
@@ -50945,7 +50945,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.39945244789124</v>
+        <v>1.39945232868195</v>
       </c>
       <c r="H1744" t="n">
         <v>10215715</v>
@@ -51003,7 +51003,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1746" t="n">
         <v>4299825</v>
@@ -51032,7 +51032,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1747" t="n">
         <v>5687761</v>
@@ -51061,7 +51061,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172077178955</v>
+        <v>1.39172065258026</v>
       </c>
       <c r="H1748" t="n">
         <v>7070109</v>
@@ -51090,7 +51090,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.38398897647858</v>
+        <v>1.38398885726929</v>
       </c>
       <c r="H1749" t="n">
         <v>7258460</v>
@@ -51177,7 +51177,7 @@
         <v>1.81239998340607</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.40130805969238</v>
+        <v>1.40130817890167</v>
       </c>
       <c r="H1752" t="n">
         <v>3775318</v>
@@ -51206,7 +51206,7 @@
         <v>1.81299996376038</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.40177190303802</v>
+        <v>1.40177202224731</v>
       </c>
       <c r="H1753" t="n">
         <v>5951051</v>
@@ -51235,7 +51235,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.391566157341</v>
+        <v>1.39156603813171</v>
       </c>
       <c r="H1754" t="n">
         <v>2641302</v>
@@ -51380,7 +51380,7 @@
         <v>1.80859994888306</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.39837002754211</v>
+        <v>1.39836990833282</v>
       </c>
       <c r="H1759" t="n">
         <v>3782624</v>
@@ -51467,7 +51467,7 @@
         <v>1.88960003852844</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.46099746227264</v>
+        <v>1.46099758148193</v>
       </c>
       <c r="H1762" t="n">
         <v>18263848</v>
@@ -51496,7 +51496,7 @@
         <v>1.88919997215271</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.46068823337555</v>
+        <v>1.46068811416626</v>
       </c>
       <c r="H1763" t="n">
         <v>3524769</v>
@@ -51554,7 +51554,7 @@
         <v>1.87360000610352</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.4486266374588</v>
+        <v>1.44862651824951</v>
       </c>
       <c r="H1765" t="n">
         <v>9888369</v>
@@ -51583,7 +51583,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537937641144</v>
+        <v>1.44537925720215</v>
       </c>
       <c r="H1766" t="n">
         <v>4191313</v>
@@ -51612,7 +51612,7 @@
         <v>1.80820000171661</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.39806067943573</v>
+        <v>1.39806079864502</v>
       </c>
       <c r="H1767" t="n">
         <v>5834324</v>
@@ -51641,7 +51641,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.40950381755829</v>
+        <v>1.409503698349</v>
       </c>
       <c r="H1768" t="n">
         <v>4615701</v>
@@ -51757,7 +51757,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.50383150577545</v>
+        <v>1.50383162498474</v>
       </c>
       <c r="H1772" t="n">
         <v>6992176</v>
@@ -51815,7 +51815,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.45125532150269</v>
+        <v>1.45125544071198</v>
       </c>
       <c r="H1774" t="n">
         <v>7152049</v>
@@ -51844,7 +51844,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903836727142</v>
+        <v>1.46903848648071</v>
       </c>
       <c r="H1775" t="n">
         <v>3814973</v>
@@ -51902,7 +51902,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.57689690589905</v>
+        <v>1.57689678668976</v>
       </c>
       <c r="H1777" t="n">
         <v>14755833</v>
@@ -52047,7 +52047,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.48805868625641</v>
+        <v>1.48805856704712</v>
       </c>
       <c r="H1782" t="n">
         <v>2159725</v>
@@ -52076,7 +52076,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.58501517772675</v>
+        <v>1.58501529693604</v>
       </c>
       <c r="H1783" t="n">
         <v>13921292</v>
@@ -52163,7 +52163,7 @@
         <v>1.98660004138947</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.53599572181702</v>
+        <v>1.53599584102631</v>
       </c>
       <c r="H1786" t="n">
         <v>9824828</v>
@@ -52366,7 +52366,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.65537452697754</v>
+        <v>1.65537440776825</v>
       </c>
       <c r="H1793" t="n">
         <v>21373665</v>
@@ -52395,7 +52395,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1794" t="n">
         <v>6601746</v>
@@ -52424,7 +52424,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.60318493843079</v>
+        <v>1.6031848192215</v>
       </c>
       <c r="H1795" t="n">
         <v>7563778</v>
@@ -52482,7 +52482,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.56800532341003</v>
+        <v>1.56800544261932</v>
       </c>
       <c r="H1797" t="n">
         <v>6304338</v>
@@ -52598,7 +52598,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.6847550868988</v>
+        <v>1.68475520610809</v>
       </c>
       <c r="H1801" t="n">
         <v>14097011</v>
@@ -52627,7 +52627,7 @@
         <v>2.18449997901917</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.68900763988495</v>
+        <v>1.68900775909424</v>
       </c>
       <c r="H1802" t="n">
         <v>7676085</v>
@@ -52685,7 +52685,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428663253784</v>
+        <v>1.89428651332855</v>
       </c>
       <c r="H1804" t="n">
         <v>18740837</v>
@@ -52743,7 +52743,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.87186431884766</v>
+        <v>1.87186419963837</v>
       </c>
       <c r="H1806" t="n">
         <v>12148200</v>
@@ -52772,7 +52772,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482697963715</v>
+        <v>1.92482709884644</v>
       </c>
       <c r="H1807" t="n">
         <v>14549250</v>
@@ -52801,7 +52801,7 @@
         <v>2.37350010871887</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.83513855934143</v>
+        <v>1.83513844013214</v>
       </c>
       <c r="H1808" t="n">
         <v>19340207</v>
@@ -52859,7 +52859,7 @@
         <v>2.31550002098083</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.79029405117035</v>
+        <v>1.79029417037964</v>
       </c>
       <c r="H1810" t="n">
         <v>25899848</v>
@@ -52888,7 +52888,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.01026296615601</v>
+        <v>2.01026320457458</v>
       </c>
       <c r="H1811" t="n">
         <v>45207296</v>
@@ -53004,7 +53004,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552515506744</v>
+        <v>1.83552503585815</v>
       </c>
       <c r="H1815" t="n">
         <v>8871781</v>
@@ -53294,7 +53294,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.90665757656097</v>
+        <v>1.90665745735168</v>
       </c>
       <c r="H1825" t="n">
         <v>21554181</v>
@@ -53323,7 +53323,7 @@
         <v>2.39050006866455</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.84828245639801</v>
+        <v>1.8482825756073</v>
       </c>
       <c r="H1826" t="n">
         <v>13530053</v>
@@ -53381,7 +53381,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428663253784</v>
+        <v>1.89428651332855</v>
       </c>
       <c r="H1828" t="n">
         <v>6331894</v>
@@ -53410,7 +53410,7 @@
         <v>2.36700010299683</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.83011281490326</v>
+        <v>1.83011269569397</v>
       </c>
       <c r="H1829" t="n">
         <v>7991760</v>
@@ -53584,7 +53584,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.48805868625641</v>
+        <v>1.48805856704712</v>
       </c>
       <c r="H1835" t="n">
         <v>21201799</v>
@@ -53642,7 +53642,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46207988262177</v>
+        <v>1.46208000183105</v>
       </c>
       <c r="H1837" t="n">
         <v>27810987</v>
@@ -53787,7 +53787,7 @@
         <v>1.88059997558594</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.45403873920441</v>
+        <v>1.4540388584137</v>
       </c>
       <c r="H1842" t="n">
         <v>11617888</v>
@@ -53816,7 +53816,7 @@
         <v>1.81420004367828</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.40269994735718</v>
+        <v>1.40269982814789</v>
       </c>
       <c r="H1843" t="n">
         <v>8718449</v>
@@ -53845,7 +53845,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.41646254062653</v>
+        <v>1.41646242141724</v>
       </c>
       <c r="H1844" t="n">
         <v>7614292</v>
@@ -54135,7 +54135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.58501517772675</v>
+        <v>1.58501529693604</v>
       </c>
       <c r="H1854" t="n">
         <v>4279847</v>
@@ -54222,7 +54222,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1857" t="n">
         <v>11220865</v>
@@ -54309,7 +54309,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666093826294</v>
+        <v>1.75666081905365</v>
       </c>
       <c r="H1860" t="n">
         <v>8508624</v>
@@ -54396,7 +54396,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1863" t="n">
         <v>7031365</v>
@@ -54425,7 +54425,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630146980286</v>
+        <v>1.68630158901215</v>
       </c>
       <c r="H1864" t="n">
         <v>5899256</v>
@@ -54454,7 +54454,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.61516916751862</v>
+        <v>1.61516928672791</v>
       </c>
       <c r="H1865" t="n">
         <v>6994580</v>
@@ -54657,7 +54657,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.60125195980072</v>
+        <v>1.60125207901001</v>
       </c>
       <c r="H1872" t="n">
         <v>6922251</v>
@@ -54686,7 +54686,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831318378448</v>
+        <v>1.62831330299377</v>
       </c>
       <c r="H1873" t="n">
         <v>6917707</v>
@@ -54773,7 +54773,7 @@
         <v>2.21300005912781</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.71104323863983</v>
+        <v>1.71104335784912</v>
       </c>
       <c r="H1876" t="n">
         <v>15770492</v>
@@ -54860,7 +54860,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.65537452697754</v>
+        <v>1.65537440776825</v>
       </c>
       <c r="H1879" t="n">
         <v>7813573</v>
@@ -54918,7 +54918,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.77444398403168</v>
+        <v>1.77444410324097</v>
       </c>
       <c r="H1881" t="n">
         <v>14803240</v>
@@ -54976,7 +54976,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594235897064</v>
+        <v>1.61594223976135</v>
       </c>
       <c r="H1883" t="n">
         <v>10738852</v>
@@ -55063,7 +55063,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.60125195980072</v>
+        <v>1.60125207901001</v>
       </c>
       <c r="H1886" t="n">
         <v>6292235</v>
@@ -55092,7 +55092,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.62985956668854</v>
+        <v>1.62985968589783</v>
       </c>
       <c r="H1887" t="n">
         <v>15958032</v>
@@ -55121,7 +55121,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006492614746</v>
+        <v>1.67006480693817</v>
       </c>
       <c r="H1888" t="n">
         <v>9732271</v>
@@ -55179,7 +55179,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.7582072019577</v>
+        <v>1.75820708274841</v>
       </c>
       <c r="H1890" t="n">
         <v>16440004</v>
@@ -55237,7 +55237,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.86954462528229</v>
+        <v>1.86954474449158</v>
       </c>
       <c r="H1892" t="n">
         <v>29342749</v>
@@ -55266,7 +55266,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.88346207141876</v>
+        <v>1.88346219062805</v>
       </c>
       <c r="H1893" t="n">
         <v>15431172</v>
@@ -55295,7 +55295,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011629581451</v>
+        <v>1.68011617660522</v>
       </c>
       <c r="H1894" t="n">
         <v>28227461</v>
@@ -55382,7 +55382,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1897" t="n">
         <v>13177383</v>
@@ -55440,7 +55440,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.76748526096344</v>
+        <v>1.76748538017273</v>
       </c>
       <c r="H1899" t="n">
         <v>12029873</v>
@@ -55469,7 +55469,7 @@
         <v>2.32100009918213</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.79454672336578</v>
+        <v>1.79454660415649</v>
       </c>
       <c r="H1900" t="n">
         <v>9000879</v>
@@ -55527,7 +55527,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82701981067657</v>
+        <v>1.82701992988586</v>
       </c>
       <c r="H1902" t="n">
         <v>11298307</v>
@@ -55614,7 +55614,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645557880402</v>
+        <v>1.71645569801331</v>
       </c>
       <c r="H1905" t="n">
         <v>7081375</v>
@@ -55643,7 +55643,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.73578488826752</v>
+        <v>1.73578500747681</v>
       </c>
       <c r="H1906" t="n">
         <v>5356916</v>
@@ -55701,7 +55701,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.77367079257965</v>
+        <v>1.77367067337036</v>
       </c>
       <c r="H1908" t="n">
         <v>7446800</v>
@@ -55730,7 +55730,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.77985620498657</v>
+        <v>1.77985608577728</v>
       </c>
       <c r="H1909" t="n">
         <v>7154278</v>
@@ -55759,7 +55759,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387615203857</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1910" t="n">
         <v>7777212</v>
@@ -55788,7 +55788,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.77444398403168</v>
+        <v>1.77444410324097</v>
       </c>
       <c r="H1911" t="n">
         <v>8748249</v>
@@ -55933,7 +55933,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387615203857</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1916" t="n">
         <v>11063863</v>
@@ -56165,7 +56165,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382118225098</v>
+        <v>1.95382130146027</v>
       </c>
       <c r="H1924" t="n">
         <v>4430041</v>
@@ -56223,7 +56223,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918215274811</v>
+        <v>1.94918203353882</v>
       </c>
       <c r="H1926" t="n">
         <v>5834369</v>
@@ -56252,7 +56252,7 @@
         <v>2.61700010299683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.02340745925903</v>
+        <v>2.02340722084045</v>
       </c>
       <c r="H1927" t="n">
         <v>20029327</v>
@@ -56310,7 +56310,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562405586243</v>
+        <v>2.00562429428101</v>
       </c>
       <c r="H1929" t="n">
         <v>10963576</v>
@@ -56339,7 +56339,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959251403809</v>
+        <v>2.02959275245667</v>
       </c>
       <c r="H1930" t="n">
         <v>11993677</v>
@@ -56368,7 +56368,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.96077966690063</v>
+        <v>1.96077978610992</v>
       </c>
       <c r="H1931" t="n">
         <v>9783275</v>
@@ -56455,7 +56455,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1934" t="n">
-        <v>1.95691394805908</v>
+        <v>1.95691382884979</v>
       </c>
       <c r="H1934" t="n">
         <v>24640061</v>
@@ -56542,7 +56542,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.95691394805908</v>
+        <v>1.95691382884979</v>
       </c>
       <c r="H1937" t="n">
         <v>24480809</v>
@@ -56571,7 +56571,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G1938" t="n">
-        <v>1.97005784511566</v>
+        <v>1.97005796432495</v>
       </c>
       <c r="H1938" t="n">
         <v>9538925</v>
@@ -56629,7 +56629,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025972366333</v>
+        <v>2.16025996208191</v>
       </c>
       <c r="H1940" t="n">
         <v>21527670</v>
@@ -56745,7 +56745,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.03500509262085</v>
+        <v>2.03500485420227</v>
       </c>
       <c r="H1944" t="n">
         <v>9682287</v>
@@ -56919,7 +56919,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.9940265417099</v>
+        <v>1.99402642250061</v>
       </c>
       <c r="H1950" t="n">
         <v>6249034</v>
@@ -56948,7 +56948,7 @@
         <v>2.62899994850159</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.03268527984619</v>
+        <v>2.03268551826477</v>
       </c>
       <c r="H1951" t="n">
         <v>12173491</v>
@@ -56977,7 +56977,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.98088240623474</v>
+        <v>1.98088228702545</v>
       </c>
       <c r="H1952" t="n">
         <v>14258681</v>
@@ -57064,7 +57064,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.90511095523834</v>
+        <v>1.90511107444763</v>
       </c>
       <c r="H1955" t="n">
         <v>11937121</v>
@@ -57093,7 +57093,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763925075531</v>
+        <v>1.7976393699646</v>
       </c>
       <c r="H1956" t="n">
         <v>22749670</v>
@@ -57209,7 +57209,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310260295868</v>
+        <v>1.81310272216797</v>
       </c>
       <c r="H1960" t="n">
         <v>6445475</v>
@@ -57267,7 +57267,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.92057454586029</v>
+        <v>1.920574426651</v>
       </c>
       <c r="H1962" t="n">
         <v>17155594</v>
@@ -57296,7 +57296,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.92675995826721</v>
+        <v>1.92676019668579</v>
       </c>
       <c r="H1963" t="n">
         <v>13390725</v>
@@ -57470,7 +57470,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.06825137138367</v>
+        <v>2.06825160980225</v>
       </c>
       <c r="H1969" t="n">
         <v>23723962</v>
@@ -57528,7 +57528,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866893291473</v>
+        <v>1.84866905212402</v>
       </c>
       <c r="H1971" t="n">
         <v>32386618</v>
@@ -57557,7 +57557,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.86181282997131</v>
+        <v>1.8618129491806</v>
       </c>
       <c r="H1972" t="n">
         <v>18377109</v>
@@ -57586,7 +57586,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.8672251701355</v>
+        <v>1.86722528934479</v>
       </c>
       <c r="H1973" t="n">
         <v>10855064</v>
@@ -57615,7 +57615,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737915992737</v>
+        <v>1.89737927913666</v>
       </c>
       <c r="H1974" t="n">
         <v>15191141</v>
@@ -57644,7 +57644,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.91748178005219</v>
+        <v>1.91748189926147</v>
       </c>
       <c r="H1975" t="n">
         <v>17294006</v>
@@ -57673,7 +57673,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639748573303</v>
+        <v>2.00639724731445</v>
       </c>
       <c r="H1976" t="n">
         <v>29570216</v>
@@ -57702,7 +57702,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.96077966690063</v>
+        <v>1.96077978610992</v>
       </c>
       <c r="H1977" t="n">
         <v>19720359</v>
@@ -57876,7 +57876,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.94840884208679</v>
+        <v>1.94840896129608</v>
       </c>
       <c r="H1983" t="n">
         <v>25197954</v>
@@ -57905,7 +57905,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.95691394805908</v>
+        <v>1.95691382884979</v>
       </c>
       <c r="H1984" t="n">
         <v>32448765</v>
@@ -57934,7 +57934,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397505283356</v>
+        <v>1.98397517204285</v>
       </c>
       <c r="H1985" t="n">
         <v>20639388</v>
@@ -57963,7 +57963,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.95614087581635</v>
+        <v>1.95614075660706</v>
       </c>
       <c r="H1986" t="n">
         <v>18660240</v>
@@ -58021,7 +58021,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.83475184440613</v>
+        <v>1.83475172519684</v>
       </c>
       <c r="H1988" t="n">
         <v>16787583</v>
@@ -58079,7 +58079,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.85408127307892</v>
+        <v>1.85408139228821</v>
       </c>
       <c r="H1990" t="n">
         <v>14799249</v>
@@ -58166,7 +58166,7 @@
         <v>2.42899990081787</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.87804973125458</v>
+        <v>1.87804961204529</v>
       </c>
       <c r="H1993" t="n">
         <v>10692244</v>
@@ -58224,7 +58224,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237777709961</v>
+        <v>1.97237765789032</v>
       </c>
       <c r="H1995" t="n">
         <v>14164042</v>
@@ -58253,7 +58253,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866569042206</v>
+        <v>1.99866557121277</v>
       </c>
       <c r="H1996" t="n">
         <v>13386081</v>
@@ -58282,7 +58282,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964376449585</v>
+        <v>2.03964400291443</v>
       </c>
       <c r="H1997" t="n">
         <v>18265540</v>
@@ -58311,7 +58311,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.0551073551178</v>
+        <v>2.05510759353638</v>
       </c>
       <c r="H1998" t="n">
         <v>14855596</v>
@@ -58572,7 +58572,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G2007" t="n">
-        <v>2.35973978042603</v>
+        <v>2.3597400188446</v>
       </c>
       <c r="H2007" t="n">
         <v>16760666</v>
@@ -58630,7 +58630,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G2009" t="n">
-        <v>2.37520313262939</v>
+        <v>2.37520337104797</v>
       </c>
       <c r="H2009" t="n">
         <v>13477044</v>
@@ -58659,7 +58659,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654775619507</v>
+        <v>2.18654799461365</v>
       </c>
       <c r="H2010" t="n">
         <v>100072608</v>
@@ -58775,7 +58775,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.28551483154297</v>
+        <v>2.28551459312439</v>
       </c>
       <c r="H2014" t="n">
         <v>26182103</v>
@@ -58949,7 +58949,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921959877014</v>
+        <v>2.55921983718872</v>
       </c>
       <c r="H2020" t="n">
         <v>36522732</v>
@@ -59065,7 +59065,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.60329079627991</v>
+        <v>2.60329103469849</v>
       </c>
       <c r="H2024" t="n">
         <v>39561081</v>
@@ -59094,7 +59094,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.53447818756104</v>
+        <v>2.53447794914246</v>
       </c>
       <c r="H2025" t="n">
         <v>37969241</v>
@@ -59239,7 +59239,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061547279358</v>
+        <v>2.38061571121216</v>
       </c>
       <c r="H2030" t="n">
         <v>33067746</v>
@@ -59268,7 +59268,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.36437892913818</v>
+        <v>2.3643786907196</v>
       </c>
       <c r="H2031" t="n">
         <v>14604732</v>
@@ -59297,7 +59297,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.35046172142029</v>
+        <v>2.35046148300171</v>
       </c>
       <c r="H2032" t="n">
         <v>11232080</v>
@@ -59558,7 +59558,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334228515625</v>
+        <v>2.61334204673767</v>
       </c>
       <c r="H2041" t="n">
         <v>21815059</v>
@@ -59587,7 +59587,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597332000732</v>
+        <v>2.52597308158875</v>
       </c>
       <c r="H2042" t="n">
         <v>27175102</v>
@@ -59616,7 +59616,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.52519989013672</v>
+        <v>2.5252001285553</v>
       </c>
       <c r="H2043" t="n">
         <v>14675290</v>
@@ -59674,7 +59674,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710874557495</v>
+        <v>2.44710898399353</v>
       </c>
       <c r="H2045" t="n">
         <v>15281373</v>
@@ -59877,7 +59877,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.4965922832489</v>
+        <v>2.49659252166748</v>
       </c>
       <c r="H2052" t="n">
         <v>21135868</v>
@@ -59964,7 +59964,7 @@
         <v>3.2409999370575</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.50587058067322</v>
+        <v>2.50587034225464</v>
       </c>
       <c r="H2055" t="n">
         <v>36516901</v>
@@ -59993,7 +59993,7 @@
         <v>3.19099998474121</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.46721148490906</v>
+        <v>2.46721172332764</v>
       </c>
       <c r="H2056" t="n">
         <v>19021872</v>
@@ -60022,7 +60022,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.53602433204651</v>
+        <v>2.53602457046509</v>
       </c>
       <c r="H2057" t="n">
         <v>20653870</v>
@@ -60051,7 +60051,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983903884888</v>
+        <v>2.5298388004303</v>
       </c>
       <c r="H2058" t="n">
         <v>17041685</v>
@@ -60167,7 +60167,7 @@
         <v>3.37299990653992</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.60792994499207</v>
+        <v>2.60792970657349</v>
       </c>
       <c r="H2062" t="n">
         <v>29705979</v>
@@ -60399,7 +60399,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467970848083</v>
+        <v>2.72467994689941</v>
       </c>
       <c r="H2070" t="n">
         <v>14759944</v>
@@ -60486,7 +60486,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.75019454956055</v>
+        <v>2.75019478797913</v>
       </c>
       <c r="H2073" t="n">
         <v>39123998</v>
@@ -60718,7 +60718,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.04632210731506</v>
+        <v>3.04632186889648</v>
       </c>
       <c r="H2081" t="n">
         <v>24628211</v>
@@ -60747,7 +60747,7 @@
         <v>3.93099999427795</v>
       </c>
       <c r="G2082" t="n">
-        <v>3.03936362266541</v>
+        <v>3.03936338424683</v>
       </c>
       <c r="H2082" t="n">
         <v>19979927</v>
@@ -60776,7 +60776,7 @@
         <v>3.93899989128113</v>
       </c>
       <c r="G2083" t="n">
-        <v>3.04554843902588</v>
+        <v>3.04554867744446</v>
       </c>
       <c r="H2083" t="n">
         <v>14348482</v>
@@ -60834,7 +60834,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2085" t="n">
-        <v>2.9829216003418</v>
+        <v>2.98292136192322</v>
       </c>
       <c r="H2085" t="n">
         <v>15537029</v>
@@ -60863,7 +60863,7 @@
         <v>3.87299990653992</v>
       </c>
       <c r="G2086" t="n">
-        <v>2.99451875686646</v>
+        <v>2.99451899528503</v>
       </c>
       <c r="H2086" t="n">
         <v>18280166</v>
@@ -60921,7 +60921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2088" t="n">
-        <v>3.17003035545349</v>
+        <v>3.17003059387207</v>
       </c>
       <c r="H2088" t="n">
         <v>24484756</v>
@@ -60979,7 +60979,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188471794128</v>
+        <v>3.23188447952271</v>
       </c>
       <c r="H2090" t="n">
         <v>36447686</v>
@@ -61240,7 +61240,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2099" t="n">
-        <v>3.24734830856323</v>
+        <v>3.24734807014465</v>
       </c>
       <c r="H2099" t="n">
         <v>35140784</v>
@@ -61327,7 +61327,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343110084534</v>
+        <v>3.23343133926392</v>
       </c>
       <c r="H2102" t="n">
         <v>15820699</v>
@@ -61472,7 +61472,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972237586975</v>
+        <v>3.10972261428833</v>
       </c>
       <c r="H2107" t="n">
         <v>24633782</v>
@@ -61530,7 +61530,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G2109" t="n">
-        <v>3.11126923561096</v>
+        <v>3.11126899719238</v>
       </c>
       <c r="H2109" t="n">
         <v>23566464</v>
@@ -61588,7 +61588,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G2111" t="n">
-        <v>3.14838171005249</v>
+        <v>3.14838147163391</v>
       </c>
       <c r="H2111" t="n">
         <v>22266963</v>
@@ -61617,7 +61617,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2112" t="n">
-        <v>3.24734830856323</v>
+        <v>3.24734807014465</v>
       </c>
       <c r="H2112" t="n">
         <v>29517947</v>
@@ -61646,7 +61646,7 @@
         <v>4.16300010681152</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.21874094009399</v>
+        <v>3.21874070167542</v>
       </c>
       <c r="H2113" t="n">
         <v>18257227</v>
@@ -61878,7 +61878,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811105728149</v>
+        <v>3.69811129570007</v>
       </c>
       <c r="H2121" t="n">
         <v>32155461</v>
@@ -61907,7 +61907,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409459114075</v>
+        <v>3.51409482955933</v>
       </c>
       <c r="H2122" t="n">
         <v>36014819</v>
@@ -62052,7 +62052,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.66022562980652</v>
+        <v>3.66022539138794</v>
       </c>
       <c r="H2127" t="n">
         <v>18548351</v>
@@ -62081,7 +62081,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G2128" t="n">
-        <v>3.66873002052307</v>
+        <v>3.66873025894165</v>
       </c>
       <c r="H2128" t="n">
         <v>13092351</v>
@@ -62139,7 +62139,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145683288574</v>
+        <v>3.90145707130432</v>
       </c>
       <c r="H2130" t="n">
         <v>31985059</v>
@@ -80067,6 +80067,35 @@
         <v>12857934</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>10.5979995727539</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>10.7019996643066</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>10.4820003509521</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>8176287</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73583984375</v>
+        <v>1765.73571777344</v>
       </c>
       <c r="H4" t="n">
         <v>22853</v>
@@ -514,7 +514,7 @@
         <v>2208.72412109375</v>
       </c>
       <c r="G5" t="n">
-        <v>1707.7373046875</v>
+        <v>1707.73718261719</v>
       </c>
       <c r="H5" t="n">
         <v>38406</v>
@@ -572,7 +572,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.0478515625</v>
+        <v>1491.04797363281</v>
       </c>
       <c r="H7" t="n">
         <v>58243</v>
@@ -601,7 +601,7 @@
         <v>1933.67529296875</v>
       </c>
       <c r="G8" t="n">
-        <v>1495.07543945312</v>
+        <v>1495.07556152344</v>
       </c>
       <c r="H8" t="n">
         <v>53763</v>
@@ -659,7 +659,7 @@
         <v>2005.56311035156</v>
       </c>
       <c r="G10" t="n">
-        <v>1550.65759277344</v>
+        <v>1550.65771484375</v>
       </c>
       <c r="H10" t="n">
         <v>43759</v>
@@ -717,7 +717,7 @@
         <v>1595.07385253906</v>
       </c>
       <c r="G12" t="n">
-        <v>1233.2763671875</v>
+        <v>1233.27624511719</v>
       </c>
       <c r="H12" t="n">
         <v>58224</v>
@@ -775,7 +775,7 @@
         <v>1062.68798828125</v>
       </c>
       <c r="G14" t="n">
-        <v>821.647155761719</v>
+        <v>821.647094726562</v>
       </c>
       <c r="H14" t="n">
         <v>36638</v>
@@ -920,7 +920,7 @@
         <v>1481.51208496094</v>
       </c>
       <c r="G19" t="n">
-        <v>1145.47277832031</v>
+        <v>1145.47290039062</v>
       </c>
       <c r="H19" t="n">
         <v>52360</v>
@@ -949,7 +949,7 @@
         <v>1364.82470703125</v>
       </c>
       <c r="G20" t="n">
-        <v>1055.25256347656</v>
+        <v>1055.25268554688</v>
       </c>
       <c r="H20" t="n">
         <v>48851</v>
@@ -978,7 +978,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14135742188</v>
+        <v>1068.14123535156</v>
       </c>
       <c r="H21" t="n">
         <v>67666</v>
@@ -1094,7 +1094,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.3115234375</v>
+        <v>918.311462402344</v>
       </c>
       <c r="H25" t="n">
         <v>64565</v>
@@ -1123,7 +1123,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.533020019531</v>
+        <v>950.532897949219</v>
       </c>
       <c r="H26" t="n">
         <v>64029</v>
@@ -1152,7 +1152,7 @@
         <v>1082.48315429688</v>
       </c>
       <c r="G27" t="n">
-        <v>836.952392578125</v>
+        <v>836.952331542969</v>
       </c>
       <c r="H27" t="n">
         <v>42864</v>
@@ -1210,7 +1210,7 @@
         <v>1119.98974609375</v>
       </c>
       <c r="G29" t="n">
-        <v>865.95166015625</v>
+        <v>865.951599121094</v>
       </c>
       <c r="H29" t="n">
         <v>60147</v>
@@ -1239,7 +1239,7 @@
         <v>1009.34521484375</v>
       </c>
       <c r="G30" t="n">
-        <v>780.403686523438</v>
+        <v>780.403625488281</v>
       </c>
       <c r="H30" t="n">
         <v>46957</v>
@@ -1268,7 +1268,7 @@
         <v>956.8359375</v>
       </c>
       <c r="G31" t="n">
-        <v>739.8046875</v>
+        <v>739.804626464844</v>
       </c>
       <c r="H31" t="n">
         <v>71729</v>
@@ -1297,7 +1297,7 @@
         <v>1044.97644042969</v>
       </c>
       <c r="G32" t="n">
-        <v>807.953002929688</v>
+        <v>807.952941894531</v>
       </c>
       <c r="H32" t="n">
         <v>67475</v>
@@ -1326,7 +1326,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.4228515625</v>
+        <v>905.422912597656</v>
       </c>
       <c r="H33" t="n">
         <v>78116</v>
@@ -1384,7 +1384,7 @@
         <v>1077.27392578125</v>
       </c>
       <c r="G35" t="n">
-        <v>832.924621582031</v>
+        <v>832.924682617188</v>
       </c>
       <c r="H35" t="n">
         <v>48406</v>
@@ -1413,7 +1413,7 @@
         <v>1066.85534667969</v>
       </c>
       <c r="G36" t="n">
-        <v>824.869323730469</v>
+        <v>824.869262695312</v>
       </c>
       <c r="H36" t="n">
         <v>40227</v>
@@ -1500,7 +1500,7 @@
         <v>1073.1064453125</v>
       </c>
       <c r="G39" t="n">
-        <v>829.702514648438</v>
+        <v>829.702453613281</v>
       </c>
       <c r="H39" t="n">
         <v>36745</v>
@@ -1529,7 +1529,7 @@
         <v>1079.35754394531</v>
       </c>
       <c r="G40" t="n">
-        <v>834.53564453125</v>
+        <v>834.535705566406</v>
       </c>
       <c r="H40" t="n">
         <v>38826</v>
@@ -1587,7 +1587,7 @@
         <v>1024.7646484375</v>
       </c>
       <c r="G42" t="n">
-        <v>792.325622558594</v>
+        <v>792.32568359375</v>
       </c>
       <c r="H42" t="n">
         <v>166009</v>
@@ -1790,7 +1790,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G49" t="n">
-        <v>853.86865234375</v>
+        <v>853.868591308594</v>
       </c>
       <c r="H49" t="n">
         <v>45335</v>
@@ -1819,7 +1819,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G50" t="n">
-        <v>853.86865234375</v>
+        <v>853.868591308594</v>
       </c>
       <c r="H50" t="n">
         <v>70901</v>
@@ -1848,7 +1848,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977905273438</v>
+        <v>927.977966308594</v>
       </c>
       <c r="H51" t="n">
         <v>78651</v>
@@ -1877,7 +1877,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03131103516</v>
+        <v>1023.03137207031</v>
       </c>
       <c r="H52" t="n">
         <v>99090</v>
@@ -1906,7 +1906,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810424804688</v>
+        <v>961.810485839844</v>
       </c>
       <c r="H53" t="n">
         <v>82251</v>
@@ -1935,7 +1935,7 @@
         <v>1245.01184082031</v>
       </c>
       <c r="G54" t="n">
-        <v>962.616027832031</v>
+        <v>962.615966796875</v>
       </c>
       <c r="H54" t="n">
         <v>47448</v>
@@ -1964,7 +1964,7 @@
         <v>1193.96118164062</v>
       </c>
       <c r="G55" t="n">
-        <v>923.144775390625</v>
+        <v>923.144714355469</v>
       </c>
       <c r="H55" t="n">
         <v>43553</v>
@@ -1993,7 +1993,7 @@
         <v>1240.84448242188</v>
       </c>
       <c r="G56" t="n">
-        <v>959.393859863281</v>
+        <v>959.393920898438</v>
       </c>
       <c r="H56" t="n">
         <v>50887</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254028320312</v>
+        <v>997.254089355469</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2080,7 +2080,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199340820312</v>
+        <v>960.199462890625</v>
       </c>
       <c r="H59" t="n">
         <v>31218</v>
@@ -2109,7 +2109,7 @@
         <v>1177.29162597656</v>
       </c>
       <c r="G60" t="n">
-        <v>910.256225585938</v>
+        <v>910.256164550781</v>
       </c>
       <c r="H60" t="n">
         <v>37028</v>
@@ -2167,7 +2167,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813232421875</v>
+        <v>845.813171386719</v>
       </c>
       <c r="H62" t="n">
         <v>30190</v>
@@ -2225,7 +2225,7 @@
         <v>1040.18395996094</v>
       </c>
       <c r="G64" t="n">
-        <v>804.24755859375</v>
+        <v>804.247497558594</v>
       </c>
       <c r="H64" t="n">
         <v>34669</v>
@@ -2254,7 +2254,7 @@
         <v>1000.80200195312</v>
       </c>
       <c r="G65" t="n">
-        <v>773.798278808594</v>
+        <v>773.798217773438</v>
       </c>
       <c r="H65" t="n">
         <v>36991</v>
@@ -2341,7 +2341,7 @@
         <v>908.702392578125</v>
       </c>
       <c r="G68" t="n">
-        <v>702.5888671875</v>
+        <v>702.588806152344</v>
       </c>
       <c r="H68" t="n">
         <v>37316</v>
@@ -2370,7 +2370,7 @@
         <v>980.381713867188</v>
       </c>
       <c r="G69" t="n">
-        <v>758.009704589844</v>
+        <v>758.009765625</v>
       </c>
       <c r="H69" t="n">
         <v>52413</v>
@@ -2428,7 +2428,7 @@
         <v>1088.73425292969</v>
       </c>
       <c r="G71" t="n">
-        <v>841.785583496094</v>
+        <v>841.785522460938</v>
       </c>
       <c r="H71" t="n">
         <v>71518</v>
@@ -2515,7 +2515,7 @@
         <v>1251.26293945312</v>
       </c>
       <c r="G74" t="n">
-        <v>967.449157714844</v>
+        <v>967.44921875</v>
       </c>
       <c r="H74" t="n">
         <v>42225</v>
@@ -2544,7 +2544,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.19738769531</v>
+        <v>1047.197265625</v>
       </c>
       <c r="H75" t="n">
         <v>71166</v>
@@ -2573,7 +2573,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03131103516</v>
+        <v>1023.03137207031</v>
       </c>
       <c r="H76" t="n">
         <v>87970</v>
@@ -2602,7 +2602,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86291503906</v>
+        <v>1085.86303710938</v>
       </c>
       <c r="H77" t="n">
         <v>60062</v>
@@ -2689,7 +2689,7 @@
         <v>1379.41064453125</v>
       </c>
       <c r="G80" t="n">
-        <v>1066.5302734375</v>
+        <v>1066.53015136719</v>
       </c>
       <c r="H80" t="n">
         <v>19070</v>
@@ -2834,7 +2834,7 @@
         <v>1390.87097167969</v>
       </c>
       <c r="G85" t="n">
-        <v>1075.39111328125</v>
+        <v>1075.39099121094</v>
       </c>
       <c r="H85" t="n">
         <v>43075</v>
@@ -2892,7 +2892,7 @@
         <v>1267.9326171875</v>
       </c>
       <c r="G87" t="n">
-        <v>980.337829589844</v>
+        <v>980.337768554688</v>
       </c>
       <c r="H87" t="n">
         <v>37678</v>
@@ -2979,7 +2979,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G90" t="n">
-        <v>965.032592773438</v>
+        <v>965.032653808594</v>
       </c>
       <c r="H90" t="n">
         <v>33396</v>
@@ -3008,7 +3008,7 @@
         <v>1208.54711914062</v>
       </c>
       <c r="G91" t="n">
-        <v>934.422241210938</v>
+        <v>934.422302246094</v>
       </c>
       <c r="H91" t="n">
         <v>37385</v>
@@ -3066,7 +3066,7 @@
         <v>1153.32897949219</v>
       </c>
       <c r="G93" t="n">
-        <v>891.728759765625</v>
+        <v>891.728820800781</v>
       </c>
       <c r="H93" t="n">
         <v>32662</v>
@@ -3124,7 +3124,7 @@
         <v>1163.74755859375</v>
       </c>
       <c r="G95" t="n">
-        <v>899.7841796875</v>
+        <v>899.784240722656</v>
       </c>
       <c r="H95" t="n">
         <v>21832</v>
@@ -3153,7 +3153,7 @@
         <v>1156.45458984375</v>
       </c>
       <c r="G96" t="n">
-        <v>894.145446777344</v>
+        <v>894.1455078125</v>
       </c>
       <c r="H96" t="n">
         <v>29015</v>
@@ -3269,7 +3269,7 @@
         <v>1159.580078125</v>
       </c>
       <c r="G100" t="n">
-        <v>896.561950683594</v>
+        <v>896.56201171875</v>
       </c>
       <c r="H100" t="n">
         <v>16345</v>
@@ -3298,7 +3298,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809753417969</v>
+        <v>990.809814453125</v>
       </c>
       <c r="H101" t="n">
         <v>46314</v>
@@ -3327,7 +3327,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47613525391</v>
+        <v>1000.47625732422</v>
       </c>
       <c r="H102" t="n">
         <v>46119</v>
@@ -3356,7 +3356,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.14270019531</v>
+        <v>1010.142578125</v>
       </c>
       <c r="H103" t="n">
         <v>21794</v>
@@ -3385,7 +3385,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17034912109</v>
+        <v>1014.17028808594</v>
       </c>
       <c r="H104" t="n">
         <v>14276</v>
@@ -3443,7 +3443,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.69830322266</v>
+        <v>1003.6982421875</v>
       </c>
       <c r="H106" t="n">
         <v>20322</v>
@@ -3472,7 +3472,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G107" t="n">
-        <v>965.032592773438</v>
+        <v>965.032653808594</v>
       </c>
       <c r="H107" t="n">
         <v>26277</v>
@@ -3501,7 +3501,7 @@
         <v>1274.18371582031</v>
       </c>
       <c r="G108" t="n">
-        <v>985.171020507812</v>
+        <v>985.170959472656</v>
       </c>
       <c r="H108" t="n">
         <v>32082</v>
@@ -3530,7 +3530,7 @@
         <v>1214.79821777344</v>
       </c>
       <c r="G109" t="n">
-        <v>939.255432128906</v>
+        <v>939.255493164062</v>
       </c>
       <c r="H109" t="n">
         <v>27462</v>
@@ -3588,7 +3588,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809753417969</v>
+        <v>990.809814453125</v>
       </c>
       <c r="H111" t="n">
         <v>28141</v>
@@ -3646,7 +3646,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.143981933594</v>
+        <v>952.143920898438</v>
       </c>
       <c r="H113" t="n">
         <v>14885</v>
@@ -3704,7 +3704,7 @@
         <v>1046.01831054688</v>
       </c>
       <c r="G115" t="n">
-        <v>808.758483886719</v>
+        <v>808.758544921875</v>
       </c>
       <c r="H115" t="n">
         <v>39052</v>
@@ -3791,7 +3791,7 @@
         <v>1003.30242919922</v>
       </c>
       <c r="G118" t="n">
-        <v>775.731506347656</v>
+        <v>775.731567382812</v>
       </c>
       <c r="H118" t="n">
         <v>34176</v>
@@ -3849,7 +3849,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368225097656</v>
+        <v>868.368286132812</v>
       </c>
       <c r="H120" t="n">
         <v>32561</v>
@@ -3965,7 +3965,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749267578125</v>
+        <v>731.749328613281</v>
       </c>
       <c r="H124" t="n">
         <v>64325</v>
@@ -3994,7 +3994,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118286132812</v>
+        <v>634.118225097656</v>
       </c>
       <c r="H125" t="n">
         <v>71078</v>
@@ -4052,7 +4052,7 @@
         <v>809.934936523438</v>
       </c>
       <c r="G127" t="n">
-        <v>626.223937988281</v>
+        <v>626.223999023438</v>
       </c>
       <c r="H127" t="n">
         <v>44209</v>
@@ -4139,7 +4139,7 @@
         <v>685.537902832031</v>
       </c>
       <c r="G130" t="n">
-        <v>530.04296875</v>
+        <v>530.042907714844</v>
       </c>
       <c r="H130" t="n">
         <v>79855</v>
@@ -4168,7 +4168,7 @@
         <v>552.597717285156</v>
       </c>
       <c r="G131" t="n">
-        <v>427.256469726562</v>
+        <v>427.256500244141</v>
       </c>
       <c r="H131" t="n">
         <v>109680</v>
@@ -4197,7 +4197,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194793701172</v>
+        <v>453.194732666016</v>
       </c>
       <c r="H132" t="n">
         <v>69237</v>
@@ -4226,7 +4226,7 @@
         <v>552.181030273438</v>
       </c>
       <c r="G133" t="n">
-        <v>426.934326171875</v>
+        <v>426.934295654297</v>
       </c>
       <c r="H133" t="n">
         <v>49476</v>
@@ -4284,7 +4284,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549652099609</v>
+        <v>481.549591064453</v>
       </c>
       <c r="H135" t="n">
         <v>39529</v>
@@ -4342,7 +4342,7 @@
         <v>680.745422363281</v>
       </c>
       <c r="G137" t="n">
-        <v>526.337524414062</v>
+        <v>526.337463378906</v>
       </c>
       <c r="H137" t="n">
         <v>93205</v>
@@ -4429,7 +4429,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259399414062</v>
+        <v>538.259460449219</v>
       </c>
       <c r="H140" t="n">
         <v>34135</v>
@@ -4458,7 +4458,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.53759765625</v>
+        <v>520.537658691406</v>
       </c>
       <c r="H141" t="n">
         <v>36777</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710083007812</v>
+        <v>510.710113525391</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4545,7 +4545,7 @@
         <v>650.114990234375</v>
       </c>
       <c r="G144" t="n">
-        <v>502.654754638672</v>
+        <v>502.654693603516</v>
       </c>
       <c r="H144" t="n">
         <v>26528</v>
@@ -4574,7 +4574,7 @@
         <v>595.313598632812</v>
       </c>
       <c r="G145" t="n">
-        <v>460.283477783203</v>
+        <v>460.283447265625</v>
       </c>
       <c r="H145" t="n">
         <v>58255</v>
@@ -4661,7 +4661,7 @@
         <v>604.273559570312</v>
       </c>
       <c r="G148" t="n">
-        <v>467.211120605469</v>
+        <v>467.211151123047</v>
       </c>
       <c r="H148" t="n">
         <v>26200</v>
@@ -4690,7 +4690,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532592773438</v>
+        <v>496.532653808594</v>
       </c>
       <c r="H149" t="n">
         <v>46906</v>
@@ -4748,7 +4748,7 @@
         <v>541.970886230469</v>
       </c>
       <c r="G151" t="n">
-        <v>419.040069580078</v>
+        <v>419.0400390625</v>
       </c>
       <c r="H151" t="n">
         <v>45660</v>
@@ -4806,7 +4806,7 @@
         <v>539.678771972656</v>
       </c>
       <c r="G153" t="n">
-        <v>417.267822265625</v>
+        <v>417.267852783203</v>
       </c>
       <c r="H153" t="n">
         <v>31277</v>
@@ -4835,7 +4835,7 @@
         <v>531.135620117188</v>
       </c>
       <c r="G154" t="n">
-        <v>410.662445068359</v>
+        <v>410.662475585938</v>
       </c>
       <c r="H154" t="n">
         <v>36401</v>
@@ -4951,7 +4951,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384948730469</v>
+        <v>399.384918212891</v>
       </c>
       <c r="H158" t="n">
         <v>11284</v>
@@ -4980,7 +4980,7 @@
         <v>523.009155273438</v>
       </c>
       <c r="G159" t="n">
-        <v>404.379241943359</v>
+        <v>404.379272460938</v>
       </c>
       <c r="H159" t="n">
         <v>21609</v>
@@ -5067,7 +5067,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G162" t="n">
-        <v>378.602111816406</v>
+        <v>378.602081298828</v>
       </c>
       <c r="H162" t="n">
         <v>24713</v>
@@ -5125,7 +5125,7 @@
         <v>477.58447265625</v>
       </c>
       <c r="G164" t="n">
-        <v>369.257873535156</v>
+        <v>369.257904052734</v>
       </c>
       <c r="H164" t="n">
         <v>11396</v>
@@ -5154,7 +5154,7 @@
         <v>494.879211425781</v>
       </c>
       <c r="G165" t="n">
-        <v>382.629821777344</v>
+        <v>382.629791259766</v>
       </c>
       <c r="H165" t="n">
         <v>15915</v>
@@ -5415,7 +5415,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724182128906</v>
+        <v>384.724212646484</v>
       </c>
       <c r="H174" t="n">
         <v>11728</v>
@@ -5444,7 +5444,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G175" t="n">
-        <v>378.602111816406</v>
+        <v>378.602081298828</v>
       </c>
       <c r="H175" t="n">
         <v>11244</v>
@@ -5502,7 +5502,7 @@
         <v>509.465118408203</v>
       </c>
       <c r="G177" t="n">
-        <v>393.907318115234</v>
+        <v>393.907287597656</v>
       </c>
       <c r="H177" t="n">
         <v>26337</v>
@@ -5589,7 +5589,7 @@
         <v>476.125885009766</v>
       </c>
       <c r="G180" t="n">
-        <v>368.130157470703</v>
+        <v>368.130126953125</v>
       </c>
       <c r="H180" t="n">
         <v>18405</v>
@@ -5676,7 +5676,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436706542969</v>
+        <v>325.436737060547</v>
       </c>
       <c r="H183" t="n">
         <v>78778</v>
@@ -5705,7 +5705,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214569091797</v>
+        <v>322.214538574219</v>
       </c>
       <c r="H184" t="n">
         <v>24033</v>
@@ -5763,7 +5763,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003784179688</v>
+        <v>309.003753662109</v>
       </c>
       <c r="H186" t="n">
         <v>27102</v>
@@ -5821,7 +5821,7 @@
         <v>392.569427490234</v>
       </c>
       <c r="G188" t="n">
-        <v>303.526123046875</v>
+        <v>303.526092529297</v>
       </c>
       <c r="H188" t="n">
         <v>15965</v>
@@ -5879,7 +5879,7 @@
         <v>404.86328125</v>
       </c>
       <c r="G190" t="n">
-        <v>313.031463623047</v>
+        <v>313.031433105469</v>
       </c>
       <c r="H190" t="n">
         <v>26142</v>
@@ -5908,7 +5908,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742584228516</v>
+        <v>311.742614746094</v>
       </c>
       <c r="H191" t="n">
         <v>13716</v>
@@ -6053,7 +6053,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843353271484</v>
+        <v>279.843322753906</v>
       </c>
       <c r="H196" t="n">
         <v>54804</v>
@@ -6082,7 +6082,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499114990234</v>
+        <v>270.499145507812</v>
       </c>
       <c r="H197" t="n">
         <v>45392</v>
@@ -6111,7 +6111,7 @@
         <v>354.229309082031</v>
       </c>
       <c r="G198" t="n">
-        <v>273.882385253906</v>
+        <v>273.882354736328</v>
       </c>
       <c r="H198" t="n">
         <v>39961</v>
@@ -6227,7 +6227,7 @@
         <v>355.896270751953</v>
       </c>
       <c r="G202" t="n">
-        <v>275.171203613281</v>
+        <v>275.171234130859</v>
       </c>
       <c r="H202" t="n">
         <v>17732</v>
@@ -6285,7 +6285,7 @@
         <v>360.897155761719</v>
       </c>
       <c r="G204" t="n">
-        <v>279.037811279297</v>
+        <v>279.037780761719</v>
       </c>
       <c r="H204" t="n">
         <v>13463</v>
@@ -6372,7 +6372,7 @@
         <v>497.379638671875</v>
       </c>
       <c r="G207" t="n">
-        <v>384.563049316406</v>
+        <v>384.563079833984</v>
       </c>
       <c r="H207" t="n">
         <v>111579</v>
@@ -6459,7 +6459,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266510009766</v>
+        <v>475.266448974609</v>
       </c>
       <c r="H210" t="n">
         <v>166520</v>
@@ -6488,7 +6488,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184112548828</v>
+        <v>434.184143066406</v>
       </c>
       <c r="H211" t="n">
         <v>136414</v>
@@ -6546,7 +6546,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906616210938</v>
+        <v>422.906585693359</v>
       </c>
       <c r="H213" t="n">
         <v>68253</v>
@@ -6575,7 +6575,7 @@
         <v>506.547943115234</v>
       </c>
       <c r="G214" t="n">
-        <v>391.651794433594</v>
+        <v>391.651824951172</v>
       </c>
       <c r="H214" t="n">
         <v>68364</v>
@@ -6691,7 +6691,7 @@
         <v>439.661102294922</v>
       </c>
       <c r="G218" t="n">
-        <v>339.936370849609</v>
+        <v>339.936340332031</v>
       </c>
       <c r="H218" t="n">
         <v>64785</v>
@@ -6720,7 +6720,7 @@
         <v>537.178344726562</v>
       </c>
       <c r="G219" t="n">
-        <v>415.334564208984</v>
+        <v>415.334594726562</v>
       </c>
       <c r="H219" t="n">
         <v>97389</v>
@@ -6749,7 +6749,7 @@
         <v>558.015380859375</v>
       </c>
       <c r="G220" t="n">
-        <v>431.445281982422</v>
+        <v>431.4453125</v>
       </c>
       <c r="H220" t="n">
         <v>158097</v>
@@ -6865,7 +6865,7 @@
         <v>583.228149414062</v>
       </c>
       <c r="G224" t="n">
-        <v>450.939270019531</v>
+        <v>450.939239501953</v>
       </c>
       <c r="H224" t="n">
         <v>123957</v>
@@ -6894,7 +6894,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829284667969</v>
+        <v>405.829254150391</v>
       </c>
       <c r="H225" t="n">
         <v>74636</v>
@@ -6952,7 +6952,7 @@
         <v>495.712677001953</v>
       </c>
       <c r="G227" t="n">
-        <v>383.274200439453</v>
+        <v>383.274230957031</v>
       </c>
       <c r="H227" t="n">
         <v>36344</v>
@@ -7068,7 +7068,7 @@
         <v>464.040405273438</v>
       </c>
       <c r="G231" t="n">
-        <v>358.785919189453</v>
+        <v>358.785888671875</v>
       </c>
       <c r="H231" t="n">
         <v>44014</v>
@@ -7126,7 +7126,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214569091797</v>
+        <v>322.214538574219</v>
       </c>
       <c r="H233" t="n">
         <v>63341</v>
@@ -7271,7 +7271,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H238" t="n">
         <v>56464</v>
@@ -7416,7 +7416,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H243" t="n">
         <v>108228</v>
@@ -7561,7 +7561,7 @@
         <v>436.118774414062</v>
       </c>
       <c r="G248" t="n">
-        <v>337.197509765625</v>
+        <v>337.197540283203</v>
       </c>
       <c r="H248" t="n">
         <v>78353</v>
@@ -7590,7 +7590,7 @@
         <v>387.985260009766</v>
       </c>
       <c r="G249" t="n">
-        <v>299.981719970703</v>
+        <v>299.981750488281</v>
       </c>
       <c r="H249" t="n">
         <v>107400</v>
@@ -7648,7 +7648,7 @@
         <v>339.643371582031</v>
       </c>
       <c r="G251" t="n">
-        <v>262.604827880859</v>
+        <v>262.604858398438</v>
       </c>
       <c r="H251" t="n">
         <v>159767</v>
@@ -13883,7 +13883,7 @@
         <v>94.8084259033203</v>
       </c>
       <c r="G466" t="n">
-        <v>73.3038024902344</v>
+        <v>73.3038101196289</v>
       </c>
       <c r="H466" t="n">
         <v>2488563</v>
@@ -13912,7 +13912,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.171516418457</v>
+        <v>76.1715087890625</v>
       </c>
       <c r="H467" t="n">
         <v>616657</v>
@@ -13941,7 +13941,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003997802734</v>
+        <v>76.3003921508789</v>
       </c>
       <c r="H468" t="n">
         <v>232423</v>
@@ -14057,7 +14057,7 @@
         <v>97.0588302612305</v>
       </c>
       <c r="G472" t="n">
-        <v>75.0437622070312</v>
+        <v>75.0437698364258</v>
       </c>
       <c r="H472" t="n">
         <v>68056</v>
@@ -14086,7 +14086,7 @@
         <v>95.4335403442383</v>
       </c>
       <c r="G473" t="n">
-        <v>73.7871322631836</v>
+        <v>73.7871246337891</v>
       </c>
       <c r="H473" t="n">
         <v>87104</v>
@@ -14144,7 +14144,7 @@
         <v>93.6832275390625</v>
       </c>
       <c r="G475" t="n">
-        <v>72.4338302612305</v>
+        <v>72.4338226318359</v>
       </c>
       <c r="H475" t="n">
         <v>148288</v>
@@ -14231,7 +14231,7 @@
         <v>85.4734420776367</v>
       </c>
       <c r="G478" t="n">
-        <v>66.0862045288086</v>
+        <v>66.0861968994141</v>
       </c>
       <c r="H478" t="n">
         <v>120033</v>
@@ -14260,7 +14260,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.1218299865723</v>
+        <v>63.1218338012695</v>
       </c>
       <c r="H479" t="n">
         <v>202691</v>
@@ -14318,7 +14318,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264404296875</v>
+        <v>56.2264366149902</v>
       </c>
       <c r="H481" t="n">
         <v>308433</v>
@@ -14347,7 +14347,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064903259277</v>
+        <v>53.9064865112305</v>
       </c>
       <c r="H482" t="n">
         <v>255815</v>
@@ -14492,7 +14492,7 @@
         <v>82.0978469848633</v>
       </c>
       <c r="G487" t="n">
-        <v>63.4762649536133</v>
+        <v>63.476261138916</v>
       </c>
       <c r="H487" t="n">
         <v>63428</v>
@@ -14521,7 +14521,7 @@
         <v>83.306396484375</v>
       </c>
       <c r="G488" t="n">
-        <v>64.4106826782227</v>
+        <v>64.4106903076172</v>
       </c>
       <c r="H488" t="n">
         <v>91362</v>
@@ -14550,7 +14550,7 @@
         <v>84.1815490722656</v>
       </c>
       <c r="G489" t="n">
-        <v>65.0873413085938</v>
+        <v>65.0873336791992</v>
       </c>
       <c r="H489" t="n">
         <v>130214</v>
@@ -14579,7 +14579,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906692504883</v>
+        <v>64.9906616210938</v>
       </c>
       <c r="H490" t="n">
         <v>123807</v>
@@ -14637,7 +14637,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539779663086</v>
+        <v>66.0539855957031</v>
       </c>
       <c r="H492" t="n">
         <v>305053</v>
@@ -14753,7 +14753,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G496" t="n">
-        <v>62.8318367004395</v>
+        <v>62.8318290710449</v>
       </c>
       <c r="H496" t="n">
         <v>50947</v>
@@ -14782,7 +14782,7 @@
         <v>80.4725646972656</v>
       </c>
       <c r="G497" t="n">
-        <v>62.2196311950684</v>
+        <v>62.2196273803711</v>
       </c>
       <c r="H497" t="n">
         <v>56838</v>
@@ -14840,7 +14840,7 @@
         <v>80.4308853149414</v>
       </c>
       <c r="G499" t="n">
-        <v>62.1874084472656</v>
+        <v>62.1874046325684</v>
       </c>
       <c r="H499" t="n">
         <v>32132</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563186645508</v>
+        <v>61.156322479248</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -14927,7 +14927,7 @@
         <v>78.430534362793</v>
       </c>
       <c r="G502" t="n">
-        <v>60.6407737731934</v>
+        <v>60.6407814025879</v>
       </c>
       <c r="H502" t="n">
         <v>45614</v>
@@ -14956,7 +14956,7 @@
         <v>77.5137023925781</v>
       </c>
       <c r="G503" t="n">
-        <v>59.9319038391113</v>
+        <v>59.9319000244141</v>
       </c>
       <c r="H503" t="n">
         <v>48461</v>
@@ -15014,7 +15014,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H505" t="n">
         <v>57550</v>
@@ -15043,7 +15043,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G506" t="n">
-        <v>62.5096168518066</v>
+        <v>62.5096206665039</v>
       </c>
       <c r="H506" t="n">
         <v>88056</v>
@@ -15101,7 +15101,7 @@
         <v>79.7640991210938</v>
       </c>
       <c r="G508" t="n">
-        <v>61.6718597412109</v>
+        <v>61.6718559265137</v>
       </c>
       <c r="H508" t="n">
         <v>34426</v>
@@ -15159,7 +15159,7 @@
         <v>81.93115234375</v>
       </c>
       <c r="G510" t="n">
-        <v>63.3473739624023</v>
+        <v>63.3473777770996</v>
       </c>
       <c r="H510" t="n">
         <v>35391</v>
@@ -15188,7 +15188,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573806762695</v>
+        <v>63.0573844909668</v>
       </c>
       <c r="H511" t="n">
         <v>34562</v>
@@ -15217,7 +15217,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H512" t="n">
         <v>22428</v>
@@ -15246,7 +15246,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.4129600524902</v>
+        <v>62.4129524230957</v>
       </c>
       <c r="H513" t="n">
         <v>27484</v>
@@ -15304,7 +15304,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H515" t="n">
         <v>30486</v>
@@ -15333,7 +15333,7 @@
         <v>80.8476257324219</v>
       </c>
       <c r="G516" t="n">
-        <v>62.5096168518066</v>
+        <v>62.5096206665039</v>
       </c>
       <c r="H516" t="n">
         <v>30537</v>
@@ -15391,7 +15391,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G518" t="n">
-        <v>63.9273643493652</v>
+        <v>63.927360534668</v>
       </c>
       <c r="H518" t="n">
         <v>298961</v>
@@ -15449,7 +15449,7 @@
         <v>83.7231369018555</v>
       </c>
       <c r="G520" t="n">
-        <v>64.7329025268555</v>
+        <v>64.7328948974609</v>
       </c>
       <c r="H520" t="n">
         <v>131635</v>
@@ -15536,7 +15536,7 @@
         <v>82.681282043457</v>
       </c>
       <c r="G523" t="n">
-        <v>63.9273643493652</v>
+        <v>63.927360534668</v>
       </c>
       <c r="H523" t="n">
         <v>45681</v>
@@ -15565,7 +15565,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G524" t="n">
-        <v>62.8318367004395</v>
+        <v>62.8318290710449</v>
       </c>
       <c r="H524" t="n">
         <v>49745</v>
@@ -15594,7 +15594,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H525" t="n">
         <v>40067</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184944152832</v>
+        <v>63.2184867858887</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15652,7 +15652,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.6707305908203</v>
+        <v>62.6707344055176</v>
       </c>
       <c r="H527" t="n">
         <v>45359</v>
@@ -15681,7 +15681,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G528" t="n">
-        <v>62.8318367004395</v>
+        <v>62.8318290710449</v>
       </c>
       <c r="H528" t="n">
         <v>57552</v>
@@ -15710,7 +15710,7 @@
         <v>81.0143203735352</v>
       </c>
       <c r="G529" t="n">
-        <v>62.6385078430176</v>
+        <v>62.6385040283203</v>
       </c>
       <c r="H529" t="n">
         <v>50236</v>
@@ -15768,7 +15768,7 @@
         <v>80.555908203125</v>
       </c>
       <c r="G531" t="n">
-        <v>62.2840728759766</v>
+        <v>62.2840690612793</v>
       </c>
       <c r="H531" t="n">
         <v>74076</v>
@@ -15797,7 +15797,7 @@
         <v>78.8055953979492</v>
       </c>
       <c r="G532" t="n">
-        <v>60.9307670593262</v>
+        <v>60.9307632446289</v>
       </c>
       <c r="H532" t="n">
         <v>101055</v>
@@ -15855,7 +15855,7 @@
         <v>77.9721221923828</v>
       </c>
       <c r="G534" t="n">
-        <v>60.2863464355469</v>
+        <v>60.2863426208496</v>
       </c>
       <c r="H534" t="n">
         <v>68146</v>
@@ -15884,7 +15884,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397041320801</v>
+        <v>58.7397117614746</v>
       </c>
       <c r="H535" t="n">
         <v>102598</v>
@@ -15942,7 +15942,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.0607872009277</v>
+        <v>60.0607833862305</v>
       </c>
       <c r="H537" t="n">
         <v>142371</v>
@@ -15971,7 +15971,7 @@
         <v>78.1388168334961</v>
       </c>
       <c r="G538" t="n">
-        <v>60.4152221679688</v>
+        <v>60.4152297973633</v>
       </c>
       <c r="H538" t="n">
         <v>64920</v>
@@ -16000,7 +16000,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.8363761901855</v>
+        <v>58.836368560791</v>
       </c>
       <c r="H539" t="n">
         <v>77063</v>
@@ -16058,7 +16058,7 @@
         <v>74.8048934936523</v>
       </c>
       <c r="G541" t="n">
-        <v>57.8375129699707</v>
+        <v>57.8375091552734</v>
       </c>
       <c r="H541" t="n">
         <v>169917</v>
@@ -16087,7 +16087,7 @@
         <v>70.8458557128906</v>
       </c>
       <c r="G542" t="n">
-        <v>54.7764701843262</v>
+        <v>54.7764663696289</v>
       </c>
       <c r="H542" t="n">
         <v>196506</v>
@@ -16145,7 +16145,7 @@
         <v>71.8877105712891</v>
       </c>
       <c r="G544" t="n">
-        <v>55.5820121765137</v>
+        <v>55.5820045471191</v>
       </c>
       <c r="H544" t="n">
         <v>70492</v>
@@ -16203,7 +16203,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.4692306518555</v>
+        <v>55.46923828125</v>
       </c>
       <c r="H546" t="n">
         <v>24192</v>
@@ -16290,7 +16290,7 @@
         <v>67.0951995849609</v>
       </c>
       <c r="G549" t="n">
-        <v>51.8765411376953</v>
+        <v>51.8765449523926</v>
       </c>
       <c r="H549" t="n">
         <v>124037</v>
@@ -16348,7 +16348,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.0054321289062</v>
+        <v>52.005428314209</v>
       </c>
       <c r="H551" t="n">
         <v>83287</v>
@@ -16406,7 +16406,7 @@
         <v>66.9910125732422</v>
       </c>
       <c r="G553" t="n">
-        <v>51.7959861755371</v>
+        <v>51.7959899902344</v>
       </c>
       <c r="H553" t="n">
         <v>50170</v>
@@ -16435,7 +16435,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832122802734</v>
+        <v>51.6832160949707</v>
       </c>
       <c r="H554" t="n">
         <v>49117</v>
@@ -16522,7 +16522,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G557" t="n">
-        <v>51.2321128845215</v>
+        <v>51.2321166992188</v>
       </c>
       <c r="H557" t="n">
         <v>73571</v>
@@ -16551,7 +16551,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G558" t="n">
-        <v>51.2321128845215</v>
+        <v>51.2321166992188</v>
       </c>
       <c r="H558" t="n">
         <v>20722</v>
@@ -16609,7 +16609,7 @@
         <v>65.4282302856445</v>
       </c>
       <c r="G560" t="n">
-        <v>50.5876770019531</v>
+        <v>50.5876808166504</v>
       </c>
       <c r="H560" t="n">
         <v>38087</v>
@@ -16638,7 +16638,7 @@
         <v>65.0114974975586</v>
       </c>
       <c r="G561" t="n">
-        <v>50.2654724121094</v>
+        <v>50.2654685974121</v>
       </c>
       <c r="H561" t="n">
         <v>34140</v>
@@ -16696,7 +16696,7 @@
         <v>63.6987609863281</v>
       </c>
       <c r="G563" t="n">
-        <v>49.25048828125</v>
+        <v>49.2504920959473</v>
       </c>
       <c r="H563" t="n">
         <v>49204</v>
@@ -16725,7 +16725,7 @@
         <v>63.8237838745117</v>
       </c>
       <c r="G564" t="n">
-        <v>49.3471527099609</v>
+        <v>49.3471565246582</v>
       </c>
       <c r="H564" t="n">
         <v>41188</v>
@@ -16899,7 +16899,7 @@
         <v>56.0099029541016</v>
       </c>
       <c r="G570" t="n">
-        <v>43.3056373596191</v>
+        <v>43.3056335449219</v>
       </c>
       <c r="H570" t="n">
         <v>225410</v>
@@ -16928,7 +16928,7 @@
         <v>54.3221054077148</v>
       </c>
       <c r="G571" t="n">
-        <v>42.0006637573242</v>
+        <v>42.0006675720215</v>
       </c>
       <c r="H571" t="n">
         <v>114062</v>
@@ -16957,7 +16957,7 @@
         <v>52.9051856994629</v>
       </c>
       <c r="G572" t="n">
-        <v>40.9051361083984</v>
+        <v>40.9051322937012</v>
       </c>
       <c r="H572" t="n">
         <v>130898</v>
@@ -17015,7 +17015,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367904663086</v>
+        <v>41.4367866516113</v>
       </c>
       <c r="H574" t="n">
         <v>153152</v>
@@ -17044,7 +17044,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184783935547</v>
+        <v>40.5184745788574</v>
       </c>
       <c r="H575" t="n">
         <v>92688</v>
@@ -17073,7 +17073,7 @@
         <v>53.1969032287598</v>
       </c>
       <c r="G576" t="n">
-        <v>41.130687713623</v>
+        <v>41.1306838989258</v>
       </c>
       <c r="H576" t="n">
         <v>90811</v>
@@ -17102,7 +17102,7 @@
         <v>57.8435592651367</v>
       </c>
       <c r="G577" t="n">
-        <v>44.7233734130859</v>
+        <v>44.7233772277832</v>
       </c>
       <c r="H577" t="n">
         <v>304629</v>
@@ -17218,7 +17218,7 @@
         <v>55.5723266601562</v>
       </c>
       <c r="G581" t="n">
-        <v>42.9673118591309</v>
+        <v>42.9673080444336</v>
       </c>
       <c r="H581" t="n">
         <v>116018</v>
@@ -17276,7 +17276,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H583" t="n">
         <v>160680</v>
@@ -17305,7 +17305,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G584" t="n">
-        <v>42.9511947631836</v>
+        <v>42.9511985778809</v>
       </c>
       <c r="H584" t="n">
         <v>78005</v>
@@ -17334,7 +17334,7 @@
         <v>55.5306510925293</v>
       </c>
       <c r="G585" t="n">
-        <v>42.9350852966309</v>
+        <v>42.9350891113281</v>
       </c>
       <c r="H585" t="n">
         <v>117880</v>
@@ -17363,7 +17363,7 @@
         <v>56.8850555419922</v>
       </c>
       <c r="G586" t="n">
-        <v>43.9822845458984</v>
+        <v>43.9822807312012</v>
       </c>
       <c r="H586" t="n">
         <v>88984</v>
@@ -17450,7 +17450,7 @@
         <v>56.1974334716797</v>
       </c>
       <c r="G589" t="n">
-        <v>43.450626373291</v>
+        <v>43.4506301879883</v>
       </c>
       <c r="H589" t="n">
         <v>63710</v>
@@ -17566,7 +17566,7 @@
         <v>55.4889755249023</v>
       </c>
       <c r="G593" t="n">
-        <v>42.9028663635254</v>
+        <v>42.9028625488281</v>
       </c>
       <c r="H593" t="n">
         <v>40012</v>
@@ -17653,7 +17653,7 @@
         <v>56.2599449157715</v>
       </c>
       <c r="G596" t="n">
-        <v>43.4989585876465</v>
+        <v>43.4989624023438</v>
       </c>
       <c r="H596" t="n">
         <v>59156</v>
@@ -17682,7 +17682,7 @@
         <v>54.780517578125</v>
       </c>
       <c r="G597" t="n">
-        <v>42.3551025390625</v>
+        <v>42.3550987243652</v>
       </c>
       <c r="H597" t="n">
         <v>77570</v>
@@ -17769,7 +17769,7 @@
         <v>57.3017959594727</v>
       </c>
       <c r="G600" t="n">
-        <v>44.304500579834</v>
+        <v>44.3044967651367</v>
       </c>
       <c r="H600" t="n">
         <v>186430</v>
@@ -17798,7 +17798,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.821174621582</v>
+        <v>43.8211784362793</v>
       </c>
       <c r="H601" t="n">
         <v>72323</v>
@@ -17856,7 +17856,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431816101074</v>
+        <v>52.8431777954102</v>
       </c>
       <c r="H603" t="n">
         <v>634116</v>
@@ -17943,7 +17943,7 @@
         <v>60.9066009521484</v>
       </c>
       <c r="G606" t="n">
-        <v>47.0916557312012</v>
+        <v>47.0916519165039</v>
       </c>
       <c r="H606" t="n">
         <v>628237</v>
@@ -17972,7 +17972,7 @@
         <v>58.7603874206543</v>
       </c>
       <c r="G607" t="n">
-        <v>45.4322509765625</v>
+        <v>45.4322471618652</v>
       </c>
       <c r="H607" t="n">
         <v>352792</v>
@@ -18030,7 +18030,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194732666016</v>
+        <v>45.3194770812988</v>
       </c>
       <c r="H609" t="n">
         <v>202532</v>
@@ -18088,7 +18088,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G611" t="n">
-        <v>44.3206062316895</v>
+        <v>44.3206100463867</v>
       </c>
       <c r="H611" t="n">
         <v>142469</v>
@@ -18175,7 +18175,7 @@
         <v>52.2800750732422</v>
       </c>
       <c r="G614" t="n">
-        <v>40.4218101501465</v>
+        <v>40.4218139648438</v>
       </c>
       <c r="H614" t="n">
         <v>255740</v>
@@ -18233,7 +18233,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H616" t="n">
         <v>281053</v>
@@ -18291,7 +18291,7 @@
         <v>55.5514869689941</v>
       </c>
       <c r="G618" t="n">
-        <v>42.9511947631836</v>
+        <v>42.9511985778809</v>
       </c>
       <c r="H618" t="n">
         <v>69954</v>
@@ -18378,7 +18378,7 @@
         <v>57.1976127624512</v>
       </c>
       <c r="G621" t="n">
-        <v>44.2239418029785</v>
+        <v>44.2239456176758</v>
       </c>
       <c r="H621" t="n">
         <v>99660</v>
@@ -18407,7 +18407,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250785827637</v>
+        <v>43.2250747680664</v>
       </c>
       <c r="H622" t="n">
         <v>51718</v>
@@ -18465,7 +18465,7 @@
         <v>57.3226356506348</v>
       </c>
       <c r="G624" t="n">
-        <v>44.3206062316895</v>
+        <v>44.3206100463867</v>
       </c>
       <c r="H624" t="n">
         <v>48032</v>
@@ -18494,7 +18494,7 @@
         <v>58.5520172119141</v>
       </c>
       <c r="G625" t="n">
-        <v>45.2711372375488</v>
+        <v>45.2711410522461</v>
       </c>
       <c r="H625" t="n">
         <v>62650</v>
@@ -18668,7 +18668,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767501831055</v>
       </c>
       <c r="H631" t="n">
         <v>46391</v>
@@ -18813,7 +18813,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.373477935791</v>
+        <v>40.3734817504883</v>
       </c>
       <c r="H636" t="n">
         <v>90143</v>
@@ -18929,7 +18929,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.567943572998</v>
+        <v>39.5679397583008</v>
       </c>
       <c r="H640" t="n">
         <v>70245</v>
@@ -18958,7 +18958,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062728881836</v>
+        <v>39.9062690734863</v>
       </c>
       <c r="H641" t="n">
         <v>47114</v>
@@ -19364,7 +19364,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374298095703</v>
       </c>
       <c r="H655" t="n">
         <v>34543</v>
@@ -19538,7 +19538,7 @@
         <v>51.5299453735352</v>
       </c>
       <c r="G661" t="n">
-        <v>39.8418312072754</v>
+        <v>39.8418273925781</v>
       </c>
       <c r="H661" t="n">
         <v>115915</v>
@@ -19596,7 +19596,7 @@
         <v>49.3628921508789</v>
       </c>
       <c r="G663" t="n">
-        <v>38.1663093566895</v>
+        <v>38.1663131713867</v>
       </c>
       <c r="H663" t="n">
         <v>91978</v>
@@ -19770,7 +19770,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G669" t="n">
-        <v>35.4435997009277</v>
+        <v>35.4435958862305</v>
       </c>
       <c r="H669" t="n">
         <v>39954</v>
@@ -19828,7 +19828,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G671" t="n">
-        <v>35.4435997009277</v>
+        <v>35.4435958862305</v>
       </c>
       <c r="H671" t="n">
         <v>76441</v>
@@ -19857,7 +19857,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G672" t="n">
-        <v>35.395263671875</v>
+        <v>35.3952674865723</v>
       </c>
       <c r="H672" t="n">
         <v>39171</v>
@@ -19915,7 +19915,7 @@
         <v>45.9247856140137</v>
       </c>
       <c r="G674" t="n">
-        <v>35.5080413818359</v>
+        <v>35.5080375671387</v>
       </c>
       <c r="H674" t="n">
         <v>38417</v>
@@ -20060,7 +20060,7 @@
         <v>45.4038581848145</v>
       </c>
       <c r="G679" t="n">
-        <v>35.1052742004395</v>
+        <v>35.1052703857422</v>
       </c>
       <c r="H679" t="n">
         <v>107371</v>
@@ -20118,7 +20118,7 @@
         <v>43.132625579834</v>
       </c>
       <c r="G681" t="n">
-        <v>33.3492012023926</v>
+        <v>33.3492050170898</v>
       </c>
       <c r="H681" t="n">
         <v>52451</v>
@@ -20234,7 +20234,7 @@
         <v>46.3206901550293</v>
       </c>
       <c r="G685" t="n">
-        <v>35.8141479492188</v>
+        <v>35.8141441345215</v>
       </c>
       <c r="H685" t="n">
         <v>78485</v>
@@ -20263,7 +20263,7 @@
         <v>45.7789268493652</v>
       </c>
       <c r="G686" t="n">
-        <v>35.395263671875</v>
+        <v>35.3952674865723</v>
       </c>
       <c r="H686" t="n">
         <v>55186</v>
@@ -20292,7 +20292,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G687" t="n">
-        <v>38.3113059997559</v>
+        <v>38.3113098144531</v>
       </c>
       <c r="H687" t="n">
         <v>246032</v>
@@ -20321,7 +20321,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374298095703</v>
       </c>
       <c r="H688" t="n">
         <v>118566</v>
@@ -20350,7 +20350,7 @@
         <v>47.695930480957</v>
       </c>
       <c r="G689" t="n">
-        <v>36.8774490356445</v>
+        <v>36.8774528503418</v>
       </c>
       <c r="H689" t="n">
         <v>132939</v>
@@ -20437,7 +20437,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057754516602</v>
+        <v>37.5057678222656</v>
       </c>
       <c r="H692" t="n">
         <v>93100</v>
@@ -20582,7 +20582,7 @@
         <v>49.5504264831543</v>
       </c>
       <c r="G697" t="n">
-        <v>38.3113059997559</v>
+        <v>38.3113098144531</v>
       </c>
       <c r="H697" t="n">
         <v>47583</v>
@@ -20611,7 +20611,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563064575195</v>
+        <v>38.4563026428223</v>
       </c>
       <c r="H698" t="n">
         <v>127098</v>
@@ -20640,7 +20640,7 @@
         <v>50.175537109375</v>
       </c>
       <c r="G699" t="n">
-        <v>38.7946319580078</v>
+        <v>38.7946281433105</v>
       </c>
       <c r="H699" t="n">
         <v>37785</v>
@@ -20756,7 +20756,7 @@
         <v>42.9242553710938</v>
       </c>
       <c r="G703" t="n">
-        <v>33.1880989074707</v>
+        <v>33.1880950927734</v>
       </c>
       <c r="H703" t="n">
         <v>149650</v>
@@ -20785,7 +20785,7 @@
         <v>42.861743927002</v>
       </c>
       <c r="G704" t="n">
-        <v>33.1397666931152</v>
+        <v>33.139762878418</v>
       </c>
       <c r="H704" t="n">
         <v>60234</v>
@@ -20930,7 +20930,7 @@
         <v>38.5068092346191</v>
       </c>
       <c r="G709" t="n">
-        <v>29.7726230621338</v>
+        <v>29.7726249694824</v>
       </c>
       <c r="H709" t="n">
         <v>137943</v>
@@ -20959,7 +20959,7 @@
         <v>37.0377998352051</v>
       </c>
       <c r="G710" t="n">
-        <v>28.6368179321289</v>
+        <v>28.6368198394775</v>
       </c>
       <c r="H710" t="n">
         <v>115092</v>
@@ -21017,7 +21017,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884857177734</v>
+        <v>28.5884838104248</v>
       </c>
       <c r="H712" t="n">
         <v>79946</v>
@@ -21046,7 +21046,7 @@
         <v>36.089714050293</v>
       </c>
       <c r="G713" t="n">
-        <v>27.9037799835205</v>
+        <v>27.9037780761719</v>
       </c>
       <c r="H713" t="n">
         <v>152219</v>
@@ -21075,7 +21075,7 @@
         <v>35.7875785827637</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6701736450195</v>
+        <v>27.6701755523682</v>
       </c>
       <c r="H714" t="n">
         <v>86668</v>
@@ -21104,7 +21104,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532451629639</v>
+        <v>26.9532432556152</v>
       </c>
       <c r="H715" t="n">
         <v>100245</v>
@@ -21162,7 +21162,7 @@
         <v>31.3805484771729</v>
       </c>
       <c r="G717" t="n">
-        <v>24.2627544403076</v>
+        <v>24.2627563476562</v>
       </c>
       <c r="H717" t="n">
         <v>177943</v>
@@ -21191,7 +21191,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766651153564</v>
+        <v>23.3766632080078</v>
       </c>
       <c r="H718" t="n">
         <v>180004</v>
@@ -21481,7 +21481,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480247497559</v>
+        <v>24.4480266571045</v>
       </c>
       <c r="H728" t="n">
         <v>59503</v>
@@ -21510,7 +21510,7 @@
         <v>30.7137622833252</v>
       </c>
       <c r="G729" t="n">
-        <v>23.7472114562988</v>
+        <v>23.7472095489502</v>
       </c>
       <c r="H729" t="n">
         <v>111085</v>
@@ -21597,7 +21597,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177577972412</v>
+        <v>24.1177558898926</v>
       </c>
       <c r="H732" t="n">
         <v>82427</v>
@@ -21684,7 +21684,7 @@
         <v>29.411449432373</v>
       </c>
       <c r="G735" t="n">
-        <v>22.740291595459</v>
+        <v>22.7402896881104</v>
       </c>
       <c r="H735" t="n">
         <v>76940</v>
@@ -21713,7 +21713,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005805969238</v>
+        <v>22.2005825042725</v>
       </c>
       <c r="H736" t="n">
         <v>72375</v>
@@ -21800,7 +21800,7 @@
         <v>28.7863388061523</v>
       </c>
       <c r="G739" t="n">
-        <v>22.2569694519043</v>
+        <v>22.2569675445557</v>
       </c>
       <c r="H739" t="n">
         <v>68543</v>
@@ -21858,7 +21858,7 @@
         <v>29.7031688690186</v>
       </c>
       <c r="G741" t="n">
-        <v>22.9658432006836</v>
+        <v>22.965841293335</v>
       </c>
       <c r="H741" t="n">
         <v>64021</v>
@@ -22061,7 +22061,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715534210205</v>
+        <v>27.8715572357178</v>
       </c>
       <c r="H748" t="n">
         <v>89948</v>
@@ -22090,7 +22090,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782302856445</v>
+        <v>27.6782283782959</v>
       </c>
       <c r="H749" t="n">
         <v>99834</v>
@@ -22119,7 +22119,7 @@
         <v>33.3809013366699</v>
       </c>
       <c r="G750" t="n">
-        <v>25.809383392334</v>
+        <v>25.8093852996826</v>
       </c>
       <c r="H750" t="n">
         <v>76706</v>
@@ -22148,7 +22148,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363166809082</v>
+        <v>26.2363185882568</v>
       </c>
       <c r="H751" t="n">
         <v>69130</v>
@@ -22206,7 +22206,7 @@
         <v>31.8285446166992</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6091365814209</v>
+        <v>24.6091346740723</v>
       </c>
       <c r="H753" t="n">
         <v>76863</v>
@@ -22235,7 +22235,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193920135498</v>
+        <v>25.5193939208984</v>
       </c>
       <c r="H754" t="n">
         <v>87590</v>
@@ -22264,7 +22264,7 @@
         <v>32.9329071044922</v>
       </c>
       <c r="G755" t="n">
-        <v>25.4630031585693</v>
+        <v>25.463005065918</v>
       </c>
       <c r="H755" t="n">
         <v>93592</v>
@@ -22322,7 +22322,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077491760254</v>
       </c>
       <c r="H757" t="n">
         <v>41825</v>
@@ -22351,7 +22351,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983089447021</v>
+        <v>24.1983127593994</v>
       </c>
       <c r="H758" t="n">
         <v>28653</v>
@@ -22409,7 +22409,7 @@
         <v>31.2451076507568</v>
       </c>
       <c r="G760" t="n">
-        <v>24.1580352783203</v>
+        <v>24.1580333709717</v>
       </c>
       <c r="H760" t="n">
         <v>71582</v>
@@ -22438,7 +22438,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H761" t="n">
         <v>113781</v>
@@ -22525,7 +22525,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G764" t="n">
-        <v>24.6494102478027</v>
+        <v>24.6494121551514</v>
       </c>
       <c r="H764" t="n">
         <v>57921</v>
@@ -22583,7 +22583,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399738311768</v>
+        <v>24.4399700164795</v>
       </c>
       <c r="H766" t="n">
         <v>84803</v>
@@ -22612,7 +22612,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G767" t="n">
-        <v>24.6171894073486</v>
+        <v>24.6171913146973</v>
       </c>
       <c r="H767" t="n">
         <v>49945</v>
@@ -22670,7 +22670,7 @@
         <v>31.6618461608887</v>
       </c>
       <c r="G769" t="n">
-        <v>24.4802474975586</v>
+        <v>24.4802494049072</v>
       </c>
       <c r="H769" t="n">
         <v>65021</v>
@@ -22699,7 +22699,7 @@
         <v>31.8181247711182</v>
       </c>
       <c r="G770" t="n">
-        <v>24.6010799407959</v>
+        <v>24.6010780334473</v>
       </c>
       <c r="H770" t="n">
         <v>51778</v>
@@ -22728,7 +22728,7 @@
         <v>31.4013843536377</v>
       </c>
       <c r="G771" t="n">
-        <v>24.278865814209</v>
+        <v>24.2788639068604</v>
       </c>
       <c r="H771" t="n">
         <v>59036</v>
@@ -22757,7 +22757,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058700561523</v>
+        <v>21.8058681488037</v>
       </c>
       <c r="H772" t="n">
         <v>398596</v>
@@ -22786,7 +22786,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G773" t="n">
-        <v>20.1384086608887</v>
+        <v>20.13840675354</v>
       </c>
       <c r="H773" t="n">
         <v>541685</v>
@@ -22873,7 +22873,7 @@
         <v>25.5774383544922</v>
       </c>
       <c r="G776" t="n">
-        <v>19.775915145874</v>
+        <v>19.7759170532227</v>
       </c>
       <c r="H776" t="n">
         <v>194733</v>
@@ -22960,7 +22960,7 @@
         <v>25.5461826324463</v>
       </c>
       <c r="G779" t="n">
-        <v>19.7517509460449</v>
+        <v>19.7517490386963</v>
       </c>
       <c r="H779" t="n">
         <v>108228</v>
@@ -23018,7 +23018,7 @@
         <v>25.8795757293701</v>
       </c>
       <c r="G781" t="n">
-        <v>20.0095233917236</v>
+        <v>20.009521484375</v>
       </c>
       <c r="H781" t="n">
         <v>68304</v>
@@ -23250,7 +23250,7 @@
         <v>25.7962265014648</v>
       </c>
       <c r="G789" t="n">
-        <v>19.9450798034668</v>
+        <v>19.9450778961182</v>
       </c>
       <c r="H789" t="n">
         <v>147656</v>
@@ -23366,7 +23366,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H793" t="n">
         <v>765447</v>
@@ -23395,7 +23395,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G794" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H794" t="n">
         <v>554437</v>
@@ -23424,7 +23424,7 @@
         <v>27.7653255462646</v>
       </c>
       <c r="G795" t="n">
-        <v>21.4675426483154</v>
+        <v>21.4675445556641</v>
       </c>
       <c r="H795" t="n">
         <v>207446</v>
@@ -23511,7 +23511,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083885192871</v>
+        <v>21.0083866119385</v>
       </c>
       <c r="H798" t="n">
         <v>100025</v>
@@ -23540,7 +23540,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G799" t="n">
-        <v>20.9922752380371</v>
+        <v>20.9922771453857</v>
       </c>
       <c r="H799" t="n">
         <v>101229</v>
@@ -23598,7 +23598,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136741638184</v>
+        <v>20.6136722564697</v>
       </c>
       <c r="H801" t="n">
         <v>58055</v>
@@ -23714,7 +23714,7 @@
         <v>28.3695983886719</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9347553253174</v>
+        <v>21.9347534179688</v>
       </c>
       <c r="H805" t="n">
         <v>225218</v>
@@ -23801,7 +23801,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H808" t="n">
         <v>86623</v>
@@ -23830,7 +23830,7 @@
         <v>28.213321685791</v>
       </c>
       <c r="G809" t="n">
-        <v>21.8139228820801</v>
+        <v>21.8139247894287</v>
       </c>
       <c r="H809" t="n">
         <v>93205</v>
@@ -23888,7 +23888,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G811" t="n">
-        <v>20.9922752380371</v>
+        <v>20.9922771453857</v>
       </c>
       <c r="H811" t="n">
         <v>85007</v>
@@ -23975,7 +23975,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G814" t="n">
-        <v>20.2109050750732</v>
+        <v>20.2109069824219</v>
       </c>
       <c r="H814" t="n">
         <v>72125</v>
@@ -24033,7 +24033,7 @@
         <v>26.4109191894531</v>
       </c>
       <c r="G816" t="n">
-        <v>20.4203472137451</v>
+        <v>20.4203453063965</v>
       </c>
       <c r="H816" t="n">
         <v>121401</v>
@@ -24062,7 +24062,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908935546875</v>
+        <v>20.7908916473389</v>
       </c>
       <c r="H817" t="n">
         <v>135708</v>
@@ -24091,7 +24091,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H818" t="n">
         <v>142172</v>
@@ -24120,7 +24120,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G819" t="n">
-        <v>21.4917087554932</v>
+        <v>21.4917106628418</v>
       </c>
       <c r="H819" t="n">
         <v>111493</v>
@@ -24149,7 +24149,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G820" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H820" t="n">
         <v>116471</v>
@@ -24178,7 +24178,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5008983612061</v>
+        <v>20.5009002685547</v>
       </c>
       <c r="H821" t="n">
         <v>75021</v>
@@ -24207,7 +24207,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H822" t="n">
         <v>72133</v>
@@ -24236,7 +24236,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G823" t="n">
-        <v>20.2995128631592</v>
+        <v>20.2995147705078</v>
       </c>
       <c r="H823" t="n">
         <v>50892</v>
@@ -24265,7 +24265,7 @@
         <v>25.9837608337402</v>
       </c>
       <c r="G824" t="n">
-        <v>20.0900783538818</v>
+        <v>20.0900764465332</v>
       </c>
       <c r="H824" t="n">
         <v>122105</v>
@@ -24294,7 +24294,7 @@
         <v>26.0462703704834</v>
       </c>
       <c r="G825" t="n">
-        <v>20.1384086608887</v>
+        <v>20.13840675354</v>
       </c>
       <c r="H825" t="n">
         <v>67600</v>
@@ -24381,7 +24381,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G828" t="n">
-        <v>20.1706314086914</v>
+        <v>20.1706295013428</v>
       </c>
       <c r="H828" t="n">
         <v>55529</v>
@@ -24410,7 +24410,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G829" t="n">
-        <v>20.2995128631592</v>
+        <v>20.2995147705078</v>
       </c>
       <c r="H829" t="n">
         <v>73545</v>
@@ -24439,7 +24439,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G830" t="n">
-        <v>20.4284019470215</v>
+        <v>20.4284000396729</v>
       </c>
       <c r="H830" t="n">
         <v>56424</v>
@@ -24497,7 +24497,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G832" t="n">
-        <v>20.4284019470215</v>
+        <v>20.4284000396729</v>
       </c>
       <c r="H832" t="n">
         <v>33693</v>
@@ -24526,7 +24526,7 @@
         <v>26.3171520233154</v>
       </c>
       <c r="G833" t="n">
-        <v>20.3478450775146</v>
+        <v>20.3478469848633</v>
       </c>
       <c r="H833" t="n">
         <v>51548</v>
@@ -24555,7 +24555,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G834" t="n">
-        <v>20.1706314086914</v>
+        <v>20.1706295013428</v>
       </c>
       <c r="H834" t="n">
         <v>86286</v>
@@ -24613,7 +24613,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H836" t="n">
         <v>263799</v>
@@ -24758,7 +24758,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G841" t="n">
-        <v>21.7494792938232</v>
+        <v>21.7494812011719</v>
       </c>
       <c r="H841" t="n">
         <v>67797</v>
@@ -24816,7 +24816,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G843" t="n">
-        <v>21.185604095459</v>
+        <v>21.1856060028076</v>
       </c>
       <c r="H843" t="n">
         <v>56383</v>
@@ -24961,7 +24961,7 @@
         <v>28.3800163269043</v>
       </c>
       <c r="G848" t="n">
-        <v>21.9428081512451</v>
+        <v>21.9428100585938</v>
       </c>
       <c r="H848" t="n">
         <v>228370</v>
@@ -25019,7 +25019,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150615692139</v>
+        <v>20.8150596618652</v>
       </c>
       <c r="H850" t="n">
         <v>79359</v>
@@ -25309,7 +25309,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G860" t="n">
-        <v>18.4145603179932</v>
+        <v>18.4145584106445</v>
       </c>
       <c r="H860" t="n">
         <v>61245</v>
@@ -25367,7 +25367,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H862" t="n">
         <v>131429</v>
@@ -25396,7 +25396,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G863" t="n">
-        <v>17.8667945861816</v>
+        <v>17.8667964935303</v>
       </c>
       <c r="H863" t="n">
         <v>69191</v>
@@ -25512,7 +25512,7 @@
         <v>21.8580303192139</v>
       </c>
       <c r="G867" t="n">
-        <v>16.9001502990723</v>
+        <v>16.9001522064209</v>
       </c>
       <c r="H867" t="n">
         <v>72401</v>
@@ -25628,7 +25628,7 @@
         <v>21.1704082489014</v>
       </c>
       <c r="G871" t="n">
-        <v>16.3684978485107</v>
+        <v>16.3684959411621</v>
       </c>
       <c r="H871" t="n">
         <v>85174</v>
@@ -25657,7 +25657,7 @@
         <v>20.9828758239746</v>
       </c>
       <c r="G872" t="n">
-        <v>16.2235012054443</v>
+        <v>16.223503112793</v>
       </c>
       <c r="H872" t="n">
         <v>64631</v>
@@ -25744,7 +25744,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907138824463</v>
+        <v>16.6907119750977</v>
       </c>
       <c r="H875" t="n">
         <v>61152</v>
@@ -25802,7 +25802,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134944915771</v>
+        <v>16.5134963989258</v>
       </c>
       <c r="H877" t="n">
         <v>48820</v>
@@ -25831,7 +25831,7 @@
         <v>21.0662231445312</v>
       </c>
       <c r="G878" t="n">
-        <v>16.2879428863525</v>
+        <v>16.2879447937012</v>
       </c>
       <c r="H878" t="n">
         <v>56625</v>
@@ -26005,7 +26005,7 @@
         <v>21.9205417633057</v>
       </c>
       <c r="G884" t="n">
-        <v>16.9484825134277</v>
+        <v>16.9484844207764</v>
       </c>
       <c r="H884" t="n">
         <v>58458</v>
@@ -26121,7 +26121,7 @@
         <v>22.4623031616211</v>
       </c>
       <c r="G888" t="n">
-        <v>17.3673629760742</v>
+        <v>17.3673610687256</v>
       </c>
       <c r="H888" t="n">
         <v>52523</v>
@@ -26208,7 +26208,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G891" t="n">
-        <v>19.187873840332</v>
+        <v>19.1878757476807</v>
       </c>
       <c r="H891" t="n">
         <v>189581</v>
@@ -26295,7 +26295,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H894" t="n">
         <v>1152937</v>
@@ -26440,7 +26440,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321678161621</v>
+        <v>25.6321659088135</v>
       </c>
       <c r="H899" t="n">
         <v>451580</v>
@@ -26498,7 +26498,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G901" t="n">
-        <v>26.1154899597168</v>
+        <v>26.1154880523682</v>
       </c>
       <c r="H901" t="n">
         <v>172580</v>
@@ -26527,7 +26527,7 @@
         <v>33.4642486572266</v>
       </c>
       <c r="G902" t="n">
-        <v>25.8738250732422</v>
+        <v>25.8738269805908</v>
       </c>
       <c r="H902" t="n">
         <v>95164</v>
@@ -26614,7 +26614,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H905" t="n">
         <v>121784</v>
@@ -26730,7 +26730,7 @@
         <v>29.4427051544189</v>
       </c>
       <c r="G909" t="n">
-        <v>22.7644577026367</v>
+        <v>22.7644557952881</v>
       </c>
       <c r="H909" t="n">
         <v>66556</v>
@@ -26759,7 +26759,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G910" t="n">
-        <v>21.7494792938232</v>
+        <v>21.7494812011719</v>
       </c>
       <c r="H910" t="n">
         <v>231966</v>
@@ -26788,7 +26788,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H911" t="n">
         <v>124106</v>
@@ -26846,7 +26846,7 @@
         <v>27.1923065185547</v>
       </c>
       <c r="G913" t="n">
-        <v>21.0244960784912</v>
+        <v>21.0244979858398</v>
       </c>
       <c r="H913" t="n">
         <v>226257</v>
@@ -26962,7 +26962,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G917" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H917" t="n">
         <v>101465</v>
@@ -26991,7 +26991,7 @@
         <v>24.7752132415771</v>
       </c>
       <c r="G918" t="n">
-        <v>19.1556529998779</v>
+        <v>19.1556549072266</v>
       </c>
       <c r="H918" t="n">
         <v>269232</v>
@@ -27020,7 +27020,7 @@
         <v>25.0877685546875</v>
       </c>
       <c r="G919" t="n">
-        <v>19.3973159790039</v>
+        <v>19.3973140716553</v>
       </c>
       <c r="H919" t="n">
         <v>122716</v>
@@ -27049,7 +27049,7 @@
         <v>26.9005889892578</v>
       </c>
       <c r="G920" t="n">
-        <v>20.7989463806152</v>
+        <v>20.7989482879639</v>
       </c>
       <c r="H920" t="n">
         <v>193491</v>
@@ -27078,7 +27078,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G921" t="n">
-        <v>20.9922752380371</v>
+        <v>20.9922771453857</v>
       </c>
       <c r="H921" t="n">
         <v>265131</v>
@@ -27107,7 +27107,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.910587310791</v>
+        <v>21.9105892181396</v>
       </c>
       <c r="H922" t="n">
         <v>183228</v>
@@ -27136,7 +27136,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005805969238</v>
+        <v>22.2005825042725</v>
       </c>
       <c r="H923" t="n">
         <v>187583</v>
@@ -27310,7 +27310,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.685037612915</v>
+        <v>21.6850395202637</v>
       </c>
       <c r="H929" t="n">
         <v>97800</v>
@@ -27397,7 +27397,7 @@
         <v>30.2136745452881</v>
       </c>
       <c r="G932" t="n">
-        <v>23.3605518341064</v>
+        <v>23.3605537414551</v>
       </c>
       <c r="H932" t="n">
         <v>674039</v>
@@ -27513,7 +27513,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H936" t="n">
         <v>340303</v>
@@ -27571,7 +27571,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416061401367</v>
+        <v>25.8416080474854</v>
       </c>
       <c r="H938" t="n">
         <v>128698</v>
@@ -27745,7 +27745,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G944" t="n">
-        <v>26.1154899597168</v>
+        <v>26.1154880523682</v>
       </c>
       <c r="H944" t="n">
         <v>380608</v>
@@ -27774,7 +27774,7 @@
         <v>33.7976417541504</v>
       </c>
       <c r="G945" t="n">
-        <v>26.1315975189209</v>
+        <v>26.1315994262695</v>
       </c>
       <c r="H945" t="n">
         <v>97707</v>
@@ -27803,7 +27803,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H946" t="n">
         <v>289611</v>
@@ -27832,7 +27832,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993766784668</v>
+        <v>26.0993747711182</v>
       </c>
       <c r="H947" t="n">
         <v>135438</v>
@@ -27890,7 +27890,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G949" t="n">
-        <v>25.1327362060547</v>
+        <v>25.1327342987061</v>
       </c>
       <c r="H949" t="n">
         <v>164909</v>
@@ -28006,7 +28006,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G953" t="n">
-        <v>24.6171894073486</v>
+        <v>24.6171913146973</v>
       </c>
       <c r="H953" t="n">
         <v>64598</v>
@@ -28064,7 +28064,7 @@
         <v>30.3178596496582</v>
       </c>
       <c r="G955" t="n">
-        <v>23.4411087036133</v>
+        <v>23.4411067962646</v>
       </c>
       <c r="H955" t="n">
         <v>170866</v>
@@ -28151,7 +28151,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727592468262</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H958" t="n">
         <v>106089</v>
@@ -28238,7 +28238,7 @@
         <v>30.5887413024902</v>
       </c>
       <c r="G961" t="n">
-        <v>23.6505451202393</v>
+        <v>23.6505470275879</v>
       </c>
       <c r="H961" t="n">
         <v>140338</v>
@@ -28354,7 +28354,7 @@
         <v>31.3388748168945</v>
       </c>
       <c r="G965" t="n">
-        <v>24.2305335998535</v>
+        <v>24.2305355072021</v>
       </c>
       <c r="H965" t="n">
         <v>256042</v>
@@ -28557,7 +28557,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G972" t="n">
-        <v>23.9244270324707</v>
+        <v>23.9244289398193</v>
       </c>
       <c r="H972" t="n">
         <v>39949</v>
@@ -28731,7 +28731,7 @@
         <v>31.2346897125244</v>
       </c>
       <c r="G978" t="n">
-        <v>24.1499786376953</v>
+        <v>24.1499805450439</v>
       </c>
       <c r="H978" t="n">
         <v>163262</v>
@@ -28818,7 +28818,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077491760254</v>
       </c>
       <c r="H981" t="n">
         <v>162326</v>
@@ -28876,7 +28876,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G983" t="n">
-        <v>23.9244270324707</v>
+        <v>23.9244289398193</v>
       </c>
       <c r="H983" t="n">
         <v>59846</v>
@@ -28963,7 +28963,7 @@
         <v>30.7971115112305</v>
       </c>
       <c r="G986" t="n">
-        <v>23.811653137207</v>
+        <v>23.8116550445557</v>
       </c>
       <c r="H986" t="n">
         <v>68207</v>
@@ -28992,7 +28992,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H987" t="n">
         <v>52930</v>
@@ -29021,7 +29021,7 @@
         <v>30.9429702758789</v>
       </c>
       <c r="G988" t="n">
-        <v>23.9244270324707</v>
+        <v>23.9244289398193</v>
       </c>
       <c r="H988" t="n">
         <v>68067</v>
@@ -29050,7 +29050,7 @@
         <v>30.4428825378418</v>
       </c>
       <c r="G989" t="n">
-        <v>23.5377712249756</v>
+        <v>23.5377731323242</v>
       </c>
       <c r="H989" t="n">
         <v>96270</v>
@@ -29108,7 +29108,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H991" t="n">
         <v>68666</v>
@@ -29166,7 +29166,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G993" t="n">
-        <v>23.5861015319824</v>
+        <v>23.5861034393311</v>
       </c>
       <c r="H993" t="n">
         <v>46714</v>
@@ -29224,7 +29224,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727592468262</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H995" t="n">
         <v>242944</v>
@@ -29282,7 +29282,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H997" t="n">
         <v>75104</v>
@@ -29398,7 +29398,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1001" t="n">
-        <v>22.5227947235107</v>
+        <v>22.5227966308594</v>
       </c>
       <c r="H1001" t="n">
         <v>101377</v>
@@ -29427,7 +29427,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1002" t="n">
-        <v>22.6355686187744</v>
+        <v>22.635570526123</v>
       </c>
       <c r="H1002" t="n">
         <v>70616</v>
@@ -29456,7 +29456,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1003" t="n">
-        <v>23.0061168670654</v>
+        <v>23.0061187744141</v>
       </c>
       <c r="H1003" t="n">
         <v>96029</v>
@@ -29514,7 +29514,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1005" t="n">
-        <v>22.4744625091553</v>
+        <v>22.4744644165039</v>
       </c>
       <c r="H1005" t="n">
         <v>82787</v>
@@ -29543,7 +29543,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1006" t="n">
-        <v>23.0061168670654</v>
+        <v>23.0061187744141</v>
       </c>
       <c r="H1006" t="n">
         <v>86215</v>
@@ -29601,7 +29601,7 @@
         <v>29.2968463897705</v>
       </c>
       <c r="G1008" t="n">
-        <v>22.651683807373</v>
+        <v>22.6516819000244</v>
       </c>
       <c r="H1008" t="n">
         <v>46369</v>
@@ -29630,7 +29630,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1009" t="n">
-        <v>22.4744625091553</v>
+        <v>22.4744644165039</v>
       </c>
       <c r="H1009" t="n">
         <v>71916</v>
@@ -29659,7 +29659,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1010" t="n">
-        <v>21.9911422729492</v>
+        <v>21.9911403656006</v>
       </c>
       <c r="H1010" t="n">
         <v>116651</v>
@@ -29688,7 +29688,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844692230225</v>
+        <v>22.1844711303711</v>
       </c>
       <c r="H1011" t="n">
         <v>138206</v>
@@ -29746,7 +29746,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1013" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1013" t="n">
         <v>50162</v>
@@ -29775,7 +29775,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1014" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1014" t="n">
         <v>48803</v>
@@ -29804,7 +29804,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1015" t="n">
-        <v>22.5227947235107</v>
+        <v>22.5227966308594</v>
       </c>
       <c r="H1015" t="n">
         <v>63776</v>
@@ -30094,7 +30094,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821323394775</v>
+        <v>27.0821304321289</v>
       </c>
       <c r="H1025" t="n">
         <v>329331</v>
@@ -30123,7 +30123,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1026" t="n">
-        <v>27.3076801300049</v>
+        <v>27.3076820373535</v>
       </c>
       <c r="H1026" t="n">
         <v>378731</v>
@@ -30181,7 +30181,7 @@
         <v>35.7146453857422</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.6137847900391</v>
+        <v>27.6137828826904</v>
       </c>
       <c r="H1028" t="n">
         <v>133385</v>
@@ -30210,7 +30210,7 @@
         <v>39.069408416748</v>
       </c>
       <c r="G1029" t="n">
-        <v>30.2076110839844</v>
+        <v>30.2076148986816</v>
       </c>
       <c r="H1029" t="n">
         <v>1179620</v>
@@ -30239,7 +30239,7 @@
         <v>38.9652214050293</v>
       </c>
       <c r="G1030" t="n">
-        <v>30.1270599365234</v>
+        <v>30.1270580291748</v>
       </c>
       <c r="H1030" t="n">
         <v>657786</v>
@@ -30268,7 +30268,7 @@
         <v>37.9650459289551</v>
       </c>
       <c r="G1031" t="n">
-        <v>29.3537464141846</v>
+        <v>29.3537425994873</v>
       </c>
       <c r="H1031" t="n">
         <v>257810</v>
@@ -30384,7 +30384,7 @@
         <v>37.73583984375</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1765289306641</v>
+        <v>29.1765270233154</v>
       </c>
       <c r="H1035" t="n">
         <v>228495</v>
@@ -30442,7 +30442,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1037" t="n">
-        <v>27.3076801300049</v>
+        <v>27.3076820373535</v>
       </c>
       <c r="H1037" t="n">
         <v>256721</v>
@@ -30471,7 +30471,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1038" t="n">
-        <v>27.3076801300049</v>
+        <v>27.3076820373535</v>
       </c>
       <c r="H1038" t="n">
         <v>147337</v>
@@ -30500,7 +30500,7 @@
         <v>37.2774238586426</v>
       </c>
       <c r="G1039" t="n">
-        <v>28.8220882415771</v>
+        <v>28.8220901489258</v>
       </c>
       <c r="H1039" t="n">
         <v>439132</v>
@@ -30529,7 +30529,7 @@
         <v>37.1940765380859</v>
       </c>
       <c r="G1040" t="n">
-        <v>28.7576465606689</v>
+        <v>28.7576484680176</v>
       </c>
       <c r="H1040" t="n">
         <v>194824</v>
@@ -30558,7 +30558,7 @@
         <v>37.9233703613281</v>
       </c>
       <c r="G1041" t="n">
-        <v>29.3215198516846</v>
+        <v>29.3215217590332</v>
       </c>
       <c r="H1041" t="n">
         <v>364128</v>
@@ -30616,7 +30616,7 @@
         <v>36.1105499267578</v>
       </c>
       <c r="G1043" t="n">
-        <v>27.9198875427246</v>
+        <v>27.9198894500732</v>
       </c>
       <c r="H1043" t="n">
         <v>263584</v>
@@ -30761,7 +30761,7 @@
         <v>37.5274696350098</v>
       </c>
       <c r="G1048" t="n">
-        <v>29.0154209136963</v>
+        <v>29.0154190063477</v>
       </c>
       <c r="H1048" t="n">
         <v>161694</v>
@@ -30790,7 +30790,7 @@
         <v>39.4444732666016</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.4976043701172</v>
+        <v>30.4976062774658</v>
       </c>
       <c r="H1049" t="n">
         <v>881669</v>
@@ -30877,7 +30877,7 @@
         <v>42.5075149536133</v>
       </c>
       <c r="G1052" t="n">
-        <v>32.8658828735352</v>
+        <v>32.8658790588379</v>
       </c>
       <c r="H1052" t="n">
         <v>937883</v>
@@ -30935,7 +30935,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820613861084</v>
+        <v>29.9820652008057</v>
       </c>
       <c r="H1054" t="n">
         <v>787822</v>
@@ -31051,7 +31051,7 @@
         <v>36.1313896179199</v>
       </c>
       <c r="G1058" t="n">
-        <v>27.9360008239746</v>
+        <v>27.9360027313232</v>
       </c>
       <c r="H1058" t="n">
         <v>542723</v>
@@ -31196,7 +31196,7 @@
         <v>26.2546405792236</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.2995128631592</v>
+        <v>20.2995147705078</v>
       </c>
       <c r="H1063" t="n">
         <v>342146</v>
@@ -31225,7 +31225,7 @@
         <v>24.6085166931152</v>
       </c>
       <c r="G1064" t="n">
-        <v>19.0267696380615</v>
+        <v>19.0267677307129</v>
       </c>
       <c r="H1064" t="n">
         <v>440901</v>
@@ -31283,7 +31283,7 @@
         <v>20.8578548431396</v>
       </c>
       <c r="G1066" t="n">
-        <v>16.1268367767334</v>
+        <v>16.126838684082</v>
       </c>
       <c r="H1066" t="n">
         <v>607780</v>
@@ -31312,7 +31312,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728973388672</v>
+        <v>18.1728992462158</v>
       </c>
       <c r="H1067" t="n">
         <v>602051</v>
@@ -31341,7 +31341,7 @@
         <v>21.0453872680664</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.2718353271484</v>
+        <v>16.2718334197998</v>
       </c>
       <c r="H1068" t="n">
         <v>439578</v>
@@ -31457,7 +31457,7 @@
         <v>20.7953433990479</v>
       </c>
       <c r="G1072" t="n">
-        <v>16.0785064697266</v>
+        <v>16.0785045623779</v>
       </c>
       <c r="H1072" t="n">
         <v>293641</v>
@@ -31486,7 +31486,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1073" t="n">
-        <v>16.561824798584</v>
+        <v>16.5618267059326</v>
       </c>
       <c r="H1073" t="n">
         <v>191571</v>
@@ -31515,7 +31515,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445804595947</v>
+        <v>17.5445823669434</v>
       </c>
       <c r="H1074" t="n">
         <v>278986</v>
@@ -31631,7 +31631,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1078" t="n">
-        <v>17.754020690918</v>
+        <v>17.7540187835693</v>
       </c>
       <c r="H1078" t="n">
         <v>133373</v>
@@ -31660,7 +31660,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1079" t="n">
-        <v>18.253454208374</v>
+        <v>18.2534523010254</v>
       </c>
       <c r="H1079" t="n">
         <v>119826</v>
@@ -31718,7 +31718,7 @@
         <v>23.6708507537842</v>
       </c>
       <c r="G1081" t="n">
-        <v>18.3017864227295</v>
+        <v>18.3017845153809</v>
       </c>
       <c r="H1081" t="n">
         <v>80116</v>
@@ -31747,7 +31747,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1082" t="n">
         <v>65084</v>
@@ -31834,7 +31834,7 @@
         <v>24.5251693725586</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.9623241424561</v>
+        <v>18.9623260498047</v>
       </c>
       <c r="H1085" t="n">
         <v>121224</v>
@@ -31950,7 +31950,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1089" t="n">
         <v>85682</v>
@@ -32008,7 +32008,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.754020690918</v>
+        <v>17.7540187835693</v>
       </c>
       <c r="H1091" t="n">
         <v>40526</v>
@@ -32095,7 +32095,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1094" t="n">
-        <v>17.6734657287598</v>
+        <v>17.6734676361084</v>
       </c>
       <c r="H1094" t="n">
         <v>86867</v>
@@ -32124,7 +32124,7 @@
         <v>22.3164443969727</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.2545871734619</v>
+        <v>17.2545890808105</v>
       </c>
       <c r="H1095" t="n">
         <v>75023</v>
@@ -32153,7 +32153,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1096" t="n">
-        <v>17.6412448883057</v>
+        <v>17.6412467956543</v>
       </c>
       <c r="H1096" t="n">
         <v>91309</v>
@@ -32182,7 +32182,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0601253509521</v>
+        <v>18.0601234436035</v>
       </c>
       <c r="H1097" t="n">
         <v>181346</v>
@@ -32269,7 +32269,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1100" t="n">
-        <v>17.6412448883057</v>
+        <v>17.6412467956543</v>
       </c>
       <c r="H1100" t="n">
         <v>53003</v>
@@ -32298,7 +32298,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1101" t="n">
         <v>70876</v>
@@ -32327,7 +32327,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1102" t="n">
-        <v>17.5123596191406</v>
+        <v>17.5123615264893</v>
       </c>
       <c r="H1102" t="n">
         <v>32012</v>
@@ -32385,7 +32385,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1104" t="n">
-        <v>17.7217998504639</v>
+        <v>17.7217979431152</v>
       </c>
       <c r="H1104" t="n">
         <v>60478</v>
@@ -32414,7 +32414,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1105" t="n">
-        <v>17.7217998504639</v>
+        <v>17.7217979431152</v>
       </c>
       <c r="H1105" t="n">
         <v>47186</v>
@@ -32501,7 +32501,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1108" t="n">
-        <v>17.9634590148926</v>
+        <v>17.9634609222412</v>
       </c>
       <c r="H1108" t="n">
         <v>76222</v>
@@ -32559,7 +32559,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G1110" t="n">
-        <v>17.8667945861816</v>
+        <v>17.8667964935303</v>
       </c>
       <c r="H1110" t="n">
         <v>49897</v>
@@ -32617,7 +32617,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.561824798584</v>
+        <v>16.5618267059326</v>
       </c>
       <c r="H1112" t="n">
         <v>116319</v>
@@ -32675,7 +32675,7 @@
         <v>21.3371047973633</v>
       </c>
       <c r="G1114" t="n">
-        <v>16.4973850250244</v>
+        <v>16.4973831176758</v>
       </c>
       <c r="H1114" t="n">
         <v>115150</v>
@@ -32704,7 +32704,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1115" t="n">
-        <v>16.4329414367676</v>
+        <v>16.4329395294189</v>
       </c>
       <c r="H1115" t="n">
         <v>101008</v>
@@ -32820,7 +32820,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G1119" t="n">
-        <v>21.185604095459</v>
+        <v>21.1856060028076</v>
       </c>
       <c r="H1119" t="n">
         <v>1322864</v>
@@ -32878,7 +32878,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H1121" t="n">
         <v>244265</v>
@@ -32907,7 +32907,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683597564697</v>
+        <v>22.1683616638184</v>
       </c>
       <c r="H1122" t="n">
         <v>393290</v>
@@ -32936,7 +32936,7 @@
         <v>29.276008605957</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.6355686187744</v>
+        <v>22.635570526123</v>
       </c>
       <c r="H1123" t="n">
         <v>408833</v>
@@ -33023,7 +33023,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1126" t="n">
         <v>401649</v>
@@ -33110,7 +33110,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1129" t="n">
-        <v>22.8611183166504</v>
+        <v>22.861120223999</v>
       </c>
       <c r="H1129" t="n">
         <v>230255</v>
@@ -33139,7 +33139,7 @@
         <v>29.2134971618652</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.5872364044189</v>
+        <v>22.5872383117676</v>
       </c>
       <c r="H1130" t="n">
         <v>133679</v>
@@ -33197,7 +33197,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1132" t="n">
         <v>117120</v>
@@ -33226,7 +33226,7 @@
         <v>31.0263175964355</v>
       </c>
       <c r="G1133" t="n">
-        <v>23.9888725280762</v>
+        <v>23.9888706207275</v>
       </c>
       <c r="H1133" t="n">
         <v>120603</v>
@@ -33371,7 +33371,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021476745605</v>
+        <v>26.5021457672119</v>
       </c>
       <c r="H1138" t="n">
         <v>299299</v>
@@ -33400,7 +33400,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.2293968200684</v>
+        <v>25.229398727417</v>
       </c>
       <c r="H1139" t="n">
         <v>249320</v>
@@ -33458,7 +33458,7 @@
         <v>32.859977722168</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.4066181182861</v>
+        <v>25.4066162109375</v>
       </c>
       <c r="H1141" t="n">
         <v>424729</v>
@@ -33574,7 +33574,7 @@
         <v>32.8808135986328</v>
       </c>
       <c r="G1145" t="n">
-        <v>25.4227256774902</v>
+        <v>25.4227275848389</v>
       </c>
       <c r="H1145" t="n">
         <v>211348</v>
@@ -33603,7 +33603,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H1146" t="n">
         <v>101636</v>
@@ -33632,7 +33632,7 @@
         <v>31.5889186859131</v>
       </c>
       <c r="G1147" t="n">
-        <v>24.4238605499268</v>
+        <v>24.4238624572754</v>
       </c>
       <c r="H1147" t="n">
         <v>65647</v>
@@ -33661,7 +33661,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G1148" t="n">
-        <v>24.6171894073486</v>
+        <v>24.6171913146973</v>
       </c>
       <c r="H1148" t="n">
         <v>124950</v>
@@ -33690,7 +33690,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G1149" t="n">
-        <v>25.1327362060547</v>
+        <v>25.1327342987061</v>
       </c>
       <c r="H1149" t="n">
         <v>67331</v>
@@ -33719,7 +33719,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944068908691</v>
+        <v>24.7944087982178</v>
       </c>
       <c r="H1150" t="n">
         <v>90180</v>
@@ -33806,7 +33806,7 @@
         <v>32.7974662780762</v>
       </c>
       <c r="G1153" t="n">
-        <v>25.3582859039307</v>
+        <v>25.358283996582</v>
       </c>
       <c r="H1153" t="n">
         <v>172785</v>
@@ -33893,7 +33893,7 @@
         <v>37.6524887084961</v>
       </c>
       <c r="G1156" t="n">
-        <v>29.11208152771</v>
+        <v>29.1120834350586</v>
       </c>
       <c r="H1156" t="n">
         <v>1160270</v>
@@ -33922,7 +33922,7 @@
         <v>40.2154426574707</v>
       </c>
       <c r="G1157" t="n">
-        <v>31.0937042236328</v>
+        <v>31.0937023162842</v>
       </c>
       <c r="H1157" t="n">
         <v>1079270</v>
@@ -33951,7 +33951,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303936004639</v>
+        <v>30.0303916931152</v>
       </c>
       <c r="H1158" t="n">
         <v>499559</v>
@@ -34009,7 +34009,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049110412598</v>
+        <v>26.9049129486084</v>
       </c>
       <c r="H1160" t="n">
         <v>710323</v>
@@ -34067,7 +34067,7 @@
         <v>33.4017372131348</v>
       </c>
       <c r="G1162" t="n">
-        <v>25.8254947662354</v>
+        <v>25.8254928588867</v>
       </c>
       <c r="H1162" t="n">
         <v>201608</v>
@@ -34096,7 +34096,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G1163" t="n">
-        <v>24.6494102478027</v>
+        <v>24.6494121551514</v>
       </c>
       <c r="H1163" t="n">
         <v>167963</v>
@@ -34125,7 +34125,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655235290527</v>
+        <v>24.6655216217041</v>
       </c>
       <c r="H1164" t="n">
         <v>153075</v>
@@ -34241,7 +34241,7 @@
         <v>32.4432373046875</v>
       </c>
       <c r="G1168" t="n">
-        <v>25.0844039916992</v>
+        <v>25.0844020843506</v>
       </c>
       <c r="H1168" t="n">
         <v>285284</v>
@@ -34444,7 +34444,7 @@
         <v>29.3801937103271</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7161254882812</v>
+        <v>22.7161235809326</v>
       </c>
       <c r="H1175" t="n">
         <v>84856</v>
@@ -34531,7 +34531,7 @@
         <v>30.2970237731934</v>
       </c>
       <c r="G1178" t="n">
-        <v>23.4249954223633</v>
+        <v>23.4249973297119</v>
       </c>
       <c r="H1178" t="n">
         <v>90363</v>
@@ -34560,7 +34560,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G1179" t="n">
-        <v>23.5861015319824</v>
+        <v>23.5861034393311</v>
       </c>
       <c r="H1179" t="n">
         <v>120513</v>
@@ -34618,7 +34618,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766651153564</v>
+        <v>23.3766632080078</v>
       </c>
       <c r="H1181" t="n">
         <v>179328</v>
@@ -34647,7 +34647,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.23166847229</v>
+        <v>23.2316703796387</v>
       </c>
       <c r="H1182" t="n">
         <v>79634</v>
@@ -34705,7 +34705,7 @@
         <v>30.6720886230469</v>
       </c>
       <c r="G1184" t="n">
-        <v>23.7149906158447</v>
+        <v>23.7149887084961</v>
       </c>
       <c r="H1184" t="n">
         <v>210874</v>
@@ -34763,7 +34763,7 @@
         <v>29.9011192321777</v>
       </c>
       <c r="G1186" t="n">
-        <v>23.1188926696777</v>
+        <v>23.1188907623291</v>
       </c>
       <c r="H1186" t="n">
         <v>142772</v>
@@ -34821,7 +34821,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.8611183166504</v>
+        <v>22.861120223999</v>
       </c>
       <c r="H1188" t="n">
         <v>181360</v>
@@ -34879,7 +34879,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094524383545</v>
+        <v>22.9094543457031</v>
       </c>
       <c r="H1190" t="n">
         <v>71944</v>
@@ -34995,7 +34995,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416732788086</v>
+        <v>22.9416751861572</v>
       </c>
       <c r="H1194" t="n">
         <v>35197</v>
@@ -35024,7 +35024,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1195" t="n">
-        <v>23.0061168670654</v>
+        <v>23.0061187744141</v>
       </c>
       <c r="H1195" t="n">
         <v>37758</v>
@@ -35082,7 +35082,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1197" t="n">
         <v>53084</v>
@@ -35111,7 +35111,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1198" t="n">
-        <v>21.9911422729492</v>
+        <v>21.9911403656006</v>
       </c>
       <c r="H1198" t="n">
         <v>75589</v>
@@ -35140,7 +35140,7 @@
         <v>28.0049514770508</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.6528186798096</v>
+        <v>21.6528167724609</v>
       </c>
       <c r="H1199" t="n">
         <v>87498</v>
@@ -35198,7 +35198,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883750915527</v>
       </c>
       <c r="H1201" t="n">
         <v>213623</v>
@@ -35256,7 +35256,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G1203" t="n">
-        <v>21.7494792938232</v>
+        <v>21.7494812011719</v>
       </c>
       <c r="H1203" t="n">
         <v>72630</v>
@@ -35285,7 +35285,7 @@
         <v>28.5258750915527</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.0555839538574</v>
+        <v>22.0555820465088</v>
       </c>
       <c r="H1204" t="n">
         <v>90794</v>
@@ -35314,7 +35314,7 @@
         <v>28.4008541107178</v>
       </c>
       <c r="G1205" t="n">
-        <v>21.9589214324951</v>
+        <v>21.9589195251465</v>
       </c>
       <c r="H1205" t="n">
         <v>82873</v>
@@ -35372,7 +35372,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.361686706543</v>
+        <v>22.3616886138916</v>
       </c>
       <c r="H1207" t="n">
         <v>83126</v>
@@ -35401,7 +35401,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.4917087554932</v>
+        <v>21.4917106628418</v>
       </c>
       <c r="H1208" t="n">
         <v>131767</v>
@@ -35430,7 +35430,7 @@
         <v>28.2758312225342</v>
       </c>
       <c r="G1209" t="n">
-        <v>21.8622531890869</v>
+        <v>21.8622550964355</v>
       </c>
       <c r="H1209" t="n">
         <v>84042</v>
@@ -35459,7 +35459,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039180755615</v>
+        <v>22.1039161682129</v>
       </c>
       <c r="H1210" t="n">
         <v>66037</v>
@@ -35488,7 +35488,7 @@
         <v>28.9842910766602</v>
       </c>
       <c r="G1211" t="n">
-        <v>22.4100189208984</v>
+        <v>22.4100208282471</v>
       </c>
       <c r="H1211" t="n">
         <v>95686</v>
@@ -35517,7 +35517,7 @@
         <v>27.7757434844971</v>
       </c>
       <c r="G1212" t="n">
-        <v>21.4755973815918</v>
+        <v>21.4755992889404</v>
       </c>
       <c r="H1212" t="n">
         <v>157370</v>
@@ -35546,7 +35546,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372718811035</v>
+        <v>21.1372737884521</v>
       </c>
       <c r="H1213" t="n">
         <v>153694</v>
@@ -35575,7 +35575,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672939300537</v>
+        <v>20.2672920227051</v>
       </c>
       <c r="H1214" t="n">
         <v>217939</v>
@@ -35633,7 +35633,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1216" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H1216" t="n">
         <v>408334</v>
@@ -35720,7 +35720,7 @@
         <v>24.2334518432617</v>
       </c>
       <c r="G1219" t="n">
-        <v>18.7367744445801</v>
+        <v>18.7367763519287</v>
       </c>
       <c r="H1219" t="n">
         <v>241385</v>
@@ -35807,7 +35807,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1222" t="n">
         <v>166257</v>
@@ -35952,7 +35952,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1227" t="n">
-        <v>16.4651641845703</v>
+        <v>16.4651622772217</v>
       </c>
       <c r="H1227" t="n">
         <v>140219</v>
@@ -36271,7 +36271,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1238" t="n">
-        <v>18.3662281036377</v>
+        <v>18.3662261962891</v>
       </c>
       <c r="H1238" t="n">
         <v>189606</v>
@@ -36445,7 +36445,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.783971786499</v>
+        <v>19.7839698791504</v>
       </c>
       <c r="H1244" t="n">
         <v>193590</v>
@@ -36474,7 +36474,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1245" t="n">
-        <v>20.0417442321777</v>
+        <v>20.0417423248291</v>
       </c>
       <c r="H1245" t="n">
         <v>379252</v>
@@ -36503,7 +36503,7 @@
         <v>26.0879459381104</v>
       </c>
       <c r="G1246" t="n">
-        <v>20.1706314086914</v>
+        <v>20.1706295013428</v>
       </c>
       <c r="H1246" t="n">
         <v>327050</v>
@@ -36590,7 +36590,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728973388672</v>
+        <v>18.1728992462158</v>
       </c>
       <c r="H1249" t="n">
         <v>265701</v>
@@ -36619,7 +36619,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206649780273</v>
+        <v>18.7206630706787</v>
       </c>
       <c r="H1250" t="n">
         <v>489077</v>
@@ -36735,7 +36735,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206649780273</v>
+        <v>18.7206630706787</v>
       </c>
       <c r="H1254" t="n">
         <v>171179</v>
@@ -36793,7 +36793,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1256" t="n">
-        <v>17.7217998504639</v>
+        <v>17.7217979431152</v>
       </c>
       <c r="H1256" t="n">
         <v>220502</v>
@@ -36822,7 +36822,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.6412448883057</v>
+        <v>17.6412467956543</v>
       </c>
       <c r="H1257" t="n">
         <v>258497</v>
@@ -36851,7 +36851,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1258" t="n">
-        <v>17.7217998504639</v>
+        <v>17.7217979431152</v>
       </c>
       <c r="H1258" t="n">
         <v>197297</v>
@@ -36880,7 +36880,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1259" t="n">
-        <v>17.754020690918</v>
+        <v>17.7540187835693</v>
       </c>
       <c r="H1259" t="n">
         <v>142502</v>
@@ -36909,7 +36909,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445804595947</v>
+        <v>17.5445823669434</v>
       </c>
       <c r="H1260" t="n">
         <v>115703</v>
@@ -36938,7 +36938,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862415313721</v>
+        <v>17.7862396240234</v>
       </c>
       <c r="H1261" t="n">
         <v>101768</v>
@@ -36967,7 +36967,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1262" t="n">
         <v>79845</v>
@@ -36996,7 +36996,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.5123596191406</v>
+        <v>17.5123615264893</v>
       </c>
       <c r="H1263" t="n">
         <v>100240</v>
@@ -37025,7 +37025,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.4318065643311</v>
+        <v>17.4318046569824</v>
       </c>
       <c r="H1264" t="n">
         <v>328679</v>
@@ -37199,7 +37199,7 @@
         <v>21.7330093383789</v>
       </c>
       <c r="G1270" t="n">
-        <v>16.8034896850586</v>
+        <v>16.80348777771</v>
       </c>
       <c r="H1270" t="n">
         <v>111326</v>
@@ -37257,7 +37257,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.6734657287598</v>
+        <v>17.6734676361084</v>
       </c>
       <c r="H1272" t="n">
         <v>374152</v>
@@ -37344,7 +37344,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.3662281036377</v>
+        <v>18.3662261962891</v>
       </c>
       <c r="H1275" t="n">
         <v>170011</v>
@@ -37402,7 +37402,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.0601253509521</v>
+        <v>18.0601234436035</v>
       </c>
       <c r="H1277" t="n">
         <v>133192</v>
@@ -37489,7 +37489,7 @@
         <v>22.3997936248779</v>
       </c>
       <c r="G1280" t="n">
-        <v>17.3190307617188</v>
+        <v>17.3190326690674</v>
       </c>
       <c r="H1280" t="n">
         <v>107216</v>
@@ -37518,7 +37518,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.4318065643311</v>
+        <v>17.4318046569824</v>
       </c>
       <c r="H1281" t="n">
         <v>82476</v>
@@ -37576,7 +37576,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1283" t="n">
         <v>188315</v>
@@ -37634,7 +37634,7 @@
         <v>22.4414672851562</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.3512516021729</v>
+        <v>17.3512535095215</v>
       </c>
       <c r="H1285" t="n">
         <v>118092</v>
@@ -37692,7 +37692,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1287" t="n">
-        <v>17.1901473999023</v>
+        <v>17.1901454925537</v>
       </c>
       <c r="H1287" t="n">
         <v>74707</v>
@@ -37721,7 +37721,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934810638428</v>
+        <v>17.0934791564941</v>
       </c>
       <c r="H1288" t="n">
         <v>71228</v>
@@ -37808,7 +37808,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357086181641</v>
+        <v>16.8357105255127</v>
       </c>
       <c r="H1291" t="n">
         <v>77029</v>
@@ -37866,7 +37866,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801387786865</v>
+        <v>17.4801406860352</v>
       </c>
       <c r="H1293" t="n">
         <v>213107</v>
@@ -37895,7 +37895,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1294" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1294" t="n">
         <v>170814</v>
@@ -38011,7 +38011,7 @@
         <v>27.0881214141846</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.9439430236816</v>
+        <v>20.9439449310303</v>
       </c>
       <c r="H1298" t="n">
         <v>910482</v>
@@ -38098,7 +38098,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.5895099639893</v>
+        <v>20.5895080566406</v>
       </c>
       <c r="H1301" t="n">
         <v>361172</v>
@@ -38156,7 +38156,7 @@
         <v>26.6297073364258</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.5895099639893</v>
+        <v>20.5895080566406</v>
       </c>
       <c r="H1303" t="n">
         <v>234506</v>
@@ -38185,7 +38185,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H1304" t="n">
         <v>141753</v>
@@ -38214,7 +38214,7 @@
         <v>26.6088714599609</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5733966827393</v>
+        <v>20.5733985900879</v>
       </c>
       <c r="H1305" t="n">
         <v>187199</v>
@@ -38475,7 +38475,7 @@
         <v>24.8793983459473</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.2362060546875</v>
+        <v>19.2362079620361</v>
       </c>
       <c r="H1314" t="n">
         <v>83220</v>
@@ -38504,7 +38504,7 @@
         <v>25.0460948944092</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.3650951385498</v>
+        <v>19.3650932312012</v>
       </c>
       <c r="H1315" t="n">
         <v>145650</v>
@@ -38533,7 +38533,7 @@
         <v>25.504508972168</v>
       </c>
       <c r="G1316" t="n">
-        <v>19.7195301055908</v>
+        <v>19.7195281982422</v>
       </c>
       <c r="H1316" t="n">
         <v>192020</v>
@@ -38649,7 +38649,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1320" t="n">
         <v>181732</v>
@@ -38678,7 +38678,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1321" t="n">
         <v>147765</v>
@@ -38736,7 +38736,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750999450684</v>
+        <v>19.0750980377197</v>
       </c>
       <c r="H1323" t="n">
         <v>120557</v>
@@ -38823,7 +38823,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1326" t="n">
-        <v>18.9784374237061</v>
+        <v>18.9784336090088</v>
       </c>
       <c r="H1326" t="n">
         <v>76196</v>
@@ -38910,7 +38910,7 @@
         <v>24.0250816345215</v>
       </c>
       <c r="G1329" t="n">
-        <v>18.5756683349609</v>
+        <v>18.5756702423096</v>
       </c>
       <c r="H1329" t="n">
         <v>59340</v>
@@ -38997,7 +38997,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.607889175415</v>
+        <v>18.6078910827637</v>
       </c>
       <c r="H1332" t="n">
         <v>53943</v>
@@ -39026,7 +39026,7 @@
         <v>23.8375473022461</v>
       </c>
       <c r="G1333" t="n">
-        <v>18.4306716918945</v>
+        <v>18.4306697845459</v>
       </c>
       <c r="H1333" t="n">
         <v>62096</v>
@@ -39113,7 +39113,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.833438873291</v>
+        <v>18.8334407806396</v>
       </c>
       <c r="H1336" t="n">
         <v>97937</v>
@@ -39142,7 +39142,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353889465332</v>
+        <v>18.5353908538818</v>
       </c>
       <c r="H1337" t="n">
         <v>143301</v>
@@ -39171,7 +39171,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1338" t="n">
-        <v>18.4870567321777</v>
+        <v>18.4870586395264</v>
       </c>
       <c r="H1338" t="n">
         <v>70075</v>
@@ -39316,7 +39316,7 @@
         <v>24.4418201446533</v>
       </c>
       <c r="G1343" t="n">
-        <v>18.8978805541992</v>
+        <v>18.8978824615479</v>
       </c>
       <c r="H1343" t="n">
         <v>117770</v>
@@ -39345,7 +39345,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864902496338</v>
+        <v>18.9864940643311</v>
       </c>
       <c r="H1344" t="n">
         <v>82258</v>
@@ -39403,7 +39403,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112228393555</v>
+        <v>18.5112266540527</v>
       </c>
       <c r="H1346" t="n">
         <v>91238</v>
@@ -39519,7 +39519,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1350" t="n">
-        <v>18.5434455871582</v>
+        <v>18.5434474945068</v>
       </c>
       <c r="H1350" t="n">
         <v>31645</v>
@@ -39577,7 +39577,7 @@
         <v>23.5875034332275</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.237340927124</v>
+        <v>18.2373428344727</v>
       </c>
       <c r="H1352" t="n">
         <v>119737</v>
@@ -39635,7 +39635,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1354" t="n">
-        <v>18.3259506225586</v>
+        <v>18.3259525299072</v>
       </c>
       <c r="H1354" t="n">
         <v>116974</v>
@@ -39693,7 +39693,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187129974365</v>
+        <v>19.0187149047852</v>
       </c>
       <c r="H1356" t="n">
         <v>228828</v>
@@ -39722,7 +39722,7 @@
         <v>24.2959613800049</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.7851066589355</v>
+        <v>18.7851047515869</v>
       </c>
       <c r="H1357" t="n">
         <v>232305</v>
@@ -39809,7 +39809,7 @@
         <v>24.5043315887451</v>
       </c>
       <c r="G1360" t="n">
-        <v>18.9462146759033</v>
+        <v>18.9462127685547</v>
       </c>
       <c r="H1360" t="n">
         <v>123870</v>
@@ -39838,7 +39838,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1361" t="n">
         <v>157303</v>
@@ -39925,7 +39925,7 @@
         <v>24.806468963623</v>
       </c>
       <c r="G1364" t="n">
-        <v>19.1798191070557</v>
+        <v>19.1798210144043</v>
       </c>
       <c r="H1364" t="n">
         <v>128975</v>
@@ -39954,7 +39954,7 @@
         <v>26.4525928497314</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.4525680541992</v>
+        <v>20.4525661468506</v>
       </c>
       <c r="H1365" t="n">
         <v>970320</v>
@@ -40128,7 +40128,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1371" t="n">
         <v>230606</v>
@@ -40186,7 +40186,7 @@
         <v>25.8483200073242</v>
       </c>
       <c r="G1373" t="n">
-        <v>19.9853553771973</v>
+        <v>19.9853572845459</v>
       </c>
       <c r="H1373" t="n">
         <v>1023932</v>
@@ -40302,7 +40302,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531364440918</v>
+        <v>19.9531345367432</v>
       </c>
       <c r="H1377" t="n">
         <v>173483</v>
@@ -40331,7 +40331,7 @@
         <v>26.1400375366211</v>
       </c>
       <c r="G1378" t="n">
-        <v>20.2109050750732</v>
+        <v>20.2109069824219</v>
       </c>
       <c r="H1378" t="n">
         <v>358719</v>
@@ -40389,7 +40389,7 @@
         <v>26.2858963012695</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.3236789703369</v>
+        <v>20.3236808776855</v>
       </c>
       <c r="H1380" t="n">
         <v>657639</v>
@@ -40447,7 +40447,7 @@
         <v>25.8379001617432</v>
       </c>
       <c r="G1382" t="n">
-        <v>19.9773006439209</v>
+        <v>19.9772987365723</v>
       </c>
       <c r="H1382" t="n">
         <v>272090</v>
@@ -40476,7 +40476,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.0417442321777</v>
+        <v>20.0417423248291</v>
       </c>
       <c r="H1383" t="n">
         <v>242252</v>
@@ -40563,7 +40563,7 @@
         <v>25.0565128326416</v>
       </c>
       <c r="G1386" t="n">
-        <v>19.3731479644775</v>
+        <v>19.3731498718262</v>
       </c>
       <c r="H1386" t="n">
         <v>256812</v>
@@ -40592,7 +40592,7 @@
         <v>24.8168869018555</v>
       </c>
       <c r="G1387" t="n">
-        <v>19.187873840332</v>
+        <v>19.1878757476807</v>
       </c>
       <c r="H1387" t="n">
         <v>247944</v>
@@ -40650,7 +40650,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187129974365</v>
+        <v>19.0187149047852</v>
       </c>
       <c r="H1389" t="n">
         <v>201477</v>
@@ -40795,7 +40795,7 @@
         <v>24.2021942138672</v>
       </c>
       <c r="G1394" t="n">
-        <v>18.7126064300537</v>
+        <v>18.7126083374023</v>
       </c>
       <c r="H1394" t="n">
         <v>201948</v>
@@ -40940,7 +40940,7 @@
         <v>23.9104766845703</v>
       </c>
       <c r="G1399" t="n">
-        <v>18.4870567321777</v>
+        <v>18.4870586395264</v>
       </c>
       <c r="H1399" t="n">
         <v>189206</v>
@@ -40969,7 +40969,7 @@
         <v>23.6187591552734</v>
       </c>
       <c r="G1400" t="n">
-        <v>18.2615070343018</v>
+        <v>18.2615089416504</v>
       </c>
       <c r="H1400" t="n">
         <v>207750</v>
@@ -40998,7 +40998,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1401" t="n">
-        <v>18.1084575653076</v>
+        <v>18.108455657959</v>
       </c>
       <c r="H1401" t="n">
         <v>352284</v>
@@ -41085,7 +41085,7 @@
         <v>23.472900390625</v>
       </c>
       <c r="G1404" t="n">
-        <v>18.1487331390381</v>
+        <v>18.1487350463867</v>
       </c>
       <c r="H1404" t="n">
         <v>251573</v>
@@ -41346,7 +41346,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1413" t="n">
         <v>387357</v>
@@ -41375,7 +41375,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1414" t="n">
         <v>234798</v>
@@ -41404,7 +41404,7 @@
         <v>23.5562477111816</v>
       </c>
       <c r="G1415" t="n">
-        <v>18.2131748199463</v>
+        <v>18.2131767272949</v>
       </c>
       <c r="H1415" t="n">
         <v>138909</v>
@@ -41433,7 +41433,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1416" t="n">
-        <v>18.3259506225586</v>
+        <v>18.3259525299072</v>
       </c>
       <c r="H1416" t="n">
         <v>113622</v>
@@ -41462,7 +41462,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1417" t="n">
-        <v>18.253454208374</v>
+        <v>18.2534523010254</v>
       </c>
       <c r="H1417" t="n">
         <v>115441</v>
@@ -41520,7 +41520,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1419" t="n">
-        <v>18.5434455871582</v>
+        <v>18.5434474945068</v>
       </c>
       <c r="H1419" t="n">
         <v>305385</v>
@@ -41665,7 +41665,7 @@
         <v>24.3897285461426</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.8576049804688</v>
+        <v>18.8576068878174</v>
       </c>
       <c r="H1424" t="n">
         <v>537633</v>
@@ -41723,7 +41723,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428791046143</v>
+        <v>19.0428771972656</v>
       </c>
       <c r="H1426" t="n">
         <v>251332</v>
@@ -41752,7 +41752,7 @@
         <v>24.2230319976807</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.7287216186523</v>
+        <v>18.7287197113037</v>
       </c>
       <c r="H1427" t="n">
         <v>215889</v>
@@ -41839,7 +41839,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742828369141</v>
+        <v>18.3742847442627</v>
       </c>
       <c r="H1430" t="n">
         <v>93708</v>
@@ -41897,7 +41897,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292881011963</v>
+        <v>18.2292861938477</v>
       </c>
       <c r="H1432" t="n">
         <v>168351</v>
@@ -41984,7 +41984,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1435" t="n">
-        <v>17.9634590148926</v>
+        <v>17.9634609222412</v>
       </c>
       <c r="H1435" t="n">
         <v>76206</v>
@@ -42013,7 +42013,7 @@
         <v>23.5354118347168</v>
       </c>
       <c r="G1436" t="n">
-        <v>18.1970672607422</v>
+        <v>18.1970653533936</v>
       </c>
       <c r="H1436" t="n">
         <v>361330</v>
@@ -42071,7 +42071,7 @@
         <v>23.2853660583496</v>
       </c>
       <c r="G1438" t="n">
-        <v>18.0037384033203</v>
+        <v>18.0037364959717</v>
       </c>
       <c r="H1438" t="n">
         <v>138869</v>
@@ -42129,7 +42129,7 @@
         <v>23.4520626068115</v>
       </c>
       <c r="G1440" t="n">
-        <v>18.1326236724854</v>
+        <v>18.1326217651367</v>
       </c>
       <c r="H1440" t="n">
         <v>97025</v>
@@ -42216,7 +42216,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1443" t="n">
-        <v>18.0601253509521</v>
+        <v>18.0601234436035</v>
       </c>
       <c r="H1443" t="n">
         <v>129448</v>
@@ -42274,7 +42274,7 @@
         <v>23.160343170166</v>
       </c>
       <c r="G1445" t="n">
-        <v>17.9070720672607</v>
+        <v>17.9070701599121</v>
       </c>
       <c r="H1445" t="n">
         <v>118808</v>
@@ -42332,7 +42332,7 @@
         <v>23.3166217803955</v>
       </c>
       <c r="G1447" t="n">
-        <v>18.027904510498</v>
+        <v>18.0279026031494</v>
       </c>
       <c r="H1447" t="n">
         <v>122725</v>
@@ -42477,7 +42477,7 @@
         <v>23.0978336334229</v>
       </c>
       <c r="G1452" t="n">
-        <v>17.8587417602539</v>
+        <v>17.8587398529053</v>
       </c>
       <c r="H1452" t="n">
         <v>274366</v>
@@ -42593,7 +42593,7 @@
         <v>22.233097076416</v>
       </c>
       <c r="G1456" t="n">
-        <v>17.1901473999023</v>
+        <v>17.1901454925537</v>
       </c>
       <c r="H1456" t="n">
         <v>147195</v>
@@ -42651,7 +42651,7 @@
         <v>22.5977458953857</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.4720840454102</v>
+        <v>17.4720821380615</v>
       </c>
       <c r="H1458" t="n">
         <v>246340</v>
@@ -42680,7 +42680,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1459" t="n">
-        <v>17.7217998504639</v>
+        <v>17.7217979431152</v>
       </c>
       <c r="H1459" t="n">
         <v>176935</v>
@@ -42709,7 +42709,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1460" t="n">
         <v>158955</v>
@@ -42767,7 +42767,7 @@
         <v>22.5248146057129</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.4156970977783</v>
+        <v>17.4156951904297</v>
       </c>
       <c r="H1462" t="n">
         <v>81655</v>
@@ -42825,7 +42825,7 @@
         <v>22.6706733703613</v>
       </c>
       <c r="G1464" t="n">
-        <v>17.528470993042</v>
+        <v>17.5284690856934</v>
       </c>
       <c r="H1464" t="n">
         <v>280896</v>
@@ -42854,7 +42854,7 @@
         <v>23.2645282745361</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.9876251220703</v>
+        <v>17.9876270294189</v>
       </c>
       <c r="H1465" t="n">
         <v>247043</v>
@@ -42883,7 +42883,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.1084575653076</v>
+        <v>18.108455657959</v>
       </c>
       <c r="H1466" t="n">
         <v>183896</v>
@@ -42912,7 +42912,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862415313721</v>
+        <v>17.7862396240234</v>
       </c>
       <c r="H1467" t="n">
         <v>172242</v>
@@ -43057,7 +43057,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.7217998504639</v>
+        <v>17.7217979431152</v>
       </c>
       <c r="H1472" t="n">
         <v>130410</v>
@@ -43173,7 +43173,7 @@
         <v>22.3789558410645</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.302921295166</v>
+        <v>17.3029193878174</v>
       </c>
       <c r="H1476" t="n">
         <v>79029</v>
@@ -43289,7 +43289,7 @@
         <v>22.1289119720459</v>
       </c>
       <c r="G1480" t="n">
-        <v>17.1095924377441</v>
+        <v>17.1095905303955</v>
       </c>
       <c r="H1480" t="n">
         <v>114206</v>
@@ -43463,7 +43463,7 @@
         <v>21.0766429901123</v>
       </c>
       <c r="G1486" t="n">
-        <v>16.2960014343262</v>
+        <v>16.2959995269775</v>
       </c>
       <c r="H1486" t="n">
         <v>123202</v>
@@ -43492,7 +43492,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1487" t="n">
-        <v>16.4651641845703</v>
+        <v>16.4651622772217</v>
       </c>
       <c r="H1487" t="n">
         <v>60560</v>
@@ -43550,7 +43550,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1489" t="n">
-        <v>16.4329414367676</v>
+        <v>16.4329395294189</v>
       </c>
       <c r="H1489" t="n">
         <v>110218</v>
@@ -43608,7 +43608,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765525817871</v>
+        <v>16.3765544891357</v>
       </c>
       <c r="H1491" t="n">
         <v>136046</v>
@@ -43753,7 +43753,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.975396156311</v>
+        <v>15.9753942489624</v>
       </c>
       <c r="H1496" t="n">
         <v>142969</v>
@@ -43782,7 +43782,7 @@
         <v>20.2244091033936</v>
       </c>
       <c r="G1497" t="n">
-        <v>15.6370706558228</v>
+        <v>15.6370716094971</v>
       </c>
       <c r="H1497" t="n">
         <v>157081</v>
@@ -43811,7 +43811,7 @@
         <v>19.3367519378662</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.9507551193237</v>
+        <v>14.9507541656494</v>
       </c>
       <c r="H1498" t="n">
         <v>306456</v>
@@ -43840,7 +43840,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668645858765</v>
+        <v>14.9668664932251</v>
       </c>
       <c r="H1499" t="n">
         <v>131664</v>
@@ -43927,7 +43927,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.2934350967407</v>
+        <v>14.293436050415</v>
       </c>
       <c r="H1502" t="n">
         <v>112108</v>
@@ -43956,7 +43956,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780061721802</v>
+        <v>13.6780052185059</v>
       </c>
       <c r="H1503" t="n">
         <v>269832</v>
@@ -44014,7 +44014,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013580322266</v>
+        <v>13.0013570785522</v>
       </c>
       <c r="H1505" t="n">
         <v>156575</v>
@@ -44130,7 +44130,7 @@
         <v>18.690803527832</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.4513216018677</v>
+        <v>14.4513206481934</v>
       </c>
       <c r="H1509" t="n">
         <v>189210</v>
@@ -44217,7 +44217,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379802703857</v>
+        <v>14.8379812240601</v>
       </c>
       <c r="H1512" t="n">
         <v>518691</v>
@@ -44246,7 +44246,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157661437988</v>
+        <v>14.5157642364502</v>
       </c>
       <c r="H1513" t="n">
         <v>165517</v>
@@ -44304,7 +44304,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.6543159484863</v>
+        <v>14.654314994812</v>
       </c>
       <c r="H1515" t="n">
         <v>168456</v>
@@ -44333,7 +44333,7 @@
         <v>19.1658878326416</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8186454772949</v>
+        <v>14.8186464309692</v>
       </c>
       <c r="H1516" t="n">
         <v>177163</v>
@@ -44362,7 +44362,7 @@
         <v>19.2950782775879</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.918532371521</v>
+        <v>14.9185333251953</v>
       </c>
       <c r="H1517" t="n">
         <v>167619</v>
@@ -44391,7 +44391,7 @@
         <v>19.3200817108154</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.9378652572632</v>
+        <v>14.9378662109375</v>
       </c>
       <c r="H1518" t="n">
         <v>167937</v>
@@ -44420,7 +44420,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157661437988</v>
+        <v>14.5157642364502</v>
       </c>
       <c r="H1519" t="n">
         <v>157517</v>
@@ -44507,7 +44507,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189867019653</v>
+        <v>14.518988609314</v>
       </c>
       <c r="H1522" t="n">
         <v>83491</v>
@@ -44594,7 +44594,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287662506104</v>
+        <v>14.4287672042847</v>
       </c>
       <c r="H1525" t="n">
         <v>203931</v>
@@ -44652,7 +44652,7 @@
         <v>18.9200115203857</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.6285409927368</v>
+        <v>14.6285400390625</v>
       </c>
       <c r="H1527" t="n">
         <v>97123</v>
@@ -44681,7 +44681,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958648681641</v>
+        <v>14.9958639144897</v>
       </c>
       <c r="H1528" t="n">
         <v>508333</v>
@@ -44768,7 +44768,7 @@
         <v>19.307580947876</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.9282007217407</v>
+        <v>14.9281997680664</v>
       </c>
       <c r="H1531" t="n">
         <v>93839</v>
@@ -44797,7 +44797,7 @@
         <v>19.1075439453125</v>
       </c>
       <c r="G1532" t="n">
-        <v>14.7735347747803</v>
+        <v>14.7735357284546</v>
       </c>
       <c r="H1532" t="n">
         <v>109512</v>
@@ -44855,7 +44855,7 @@
         <v>19.2867431640625</v>
       </c>
       <c r="G1534" t="n">
-        <v>14.912088394165</v>
+        <v>14.9120874404907</v>
       </c>
       <c r="H1534" t="n">
         <v>132919</v>
@@ -44884,7 +44884,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316474914551</v>
+        <v>14.7316484451294</v>
       </c>
       <c r="H1535" t="n">
         <v>124218</v>
@@ -44913,7 +44913,7 @@
         <v>18.8116588592529</v>
       </c>
       <c r="G1536" t="n">
-        <v>14.5447645187378</v>
+        <v>14.5447635650635</v>
       </c>
       <c r="H1536" t="n">
         <v>106444</v>
@@ -44942,7 +44942,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154239654541</v>
+        <v>14.8154230117798</v>
       </c>
       <c r="H1537" t="n">
         <v>73886</v>
@@ -44971,7 +44971,7 @@
         <v>18.9658527374268</v>
       </c>
       <c r="G1538" t="n">
-        <v>14.6639842987061</v>
+        <v>14.6639833450317</v>
       </c>
       <c r="H1538" t="n">
         <v>115175</v>
@@ -45000,7 +45000,7 @@
         <v>18.9116764068604</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.6220960617065</v>
+        <v>14.6220941543579</v>
       </c>
       <c r="H1539" t="n">
         <v>34303</v>
@@ -45029,7 +45029,7 @@
         <v>18.9241790771484</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.6317615509033</v>
+        <v>14.6317625045776</v>
       </c>
       <c r="H1540" t="n">
         <v>58627</v>
@@ -45087,7 +45087,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1542" t="n">
-        <v>14.0002212524414</v>
+        <v>14.0002222061157</v>
       </c>
       <c r="H1542" t="n">
         <v>149427</v>
@@ -45145,7 +45145,7 @@
         <v>18.5241088867188</v>
       </c>
       <c r="G1544" t="n">
-        <v>14.3224353790283</v>
+        <v>14.3224363327026</v>
       </c>
       <c r="H1544" t="n">
         <v>44397</v>
@@ -45174,7 +45174,7 @@
         <v>18.8283271789551</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.5576515197754</v>
+        <v>14.5576505661011</v>
       </c>
       <c r="H1545" t="n">
         <v>72837</v>
@@ -45203,7 +45203,7 @@
         <v>18.7116413116455</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.4674320220947</v>
+        <v>14.467432975769</v>
       </c>
       <c r="H1546" t="n">
         <v>228021</v>
@@ -45232,7 +45232,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.699426651001</v>
+        <v>14.6994276046753</v>
       </c>
       <c r="H1547" t="n">
         <v>198643</v>
@@ -45261,7 +45261,7 @@
         <v>19.1950607299805</v>
       </c>
       <c r="G1548" t="n">
-        <v>14.8412008285522</v>
+        <v>14.8412017822266</v>
       </c>
       <c r="H1548" t="n">
         <v>148931</v>
@@ -45319,7 +45319,7 @@
         <v>19.7618274688721</v>
       </c>
       <c r="G1550" t="n">
-        <v>15.2794122695923</v>
+        <v>15.2794141769409</v>
       </c>
       <c r="H1550" t="n">
         <v>232939</v>
@@ -45377,7 +45377,7 @@
         <v>19.3784255981445</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.9829759597778</v>
+        <v>14.9829750061035</v>
       </c>
       <c r="H1552" t="n">
         <v>194072</v>
@@ -45406,7 +45406,7 @@
         <v>20.6703205108643</v>
       </c>
       <c r="G1553" t="n">
-        <v>15.9818410873413</v>
+        <v>15.981840133667</v>
       </c>
       <c r="H1553" t="n">
         <v>660001</v>
@@ -45464,7 +45464,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.6435146331787</v>
+        <v>15.6435136795044</v>
       </c>
       <c r="H1555" t="n">
         <v>151091</v>
@@ -45493,7 +45493,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357086181641</v>
+        <v>16.8357105255127</v>
       </c>
       <c r="H1556" t="n">
         <v>411312</v>
@@ -45580,7 +45580,7 @@
         <v>20.6244792938232</v>
       </c>
       <c r="G1559" t="n">
-        <v>15.9463987350464</v>
+        <v>15.9463977813721</v>
       </c>
       <c r="H1559" t="n">
         <v>435045</v>
@@ -45609,7 +45609,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147424697876</v>
+        <v>15.4147443771362</v>
       </c>
       <c r="H1560" t="n">
         <v>254459</v>
@@ -45638,7 +45638,7 @@
         <v>19.5784606933594</v>
       </c>
       <c r="G1561" t="n">
-        <v>15.137638092041</v>
+        <v>15.1376390457153</v>
       </c>
       <c r="H1561" t="n">
         <v>134574</v>
@@ -45725,7 +45725,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157661437988</v>
+        <v>14.5157642364502</v>
       </c>
       <c r="H1564" t="n">
         <v>315453</v>
@@ -45783,7 +45783,7 @@
         <v>18.1573753356934</v>
       </c>
       <c r="G1566" t="n">
-        <v>14.0388860702515</v>
+        <v>14.0388870239258</v>
       </c>
       <c r="H1566" t="n">
         <v>543373</v>
@@ -45928,7 +45928,7 @@
         <v>15.940318107605</v>
       </c>
       <c r="G1571" t="n">
-        <v>12.3247051239014</v>
+        <v>12.3247060775757</v>
       </c>
       <c r="H1571" t="n">
         <v>242452</v>
@@ -45957,7 +45957,7 @@
         <v>16.9196586608887</v>
       </c>
       <c r="G1572" t="n">
-        <v>13.0819101333618</v>
+        <v>13.0819110870361</v>
       </c>
       <c r="H1572" t="n">
         <v>407858</v>
@@ -46015,7 +46015,7 @@
         <v>17.807315826416</v>
       </c>
       <c r="G1574" t="n">
-        <v>13.7682275772095</v>
+        <v>13.7682285308838</v>
       </c>
       <c r="H1574" t="n">
         <v>308404</v>
@@ -46044,7 +46044,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584470748901</v>
+        <v>13.8584480285645</v>
       </c>
       <c r="H1575" t="n">
         <v>588208</v>
@@ -46073,7 +46073,7 @@
         <v>18.1865482330322</v>
       </c>
       <c r="G1576" t="n">
-        <v>14.0614414215088</v>
+        <v>14.0614423751831</v>
       </c>
       <c r="H1576" t="n">
         <v>334948</v>
@@ -46102,7 +46102,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151968002319</v>
+        <v>15.0151958465576</v>
       </c>
       <c r="H1577" t="n">
         <v>400947</v>
@@ -46160,7 +46160,7 @@
         <v>20.2119064331055</v>
       </c>
       <c r="G1579" t="n">
-        <v>15.6274042129517</v>
+        <v>15.627405166626</v>
       </c>
       <c r="H1579" t="n">
         <v>454220</v>
@@ -46218,7 +46218,7 @@
         <v>20.3661003112793</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.7466249465942</v>
+        <v>15.7466239929199</v>
       </c>
       <c r="H1581" t="n">
         <v>349520</v>
@@ -46276,7 +46276,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1583" t="n">
-        <v>15.9496183395386</v>
+        <v>15.9496192932129</v>
       </c>
       <c r="H1583" t="n">
         <v>228335</v>
@@ -46305,7 +46305,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.9496183395386</v>
+        <v>15.9496192932129</v>
       </c>
       <c r="H1584" t="n">
         <v>108428</v>
@@ -46334,7 +46334,7 @@
         <v>20.1077213287354</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.5468521118164</v>
+        <v>15.5468511581421</v>
       </c>
       <c r="H1585" t="n">
         <v>177619</v>
@@ -46421,7 +46421,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8303995132446</v>
+        <v>15.8304004669189</v>
       </c>
       <c r="H1588" t="n">
         <v>187148</v>
@@ -46450,7 +46450,7 @@
         <v>19.9493598937988</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.4244089126587</v>
+        <v>15.424409866333</v>
       </c>
       <c r="H1589" t="n">
         <v>222730</v>
@@ -46479,7 +46479,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.0699739456177</v>
+        <v>15.0699729919434</v>
       </c>
       <c r="H1590" t="n">
         <v>151523</v>
@@ -46508,7 +46508,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199169158936</v>
+        <v>15.1199178695679</v>
       </c>
       <c r="H1591" t="n">
         <v>163415</v>
@@ -46537,7 +46537,7 @@
         <v>18.9616851806641</v>
       </c>
       <c r="G1592" t="n">
-        <v>14.6607599258423</v>
+        <v>14.6607608795166</v>
       </c>
       <c r="H1592" t="n">
         <v>276239</v>
@@ -46595,7 +46595,7 @@
         <v>18.024019241333</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.9357767105103</v>
+        <v>13.9357786178589</v>
       </c>
       <c r="H1594" t="n">
         <v>185388</v>
@@ -46624,7 +46624,7 @@
         <v>18.1073684692383</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.0002212524414</v>
+        <v>14.0002222061157</v>
       </c>
       <c r="H1595" t="n">
         <v>171574</v>
@@ -46653,7 +46653,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660484313965</v>
+        <v>14.2660474777222</v>
       </c>
       <c r="H1596" t="n">
         <v>137521</v>
@@ -46682,7 +46682,7 @@
         <v>18.1177864074707</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0082778930664</v>
+        <v>14.0082769393921</v>
       </c>
       <c r="H1597" t="n">
         <v>193042</v>
@@ -46711,7 +46711,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585601806641</v>
+        <v>13.7585592269897</v>
       </c>
       <c r="H1598" t="n">
         <v>171526</v>
@@ -46740,7 +46740,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116115570068</v>
+        <v>13.9116125106812</v>
       </c>
       <c r="H1599" t="n">
         <v>156203</v>
@@ -46769,7 +46769,7 @@
         <v>17.8469047546387</v>
       </c>
       <c r="G1600" t="n">
-        <v>13.7988357543945</v>
+        <v>13.7988367080688</v>
       </c>
       <c r="H1600" t="n">
         <v>70442</v>
@@ -46798,7 +46798,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780061721802</v>
+        <v>13.6780052185059</v>
       </c>
       <c r="H1601" t="n">
         <v>280445</v>
@@ -46827,7 +46827,7 @@
         <v>17.9719276428223</v>
       </c>
       <c r="G1602" t="n">
-        <v>13.8955030441284</v>
+        <v>13.8955011367798</v>
       </c>
       <c r="H1602" t="n">
         <v>168613</v>
@@ -46885,7 +46885,7 @@
         <v>17.8469047546387</v>
       </c>
       <c r="G1604" t="n">
-        <v>13.7988357543945</v>
+        <v>13.7988367080688</v>
       </c>
       <c r="H1604" t="n">
         <v>282454</v>
@@ -46943,7 +46943,7 @@
         <v>18.3678302764893</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.201605796814</v>
+        <v>14.2016048431396</v>
       </c>
       <c r="H1606" t="n">
         <v>655478</v>
@@ -46972,7 +46972,7 @@
         <v>17.8573226928711</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8068923950195</v>
+        <v>13.8068914413452</v>
       </c>
       <c r="H1607" t="n">
         <v>594069</v>
@@ -47030,7 +47030,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1609" t="n">
-        <v>12.9691352844238</v>
+        <v>12.9691362380981</v>
       </c>
       <c r="H1609" t="n">
         <v>243613</v>
@@ -47059,7 +47059,7 @@
         <v>16.7737998962402</v>
       </c>
       <c r="G1610" t="n">
-        <v>12.9691352844238</v>
+        <v>12.9691362380981</v>
       </c>
       <c r="H1610" t="n">
         <v>466473</v>
@@ -47146,7 +47146,7 @@
         <v>15.8986444473267</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.2924842834473</v>
+        <v>12.2924852371216</v>
       </c>
       <c r="H1613" t="n">
         <v>194884</v>
@@ -47175,7 +47175,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722221374512</v>
+        <v>11.6722211837769</v>
       </c>
       <c r="H1614" t="n">
         <v>366805</v>
@@ -47204,7 +47204,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519590377808</v>
+        <v>11.0519580841064</v>
       </c>
       <c r="H1615" t="n">
         <v>230061</v>
@@ -47320,7 +47320,7 @@
         <v>14.6484231948853</v>
       </c>
       <c r="G1619" t="n">
-        <v>11.3258419036865</v>
+        <v>11.3258409500122</v>
       </c>
       <c r="H1619" t="n">
         <v>113034</v>
@@ -47494,7 +47494,7 @@
         <v>15.0130710601807</v>
       </c>
       <c r="G1625" t="n">
-        <v>11.6077795028687</v>
+        <v>11.6077785491943</v>
       </c>
       <c r="H1625" t="n">
         <v>59931</v>
@@ -47523,7 +47523,7 @@
         <v>15.5131587982178</v>
       </c>
       <c r="G1626" t="n">
-        <v>11.9944362640381</v>
+        <v>11.9944353103638</v>
       </c>
       <c r="H1626" t="n">
         <v>418987</v>
@@ -47552,7 +47552,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.9702701568604</v>
+        <v>11.970269203186</v>
       </c>
       <c r="H1627" t="n">
         <v>161789</v>
@@ -47581,7 +47581,7 @@
         <v>15.5860891342163</v>
       </c>
       <c r="G1628" t="n">
-        <v>12.0508241653442</v>
+        <v>12.0508232116699</v>
       </c>
       <c r="H1628" t="n">
         <v>106888</v>
@@ -47610,7 +47610,7 @@
         <v>15.5235767364502</v>
       </c>
       <c r="G1629" t="n">
-        <v>12.0024900436401</v>
+        <v>12.0024909973145</v>
       </c>
       <c r="H1629" t="n">
         <v>65253</v>
@@ -47697,7 +47697,7 @@
         <v>16.0236663818359</v>
       </c>
       <c r="G1632" t="n">
-        <v>12.3891496658325</v>
+        <v>12.3891487121582</v>
       </c>
       <c r="H1632" t="n">
         <v>63823</v>
@@ -47755,7 +47755,7 @@
         <v>16.429988861084</v>
       </c>
       <c r="G1634" t="n">
-        <v>12.7033090591431</v>
+        <v>12.7033081054688</v>
       </c>
       <c r="H1634" t="n">
         <v>81533</v>
@@ -47842,7 +47842,7 @@
         <v>16.2632923126221</v>
       </c>
       <c r="G1637" t="n">
-        <v>12.5744218826294</v>
+        <v>12.5744228363037</v>
       </c>
       <c r="H1637" t="n">
         <v>89530</v>
@@ -47929,7 +47929,7 @@
         <v>14.7213516235352</v>
       </c>
       <c r="G1640" t="n">
-        <v>11.382227897644</v>
+        <v>11.3822269439697</v>
       </c>
       <c r="H1640" t="n">
         <v>200632</v>
@@ -47987,7 +47987,7 @@
         <v>14.7734451293945</v>
       </c>
       <c r="G1642" t="n">
-        <v>11.4225053787231</v>
+        <v>11.4225063323975</v>
       </c>
       <c r="H1642" t="n">
         <v>170224</v>
@@ -48016,7 +48016,7 @@
         <v>14.5650749206543</v>
       </c>
       <c r="G1643" t="n">
-        <v>11.2613973617554</v>
+        <v>11.2613983154297</v>
       </c>
       <c r="H1643" t="n">
         <v>60975</v>
@@ -48045,7 +48045,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.2533416748047</v>
+        <v>11.253342628479</v>
       </c>
       <c r="H1644" t="n">
         <v>145140</v>
@@ -48161,7 +48161,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136335372925</v>
+        <v>10.7136325836182</v>
       </c>
       <c r="H1648" t="n">
         <v>160860</v>
@@ -48190,7 +48190,7 @@
         <v>14.0441493988037</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.8586292266846</v>
+        <v>10.8586301803589</v>
       </c>
       <c r="H1649" t="n">
         <v>111558</v>
@@ -48277,7 +48277,7 @@
         <v>11.6166372299194</v>
       </c>
       <c r="G1652" t="n">
-        <v>8.98172950744629</v>
+        <v>8.98173046112061</v>
       </c>
       <c r="H1652" t="n">
         <v>1035045</v>
@@ -48306,7 +48306,7 @@
         <v>11.2728261947632</v>
       </c>
       <c r="G1653" t="n">
-        <v>8.71590328216553</v>
+        <v>8.71590232849121</v>
       </c>
       <c r="H1653" t="n">
         <v>358963</v>
@@ -48335,7 +48335,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535694122314</v>
+        <v>8.34535598754883</v>
       </c>
       <c r="H1654" t="n">
         <v>225381</v>
@@ -48422,7 +48422,7 @@
         <v>9.64753913879395</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.4592661857605</v>
+        <v>7.45926666259766</v>
       </c>
       <c r="H1657" t="n">
         <v>314217</v>
@@ -48451,7 +48451,7 @@
         <v>10.010103225708</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.73959255218506</v>
+        <v>7.73959350585938</v>
       </c>
       <c r="H1658" t="n">
         <v>359843</v>
@@ -48480,7 +48480,7 @@
         <v>11.1894779205322</v>
       </c>
       <c r="G1659" t="n">
-        <v>8.65146064758301</v>
+        <v>8.65145969390869</v>
       </c>
       <c r="H1659" t="n">
         <v>479547</v>
@@ -48509,7 +48509,7 @@
         <v>10.5331115722656</v>
       </c>
       <c r="G1660" t="n">
-        <v>8.14397144317627</v>
+        <v>8.14397239685059</v>
       </c>
       <c r="H1660" t="n">
         <v>318695</v>
@@ -48567,7 +48567,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392160415649</v>
+        <v>7.90392208099365</v>
       </c>
       <c r="H1662" t="n">
         <v>148424</v>
@@ -48596,7 +48596,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971332550049</v>
+        <v>7.34971380233765</v>
       </c>
       <c r="H1663" t="n">
         <v>388404</v>
@@ -48625,7 +48625,7 @@
         <v>8.91824340820312</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.8953914642334</v>
+        <v>6.89539098739624</v>
       </c>
       <c r="H1664" t="n">
         <v>278474</v>
@@ -48654,7 +48654,7 @@
         <v>9.20162582397461</v>
       </c>
       <c r="G1665" t="n">
-        <v>7.11449670791626</v>
+        <v>7.11449575424194</v>
       </c>
       <c r="H1665" t="n">
         <v>236205</v>
@@ -48683,7 +48683,7 @@
         <v>9.54335308074951</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.37871217727661</v>
+        <v>7.37871170043945</v>
       </c>
       <c r="H1666" t="n">
         <v>148370</v>
@@ -48770,7 +48770,7 @@
         <v>8.75154685974121</v>
       </c>
       <c r="G1669" t="n">
-        <v>6.76650524139404</v>
+        <v>6.76650476455688</v>
       </c>
       <c r="H1669" t="n">
         <v>299096</v>
@@ -48828,7 +48828,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795162200928</v>
+        <v>6.62795209884644</v>
       </c>
       <c r="H1671" t="n">
         <v>134394</v>
@@ -48857,7 +48857,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539770126343</v>
+        <v>6.60539722442627</v>
       </c>
       <c r="H1672" t="n">
         <v>149384</v>
@@ -48944,7 +48944,7 @@
         <v>8.99325561523438</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.95338916778564</v>
+        <v>6.95338869094849</v>
       </c>
       <c r="H1675" t="n">
         <v>183001</v>
@@ -49002,7 +49002,7 @@
         <v>9.01409339904785</v>
       </c>
       <c r="G1677" t="n">
-        <v>6.96950054168701</v>
+        <v>6.96950006484985</v>
       </c>
       <c r="H1677" t="n">
         <v>218588</v>
@@ -49089,7 +49089,7 @@
         <v>8.73487663269043</v>
       </c>
       <c r="G1680" t="n">
-        <v>6.75361585617065</v>
+        <v>6.7536153793335</v>
       </c>
       <c r="H1680" t="n">
         <v>210660</v>
@@ -49205,7 +49205,7 @@
         <v>8.95158195495605</v>
       </c>
       <c r="G1684" t="n">
-        <v>6.92116737365723</v>
+        <v>6.92116785049438</v>
       </c>
       <c r="H1684" t="n">
         <v>262827</v>
@@ -49234,7 +49234,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.7407283782959</v>
+        <v>6.74072790145874</v>
       </c>
       <c r="H1685" t="n">
         <v>219529</v>
@@ -49321,7 +49321,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973394393921</v>
+        <v>6.47973346710205</v>
       </c>
       <c r="H1688" t="n">
         <v>211830</v>
@@ -49379,7 +49379,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107488632202</v>
+        <v>6.15107583999634</v>
       </c>
       <c r="H1690" t="n">
         <v>346128</v>
@@ -49408,7 +49408,7 @@
         <v>7.97640991210938</v>
       </c>
       <c r="G1691" t="n">
-        <v>6.16718578338623</v>
+        <v>6.16718626022339</v>
       </c>
       <c r="H1691" t="n">
         <v>184846</v>
@@ -49437,7 +49437,7 @@
         <v>7.7680401802063</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.00607919692993</v>
+        <v>6.00607872009277</v>
       </c>
       <c r="H1692" t="n">
         <v>226862</v>
@@ -49553,7 +49553,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032152175903</v>
+        <v>5.11032199859619</v>
       </c>
       <c r="H1696" t="n">
         <v>868645</v>
@@ -49640,7 +49640,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799476623535</v>
+        <v>4.88799428939819</v>
       </c>
       <c r="H1699" t="n">
         <v>228803</v>
@@ -49959,7 +49959,7 @@
         <v>6.27194213867188</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.84932899475098</v>
+        <v>4.84932851791382</v>
       </c>
       <c r="H1710" t="n">
         <v>660674</v>
@@ -50017,7 +50017,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555252075195</v>
+        <v>4.76555204391479</v>
       </c>
       <c r="H1712" t="n">
         <v>627926</v>
@@ -50220,7 +50220,7 @@
         <v>5.1717472076416</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.99868226051331</v>
+        <v>3.99868178367615</v>
       </c>
       <c r="H1719" t="n">
         <v>801083</v>
@@ -50249,7 +50249,7 @@
         <v>4.99671602249146</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.86335182189941</v>
+        <v>3.86335134506226</v>
       </c>
       <c r="H1720" t="n">
         <v>478249</v>
@@ -50278,7 +50278,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179785728455</v>
+        <v>3.81179761886597</v>
       </c>
       <c r="H1721" t="n">
         <v>554124</v>
@@ -50365,7 +50365,7 @@
         <v>4.68311882019043</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.62088513374329</v>
+        <v>3.62088489532471</v>
       </c>
       <c r="H1724" t="n">
         <v>677198</v>
@@ -50771,7 +50771,7 @@
         <v>1.93019998073578</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.49238848686218</v>
+        <v>1.49238836765289</v>
       </c>
       <c r="H1738" t="n">
         <v>977946</v>
@@ -50800,7 +50800,7 @@
         <v>1.90980005264282</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.47661566734314</v>
+        <v>1.47661578655243</v>
       </c>
       <c r="H1739" t="n">
         <v>1929525</v>
@@ -50945,7 +50945,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.39945232868195</v>
+        <v>1.39945244789124</v>
       </c>
       <c r="H1744" t="n">
         <v>10215715</v>
@@ -51119,7 +51119,7 @@
         <v>1.81560003757477</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.40378224849701</v>
+        <v>1.4037823677063</v>
       </c>
       <c r="H1750" t="n">
         <v>4722464</v>
@@ -51148,7 +51148,7 @@
         <v>1.76339995861053</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.36342239379883</v>
+        <v>1.36342227458954</v>
       </c>
       <c r="H1751" t="n">
         <v>3047867</v>
@@ -51177,7 +51177,7 @@
         <v>1.81239998340607</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.40130817890167</v>
+        <v>1.40130805969238</v>
       </c>
       <c r="H1752" t="n">
         <v>3775318</v>
@@ -51235,7 +51235,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.39156603813171</v>
+        <v>1.391566157341</v>
       </c>
       <c r="H1754" t="n">
         <v>2641302</v>
@@ -51293,7 +51293,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.41615319252014</v>
+        <v>1.41615307331085</v>
       </c>
       <c r="H1756" t="n">
         <v>9845377</v>
@@ -51351,7 +51351,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393760681152</v>
+        <v>1.37393748760223</v>
       </c>
       <c r="H1758" t="n">
         <v>3847795</v>
@@ -51380,7 +51380,7 @@
         <v>1.80859994888306</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.39836990833282</v>
+        <v>1.39837002754211</v>
       </c>
       <c r="H1759" t="n">
         <v>3782624</v>
@@ -51409,7 +51409,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006965637207</v>
+        <v>1.46006953716278</v>
       </c>
       <c r="H1760" t="n">
         <v>10216109</v>
@@ -51438,7 +51438,7 @@
         <v>1.88339996337891</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.45620381832123</v>
+        <v>1.45620369911194</v>
       </c>
       <c r="H1761" t="n">
         <v>12545701</v>
@@ -51467,7 +51467,7 @@
         <v>1.88960003852844</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.46099758148193</v>
+        <v>1.46099746227264</v>
       </c>
       <c r="H1762" t="n">
         <v>18263848</v>
@@ -51496,7 +51496,7 @@
         <v>1.88919997215271</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.46068811416626</v>
+        <v>1.46068823337555</v>
       </c>
       <c r="H1763" t="n">
         <v>3524769</v>
@@ -51525,7 +51525,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.51929497718811</v>
+        <v>1.5192950963974</v>
       </c>
       <c r="H1764" t="n">
         <v>6153718</v>
@@ -51554,7 +51554,7 @@
         <v>1.87360000610352</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.44862651824951</v>
+        <v>1.4486266374588</v>
       </c>
       <c r="H1765" t="n">
         <v>9888369</v>
@@ -51699,7 +51699,7 @@
         <v>1.94640004634857</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.50491404533386</v>
+        <v>1.50491392612457</v>
       </c>
       <c r="H1770" t="n">
         <v>8428502</v>
@@ -51815,7 +51815,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.45125544071198</v>
+        <v>1.45125532150269</v>
       </c>
       <c r="H1774" t="n">
         <v>7152049</v>
@@ -51902,7 +51902,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.57689678668976</v>
+        <v>1.57689690589905</v>
       </c>
       <c r="H1777" t="n">
         <v>14755833</v>
@@ -52018,7 +52018,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.50213062763214</v>
+        <v>1.50213050842285</v>
       </c>
       <c r="H1781" t="n">
         <v>3033681</v>
@@ -52047,7 +52047,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.48805856704712</v>
+        <v>1.48805868625641</v>
       </c>
       <c r="H1782" t="n">
         <v>2159725</v>
@@ -52076,7 +52076,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.58501529693604</v>
+        <v>1.58501517772675</v>
       </c>
       <c r="H1783" t="n">
         <v>13921292</v>
@@ -52163,7 +52163,7 @@
         <v>1.98660004138947</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.53599584102631</v>
+        <v>1.53599572181702</v>
       </c>
       <c r="H1786" t="n">
         <v>9824828</v>
@@ -52279,7 +52279,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702341079712</v>
+        <v>1.67702329158783</v>
       </c>
       <c r="H1790" t="n">
         <v>8965001</v>
@@ -52308,7 +52308,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.7017650604248</v>
+        <v>1.70176517963409</v>
       </c>
       <c r="H1791" t="n">
         <v>8676097</v>
@@ -52366,7 +52366,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.65537440776825</v>
+        <v>1.65537452697754</v>
       </c>
       <c r="H1793" t="n">
         <v>21373665</v>
@@ -52453,7 +52453,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259298324585</v>
+        <v>1.56259310245514</v>
       </c>
       <c r="H1796" t="n">
         <v>7220763</v>
@@ -52540,7 +52540,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681817054749</v>
+        <v>1.63681828975677</v>
       </c>
       <c r="H1799" t="n">
         <v>5974419</v>
@@ -52598,7 +52598,7 @@
         <v>2.17899990081787</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.68475520610809</v>
+        <v>1.6847550868988</v>
       </c>
       <c r="H1801" t="n">
         <v>14097011</v>
@@ -52656,7 +52656,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.79377341270447</v>
+        <v>1.79377329349518</v>
       </c>
       <c r="H1803" t="n">
         <v>18893517</v>
@@ -52743,7 +52743,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.87186419963837</v>
+        <v>1.87186431884766</v>
       </c>
       <c r="H1806" t="n">
         <v>12148200</v>
@@ -52772,7 +52772,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482709884644</v>
+        <v>1.92482697963715</v>
       </c>
       <c r="H1807" t="n">
         <v>14549250</v>
@@ -52801,7 +52801,7 @@
         <v>2.37350010871887</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.83513844013214</v>
+        <v>1.83513855934143</v>
       </c>
       <c r="H1808" t="n">
         <v>19340207</v>
@@ -52830,7 +52830,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.847895860672</v>
+        <v>1.84789597988129</v>
       </c>
       <c r="H1809" t="n">
         <v>9933747</v>
@@ -52859,7 +52859,7 @@
         <v>2.31550002098083</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.79029417037964</v>
+        <v>1.79029405117035</v>
       </c>
       <c r="H1810" t="n">
         <v>25899848</v>
@@ -52888,7 +52888,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.01026320457458</v>
+        <v>2.01026296615601</v>
       </c>
       <c r="H1811" t="n">
         <v>45207296</v>
@@ -52917,7 +52917,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.90201818943024</v>
+        <v>1.90201842784882</v>
       </c>
       <c r="H1812" t="n">
         <v>16282025</v>
@@ -53004,7 +53004,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552503585815</v>
+        <v>1.83552491664886</v>
       </c>
       <c r="H1815" t="n">
         <v>8871781</v>
@@ -53033,7 +53033,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.91052305698395</v>
+        <v>1.91052317619324</v>
       </c>
       <c r="H1816" t="n">
         <v>14267354</v>
@@ -53149,7 +53149,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.0380973815918</v>
+        <v>2.03809762001038</v>
       </c>
       <c r="H1820" t="n">
         <v>13501447</v>
@@ -53178,7 +53178,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.03384494781494</v>
+        <v>2.0338454246521</v>
       </c>
       <c r="H1821" t="n">
         <v>13235723</v>
@@ -53236,7 +53236,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198734283447</v>
+        <v>2.12198758125305</v>
       </c>
       <c r="H1823" t="n">
         <v>9639295</v>
@@ -53265,7 +53265,7 @@
         <v>2.52349996566772</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.95111513137817</v>
+        <v>1.95111525058746</v>
       </c>
       <c r="H1824" t="n">
         <v>54311078</v>
@@ -53323,7 +53323,7 @@
         <v>2.39050006866455</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.8482825756073</v>
+        <v>1.84828245639801</v>
       </c>
       <c r="H1826" t="n">
         <v>13530053</v>
@@ -53352,7 +53352,7 @@
         <v>2.46099996566772</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.90279150009155</v>
+        <v>1.90279138088226</v>
       </c>
       <c r="H1827" t="n">
         <v>7484611</v>
@@ -53468,7 +53468,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305135250092</v>
+        <v>1.80305159091949</v>
       </c>
       <c r="H1831" t="n">
         <v>6664209</v>
@@ -53584,7 +53584,7 @@
         <v>1.92460000514984</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.48805856704712</v>
+        <v>1.48805868625641</v>
       </c>
       <c r="H1835" t="n">
         <v>21201799</v>
@@ -53613,7 +53613,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.48450207710266</v>
+        <v>1.48450195789337</v>
       </c>
       <c r="H1836" t="n">
         <v>20305784</v>
@@ -53729,7 +53729,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.5175940990448</v>
+        <v>1.51759397983551</v>
       </c>
       <c r="H1840" t="n">
         <v>7183811</v>
@@ -53903,7 +53903,7 @@
         <v>1.99520003795624</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.54264509677887</v>
+        <v>1.54264497756958</v>
       </c>
       <c r="H1846" t="n">
         <v>10952973</v>
@@ -53990,7 +53990,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.49532663822174</v>
+        <v>1.49532651901245</v>
       </c>
       <c r="H1849" t="n">
         <v>5122410</v>
@@ -54019,7 +54019,7 @@
         <v>1.91349995136261</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.47947645187378</v>
+        <v>1.47947633266449</v>
       </c>
       <c r="H1850" t="n">
         <v>4817935</v>
@@ -54077,7 +54077,7 @@
         <v>1.99950003623962</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.54596984386444</v>
+        <v>1.54596972465515</v>
       </c>
       <c r="H1852" t="n">
         <v>6684358</v>
@@ -54135,7 +54135,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.58501529693604</v>
+        <v>1.58501517772675</v>
       </c>
       <c r="H1854" t="n">
         <v>4279847</v>
@@ -54164,7 +54164,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.6344987154007</v>
+        <v>1.63449859619141</v>
       </c>
       <c r="H1855" t="n">
         <v>7814956</v>
@@ -54193,7 +54193,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.6344987154007</v>
+        <v>1.63449859619141</v>
       </c>
       <c r="H1856" t="n">
         <v>6891203</v>
@@ -54222,7 +54222,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1857" t="n">
         <v>11220865</v>
@@ -54251,7 +54251,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222702980042</v>
+        <v>1.79222691059113</v>
       </c>
       <c r="H1858" t="n">
         <v>11711966</v>
@@ -54309,7 +54309,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666081905365</v>
+        <v>1.75666093826294</v>
       </c>
       <c r="H1860" t="n">
         <v>8508624</v>
@@ -54454,7 +54454,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.61516928672791</v>
+        <v>1.61516916751862</v>
       </c>
       <c r="H1865" t="n">
         <v>6994580</v>
@@ -54483,7 +54483,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.58037614822388</v>
+        <v>1.58037602901459</v>
       </c>
       <c r="H1866" t="n">
         <v>6951613</v>
@@ -54599,7 +54599,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.67315769195557</v>
+        <v>1.67315757274628</v>
       </c>
       <c r="H1870" t="n">
         <v>10635223</v>
@@ -54628,7 +54628,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681817054749</v>
+        <v>1.63681828975677</v>
       </c>
       <c r="H1871" t="n">
         <v>17872031</v>
@@ -54686,7 +54686,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831330299377</v>
+        <v>1.62831318378448</v>
       </c>
       <c r="H1873" t="n">
         <v>6917707</v>
@@ -54802,7 +54802,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.73501181602478</v>
+        <v>1.73501169681549</v>
       </c>
       <c r="H1877" t="n">
         <v>5397862</v>
@@ -54860,7 +54860,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.65537440776825</v>
+        <v>1.65537452697754</v>
       </c>
       <c r="H1879" t="n">
         <v>7813573</v>
@@ -54918,7 +54918,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.77444410324097</v>
+        <v>1.77444386482239</v>
       </c>
       <c r="H1881" t="n">
         <v>14803240</v>
@@ -54947,7 +54947,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.64841592311859</v>
+        <v>1.6484158039093</v>
       </c>
       <c r="H1882" t="n">
         <v>29583047</v>
@@ -55005,7 +55005,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.62058138847351</v>
+        <v>1.6205815076828</v>
       </c>
       <c r="H1884" t="n">
         <v>14947292</v>
@@ -55034,7 +55034,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.59738600254059</v>
+        <v>1.59738612174988</v>
       </c>
       <c r="H1885" t="n">
         <v>18251323</v>
@@ -55092,7 +55092,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.62985968589783</v>
+        <v>1.62985956668854</v>
       </c>
       <c r="H1887" t="n">
         <v>15958032</v>
@@ -55121,7 +55121,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006480693817</v>
+        <v>1.67006492614746</v>
       </c>
       <c r="H1888" t="n">
         <v>9732271</v>
@@ -55353,7 +55353,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.68552839756012</v>
+        <v>1.68552851676941</v>
       </c>
       <c r="H1896" t="n">
         <v>10826926</v>
@@ -55382,7 +55382,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650694847107</v>
       </c>
       <c r="H1897" t="n">
         <v>13177383</v>
@@ -55411,7 +55411,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.76593899726868</v>
+        <v>1.7659387588501</v>
       </c>
       <c r="H1898" t="n">
         <v>9180042</v>
@@ -55440,7 +55440,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.76748538017273</v>
+        <v>1.76748526096344</v>
       </c>
       <c r="H1899" t="n">
         <v>12029873</v>
@@ -55469,7 +55469,7 @@
         <v>2.32100009918213</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.79454660415649</v>
+        <v>1.7945464849472</v>
       </c>
       <c r="H1900" t="n">
         <v>9000879</v>
@@ -55498,7 +55498,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.80073189735413</v>
+        <v>1.80073201656342</v>
       </c>
       <c r="H1901" t="n">
         <v>7297805</v>
@@ -55556,7 +55556,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.79068052768707</v>
+        <v>1.79068064689636</v>
       </c>
       <c r="H1903" t="n">
         <v>9401467</v>
@@ -55585,7 +55585,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.74583625793457</v>
+        <v>1.74583613872528</v>
       </c>
       <c r="H1904" t="n">
         <v>7115446</v>
@@ -55614,7 +55614,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645569801331</v>
+        <v>1.71645557880402</v>
       </c>
       <c r="H1905" t="n">
         <v>7081375</v>
@@ -55701,7 +55701,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.77367067337036</v>
+        <v>1.77367055416107</v>
       </c>
       <c r="H1908" t="n">
         <v>7446800</v>
@@ -55730,7 +55730,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.77985608577728</v>
+        <v>1.77985620498657</v>
       </c>
       <c r="H1909" t="n">
         <v>7154278</v>
@@ -55759,7 +55759,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1910" t="n">
         <v>7777212</v>
@@ -55788,7 +55788,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.77444410324097</v>
+        <v>1.77444386482239</v>
       </c>
       <c r="H1911" t="n">
         <v>8748249</v>
@@ -55817,7 +55817,7 @@
         <v>2.30699992179871</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.78372204303741</v>
+        <v>1.78372192382812</v>
       </c>
       <c r="H1912" t="n">
         <v>6290363</v>
@@ -55875,7 +55875,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.77057790756226</v>
+        <v>1.77057802677155</v>
       </c>
       <c r="H1914" t="n">
         <v>6184037</v>
@@ -55904,7 +55904,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.80150496959686</v>
+        <v>1.80150508880615</v>
       </c>
       <c r="H1915" t="n">
         <v>7696382</v>
@@ -55933,7 +55933,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1916" t="n">
         <v>11063863</v>
@@ -55991,7 +55991,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985272407532</v>
+        <v>1.92985284328461</v>
       </c>
       <c r="H1918" t="n">
         <v>16178743</v>
@@ -56020,7 +56020,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.963099360466</v>
+        <v>1.96309947967529</v>
       </c>
       <c r="H1919" t="n">
         <v>16639251</v>
@@ -56049,7 +56049,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.9600065946579</v>
+        <v>1.96000671386719</v>
       </c>
       <c r="H1920" t="n">
         <v>11600649</v>
@@ -56078,7 +56078,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.97624325752258</v>
+        <v>1.97624337673187</v>
       </c>
       <c r="H1921" t="n">
         <v>6898571</v>
@@ -56107,7 +56107,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.97160446643829</v>
+        <v>1.97160422801971</v>
       </c>
       <c r="H1922" t="n">
         <v>5995361</v>
@@ -56136,7 +56136,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.95923328399658</v>
+        <v>1.95923340320587</v>
       </c>
       <c r="H1923" t="n">
         <v>6467525</v>
@@ -56165,7 +56165,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382130146027</v>
+        <v>1.95382106304169</v>
       </c>
       <c r="H1924" t="n">
         <v>4430041</v>
@@ -56194,7 +56194,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.97160446643829</v>
+        <v>1.97160422801971</v>
       </c>
       <c r="H1925" t="n">
         <v>5300597</v>
@@ -56223,7 +56223,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918203353882</v>
+        <v>1.94918191432953</v>
       </c>
       <c r="H1926" t="n">
         <v>5834369</v>
@@ -56252,7 +56252,7 @@
         <v>2.61700010299683</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.02340722084045</v>
+        <v>2.02340745925903</v>
       </c>
       <c r="H1927" t="n">
         <v>20029327</v>
@@ -56310,7 +56310,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562429428101</v>
+        <v>2.00562405586243</v>
       </c>
       <c r="H1929" t="n">
         <v>10963576</v>
@@ -56339,7 +56339,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959275245667</v>
+        <v>2.02959251403809</v>
       </c>
       <c r="H1930" t="n">
         <v>11993677</v>
@@ -56368,7 +56368,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.96077978610992</v>
+        <v>1.96077990531921</v>
       </c>
       <c r="H1931" t="n">
         <v>9783275</v>
@@ -56426,7 +56426,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.90356457233429</v>
+        <v>1.90356469154358</v>
       </c>
       <c r="H1933" t="n">
         <v>13404200</v>
@@ -56513,7 +56513,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.90974998474121</v>
+        <v>1.9097501039505</v>
       </c>
       <c r="H1936" t="n">
         <v>39674896</v>
@@ -56600,7 +56600,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.03191232681274</v>
+        <v>2.03191208839417</v>
       </c>
       <c r="H1939" t="n">
         <v>13224837</v>
@@ -56629,7 +56629,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025996208191</v>
+        <v>2.16025948524475</v>
       </c>
       <c r="H1940" t="n">
         <v>21527670</v>
@@ -56803,7 +56803,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.97624325752258</v>
+        <v>1.97624337673187</v>
       </c>
       <c r="H1946" t="n">
         <v>12028860</v>
@@ -56832,7 +56832,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.95459449291229</v>
+        <v>1.954594373703</v>
       </c>
       <c r="H1947" t="n">
         <v>11144521</v>
@@ -56890,7 +56890,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.963099360466</v>
+        <v>1.96309947967529</v>
       </c>
       <c r="H1949" t="n">
         <v>5429828</v>
@@ -56919,7 +56919,7 @@
         <v>2.5789999961853</v>
       </c>
       <c r="G1950" t="n">
-        <v>1.99402642250061</v>
+        <v>1.9940265417099</v>
       </c>
       <c r="H1950" t="n">
         <v>6249034</v>
@@ -56977,7 +56977,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.98088228702545</v>
+        <v>1.98088252544403</v>
       </c>
       <c r="H1952" t="n">
         <v>14258681</v>
@@ -57006,7 +57006,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.9600065946579</v>
+        <v>1.96000671386719</v>
       </c>
       <c r="H1953" t="n">
         <v>6716319</v>
@@ -57064,7 +57064,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.90511107444763</v>
+        <v>1.90511095523834</v>
       </c>
       <c r="H1955" t="n">
         <v>11937121</v>
@@ -57093,7 +57093,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.7976393699646</v>
+        <v>1.79763913154602</v>
       </c>
       <c r="H1956" t="n">
         <v>22749670</v>
@@ -57238,7 +57238,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645209789276</v>
+        <v>1.86645197868347</v>
       </c>
       <c r="H1961" t="n">
         <v>10420578</v>
@@ -57296,7 +57296,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.92676019668579</v>
+        <v>1.9267600774765</v>
       </c>
       <c r="H1963" t="n">
         <v>13390725</v>
@@ -57383,7 +57383,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.10768365859985</v>
+        <v>2.10768389701843</v>
       </c>
       <c r="H1966" t="n">
         <v>26715391</v>
@@ -57412,7 +57412,7 @@
         <v>2.73900008201599</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.11773490905762</v>
+        <v>2.1177351474762</v>
       </c>
       <c r="H1967" t="n">
         <v>25132081</v>
@@ -57528,7 +57528,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866905212402</v>
+        <v>1.84866893291473</v>
       </c>
       <c r="H1971" t="n">
         <v>32386618</v>
@@ -57557,7 +57557,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.8618129491806</v>
+        <v>1.86181282997131</v>
       </c>
       <c r="H1972" t="n">
         <v>18377109</v>
@@ -57586,7 +57586,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.86722528934479</v>
+        <v>1.8672251701355</v>
       </c>
       <c r="H1973" t="n">
         <v>10855064</v>
@@ -57644,7 +57644,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.91748189926147</v>
+        <v>1.91748178005219</v>
       </c>
       <c r="H1975" t="n">
         <v>17294006</v>
@@ -57702,7 +57702,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.96077978610992</v>
+        <v>1.96077990531921</v>
       </c>
       <c r="H1977" t="n">
         <v>19720359</v>
@@ -57731,7 +57731,7 @@
         <v>2.60899996757507</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.01722168922424</v>
+        <v>2.01722192764282</v>
       </c>
       <c r="H1978" t="n">
         <v>16862561</v>
@@ -57760,7 +57760,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.89119374752045</v>
+        <v>1.89119386672974</v>
       </c>
       <c r="H1979" t="n">
         <v>28800121</v>
@@ -57789,7 +57789,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.9012451171875</v>
+        <v>1.90124535560608</v>
       </c>
       <c r="H1980" t="n">
         <v>37059275</v>
@@ -57847,7 +57847,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.98552167415619</v>
+        <v>1.98552143573761</v>
       </c>
       <c r="H1982" t="n">
         <v>29807799</v>
@@ -57934,7 +57934,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397517204285</v>
+        <v>1.98397505283356</v>
       </c>
       <c r="H1985" t="n">
         <v>20639388</v>
@@ -57963,7 +57963,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.95614075660706</v>
+        <v>1.95614063739777</v>
       </c>
       <c r="H1986" t="n">
         <v>18660240</v>
@@ -57992,7 +57992,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.91052305698395</v>
+        <v>1.91052317619324</v>
       </c>
       <c r="H1987" t="n">
         <v>16615036</v>
@@ -58021,7 +58021,7 @@
         <v>2.37299990653992</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.83475172519684</v>
+        <v>1.83475160598755</v>
       </c>
       <c r="H1988" t="n">
         <v>16787583</v>
@@ -58050,7 +58050,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.85949337482452</v>
+        <v>1.85949349403381</v>
       </c>
       <c r="H1989" t="n">
         <v>32110096</v>
@@ -58079,7 +58079,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.85408139228821</v>
+        <v>1.85408115386963</v>
       </c>
       <c r="H1990" t="n">
         <v>14799249</v>
@@ -58108,7 +58108,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.81155622005463</v>
+        <v>1.81155633926392</v>
       </c>
       <c r="H1991" t="n">
         <v>6593039</v>
@@ -58166,7 +58166,7 @@
         <v>2.42899990081787</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.87804961204529</v>
+        <v>1.87804973125458</v>
       </c>
       <c r="H1993" t="n">
         <v>10692244</v>
@@ -58195,7 +58195,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062579631805</v>
+        <v>1.93062591552734</v>
       </c>
       <c r="H1994" t="n">
         <v>10863078</v>
@@ -58224,7 +58224,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237765789032</v>
+        <v>1.97237753868103</v>
       </c>
       <c r="H1995" t="n">
         <v>14164042</v>
@@ -58253,7 +58253,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866557121277</v>
+        <v>1.99866545200348</v>
       </c>
       <c r="H1996" t="n">
         <v>13386081</v>
@@ -58282,7 +58282,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964400291443</v>
+        <v>2.03964376449585</v>
       </c>
       <c r="H1997" t="n">
         <v>18265540</v>
@@ -58340,7 +58340,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1999" t="n">
-        <v>2.03191232681274</v>
+        <v>2.03191208839417</v>
       </c>
       <c r="H1999" t="n">
         <v>11141976</v>
@@ -58427,7 +58427,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.08680772781372</v>
+        <v>2.0868079662323</v>
       </c>
       <c r="H2002" t="n">
         <v>18452495</v>
@@ -58456,7 +58456,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443714141846</v>
+        <v>2.07443690299988</v>
       </c>
       <c r="H2003" t="n">
         <v>11980891</v>
@@ -58572,7 +58572,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G2007" t="n">
-        <v>2.3597400188446</v>
+        <v>2.35973978042603</v>
       </c>
       <c r="H2007" t="n">
         <v>16760666</v>
@@ -58659,7 +58659,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654799461365</v>
+        <v>2.18654775619507</v>
       </c>
       <c r="H2010" t="n">
         <v>100072608</v>
@@ -58717,7 +58717,7 @@
         <v>2.92899990081787</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.26463866233826</v>
+        <v>2.26463890075684</v>
       </c>
       <c r="H2012" t="n">
         <v>40936353</v>
@@ -58746,7 +58746,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716371536255</v>
+        <v>2.30716347694397</v>
       </c>
       <c r="H2013" t="n">
         <v>31624933</v>
@@ -58833,7 +58833,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071821212769</v>
+        <v>2.40071797370911</v>
       </c>
       <c r="H2016" t="n">
         <v>54965782</v>
@@ -58891,7 +58891,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.42777967453003</v>
+        <v>2.42777943611145</v>
       </c>
       <c r="H2018" t="n">
         <v>25023304</v>
@@ -59094,7 +59094,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.53447794914246</v>
+        <v>2.53447818756104</v>
       </c>
       <c r="H2025" t="n">
         <v>37969241</v>
@@ -59210,7 +59210,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876134872437</v>
+        <v>2.31876158714294</v>
       </c>
       <c r="H2029" t="n">
         <v>17461139</v>
@@ -59297,7 +59297,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.35046148300171</v>
+        <v>2.35046172142029</v>
       </c>
       <c r="H2032" t="n">
         <v>11232080</v>
@@ -59326,7 +59326,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37443017959595</v>
+        <v>2.37442994117737</v>
       </c>
       <c r="H2033" t="n">
         <v>6292252</v>
@@ -59355,7 +59355,7 @@
         <v>3.11899995803833</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.41154265403748</v>
+        <v>2.41154289245605</v>
       </c>
       <c r="H2034" t="n">
         <v>8906628</v>
@@ -59413,7 +59413,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.35510063171387</v>
+        <v>2.35510087013245</v>
       </c>
       <c r="H2036" t="n">
         <v>10336670</v>
@@ -59529,7 +59529,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.57777619361877</v>
+        <v>2.5777759552002</v>
       </c>
       <c r="H2040" t="n">
         <v>21608685</v>
@@ -59558,7 +59558,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334204673767</v>
+        <v>2.61334228515625</v>
       </c>
       <c r="H2041" t="n">
         <v>21815059</v>
@@ -59935,7 +59935,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.59169316291809</v>
+        <v>2.59169340133667</v>
       </c>
       <c r="H2054" t="n">
         <v>26331357</v>
@@ -59993,7 +59993,7 @@
         <v>3.19099998474121</v>
       </c>
       <c r="G2056" t="n">
-        <v>2.46721172332764</v>
+        <v>2.46721148490906</v>
       </c>
       <c r="H2056" t="n">
         <v>19021872</v>
@@ -60022,7 +60022,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.53602457046509</v>
+        <v>2.53602433204651</v>
       </c>
       <c r="H2057" t="n">
         <v>20653870</v>
@@ -60051,7 +60051,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.5298388004303</v>
+        <v>2.52983927726746</v>
       </c>
       <c r="H2058" t="n">
         <v>17041685</v>
@@ -60283,7 +60283,7 @@
         <v>3.53900003433228</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.73627758026123</v>
+        <v>2.73627781867981</v>
       </c>
       <c r="H2066" t="n">
         <v>30033671</v>
@@ -60312,7 +60312,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.74323630332947</v>
+        <v>2.74323606491089</v>
       </c>
       <c r="H2067" t="n">
         <v>44075315</v>
@@ -60341,7 +60341,7 @@
         <v>3.6489999294281</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.82132720947266</v>
+        <v>2.82132697105408</v>
       </c>
       <c r="H2068" t="n">
         <v>26692588</v>
@@ -60370,7 +60370,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792646408081</v>
+        <v>2.75792622566223</v>
       </c>
       <c r="H2069" t="n">
         <v>27477458</v>
@@ -60399,7 +60399,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467994689941</v>
+        <v>2.72467970848083</v>
       </c>
       <c r="H2070" t="n">
         <v>14759944</v>
@@ -60428,7 +60428,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452571868896</v>
+        <v>2.69452595710754</v>
       </c>
       <c r="H2071" t="n">
         <v>16175878</v>
@@ -60486,7 +60486,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.75019478797913</v>
+        <v>2.75019454956055</v>
       </c>
       <c r="H2073" t="n">
         <v>39123998</v>
@@ -60544,7 +60544,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.89245963096619</v>
+        <v>2.89245939254761</v>
       </c>
       <c r="H2075" t="n">
         <v>28364901</v>
@@ -60573,7 +60573,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.88859343528748</v>
+        <v>2.88859367370605</v>
       </c>
       <c r="H2076" t="n">
         <v>26425626</v>
@@ -60631,7 +60631,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2078" t="n">
-        <v>2.89245963096619</v>
+        <v>2.89245939254761</v>
       </c>
       <c r="H2078" t="n">
         <v>15255947</v>
@@ -60718,7 +60718,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.04632186889648</v>
+        <v>3.04632210731506</v>
       </c>
       <c r="H2081" t="n">
         <v>24628211</v>
@@ -60921,7 +60921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2088" t="n">
-        <v>3.17003059387207</v>
+        <v>3.17003035545349</v>
       </c>
       <c r="H2088" t="n">
         <v>24484756</v>
@@ -61124,7 +61124,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G2095" t="n">
-        <v>3.21564769744873</v>
+        <v>3.21564793586731</v>
       </c>
       <c r="H2095" t="n">
         <v>22065801</v>
@@ -61298,7 +61298,7 @@
         <v>4.1710000038147</v>
       </c>
       <c r="G2101" t="n">
-        <v>3.22492623329163</v>
+        <v>3.22492599487305</v>
       </c>
       <c r="H2101" t="n">
         <v>15860905</v>
@@ -61385,7 +61385,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.15843296051025</v>
+        <v>3.15843272209167</v>
       </c>
       <c r="H2104" t="n">
         <v>12108834</v>
@@ -61414,7 +61414,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.07338309288025</v>
+        <v>3.07338333129883</v>
       </c>
       <c r="H2105" t="n">
         <v>15454340</v>
@@ -61472,7 +61472,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972261428833</v>
+        <v>3.10972237586975</v>
       </c>
       <c r="H2107" t="n">
         <v>24633782</v>
@@ -61646,7 +61646,7 @@
         <v>4.16300010681152</v>
       </c>
       <c r="G2113" t="n">
-        <v>3.21874070167542</v>
+        <v>3.21874094009399</v>
       </c>
       <c r="H2113" t="n">
         <v>18257227</v>
@@ -61704,7 +61704,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739631652832</v>
+        <v>3.40739607810974</v>
       </c>
       <c r="H2115" t="n">
         <v>25716222</v>
@@ -61791,7 +61791,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471403121948</v>
+        <v>3.48471426963806</v>
       </c>
       <c r="H2118" t="n">
         <v>28093096</v>
@@ -61820,7 +61820,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G2119" t="n">
-        <v>3.47466278076172</v>
+        <v>3.47466254234314</v>
       </c>
       <c r="H2119" t="n">
         <v>18482624</v>
@@ -61849,7 +61849,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2120" t="n">
-        <v>3.51796078681946</v>
+        <v>3.51796054840088</v>
       </c>
       <c r="H2120" t="n">
         <v>24621349</v>
@@ -61878,7 +61878,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811129570007</v>
+        <v>3.69811105728149</v>
       </c>
       <c r="H2121" t="n">
         <v>32155461</v>
@@ -61936,7 +61936,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.5666708946228</v>
+        <v>3.56667041778564</v>
       </c>
       <c r="H2123" t="n">
         <v>15663428</v>
@@ -61965,7 +61965,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2124" t="n">
-        <v>3.60300993919373</v>
+        <v>3.6030101776123</v>
       </c>
       <c r="H2124" t="n">
         <v>34298846</v>
@@ -61994,7 +61994,7 @@
         <v>4.64900016784668</v>
       </c>
       <c r="G2125" t="n">
-        <v>3.59450507164001</v>
+        <v>3.59450531005859</v>
       </c>
       <c r="H2125" t="n">
         <v>25660150</v>
@@ -62110,7 +62110,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G2129" t="n">
-        <v>3.76769709587097</v>
+        <v>3.76769733428955</v>
       </c>
       <c r="H2129" t="n">
         <v>26746590</v>
@@ -62139,7 +62139,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145707130432</v>
+        <v>3.90145683288574</v>
       </c>
       <c r="H2130" t="n">
         <v>31985059</v>
@@ -62168,7 +62168,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2131" t="n">
-        <v>3.98186731338501</v>
+        <v>3.98186755180359</v>
       </c>
       <c r="H2131" t="n">
         <v>28979314</v>
@@ -62197,7 +62197,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G2132" t="n">
-        <v>4.09320497512817</v>
+        <v>4.09320545196533</v>
       </c>
       <c r="H2132" t="n">
         <v>33248614</v>
@@ -62255,7 +62255,7 @@
         <v>4.98099994659424</v>
       </c>
       <c r="G2134" t="n">
-        <v>4.04208040237427</v>
+        <v>4.04208087921143</v>
       </c>
       <c r="H2134" t="n">
         <v>12971734</v>
@@ -62458,7 +62458,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2141" t="n">
-        <v>3.99257898330688</v>
+        <v>3.99257922172546</v>
       </c>
       <c r="H2141" t="n">
         <v>26160718</v>
@@ -62516,7 +62516,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G2143" t="n">
-        <v>3.9990713596344</v>
+        <v>3.99907112121582</v>
       </c>
       <c r="H2143" t="n">
         <v>11607781</v>
@@ -62690,7 +62690,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2149" t="n">
-        <v>3.757244348526</v>
+        <v>3.75724411010742</v>
       </c>
       <c r="H2149" t="n">
         <v>21711731</v>
@@ -62719,7 +62719,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2150" t="n">
-        <v>3.78970456123352</v>
+        <v>3.78970408439636</v>
       </c>
       <c r="H2150" t="n">
         <v>15083376</v>
@@ -62748,7 +62748,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G2151" t="n">
-        <v>3.64201140403748</v>
+        <v>3.6420111656189</v>
       </c>
       <c r="H2151" t="n">
         <v>19374406</v>
@@ -62835,7 +62835,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G2154" t="n">
-        <v>3.6777172088623</v>
+        <v>3.67771744728088</v>
       </c>
       <c r="H2154" t="n">
         <v>20881847</v>
@@ -62864,7 +62864,7 @@
         <v>4.56699991226196</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.70611953735352</v>
+        <v>3.70611977577209</v>
       </c>
       <c r="H2155" t="n">
         <v>13574114</v>
@@ -62951,7 +62951,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2158" t="n">
-        <v>3.74994039535522</v>
+        <v>3.7499406337738</v>
       </c>
       <c r="H2158" t="n">
         <v>19858583</v>
@@ -63009,7 +63009,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2160" t="n">
-        <v>3.60305953025818</v>
+        <v>3.6030592918396</v>
       </c>
       <c r="H2160" t="n">
         <v>12604005</v>
@@ -63096,7 +63096,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G2163" t="n">
-        <v>3.79700779914856</v>
+        <v>3.79700756072998</v>
       </c>
       <c r="H2163" t="n">
         <v>21436986</v>
@@ -63125,7 +63125,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2164" t="n">
-        <v>3.74994039535522</v>
+        <v>3.7499406337738</v>
       </c>
       <c r="H2164" t="n">
         <v>10077225</v>
@@ -63154,7 +63154,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G2165" t="n">
-        <v>3.96417713165283</v>
+        <v>3.96417689323425</v>
       </c>
       <c r="H2165" t="n">
         <v>30567140</v>
@@ -63212,7 +63212,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G2167" t="n">
-        <v>3.92522478103638</v>
+        <v>3.9252245426178</v>
       </c>
       <c r="H2167" t="n">
         <v>13060115</v>
@@ -63444,7 +63444,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G2175" t="n">
-        <v>3.99501347541809</v>
+        <v>3.99501371383667</v>
       </c>
       <c r="H2175" t="n">
         <v>11662675</v>
@@ -63676,7 +63676,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.99420237541199</v>
+        <v>3.99420213699341</v>
       </c>
       <c r="H2183" t="n">
         <v>8046997</v>
@@ -63763,7 +63763,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2186" t="n">
-        <v>3.814049243927</v>
+        <v>3.81404900550842</v>
       </c>
       <c r="H2186" t="n">
         <v>21749998</v>
@@ -63792,7 +63792,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G2187" t="n">
-        <v>3.63470792770386</v>
+        <v>3.63470768928528</v>
       </c>
       <c r="H2187" t="n">
         <v>19583127</v>
@@ -63821,7 +63821,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G2188" t="n">
-        <v>3.52028632164001</v>
+        <v>3.52028608322144</v>
       </c>
       <c r="H2188" t="n">
         <v>25013968</v>
@@ -63908,7 +63908,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G2191" t="n">
-        <v>4.0785984992981</v>
+        <v>4.07859802246094</v>
       </c>
       <c r="H2191" t="n">
         <v>19208194</v>
@@ -64111,7 +64111,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2198" t="n">
-        <v>4.22629165649414</v>
+        <v>4.22629117965698</v>
       </c>
       <c r="H2198" t="n">
         <v>10355970</v>
@@ -64140,7 +64140,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G2199" t="n">
-        <v>4.23440599441528</v>
+        <v>4.23440647125244</v>
       </c>
       <c r="H2199" t="n">
         <v>8128461</v>
@@ -64227,7 +64227,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G2202" t="n">
-        <v>4.24089765548706</v>
+        <v>4.24089813232422</v>
       </c>
       <c r="H2202" t="n">
         <v>3987011</v>
@@ -64256,7 +64256,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2203" t="n">
-        <v>4.24414443969727</v>
+        <v>4.24414396286011</v>
       </c>
       <c r="H2203" t="n">
         <v>5969529</v>
@@ -64314,7 +64314,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G2205" t="n">
-        <v>4.23278331756592</v>
+        <v>4.23278284072876</v>
       </c>
       <c r="H2205" t="n">
         <v>7947589</v>
@@ -64372,7 +64372,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G2207" t="n">
-        <v>4.21006155014038</v>
+        <v>4.21006107330322</v>
       </c>
       <c r="H2207" t="n">
         <v>10026352</v>
@@ -64459,7 +64459,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2210" t="n">
-        <v>4.09807443618774</v>
+        <v>4.09807395935059</v>
       </c>
       <c r="H2210" t="n">
         <v>9610643</v>
@@ -64488,7 +64488,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.98608732223511</v>
+        <v>3.98608756065369</v>
       </c>
       <c r="H2211" t="n">
         <v>13196853</v>
@@ -64575,7 +64575,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.96904563903809</v>
+        <v>3.96904540061951</v>
       </c>
       <c r="H2214" t="n">
         <v>12020355</v>
@@ -64691,7 +64691,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G2218" t="n">
-        <v>3.99582505226135</v>
+        <v>3.99582529067993</v>
       </c>
       <c r="H2218" t="n">
         <v>10120832</v>
@@ -64749,7 +64749,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2220" t="n">
-        <v>4.05587673187256</v>
+        <v>4.0558762550354</v>
       </c>
       <c r="H2220" t="n">
         <v>12990332</v>
@@ -64778,7 +64778,7 @@
         <v>4.97100019454956</v>
       </c>
       <c r="G2221" t="n">
-        <v>4.03396606445312</v>
+        <v>4.03396558761597</v>
       </c>
       <c r="H2221" t="n">
         <v>14888759</v>
@@ -64836,7 +64836,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G2223" t="n">
-        <v>4.06074523925781</v>
+        <v>4.06074571609497</v>
       </c>
       <c r="H2223" t="n">
         <v>11996497</v>
@@ -64952,7 +64952,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G2227" t="n">
-        <v>4.20519256591797</v>
+        <v>4.20519208908081</v>
       </c>
       <c r="H2227" t="n">
         <v>12886962</v>
@@ -65039,7 +65039,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.88870739936829</v>
+        <v>3.88870716094971</v>
       </c>
       <c r="H2230" t="n">
         <v>16144924</v>
@@ -65097,7 +65097,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2232" t="n">
-        <v>4.05587673187256</v>
+        <v>4.0558762550354</v>
       </c>
       <c r="H2232" t="n">
         <v>10452631</v>
@@ -65126,7 +65126,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G2233" t="n">
-        <v>4.15325593948364</v>
+        <v>4.1532564163208</v>
       </c>
       <c r="H2233" t="n">
         <v>16873513</v>
@@ -65155,7 +65155,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G2234" t="n">
-        <v>4.1613712310791</v>
+        <v>4.16137075424194</v>
       </c>
       <c r="H2234" t="n">
         <v>7535202</v>
@@ -65271,7 +65271,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G2238" t="n">
-        <v>4.25712776184082</v>
+        <v>4.25712823867798</v>
       </c>
       <c r="H2238" t="n">
         <v>12216723</v>
@@ -65416,7 +65416,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G2243" t="n">
-        <v>4.25875091552734</v>
+        <v>4.2587513923645</v>
       </c>
       <c r="H2243" t="n">
         <v>8824041</v>
@@ -65445,7 +65445,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G2244" t="n">
-        <v>4.12566518783569</v>
+        <v>4.12566566467285</v>
       </c>
       <c r="H2244" t="n">
         <v>14098523</v>
@@ -65503,7 +65503,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G2246" t="n">
-        <v>4.09645128250122</v>
+        <v>4.09645080566406</v>
       </c>
       <c r="H2246" t="n">
         <v>9115898</v>
@@ -65561,7 +65561,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G2248" t="n">
-        <v>4.14838695526123</v>
+        <v>4.14838743209839</v>
       </c>
       <c r="H2248" t="n">
         <v>9089883</v>
@@ -65677,7 +65677,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G2252" t="n">
-        <v>4.13702583312988</v>
+        <v>4.13702630996704</v>
       </c>
       <c r="H2252" t="n">
         <v>8443415</v>
@@ -65764,7 +65764,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2255" t="n">
-        <v>4.22629165649414</v>
+        <v>4.22629117965698</v>
       </c>
       <c r="H2255" t="n">
         <v>19992634</v>
@@ -65880,7 +65880,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G2259" t="n">
-        <v>4.47623300552368</v>
+        <v>4.47623252868652</v>
       </c>
       <c r="H2259" t="n">
         <v>24618281</v>
@@ -65938,7 +65938,7 @@
         <v>6.01800012588501</v>
       </c>
       <c r="G2261" t="n">
-        <v>4.88360595703125</v>
+        <v>4.88360643386841</v>
       </c>
       <c r="H2261" t="n">
         <v>15163406</v>
@@ -66083,7 +66083,7 @@
         <v>5.93200016021729</v>
       </c>
       <c r="G2266" t="n">
-        <v>4.81381702423096</v>
+        <v>4.81381750106812</v>
       </c>
       <c r="H2266" t="n">
         <v>14209848</v>
@@ -66373,7 +66373,7 @@
         <v>6.37200021743774</v>
       </c>
       <c r="G2276" t="n">
-        <v>5.17087697982788</v>
+        <v>5.17087745666504</v>
       </c>
       <c r="H2276" t="n">
         <v>8697069</v>
@@ -66402,7 +66402,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2277" t="n">
-        <v>5.12867879867554</v>
+        <v>5.1286792755127</v>
       </c>
       <c r="H2277" t="n">
         <v>9776574</v>
@@ -66721,7 +66721,7 @@
         <v>6.65199995040894</v>
       </c>
       <c r="G2288" t="n">
-        <v>5.39809656143188</v>
+        <v>5.39809703826904</v>
       </c>
       <c r="H2288" t="n">
         <v>5442007</v>
@@ -66779,7 +66779,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2290" t="n">
-        <v>5.4451642036438</v>
+        <v>5.44516372680664</v>
       </c>
       <c r="H2290" t="n">
         <v>13302467</v>
@@ -66837,7 +66837,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2292" t="n">
-        <v>5.52631378173828</v>
+        <v>5.52631425857544</v>
       </c>
       <c r="H2292" t="n">
         <v>8534256</v>
@@ -66924,7 +66924,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2295" t="n">
-        <v>5.7113356590271</v>
+        <v>5.71133613586426</v>
       </c>
       <c r="H2295" t="n">
         <v>13899191</v>
@@ -67011,7 +67011,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2298" t="n">
-        <v>5.7113356590271</v>
+        <v>5.71133613586426</v>
       </c>
       <c r="H2298" t="n">
         <v>10737504</v>
@@ -67040,7 +67040,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2299" t="n">
-        <v>5.74217319488525</v>
+        <v>5.7421727180481</v>
       </c>
       <c r="H2299" t="n">
         <v>12020301</v>
@@ -67069,7 +67069,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2300" t="n">
-        <v>5.74217319488525</v>
+        <v>5.7421727180481</v>
       </c>
       <c r="H2300" t="n">
         <v>10188937</v>
@@ -67098,7 +67098,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G2301" t="n">
-        <v>5.71945095062256</v>
+        <v>5.7194504737854</v>
       </c>
       <c r="H2301" t="n">
         <v>9495869</v>
@@ -67272,7 +67272,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G2307" t="n">
-        <v>5.16276216506958</v>
+        <v>5.16276168823242</v>
       </c>
       <c r="H2307" t="n">
         <v>34036799</v>
@@ -67359,7 +67359,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G2310" t="n">
-        <v>5.05402135848999</v>
+        <v>5.05402088165283</v>
       </c>
       <c r="H2310" t="n">
         <v>20549379</v>
@@ -67417,7 +67417,7 @@
         <v>6.30200004577637</v>
       </c>
       <c r="G2312" t="n">
-        <v>5.11407232284546</v>
+        <v>5.1140718460083</v>
       </c>
       <c r="H2312" t="n">
         <v>15019935</v>
@@ -67620,7 +67620,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2319" t="n">
-        <v>5.12867879867554</v>
+        <v>5.1286792755127</v>
       </c>
       <c r="H2319" t="n">
         <v>15133688</v>
@@ -67852,7 +67852,7 @@
         <v>6.60799980163574</v>
       </c>
       <c r="G2327" t="n">
-        <v>5.36239099502563</v>
+        <v>5.36239051818848</v>
       </c>
       <c r="H2327" t="n">
         <v>26555901</v>
@@ -67910,7 +67910,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G2329" t="n">
-        <v>5.69835186004639</v>
+        <v>5.69835138320923</v>
       </c>
       <c r="H2329" t="n">
         <v>30197117</v>
@@ -67939,7 +67939,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G2330" t="n">
-        <v>5.69348287582397</v>
+        <v>5.69348239898682</v>
       </c>
       <c r="H2330" t="n">
         <v>20333854</v>
@@ -67997,7 +67997,7 @@
         <v>7.11800003051758</v>
       </c>
       <c r="G2332" t="n">
-        <v>5.77625560760498</v>
+        <v>5.77625608444214</v>
       </c>
       <c r="H2332" t="n">
         <v>25105102</v>
@@ -68142,7 +68142,7 @@
         <v>6.88800001144409</v>
       </c>
       <c r="G2337" t="n">
-        <v>5.58961057662964</v>
+        <v>5.5896110534668</v>
       </c>
       <c r="H2337" t="n">
         <v>31043675</v>
@@ -68229,7 +68229,7 @@
         <v>7.09600019454956</v>
       </c>
       <c r="G2340" t="n">
-        <v>5.75840330123901</v>
+        <v>5.75840282440186</v>
       </c>
       <c r="H2340" t="n">
         <v>18107631</v>
@@ -68345,7 +68345,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2344" t="n">
-        <v>6.34592914581299</v>
+        <v>6.34592866897583</v>
       </c>
       <c r="H2344" t="n">
         <v>26774763</v>
@@ -68403,7 +68403,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G2346" t="n">
-        <v>6.17064476013184</v>
+        <v>6.17064523696899</v>
       </c>
       <c r="H2346" t="n">
         <v>35553613</v>
@@ -68780,7 +68780,7 @@
         <v>5.89300012588501</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.78216886520386</v>
+        <v>4.7821683883667</v>
       </c>
       <c r="H2359" t="n">
         <v>19388932</v>
@@ -68809,7 +68809,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G2360" t="n">
-        <v>5.01020002365112</v>
+        <v>5.01019954681396</v>
       </c>
       <c r="H2360" t="n">
         <v>25575508</v>
@@ -68896,7 +68896,7 @@
         <v>6.67799997329712</v>
       </c>
       <c r="G2363" t="n">
-        <v>5.41919565200806</v>
+        <v>5.41919612884521</v>
       </c>
       <c r="H2363" t="n">
         <v>16423481</v>
@@ -68954,7 +68954,7 @@
         <v>6.53200006484985</v>
       </c>
       <c r="G2365" t="n">
-        <v>5.3007173538208</v>
+        <v>5.30071687698364</v>
       </c>
       <c r="H2365" t="n">
         <v>10138487</v>
@@ -68983,7 +68983,7 @@
         <v>6.50899982452393</v>
       </c>
       <c r="G2366" t="n">
-        <v>5.2820520401001</v>
+        <v>5.28205251693726</v>
       </c>
       <c r="H2366" t="n">
         <v>11026759</v>
@@ -69273,7 +69273,7 @@
         <v>7.48899984359741</v>
       </c>
       <c r="G2376" t="n">
-        <v>6.07732248306274</v>
+        <v>6.07732200622559</v>
       </c>
       <c r="H2376" t="n">
         <v>12569452</v>
@@ -69302,7 +69302,7 @@
         <v>7.68400001525879</v>
       </c>
       <c r="G2377" t="n">
-        <v>6.23556470870972</v>
+        <v>6.23556518554688</v>
       </c>
       <c r="H2377" t="n">
         <v>20468675</v>
@@ -69418,7 +69418,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2381" t="n">
-        <v>6.72733354568481</v>
+        <v>6.72733402252197</v>
       </c>
       <c r="H2381" t="n">
         <v>21907312</v>
@@ -69447,7 +69447,7 @@
         <v>8.14200019836426</v>
       </c>
       <c r="G2382" t="n">
-        <v>6.60723209381104</v>
+        <v>6.60723161697388</v>
       </c>
       <c r="H2382" t="n">
         <v>27889420</v>
@@ -69476,7 +69476,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G2383" t="n">
-        <v>6.55286073684692</v>
+        <v>6.55286121368408</v>
       </c>
       <c r="H2383" t="n">
         <v>25770231</v>
@@ -80096,6 +80096,35 @@
         <v>8176287</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>10.6920003890991</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>10.8859996795654</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>10.8739995956421</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>10.8739995956421</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>6625854</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2283.7373046875</v>
       </c>
       <c r="G4" t="n">
-        <v>1765.73571777344</v>
+        <v>1765.73583984375</v>
       </c>
       <c r="H4" t="n">
         <v>22853</v>
@@ -572,7 +572,7 @@
         <v>1928.46606445312</v>
       </c>
       <c r="G7" t="n">
-        <v>1491.04797363281</v>
+        <v>1491.0478515625</v>
       </c>
       <c r="H7" t="n">
         <v>58243</v>
@@ -630,7 +630,7 @@
         <v>1970.14013671875</v>
       </c>
       <c r="G9" t="n">
-        <v>1523.26940917969</v>
+        <v>1523.26928710938</v>
       </c>
       <c r="H9" t="n">
         <v>41776</v>
@@ -746,7 +746,7 @@
         <v>1365.86657714844</v>
       </c>
       <c r="G13" t="n">
-        <v>1056.05822753906</v>
+        <v>1056.05810546875</v>
       </c>
       <c r="H13" t="n">
         <v>75020</v>
@@ -775,7 +775,7 @@
         <v>1062.68798828125</v>
       </c>
       <c r="G14" t="n">
-        <v>821.647094726562</v>
+        <v>821.647155761719</v>
       </c>
       <c r="H14" t="n">
         <v>36638</v>
@@ -949,7 +949,7 @@
         <v>1364.82470703125</v>
       </c>
       <c r="G20" t="n">
-        <v>1055.25268554688</v>
+        <v>1055.25256347656</v>
       </c>
       <c r="H20" t="n">
         <v>48851</v>
@@ -1094,7 +1094,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.311462402344</v>
+        <v>918.3115234375</v>
       </c>
       <c r="H25" t="n">
         <v>64565</v>
@@ -1123,7 +1123,7 @@
         <v>1229.38415527344</v>
       </c>
       <c r="G26" t="n">
-        <v>950.532897949219</v>
+        <v>950.533020019531</v>
       </c>
       <c r="H26" t="n">
         <v>64029</v>
@@ -1210,7 +1210,7 @@
         <v>1119.98974609375</v>
       </c>
       <c r="G29" t="n">
-        <v>865.951599121094</v>
+        <v>865.95166015625</v>
       </c>
       <c r="H29" t="n">
         <v>60147</v>
@@ -1326,7 +1326,7 @@
         <v>1171.04040527344</v>
       </c>
       <c r="G33" t="n">
-        <v>905.422912597656</v>
+        <v>905.4228515625</v>
       </c>
       <c r="H33" t="n">
         <v>78116</v>
@@ -1355,7 +1355,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366882324219</v>
+        <v>926.366760253906</v>
       </c>
       <c r="H34" t="n">
         <v>65735</v>
@@ -1413,7 +1413,7 @@
         <v>1066.85534667969</v>
       </c>
       <c r="G36" t="n">
-        <v>824.869262695312</v>
+        <v>824.869323730469</v>
       </c>
       <c r="H36" t="n">
         <v>40227</v>
@@ -1442,7 +1442,7 @@
         <v>1115.82238769531</v>
       </c>
       <c r="G37" t="n">
-        <v>862.7294921875</v>
+        <v>862.729553222656</v>
       </c>
       <c r="H37" t="n">
         <v>36987</v>
@@ -1587,7 +1587,7 @@
         <v>1024.7646484375</v>
       </c>
       <c r="G42" t="n">
-        <v>792.32568359375</v>
+        <v>792.325622558594</v>
       </c>
       <c r="H42" t="n">
         <v>166009</v>
@@ -1703,7 +1703,7 @@
         <v>1167.91491699219</v>
       </c>
       <c r="G46" t="n">
-        <v>903.006286621094</v>
+        <v>903.00634765625</v>
       </c>
       <c r="H46" t="n">
         <v>46525</v>
@@ -1848,7 +1848,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977966308594</v>
+        <v>927.977905273438</v>
       </c>
       <c r="H51" t="n">
         <v>78651</v>
@@ -1877,7 +1877,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G52" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03125</v>
       </c>
       <c r="H52" t="n">
         <v>99090</v>
@@ -1906,7 +1906,7 @@
         <v>1243.96997070312</v>
       </c>
       <c r="G53" t="n">
-        <v>961.810485839844</v>
+        <v>961.810363769531</v>
       </c>
       <c r="H53" t="n">
         <v>82251</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254089355469</v>
+        <v>997.254211425781</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2138,7 +2138,7 @@
         <v>1121.03161621094</v>
       </c>
       <c r="G61" t="n">
-        <v>866.757141113281</v>
+        <v>866.757202148438</v>
       </c>
       <c r="H61" t="n">
         <v>44323</v>
@@ -2167,7 +2167,7 @@
         <v>1093.94348144531</v>
       </c>
       <c r="G62" t="n">
-        <v>845.813171386719</v>
+        <v>845.813232421875</v>
       </c>
       <c r="H62" t="n">
         <v>30190</v>
@@ -2196,7 +2196,7 @@
         <v>1048.10205078125</v>
       </c>
       <c r="G63" t="n">
-        <v>810.36962890625</v>
+        <v>810.369567871094</v>
       </c>
       <c r="H63" t="n">
         <v>77981</v>
@@ -2283,7 +2283,7 @@
         <v>962.670288085938</v>
       </c>
       <c r="G66" t="n">
-        <v>744.315673828125</v>
+        <v>744.315612792969</v>
       </c>
       <c r="H66" t="n">
         <v>36197</v>
@@ -2486,7 +2486,7 @@
         <v>1227.30041503906</v>
       </c>
       <c r="G73" t="n">
-        <v>948.921813964844</v>
+        <v>948.921875</v>
       </c>
       <c r="H73" t="n">
         <v>64701</v>
@@ -2544,7 +2544,7 @@
         <v>1354.40625</v>
       </c>
       <c r="G75" t="n">
-        <v>1047.197265625</v>
+        <v>1047.19738769531</v>
       </c>
       <c r="H75" t="n">
         <v>71166</v>
@@ -2573,7 +2573,7 @@
         <v>1323.15075683594</v>
       </c>
       <c r="G76" t="n">
-        <v>1023.03137207031</v>
+        <v>1023.03125</v>
       </c>
       <c r="H76" t="n">
         <v>87970</v>
@@ -2631,7 +2631,7 @@
         <v>1441.92175292969</v>
       </c>
       <c r="G78" t="n">
-        <v>1114.86242675781</v>
+        <v>1114.8623046875</v>
       </c>
       <c r="H78" t="n">
         <v>56991</v>
@@ -2921,7 +2921,7 @@
         <v>1318.98327636719</v>
       </c>
       <c r="G88" t="n">
-        <v>1019.80908203125</v>
+        <v>1019.80902099609</v>
       </c>
       <c r="H88" t="n">
         <v>45362</v>
@@ -3066,7 +3066,7 @@
         <v>1153.32897949219</v>
       </c>
       <c r="G93" t="n">
-        <v>891.728820800781</v>
+        <v>891.728759765625</v>
       </c>
       <c r="H93" t="n">
         <v>32662</v>
@@ -3095,7 +3095,7 @@
         <v>1168.95678710938</v>
       </c>
       <c r="G94" t="n">
-        <v>903.811889648438</v>
+        <v>903.811950683594</v>
       </c>
       <c r="H94" t="n">
         <v>30176</v>
@@ -3153,7 +3153,7 @@
         <v>1156.45458984375</v>
       </c>
       <c r="G96" t="n">
-        <v>894.1455078125</v>
+        <v>894.145446777344</v>
       </c>
       <c r="H96" t="n">
         <v>29015</v>
@@ -3240,7 +3240,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839538574219</v>
+        <v>907.839477539062</v>
       </c>
       <c r="H99" t="n">
         <v>19584</v>
@@ -3356,7 +3356,7 @@
         <v>1306.48107910156</v>
       </c>
       <c r="G103" t="n">
-        <v>1010.142578125</v>
+        <v>1010.14263916016</v>
       </c>
       <c r="H103" t="n">
         <v>21794</v>
@@ -3385,7 +3385,7 @@
         <v>1311.69030761719</v>
       </c>
       <c r="G104" t="n">
-        <v>1014.17028808594</v>
+        <v>1014.17034912109</v>
       </c>
       <c r="H104" t="n">
         <v>14276</v>
@@ -3646,7 +3646,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.143920898438</v>
+        <v>952.14404296875</v>
       </c>
       <c r="H113" t="n">
         <v>14885</v>
@@ -3675,7 +3675,7 @@
         <v>1151.24523925781</v>
       </c>
       <c r="G114" t="n">
-        <v>890.117614746094</v>
+        <v>890.11767578125</v>
       </c>
       <c r="H114" t="n">
         <v>28584</v>
@@ -3762,7 +3762,7 @@
         <v>1038.10021972656</v>
       </c>
       <c r="G117" t="n">
-        <v>802.636413574219</v>
+        <v>802.636474609375</v>
       </c>
       <c r="H117" t="n">
         <v>30134</v>
@@ -3849,7 +3849,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368286132812</v>
+        <v>868.368225097656</v>
       </c>
       <c r="H120" t="n">
         <v>32561</v>
@@ -3965,7 +3965,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749328613281</v>
+        <v>731.749267578125</v>
       </c>
       <c r="H124" t="n">
         <v>64325</v>
@@ -3994,7 +3994,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118225097656</v>
+        <v>634.118286132812</v>
       </c>
       <c r="H125" t="n">
         <v>71078</v>
@@ -4197,7 +4197,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194732666016</v>
+        <v>453.194763183594</v>
       </c>
       <c r="H132" t="n">
         <v>69237</v>
@@ -4284,7 +4284,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549591064453</v>
+        <v>481.549652099609</v>
       </c>
       <c r="H135" t="n">
         <v>39529</v>
@@ -4429,7 +4429,7 @@
         <v>696.164794921875</v>
       </c>
       <c r="G140" t="n">
-        <v>538.259460449219</v>
+        <v>538.259399414062</v>
       </c>
       <c r="H140" t="n">
         <v>34135</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710113525391</v>
+        <v>510.710052490234</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4690,7 +4690,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532653808594</v>
+        <v>496.532592773438</v>
       </c>
       <c r="H149" t="n">
         <v>46906</v>
@@ -4748,7 +4748,7 @@
         <v>541.970886230469</v>
       </c>
       <c r="G151" t="n">
-        <v>419.0400390625</v>
+        <v>419.040069580078</v>
       </c>
       <c r="H151" t="n">
         <v>45660</v>
@@ -4777,7 +4777,7 @@
         <v>551.764282226562</v>
       </c>
       <c r="G152" t="n">
-        <v>426.612091064453</v>
+        <v>426.612121582031</v>
       </c>
       <c r="H152" t="n">
         <v>35494</v>
@@ -4951,7 +4951,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384918212891</v>
+        <v>399.384948730469</v>
       </c>
       <c r="H158" t="n">
         <v>11284</v>
@@ -5009,7 +5009,7 @@
         <v>518.00830078125</v>
       </c>
       <c r="G160" t="n">
-        <v>400.5126953125</v>
+        <v>400.512725830078</v>
       </c>
       <c r="H160" t="n">
         <v>10381</v>
@@ -5067,7 +5067,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G162" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H162" t="n">
         <v>24713</v>
@@ -5299,7 +5299,7 @@
         <v>503.630737304688</v>
       </c>
       <c r="G170" t="n">
-        <v>389.396270751953</v>
+        <v>389.396301269531</v>
       </c>
       <c r="H170" t="n">
         <v>13936</v>
@@ -5415,7 +5415,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724212646484</v>
+        <v>384.724182128906</v>
       </c>
       <c r="H174" t="n">
         <v>11728</v>
@@ -5444,7 +5444,7 @@
         <v>489.669952392578</v>
       </c>
       <c r="G175" t="n">
-        <v>378.602081298828</v>
+        <v>378.602111816406</v>
       </c>
       <c r="H175" t="n">
         <v>11244</v>
@@ -5502,7 +5502,7 @@
         <v>509.465118408203</v>
       </c>
       <c r="G177" t="n">
-        <v>393.907287597656</v>
+        <v>393.907318115234</v>
       </c>
       <c r="H177" t="n">
         <v>26337</v>
@@ -5676,7 +5676,7 @@
         <v>420.907775878906</v>
       </c>
       <c r="G183" t="n">
-        <v>325.436737060547</v>
+        <v>325.436706542969</v>
       </c>
       <c r="H183" t="n">
         <v>78778</v>
@@ -5705,7 +5705,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G184" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H184" t="n">
         <v>24033</v>
@@ -5763,7 +5763,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003753662109</v>
+        <v>309.003784179688</v>
       </c>
       <c r="H186" t="n">
         <v>27102</v>
@@ -5879,7 +5879,7 @@
         <v>404.86328125</v>
       </c>
       <c r="G190" t="n">
-        <v>313.031433105469</v>
+        <v>313.031463623047</v>
       </c>
       <c r="H190" t="n">
         <v>26142</v>
@@ -5908,7 +5908,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742614746094</v>
+        <v>311.742584228516</v>
       </c>
       <c r="H191" t="n">
         <v>13716</v>
@@ -6024,7 +6024,7 @@
         <v>376.733306884766</v>
       </c>
       <c r="G195" t="n">
-        <v>291.281982421875</v>
+        <v>291.281951904297</v>
       </c>
       <c r="H195" t="n">
         <v>13255</v>
@@ -6053,7 +6053,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843322753906</v>
+        <v>279.843353271484</v>
       </c>
       <c r="H196" t="n">
         <v>54804</v>
@@ -6082,7 +6082,7 @@
         <v>349.853546142578</v>
       </c>
       <c r="G197" t="n">
-        <v>270.499145507812</v>
+        <v>270.499114990234</v>
       </c>
       <c r="H197" t="n">
         <v>45392</v>
@@ -6401,7 +6401,7 @@
         <v>563.641357421875</v>
       </c>
       <c r="G208" t="n">
-        <v>435.795196533203</v>
+        <v>435.795166015625</v>
       </c>
       <c r="H208" t="n">
         <v>168620</v>
@@ -6430,7 +6430,7 @@
         <v>723.044555664062</v>
       </c>
       <c r="G209" t="n">
-        <v>559.042297363281</v>
+        <v>559.042236328125</v>
       </c>
       <c r="H209" t="n">
         <v>206944</v>
@@ -6459,7 +6459,7 @@
         <v>614.692077636719</v>
       </c>
       <c r="G210" t="n">
-        <v>475.266448974609</v>
+        <v>475.266510009766</v>
       </c>
       <c r="H210" t="n">
         <v>166520</v>
@@ -6488,7 +6488,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184143066406</v>
+        <v>434.184112548828</v>
       </c>
       <c r="H211" t="n">
         <v>136414</v>
@@ -6546,7 +6546,7 @@
         <v>546.971740722656</v>
       </c>
       <c r="G213" t="n">
-        <v>422.906585693359</v>
+        <v>422.906616210938</v>
       </c>
       <c r="H213" t="n">
         <v>68253</v>
@@ -6662,7 +6662,7 @@
         <v>484.0439453125</v>
       </c>
       <c r="G217" t="n">
-        <v>374.252197265625</v>
+        <v>374.252227783203</v>
       </c>
       <c r="H217" t="n">
         <v>29696</v>
@@ -6720,7 +6720,7 @@
         <v>537.178344726562</v>
       </c>
       <c r="G219" t="n">
-        <v>415.334594726562</v>
+        <v>415.334564208984</v>
       </c>
       <c r="H219" t="n">
         <v>97389</v>
@@ -6749,7 +6749,7 @@
         <v>558.015380859375</v>
       </c>
       <c r="G220" t="n">
-        <v>431.4453125</v>
+        <v>431.445281982422</v>
       </c>
       <c r="H220" t="n">
         <v>158097</v>
@@ -6807,7 +6807,7 @@
         <v>537.595092773438</v>
       </c>
       <c r="G222" t="n">
-        <v>415.656799316406</v>
+        <v>415.656768798828</v>
       </c>
       <c r="H222" t="n">
         <v>116257</v>
@@ -6865,7 +6865,7 @@
         <v>583.228149414062</v>
       </c>
       <c r="G224" t="n">
-        <v>450.939239501953</v>
+        <v>450.939270019531</v>
       </c>
       <c r="H224" t="n">
         <v>123957</v>
@@ -7126,7 +7126,7 @@
         <v>416.740386962891</v>
       </c>
       <c r="G233" t="n">
-        <v>322.214538574219</v>
+        <v>322.214569091797</v>
       </c>
       <c r="H233" t="n">
         <v>63341</v>
@@ -7271,7 +7271,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H238" t="n">
         <v>56464</v>
@@ -7387,7 +7387,7 @@
         <v>454.246978759766</v>
       </c>
       <c r="G242" t="n">
-        <v>351.213836669922</v>
+        <v>351.2138671875</v>
       </c>
       <c r="H242" t="n">
         <v>104991</v>
@@ -7416,7 +7416,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.159149169922</v>
+        <v>314.1591796875</v>
       </c>
       <c r="H243" t="n">
         <v>108228</v>
@@ -13883,7 +13883,7 @@
         <v>94.8084259033203</v>
       </c>
       <c r="G466" t="n">
-        <v>73.3038101196289</v>
+        <v>73.3038024902344</v>
       </c>
       <c r="H466" t="n">
         <v>2488563</v>
@@ -13912,7 +13912,7 @@
         <v>98.5174179077148</v>
       </c>
       <c r="G467" t="n">
-        <v>76.1715087890625</v>
+        <v>76.171516418457</v>
       </c>
       <c r="H467" t="n">
         <v>616657</v>
@@ -13941,7 +13941,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003921508789</v>
+        <v>76.3003997802734</v>
       </c>
       <c r="H468" t="n">
         <v>232423</v>
@@ -13970,7 +13970,7 @@
         <v>97.3505477905273</v>
       </c>
       <c r="G469" t="n">
-        <v>75.2693176269531</v>
+        <v>75.2693099975586</v>
       </c>
       <c r="H469" t="n">
         <v>139388</v>
@@ -13999,7 +13999,7 @@
         <v>98.3507232666016</v>
       </c>
       <c r="G470" t="n">
-        <v>76.0426254272461</v>
+        <v>76.0426330566406</v>
       </c>
       <c r="H470" t="n">
         <v>149896</v>
@@ -14086,7 +14086,7 @@
         <v>95.4335403442383</v>
       </c>
       <c r="G473" t="n">
-        <v>73.7871246337891</v>
+        <v>73.7871322631836</v>
       </c>
       <c r="H473" t="n">
         <v>87104</v>
@@ -14347,7 +14347,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064865112305</v>
+        <v>53.9064903259277</v>
       </c>
       <c r="H482" t="n">
         <v>255815</v>
@@ -14405,7 +14405,7 @@
         <v>85.6401443481445</v>
       </c>
       <c r="G484" t="n">
-        <v>66.215087890625</v>
+        <v>66.2150955200195</v>
       </c>
       <c r="H484" t="n">
         <v>473567</v>
@@ -14434,7 +14434,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.1540451049805</v>
+        <v>63.154052734375</v>
       </c>
       <c r="H485" t="n">
         <v>461818</v>
@@ -14579,7 +14579,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906616210938</v>
+        <v>64.9906692504883</v>
       </c>
       <c r="H490" t="n">
         <v>123807</v>
@@ -14608,7 +14608,7 @@
         <v>83.9731826782227</v>
       </c>
       <c r="G491" t="n">
-        <v>64.9262313842773</v>
+        <v>64.9262390136719</v>
       </c>
       <c r="H491" t="n">
         <v>97304</v>
@@ -14637,7 +14637,7 @@
         <v>85.431770324707</v>
       </c>
       <c r="G492" t="n">
-        <v>66.0539855957031</v>
+        <v>66.0539779663086</v>
       </c>
       <c r="H492" t="n">
         <v>305053</v>
@@ -14695,7 +14695,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.1540451049805</v>
+        <v>63.154052734375</v>
       </c>
       <c r="H494" t="n">
         <v>82320</v>
@@ -14869,7 +14869,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618530273438</v>
+        <v>61.9618606567383</v>
       </c>
       <c r="H500" t="n">
         <v>52866</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.156322479248</v>
+        <v>61.1563148498535</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -15275,7 +15275,7 @@
         <v>81.5977630615234</v>
       </c>
       <c r="G514" t="n">
-        <v>63.0896034240723</v>
+        <v>63.0896110534668</v>
       </c>
       <c r="H514" t="n">
         <v>53122</v>
@@ -15507,7 +15507,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695938110352</v>
+        <v>63.6695861816406</v>
       </c>
       <c r="H522" t="n">
         <v>52551</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184867858887</v>
+        <v>63.2184944152832</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15884,7 +15884,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397117614746</v>
+        <v>58.7397079467773</v>
       </c>
       <c r="H535" t="n">
         <v>102598</v>
@@ -15913,7 +15913,7 @@
         <v>75.1591186523438</v>
       </c>
       <c r="G536" t="n">
-        <v>58.1113929748535</v>
+        <v>58.111385345459</v>
       </c>
       <c r="H536" t="n">
         <v>86581</v>
@@ -15942,7 +15942,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.0607833862305</v>
+        <v>60.060791015625</v>
       </c>
       <c r="H537" t="n">
         <v>142371</v>
@@ -16000,7 +16000,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.836368560791</v>
+        <v>58.8363761901855</v>
       </c>
       <c r="H539" t="n">
         <v>77063</v>
@@ -16203,7 +16203,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.46923828125</v>
+        <v>55.4692344665527</v>
       </c>
       <c r="H546" t="n">
         <v>24192</v>
@@ -16232,7 +16232,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.9536895751953</v>
+        <v>54.953685760498</v>
       </c>
       <c r="H547" t="n">
         <v>43186</v>
@@ -16261,7 +16261,7 @@
         <v>69.4706192016602</v>
       </c>
       <c r="G548" t="n">
-        <v>53.7131652832031</v>
+        <v>53.7131614685059</v>
       </c>
       <c r="H548" t="n">
         <v>52411</v>
@@ -16348,7 +16348,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.005428314209</v>
+        <v>52.0054321289062</v>
       </c>
       <c r="H551" t="n">
         <v>83287</v>
@@ -16435,7 +16435,7 @@
         <v>66.8451538085938</v>
       </c>
       <c r="G554" t="n">
-        <v>51.6832160949707</v>
+        <v>51.6832122802734</v>
       </c>
       <c r="H554" t="n">
         <v>49117</v>
@@ -17044,7 +17044,7 @@
         <v>52.4050979614258</v>
       </c>
       <c r="G575" t="n">
-        <v>40.5184745788574</v>
+        <v>40.5184783935547</v>
       </c>
       <c r="H575" t="n">
         <v>92688</v>
@@ -17073,7 +17073,7 @@
         <v>53.1969032287598</v>
       </c>
       <c r="G576" t="n">
-        <v>41.1306838989258</v>
+        <v>41.130687713623</v>
       </c>
       <c r="H576" t="n">
         <v>90811</v>
@@ -17131,7 +17131,7 @@
         <v>61.0524597167969</v>
       </c>
       <c r="G578" t="n">
-        <v>47.2044296264648</v>
+        <v>47.2044258117676</v>
       </c>
       <c r="H578" t="n">
         <v>397440</v>
@@ -17160,7 +17160,7 @@
         <v>58.9687576293945</v>
       </c>
       <c r="G579" t="n">
-        <v>45.5933570861816</v>
+        <v>45.5933532714844</v>
       </c>
       <c r="H579" t="n">
         <v>215665</v>
@@ -17189,7 +17189,7 @@
         <v>57.1351013183594</v>
       </c>
       <c r="G580" t="n">
-        <v>44.175609588623</v>
+        <v>44.1756134033203</v>
       </c>
       <c r="H580" t="n">
         <v>158204</v>
@@ -17276,7 +17276,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H583" t="n">
         <v>160680</v>
@@ -17421,7 +17421,7 @@
         <v>56.5933380126953</v>
       </c>
       <c r="G588" t="n">
-        <v>43.7567367553711</v>
+        <v>43.7567329406738</v>
       </c>
       <c r="H588" t="n">
         <v>57313</v>
@@ -17450,7 +17450,7 @@
         <v>56.1974334716797</v>
       </c>
       <c r="G589" t="n">
-        <v>43.4506301879883</v>
+        <v>43.450626373291</v>
       </c>
       <c r="H589" t="n">
         <v>63710</v>
@@ -17682,7 +17682,7 @@
         <v>54.780517578125</v>
       </c>
       <c r="G597" t="n">
-        <v>42.3550987243652</v>
+        <v>42.3551025390625</v>
       </c>
       <c r="H597" t="n">
         <v>77570</v>
@@ -17798,7 +17798,7 @@
         <v>56.676685333252</v>
       </c>
       <c r="G601" t="n">
-        <v>43.8211784362793</v>
+        <v>43.821174621582</v>
       </c>
       <c r="H601" t="n">
         <v>72323</v>
@@ -17856,7 +17856,7 @@
         <v>68.3454132080078</v>
       </c>
       <c r="G603" t="n">
-        <v>52.8431777954102</v>
+        <v>52.8431816101074</v>
       </c>
       <c r="H603" t="n">
         <v>634116</v>
@@ -17972,7 +17972,7 @@
         <v>58.7603874206543</v>
       </c>
       <c r="G607" t="n">
-        <v>45.4322471618652</v>
+        <v>45.4322509765625</v>
       </c>
       <c r="H607" t="n">
         <v>352792</v>
@@ -18001,7 +18001,7 @@
         <v>59.0312690734863</v>
       </c>
       <c r="G608" t="n">
-        <v>45.6416893005371</v>
+        <v>45.6416854858398</v>
       </c>
       <c r="H608" t="n">
         <v>166866</v>
@@ -18030,7 +18030,7 @@
         <v>58.6145286560059</v>
       </c>
       <c r="G609" t="n">
-        <v>45.3194770812988</v>
+        <v>45.3194732666016</v>
       </c>
       <c r="H609" t="n">
         <v>202532</v>
@@ -18233,7 +18233,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H616" t="n">
         <v>281053</v>
@@ -18407,7 +18407,7 @@
         <v>55.9057159423828</v>
       </c>
       <c r="G622" t="n">
-        <v>43.2250747680664</v>
+        <v>43.2250785827637</v>
       </c>
       <c r="H622" t="n">
         <v>51718</v>
@@ -18436,7 +18436,7 @@
         <v>57.9269065856934</v>
       </c>
       <c r="G623" t="n">
-        <v>44.7878189086914</v>
+        <v>44.7878227233887</v>
       </c>
       <c r="H623" t="n">
         <v>250852</v>
@@ -18639,7 +18639,7 @@
         <v>56.6975250244141</v>
       </c>
       <c r="G630" t="n">
-        <v>43.837287902832</v>
+        <v>43.8372917175293</v>
       </c>
       <c r="H630" t="n">
         <v>35877</v>
@@ -18668,7 +18668,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767501831055</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H631" t="n">
         <v>46391</v>
@@ -18755,7 +18755,7 @@
         <v>53.1135559082031</v>
       </c>
       <c r="G634" t="n">
-        <v>41.0662422180176</v>
+        <v>41.0662460327148</v>
       </c>
       <c r="H634" t="n">
         <v>54253</v>
@@ -18813,7 +18813,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.3734817504883</v>
+        <v>40.373477935791</v>
       </c>
       <c r="H636" t="n">
         <v>90143</v>
@@ -18929,7 +18929,7 @@
         <v>51.1757125854492</v>
       </c>
       <c r="G640" t="n">
-        <v>39.5679397583008</v>
+        <v>39.567943572998</v>
       </c>
       <c r="H640" t="n">
         <v>70245</v>
@@ -18958,7 +18958,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062690734863</v>
+        <v>39.9062728881836</v>
       </c>
       <c r="H641" t="n">
         <v>47114</v>
@@ -18987,7 +18987,7 @@
         <v>51.0715293884277</v>
       </c>
       <c r="G642" t="n">
-        <v>39.4873924255371</v>
+        <v>39.4873886108398</v>
       </c>
       <c r="H642" t="n">
         <v>48431</v>
@@ -19045,7 +19045,7 @@
         <v>51.1965522766113</v>
       </c>
       <c r="G644" t="n">
-        <v>39.584056854248</v>
+        <v>39.5840606689453</v>
       </c>
       <c r="H644" t="n">
         <v>56401</v>
@@ -19393,7 +19393,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G656" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H656" t="n">
         <v>39162</v>
@@ -19538,7 +19538,7 @@
         <v>51.5299453735352</v>
       </c>
       <c r="G661" t="n">
-        <v>39.8418273925781</v>
+        <v>39.8418312072754</v>
       </c>
       <c r="H661" t="n">
         <v>115915</v>
@@ -19683,7 +19683,7 @@
         <v>49.5921020507812</v>
       </c>
       <c r="G666" t="n">
-        <v>38.3435325622559</v>
+        <v>38.3435287475586</v>
       </c>
       <c r="H666" t="n">
         <v>29704</v>
@@ -19741,7 +19741,7 @@
         <v>46.3415260314941</v>
       </c>
       <c r="G668" t="n">
-        <v>35.8302574157715</v>
+        <v>35.8302536010742</v>
       </c>
       <c r="H668" t="n">
         <v>138277</v>
@@ -19944,7 +19944,7 @@
         <v>45.570556640625</v>
       </c>
       <c r="G675" t="n">
-        <v>35.2341575622559</v>
+        <v>35.2341613769531</v>
       </c>
       <c r="H675" t="n">
         <v>20036</v>
@@ -20089,7 +20089,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580749511719</v>
+        <v>34.0580787658691</v>
       </c>
       <c r="H680" t="n">
         <v>49600</v>
@@ -20379,7 +20379,7 @@
         <v>47.1958427429199</v>
       </c>
       <c r="G690" t="n">
-        <v>36.490795135498</v>
+        <v>36.4907989501953</v>
       </c>
       <c r="H690" t="n">
         <v>97677</v>
@@ -20437,7 +20437,7 @@
         <v>48.5085754394531</v>
       </c>
       <c r="G692" t="n">
-        <v>37.5057678222656</v>
+        <v>37.5057716369629</v>
       </c>
       <c r="H692" t="n">
         <v>93100</v>
@@ -20611,7 +20611,7 @@
         <v>49.7379608154297</v>
       </c>
       <c r="G698" t="n">
-        <v>38.4563026428223</v>
+        <v>38.4563064575195</v>
       </c>
       <c r="H698" t="n">
         <v>127098</v>
@@ -20669,7 +20669,7 @@
         <v>49.1753616333008</v>
       </c>
       <c r="G700" t="n">
-        <v>38.021312713623</v>
+        <v>38.0213165283203</v>
       </c>
       <c r="H700" t="n">
         <v>69415</v>
@@ -20959,7 +20959,7 @@
         <v>37.0377998352051</v>
       </c>
       <c r="G710" t="n">
-        <v>28.6368198394775</v>
+        <v>28.6368179321289</v>
       </c>
       <c r="H710" t="n">
         <v>115092</v>
@@ -21017,7 +21017,7 @@
         <v>36.9752883911133</v>
       </c>
       <c r="G712" t="n">
-        <v>28.5884838104248</v>
+        <v>28.5884857177734</v>
       </c>
       <c r="H712" t="n">
         <v>79946</v>
@@ -21046,7 +21046,7 @@
         <v>36.089714050293</v>
       </c>
       <c r="G713" t="n">
-        <v>27.9037780761719</v>
+        <v>27.9037799835205</v>
       </c>
       <c r="H713" t="n">
         <v>152219</v>
@@ -21104,7 +21104,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532432556152</v>
+        <v>26.9532451629639</v>
       </c>
       <c r="H715" t="n">
         <v>100245</v>
@@ -21133,7 +21133,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241111755371</v>
+        <v>25.6241130828857</v>
       </c>
       <c r="H716" t="n">
         <v>204453</v>
@@ -21191,7 +21191,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H718" t="n">
         <v>180004</v>
@@ -21220,7 +21220,7 @@
         <v>28.5467128753662</v>
       </c>
       <c r="G719" t="n">
-        <v>22.0716953277588</v>
+        <v>22.0716972351074</v>
       </c>
       <c r="H719" t="n">
         <v>144762</v>
@@ -21249,7 +21249,7 @@
         <v>29.2864265441895</v>
       </c>
       <c r="G720" t="n">
-        <v>22.6436252593994</v>
+        <v>22.6436233520508</v>
       </c>
       <c r="H720" t="n">
         <v>183232</v>
@@ -21278,7 +21278,7 @@
         <v>29.5260524749756</v>
       </c>
       <c r="G721" t="n">
-        <v>22.8288993835449</v>
+        <v>22.8288974761963</v>
       </c>
       <c r="H721" t="n">
         <v>167797</v>
@@ -21597,7 +21597,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177558898926</v>
+        <v>24.1177577972412</v>
       </c>
       <c r="H732" t="n">
         <v>82427</v>
@@ -21713,7 +21713,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G736" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H736" t="n">
         <v>72375</v>
@@ -21829,7 +21829,7 @@
         <v>28.8071765899658</v>
       </c>
       <c r="G740" t="n">
-        <v>22.273078918457</v>
+        <v>22.2730808258057</v>
       </c>
       <c r="H740" t="n">
         <v>68762</v>
@@ -21887,7 +21887,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G742" t="n">
-        <v>24.8105182647705</v>
+        <v>24.8105163574219</v>
       </c>
       <c r="H742" t="n">
         <v>190080</v>
@@ -21916,7 +21916,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H743" t="n">
         <v>69577</v>
@@ -22032,7 +22032,7 @@
         <v>36.7564964294434</v>
       </c>
       <c r="G747" t="n">
-        <v>28.4193210601807</v>
+        <v>28.419319152832</v>
       </c>
       <c r="H747" t="n">
         <v>286148</v>
@@ -22090,7 +22090,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782283782959</v>
+        <v>27.6782302856445</v>
       </c>
       <c r="H749" t="n">
         <v>99834</v>
@@ -22148,7 +22148,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363185882568</v>
+        <v>26.2363166809082</v>
       </c>
       <c r="H751" t="n">
         <v>69130</v>
@@ -22235,7 +22235,7 @@
         <v>33.0058364868164</v>
       </c>
       <c r="G754" t="n">
-        <v>25.5193939208984</v>
+        <v>25.5193920135498</v>
       </c>
       <c r="H754" t="n">
         <v>87590</v>
@@ -22293,7 +22293,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G756" t="n">
-        <v>24.8105182647705</v>
+        <v>24.8105163574219</v>
       </c>
       <c r="H756" t="n">
         <v>41000</v>
@@ -22322,7 +22322,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H757" t="n">
         <v>41825</v>
@@ -22351,7 +22351,7 @@
         <v>31.2971992492676</v>
       </c>
       <c r="G758" t="n">
-        <v>24.1983127593994</v>
+        <v>24.1983108520508</v>
       </c>
       <c r="H758" t="n">
         <v>28653</v>
@@ -22438,7 +22438,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G761" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H761" t="n">
         <v>113781</v>
@@ -22583,7 +22583,7 @@
         <v>31.6097545623779</v>
       </c>
       <c r="G766" t="n">
-        <v>24.4399700164795</v>
+        <v>24.4399719238281</v>
       </c>
       <c r="H766" t="n">
         <v>84803</v>
@@ -22757,7 +22757,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058681488037</v>
+        <v>21.8058700561523</v>
       </c>
       <c r="H772" t="n">
         <v>398596</v>
@@ -22902,7 +22902,7 @@
         <v>25.4107418060303</v>
       </c>
       <c r="G777" t="n">
-        <v>19.6470317840576</v>
+        <v>19.647029876709</v>
       </c>
       <c r="H777" t="n">
         <v>103123</v>
@@ -22989,7 +22989,7 @@
         <v>25.598274230957</v>
       </c>
       <c r="G780" t="n">
-        <v>19.7920265197754</v>
+        <v>19.792028427124</v>
       </c>
       <c r="H780" t="n">
         <v>186608</v>
@@ -23047,7 +23047,7 @@
         <v>26.1504554748535</v>
       </c>
       <c r="G782" t="n">
-        <v>20.2189617156982</v>
+        <v>20.2189598083496</v>
       </c>
       <c r="H782" t="n">
         <v>91503</v>
@@ -23134,7 +23134,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G785" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H785" t="n">
         <v>94288</v>
@@ -23192,7 +23192,7 @@
         <v>24.9523277282715</v>
       </c>
       <c r="G787" t="n">
-        <v>19.292594909668</v>
+        <v>19.2925930023193</v>
       </c>
       <c r="H787" t="n">
         <v>67521</v>
@@ -23366,7 +23366,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H793" t="n">
         <v>765447</v>
@@ -23598,7 +23598,7 @@
         <v>26.6609630584717</v>
       </c>
       <c r="G801" t="n">
-        <v>20.6136722564697</v>
+        <v>20.6136741638184</v>
       </c>
       <c r="H801" t="n">
         <v>58055</v>
@@ -23801,7 +23801,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H808" t="n">
         <v>86623</v>
@@ -24091,7 +24091,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G818" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H818" t="n">
         <v>142172</v>
@@ -24207,7 +24207,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H822" t="n">
         <v>72133</v>
@@ -24613,7 +24613,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H836" t="n">
         <v>263799</v>
@@ -24700,7 +24700,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G839" t="n">
-        <v>22.4583530426025</v>
+        <v>22.4583549499512</v>
       </c>
       <c r="H839" t="n">
         <v>174253</v>
@@ -24787,7 +24787,7 @@
         <v>27.671558380127</v>
       </c>
       <c r="G842" t="n">
-        <v>21.3950443267822</v>
+        <v>21.3950462341309</v>
       </c>
       <c r="H842" t="n">
         <v>78494</v>
@@ -25019,7 +25019,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150596618652</v>
+        <v>20.8150577545166</v>
       </c>
       <c r="H850" t="n">
         <v>79359</v>
@@ -25077,7 +25077,7 @@
         <v>25.4003238677979</v>
       </c>
       <c r="G852" t="n">
-        <v>19.6389751434326</v>
+        <v>19.6389770507812</v>
       </c>
       <c r="H852" t="n">
         <v>205905</v>
@@ -25193,7 +25193,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G856" t="n">
-        <v>18.6723327636719</v>
+        <v>18.6723308563232</v>
       </c>
       <c r="H856" t="n">
         <v>103442</v>
@@ -25251,7 +25251,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G858" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H858" t="n">
         <v>84494</v>
@@ -25309,7 +25309,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G860" t="n">
-        <v>18.4145584106445</v>
+        <v>18.4145603179932</v>
       </c>
       <c r="H860" t="n">
         <v>61245</v>
@@ -25338,7 +25338,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G861" t="n">
-        <v>18.1245670318604</v>
+        <v>18.124568939209</v>
       </c>
       <c r="H861" t="n">
         <v>98341</v>
@@ -25367,7 +25367,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H862" t="n">
         <v>131429</v>
@@ -25425,7 +25425,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G864" t="n">
-        <v>17.7701320648193</v>
+        <v>17.770133972168</v>
       </c>
       <c r="H864" t="n">
         <v>36909</v>
@@ -25483,7 +25483,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G866" t="n">
-        <v>17.1418132781982</v>
+        <v>17.1418113708496</v>
       </c>
       <c r="H866" t="n">
         <v>41924</v>
@@ -25541,7 +25541,7 @@
         <v>21.7538452148438</v>
       </c>
       <c r="G868" t="n">
-        <v>16.8195991516113</v>
+        <v>16.8195972442627</v>
       </c>
       <c r="H868" t="n">
         <v>75682</v>
@@ -25599,7 +25599,7 @@
         <v>21.6079864501953</v>
       </c>
       <c r="G870" t="n">
-        <v>16.706823348999</v>
+        <v>16.7068252563477</v>
       </c>
       <c r="H870" t="n">
         <v>102649</v>
@@ -25744,7 +25744,7 @@
         <v>21.5871505737305</v>
       </c>
       <c r="G875" t="n">
-        <v>16.6907119750977</v>
+        <v>16.6907138824463</v>
       </c>
       <c r="H875" t="n">
         <v>61152</v>
@@ -25802,7 +25802,7 @@
         <v>21.3579425811768</v>
       </c>
       <c r="G877" t="n">
-        <v>16.5134963989258</v>
+        <v>16.5134944915771</v>
       </c>
       <c r="H877" t="n">
         <v>48820</v>
@@ -25860,7 +25860,7 @@
         <v>20.8370170593262</v>
       </c>
       <c r="G879" t="n">
-        <v>16.110725402832</v>
+        <v>16.1107273101807</v>
       </c>
       <c r="H879" t="n">
         <v>44522</v>
@@ -26005,7 +26005,7 @@
         <v>21.9205417633057</v>
       </c>
       <c r="G884" t="n">
-        <v>16.9484844207764</v>
+        <v>16.9484825134277</v>
       </c>
       <c r="H884" t="n">
         <v>58458</v>
@@ -26063,7 +26063,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290374755859</v>
+        <v>17.0290393829346</v>
       </c>
       <c r="H886" t="n">
         <v>60342</v>
@@ -26150,7 +26150,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406784057617</v>
+        <v>18.1406764984131</v>
       </c>
       <c r="H889" t="n">
         <v>284480</v>
@@ -26179,7 +26179,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G890" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H890" t="n">
         <v>95871</v>
@@ -26295,7 +26295,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G894" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H894" t="n">
         <v>1152937</v>
@@ -26382,7 +26382,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493412017822</v>
+        <v>27.5493431091309</v>
       </c>
       <c r="H897" t="n">
         <v>754780</v>
@@ -26440,7 +26440,7 @@
         <v>33.1516952514648</v>
       </c>
       <c r="G899" t="n">
-        <v>25.6321659088135</v>
+        <v>25.6321678161621</v>
       </c>
       <c r="H899" t="n">
         <v>451580</v>
@@ -26469,7 +26469,7 @@
         <v>34.4435882568359</v>
       </c>
       <c r="G900" t="n">
-        <v>26.6310291290283</v>
+        <v>26.631031036377</v>
       </c>
       <c r="H900" t="n">
         <v>494613</v>
@@ -26614,7 +26614,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G905" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H905" t="n">
         <v>121784</v>
@@ -26643,7 +26643,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G906" t="n">
-        <v>23.8922080993652</v>
+        <v>23.8922061920166</v>
       </c>
       <c r="H906" t="n">
         <v>165007</v>
@@ -26788,7 +26788,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G911" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H911" t="n">
         <v>124106</v>
@@ -27107,7 +27107,7 @@
         <v>28.338342666626</v>
       </c>
       <c r="G922" t="n">
-        <v>21.9105892181396</v>
+        <v>21.910587310791</v>
       </c>
       <c r="H922" t="n">
         <v>183228</v>
@@ -27136,7 +27136,7 @@
         <v>28.7134094238281</v>
       </c>
       <c r="G923" t="n">
-        <v>22.2005825042725</v>
+        <v>22.2005805969238</v>
       </c>
       <c r="H923" t="n">
         <v>187583</v>
@@ -27455,7 +27455,7 @@
         <v>33.089183807373</v>
       </c>
       <c r="G934" t="n">
-        <v>25.5838356018066</v>
+        <v>25.583833694458</v>
       </c>
       <c r="H934" t="n">
         <v>517926</v>
@@ -27513,7 +27513,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G936" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H936" t="n">
         <v>340303</v>
@@ -27542,7 +27542,7 @@
         <v>33.0475082397461</v>
       </c>
       <c r="G937" t="n">
-        <v>25.5516128540039</v>
+        <v>25.5516109466553</v>
       </c>
       <c r="H937" t="n">
         <v>279125</v>
@@ -27571,7 +27571,7 @@
         <v>33.4225769042969</v>
       </c>
       <c r="G938" t="n">
-        <v>25.8416080474854</v>
+        <v>25.8416061401367</v>
       </c>
       <c r="H938" t="n">
         <v>128698</v>
@@ -27600,7 +27600,7 @@
         <v>33.4850845336914</v>
       </c>
       <c r="G939" t="n">
-        <v>25.8899364471436</v>
+        <v>25.8899345397949</v>
       </c>
       <c r="H939" t="n">
         <v>202392</v>
@@ -27687,7 +27687,7 @@
         <v>34.0268478393555</v>
       </c>
       <c r="G942" t="n">
-        <v>26.3088150024414</v>
+        <v>26.30881690979</v>
       </c>
       <c r="H942" t="n">
         <v>282982</v>
@@ -27803,7 +27803,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G946" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H946" t="n">
         <v>289611</v>
@@ -27832,7 +27832,7 @@
         <v>33.7559661865234</v>
       </c>
       <c r="G947" t="n">
-        <v>26.0993747711182</v>
+        <v>26.0993766784668</v>
       </c>
       <c r="H947" t="n">
         <v>135438</v>
@@ -27861,7 +27861,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G948" t="n">
-        <v>25.0360698699951</v>
+        <v>25.0360717773438</v>
       </c>
       <c r="H948" t="n">
         <v>171000</v>
@@ -27919,7 +27919,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G950" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H950" t="n">
         <v>295808</v>
@@ -27948,7 +27948,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G951" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H951" t="n">
         <v>107978</v>
@@ -28093,7 +28093,7 @@
         <v>30.5262298583984</v>
       </c>
       <c r="G956" t="n">
-        <v>23.6022148132324</v>
+        <v>23.6022129058838</v>
       </c>
       <c r="H956" t="n">
         <v>76872</v>
@@ -28151,7 +28151,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727630615234</v>
       </c>
       <c r="H958" t="n">
         <v>106089</v>
@@ -28267,7 +28267,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G962" t="n">
-        <v>23.8922080993652</v>
+        <v>23.8922061920166</v>
       </c>
       <c r="H962" t="n">
         <v>158871</v>
@@ -28325,7 +28325,7 @@
         <v>30.8596210479736</v>
       </c>
       <c r="G964" t="n">
-        <v>23.8599853515625</v>
+        <v>23.8599834442139</v>
       </c>
       <c r="H964" t="n">
         <v>96752</v>
@@ -28441,7 +28441,7 @@
         <v>31.9431476593018</v>
       </c>
       <c r="G968" t="n">
-        <v>24.6977424621582</v>
+        <v>24.6977443695068</v>
       </c>
       <c r="H968" t="n">
         <v>117112</v>
@@ -28586,7 +28586,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G973" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H973" t="n">
         <v>61466</v>
@@ -28644,7 +28644,7 @@
         <v>30.1511631011963</v>
       </c>
       <c r="G975" t="n">
-        <v>23.312219619751</v>
+        <v>23.3122215270996</v>
       </c>
       <c r="H975" t="n">
         <v>121812</v>
@@ -28789,7 +28789,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G980" t="n">
-        <v>24.4883060455322</v>
+        <v>24.4883041381836</v>
       </c>
       <c r="H980" t="n">
         <v>552266</v>
@@ -28818,7 +28818,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.4077491760254</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H981" t="n">
         <v>162326</v>
@@ -28992,7 +28992,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H987" t="n">
         <v>52930</v>
@@ -29050,7 +29050,7 @@
         <v>30.4428825378418</v>
       </c>
       <c r="G989" t="n">
-        <v>23.5377731323242</v>
+        <v>23.5377712249756</v>
       </c>
       <c r="H989" t="n">
         <v>96270</v>
@@ -29108,7 +29108,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H991" t="n">
         <v>68666</v>
@@ -29224,7 +29224,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727611541748</v>
+        <v>23.9727630615234</v>
       </c>
       <c r="H995" t="n">
         <v>242944</v>
@@ -29253,7 +29253,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G996" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H996" t="n">
         <v>84268</v>
@@ -29282,7 +29282,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H997" t="n">
         <v>75104</v>
@@ -29311,7 +29311,7 @@
         <v>29.8177719116211</v>
       </c>
       <c r="G998" t="n">
-        <v>23.0544490814209</v>
+        <v>23.0544509887695</v>
       </c>
       <c r="H998" t="n">
         <v>173291</v>
@@ -29340,7 +29340,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G999" t="n">
-        <v>22.7483444213867</v>
+        <v>22.7483463287354</v>
       </c>
       <c r="H999" t="n">
         <v>85330</v>
@@ -29514,7 +29514,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1005" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1005" t="n">
         <v>82787</v>
@@ -29572,7 +29572,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1007" t="n">
-        <v>22.7966785430908</v>
+        <v>22.7966766357422</v>
       </c>
       <c r="H1007" t="n">
         <v>90007</v>
@@ -29630,7 +29630,7 @@
         <v>29.0676383972168</v>
       </c>
       <c r="G1009" t="n">
-        <v>22.4744644165039</v>
+        <v>22.4744625091553</v>
       </c>
       <c r="H1009" t="n">
         <v>71916</v>
@@ -29688,7 +29688,7 @@
         <v>28.6925716400146</v>
       </c>
       <c r="G1011" t="n">
-        <v>22.1844711303711</v>
+        <v>22.1844692230225</v>
       </c>
       <c r="H1011" t="n">
         <v>138206</v>
@@ -29833,7 +29833,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G1016" t="n">
-        <v>22.7483444213867</v>
+        <v>22.7483463287354</v>
       </c>
       <c r="H1016" t="n">
         <v>115421</v>
@@ -29862,7 +29862,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G1017" t="n">
-        <v>22.4583530426025</v>
+        <v>22.4583549499512</v>
       </c>
       <c r="H1017" t="n">
         <v>91048</v>
@@ -29949,7 +29949,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1020" t="n">
-        <v>22.7966785430908</v>
+        <v>22.7966766357422</v>
       </c>
       <c r="H1020" t="n">
         <v>127518</v>
@@ -30007,7 +30007,7 @@
         <v>35.8396682739258</v>
       </c>
       <c r="G1022" t="n">
-        <v>27.7104473114014</v>
+        <v>27.71044921875</v>
       </c>
       <c r="H1022" t="n">
         <v>1331456</v>
@@ -30065,7 +30065,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493412017822</v>
+        <v>27.5493431091309</v>
       </c>
       <c r="H1024" t="n">
         <v>809390</v>
@@ -30094,7 +30094,7 @@
         <v>35.027027130127</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.0821304321289</v>
+        <v>27.0821323394775</v>
       </c>
       <c r="H1025" t="n">
         <v>329331</v>
@@ -30181,7 +30181,7 @@
         <v>35.7146453857422</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.6137828826904</v>
+        <v>27.6137847900391</v>
       </c>
       <c r="H1028" t="n">
         <v>133385</v>
@@ -30297,7 +30297,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1032" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1032" t="n">
         <v>254966</v>
@@ -30326,7 +30326,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.627628326416</v>
+        <v>29.6276245117188</v>
       </c>
       <c r="H1033" t="n">
         <v>422202</v>
@@ -30413,7 +30413,7 @@
         <v>36.2564086914062</v>
       </c>
       <c r="G1036" t="n">
-        <v>28.0326614379883</v>
+        <v>28.0326633453369</v>
       </c>
       <c r="H1036" t="n">
         <v>264193</v>
@@ -30529,7 +30529,7 @@
         <v>37.1940765380859</v>
       </c>
       <c r="G1040" t="n">
-        <v>28.7576484680176</v>
+        <v>28.7576465606689</v>
       </c>
       <c r="H1040" t="n">
         <v>194824</v>
@@ -30587,7 +30587,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1042" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1042" t="n">
         <v>912645</v>
@@ -30645,7 +30645,7 @@
         <v>37.2982597351074</v>
       </c>
       <c r="G1044" t="n">
-        <v>28.8381996154785</v>
+        <v>28.8382015228271</v>
       </c>
       <c r="H1044" t="n">
         <v>248431</v>
@@ -30732,7 +30732,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737560272217</v>
+        <v>28.7737598419189</v>
       </c>
       <c r="H1047" t="n">
         <v>145626</v>
@@ -30819,7 +30819,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936332702637</v>
+        <v>33.9936370849609</v>
       </c>
       <c r="H1050" t="n">
         <v>1453453</v>
@@ -30877,7 +30877,7 @@
         <v>42.5075149536133</v>
       </c>
       <c r="G1052" t="n">
-        <v>32.8658790588379</v>
+        <v>32.8658828735352</v>
       </c>
       <c r="H1052" t="n">
         <v>937883</v>
@@ -30935,7 +30935,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820652008057</v>
+        <v>29.9820613861084</v>
       </c>
       <c r="H1054" t="n">
         <v>787822</v>
@@ -30964,7 +30964,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770225524902</v>
+        <v>31.5770263671875</v>
       </c>
       <c r="H1055" t="n">
         <v>622084</v>
@@ -31080,7 +31080,7 @@
         <v>34.0893592834473</v>
       </c>
       <c r="G1059" t="n">
-        <v>26.3571472167969</v>
+        <v>26.3571491241455</v>
       </c>
       <c r="H1059" t="n">
         <v>364508</v>
@@ -31109,7 +31109,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610492706299</v>
+        <v>25.7610511779785</v>
       </c>
       <c r="H1060" t="n">
         <v>600964</v>
@@ -31312,7 +31312,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1067" t="n">
         <v>602051</v>
@@ -31428,7 +31428,7 @@
         <v>21.3787784576416</v>
       </c>
       <c r="G1071" t="n">
-        <v>16.5296039581299</v>
+        <v>16.5296058654785</v>
       </c>
       <c r="H1071" t="n">
         <v>217076</v>
@@ -31457,7 +31457,7 @@
         <v>20.7953433990479</v>
       </c>
       <c r="G1072" t="n">
-        <v>16.0785045623779</v>
+        <v>16.0785064697266</v>
       </c>
       <c r="H1072" t="n">
         <v>293641</v>
@@ -31515,7 +31515,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1074" t="n">
         <v>278986</v>
@@ -31573,7 +31573,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1076" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1076" t="n">
         <v>255584</v>
@@ -31602,7 +31602,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.8023529052734</v>
+        <v>17.8023548126221</v>
       </c>
       <c r="H1077" t="n">
         <v>235697</v>
@@ -31747,7 +31747,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1082" t="n">
         <v>65084</v>
@@ -31805,7 +31805,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1084" t="n">
         <v>220735</v>
@@ -31863,7 +31863,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1086" t="n">
         <v>126056</v>
@@ -32124,7 +32124,7 @@
         <v>22.3164443969727</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.2545890808105</v>
+        <v>17.2545871734619</v>
       </c>
       <c r="H1095" t="n">
         <v>75023</v>
@@ -32211,7 +32211,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.1245670318604</v>
+        <v>18.124568939209</v>
       </c>
       <c r="H1098" t="n">
         <v>194444</v>
@@ -32298,7 +32298,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1101" t="n">
         <v>70876</v>
@@ -32327,7 +32327,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1102" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1102" t="n">
         <v>32012</v>
@@ -32443,7 +32443,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G1106" t="n">
-        <v>17.7701320648193</v>
+        <v>17.770133972168</v>
       </c>
       <c r="H1106" t="n">
         <v>26540</v>
@@ -32704,7 +32704,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1115" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1115" t="n">
         <v>101008</v>
@@ -32878,7 +32878,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1121" t="n">
         <v>244265</v>
@@ -32907,7 +32907,7 @@
         <v>28.6717357635498</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.1683616638184</v>
+        <v>22.1683597564697</v>
       </c>
       <c r="H1122" t="n">
         <v>393290</v>
@@ -32965,7 +32965,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G1124" t="n">
-        <v>24.0049819946289</v>
+        <v>24.0049839019775</v>
       </c>
       <c r="H1124" t="n">
         <v>528373</v>
@@ -32994,7 +32994,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G1125" t="n">
-        <v>25.0360698699951</v>
+        <v>25.0360717773438</v>
       </c>
       <c r="H1125" t="n">
         <v>445464</v>
@@ -33023,7 +33023,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1126" t="n">
         <v>401649</v>
@@ -33197,7 +33197,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633209228516</v>
+        <v>23.7633228302002</v>
       </c>
       <c r="H1132" t="n">
         <v>117120</v>
@@ -33371,7 +33371,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021457672119</v>
+        <v>26.5021438598633</v>
       </c>
       <c r="H1138" t="n">
         <v>299299</v>
@@ -33400,7 +33400,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.229398727417</v>
+        <v>25.2293968200684</v>
       </c>
       <c r="H1139" t="n">
         <v>249320</v>
@@ -33429,7 +33429,7 @@
         <v>33.6726188659668</v>
       </c>
       <c r="G1140" t="n">
-        <v>26.03493309021</v>
+        <v>26.0349349975586</v>
       </c>
       <c r="H1140" t="n">
         <v>192736</v>
@@ -33487,7 +33487,7 @@
         <v>32.0056571960449</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.7460746765137</v>
+        <v>24.7460765838623</v>
       </c>
       <c r="H1142" t="n">
         <v>259051</v>
@@ -33603,7 +33603,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1146" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1146" t="n">
         <v>101636</v>
@@ -33719,7 +33719,7 @@
         <v>32.0681686401367</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.7944087982178</v>
+        <v>24.7944068908691</v>
       </c>
       <c r="H1150" t="n">
         <v>90180</v>
@@ -33777,7 +33777,7 @@
         <v>31.8597984313965</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.63330078125</v>
+        <v>24.6332988739014</v>
       </c>
       <c r="H1152" t="n">
         <v>144542</v>
@@ -33806,7 +33806,7 @@
         <v>32.7974662780762</v>
       </c>
       <c r="G1153" t="n">
-        <v>25.358283996582</v>
+        <v>25.3582859039307</v>
       </c>
       <c r="H1153" t="n">
         <v>172785</v>
@@ -33864,7 +33864,7 @@
         <v>37.5066299438477</v>
       </c>
       <c r="G1155" t="n">
-        <v>28.9993076324463</v>
+        <v>28.9993057250977</v>
       </c>
       <c r="H1155" t="n">
         <v>781786</v>
@@ -33951,7 +33951,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303916931152</v>
+        <v>30.0303955078125</v>
       </c>
       <c r="H1158" t="n">
         <v>499559</v>
@@ -33980,7 +33980,7 @@
         <v>36.4856185913086</v>
       </c>
       <c r="G1159" t="n">
-        <v>28.2098827362061</v>
+        <v>28.2098846435547</v>
       </c>
       <c r="H1159" t="n">
         <v>462214</v>
@@ -34009,7 +34009,7 @@
         <v>34.7978172302246</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.9049129486084</v>
+        <v>26.9049110412598</v>
       </c>
       <c r="H1160" t="n">
         <v>710323</v>
@@ -34038,7 +34038,7 @@
         <v>34.7353096008301</v>
       </c>
       <c r="G1161" t="n">
-        <v>26.8565826416016</v>
+        <v>26.8565807342529</v>
       </c>
       <c r="H1161" t="n">
         <v>155272</v>
@@ -34125,7 +34125,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655216217041</v>
+        <v>24.6655197143555</v>
       </c>
       <c r="H1164" t="n">
         <v>153075</v>
@@ -34270,7 +34270,7 @@
         <v>30.3386974334717</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.457218170166</v>
+        <v>23.4572200775146</v>
       </c>
       <c r="H1169" t="n">
         <v>427776</v>
@@ -34328,7 +34328,7 @@
         <v>31.2555255889893</v>
       </c>
       <c r="G1171" t="n">
-        <v>24.1660919189453</v>
+        <v>24.1660900115967</v>
       </c>
       <c r="H1171" t="n">
         <v>144072</v>
@@ -34444,7 +34444,7 @@
         <v>29.3801937103271</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7161235809326</v>
+        <v>22.7161254882812</v>
       </c>
       <c r="H1175" t="n">
         <v>84856</v>
@@ -34618,7 +34618,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H1181" t="n">
         <v>179328</v>
@@ -34879,7 +34879,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094543457031</v>
+        <v>22.9094524383545</v>
       </c>
       <c r="H1190" t="n">
         <v>71944</v>
@@ -34995,7 +34995,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416751861572</v>
+        <v>22.9416732788086</v>
       </c>
       <c r="H1194" t="n">
         <v>35197</v>
@@ -35198,7 +35198,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883750915527</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1201" t="n">
         <v>213623</v>
@@ -35459,7 +35459,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039161682129</v>
+        <v>22.1039180755615</v>
       </c>
       <c r="H1210" t="n">
         <v>66037</v>
@@ -35546,7 +35546,7 @@
         <v>27.3381652832031</v>
       </c>
       <c r="G1213" t="n">
-        <v>21.1372737884521</v>
+        <v>21.1372718811035</v>
       </c>
       <c r="H1213" t="n">
         <v>153694</v>
@@ -35575,7 +35575,7 @@
         <v>26.2129669189453</v>
       </c>
       <c r="G1214" t="n">
-        <v>20.2672920227051</v>
+        <v>20.2672939300537</v>
       </c>
       <c r="H1214" t="n">
         <v>217939</v>
@@ -35836,7 +35836,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1223" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1223" t="n">
         <v>87232</v>
@@ -36010,7 +36010,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.6584911346436</v>
+        <v>16.6584892272949</v>
       </c>
       <c r="H1229" t="n">
         <v>218937</v>
@@ -36068,7 +36068,7 @@
         <v>22.7748603820801</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.6090259552002</v>
+        <v>17.6090240478516</v>
       </c>
       <c r="H1231" t="n">
         <v>366850</v>
@@ -36329,7 +36329,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1240" t="n">
-        <v>19.2684288024902</v>
+        <v>19.2684268951416</v>
       </c>
       <c r="H1240" t="n">
         <v>471979</v>
@@ -36387,7 +36387,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1242" t="n">
         <v>245897</v>
@@ -36416,7 +36416,7 @@
         <v>25.733715057373</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.8967475891113</v>
+        <v>19.8967456817627</v>
       </c>
       <c r="H1243" t="n">
         <v>239601</v>
@@ -36445,7 +36445,7 @@
         <v>25.5878562927246</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.7839698791504</v>
+        <v>19.783971786499</v>
       </c>
       <c r="H1244" t="n">
         <v>193590</v>
@@ -36561,7 +36561,7 @@
         <v>24.1709403991699</v>
       </c>
       <c r="G1248" t="n">
-        <v>18.6884422302246</v>
+        <v>18.6884441375732</v>
       </c>
       <c r="H1248" t="n">
         <v>312209</v>
@@ -36590,7 +36590,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1249" t="n">
         <v>265701</v>
@@ -36619,7 +36619,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1250" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1250" t="n">
         <v>489077</v>
@@ -36735,7 +36735,7 @@
         <v>24.2126140594482</v>
       </c>
       <c r="G1254" t="n">
-        <v>18.7206630706787</v>
+        <v>18.7206649780273</v>
       </c>
       <c r="H1254" t="n">
         <v>171179</v>
@@ -36909,7 +36909,7 @@
         <v>22.6915111541748</v>
       </c>
       <c r="G1260" t="n">
-        <v>17.5445823669434</v>
+        <v>17.5445804595947</v>
       </c>
       <c r="H1260" t="n">
         <v>115703</v>
@@ -36938,7 +36938,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1261" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1261" t="n">
         <v>101768</v>
@@ -36967,7 +36967,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1262" t="n">
         <v>79845</v>
@@ -36996,7 +36996,7 @@
         <v>22.6498374938965</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.5123615264893</v>
+        <v>17.5123596191406</v>
       </c>
       <c r="H1263" t="n">
         <v>100240</v>
@@ -37054,7 +37054,7 @@
         <v>21.962215423584</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.9807052612305</v>
+        <v>16.9807033538818</v>
       </c>
       <c r="H1265" t="n">
         <v>177381</v>
@@ -37228,7 +37228,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6584911346436</v>
+        <v>16.6584892272949</v>
       </c>
       <c r="H1271" t="n">
         <v>110209</v>
@@ -37315,7 +37315,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1274" t="n">
         <v>234349</v>
@@ -37576,7 +37576,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768032073975</v>
+        <v>17.5768013000488</v>
       </c>
       <c r="H1283" t="n">
         <v>188315</v>
@@ -37721,7 +37721,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934791564941</v>
+        <v>17.0934810638428</v>
       </c>
       <c r="H1288" t="n">
         <v>71228</v>
@@ -37808,7 +37808,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1291" t="n">
         <v>77029</v>
@@ -37866,7 +37866,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801406860352</v>
+        <v>17.4801387786865</v>
       </c>
       <c r="H1293" t="n">
         <v>213107</v>
@@ -37924,7 +37924,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.6723327636719</v>
+        <v>18.6723308563232</v>
       </c>
       <c r="H1295" t="n">
         <v>825878</v>
@@ -38040,7 +38040,7 @@
         <v>26.5255222320557</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.5089550018311</v>
+        <v>20.5089530944824</v>
       </c>
       <c r="H1299" t="n">
         <v>624530</v>
@@ -38185,7 +38185,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867408752441</v>
+        <v>20.1867389678955</v>
       </c>
       <c r="H1304" t="n">
         <v>141753</v>
@@ -38301,7 +38301,7 @@
         <v>25.9629230499268</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.0739631652832</v>
+        <v>20.0739650726318</v>
       </c>
       <c r="H1308" t="n">
         <v>139323</v>
@@ -38359,7 +38359,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1310" t="n">
         <v>220708</v>
@@ -38388,7 +38388,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1311" t="n">
         <v>192874</v>
@@ -38475,7 +38475,7 @@
         <v>24.8793983459473</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.2362079620361</v>
+        <v>19.2362060546875</v>
       </c>
       <c r="H1314" t="n">
         <v>83220</v>
@@ -38591,7 +38591,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617576599121</v>
+        <v>19.4617595672607</v>
       </c>
       <c r="H1318" t="n">
         <v>140324</v>
@@ -38620,7 +38620,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1319" t="n">
         <v>101081</v>
@@ -38707,7 +38707,7 @@
         <v>24.7543754577637</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.1395435333252</v>
+        <v>19.1395416259766</v>
       </c>
       <c r="H1322" t="n">
         <v>105576</v>
@@ -38736,7 +38736,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750980377197</v>
+        <v>19.0750999450684</v>
       </c>
       <c r="H1323" t="n">
         <v>120557</v>
@@ -38852,7 +38852,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1327" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1327" t="n">
         <v>104855</v>
@@ -38939,7 +38939,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1330" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1330" t="n">
         <v>62081</v>
@@ -38997,7 +38997,7 @@
         <v>24.0667552947998</v>
       </c>
       <c r="G1332" t="n">
-        <v>18.6078910827637</v>
+        <v>18.607889175415</v>
       </c>
       <c r="H1332" t="n">
         <v>53943</v>
@@ -39084,7 +39084,7 @@
         <v>24.7231216430664</v>
       </c>
       <c r="G1335" t="n">
-        <v>19.1153793334961</v>
+        <v>19.1153774261475</v>
       </c>
       <c r="H1335" t="n">
         <v>175794</v>
@@ -39113,7 +39113,7 @@
         <v>24.3584728240967</v>
       </c>
       <c r="G1336" t="n">
-        <v>18.8334407806396</v>
+        <v>18.833438873291</v>
       </c>
       <c r="H1336" t="n">
         <v>97937</v>
@@ -39142,7 +39142,7 @@
         <v>23.9729881286621</v>
       </c>
       <c r="G1337" t="n">
-        <v>18.5353908538818</v>
+        <v>18.5353927612305</v>
       </c>
       <c r="H1337" t="n">
         <v>143301</v>
@@ -39200,7 +39200,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1339" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1339" t="n">
         <v>83809</v>
@@ -39345,7 +39345,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864940643311</v>
+        <v>18.9864921569824</v>
       </c>
       <c r="H1344" t="n">
         <v>82258</v>
@@ -39374,7 +39374,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1345" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1345" t="n">
         <v>129776</v>
@@ -39403,7 +39403,7 @@
         <v>23.9417324066162</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.5112266540527</v>
+        <v>18.5112247467041</v>
       </c>
       <c r="H1346" t="n">
         <v>91238</v>
@@ -39461,7 +39461,7 @@
         <v>23.9625701904297</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.5273361206055</v>
+        <v>18.5273342132568</v>
       </c>
       <c r="H1348" t="n">
         <v>39566</v>
@@ -39635,7 +39635,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1354" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1354" t="n">
         <v>116974</v>
@@ -39722,7 +39722,7 @@
         <v>24.2959613800049</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.7851047515869</v>
+        <v>18.7851066589355</v>
       </c>
       <c r="H1357" t="n">
         <v>232305</v>
@@ -39751,7 +39751,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.2684288024902</v>
+        <v>19.2684268951416</v>
       </c>
       <c r="H1358" t="n">
         <v>331765</v>
@@ -39838,7 +39838,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1361" t="n">
         <v>157303</v>
@@ -40128,7 +40128,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.195930480957</v>
+        <v>19.1959323883057</v>
       </c>
       <c r="H1371" t="n">
         <v>230606</v>
@@ -40302,7 +40302,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531345367432</v>
+        <v>19.9531364440918</v>
       </c>
       <c r="H1377" t="n">
         <v>173483</v>
@@ -40360,7 +40360,7 @@
         <v>26.306734085083</v>
       </c>
       <c r="G1379" t="n">
-        <v>20.3397941589355</v>
+        <v>20.3397922515869</v>
       </c>
       <c r="H1379" t="n">
         <v>314666</v>
@@ -40505,7 +40505,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598056793213</v>
+        <v>19.7598075866699</v>
       </c>
       <c r="H1384" t="n">
         <v>217234</v>
@@ -40737,7 +40737,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1392" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1392" t="n">
         <v>83268</v>
@@ -41027,7 +41027,7 @@
         <v>23.1707630157471</v>
       </c>
       <c r="G1402" t="n">
-        <v>17.9151287078857</v>
+        <v>17.9151268005371</v>
       </c>
       <c r="H1402" t="n">
         <v>231509</v>
@@ -41230,7 +41230,7 @@
         <v>21.9830532073975</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.9968166351318</v>
+        <v>16.9968185424805</v>
       </c>
       <c r="H1409" t="n">
         <v>449083</v>
@@ -41259,7 +41259,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G1410" t="n">
-        <v>17.1418132781982</v>
+        <v>17.1418113708496</v>
       </c>
       <c r="H1410" t="n">
         <v>158800</v>
@@ -41317,7 +41317,7 @@
         <v>24.1084289550781</v>
       </c>
       <c r="G1412" t="n">
-        <v>18.6401119232178</v>
+        <v>18.6401100158691</v>
       </c>
       <c r="H1412" t="n">
         <v>692896</v>
@@ -41346,7 +41346,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1413" t="n">
         <v>387357</v>
@@ -41375,7 +41375,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1414" t="n">
-        <v>18.3823375701904</v>
+        <v>18.3823394775391</v>
       </c>
       <c r="H1414" t="n">
         <v>234798</v>
@@ -41433,7 +41433,7 @@
         <v>23.7021064758301</v>
       </c>
       <c r="G1416" t="n">
-        <v>18.3259525299072</v>
+        <v>18.3259506225586</v>
       </c>
       <c r="H1416" t="n">
         <v>113622</v>
@@ -41549,7 +41549,7 @@
         <v>23.4103889465332</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.1004009246826</v>
+        <v>18.1004028320312</v>
       </c>
       <c r="H1420" t="n">
         <v>196996</v>
@@ -41694,7 +41694,7 @@
         <v>24.5876808166504</v>
       </c>
       <c r="G1425" t="n">
-        <v>19.0106563568115</v>
+        <v>19.0106582641602</v>
       </c>
       <c r="H1425" t="n">
         <v>269832</v>
@@ -41723,7 +41723,7 @@
         <v>24.6293544769287</v>
       </c>
       <c r="G1426" t="n">
-        <v>19.0428771972656</v>
+        <v>19.0428791046143</v>
       </c>
       <c r="H1426" t="n">
         <v>251332</v>
@@ -41810,7 +41810,7 @@
         <v>23.9208946228027</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.4951133728027</v>
+        <v>18.4951114654541</v>
       </c>
       <c r="H1429" t="n">
         <v>97564</v>
@@ -41839,7 +41839,7 @@
         <v>23.7646179199219</v>
       </c>
       <c r="G1430" t="n">
-        <v>18.3742847442627</v>
+        <v>18.3742828369141</v>
       </c>
       <c r="H1430" t="n">
         <v>93708</v>
@@ -41897,7 +41897,7 @@
         <v>23.5770854949951</v>
       </c>
       <c r="G1432" t="n">
-        <v>18.2292861938477</v>
+        <v>18.2292881011963</v>
       </c>
       <c r="H1432" t="n">
         <v>168351</v>
@@ -41955,7 +41955,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1434" t="n">
-        <v>18.0923442840576</v>
+        <v>18.0923461914062</v>
       </c>
       <c r="H1434" t="n">
         <v>68611</v>
@@ -42129,7 +42129,7 @@
         <v>23.4520626068115</v>
       </c>
       <c r="G1440" t="n">
-        <v>18.1326217651367</v>
+        <v>18.1326236724854</v>
       </c>
       <c r="H1440" t="n">
         <v>97025</v>
@@ -42158,7 +42158,7 @@
         <v>23.5458297729492</v>
       </c>
       <c r="G1441" t="n">
-        <v>18.2051219940186</v>
+        <v>18.2051200866699</v>
       </c>
       <c r="H1441" t="n">
         <v>161224</v>
@@ -42245,7 +42245,7 @@
         <v>23.3999691009521</v>
       </c>
       <c r="G1444" t="n">
-        <v>18.0923442840576</v>
+        <v>18.0923461914062</v>
       </c>
       <c r="H1444" t="n">
         <v>100237</v>
@@ -42361,7 +42361,7 @@
         <v>23.202018737793</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.9392929077148</v>
+        <v>17.9392948150635</v>
       </c>
       <c r="H1448" t="n">
         <v>194792</v>
@@ -42651,7 +42651,7 @@
         <v>22.5977458953857</v>
       </c>
       <c r="G1458" t="n">
-        <v>17.4720821380615</v>
+        <v>17.4720840454102</v>
       </c>
       <c r="H1458" t="n">
         <v>246340</v>
@@ -42854,7 +42854,7 @@
         <v>23.2645282745361</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.9876270294189</v>
+        <v>17.9876251220703</v>
       </c>
       <c r="H1465" t="n">
         <v>247043</v>
@@ -42912,7 +42912,7 @@
         <v>23.0040664672852</v>
       </c>
       <c r="G1467" t="n">
-        <v>17.7862396240234</v>
+        <v>17.7862415313721</v>
       </c>
       <c r="H1467" t="n">
         <v>172242</v>
@@ -42970,7 +42970,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8023529052734</v>
+        <v>17.8023548126221</v>
       </c>
       <c r="H1469" t="n">
         <v>177997</v>
@@ -43434,7 +43434,7 @@
         <v>21.3475246429443</v>
       </c>
       <c r="G1485" t="n">
-        <v>16.5054397583008</v>
+        <v>16.5054378509521</v>
       </c>
       <c r="H1485" t="n">
         <v>156005</v>
@@ -43550,7 +43550,7 @@
         <v>21.2537574768066</v>
       </c>
       <c r="G1489" t="n">
-        <v>16.4329395294189</v>
+        <v>16.4329414367676</v>
       </c>
       <c r="H1489" t="n">
         <v>110218</v>
@@ -43608,7 +43608,7 @@
         <v>21.1808280944824</v>
       </c>
       <c r="G1491" t="n">
-        <v>16.3765544891357</v>
+        <v>16.3765525817871</v>
       </c>
       <c r="H1491" t="n">
         <v>136046</v>
@@ -43753,7 +43753,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.9753942489624</v>
+        <v>15.975396156311</v>
       </c>
       <c r="H1496" t="n">
         <v>142969</v>
@@ -43840,7 +43840,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668664932251</v>
+        <v>14.9668645858765</v>
       </c>
       <c r="H1499" t="n">
         <v>131664</v>
@@ -43869,7 +43869,7 @@
         <v>18.9325141906738</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.6382064819336</v>
+        <v>14.6382083892822</v>
       </c>
       <c r="H1500" t="n">
         <v>136580</v>
@@ -43898,7 +43898,7 @@
         <v>18.7366466522217</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.4867658615112</v>
+        <v>14.4867668151855</v>
       </c>
       <c r="H1501" t="n">
         <v>287038</v>
@@ -43927,7 +43927,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.293436050415</v>
+        <v>14.2934370040894</v>
       </c>
       <c r="H1502" t="n">
         <v>112108</v>
@@ -43956,7 +43956,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1503" t="n">
         <v>269832</v>
@@ -44014,7 +44014,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013570785522</v>
+        <v>13.0013580322266</v>
       </c>
       <c r="H1505" t="n">
         <v>156575</v>
@@ -44188,7 +44188,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1511" t="n">
         <v>68657</v>
@@ -44217,7 +44217,7 @@
         <v>19.1908931732178</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.8379812240601</v>
+        <v>14.8379793167114</v>
       </c>
       <c r="H1512" t="n">
         <v>518691</v>
@@ -44304,7 +44304,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.654314994812</v>
+        <v>14.6543169021606</v>
       </c>
       <c r="H1515" t="n">
         <v>168456</v>
@@ -44449,7 +44449,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.6253175735474</v>
+        <v>14.625316619873</v>
       </c>
       <c r="H1520" t="n">
         <v>192381</v>
@@ -44507,7 +44507,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.518988609314</v>
+        <v>14.5189876556396</v>
       </c>
       <c r="H1522" t="n">
         <v>83491</v>
@@ -44536,7 +44536,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1523" t="n">
         <v>155943</v>
@@ -44565,7 +44565,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4996538162231</v>
+        <v>14.4996528625488</v>
       </c>
       <c r="H1524" t="n">
         <v>184928</v>
@@ -44594,7 +44594,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287672042847</v>
+        <v>14.4287662506104</v>
       </c>
       <c r="H1525" t="n">
         <v>203931</v>
@@ -44623,7 +44623,7 @@
         <v>18.5866184234619</v>
       </c>
       <c r="G1526" t="n">
-        <v>14.3707675933838</v>
+        <v>14.3707666397095</v>
       </c>
       <c r="H1526" t="n">
         <v>75889</v>
@@ -44681,7 +44681,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958639144897</v>
+        <v>14.9958648681641</v>
       </c>
       <c r="H1528" t="n">
         <v>508333</v>
@@ -44826,7 +44826,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024209976196</v>
       </c>
       <c r="H1533" t="n">
         <v>79836</v>
@@ -44884,7 +44884,7 @@
         <v>19.0533676147461</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.7316484451294</v>
+        <v>14.7316465377808</v>
       </c>
       <c r="H1535" t="n">
         <v>124218</v>
@@ -44942,7 +44942,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154230117798</v>
+        <v>14.8154249191284</v>
       </c>
       <c r="H1537" t="n">
         <v>73886</v>
@@ -45116,7 +45116,7 @@
         <v>18.3365745544434</v>
       </c>
       <c r="G1543" t="n">
-        <v>14.1774396896362</v>
+        <v>14.1774387359619</v>
       </c>
       <c r="H1543" t="n">
         <v>71877</v>
@@ -45203,7 +45203,7 @@
         <v>18.7116413116455</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.467432975769</v>
+        <v>14.4674320220947</v>
       </c>
       <c r="H1546" t="n">
         <v>228021</v>
@@ -45232,7 +45232,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994276046753</v>
+        <v>14.6994256973267</v>
       </c>
       <c r="H1547" t="n">
         <v>198643</v>
@@ -45290,7 +45290,7 @@
         <v>19.5867958068848</v>
       </c>
       <c r="G1549" t="n">
-        <v>15.1440830230713</v>
+        <v>15.1440811157227</v>
       </c>
       <c r="H1549" t="n">
         <v>378368</v>
@@ -45348,7 +45348,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024229049683</v>
+        <v>14.9024209976196</v>
       </c>
       <c r="H1551" t="n">
         <v>264963</v>
@@ -45464,7 +45464,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.6435136795044</v>
+        <v>15.643515586853</v>
       </c>
       <c r="H1555" t="n">
         <v>151091</v>
@@ -45493,7 +45493,7 @@
         <v>21.7746829986572</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.8357105255127</v>
+        <v>16.8357086181641</v>
       </c>
       <c r="H1556" t="n">
         <v>411312</v>
@@ -45551,7 +45551,7 @@
         <v>21.6496601104736</v>
       </c>
       <c r="G1558" t="n">
-        <v>16.7390441894531</v>
+        <v>16.7390460968018</v>
       </c>
       <c r="H1558" t="n">
         <v>523113</v>
@@ -45609,7 +45609,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147443771362</v>
+        <v>15.4147424697876</v>
       </c>
       <c r="H1560" t="n">
         <v>254459</v>
@@ -45667,7 +45667,7 @@
         <v>19.1325492858887</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.7928686141968</v>
+        <v>14.7928705215454</v>
       </c>
       <c r="H1562" t="n">
         <v>328129</v>
@@ -45754,7 +45754,7 @@
         <v>17.2863883972168</v>
       </c>
       <c r="G1565" t="n">
-        <v>13.3654584884644</v>
+        <v>13.36545753479</v>
       </c>
       <c r="H1565" t="n">
         <v>596953</v>
@@ -45783,7 +45783,7 @@
         <v>18.1573753356934</v>
       </c>
       <c r="G1566" t="n">
-        <v>14.0388870239258</v>
+        <v>14.0388860702515</v>
       </c>
       <c r="H1566" t="n">
         <v>543373</v>
@@ -45812,7 +45812,7 @@
         <v>17.88649559021</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.8294477462769</v>
+        <v>13.8294486999512</v>
       </c>
       <c r="H1567" t="n">
         <v>271257</v>
@@ -45870,7 +45870,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781192779541</v>
+        <v>13.5781202316284</v>
       </c>
       <c r="H1569" t="n">
         <v>306814</v>
@@ -46044,7 +46044,7 @@
         <v>17.9240016937256</v>
       </c>
       <c r="G1575" t="n">
-        <v>13.8584480285645</v>
+        <v>13.8584470748901</v>
       </c>
       <c r="H1575" t="n">
         <v>588208</v>
@@ -46102,7 +46102,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151958465576</v>
+        <v>15.0151977539062</v>
       </c>
       <c r="H1577" t="n">
         <v>400947</v>
@@ -46363,7 +46363,7 @@
         <v>20.0952186584473</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5371837615967</v>
+        <v>15.537184715271</v>
       </c>
       <c r="H1586" t="n">
         <v>198619</v>
@@ -46392,7 +46392,7 @@
         <v>20.1202239990234</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.5565176010132</v>
+        <v>15.5565195083618</v>
       </c>
       <c r="H1587" t="n">
         <v>228146</v>
@@ -46421,7 +46421,7 @@
         <v>20.4744529724121</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8304004669189</v>
+        <v>15.8303985595703</v>
       </c>
       <c r="H1588" t="n">
         <v>187148</v>
@@ -46479,7 +46479,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.0699729919434</v>
+        <v>15.069974899292</v>
       </c>
       <c r="H1590" t="n">
         <v>151523</v>
@@ -46508,7 +46508,7 @@
         <v>19.5555400848389</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1199178695679</v>
+        <v>15.1199159622192</v>
       </c>
       <c r="H1591" t="n">
         <v>163415</v>
@@ -46566,7 +46566,7 @@
         <v>18.6178741455078</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.3949337005615</v>
+        <v>14.3949346542358</v>
       </c>
       <c r="H1593" t="n">
         <v>185873</v>
@@ -46653,7 +46653,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660474777222</v>
+        <v>14.2660484313965</v>
       </c>
       <c r="H1596" t="n">
         <v>137521</v>
@@ -46711,7 +46711,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585592269897</v>
+        <v>13.7585582733154</v>
       </c>
       <c r="H1598" t="n">
         <v>171526</v>
@@ -46740,7 +46740,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116125106812</v>
+        <v>13.9116115570068</v>
       </c>
       <c r="H1599" t="n">
         <v>156203</v>
@@ -46798,7 +46798,7 @@
         <v>17.6906261444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.6780052185059</v>
+        <v>13.6780061721802</v>
       </c>
       <c r="H1601" t="n">
         <v>280445</v>
@@ -46972,7 +46972,7 @@
         <v>17.8573226928711</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8068914413452</v>
+        <v>13.8068923950195</v>
       </c>
       <c r="H1607" t="n">
         <v>594069</v>
@@ -47175,7 +47175,7 @@
         <v>15.0964193344116</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.6722211837769</v>
+        <v>11.6722221374512</v>
       </c>
       <c r="H1614" t="n">
         <v>366805</v>
@@ -47204,7 +47204,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519580841064</v>
+        <v>11.0519590377808</v>
       </c>
       <c r="H1615" t="n">
         <v>230061</v>
@@ -47262,7 +47262,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.3902835845947</v>
+        <v>11.390284538269</v>
       </c>
       <c r="H1617" t="n">
         <v>109832</v>
@@ -47378,7 +47378,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3902835845947</v>
+        <v>11.390284538269</v>
       </c>
       <c r="H1621" t="n">
         <v>197863</v>
@@ -47436,7 +47436,7 @@
         <v>14.9297218322754</v>
       </c>
       <c r="G1623" t="n">
-        <v>11.5433340072632</v>
+        <v>11.5433349609375</v>
       </c>
       <c r="H1623" t="n">
         <v>121159</v>
@@ -47552,7 +47552,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.970269203186</v>
+        <v>11.9702701568604</v>
       </c>
       <c r="H1627" t="n">
         <v>161789</v>
@@ -47581,7 +47581,7 @@
         <v>15.5860891342163</v>
       </c>
       <c r="G1628" t="n">
-        <v>12.0508232116699</v>
+        <v>12.0508241653442</v>
       </c>
       <c r="H1628" t="n">
         <v>106888</v>
@@ -47639,7 +47639,7 @@
         <v>16.1903629302979</v>
       </c>
       <c r="G1630" t="n">
-        <v>12.5180349349976</v>
+        <v>12.5180358886719</v>
       </c>
       <c r="H1630" t="n">
         <v>120708</v>
@@ -47668,7 +47668,7 @@
         <v>16.0445022583008</v>
       </c>
       <c r="G1631" t="n">
-        <v>12.4052591323853</v>
+        <v>12.4052581787109</v>
       </c>
       <c r="H1631" t="n">
         <v>192305</v>
@@ -47784,7 +47784,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805246353149</v>
+        <v>12.8805255889893</v>
       </c>
       <c r="H1635" t="n">
         <v>140616</v>
@@ -48045,7 +48045,7 @@
         <v>14.5546560287476</v>
       </c>
       <c r="G1644" t="n">
-        <v>11.253342628479</v>
+        <v>11.2533416748047</v>
       </c>
       <c r="H1644" t="n">
         <v>145140</v>
@@ -48132,7 +48132,7 @@
         <v>14.2837753295898</v>
       </c>
       <c r="G1647" t="n">
-        <v>11.0439023971558</v>
+        <v>11.0439033508301</v>
       </c>
       <c r="H1647" t="n">
         <v>123714</v>
@@ -48161,7 +48161,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136325836182</v>
+        <v>10.7136335372925</v>
       </c>
       <c r="H1648" t="n">
         <v>160860</v>
@@ -48335,7 +48335,7 @@
         <v>10.7935752868652</v>
       </c>
       <c r="G1654" t="n">
-        <v>8.34535598754883</v>
+        <v>8.34535694122314</v>
       </c>
       <c r="H1654" t="n">
         <v>225381</v>
@@ -48596,7 +48596,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971380233765</v>
+        <v>7.34971284866333</v>
       </c>
       <c r="H1663" t="n">
         <v>388404</v>
@@ -48625,7 +48625,7 @@
         <v>8.91824340820312</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.89539098739624</v>
+        <v>6.8953914642334</v>
       </c>
       <c r="H1664" t="n">
         <v>278474</v>
@@ -48712,7 +48712,7 @@
         <v>9.3766565322876</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.24982595443726</v>
+        <v>7.2498254776001</v>
       </c>
       <c r="H1667" t="n">
         <v>419862</v>
@@ -48741,7 +48741,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316919326782</v>
+        <v>6.86316871643066</v>
       </c>
       <c r="H1668" t="n">
         <v>393325</v>
@@ -48857,7 +48857,7 @@
         <v>8.54317665100098</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.60539722442627</v>
+        <v>6.60539770126343</v>
       </c>
       <c r="H1672" t="n">
         <v>149384</v>
@@ -48973,7 +48973,7 @@
         <v>8.8223934173584</v>
       </c>
       <c r="G1676" t="n">
-        <v>6.82128143310547</v>
+        <v>6.82128190994263</v>
       </c>
       <c r="H1676" t="n">
         <v>109570</v>
@@ -49031,7 +49031,7 @@
         <v>9.2724723815918</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.16927337646484</v>
+        <v>7.16927289962769</v>
       </c>
       <c r="H1678" t="n">
         <v>171846</v>
@@ -49234,7 +49234,7 @@
         <v>8.71820831298828</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.74072790145874</v>
+        <v>6.7407283782959</v>
       </c>
       <c r="H1685" t="n">
         <v>219529</v>
@@ -49321,7 +49321,7 @@
         <v>8.38064765930176</v>
       </c>
       <c r="G1688" t="n">
-        <v>6.47973346710205</v>
+        <v>6.47973394393921</v>
       </c>
       <c r="H1688" t="n">
         <v>211830</v>
@@ -49350,7 +49350,7 @@
         <v>7.91806602478027</v>
       </c>
       <c r="G1689" t="n">
-        <v>6.1220760345459</v>
+        <v>6.12207555770874</v>
       </c>
       <c r="H1689" t="n">
         <v>278929</v>
@@ -49640,7 +49640,7 @@
         <v>6.32195091247559</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.88799428939819</v>
+        <v>4.88799476623535</v>
       </c>
       <c r="H1699" t="n">
         <v>228803</v>
@@ -49669,7 +49669,7 @@
         <v>6.05523681640625</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.68177700042725</v>
+        <v>4.68177652359009</v>
       </c>
       <c r="H1700" t="n">
         <v>576189</v>
@@ -50017,7 +50017,7 @@
         <v>6.1635890007019</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.76555204391479</v>
+        <v>4.76555252075195</v>
       </c>
       <c r="H1712" t="n">
         <v>627926</v>
@@ -50046,7 +50046,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.91699314117432</v>
+        <v>4.91699361801147</v>
       </c>
       <c r="H1713" t="n">
         <v>765955</v>
@@ -50075,7 +50075,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.91699314117432</v>
+        <v>4.91699361801147</v>
       </c>
       <c r="H1714" t="n">
         <v>0</v>
@@ -50133,7 +50133,7 @@
         <v>6.2302680015564</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.81710720062256</v>
+        <v>4.8171067237854</v>
       </c>
       <c r="H1716" t="n">
         <v>855847</v>
@@ -50278,7 +50278,7 @@
         <v>4.93003797531128</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.81179761886597</v>
+        <v>3.81179785728455</v>
       </c>
       <c r="H1721" t="n">
         <v>554124</v>
@@ -50365,7 +50365,7 @@
         <v>4.68311882019043</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.62088489532471</v>
+        <v>3.62088513374329</v>
       </c>
       <c r="H1724" t="n">
         <v>677198</v>
@@ -50597,7 +50597,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.55331492424011</v>
+        <v>1.5533150434494</v>
       </c>
       <c r="H1732" t="n">
         <v>1270999</v>
@@ -50713,7 +50713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.53089272975922</v>
+        <v>1.53089284896851</v>
       </c>
       <c r="H1736" t="n">
         <v>1871837</v>
@@ -51003,7 +51003,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1746" t="n">
         <v>4299825</v>
@@ -51032,7 +51032,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1747" t="n">
         <v>5687761</v>
@@ -51061,7 +51061,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.39172065258026</v>
+        <v>1.39172077178955</v>
       </c>
       <c r="H1748" t="n">
         <v>7070109</v>
@@ -51351,7 +51351,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.37393748760223</v>
+        <v>1.37393760681152</v>
       </c>
       <c r="H1758" t="n">
         <v>3847795</v>
@@ -51409,7 +51409,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006953716278</v>
+        <v>1.46006965637207</v>
       </c>
       <c r="H1760" t="n">
         <v>10216109</v>
@@ -51438,7 +51438,7 @@
         <v>1.88339996337891</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.45620369911194</v>
+        <v>1.45620381832123</v>
       </c>
       <c r="H1761" t="n">
         <v>12545701</v>
@@ -51583,7 +51583,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.44537925720215</v>
+        <v>1.44537937641144</v>
       </c>
       <c r="H1766" t="n">
         <v>4191313</v>
@@ -51844,7 +51844,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903848648071</v>
+        <v>1.46903860569</v>
       </c>
       <c r="H1775" t="n">
         <v>3814973</v>
@@ -51931,7 +51931,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.52161467075348</v>
+        <v>1.52161455154419</v>
       </c>
       <c r="H1778" t="n">
         <v>5872856</v>
@@ -52018,7 +52018,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.50213050842285</v>
+        <v>1.50213062763214</v>
       </c>
       <c r="H1781" t="n">
         <v>3033681</v>
@@ -52134,7 +52134,7 @@
         <v>2.06299996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.5950665473938</v>
+        <v>1.59506642818451</v>
       </c>
       <c r="H1785" t="n">
         <v>11778628</v>
@@ -52221,7 +52221,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490919589996</v>
+        <v>1.71490931510925</v>
       </c>
       <c r="H1788" t="n">
         <v>25457401</v>
@@ -52279,7 +52279,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702329158783</v>
+        <v>1.67702341079712</v>
       </c>
       <c r="H1790" t="n">
         <v>8965001</v>
@@ -52395,7 +52395,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1794" t="n">
         <v>6601746</v>
@@ -52424,7 +52424,7 @@
         <v>2.07349991798401</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.6031848192215</v>
+        <v>1.60318493843079</v>
       </c>
       <c r="H1795" t="n">
         <v>7563778</v>
@@ -52453,7 +52453,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.56259310245514</v>
+        <v>1.56259298324585</v>
       </c>
       <c r="H1796" t="n">
         <v>7220763</v>
@@ -52511,7 +52511,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.65305495262146</v>
+        <v>1.65305483341217</v>
       </c>
       <c r="H1798" t="n">
         <v>10373984</v>
@@ -52540,7 +52540,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1799" t="n">
         <v>5974419</v>
@@ -52569,7 +52569,7 @@
         <v>2.10450005531311</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.62715351581573</v>
+        <v>1.62715339660645</v>
       </c>
       <c r="H1800" t="n">
         <v>8236893</v>
@@ -52656,7 +52656,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.79377329349518</v>
+        <v>1.79377341270447</v>
       </c>
       <c r="H1803" t="n">
         <v>18893517</v>
@@ -52685,7 +52685,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1804" t="n">
         <v>18740837</v>
@@ -53004,7 +53004,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.83552491664886</v>
+        <v>1.83552515506744</v>
       </c>
       <c r="H1815" t="n">
         <v>8871781</v>
@@ -53062,7 +53062,7 @@
         <v>2.63949990272522</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.04080367088318</v>
+        <v>2.04080390930176</v>
       </c>
       <c r="H1817" t="n">
         <v>28638347</v>
@@ -53178,7 +53178,7 @@
         <v>2.63050007820129</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.0338454246521</v>
+        <v>2.03384518623352</v>
       </c>
       <c r="H1821" t="n">
         <v>13235723</v>
@@ -53236,7 +53236,7 @@
         <v>2.74449992179871</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.12198758125305</v>
+        <v>2.12198734283447</v>
       </c>
       <c r="H1823" t="n">
         <v>9639295</v>
@@ -53294,7 +53294,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.90665745735168</v>
+        <v>1.9066573381424</v>
       </c>
       <c r="H1825" t="n">
         <v>21554181</v>
@@ -53381,7 +53381,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.89428651332855</v>
+        <v>1.89428663253784</v>
       </c>
       <c r="H1828" t="n">
         <v>6331894</v>
@@ -53468,7 +53468,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305159091949</v>
+        <v>1.80305147171021</v>
       </c>
       <c r="H1831" t="n">
         <v>6664209</v>
@@ -53526,7 +53526,7 @@
         <v>2.13649988174438</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.65189504623413</v>
+        <v>1.65189492702484</v>
       </c>
       <c r="H1833" t="n">
         <v>20642011</v>
@@ -53642,7 +53642,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.46208000183105</v>
+        <v>1.46207988262177</v>
       </c>
       <c r="H1837" t="n">
         <v>27810987</v>
@@ -53729,7 +53729,7 @@
         <v>1.96280002593994</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.51759397983551</v>
+        <v>1.5175940990448</v>
       </c>
       <c r="H1840" t="n">
         <v>7183811</v>
@@ -54164,7 +54164,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1855" t="n">
         <v>7814956</v>
@@ -54193,7 +54193,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.63449859619141</v>
+        <v>1.6344987154007</v>
       </c>
       <c r="H1856" t="n">
         <v>6891203</v>
@@ -54222,7 +54222,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1857" t="n">
         <v>11220865</v>
@@ -54251,7 +54251,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.79222691059113</v>
+        <v>1.79222702980042</v>
       </c>
       <c r="H1858" t="n">
         <v>11711966</v>
@@ -54280,7 +54280,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1859" t="n">
         <v>7526359</v>
@@ -54309,7 +54309,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666093826294</v>
+        <v>1.75666081905365</v>
       </c>
       <c r="H1860" t="n">
         <v>8508624</v>
@@ -54338,7 +54338,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1861" t="n">
         <v>3806799</v>
@@ -54396,7 +54396,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1863" t="n">
         <v>7031365</v>
@@ -54425,7 +54425,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630158901215</v>
+        <v>1.68630146980286</v>
       </c>
       <c r="H1864" t="n">
         <v>5899256</v>
@@ -54628,7 +54628,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.63681828975677</v>
+        <v>1.63681817054749</v>
       </c>
       <c r="H1871" t="n">
         <v>17872031</v>
@@ -54686,7 +54686,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.62831318378448</v>
+        <v>1.6283130645752</v>
       </c>
       <c r="H1873" t="n">
         <v>6917707</v>
@@ -54715,7 +54715,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.64686954021454</v>
+        <v>1.64686965942383</v>
       </c>
       <c r="H1874" t="n">
         <v>8552244</v>
@@ -54802,7 +54802,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.73501169681549</v>
+        <v>1.73501181602478</v>
       </c>
       <c r="H1877" t="n">
         <v>5397862</v>
@@ -54831,7 +54831,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.68939423561096</v>
+        <v>1.68939435482025</v>
       </c>
       <c r="H1878" t="n">
         <v>12211949</v>
@@ -54976,7 +54976,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.61594223976135</v>
+        <v>1.61594235897064</v>
       </c>
       <c r="H1883" t="n">
         <v>10738852</v>
@@ -55005,7 +55005,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.6205815076828</v>
+        <v>1.62058138847351</v>
       </c>
       <c r="H1884" t="n">
         <v>14947292</v>
@@ -55121,7 +55121,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67006492614746</v>
+        <v>1.67006480693817</v>
       </c>
       <c r="H1888" t="n">
         <v>9732271</v>
@@ -55150,7 +55150,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.73037266731262</v>
+        <v>1.73037254810333</v>
       </c>
       <c r="H1889" t="n">
         <v>8200584</v>
@@ -55179,7 +55179,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.75820708274841</v>
+        <v>1.7582072019577</v>
       </c>
       <c r="H1890" t="n">
         <v>16440004</v>
@@ -55295,7 +55295,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.68011617660522</v>
+        <v>1.68011629581451</v>
       </c>
       <c r="H1894" t="n">
         <v>28227461</v>
@@ -55324,7 +55324,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65769398212433</v>
+        <v>1.65769410133362</v>
       </c>
       <c r="H1895" t="n">
         <v>18838481</v>
@@ -55382,7 +55382,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650694847107</v>
+        <v>1.72650682926178</v>
       </c>
       <c r="H1897" t="n">
         <v>13177383</v>
@@ -55411,7 +55411,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.7659387588501</v>
+        <v>1.76593887805939</v>
       </c>
       <c r="H1898" t="n">
         <v>9180042</v>
@@ -55498,7 +55498,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.80073201656342</v>
+        <v>1.80073189735413</v>
       </c>
       <c r="H1901" t="n">
         <v>7297805</v>
@@ -55527,7 +55527,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82701992988586</v>
+        <v>1.82702016830444</v>
       </c>
       <c r="H1902" t="n">
         <v>11298307</v>
@@ -55585,7 +55585,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.74583613872528</v>
+        <v>1.74583625793457</v>
       </c>
       <c r="H1904" t="n">
         <v>7115446</v>
@@ -55614,7 +55614,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645557880402</v>
+        <v>1.71645545959473</v>
       </c>
       <c r="H1905" t="n">
         <v>7081375</v>
@@ -55759,7 +55759,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1910" t="n">
         <v>7777212</v>
@@ -55846,7 +55846,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.72728002071381</v>
+        <v>1.72727990150452</v>
       </c>
       <c r="H1913" t="n">
         <v>9515588</v>
@@ -55933,7 +55933,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387591362</v>
+        <v>1.81387603282928</v>
       </c>
       <c r="H1916" t="n">
         <v>11063863</v>
@@ -55991,7 +55991,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985284328461</v>
+        <v>1.92985260486603</v>
       </c>
       <c r="H1918" t="n">
         <v>16178743</v>
@@ -56020,7 +56020,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309947967529</v>
+        <v>1.96309924125671</v>
       </c>
       <c r="H1919" t="n">
         <v>16639251</v>
@@ -56223,7 +56223,7 @@
         <v>2.52099990844727</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.94918191432953</v>
+        <v>1.94918215274811</v>
       </c>
       <c r="H1926" t="n">
         <v>5834369</v>
@@ -56310,7 +56310,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.00562405586243</v>
+        <v>2.00562429428101</v>
       </c>
       <c r="H1929" t="n">
         <v>10963576</v>
@@ -56339,7 +56339,7 @@
         <v>2.625</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.02959251403809</v>
+        <v>2.02959275245667</v>
       </c>
       <c r="H1930" t="n">
         <v>11993677</v>
@@ -56629,7 +56629,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.16025948524475</v>
+        <v>2.16025972366333</v>
       </c>
       <c r="H1940" t="n">
         <v>21527670</v>
@@ -56774,7 +56774,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.02263402938843</v>
+        <v>2.02263379096985</v>
       </c>
       <c r="H1945" t="n">
         <v>6289247</v>
@@ -56832,7 +56832,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.954594373703</v>
+        <v>1.95459449291229</v>
       </c>
       <c r="H1947" t="n">
         <v>11144521</v>
@@ -56890,7 +56890,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309947967529</v>
+        <v>1.96309924125671</v>
       </c>
       <c r="H1949" t="n">
         <v>5429828</v>
@@ -57093,7 +57093,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.79763913154602</v>
+        <v>1.79763925075531</v>
       </c>
       <c r="H1956" t="n">
         <v>22749670</v>
@@ -57122,7 +57122,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.7497022151947</v>
+        <v>1.74970209598541</v>
       </c>
       <c r="H1957" t="n">
         <v>16237631</v>
@@ -57209,7 +57209,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.81310272216797</v>
+        <v>1.81310284137726</v>
       </c>
       <c r="H1960" t="n">
         <v>6445475</v>
@@ -57238,7 +57238,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645197868347</v>
+        <v>1.86645221710205</v>
       </c>
       <c r="H1961" t="n">
         <v>10420578</v>
@@ -57528,7 +57528,7 @@
         <v>2.39100003242493</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.84866893291473</v>
+        <v>1.84866917133331</v>
       </c>
       <c r="H1971" t="n">
         <v>32386618</v>
@@ -57615,7 +57615,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737927913666</v>
+        <v>1.89737904071808</v>
       </c>
       <c r="H1974" t="n">
         <v>15191141</v>
@@ -57673,7 +57673,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.00639724731445</v>
+        <v>2.00639748573303</v>
       </c>
       <c r="H1976" t="n">
         <v>29570216</v>
@@ -57789,7 +57789,7 @@
         <v>2.45900011062622</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.90124535560608</v>
+        <v>1.9012451171875</v>
       </c>
       <c r="H1980" t="n">
         <v>37059275</v>
@@ -57934,7 +57934,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.98397505283356</v>
+        <v>1.98397529125214</v>
       </c>
       <c r="H1985" t="n">
         <v>20639388</v>
@@ -58137,7 +58137,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.85872030258179</v>
+        <v>1.85872042179108</v>
       </c>
       <c r="H1992" t="n">
         <v>17881971</v>
@@ -58195,7 +58195,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062591552734</v>
+        <v>1.93062567710876</v>
       </c>
       <c r="H1994" t="n">
         <v>10863078</v>
@@ -58224,7 +58224,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.97237753868103</v>
+        <v>1.97237777709961</v>
       </c>
       <c r="H1995" t="n">
         <v>14164042</v>
@@ -58282,7 +58282,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.03964376449585</v>
+        <v>2.03964400291443</v>
       </c>
       <c r="H1997" t="n">
         <v>18265540</v>
@@ -58427,7 +58427,7 @@
         <v>2.69899988174438</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.0868079662323</v>
+        <v>2.08680772781372</v>
       </c>
       <c r="H2002" t="n">
         <v>18452495</v>
@@ -58456,7 +58456,7 @@
         <v>2.68300008773804</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.07443690299988</v>
+        <v>2.07443714141846</v>
       </c>
       <c r="H2003" t="n">
         <v>11980891</v>
@@ -58514,7 +58514,7 @@
         <v>3.06100010871887</v>
       </c>
       <c r="G2005" t="n">
-        <v>2.36669826507568</v>
+        <v>2.36669850349426</v>
       </c>
       <c r="H2005" t="n">
         <v>41979843</v>
@@ -58659,7 +58659,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.18654775619507</v>
+        <v>2.18654799461365</v>
       </c>
       <c r="H2010" t="n">
         <v>100072608</v>
@@ -58746,7 +58746,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716347694397</v>
+        <v>2.30716371536255</v>
       </c>
       <c r="H2013" t="n">
         <v>31624933</v>
@@ -58833,7 +58833,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.40071797370911</v>
+        <v>2.40071821212769</v>
       </c>
       <c r="H2016" t="n">
         <v>54965782</v>
@@ -58949,7 +58949,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.55921983718872</v>
+        <v>2.55921959877014</v>
       </c>
       <c r="H2020" t="n">
         <v>36522732</v>
@@ -59152,7 +59152,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G2027" t="n">
-        <v>2.35742044448853</v>
+        <v>2.35742020606995</v>
       </c>
       <c r="H2027" t="n">
         <v>51251800</v>
@@ -59210,7 +59210,7 @@
         <v>2.99900007247925</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.31876158714294</v>
+        <v>2.31876134872437</v>
       </c>
       <c r="H2029" t="n">
         <v>17461139</v>
@@ -59239,7 +59239,7 @@
         <v>3.0789999961853</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.38061571121216</v>
+        <v>2.38061547279358</v>
       </c>
       <c r="H2030" t="n">
         <v>33067746</v>
@@ -59268,7 +59268,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.3643786907196</v>
+        <v>2.36437892913818</v>
       </c>
       <c r="H2031" t="n">
         <v>14604732</v>
@@ -59326,7 +59326,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37442994117737</v>
+        <v>2.37443017959595</v>
       </c>
       <c r="H2033" t="n">
         <v>6292252</v>
@@ -59384,7 +59384,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.38757419586182</v>
+        <v>2.3875744342804</v>
       </c>
       <c r="H2035" t="n">
         <v>9119120</v>
@@ -59529,7 +59529,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.5777759552002</v>
+        <v>2.57777619361877</v>
       </c>
       <c r="H2040" t="n">
         <v>21608685</v>
@@ -59558,7 +59558,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.61334228515625</v>
+        <v>2.61334252357483</v>
       </c>
       <c r="H2041" t="n">
         <v>21815059</v>
@@ -59587,7 +59587,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597308158875</v>
+        <v>2.52597284317017</v>
       </c>
       <c r="H2042" t="n">
         <v>27175102</v>
@@ -59616,7 +59616,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.5252001285553</v>
+        <v>2.52519989013672</v>
       </c>
       <c r="H2043" t="n">
         <v>14675290</v>
@@ -59674,7 +59674,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.44710898399353</v>
+        <v>2.44710874557495</v>
       </c>
       <c r="H2045" t="n">
         <v>15281373</v>
@@ -59848,7 +59848,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.49891209602356</v>
+        <v>2.49891185760498</v>
       </c>
       <c r="H2051" t="n">
         <v>12882380</v>
@@ -59877,7 +59877,7 @@
         <v>3.22900009155273</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.49659252166748</v>
+        <v>2.4965922832489</v>
       </c>
       <c r="H2052" t="n">
         <v>21135868</v>
@@ -59906,7 +59906,7 @@
         <v>3.38899993896484</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.62030076980591</v>
+        <v>2.62030053138733</v>
       </c>
       <c r="H2053" t="n">
         <v>38395558</v>
@@ -60051,7 +60051,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.52983927726746</v>
+        <v>2.52983903884888</v>
       </c>
       <c r="H2058" t="n">
         <v>17041685</v>
@@ -60370,7 +60370,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.75792622566223</v>
+        <v>2.75792646408081</v>
       </c>
       <c r="H2069" t="n">
         <v>27477458</v>
@@ -60399,7 +60399,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467970848083</v>
+        <v>2.72467994689941</v>
       </c>
       <c r="H2070" t="n">
         <v>14759944</v>
@@ -60428,7 +60428,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.69452595710754</v>
+        <v>2.69452571868896</v>
       </c>
       <c r="H2071" t="n">
         <v>16175878</v>
@@ -60515,7 +60515,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.83137845993042</v>
+        <v>2.83137822151184</v>
       </c>
       <c r="H2074" t="n">
         <v>31284132</v>
@@ -60892,7 +60892,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2087" t="n">
-        <v>3.14219617843628</v>
+        <v>3.14219641685486</v>
       </c>
       <c r="H2087" t="n">
         <v>30756951</v>
@@ -60979,7 +60979,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.23188447952271</v>
+        <v>3.23188471794128</v>
       </c>
       <c r="H2090" t="n">
         <v>36447686</v>
@@ -61066,7 +61066,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.36487150192261</v>
+        <v>3.36487126350403</v>
       </c>
       <c r="H2093" t="n">
         <v>20421753</v>
@@ -61153,7 +61153,7 @@
         <v>4.20900011062622</v>
       </c>
       <c r="G2096" t="n">
-        <v>3.25430703163147</v>
+        <v>3.25430679321289</v>
       </c>
       <c r="H2096" t="n">
         <v>12157528</v>
@@ -61327,7 +61327,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2102" t="n">
-        <v>3.23343133926392</v>
+        <v>3.23343110084534</v>
       </c>
       <c r="H2102" t="n">
         <v>15820699</v>
@@ -61675,7 +61675,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693434715271</v>
+        <v>3.31693458557129</v>
       </c>
       <c r="H2114" t="n">
         <v>22785909</v>
@@ -61704,7 +61704,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.40739607810974</v>
+        <v>3.40739631652832</v>
       </c>
       <c r="H2115" t="n">
         <v>25716222</v>
@@ -61791,7 +61791,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G2118" t="n">
-        <v>3.48471426963806</v>
+        <v>3.48471403121948</v>
       </c>
       <c r="H2118" t="n">
         <v>28093096</v>
@@ -61820,7 +61820,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G2119" t="n">
-        <v>3.47466254234314</v>
+        <v>3.47466278076172</v>
       </c>
       <c r="H2119" t="n">
         <v>18482624</v>
@@ -61849,7 +61849,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2120" t="n">
-        <v>3.51796054840088</v>
+        <v>3.51796078681946</v>
       </c>
       <c r="H2120" t="n">
         <v>24621349</v>
@@ -61878,7 +61878,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.69811105728149</v>
+        <v>3.69811153411865</v>
       </c>
       <c r="H2121" t="n">
         <v>32155461</v>
@@ -61907,7 +61907,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409482955933</v>
+        <v>3.51409506797791</v>
       </c>
       <c r="H2122" t="n">
         <v>36014819</v>
@@ -61936,7 +61936,7 @@
         <v>4.61299991607666</v>
       </c>
       <c r="G2123" t="n">
-        <v>3.56667041778564</v>
+        <v>3.56667065620422</v>
       </c>
       <c r="H2123" t="n">
         <v>15663428</v>
@@ -62023,7 +62023,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.62002015113831</v>
+        <v>3.62002038955688</v>
       </c>
       <c r="H2126" t="n">
         <v>19618847</v>
@@ -62139,7 +62139,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G2130" t="n">
-        <v>3.90145683288574</v>
+        <v>3.9014573097229</v>
       </c>
       <c r="H2130" t="n">
         <v>31985059</v>
@@ -80125,6 +80125,35 @@
         <v>6625854</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>10.7700004577637</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>10.9899997711182</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>10.7580003738403</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>10.9540004730225</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>10.9540004730225</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>5223132</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>10.9840002059937</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>10.8240003585815</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>10.8760004043579</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>10.8760004043579</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>5545530</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2369.1689453125</v>
       </c>
       <c r="G3" t="n">
-        <v>1831.78967285156</v>
+        <v>1831.78979492188</v>
       </c>
       <c r="H3" t="n">
         <v>30489</v>
@@ -514,7 +514,7 @@
         <v>2208.72412109375</v>
       </c>
       <c r="G5" t="n">
-        <v>1707.73718261719</v>
+        <v>1707.7373046875</v>
       </c>
       <c r="H5" t="n">
         <v>38406</v>
@@ -659,7 +659,7 @@
         <v>2005.56311035156</v>
       </c>
       <c r="G10" t="n">
-        <v>1550.65771484375</v>
+        <v>1550.65759277344</v>
       </c>
       <c r="H10" t="n">
         <v>43759</v>
@@ -746,7 +746,7 @@
         <v>1365.86657714844</v>
       </c>
       <c r="G13" t="n">
-        <v>1056.05810546875</v>
+        <v>1056.05822753906</v>
       </c>
       <c r="H13" t="n">
         <v>75020</v>
@@ -891,7 +891,7 @@
         <v>1464.84240722656</v>
       </c>
       <c r="G18" t="n">
-        <v>1132.58410644531</v>
+        <v>1132.58422851562</v>
       </c>
       <c r="H18" t="n">
         <v>55490</v>
@@ -920,7 +920,7 @@
         <v>1481.51208496094</v>
       </c>
       <c r="G19" t="n">
-        <v>1145.47290039062</v>
+        <v>1145.47277832031</v>
       </c>
       <c r="H19" t="n">
         <v>52360</v>
@@ -978,7 +978,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14123535156</v>
+        <v>1068.14135742188</v>
       </c>
       <c r="H21" t="n">
         <v>67666</v>
@@ -1036,7 +1036,7 @@
         <v>1218.96557617188</v>
       </c>
       <c r="G23" t="n">
-        <v>942.477478027344</v>
+        <v>942.4775390625</v>
       </c>
       <c r="H23" t="n">
         <v>56261</v>
@@ -1384,7 +1384,7 @@
         <v>1077.27392578125</v>
       </c>
       <c r="G35" t="n">
-        <v>832.924682617188</v>
+        <v>832.924621582031</v>
       </c>
       <c r="H35" t="n">
         <v>48406</v>
@@ -1529,7 +1529,7 @@
         <v>1079.35754394531</v>
       </c>
       <c r="G40" t="n">
-        <v>834.535705566406</v>
+        <v>834.53564453125</v>
       </c>
       <c r="H40" t="n">
         <v>38826</v>
@@ -1790,7 +1790,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G49" t="n">
-        <v>853.868591308594</v>
+        <v>853.86865234375</v>
       </c>
       <c r="H49" t="n">
         <v>45335</v>
@@ -1819,7 +1819,7 @@
         <v>1104.36206054688</v>
       </c>
       <c r="G50" t="n">
-        <v>853.868591308594</v>
+        <v>853.86865234375</v>
       </c>
       <c r="H50" t="n">
         <v>70901</v>
@@ -1848,7 +1848,7 @@
         <v>1200.21228027344</v>
       </c>
       <c r="G51" t="n">
-        <v>927.977905273438</v>
+        <v>927.977966308594</v>
       </c>
       <c r="H51" t="n">
         <v>78651</v>
@@ -1964,7 +1964,7 @@
         <v>1193.96118164062</v>
       </c>
       <c r="G55" t="n">
-        <v>923.144714355469</v>
+        <v>923.144775390625</v>
       </c>
       <c r="H55" t="n">
         <v>43553</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254211425781</v>
+        <v>997.254150390625</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2051,7 +2051,7 @@
         <v>1259.59777832031</v>
       </c>
       <c r="G58" t="n">
-        <v>973.893493652344</v>
+        <v>973.8935546875</v>
       </c>
       <c r="H58" t="n">
         <v>36967</v>
@@ -2080,7 +2080,7 @@
         <v>1241.88635253906</v>
       </c>
       <c r="G59" t="n">
-        <v>960.199462890625</v>
+        <v>960.199401855469</v>
       </c>
       <c r="H59" t="n">
         <v>31218</v>
@@ -2196,7 +2196,7 @@
         <v>1048.10205078125</v>
       </c>
       <c r="G63" t="n">
-        <v>810.369567871094</v>
+        <v>810.36962890625</v>
       </c>
       <c r="H63" t="n">
         <v>77981</v>
@@ -2283,7 +2283,7 @@
         <v>962.670288085938</v>
       </c>
       <c r="G66" t="n">
-        <v>744.315612792969</v>
+        <v>744.315673828125</v>
       </c>
       <c r="H66" t="n">
         <v>36197</v>
@@ -2370,7 +2370,7 @@
         <v>980.381713867188</v>
       </c>
       <c r="G69" t="n">
-        <v>758.009765625</v>
+        <v>758.009704589844</v>
       </c>
       <c r="H69" t="n">
         <v>52413</v>
@@ -2428,7 +2428,7 @@
         <v>1088.73425292969</v>
       </c>
       <c r="G71" t="n">
-        <v>841.785522460938</v>
+        <v>841.785583496094</v>
       </c>
       <c r="H71" t="n">
         <v>71518</v>
@@ -2486,7 +2486,7 @@
         <v>1227.30041503906</v>
       </c>
       <c r="G73" t="n">
-        <v>948.921875</v>
+        <v>948.921813964844</v>
       </c>
       <c r="H73" t="n">
         <v>64701</v>
@@ -2515,7 +2515,7 @@
         <v>1251.26293945312</v>
       </c>
       <c r="G74" t="n">
-        <v>967.44921875</v>
+        <v>967.449157714844</v>
       </c>
       <c r="H74" t="n">
         <v>42225</v>
@@ -2602,7 +2602,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86303710938</v>
+        <v>1085.86315917969</v>
       </c>
       <c r="H77" t="n">
         <v>60062</v>
@@ -2631,7 +2631,7 @@
         <v>1441.92175292969</v>
       </c>
       <c r="G78" t="n">
-        <v>1114.8623046875</v>
+        <v>1114.86242675781</v>
       </c>
       <c r="H78" t="n">
         <v>56991</v>
@@ -2660,7 +2660,7 @@
         <v>1421.08471679688</v>
       </c>
       <c r="G79" t="n">
-        <v>1098.75158691406</v>
+        <v>1098.75170898438</v>
       </c>
       <c r="H79" t="n">
         <v>33838</v>
@@ -2805,7 +2805,7 @@
         <v>1472.13537597656</v>
       </c>
       <c r="G84" t="n">
-        <v>1138.22290039062</v>
+        <v>1138.22302246094</v>
       </c>
       <c r="H84" t="n">
         <v>42537</v>
@@ -2892,7 +2892,7 @@
         <v>1267.9326171875</v>
       </c>
       <c r="G87" t="n">
-        <v>980.337768554688</v>
+        <v>980.337829589844</v>
       </c>
       <c r="H87" t="n">
         <v>37678</v>
@@ -2979,7 +2979,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G90" t="n">
-        <v>965.032653808594</v>
+        <v>965.032592773438</v>
       </c>
       <c r="H90" t="n">
         <v>33396</v>
@@ -3008,7 +3008,7 @@
         <v>1208.54711914062</v>
       </c>
       <c r="G91" t="n">
-        <v>934.422302246094</v>
+        <v>934.422241210938</v>
       </c>
       <c r="H91" t="n">
         <v>37385</v>
@@ -3327,7 +3327,7 @@
         <v>1293.97888183594</v>
       </c>
       <c r="G102" t="n">
-        <v>1000.47625732422</v>
+        <v>1000.47619628906</v>
       </c>
       <c r="H102" t="n">
         <v>46119</v>
@@ -3443,7 +3443,7 @@
         <v>1298.14624023438</v>
       </c>
       <c r="G106" t="n">
-        <v>1003.6982421875</v>
+        <v>1003.69836425781</v>
       </c>
       <c r="H106" t="n">
         <v>20322</v>
@@ -3472,7 +3472,7 @@
         <v>1248.13745117188</v>
       </c>
       <c r="G107" t="n">
-        <v>965.032653808594</v>
+        <v>965.032592773438</v>
       </c>
       <c r="H107" t="n">
         <v>26277</v>
@@ -3501,7 +3501,7 @@
         <v>1274.18371582031</v>
       </c>
       <c r="G108" t="n">
-        <v>985.170959472656</v>
+        <v>985.171020507812</v>
       </c>
       <c r="H108" t="n">
         <v>32082</v>
@@ -3530,7 +3530,7 @@
         <v>1214.79821777344</v>
       </c>
       <c r="G109" t="n">
-        <v>939.255493164062</v>
+        <v>939.255554199219</v>
       </c>
       <c r="H109" t="n">
         <v>27462</v>
@@ -3617,7 +3617,7 @@
         <v>1256.47229003906</v>
       </c>
       <c r="G112" t="n">
-        <v>971.476928710938</v>
+        <v>971.476989746094</v>
       </c>
       <c r="H112" t="n">
         <v>17386</v>
@@ -3646,7 +3646,7 @@
         <v>1231.4677734375</v>
       </c>
       <c r="G113" t="n">
-        <v>952.14404296875</v>
+        <v>952.143981933594</v>
       </c>
       <c r="H113" t="n">
         <v>14885</v>
@@ -3675,7 +3675,7 @@
         <v>1151.24523925781</v>
       </c>
       <c r="G114" t="n">
-        <v>890.11767578125</v>
+        <v>890.117614746094</v>
       </c>
       <c r="H114" t="n">
         <v>28584</v>
@@ -3762,7 +3762,7 @@
         <v>1038.10021972656</v>
       </c>
       <c r="G117" t="n">
-        <v>802.636474609375</v>
+        <v>802.636413574219</v>
       </c>
       <c r="H117" t="n">
         <v>30134</v>
@@ -3791,7 +3791,7 @@
         <v>1003.30242919922</v>
       </c>
       <c r="G118" t="n">
-        <v>775.731567382812</v>
+        <v>775.731506347656</v>
       </c>
       <c r="H118" t="n">
         <v>34176</v>
@@ -3965,7 +3965,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749267578125</v>
+        <v>731.749328613281</v>
       </c>
       <c r="H124" t="n">
         <v>64325</v>
@@ -4226,7 +4226,7 @@
         <v>552.181030273438</v>
       </c>
       <c r="G133" t="n">
-        <v>426.934295654297</v>
+        <v>426.934326171875</v>
       </c>
       <c r="H133" t="n">
         <v>49476</v>
@@ -4255,7 +4255,7 @@
         <v>582.394653320312</v>
       </c>
       <c r="G134" t="n">
-        <v>450.294830322266</v>
+        <v>450.294860839844</v>
       </c>
       <c r="H134" t="n">
         <v>57016</v>
@@ -4284,7 +4284,7 @@
         <v>622.818481445312</v>
       </c>
       <c r="G135" t="n">
-        <v>481.549652099609</v>
+        <v>481.549682617188</v>
       </c>
       <c r="H135" t="n">
         <v>39529</v>
@@ -4313,7 +4313,7 @@
         <v>645.947570800781</v>
       </c>
       <c r="G136" t="n">
-        <v>499.432556152344</v>
+        <v>499.432525634766</v>
       </c>
       <c r="H136" t="n">
         <v>59299</v>
@@ -4400,7 +4400,7 @@
         <v>709.083740234375</v>
       </c>
       <c r="G139" t="n">
-        <v>548.248046875</v>
+        <v>548.248107910156</v>
       </c>
       <c r="H139" t="n">
         <v>39413</v>
@@ -4458,7 +4458,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.537658691406</v>
+        <v>520.53759765625</v>
       </c>
       <c r="H141" t="n">
         <v>36777</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710052490234</v>
+        <v>510.710083007812</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4661,7 +4661,7 @@
         <v>604.273559570312</v>
       </c>
       <c r="G148" t="n">
-        <v>467.211151123047</v>
+        <v>467.211120605469</v>
       </c>
       <c r="H148" t="n">
         <v>26200</v>
@@ -4690,7 +4690,7 @@
         <v>642.196899414062</v>
       </c>
       <c r="G149" t="n">
-        <v>496.532592773438</v>
+        <v>496.532623291016</v>
       </c>
       <c r="H149" t="n">
         <v>46906</v>
@@ -4719,7 +4719,7 @@
         <v>645.947570800781</v>
       </c>
       <c r="G150" t="n">
-        <v>499.432556152344</v>
+        <v>499.432525634766</v>
       </c>
       <c r="H150" t="n">
         <v>48364</v>
@@ -4806,7 +4806,7 @@
         <v>539.678771972656</v>
       </c>
       <c r="G153" t="n">
-        <v>417.267852783203</v>
+        <v>417.267822265625</v>
       </c>
       <c r="H153" t="n">
         <v>31277</v>
@@ -4835,7 +4835,7 @@
         <v>531.135620117188</v>
       </c>
       <c r="G154" t="n">
-        <v>410.662475585938</v>
+        <v>410.662445068359</v>
       </c>
       <c r="H154" t="n">
         <v>36401</v>
@@ -4922,7 +4922,7 @@
         <v>515.299499511719</v>
       </c>
       <c r="G157" t="n">
-        <v>398.418334960938</v>
+        <v>398.418304443359</v>
       </c>
       <c r="H157" t="n">
         <v>17072</v>
@@ -4951,7 +4951,7 @@
         <v>516.549682617188</v>
       </c>
       <c r="G158" t="n">
-        <v>399.384948730469</v>
+        <v>399.384918212891</v>
       </c>
       <c r="H158" t="n">
         <v>11284</v>
@@ -5125,7 +5125,7 @@
         <v>477.58447265625</v>
       </c>
       <c r="G164" t="n">
-        <v>369.257904052734</v>
+        <v>369.257873535156</v>
       </c>
       <c r="H164" t="n">
         <v>11396</v>
@@ -5212,7 +5212,7 @@
         <v>490.50341796875</v>
       </c>
       <c r="G167" t="n">
-        <v>379.246551513672</v>
+        <v>379.246520996094</v>
       </c>
       <c r="H167" t="n">
         <v>15313</v>
@@ -5357,7 +5357,7 @@
         <v>498.629852294922</v>
       </c>
       <c r="G172" t="n">
-        <v>385.529724121094</v>
+        <v>385.529693603516</v>
       </c>
       <c r="H172" t="n">
         <v>21623</v>
@@ -5473,7 +5473,7 @@
         <v>491.545288085938</v>
       </c>
       <c r="G176" t="n">
-        <v>380.052062988281</v>
+        <v>380.052093505859</v>
       </c>
       <c r="H176" t="n">
         <v>10221</v>
@@ -5560,7 +5560,7 @@
         <v>481.126770019531</v>
       </c>
       <c r="G179" t="n">
-        <v>371.996704101562</v>
+        <v>371.996734619141</v>
       </c>
       <c r="H179" t="n">
         <v>19101</v>
@@ -5618,7 +5618,7 @@
         <v>466.749237060547</v>
       </c>
       <c r="G181" t="n">
-        <v>360.880310058594</v>
+        <v>360.880340576172</v>
       </c>
       <c r="H181" t="n">
         <v>25529</v>
@@ -5734,7 +5734,7 @@
         <v>390.069000244141</v>
       </c>
       <c r="G185" t="n">
-        <v>301.592834472656</v>
+        <v>301.592864990234</v>
       </c>
       <c r="H185" t="n">
         <v>38113</v>
@@ -5821,7 +5821,7 @@
         <v>392.569427490234</v>
       </c>
       <c r="G188" t="n">
-        <v>303.526092529297</v>
+        <v>303.526123046875</v>
       </c>
       <c r="H188" t="n">
         <v>15965</v>
@@ -5850,7 +5850,7 @@
         <v>398.195434570312</v>
       </c>
       <c r="G189" t="n">
-        <v>307.876007080078</v>
+        <v>307.876037597656</v>
       </c>
       <c r="H189" t="n">
         <v>25724</v>
@@ -5937,7 +5937,7 @@
         <v>392.361053466797</v>
       </c>
       <c r="G192" t="n">
-        <v>303.364990234375</v>
+        <v>303.365020751953</v>
       </c>
       <c r="H192" t="n">
         <v>11171</v>
@@ -5995,7 +5995,7 @@
         <v>381.942565917969</v>
       </c>
       <c r="G194" t="n">
-        <v>295.309631347656</v>
+        <v>295.309661865234</v>
       </c>
       <c r="H194" t="n">
         <v>11584</v>
@@ -6053,7 +6053,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843353271484</v>
+        <v>279.843322753906</v>
       </c>
       <c r="H196" t="n">
         <v>54804</v>
@@ -6285,7 +6285,7 @@
         <v>360.897155761719</v>
       </c>
       <c r="G204" t="n">
-        <v>279.037780761719</v>
+        <v>279.037811279297</v>
       </c>
       <c r="H204" t="n">
         <v>13463</v>
@@ -6401,7 +6401,7 @@
         <v>563.641357421875</v>
       </c>
       <c r="G208" t="n">
-        <v>435.795166015625</v>
+        <v>435.795196533203</v>
       </c>
       <c r="H208" t="n">
         <v>168620</v>
@@ -6430,7 +6430,7 @@
         <v>723.044555664062</v>
       </c>
       <c r="G209" t="n">
-        <v>559.042236328125</v>
+        <v>559.042297363281</v>
       </c>
       <c r="H209" t="n">
         <v>206944</v>
@@ -6662,7 +6662,7 @@
         <v>484.0439453125</v>
       </c>
       <c r="G217" t="n">
-        <v>374.252227783203</v>
+        <v>374.252197265625</v>
       </c>
       <c r="H217" t="n">
         <v>29696</v>
@@ -6691,7 +6691,7 @@
         <v>439.661102294922</v>
       </c>
       <c r="G218" t="n">
-        <v>339.936340332031</v>
+        <v>339.936370849609</v>
       </c>
       <c r="H218" t="n">
         <v>64785</v>
@@ -6894,7 +6894,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829254150391</v>
+        <v>405.829223632812</v>
       </c>
       <c r="H225" t="n">
         <v>74636</v>
@@ -6952,7 +6952,7 @@
         <v>495.712677001953</v>
       </c>
       <c r="G227" t="n">
-        <v>383.274230957031</v>
+        <v>383.274200439453</v>
       </c>
       <c r="H227" t="n">
         <v>36344</v>
@@ -6981,7 +6981,7 @@
         <v>492.587127685547</v>
       </c>
       <c r="G228" t="n">
-        <v>380.857604980469</v>
+        <v>380.857635498047</v>
       </c>
       <c r="H228" t="n">
         <v>55438</v>
@@ -7010,7 +7010,7 @@
         <v>469.666412353516</v>
       </c>
       <c r="G229" t="n">
-        <v>363.135803222656</v>
+        <v>363.135833740234</v>
       </c>
       <c r="H229" t="n">
         <v>34267</v>
@@ -7184,7 +7184,7 @@
         <v>421.949615478516</v>
       </c>
       <c r="G235" t="n">
-        <v>326.242218017578</v>
+        <v>326.242248535156</v>
       </c>
       <c r="H235" t="n">
         <v>85324</v>
@@ -7387,7 +7387,7 @@
         <v>454.246978759766</v>
       </c>
       <c r="G242" t="n">
-        <v>351.2138671875</v>
+        <v>351.213836669922</v>
       </c>
       <c r="H242" t="n">
         <v>104991</v>
@@ -7532,7 +7532,7 @@
         <v>430.492767333984</v>
       </c>
       <c r="G247" t="n">
-        <v>332.847625732422</v>
+        <v>332.847595214844</v>
       </c>
       <c r="H247" t="n">
         <v>82950</v>
@@ -7561,7 +7561,7 @@
         <v>436.118774414062</v>
       </c>
       <c r="G248" t="n">
-        <v>337.197540283203</v>
+        <v>337.197509765625</v>
       </c>
       <c r="H248" t="n">
         <v>78353</v>
@@ -7590,7 +7590,7 @@
         <v>387.985260009766</v>
       </c>
       <c r="G249" t="n">
-        <v>299.981750488281</v>
+        <v>299.981719970703</v>
       </c>
       <c r="H249" t="n">
         <v>107400</v>
@@ -7677,7 +7677,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G252" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H252" t="n">
         <v>181498</v>
@@ -7706,7 +7706,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G253" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G254" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G255" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G256" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G257" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G258" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G259" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G260" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G261" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G262" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G263" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G264" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G265" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G266" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G267" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G268" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G269" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G270" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G271" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G272" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G273" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G274" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G275" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G276" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G277" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G278" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G279" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G280" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G281" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G282" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G283" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G284" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G285" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G286" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G287" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G288" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G289" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G290" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G291" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G292" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G293" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G294" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G295" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G296" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G297" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G298" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G299" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G300" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G301" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G302" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G303" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G304" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G305" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G306" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G307" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G308" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G309" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G310" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G311" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G312" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G313" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G314" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G315" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G316" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G317" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G318" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G319" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G320" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G321" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G322" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G323" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G324" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G325" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G326" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G327" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G328" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G329" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G330" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G331" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G332" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G333" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G334" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G335" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G336" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G337" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G338" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G339" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G340" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G341" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G342" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G343" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G344" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G345" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G346" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G347" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G348" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G349" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G350" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G351" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G352" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G353" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G354" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G355" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G356" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G357" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G358" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G359" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G360" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G361" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G362" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G363" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G364" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G365" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G366" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G367" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G368" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G369" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G370" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G371" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G372" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G373" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G374" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G375" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G376" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G377" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G378" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G379" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G380" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G381" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G382" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G383" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G384" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G385" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G386" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G387" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G388" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G389" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G390" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G391" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G392" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G393" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G394" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G395" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G396" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G397" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G398" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G399" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G400" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G401" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G402" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G403" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G404" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G405" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G406" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G407" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G408" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G409" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G410" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G411" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G412" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G413" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G414" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G415" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G416" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G417" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G418" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G419" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G420" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G421" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G422" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G423" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G424" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G425" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G426" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G427" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G428" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G429" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G430" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G431" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G432" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G433" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G434" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G435" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G436" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G437" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G438" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G439" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G440" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G441" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G442" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G443" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G444" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G445" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G446" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G447" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G448" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G449" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G450" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G451" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G452" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G453" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G454" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G455" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G456" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G457" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G458" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G459" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G460" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G461" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G462" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G463" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G464" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>314.222229003906</v>
       </c>
       <c r="G465" t="n">
-        <v>242.949783325195</v>
+        <v>242.949768066406</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>98.6841125488281</v>
       </c>
       <c r="G468" t="n">
-        <v>76.3003997802734</v>
+        <v>76.300407409668</v>
       </c>
       <c r="H468" t="n">
         <v>232423</v>
@@ -13970,7 +13970,7 @@
         <v>97.3505477905273</v>
       </c>
       <c r="G469" t="n">
-        <v>75.2693099975586</v>
+        <v>75.2693176269531</v>
       </c>
       <c r="H469" t="n">
         <v>139388</v>
@@ -14028,7 +14028,7 @@
         <v>97.5172424316406</v>
       </c>
       <c r="G471" t="n">
-        <v>75.3982009887695</v>
+        <v>75.3982086181641</v>
       </c>
       <c r="H471" t="n">
         <v>60497</v>
@@ -14115,7 +14115,7 @@
         <v>93.7249069213867</v>
       </c>
       <c r="G474" t="n">
-        <v>72.4660491943359</v>
+        <v>72.4660568237305</v>
       </c>
       <c r="H474" t="n">
         <v>152747</v>
@@ -14144,7 +14144,7 @@
         <v>93.6832275390625</v>
       </c>
       <c r="G475" t="n">
-        <v>72.4338226318359</v>
+        <v>72.4338302612305</v>
       </c>
       <c r="H475" t="n">
         <v>148288</v>
@@ -14318,7 +14318,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.2264366149902</v>
+        <v>56.226432800293</v>
       </c>
       <c r="H481" t="n">
         <v>308433</v>
@@ -14347,7 +14347,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.9064903259277</v>
+        <v>53.906494140625</v>
       </c>
       <c r="H482" t="n">
         <v>255815</v>
@@ -14405,7 +14405,7 @@
         <v>85.6401443481445</v>
       </c>
       <c r="G484" t="n">
-        <v>66.2150955200195</v>
+        <v>66.215087890625</v>
       </c>
       <c r="H484" t="n">
         <v>473567</v>
@@ -14434,7 +14434,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G485" t="n">
-        <v>63.154052734375</v>
+        <v>63.1540489196777</v>
       </c>
       <c r="H485" t="n">
         <v>461818</v>
@@ -14579,7 +14579,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906692504883</v>
+        <v>64.9906768798828</v>
       </c>
       <c r="H490" t="n">
         <v>123807</v>
@@ -14608,7 +14608,7 @@
         <v>83.9731826782227</v>
       </c>
       <c r="G491" t="n">
-        <v>64.9262390136719</v>
+        <v>64.9262313842773</v>
       </c>
       <c r="H491" t="n">
         <v>97304</v>
@@ -14695,7 +14695,7 @@
         <v>81.6811065673828</v>
       </c>
       <c r="G494" t="n">
-        <v>63.154052734375</v>
+        <v>63.1540489196777</v>
       </c>
       <c r="H494" t="n">
         <v>82320</v>
@@ -14724,7 +14724,7 @@
         <v>82.3062210083008</v>
       </c>
       <c r="G495" t="n">
-        <v>63.6373748779297</v>
+        <v>63.6373710632324</v>
       </c>
       <c r="H495" t="n">
         <v>41220</v>
@@ -14753,7 +14753,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G496" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318328857422</v>
       </c>
       <c r="H496" t="n">
         <v>50947</v>
@@ -14782,7 +14782,7 @@
         <v>80.4725646972656</v>
       </c>
       <c r="G497" t="n">
-        <v>62.2196273803711</v>
+        <v>62.2196311950684</v>
       </c>
       <c r="H497" t="n">
         <v>56838</v>
@@ -14840,7 +14840,7 @@
         <v>80.4308853149414</v>
       </c>
       <c r="G499" t="n">
-        <v>62.1874046325684</v>
+        <v>62.1874084472656</v>
       </c>
       <c r="H499" t="n">
         <v>32132</v>
@@ -14869,7 +14869,7 @@
         <v>80.1391677856445</v>
       </c>
       <c r="G500" t="n">
-        <v>61.9618606567383</v>
+        <v>61.961856842041</v>
       </c>
       <c r="H500" t="n">
         <v>52866</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563148498535</v>
+        <v>61.1563186645508</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -14927,7 +14927,7 @@
         <v>78.430534362793</v>
       </c>
       <c r="G502" t="n">
-        <v>60.6407814025879</v>
+        <v>60.6407775878906</v>
       </c>
       <c r="H502" t="n">
         <v>45614</v>
@@ -14985,7 +14985,7 @@
         <v>80.0974960327148</v>
       </c>
       <c r="G504" t="n">
-        <v>61.9296379089355</v>
+        <v>61.9296340942383</v>
       </c>
       <c r="H504" t="n">
         <v>38478</v>
@@ -15014,7 +15014,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G505" t="n">
-        <v>62.6707344055176</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H505" t="n">
         <v>57550</v>
@@ -15188,7 +15188,7 @@
         <v>81.5560836791992</v>
       </c>
       <c r="G511" t="n">
-        <v>63.0573844909668</v>
+        <v>63.0573883056641</v>
       </c>
       <c r="H511" t="n">
         <v>34562</v>
@@ -15217,7 +15217,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G512" t="n">
-        <v>62.6707344055176</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H512" t="n">
         <v>22428</v>
@@ -15246,7 +15246,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.4129524230957</v>
+        <v>62.4129486083984</v>
       </c>
       <c r="H513" t="n">
         <v>27484</v>
@@ -15304,7 +15304,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G515" t="n">
-        <v>62.6707344055176</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H515" t="n">
         <v>30486</v>
@@ -15362,7 +15362,7 @@
         <v>80.0141448974609</v>
       </c>
       <c r="G517" t="n">
-        <v>61.8651885986328</v>
+        <v>61.8651962280273</v>
       </c>
       <c r="H517" t="n">
         <v>45464</v>
@@ -15449,7 +15449,7 @@
         <v>83.7231369018555</v>
       </c>
       <c r="G520" t="n">
-        <v>64.7328948974609</v>
+        <v>64.7329025268555</v>
       </c>
       <c r="H520" t="n">
         <v>131635</v>
@@ -15507,7 +15507,7 @@
         <v>82.3478927612305</v>
       </c>
       <c r="G522" t="n">
-        <v>63.6695861816406</v>
+        <v>63.6695899963379</v>
       </c>
       <c r="H522" t="n">
         <v>52551</v>
@@ -15565,7 +15565,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G524" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318328857422</v>
       </c>
       <c r="H524" t="n">
         <v>49745</v>
@@ -15594,7 +15594,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G525" t="n">
-        <v>62.6707344055176</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H525" t="n">
         <v>40067</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184944152832</v>
+        <v>63.2184982299805</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15652,7 +15652,7 @@
         <v>81.0559997558594</v>
       </c>
       <c r="G527" t="n">
-        <v>62.6707344055176</v>
+        <v>62.670726776123</v>
       </c>
       <c r="H527" t="n">
         <v>45359</v>
@@ -15681,7 +15681,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G528" t="n">
-        <v>62.8318290710449</v>
+        <v>62.8318328857422</v>
       </c>
       <c r="H528" t="n">
         <v>57552</v>
@@ -15797,7 +15797,7 @@
         <v>78.8055953979492</v>
       </c>
       <c r="G532" t="n">
-        <v>60.9307632446289</v>
+        <v>60.9307670593262</v>
       </c>
       <c r="H532" t="n">
         <v>101055</v>
@@ -15826,7 +15826,7 @@
         <v>78.7639236450195</v>
       </c>
       <c r="G533" t="n">
-        <v>60.8985481262207</v>
+        <v>60.8985443115234</v>
       </c>
       <c r="H533" t="n">
         <v>102976</v>
@@ -15942,7 +15942,7 @@
         <v>77.6803970336914</v>
       </c>
       <c r="G537" t="n">
-        <v>60.060791015625</v>
+        <v>60.0607872009277</v>
       </c>
       <c r="H537" t="n">
         <v>142371</v>
@@ -15971,7 +15971,7 @@
         <v>78.1388168334961</v>
       </c>
       <c r="G538" t="n">
-        <v>60.4152297973633</v>
+        <v>60.4152221679688</v>
       </c>
       <c r="H538" t="n">
         <v>64920</v>
@@ -16000,7 +16000,7 @@
         <v>76.0967864990234</v>
       </c>
       <c r="G539" t="n">
-        <v>58.8363761901855</v>
+        <v>58.8363800048828</v>
       </c>
       <c r="H539" t="n">
         <v>77063</v>
@@ -16029,7 +16029,7 @@
         <v>78.7639236450195</v>
       </c>
       <c r="G540" t="n">
-        <v>60.8985481262207</v>
+        <v>60.8985443115234</v>
       </c>
       <c r="H540" t="n">
         <v>63710</v>
@@ -16058,7 +16058,7 @@
         <v>74.8048934936523</v>
       </c>
       <c r="G541" t="n">
-        <v>57.8375091552734</v>
+        <v>57.8375129699707</v>
       </c>
       <c r="H541" t="n">
         <v>169917</v>
@@ -16087,7 +16087,7 @@
         <v>70.8458557128906</v>
       </c>
       <c r="G542" t="n">
-        <v>54.7764663696289</v>
+        <v>54.7764701843262</v>
       </c>
       <c r="H542" t="n">
         <v>196506</v>
@@ -16145,7 +16145,7 @@
         <v>71.8877105712891</v>
       </c>
       <c r="G544" t="n">
-        <v>55.5820045471191</v>
+        <v>55.5820083618164</v>
       </c>
       <c r="H544" t="n">
         <v>70492</v>
@@ -16174,7 +16174,7 @@
         <v>72.1377563476562</v>
       </c>
       <c r="G545" t="n">
-        <v>55.7753372192383</v>
+        <v>55.7753410339355</v>
       </c>
       <c r="H545" t="n">
         <v>35747</v>
@@ -16203,7 +16203,7 @@
         <v>71.7418518066406</v>
       </c>
       <c r="G546" t="n">
-        <v>55.4692344665527</v>
+        <v>55.4692306518555</v>
       </c>
       <c r="H546" t="n">
         <v>24192</v>
@@ -16261,7 +16261,7 @@
         <v>69.4706192016602</v>
       </c>
       <c r="G548" t="n">
-        <v>53.7131614685059</v>
+        <v>53.7131652832031</v>
       </c>
       <c r="H548" t="n">
         <v>52411</v>
@@ -16348,7 +16348,7 @@
         <v>67.2618942260742</v>
       </c>
       <c r="G551" t="n">
-        <v>52.0054321289062</v>
+        <v>52.005428314209</v>
       </c>
       <c r="H551" t="n">
         <v>83287</v>
@@ -16377,7 +16377,7 @@
         <v>67.3035659790039</v>
       </c>
       <c r="G552" t="n">
-        <v>52.0376472473145</v>
+        <v>52.0376510620117</v>
       </c>
       <c r="H552" t="n">
         <v>75893</v>
@@ -16493,7 +16493,7 @@
         <v>63.5529022216797</v>
       </c>
       <c r="G556" t="n">
-        <v>49.1377143859863</v>
+        <v>49.1377182006836</v>
       </c>
       <c r="H556" t="n">
         <v>55076</v>
@@ -16725,7 +16725,7 @@
         <v>63.8237838745117</v>
       </c>
       <c r="G564" t="n">
-        <v>49.3471565246582</v>
+        <v>49.3471527099609</v>
       </c>
       <c r="H564" t="n">
         <v>41188</v>
@@ -17015,7 +17015,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367866516113</v>
+        <v>41.4367904663086</v>
       </c>
       <c r="H574" t="n">
         <v>153152</v>
@@ -17102,7 +17102,7 @@
         <v>57.8435592651367</v>
       </c>
       <c r="G577" t="n">
-        <v>44.7233772277832</v>
+        <v>44.7233734130859</v>
       </c>
       <c r="H577" t="n">
         <v>304629</v>
@@ -17160,7 +17160,7 @@
         <v>58.9687576293945</v>
       </c>
       <c r="G579" t="n">
-        <v>45.5933532714844</v>
+        <v>45.5933570861816</v>
       </c>
       <c r="H579" t="n">
         <v>215665</v>
@@ -17247,7 +17247,7 @@
         <v>56.2391090393066</v>
       </c>
       <c r="G582" t="n">
-        <v>43.4828491210938</v>
+        <v>43.482852935791</v>
       </c>
       <c r="H582" t="n">
         <v>113949</v>
@@ -17276,7 +17276,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767425537109</v>
       </c>
       <c r="H583" t="n">
         <v>160680</v>
@@ -17334,7 +17334,7 @@
         <v>55.5306510925293</v>
       </c>
       <c r="G585" t="n">
-        <v>42.9350891113281</v>
+        <v>42.9350852966309</v>
       </c>
       <c r="H585" t="n">
         <v>117880</v>
@@ -17624,7 +17624,7 @@
         <v>55.6348342895508</v>
       </c>
       <c r="G595" t="n">
-        <v>43.0156402587891</v>
+        <v>43.0156364440918</v>
       </c>
       <c r="H595" t="n">
         <v>43278</v>
@@ -17653,7 +17653,7 @@
         <v>56.2599449157715</v>
       </c>
       <c r="G596" t="n">
-        <v>43.4989624023438</v>
+        <v>43.4989585876465</v>
       </c>
       <c r="H596" t="n">
         <v>59156</v>
@@ -17885,7 +17885,7 @@
         <v>67.3035659790039</v>
       </c>
       <c r="G604" t="n">
-        <v>52.0376472473145</v>
+        <v>52.0376510620117</v>
       </c>
       <c r="H604" t="n">
         <v>379106</v>
@@ -17943,7 +17943,7 @@
         <v>60.9066009521484</v>
       </c>
       <c r="G606" t="n">
-        <v>47.0916519165039</v>
+        <v>47.0916557312012</v>
       </c>
       <c r="H606" t="n">
         <v>628237</v>
@@ -18059,7 +18059,7 @@
         <v>59.1771278381348</v>
       </c>
       <c r="G610" t="n">
-        <v>45.754467010498</v>
+        <v>45.7544631958008</v>
       </c>
       <c r="H610" t="n">
         <v>95657</v>
@@ -18233,7 +18233,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767425537109</v>
       </c>
       <c r="H616" t="n">
         <v>281053</v>
@@ -18262,7 +18262,7 @@
         <v>55.6348342895508</v>
       </c>
       <c r="G617" t="n">
-        <v>43.0156402587891</v>
+        <v>43.0156364440918</v>
       </c>
       <c r="H617" t="n">
         <v>190893</v>
@@ -18349,7 +18349,7 @@
         <v>59.1771278381348</v>
       </c>
       <c r="G620" t="n">
-        <v>45.754467010498</v>
+        <v>45.7544631958008</v>
       </c>
       <c r="H620" t="n">
         <v>121797</v>
@@ -18668,7 +18668,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767463684082</v>
+        <v>43.1767425537109</v>
       </c>
       <c r="H631" t="n">
         <v>46391</v>
@@ -18755,7 +18755,7 @@
         <v>53.1135559082031</v>
       </c>
       <c r="G634" t="n">
-        <v>41.0662460327148</v>
+        <v>41.0662422180176</v>
       </c>
       <c r="H634" t="n">
         <v>54253</v>
@@ -18813,7 +18813,7 @@
         <v>52.2175636291504</v>
       </c>
       <c r="G636" t="n">
-        <v>40.373477935791</v>
+        <v>40.3734817504883</v>
       </c>
       <c r="H636" t="n">
         <v>90143</v>
@@ -18958,7 +18958,7 @@
         <v>51.6132926940918</v>
       </c>
       <c r="G641" t="n">
-        <v>39.9062728881836</v>
+        <v>39.9062690734863</v>
       </c>
       <c r="H641" t="n">
         <v>47114</v>
@@ -19045,7 +19045,7 @@
         <v>51.1965522766113</v>
       </c>
       <c r="G644" t="n">
-        <v>39.5840606689453</v>
+        <v>39.584056854248</v>
       </c>
       <c r="H644" t="n">
         <v>56401</v>
@@ -19074,7 +19074,7 @@
         <v>50.6339530944824</v>
       </c>
       <c r="G645" t="n">
-        <v>39.1490669250488</v>
+        <v>39.1490631103516</v>
       </c>
       <c r="H645" t="n">
         <v>34642</v>
@@ -19132,7 +19132,7 @@
         <v>50.4255828857422</v>
       </c>
       <c r="G647" t="n">
-        <v>38.9879608154297</v>
+        <v>38.9879570007324</v>
       </c>
       <c r="H647" t="n">
         <v>33718</v>
@@ -19277,7 +19277,7 @@
         <v>50.0088424682617</v>
       </c>
       <c r="G652" t="n">
-        <v>38.6657447814941</v>
+        <v>38.6657485961914</v>
       </c>
       <c r="H652" t="n">
         <v>24569</v>
@@ -19335,7 +19335,7 @@
         <v>50.0088424682617</v>
       </c>
       <c r="G654" t="n">
-        <v>38.6657447814941</v>
+        <v>38.6657485961914</v>
       </c>
       <c r="H654" t="n">
         <v>54520</v>
@@ -19364,7 +19364,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.0374298095703</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H655" t="n">
         <v>34543</v>
@@ -19422,7 +19422,7 @@
         <v>52.071704864502</v>
       </c>
       <c r="G657" t="n">
-        <v>40.2607040405273</v>
+        <v>40.2607078552246</v>
       </c>
       <c r="H657" t="n">
         <v>248665</v>
@@ -19509,7 +19509,7 @@
         <v>54.1762466430664</v>
       </c>
       <c r="G660" t="n">
-        <v>41.8878898620605</v>
+        <v>41.8878936767578</v>
       </c>
       <c r="H660" t="n">
         <v>68284</v>
@@ -19567,7 +19567,7 @@
         <v>50.6339530944824</v>
       </c>
       <c r="G662" t="n">
-        <v>39.1490669250488</v>
+        <v>39.1490631103516</v>
       </c>
       <c r="H662" t="n">
         <v>400900</v>
@@ -19596,7 +19596,7 @@
         <v>49.3628921508789</v>
       </c>
       <c r="G663" t="n">
-        <v>38.1663131713867</v>
+        <v>38.1663093566895</v>
       </c>
       <c r="H663" t="n">
         <v>91978</v>
@@ -19625,7 +19625,7 @@
         <v>50.4255828857422</v>
       </c>
       <c r="G664" t="n">
-        <v>38.9879608154297</v>
+        <v>38.9879570007324</v>
       </c>
       <c r="H664" t="n">
         <v>60973</v>
@@ -19683,7 +19683,7 @@
         <v>49.5921020507812</v>
       </c>
       <c r="G666" t="n">
-        <v>38.3435287475586</v>
+        <v>38.3435325622559</v>
       </c>
       <c r="H666" t="n">
         <v>29704</v>
@@ -19770,7 +19770,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G669" t="n">
-        <v>35.4435958862305</v>
+        <v>35.4435997009277</v>
       </c>
       <c r="H669" t="n">
         <v>39954</v>
@@ -19828,7 +19828,7 @@
         <v>45.841438293457</v>
       </c>
       <c r="G671" t="n">
-        <v>35.4435958862305</v>
+        <v>35.4435997009277</v>
       </c>
       <c r="H671" t="n">
         <v>76441</v>
@@ -19915,7 +19915,7 @@
         <v>45.9247856140137</v>
       </c>
       <c r="G674" t="n">
-        <v>35.5080375671387</v>
+        <v>35.5080413818359</v>
       </c>
       <c r="H674" t="n">
         <v>38417</v>
@@ -20089,7 +20089,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580787658691</v>
+        <v>34.0580749511719</v>
       </c>
       <c r="H680" t="n">
         <v>49600</v>
@@ -20118,7 +20118,7 @@
         <v>43.132625579834</v>
       </c>
       <c r="G681" t="n">
-        <v>33.3492050170898</v>
+        <v>33.3492012023926</v>
       </c>
       <c r="H681" t="n">
         <v>52451</v>
@@ -20147,7 +20147,7 @@
         <v>44.507869720459</v>
       </c>
       <c r="G682" t="n">
-        <v>34.4125137329102</v>
+        <v>34.4125099182129</v>
       </c>
       <c r="H682" t="n">
         <v>55885</v>
@@ -20321,7 +20321,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.0374298095703</v>
+        <v>38.037425994873</v>
       </c>
       <c r="H688" t="n">
         <v>118566</v>
@@ -20379,7 +20379,7 @@
         <v>47.1958427429199</v>
       </c>
       <c r="G690" t="n">
-        <v>36.4907989501953</v>
+        <v>36.490795135498</v>
       </c>
       <c r="H690" t="n">
         <v>97677</v>
@@ -20727,7 +20727,7 @@
         <v>44.8412628173828</v>
       </c>
       <c r="G702" t="n">
-        <v>34.6702842712402</v>
+        <v>34.6702880859375</v>
       </c>
       <c r="H702" t="n">
         <v>58496</v>
@@ -20872,7 +20872,7 @@
         <v>40.1008377075195</v>
       </c>
       <c r="G707" t="n">
-        <v>31.0050926208496</v>
+        <v>31.005090713501</v>
       </c>
       <c r="H707" t="n">
         <v>128220</v>
@@ -20901,7 +20901,7 @@
         <v>39.3715438842773</v>
       </c>
       <c r="G708" t="n">
-        <v>30.441219329834</v>
+        <v>30.4412174224854</v>
       </c>
       <c r="H708" t="n">
         <v>153302</v>
@@ -21104,7 +21104,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532451629639</v>
+        <v>26.9532470703125</v>
       </c>
       <c r="H715" t="n">
         <v>100245</v>
@@ -21133,7 +21133,7 @@
         <v>33.1412773132324</v>
       </c>
       <c r="G716" t="n">
-        <v>25.6241130828857</v>
+        <v>25.6241111755371</v>
       </c>
       <c r="H716" t="n">
         <v>204453</v>
@@ -21191,7 +21191,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766651153564</v>
+        <v>23.3766632080078</v>
       </c>
       <c r="H718" t="n">
         <v>180004</v>
@@ -21220,7 +21220,7 @@
         <v>28.5467128753662</v>
       </c>
       <c r="G719" t="n">
-        <v>22.0716972351074</v>
+        <v>22.0716953277588</v>
       </c>
       <c r="H719" t="n">
         <v>144762</v>
@@ -21249,7 +21249,7 @@
         <v>29.2864265441895</v>
       </c>
       <c r="G720" t="n">
-        <v>22.6436233520508</v>
+        <v>22.6436252593994</v>
       </c>
       <c r="H720" t="n">
         <v>183232</v>
@@ -21307,7 +21307,7 @@
         <v>31.7764511108398</v>
       </c>
       <c r="G722" t="n">
-        <v>24.5688571929932</v>
+        <v>24.5688591003418</v>
       </c>
       <c r="H722" t="n">
         <v>227745</v>
@@ -21394,7 +21394,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G725" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H725" t="n">
         <v>79264</v>
@@ -21452,7 +21452,7 @@
         <v>32.3598861694336</v>
       </c>
       <c r="G727" t="n">
-        <v>25.0199565887451</v>
+        <v>25.0199584960938</v>
       </c>
       <c r="H727" t="n">
         <v>103399</v>
@@ -21481,7 +21481,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480266571045</v>
+        <v>24.4480285644531</v>
       </c>
       <c r="H728" t="n">
         <v>59503</v>
@@ -21568,7 +21568,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G731" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H731" t="n">
         <v>152132</v>
@@ -21771,7 +21771,7 @@
         <v>27.8174171447754</v>
       </c>
       <c r="G738" t="n">
-        <v>21.5078201293945</v>
+        <v>21.5078182220459</v>
       </c>
       <c r="H738" t="n">
         <v>74571</v>
@@ -21800,7 +21800,7 @@
         <v>28.7863388061523</v>
       </c>
       <c r="G739" t="n">
-        <v>22.2569675445557</v>
+        <v>22.2569694519043</v>
       </c>
       <c r="H739" t="n">
         <v>68543</v>
@@ -22090,7 +22090,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782302856445</v>
+        <v>27.6782283782959</v>
       </c>
       <c r="H749" t="n">
         <v>99834</v>
@@ -22119,7 +22119,7 @@
         <v>33.3809013366699</v>
       </c>
       <c r="G750" t="n">
-        <v>25.8093852996826</v>
+        <v>25.809383392334</v>
       </c>
       <c r="H750" t="n">
         <v>76706</v>
@@ -22148,7 +22148,7 @@
         <v>33.9330825805664</v>
       </c>
       <c r="G751" t="n">
-        <v>26.2363166809082</v>
+        <v>26.2363185882568</v>
       </c>
       <c r="H751" t="n">
         <v>69130</v>
@@ -22177,7 +22177,7 @@
         <v>33.2037887573242</v>
       </c>
       <c r="G752" t="n">
-        <v>25.6724433898926</v>
+        <v>25.6724452972412</v>
       </c>
       <c r="H752" t="n">
         <v>107022</v>
@@ -22322,7 +22322,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077529907227</v>
       </c>
       <c r="H757" t="n">
         <v>41825</v>
@@ -22380,7 +22380,7 @@
         <v>31.5055694580078</v>
       </c>
       <c r="G759" t="n">
-        <v>24.3594188690186</v>
+        <v>24.3594169616699</v>
       </c>
       <c r="H759" t="n">
         <v>65014</v>
@@ -22409,7 +22409,7 @@
         <v>31.2451076507568</v>
       </c>
       <c r="G760" t="n">
-        <v>24.1580333709717</v>
+        <v>24.1580352783203</v>
       </c>
       <c r="H760" t="n">
         <v>71582</v>
@@ -22525,7 +22525,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G764" t="n">
-        <v>24.6494121551514</v>
+        <v>24.6494102478027</v>
       </c>
       <c r="H764" t="n">
         <v>57921</v>
@@ -22670,7 +22670,7 @@
         <v>31.6618461608887</v>
       </c>
       <c r="G769" t="n">
-        <v>24.4802494049072</v>
+        <v>24.4802474975586</v>
       </c>
       <c r="H769" t="n">
         <v>65021</v>
@@ -22699,7 +22699,7 @@
         <v>31.8181247711182</v>
       </c>
       <c r="G770" t="n">
-        <v>24.6010780334473</v>
+        <v>24.6010799407959</v>
       </c>
       <c r="H770" t="n">
         <v>51778</v>
@@ -22902,7 +22902,7 @@
         <v>25.4107418060303</v>
       </c>
       <c r="G777" t="n">
-        <v>19.647029876709</v>
+        <v>19.6470317840576</v>
       </c>
       <c r="H777" t="n">
         <v>103123</v>
@@ -22960,7 +22960,7 @@
         <v>25.5461826324463</v>
       </c>
       <c r="G779" t="n">
-        <v>19.7517490386963</v>
+        <v>19.7517509460449</v>
       </c>
       <c r="H779" t="n">
         <v>108228</v>
@@ -23018,7 +23018,7 @@
         <v>25.8795757293701</v>
       </c>
       <c r="G781" t="n">
-        <v>20.009521484375</v>
+        <v>20.0095233917236</v>
       </c>
       <c r="H781" t="n">
         <v>68304</v>
@@ -23192,7 +23192,7 @@
         <v>24.9523277282715</v>
       </c>
       <c r="G787" t="n">
-        <v>19.2925930023193</v>
+        <v>19.292594909668</v>
       </c>
       <c r="H787" t="n">
         <v>67521</v>
@@ -23221,7 +23221,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G788" t="n">
-        <v>19.3328704833984</v>
+        <v>19.3328723907471</v>
       </c>
       <c r="H788" t="n">
         <v>72501</v>
@@ -23250,7 +23250,7 @@
         <v>25.7962265014648</v>
       </c>
       <c r="G789" t="n">
-        <v>19.9450778961182</v>
+        <v>19.9450798034668</v>
       </c>
       <c r="H789" t="n">
         <v>147656</v>
@@ -23366,7 +23366,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883712768555</v>
       </c>
       <c r="H793" t="n">
         <v>765447</v>
@@ -23395,7 +23395,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G794" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H794" t="n">
         <v>554437</v>
@@ -23424,7 +23424,7 @@
         <v>27.7653255462646</v>
       </c>
       <c r="G795" t="n">
-        <v>21.4675445556641</v>
+        <v>21.4675426483154</v>
       </c>
       <c r="H795" t="n">
         <v>207446</v>
@@ -23511,7 +23511,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083866119385</v>
+        <v>21.0083885192871</v>
       </c>
       <c r="H798" t="n">
         <v>100025</v>
@@ -23714,7 +23714,7 @@
         <v>28.3695983886719</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9347534179688</v>
+        <v>21.9347553253174</v>
       </c>
       <c r="H805" t="n">
         <v>225218</v>
@@ -23743,7 +23743,7 @@
         <v>27.9841136932373</v>
       </c>
       <c r="G806" t="n">
-        <v>21.6367053985596</v>
+        <v>21.6367073059082</v>
       </c>
       <c r="H806" t="n">
         <v>111838</v>
@@ -23801,7 +23801,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883712768555</v>
       </c>
       <c r="H808" t="n">
         <v>86623</v>
@@ -23917,7 +23917,7 @@
         <v>27.1297950744629</v>
       </c>
       <c r="G812" t="n">
-        <v>20.9761657714844</v>
+        <v>20.9761638641357</v>
       </c>
       <c r="H812" t="n">
         <v>42335</v>
@@ -24004,7 +24004,7 @@
         <v>26.4630126953125</v>
       </c>
       <c r="G815" t="n">
-        <v>20.4606227874756</v>
+        <v>20.4606246948242</v>
       </c>
       <c r="H815" t="n">
         <v>66042</v>
@@ -24033,7 +24033,7 @@
         <v>26.4109191894531</v>
       </c>
       <c r="G816" t="n">
-        <v>20.4203453063965</v>
+        <v>20.4203472137451</v>
       </c>
       <c r="H816" t="n">
         <v>121401</v>
@@ -24062,7 +24062,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908916473389</v>
+        <v>20.7908897399902</v>
       </c>
       <c r="H817" t="n">
         <v>135708</v>
@@ -24178,7 +24178,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5009002685547</v>
+        <v>20.5008983612061</v>
       </c>
       <c r="H821" t="n">
         <v>75021</v>
@@ -24207,7 +24207,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G822" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H822" t="n">
         <v>72133</v>
@@ -24323,7 +24323,7 @@
         <v>25.9420852661133</v>
       </c>
       <c r="G826" t="n">
-        <v>20.0578536987305</v>
+        <v>20.0578517913818</v>
       </c>
       <c r="H826" t="n">
         <v>46026</v>
@@ -24439,7 +24439,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G830" t="n">
-        <v>20.4284000396729</v>
+        <v>20.4284019470215</v>
       </c>
       <c r="H830" t="n">
         <v>56424</v>
@@ -24497,7 +24497,7 @@
         <v>26.4213371276855</v>
       </c>
       <c r="G832" t="n">
-        <v>20.4284000396729</v>
+        <v>20.4284019470215</v>
       </c>
       <c r="H832" t="n">
         <v>33693</v>
@@ -24613,7 +24613,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883712768555</v>
       </c>
       <c r="H836" t="n">
         <v>263799</v>
@@ -24700,7 +24700,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G839" t="n">
-        <v>22.4583549499512</v>
+        <v>22.4583530426025</v>
       </c>
       <c r="H839" t="n">
         <v>174253</v>
@@ -24729,7 +24729,7 @@
         <v>29.0884761810303</v>
       </c>
       <c r="G840" t="n">
-        <v>22.4905757904053</v>
+        <v>22.4905738830566</v>
       </c>
       <c r="H840" t="n">
         <v>136313</v>
@@ -24758,7 +24758,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G841" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H841" t="n">
         <v>67797</v>
@@ -24787,7 +24787,7 @@
         <v>27.671558380127</v>
       </c>
       <c r="G842" t="n">
-        <v>21.3950462341309</v>
+        <v>21.3950443267822</v>
       </c>
       <c r="H842" t="n">
         <v>78494</v>
@@ -24932,7 +24932,7 @@
         <v>27.9841136932373</v>
       </c>
       <c r="G847" t="n">
-        <v>21.6367053985596</v>
+        <v>21.6367073059082</v>
       </c>
       <c r="H847" t="n">
         <v>78060</v>
@@ -24961,7 +24961,7 @@
         <v>28.3800163269043</v>
       </c>
       <c r="G848" t="n">
-        <v>21.9428100585938</v>
+        <v>21.9428081512451</v>
       </c>
       <c r="H848" t="n">
         <v>228370</v>
@@ -25077,7 +25077,7 @@
         <v>25.4003238677979</v>
       </c>
       <c r="G852" t="n">
-        <v>19.6389770507812</v>
+        <v>19.6389751434326</v>
       </c>
       <c r="H852" t="n">
         <v>205905</v>
@@ -25106,7 +25106,7 @@
         <v>25.3169765472412</v>
       </c>
       <c r="G853" t="n">
-        <v>19.5745334625244</v>
+        <v>19.5745315551758</v>
       </c>
       <c r="H853" t="n">
         <v>88528</v>
@@ -25338,7 +25338,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G861" t="n">
-        <v>18.124568939209</v>
+        <v>18.1245670318604</v>
       </c>
       <c r="H861" t="n">
         <v>98341</v>
@@ -25396,7 +25396,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G863" t="n">
-        <v>17.8667964935303</v>
+        <v>17.8667945861816</v>
       </c>
       <c r="H863" t="n">
         <v>69191</v>
@@ -25425,7 +25425,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G864" t="n">
-        <v>17.770133972168</v>
+        <v>17.7701320648193</v>
       </c>
       <c r="H864" t="n">
         <v>36909</v>
@@ -25483,7 +25483,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G866" t="n">
-        <v>17.1418113708496</v>
+        <v>17.1418132781982</v>
       </c>
       <c r="H866" t="n">
         <v>41924</v>
@@ -25570,7 +25570,7 @@
         <v>21.4829635620117</v>
       </c>
       <c r="G869" t="n">
-        <v>16.6101589202881</v>
+        <v>16.6101570129395</v>
       </c>
       <c r="H869" t="n">
         <v>57928</v>
@@ -25599,7 +25599,7 @@
         <v>21.6079864501953</v>
       </c>
       <c r="G870" t="n">
-        <v>16.7068252563477</v>
+        <v>16.706823348999</v>
       </c>
       <c r="H870" t="n">
         <v>102649</v>
@@ -25628,7 +25628,7 @@
         <v>21.1704082489014</v>
       </c>
       <c r="G871" t="n">
-        <v>16.3684959411621</v>
+        <v>16.3684978485107</v>
       </c>
       <c r="H871" t="n">
         <v>85174</v>
@@ -25976,7 +25976,7 @@
         <v>22.2539348602295</v>
       </c>
       <c r="G883" t="n">
-        <v>17.2062568664551</v>
+        <v>17.2062549591064</v>
       </c>
       <c r="H883" t="n">
         <v>82411</v>
@@ -26063,7 +26063,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290393829346</v>
+        <v>17.0290374755859</v>
       </c>
       <c r="H886" t="n">
         <v>60342</v>
@@ -26150,7 +26150,7 @@
         <v>23.4624805450439</v>
       </c>
       <c r="G889" t="n">
-        <v>18.1406764984131</v>
+        <v>18.1406784057617</v>
       </c>
       <c r="H889" t="n">
         <v>284480</v>
@@ -26353,7 +26353,7 @@
         <v>35.1520462036133</v>
       </c>
       <c r="G896" t="n">
-        <v>27.1787948608398</v>
+        <v>27.1787929534912</v>
       </c>
       <c r="H896" t="n">
         <v>688052</v>
@@ -26411,7 +26411,7 @@
         <v>35.4854393005371</v>
       </c>
       <c r="G898" t="n">
-        <v>27.4365673065186</v>
+        <v>27.4365653991699</v>
       </c>
       <c r="H898" t="n">
         <v>324224</v>
@@ -26498,7 +26498,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G901" t="n">
-        <v>26.1154880523682</v>
+        <v>26.1154899597168</v>
       </c>
       <c r="H901" t="n">
         <v>172580</v>
@@ -26527,7 +26527,7 @@
         <v>33.4642486572266</v>
       </c>
       <c r="G902" t="n">
-        <v>25.8738269805908</v>
+        <v>25.8738250732422</v>
       </c>
       <c r="H902" t="n">
         <v>95164</v>
@@ -26643,7 +26643,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G906" t="n">
-        <v>23.8922061920166</v>
+        <v>23.8922080993652</v>
       </c>
       <c r="H906" t="n">
         <v>165007</v>
@@ -26701,7 +26701,7 @@
         <v>29.9427947998047</v>
       </c>
       <c r="G908" t="n">
-        <v>23.1511154174805</v>
+        <v>23.1511173248291</v>
       </c>
       <c r="H908" t="n">
         <v>158585</v>
@@ -26759,7 +26759,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G910" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H910" t="n">
         <v>231966</v>
@@ -26904,7 +26904,7 @@
         <v>26.7547302246094</v>
       </c>
       <c r="G915" t="n">
-        <v>20.6861724853516</v>
+        <v>20.6861743927002</v>
       </c>
       <c r="H915" t="n">
         <v>108233</v>
@@ -26933,7 +26933,7 @@
         <v>26.4630126953125</v>
       </c>
       <c r="G916" t="n">
-        <v>20.4606227874756</v>
+        <v>20.4606246948242</v>
       </c>
       <c r="H916" t="n">
         <v>120821</v>
@@ -27310,7 +27310,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.6850395202637</v>
+        <v>21.685037612915</v>
       </c>
       <c r="H929" t="n">
         <v>97800</v>
@@ -27339,7 +27339,7 @@
         <v>28.0674629211426</v>
       </c>
       <c r="G930" t="n">
-        <v>21.7011489868164</v>
+        <v>21.701150894165</v>
       </c>
       <c r="H930" t="n">
         <v>138426</v>
@@ -27368,7 +27368,7 @@
         <v>31.7556133270264</v>
       </c>
       <c r="G931" t="n">
-        <v>24.5527477264404</v>
+        <v>24.5527458190918</v>
       </c>
       <c r="H931" t="n">
         <v>595323</v>
@@ -27629,7 +27629,7 @@
         <v>33.4434127807617</v>
       </c>
       <c r="G940" t="n">
-        <v>25.8577156066895</v>
+        <v>25.8577175140381</v>
       </c>
       <c r="H940" t="n">
         <v>218952</v>
@@ -27658,7 +27658,7 @@
         <v>33.651782989502</v>
       </c>
       <c r="G941" t="n">
-        <v>26.0188236236572</v>
+        <v>26.0188255310059</v>
       </c>
       <c r="H941" t="n">
         <v>233460</v>
@@ -27745,7 +27745,7 @@
         <v>33.7768058776855</v>
       </c>
       <c r="G944" t="n">
-        <v>26.1154880523682</v>
+        <v>26.1154899597168</v>
       </c>
       <c r="H944" t="n">
         <v>380608</v>
@@ -27861,7 +27861,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G948" t="n">
-        <v>25.0360717773438</v>
+        <v>25.0360698699951</v>
       </c>
       <c r="H948" t="n">
         <v>171000</v>
@@ -27948,7 +27948,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G951" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H951" t="n">
         <v>107978</v>
@@ -27977,7 +27977,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G952" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H952" t="n">
         <v>91792</v>
@@ -28035,7 +28035,7 @@
         <v>31.2138519287109</v>
       </c>
       <c r="G954" t="n">
-        <v>24.1338691711426</v>
+        <v>24.1338672637939</v>
       </c>
       <c r="H954" t="n">
         <v>110938</v>
@@ -28122,7 +28122,7 @@
         <v>31.3597106933594</v>
       </c>
       <c r="G957" t="n">
-        <v>24.2466430664062</v>
+        <v>24.2466449737549</v>
       </c>
       <c r="H957" t="n">
         <v>141695</v>
@@ -28151,7 +28151,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G958" t="n">
-        <v>23.9727630615234</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H958" t="n">
         <v>106089</v>
@@ -28209,7 +28209,7 @@
         <v>29.9427947998047</v>
       </c>
       <c r="G960" t="n">
-        <v>23.1511154174805</v>
+        <v>23.1511173248291</v>
       </c>
       <c r="H960" t="n">
         <v>82455</v>
@@ -28267,7 +28267,7 @@
         <v>30.9012966156006</v>
       </c>
       <c r="G962" t="n">
-        <v>23.8922061920166</v>
+        <v>23.8922080993652</v>
       </c>
       <c r="H962" t="n">
         <v>158871</v>
@@ -28325,7 +28325,7 @@
         <v>30.8596210479736</v>
       </c>
       <c r="G964" t="n">
-        <v>23.8599834442139</v>
+        <v>23.8599853515625</v>
       </c>
       <c r="H964" t="n">
         <v>96752</v>
@@ -28354,7 +28354,7 @@
         <v>31.3388748168945</v>
       </c>
       <c r="G965" t="n">
-        <v>24.2305355072021</v>
+        <v>24.2305335998535</v>
       </c>
       <c r="H965" t="n">
         <v>256042</v>
@@ -28412,7 +28412,7 @@
         <v>31.5055694580078</v>
       </c>
       <c r="G967" t="n">
-        <v>24.3594188690186</v>
+        <v>24.3594169616699</v>
       </c>
       <c r="H967" t="n">
         <v>130230</v>
@@ -28586,7 +28586,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G973" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H973" t="n">
         <v>61466</v>
@@ -28818,7 +28818,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.407751083374</v>
+        <v>24.4077529907227</v>
       </c>
       <c r="H981" t="n">
         <v>162326</v>
@@ -28905,7 +28905,7 @@
         <v>31.2138519287109</v>
       </c>
       <c r="G984" t="n">
-        <v>24.1338691711426</v>
+        <v>24.1338672637939</v>
       </c>
       <c r="H984" t="n">
         <v>84349</v>
@@ -29079,7 +29079,7 @@
         <v>30.4012088775635</v>
       </c>
       <c r="G990" t="n">
-        <v>23.5055503845215</v>
+        <v>23.5055522918701</v>
       </c>
       <c r="H990" t="n">
         <v>90326</v>
@@ -29166,7 +29166,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G993" t="n">
-        <v>23.5861034393311</v>
+        <v>23.5861015319824</v>
       </c>
       <c r="H993" t="n">
         <v>46714</v>
@@ -29195,7 +29195,7 @@
         <v>30.776273727417</v>
       </c>
       <c r="G994" t="n">
-        <v>23.7955436706543</v>
+        <v>23.7955417633057</v>
       </c>
       <c r="H994" t="n">
         <v>129866</v>
@@ -29224,7 +29224,7 @@
         <v>31.0054817199707</v>
       </c>
       <c r="G995" t="n">
-        <v>23.9727630615234</v>
+        <v>23.9727611541748</v>
       </c>
       <c r="H995" t="n">
         <v>242944</v>
@@ -29253,7 +29253,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G996" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H996" t="n">
         <v>84268</v>
@@ -29398,7 +29398,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1001" t="n">
-        <v>22.5227966308594</v>
+        <v>22.5227947235107</v>
       </c>
       <c r="H1001" t="n">
         <v>101377</v>
@@ -29485,7 +29485,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1004" t="n">
-        <v>23.086669921875</v>
+        <v>23.0866718292236</v>
       </c>
       <c r="H1004" t="n">
         <v>49988</v>
@@ -29572,7 +29572,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1007" t="n">
-        <v>22.7966766357422</v>
+        <v>22.7966785430908</v>
       </c>
       <c r="H1007" t="n">
         <v>90007</v>
@@ -29746,7 +29746,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1013" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1013" t="n">
         <v>50162</v>
@@ -29775,7 +29775,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1014" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1014" t="n">
         <v>48803</v>
@@ -29804,7 +29804,7 @@
         <v>29.1301498413086</v>
       </c>
       <c r="G1015" t="n">
-        <v>22.5227966308594</v>
+        <v>22.5227947235107</v>
       </c>
       <c r="H1015" t="n">
         <v>63776</v>
@@ -29862,7 +29862,7 @@
         <v>29.046802520752</v>
       </c>
       <c r="G1017" t="n">
-        <v>22.4583549499512</v>
+        <v>22.4583530426025</v>
       </c>
       <c r="H1017" t="n">
         <v>91048</v>
@@ -29920,7 +29920,7 @@
         <v>28.609224319458</v>
       </c>
       <c r="G1019" t="n">
-        <v>22.1200275421143</v>
+        <v>22.1200294494629</v>
       </c>
       <c r="H1019" t="n">
         <v>72155</v>
@@ -29949,7 +29949,7 @@
         <v>29.4843788146973</v>
       </c>
       <c r="G1020" t="n">
-        <v>22.7966766357422</v>
+        <v>22.7966785430908</v>
       </c>
       <c r="H1020" t="n">
         <v>127518</v>
@@ -29978,7 +29978,7 @@
         <v>29.9427947998047</v>
       </c>
       <c r="G1021" t="n">
-        <v>23.1511154174805</v>
+        <v>23.1511173248291</v>
       </c>
       <c r="H1021" t="n">
         <v>110137</v>
@@ -30123,7 +30123,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1026" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076839447021</v>
       </c>
       <c r="H1026" t="n">
         <v>378731</v>
@@ -30152,7 +30152,7 @@
         <v>35.5687866210938</v>
       </c>
       <c r="G1027" t="n">
-        <v>27.5010089874268</v>
+        <v>27.5010070800781</v>
       </c>
       <c r="H1027" t="n">
         <v>242772</v>
@@ -30210,7 +30210,7 @@
         <v>39.069408416748</v>
       </c>
       <c r="G1029" t="n">
-        <v>30.2076148986816</v>
+        <v>30.2076110839844</v>
       </c>
       <c r="H1029" t="n">
         <v>1179620</v>
@@ -30239,7 +30239,7 @@
         <v>38.9652214050293</v>
       </c>
       <c r="G1030" t="n">
-        <v>30.1270580291748</v>
+        <v>30.1270561218262</v>
       </c>
       <c r="H1030" t="n">
         <v>657786</v>
@@ -30326,7 +30326,7 @@
         <v>38.3192749023438</v>
       </c>
       <c r="G1033" t="n">
-        <v>29.6276245117188</v>
+        <v>29.6276264190674</v>
       </c>
       <c r="H1033" t="n">
         <v>422202</v>
@@ -30384,7 +30384,7 @@
         <v>37.73583984375</v>
       </c>
       <c r="G1035" t="n">
-        <v>29.1765270233154</v>
+        <v>29.1765289306641</v>
       </c>
       <c r="H1035" t="n">
         <v>228495</v>
@@ -30442,7 +30442,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1037" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076839447021</v>
       </c>
       <c r="H1037" t="n">
         <v>256721</v>
@@ -30471,7 +30471,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1038" t="n">
-        <v>27.3076820373535</v>
+        <v>27.3076839447021</v>
       </c>
       <c r="H1038" t="n">
         <v>147337</v>
@@ -30558,7 +30558,7 @@
         <v>37.9233703613281</v>
       </c>
       <c r="G1041" t="n">
-        <v>29.3215217590332</v>
+        <v>29.3215198516846</v>
       </c>
       <c r="H1041" t="n">
         <v>364128</v>
@@ -30732,7 +30732,7 @@
         <v>37.2149124145508</v>
       </c>
       <c r="G1047" t="n">
-        <v>28.7737598419189</v>
+        <v>28.7737579345703</v>
       </c>
       <c r="H1047" t="n">
         <v>145626</v>
@@ -30790,7 +30790,7 @@
         <v>39.4444732666016</v>
       </c>
       <c r="G1049" t="n">
-        <v>30.4976062774658</v>
+        <v>30.4976043701172</v>
       </c>
       <c r="H1049" t="n">
         <v>881669</v>
@@ -30906,7 +30906,7 @@
         <v>37.7566757202148</v>
       </c>
       <c r="G1053" t="n">
-        <v>29.1926383972168</v>
+        <v>29.1926364898682</v>
       </c>
       <c r="H1053" t="n">
         <v>774052</v>
@@ -30935,7 +30935,7 @@
         <v>38.7776908874512</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.9820613861084</v>
+        <v>29.982063293457</v>
       </c>
       <c r="H1054" t="n">
         <v>787822</v>
@@ -30964,7 +30964,7 @@
         <v>40.8405532836914</v>
       </c>
       <c r="G1055" t="n">
-        <v>31.5770263671875</v>
+        <v>31.5770244598389</v>
       </c>
       <c r="H1055" t="n">
         <v>622084</v>
@@ -30993,7 +30993,7 @@
         <v>39.3819618225098</v>
       </c>
       <c r="G1056" t="n">
-        <v>30.4492740631104</v>
+        <v>30.4492721557617</v>
       </c>
       <c r="H1056" t="n">
         <v>399174</v>
@@ -31051,7 +31051,7 @@
         <v>36.1313896179199</v>
       </c>
       <c r="G1058" t="n">
-        <v>27.9360027313232</v>
+        <v>27.9360008239746</v>
       </c>
       <c r="H1058" t="n">
         <v>542723</v>
@@ -31109,7 +31109,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610511779785</v>
+        <v>25.7610530853271</v>
       </c>
       <c r="H1060" t="n">
         <v>600964</v>
@@ -31167,7 +31167,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1062" t="n">
-        <v>23.0383396148682</v>
+        <v>23.0383377075195</v>
       </c>
       <c r="H1062" t="n">
         <v>516650</v>
@@ -31312,7 +31312,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728973388672</v>
+        <v>18.1728992462158</v>
       </c>
       <c r="H1067" t="n">
         <v>602051</v>
@@ -31428,7 +31428,7 @@
         <v>21.3787784576416</v>
       </c>
       <c r="G1071" t="n">
-        <v>16.5296058654785</v>
+        <v>16.5296039581299</v>
       </c>
       <c r="H1071" t="n">
         <v>217076</v>
@@ -31544,7 +31544,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1075" t="n">
-        <v>18.0440139770508</v>
+        <v>18.0440120697021</v>
       </c>
       <c r="H1075" t="n">
         <v>380243</v>
@@ -31602,7 +31602,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1077" t="n">
-        <v>17.8023548126221</v>
+        <v>17.8023529052734</v>
       </c>
       <c r="H1077" t="n">
         <v>235697</v>
@@ -31631,7 +31631,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1078" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1078" t="n">
         <v>133373</v>
@@ -31776,7 +31776,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1083" t="n">
-        <v>18.8495502471924</v>
+        <v>18.849552154541</v>
       </c>
       <c r="H1083" t="n">
         <v>133398</v>
@@ -31834,7 +31834,7 @@
         <v>24.5251693725586</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.9623260498047</v>
+        <v>18.9623241424561</v>
       </c>
       <c r="H1085" t="n">
         <v>121224</v>
@@ -31863,7 +31863,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1086" t="n">
         <v>126056</v>
@@ -31892,7 +31892,7 @@
         <v>24.5668430328369</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.9945468902588</v>
+        <v>18.9945487976074</v>
       </c>
       <c r="H1087" t="n">
         <v>102725</v>
@@ -32008,7 +32008,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1091" t="n">
         <v>40526</v>
@@ -32037,7 +32037,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1092" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1092" t="n">
         <v>95086</v>
@@ -32211,7 +32211,7 @@
         <v>23.4416446685791</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.124568939209</v>
+        <v>18.1245670318604</v>
       </c>
       <c r="H1098" t="n">
         <v>194444</v>
@@ -32385,7 +32385,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1104" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1104" t="n">
         <v>60478</v>
@@ -32414,7 +32414,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1105" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1105" t="n">
         <v>47186</v>
@@ -32443,7 +32443,7 @@
         <v>22.9832305908203</v>
       </c>
       <c r="G1106" t="n">
-        <v>17.770133972168</v>
+        <v>17.7701320648193</v>
       </c>
       <c r="H1106" t="n">
         <v>26540</v>
@@ -32559,7 +32559,7 @@
         <v>23.1082515716553</v>
       </c>
       <c r="G1110" t="n">
-        <v>17.8667964935303</v>
+        <v>17.8667945861816</v>
       </c>
       <c r="H1110" t="n">
         <v>49897</v>
@@ -32762,7 +32762,7 @@
         <v>22.8790454864502</v>
       </c>
       <c r="G1117" t="n">
-        <v>17.6895771026611</v>
+        <v>17.6895790100098</v>
       </c>
       <c r="H1117" t="n">
         <v>312068</v>
@@ -32849,7 +32849,7 @@
         <v>27.8174171447754</v>
       </c>
       <c r="G1120" t="n">
-        <v>21.5078201293945</v>
+        <v>21.5078182220459</v>
       </c>
       <c r="H1120" t="n">
         <v>741547</v>
@@ -32878,7 +32878,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883712768555</v>
       </c>
       <c r="H1121" t="n">
         <v>244265</v>
@@ -32965,7 +32965,7 @@
         <v>31.047155380249</v>
       </c>
       <c r="G1124" t="n">
-        <v>24.0049839019775</v>
+        <v>24.0049819946289</v>
       </c>
       <c r="H1124" t="n">
         <v>528373</v>
@@ -32994,7 +32994,7 @@
         <v>32.3807258605957</v>
       </c>
       <c r="G1125" t="n">
-        <v>25.0360717773438</v>
+        <v>25.0360698699951</v>
       </c>
       <c r="H1125" t="n">
         <v>445464</v>
@@ -33081,7 +33081,7 @@
         <v>28.4633655548096</v>
       </c>
       <c r="G1128" t="n">
-        <v>22.0072536468506</v>
+        <v>22.007251739502</v>
       </c>
       <c r="H1128" t="n">
         <v>243052</v>
@@ -33226,7 +33226,7 @@
         <v>31.0263175964355</v>
       </c>
       <c r="G1133" t="n">
-        <v>23.9888706207275</v>
+        <v>23.9888725280762</v>
       </c>
       <c r="H1133" t="n">
         <v>120603</v>
@@ -33748,7 +33748,7 @@
         <v>31.7764511108398</v>
       </c>
       <c r="G1151" t="n">
-        <v>24.5688571929932</v>
+        <v>24.5688591003418</v>
       </c>
       <c r="H1151" t="n">
         <v>53540</v>
@@ -33864,7 +33864,7 @@
         <v>37.5066299438477</v>
       </c>
       <c r="G1155" t="n">
-        <v>28.9993057250977</v>
+        <v>28.9993076324463</v>
       </c>
       <c r="H1155" t="n">
         <v>781786</v>
@@ -33893,7 +33893,7 @@
         <v>37.6524887084961</v>
       </c>
       <c r="G1156" t="n">
-        <v>29.1120834350586</v>
+        <v>29.11208152771</v>
       </c>
       <c r="H1156" t="n">
         <v>1160270</v>
@@ -33922,7 +33922,7 @@
         <v>40.2154426574707</v>
       </c>
       <c r="G1157" t="n">
-        <v>31.0937023162842</v>
+        <v>31.0937042236328</v>
       </c>
       <c r="H1157" t="n">
         <v>1079270</v>
@@ -33951,7 +33951,7 @@
         <v>38.8401985168457</v>
       </c>
       <c r="G1158" t="n">
-        <v>30.0303955078125</v>
+        <v>30.0303936004639</v>
       </c>
       <c r="H1158" t="n">
         <v>499559</v>
@@ -34038,7 +34038,7 @@
         <v>34.7353096008301</v>
       </c>
       <c r="G1161" t="n">
-        <v>26.8565807342529</v>
+        <v>26.8565826416016</v>
       </c>
       <c r="H1161" t="n">
         <v>155272</v>
@@ -34096,7 +34096,7 @@
         <v>31.88063621521</v>
       </c>
       <c r="G1163" t="n">
-        <v>24.6494121551514</v>
+        <v>24.6494102478027</v>
       </c>
       <c r="H1163" t="n">
         <v>167963</v>
@@ -34125,7 +34125,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655197143555</v>
+        <v>24.6655216217041</v>
       </c>
       <c r="H1164" t="n">
         <v>153075</v>
@@ -34241,7 +34241,7 @@
         <v>32.4432373046875</v>
       </c>
       <c r="G1168" t="n">
-        <v>25.0844020843506</v>
+        <v>25.0844039916992</v>
       </c>
       <c r="H1168" t="n">
         <v>285284</v>
@@ -34270,7 +34270,7 @@
         <v>30.3386974334717</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.4572200775146</v>
+        <v>23.457218170166</v>
       </c>
       <c r="H1169" t="n">
         <v>427776</v>
@@ -34357,7 +34357,7 @@
         <v>30.8804588317871</v>
       </c>
       <c r="G1172" t="n">
-        <v>23.8760967254639</v>
+        <v>23.8760948181152</v>
       </c>
       <c r="H1172" t="n">
         <v>225571</v>
@@ -34415,7 +34415,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1174" t="n">
-        <v>23.0383396148682</v>
+        <v>23.0383377075195</v>
       </c>
       <c r="H1174" t="n">
         <v>198986</v>
@@ -34560,7 +34560,7 @@
         <v>30.505392074585</v>
       </c>
       <c r="G1179" t="n">
-        <v>23.5861034393311</v>
+        <v>23.5861015319824</v>
       </c>
       <c r="H1179" t="n">
         <v>120513</v>
@@ -34618,7 +34618,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766651153564</v>
+        <v>23.3766632080078</v>
       </c>
       <c r="H1181" t="n">
         <v>179328</v>
@@ -34647,7 +34647,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.2316703796387</v>
+        <v>23.23166847229</v>
       </c>
       <c r="H1182" t="n">
         <v>79634</v>
@@ -34676,7 +34676,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.086669921875</v>
+        <v>23.0866718292236</v>
       </c>
       <c r="H1183" t="n">
         <v>53322</v>
@@ -34734,7 +34734,7 @@
         <v>29.8594455718994</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.086669921875</v>
+        <v>23.0866718292236</v>
       </c>
       <c r="H1185" t="n">
         <v>108022</v>
@@ -34792,7 +34792,7 @@
         <v>29.7969341278076</v>
       </c>
       <c r="G1187" t="n">
-        <v>23.0383396148682</v>
+        <v>23.0383377075195</v>
       </c>
       <c r="H1187" t="n">
         <v>68126</v>
@@ -34850,7 +34850,7 @@
         <v>29.8802814483643</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.1027812957764</v>
+        <v>23.1027793884277</v>
       </c>
       <c r="H1189" t="n">
         <v>102070</v>
@@ -34937,7 +34937,7 @@
         <v>29.4010314941406</v>
       </c>
       <c r="G1192" t="n">
-        <v>22.732234954834</v>
+        <v>22.7322368621826</v>
       </c>
       <c r="H1192" t="n">
         <v>80247</v>
@@ -35082,7 +35082,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1197" t="n">
         <v>53084</v>
@@ -35198,7 +35198,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883731842041</v>
+        <v>21.5883712768555</v>
       </c>
       <c r="H1201" t="n">
         <v>213623</v>
@@ -35256,7 +35256,7 @@
         <v>28.1299724578857</v>
       </c>
       <c r="G1203" t="n">
-        <v>21.7494812011719</v>
+        <v>21.7494792938232</v>
       </c>
       <c r="H1203" t="n">
         <v>72630</v>
@@ -35285,7 +35285,7 @@
         <v>28.5258750915527</v>
       </c>
       <c r="G1204" t="n">
-        <v>22.0555820465088</v>
+        <v>22.0555839538574</v>
       </c>
       <c r="H1204" t="n">
         <v>90794</v>
@@ -35314,7 +35314,7 @@
         <v>28.4008541107178</v>
       </c>
       <c r="G1205" t="n">
-        <v>21.9589195251465</v>
+        <v>21.9589214324951</v>
       </c>
       <c r="H1205" t="n">
         <v>82873</v>
@@ -35372,7 +35372,7 @@
         <v>28.9217796325684</v>
       </c>
       <c r="G1207" t="n">
-        <v>22.3616886138916</v>
+        <v>22.361686706543</v>
       </c>
       <c r="H1207" t="n">
         <v>83126</v>
@@ -35459,7 +35459,7 @@
         <v>28.5883865356445</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.1039180755615</v>
+        <v>22.1039161682129</v>
       </c>
       <c r="H1210" t="n">
         <v>66037</v>
@@ -35691,7 +35691,7 @@
         <v>24.8585605621338</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.2200965881348</v>
+        <v>19.2200946807861</v>
       </c>
       <c r="H1218" t="n">
         <v>227042</v>
@@ -35778,7 +35778,7 @@
         <v>24.0459175109863</v>
       </c>
       <c r="G1221" t="n">
-        <v>18.5917778015137</v>
+        <v>18.5917797088623</v>
       </c>
       <c r="H1221" t="n">
         <v>382349</v>
@@ -35865,7 +35865,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1224" t="n">
-        <v>18.8495502471924</v>
+        <v>18.849552154541</v>
       </c>
       <c r="H1224" t="n">
         <v>77151</v>
@@ -35894,7 +35894,7 @@
         <v>23.3791332244873</v>
       </c>
       <c r="G1225" t="n">
-        <v>18.0762348175049</v>
+        <v>18.0762367248535</v>
       </c>
       <c r="H1225" t="n">
         <v>105717</v>
@@ -36010,7 +36010,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1229" t="n">
-        <v>16.6584892272949</v>
+        <v>16.6584911346436</v>
       </c>
       <c r="H1229" t="n">
         <v>218937</v>
@@ -36039,7 +36039,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1230" t="n">
-        <v>18.0440139770508</v>
+        <v>18.0440120697021</v>
       </c>
       <c r="H1230" t="n">
         <v>356714</v>
@@ -36126,7 +36126,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1233" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1233" t="n">
         <v>394163</v>
@@ -36329,7 +36329,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1240" t="n">
-        <v>19.2684268951416</v>
+        <v>19.2684288024902</v>
       </c>
       <c r="H1240" t="n">
         <v>471979</v>
@@ -36474,7 +36474,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1245" t="n">
-        <v>20.0417423248291</v>
+        <v>20.0417442321777</v>
       </c>
       <c r="H1245" t="n">
         <v>379252</v>
@@ -36532,7 +36532,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G1247" t="n">
-        <v>19.3328704833984</v>
+        <v>19.3328723907471</v>
       </c>
       <c r="H1247" t="n">
         <v>451275</v>
@@ -36590,7 +36590,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728973388672</v>
+        <v>18.1728992462158</v>
       </c>
       <c r="H1249" t="n">
         <v>265701</v>
@@ -36648,7 +36648,7 @@
         <v>25.1086044311523</v>
       </c>
       <c r="G1251" t="n">
-        <v>19.413423538208</v>
+        <v>19.4134254455566</v>
       </c>
       <c r="H1251" t="n">
         <v>488244</v>
@@ -36677,7 +36677,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1252" t="n">
-        <v>18.8495502471924</v>
+        <v>18.849552154541</v>
       </c>
       <c r="H1252" t="n">
         <v>159678</v>
@@ -36764,7 +36764,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1255" t="n">
-        <v>18.0440139770508</v>
+        <v>18.0440120697021</v>
       </c>
       <c r="H1255" t="n">
         <v>260189</v>
@@ -36793,7 +36793,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1256" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1256" t="n">
         <v>220502</v>
@@ -36851,7 +36851,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1258" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1258" t="n">
         <v>197297</v>
@@ -36880,7 +36880,7 @@
         <v>22.9623928070068</v>
       </c>
       <c r="G1259" t="n">
-        <v>17.7540187835693</v>
+        <v>17.754020690918</v>
       </c>
       <c r="H1259" t="n">
         <v>142502</v>
@@ -37054,7 +37054,7 @@
         <v>21.962215423584</v>
       </c>
       <c r="G1265" t="n">
-        <v>16.9807033538818</v>
+        <v>16.9807052612305</v>
       </c>
       <c r="H1265" t="n">
         <v>177381</v>
@@ -37228,7 +37228,7 @@
         <v>21.5454750061035</v>
       </c>
       <c r="G1271" t="n">
-        <v>16.6584892272949</v>
+        <v>16.6584911346436</v>
       </c>
       <c r="H1271" t="n">
         <v>110209</v>
@@ -37605,7 +37605,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1284" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1284" t="n">
         <v>99256</v>
@@ -37634,7 +37634,7 @@
         <v>22.4414672851562</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.3512535095215</v>
+        <v>17.3512516021729</v>
       </c>
       <c r="H1285" t="n">
         <v>118092</v>
@@ -37721,7 +37721,7 @@
         <v>22.1080741882324</v>
       </c>
       <c r="G1288" t="n">
-        <v>17.0934810638428</v>
+        <v>17.0934791564941</v>
       </c>
       <c r="H1288" t="n">
         <v>71228</v>
@@ -37779,7 +37779,7 @@
         <v>21.5038013458252</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.6262683868408</v>
+        <v>16.6262702941895</v>
       </c>
       <c r="H1290" t="n">
         <v>126746</v>
@@ -37866,7 +37866,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801387786865</v>
+        <v>17.4801406860352</v>
       </c>
       <c r="H1293" t="n">
         <v>213107</v>
@@ -38040,7 +38040,7 @@
         <v>26.5255222320557</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.5089530944824</v>
+        <v>20.5089550018311</v>
       </c>
       <c r="H1299" t="n">
         <v>624530</v>
@@ -38185,7 +38185,7 @@
         <v>26.1087818145752</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.1867389678955</v>
+        <v>20.1867408752441</v>
       </c>
       <c r="H1304" t="n">
         <v>141753</v>
@@ -38272,7 +38272,7 @@
         <v>26.0045967102051</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1061859130859</v>
+        <v>20.1061878204346</v>
       </c>
       <c r="H1307" t="n">
         <v>173167</v>
@@ -38446,7 +38446,7 @@
         <v>25.1086044311523</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.413423538208</v>
+        <v>19.4134254455566</v>
       </c>
       <c r="H1313" t="n">
         <v>127568</v>
@@ -38562,7 +38562,7 @@
         <v>25.3794860839844</v>
       </c>
       <c r="G1317" t="n">
-        <v>19.6228637695312</v>
+        <v>19.6228656768799</v>
       </c>
       <c r="H1317" t="n">
         <v>206937</v>
@@ -38620,7 +38620,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.2039852142334</v>
+        <v>19.203987121582</v>
       </c>
       <c r="H1319" t="n">
         <v>101081</v>
@@ -38736,7 +38736,7 @@
         <v>24.671028137207</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.0750999450684</v>
+        <v>19.075101852417</v>
       </c>
       <c r="H1323" t="n">
         <v>120557</v>
@@ -38765,7 +38765,7 @@
         <v>24.5668430328369</v>
       </c>
       <c r="G1324" t="n">
-        <v>18.9945468902588</v>
+        <v>18.9945487976074</v>
       </c>
       <c r="H1324" t="n">
         <v>100915</v>
@@ -38881,7 +38881,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1328" t="n">
-        <v>18.8495502471924</v>
+        <v>18.849552154541</v>
       </c>
       <c r="H1328" t="n">
         <v>95840</v>
@@ -39026,7 +39026,7 @@
         <v>23.8375473022461</v>
       </c>
       <c r="G1333" t="n">
-        <v>18.4306697845459</v>
+        <v>18.4306716918945</v>
       </c>
       <c r="H1333" t="n">
         <v>62096</v>
@@ -39258,7 +39258,7 @@
         <v>25.0044193267822</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.3328704833984</v>
+        <v>19.3328723907471</v>
       </c>
       <c r="H1341" t="n">
         <v>461267</v>
@@ -39345,7 +39345,7 @@
         <v>24.5564250946045</v>
       </c>
       <c r="G1344" t="n">
-        <v>18.9864921569824</v>
+        <v>18.9864902496338</v>
       </c>
       <c r="H1344" t="n">
         <v>82258</v>
@@ -39490,7 +39490,7 @@
         <v>23.9938259124756</v>
       </c>
       <c r="G1349" t="n">
-        <v>18.5515022277832</v>
+        <v>18.5515041351318</v>
       </c>
       <c r="H1349" t="n">
         <v>67294</v>
@@ -39519,7 +39519,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1350" t="n">
-        <v>18.5434474945068</v>
+        <v>18.5434455871582</v>
       </c>
       <c r="H1350" t="n">
         <v>31645</v>
@@ -39548,7 +39548,7 @@
         <v>23.9938259124756</v>
       </c>
       <c r="G1351" t="n">
-        <v>18.5515022277832</v>
+        <v>18.5515041351318</v>
       </c>
       <c r="H1351" t="n">
         <v>70079</v>
@@ -39577,7 +39577,7 @@
         <v>23.5875034332275</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.2373428344727</v>
+        <v>18.2373447418213</v>
       </c>
       <c r="H1352" t="n">
         <v>119737</v>
@@ -39693,7 +39693,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0187149047852</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1356" t="n">
         <v>228828</v>
@@ -39751,7 +39751,7 @@
         <v>24.9210720062256</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.2684268951416</v>
+        <v>19.2684288024902</v>
       </c>
       <c r="H1358" t="n">
         <v>331765</v>
@@ -39780,7 +39780,7 @@
         <v>24.8585605621338</v>
       </c>
       <c r="G1359" t="n">
-        <v>19.2200965881348</v>
+        <v>19.2200946807861</v>
       </c>
       <c r="H1359" t="n">
         <v>239852</v>
@@ -39838,7 +39838,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1361" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1361" t="n">
         <v>157303</v>
@@ -39867,7 +39867,7 @@
         <v>24.8585605621338</v>
       </c>
       <c r="G1362" t="n">
-        <v>19.2200965881348</v>
+        <v>19.2200946807861</v>
       </c>
       <c r="H1362" t="n">
         <v>166147</v>
@@ -39896,7 +39896,7 @@
         <v>24.8585605621338</v>
       </c>
       <c r="G1363" t="n">
-        <v>19.2200965881348</v>
+        <v>19.2200946807861</v>
       </c>
       <c r="H1363" t="n">
         <v>133163</v>
@@ -39983,7 +39983,7 @@
         <v>25.4628353118896</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.6873073577881</v>
+        <v>19.6873092651367</v>
       </c>
       <c r="H1366" t="n">
         <v>576263</v>
@@ -40012,7 +40012,7 @@
         <v>25.3169765472412</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.5745334625244</v>
+        <v>19.5745315551758</v>
       </c>
       <c r="H1367" t="n">
         <v>278725</v>
@@ -40041,7 +40041,7 @@
         <v>25.2127914428711</v>
       </c>
       <c r="G1368" t="n">
-        <v>19.4939804077148</v>
+        <v>19.4939785003662</v>
       </c>
       <c r="H1368" t="n">
         <v>211758</v>
@@ -40128,7 +40128,7 @@
         <v>24.8273067474365</v>
       </c>
       <c r="G1371" t="n">
-        <v>19.1959323883057</v>
+        <v>19.195930480957</v>
       </c>
       <c r="H1371" t="n">
         <v>230606</v>
@@ -40157,7 +40157,7 @@
         <v>25.0148391723633</v>
       </c>
       <c r="G1372" t="n">
-        <v>19.3409290313721</v>
+        <v>19.3409271240234</v>
       </c>
       <c r="H1372" t="n">
         <v>175588</v>
@@ -40302,7 +40302,7 @@
         <v>25.8066463470459</v>
       </c>
       <c r="G1377" t="n">
-        <v>19.9531364440918</v>
+        <v>19.9531345367432</v>
       </c>
       <c r="H1377" t="n">
         <v>173483</v>
@@ -40418,7 +40418,7 @@
         <v>26.0045967102051</v>
       </c>
       <c r="G1381" t="n">
-        <v>20.1061859130859</v>
+        <v>20.1061878204346</v>
       </c>
       <c r="H1381" t="n">
         <v>332104</v>
@@ -40447,7 +40447,7 @@
         <v>25.8379001617432</v>
       </c>
       <c r="G1382" t="n">
-        <v>19.9772987365723</v>
+        <v>19.9773006439209</v>
       </c>
       <c r="H1382" t="n">
         <v>272090</v>
@@ -40476,7 +40476,7 @@
         <v>25.9212493896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.0417423248291</v>
+        <v>20.0417442321777</v>
       </c>
       <c r="H1383" t="n">
         <v>242252</v>
@@ -40505,7 +40505,7 @@
         <v>25.5566005706787</v>
       </c>
       <c r="G1384" t="n">
-        <v>19.7598075866699</v>
+        <v>19.7598056793213</v>
       </c>
       <c r="H1384" t="n">
         <v>217234</v>
@@ -40650,7 +40650,7 @@
         <v>24.5980987548828</v>
       </c>
       <c r="G1389" t="n">
-        <v>19.0187149047852</v>
+        <v>19.0187129974365</v>
       </c>
       <c r="H1389" t="n">
         <v>201477</v>
@@ -40679,7 +40679,7 @@
         <v>24.5668430328369</v>
       </c>
       <c r="G1390" t="n">
-        <v>18.9945468902588</v>
+        <v>18.9945487976074</v>
       </c>
       <c r="H1390" t="n">
         <v>84552</v>
@@ -40766,7 +40766,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1393" t="n">
-        <v>18.8495502471924</v>
+        <v>18.849552154541</v>
       </c>
       <c r="H1393" t="n">
         <v>77936</v>
@@ -40853,7 +40853,7 @@
         <v>24.0459175109863</v>
       </c>
       <c r="G1396" t="n">
-        <v>18.5917778015137</v>
+        <v>18.5917797088623</v>
       </c>
       <c r="H1396" t="n">
         <v>306697</v>
@@ -40998,7 +40998,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1401" t="n">
-        <v>18.108455657959</v>
+        <v>18.1084575653076</v>
       </c>
       <c r="H1401" t="n">
         <v>352284</v>
@@ -41085,7 +41085,7 @@
         <v>23.472900390625</v>
       </c>
       <c r="G1404" t="n">
-        <v>18.1487350463867</v>
+        <v>18.1487331390381</v>
       </c>
       <c r="H1404" t="n">
         <v>251573</v>
@@ -41143,7 +41143,7 @@
         <v>23.066577911377</v>
       </c>
       <c r="G1406" t="n">
-        <v>17.8345756530762</v>
+        <v>17.8345737457275</v>
       </c>
       <c r="H1406" t="n">
         <v>360550</v>
@@ -41201,7 +41201,7 @@
         <v>22.6602554321289</v>
       </c>
       <c r="G1408" t="n">
-        <v>17.520414352417</v>
+        <v>17.5204162597656</v>
       </c>
       <c r="H1408" t="n">
         <v>224491</v>
@@ -41259,7 +41259,7 @@
         <v>22.1705856323242</v>
       </c>
       <c r="G1410" t="n">
-        <v>17.1418113708496</v>
+        <v>17.1418132781982</v>
       </c>
       <c r="H1410" t="n">
         <v>158800</v>
@@ -41520,7 +41520,7 @@
         <v>23.9834060668945</v>
       </c>
       <c r="G1419" t="n">
-        <v>18.5434474945068</v>
+        <v>18.5434455871582</v>
       </c>
       <c r="H1419" t="n">
         <v>305385</v>
@@ -41549,7 +41549,7 @@
         <v>23.4103889465332</v>
       </c>
       <c r="G1420" t="n">
-        <v>18.1004028320312</v>
+        <v>18.1004009246826</v>
       </c>
       <c r="H1420" t="n">
         <v>196996</v>
@@ -41665,7 +41665,7 @@
         <v>24.3897285461426</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.8576068878174</v>
+        <v>18.8576049804688</v>
       </c>
       <c r="H1424" t="n">
         <v>537633</v>
@@ -41810,7 +41810,7 @@
         <v>23.9208946228027</v>
       </c>
       <c r="G1429" t="n">
-        <v>18.4951114654541</v>
+        <v>18.4951133728027</v>
       </c>
       <c r="H1429" t="n">
         <v>97564</v>
@@ -41926,7 +41926,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1433" t="n">
-        <v>18.0440139770508</v>
+        <v>18.0440120697021</v>
       </c>
       <c r="H1433" t="n">
         <v>289517</v>
@@ -42013,7 +42013,7 @@
         <v>23.5354118347168</v>
       </c>
       <c r="G1436" t="n">
-        <v>18.1970653533936</v>
+        <v>18.1970672607422</v>
       </c>
       <c r="H1436" t="n">
         <v>361330</v>
@@ -42042,7 +42042,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1437" t="n">
-        <v>18.0440139770508</v>
+        <v>18.0440120697021</v>
       </c>
       <c r="H1437" t="n">
         <v>102003</v>
@@ -42100,7 +42100,7 @@
         <v>23.3895511627197</v>
       </c>
       <c r="G1439" t="n">
-        <v>18.0842914581299</v>
+        <v>18.0842895507812</v>
       </c>
       <c r="H1439" t="n">
         <v>177402</v>
@@ -42187,7 +42187,7 @@
         <v>23.3895511627197</v>
       </c>
       <c r="G1442" t="n">
-        <v>18.0842914581299</v>
+        <v>18.0842895507812</v>
       </c>
       <c r="H1442" t="n">
         <v>315746</v>
@@ -42303,7 +42303,7 @@
         <v>23.066577911377</v>
       </c>
       <c r="G1446" t="n">
-        <v>17.8345756530762</v>
+        <v>17.8345737457275</v>
       </c>
       <c r="H1446" t="n">
         <v>238108</v>
@@ -42477,7 +42477,7 @@
         <v>23.0978336334229</v>
       </c>
       <c r="G1452" t="n">
-        <v>17.8587398529053</v>
+        <v>17.8587417602539</v>
       </c>
       <c r="H1452" t="n">
         <v>274366</v>
@@ -42506,7 +42506,7 @@
         <v>22.899881362915</v>
       </c>
       <c r="G1453" t="n">
-        <v>17.7056884765625</v>
+        <v>17.7056865692139</v>
       </c>
       <c r="H1453" t="n">
         <v>292793</v>
@@ -42622,7 +42622,7 @@
         <v>22.503978729248</v>
       </c>
       <c r="G1457" t="n">
-        <v>17.3995838165283</v>
+        <v>17.399585723877</v>
       </c>
       <c r="H1457" t="n">
         <v>107698</v>
@@ -42680,7 +42680,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1459" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1459" t="n">
         <v>176935</v>
@@ -42883,7 +42883,7 @@
         <v>23.4208068847656</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.108455657959</v>
+        <v>18.1084575653076</v>
       </c>
       <c r="H1466" t="n">
         <v>183896</v>
@@ -42941,7 +42941,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.0440139770508</v>
+        <v>18.0440120697021</v>
       </c>
       <c r="H1468" t="n">
         <v>153990</v>
@@ -42970,7 +42970,7 @@
         <v>23.0249042510986</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8023548126221</v>
+        <v>17.8023529052734</v>
       </c>
       <c r="H1469" t="n">
         <v>177997</v>
@@ -43028,7 +43028,7 @@
         <v>22.899881362915</v>
       </c>
       <c r="G1471" t="n">
-        <v>17.7056884765625</v>
+        <v>17.7056865692139</v>
       </c>
       <c r="H1471" t="n">
         <v>144340</v>
@@ -43057,7 +43057,7 @@
         <v>22.9207191467285</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.7217979431152</v>
+        <v>17.7217998504639</v>
       </c>
       <c r="H1472" t="n">
         <v>130410</v>
@@ -43173,7 +43173,7 @@
         <v>22.3789558410645</v>
       </c>
       <c r="G1476" t="n">
-        <v>17.3029193878174</v>
+        <v>17.302921295166</v>
       </c>
       <c r="H1476" t="n">
         <v>79029</v>
@@ -43202,7 +43202,7 @@
         <v>22.6602554321289</v>
       </c>
       <c r="G1477" t="n">
-        <v>17.520414352417</v>
+        <v>17.5204162597656</v>
       </c>
       <c r="H1477" t="n">
         <v>102803</v>
@@ -43260,7 +43260,7 @@
         <v>21.8059387207031</v>
       </c>
       <c r="G1479" t="n">
-        <v>16.8598747253418</v>
+        <v>16.8598766326904</v>
       </c>
       <c r="H1479" t="n">
         <v>469024</v>
@@ -43318,7 +43318,7 @@
         <v>21.8997058868408</v>
       </c>
       <c r="G1481" t="n">
-        <v>16.9323749542236</v>
+        <v>16.932373046875</v>
       </c>
       <c r="H1481" t="n">
         <v>61817</v>
@@ -43376,7 +43376,7 @@
         <v>21.4829635620117</v>
       </c>
       <c r="G1483" t="n">
-        <v>16.6101589202881</v>
+        <v>16.6101570129395</v>
       </c>
       <c r="H1483" t="n">
         <v>73766</v>
@@ -43434,7 +43434,7 @@
         <v>21.3475246429443</v>
       </c>
       <c r="G1485" t="n">
-        <v>16.5054378509521</v>
+        <v>16.5054397583008</v>
       </c>
       <c r="H1485" t="n">
         <v>156005</v>
@@ -43521,7 +43521,7 @@
         <v>21.2745933532715</v>
       </c>
       <c r="G1488" t="n">
-        <v>16.4490509033203</v>
+        <v>16.4490528106689</v>
       </c>
       <c r="H1488" t="n">
         <v>129536</v>
@@ -43666,7 +43666,7 @@
         <v>20.9203643798828</v>
       </c>
       <c r="G1493" t="n">
-        <v>16.1751689910889</v>
+        <v>16.1751670837402</v>
       </c>
       <c r="H1493" t="n">
         <v>89259</v>
@@ -43724,7 +43724,7 @@
         <v>20.7369995117188</v>
       </c>
       <c r="G1495" t="n">
-        <v>16.0333957672119</v>
+        <v>16.0333938598633</v>
       </c>
       <c r="H1495" t="n">
         <v>217462</v>
@@ -43753,7 +43753,7 @@
         <v>20.6619853973389</v>
       </c>
       <c r="G1496" t="n">
-        <v>15.975396156311</v>
+        <v>15.9753952026367</v>
       </c>
       <c r="H1496" t="n">
         <v>142969</v>
@@ -43782,7 +43782,7 @@
         <v>20.2244091033936</v>
       </c>
       <c r="G1497" t="n">
-        <v>15.6370716094971</v>
+        <v>15.6370706558228</v>
       </c>
       <c r="H1497" t="n">
         <v>157081</v>
@@ -43840,7 +43840,7 @@
         <v>19.3575897216797</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.9668645858765</v>
+        <v>14.9668655395508</v>
       </c>
       <c r="H1499" t="n">
         <v>131664</v>
@@ -43927,7 +43927,7 @@
         <v>18.4866008758545</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.2934370040894</v>
+        <v>14.293436050415</v>
       </c>
       <c r="H1502" t="n">
         <v>112108</v>
@@ -44014,7 +44014,7 @@
         <v>16.8154735565186</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.0013580322266</v>
+        <v>13.0013570785522</v>
       </c>
       <c r="H1505" t="n">
         <v>156575</v>
@@ -44043,7 +44043,7 @@
         <v>19.6284694671631</v>
       </c>
       <c r="G1506" t="n">
-        <v>15.1763038635254</v>
+        <v>15.1763048171997</v>
       </c>
       <c r="H1506" t="n">
         <v>979944</v>
@@ -44072,7 +44072,7 @@
         <v>19.0783729553223</v>
       </c>
       <c r="G1507" t="n">
-        <v>14.7509813308716</v>
+        <v>14.7509803771973</v>
       </c>
       <c r="H1507" t="n">
         <v>512576</v>
@@ -44101,7 +44101,7 @@
         <v>18.507438659668</v>
       </c>
       <c r="G1508" t="n">
-        <v>14.3095483779907</v>
+        <v>14.3095474243164</v>
       </c>
       <c r="H1508" t="n">
         <v>223480</v>
@@ -44188,7 +44188,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1511" t="n">
         <v>68657</v>
@@ -44246,7 +44246,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157632827759</v>
       </c>
       <c r="H1513" t="n">
         <v>165517</v>
@@ -44275,7 +44275,7 @@
         <v>18.8908386230469</v>
       </c>
       <c r="G1514" t="n">
-        <v>14.6059837341309</v>
+        <v>14.6059827804565</v>
       </c>
       <c r="H1514" t="n">
         <v>149007</v>
@@ -44304,7 +44304,7 @@
         <v>18.9533500671387</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.6543169021606</v>
+        <v>14.6543159484863</v>
       </c>
       <c r="H1515" t="n">
         <v>168456</v>
@@ -44362,7 +44362,7 @@
         <v>19.2950782775879</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.9185333251953</v>
+        <v>14.9185342788696</v>
       </c>
       <c r="H1517" t="n">
         <v>167619</v>
@@ -44391,7 +44391,7 @@
         <v>19.3200817108154</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.9378662109375</v>
+        <v>14.9378652572632</v>
       </c>
       <c r="H1518" t="n">
         <v>167937</v>
@@ -44420,7 +44420,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157632827759</v>
       </c>
       <c r="H1519" t="n">
         <v>157517</v>
@@ -44449,7 +44449,7 @@
         <v>18.915843963623</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.625316619873</v>
+        <v>14.6253175735474</v>
       </c>
       <c r="H1520" t="n">
         <v>192381</v>
@@ -44478,7 +44478,7 @@
         <v>19.1575527191162</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.8122005462646</v>
+        <v>14.812201499939</v>
       </c>
       <c r="H1521" t="n">
         <v>111135</v>
@@ -44507,7 +44507,7 @@
         <v>18.7783203125</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5189876556396</v>
+        <v>14.5189867019653</v>
       </c>
       <c r="H1522" t="n">
         <v>83491</v>
@@ -44536,7 +44536,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1523" t="n">
         <v>155943</v>
@@ -44565,7 +44565,7 @@
         <v>18.7533149719238</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4996528625488</v>
+        <v>14.4996538162231</v>
       </c>
       <c r="H1524" t="n">
         <v>184928</v>
@@ -44594,7 +44594,7 @@
         <v>18.6616325378418</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.4287662506104</v>
+        <v>14.4287672042847</v>
       </c>
       <c r="H1525" t="n">
         <v>203931</v>
@@ -44623,7 +44623,7 @@
         <v>18.5866184234619</v>
       </c>
       <c r="G1526" t="n">
-        <v>14.3707666397095</v>
+        <v>14.3707675933838</v>
       </c>
       <c r="H1526" t="n">
         <v>75889</v>
@@ -44681,7 +44681,7 @@
         <v>19.3950958251953</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.9958648681641</v>
+        <v>14.9958639144897</v>
       </c>
       <c r="H1528" t="n">
         <v>508333</v>
@@ -44768,7 +44768,7 @@
         <v>19.307580947876</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.9281997680664</v>
+        <v>14.9281988143921</v>
       </c>
       <c r="H1531" t="n">
         <v>93839</v>
@@ -44826,7 +44826,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.9024209976196</v>
+        <v>14.9024219512939</v>
       </c>
       <c r="H1533" t="n">
         <v>79836</v>
@@ -44855,7 +44855,7 @@
         <v>19.2867431640625</v>
       </c>
       <c r="G1534" t="n">
-        <v>14.9120874404907</v>
+        <v>14.912088394165</v>
       </c>
       <c r="H1534" t="n">
         <v>132919</v>
@@ -44913,7 +44913,7 @@
         <v>18.8116588592529</v>
       </c>
       <c r="G1536" t="n">
-        <v>14.5447635650635</v>
+        <v>14.5447645187378</v>
       </c>
       <c r="H1536" t="n">
         <v>106444</v>
@@ -44942,7 +44942,7 @@
         <v>19.1617202758789</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.8154249191284</v>
+        <v>14.8154239654541</v>
       </c>
       <c r="H1537" t="n">
         <v>73886</v>
@@ -44971,7 +44971,7 @@
         <v>18.9658527374268</v>
       </c>
       <c r="G1538" t="n">
-        <v>14.6639833450317</v>
+        <v>14.6639823913574</v>
       </c>
       <c r="H1538" t="n">
         <v>115175</v>
@@ -45000,7 +45000,7 @@
         <v>18.9116764068604</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.6220941543579</v>
+        <v>14.6220951080322</v>
       </c>
       <c r="H1539" t="n">
         <v>34303</v>
@@ -45174,7 +45174,7 @@
         <v>18.8283271789551</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.5576505661011</v>
+        <v>14.5576515197754</v>
       </c>
       <c r="H1545" t="n">
         <v>72837</v>
@@ -45232,7 +45232,7 @@
         <v>19.0116939544678</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.6994256973267</v>
+        <v>14.699426651001</v>
       </c>
       <c r="H1547" t="n">
         <v>198643</v>
@@ -45319,7 +45319,7 @@
         <v>19.7618274688721</v>
       </c>
       <c r="G1550" t="n">
-        <v>15.2794141769409</v>
+        <v>15.2794132232666</v>
       </c>
       <c r="H1550" t="n">
         <v>232939</v>
@@ -45348,7 +45348,7 @@
         <v>19.2742404937744</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.9024209976196</v>
+        <v>14.9024219512939</v>
       </c>
       <c r="H1551" t="n">
         <v>264963</v>
@@ -45435,7 +45435,7 @@
         <v>20.0243721008301</v>
       </c>
       <c r="G1554" t="n">
-        <v>15.4824075698853</v>
+        <v>15.4824066162109</v>
       </c>
       <c r="H1554" t="n">
         <v>487112</v>
@@ -45464,7 +45464,7 @@
         <v>20.2327423095703</v>
       </c>
       <c r="G1555" t="n">
-        <v>15.643515586853</v>
+        <v>15.6435146331787</v>
       </c>
       <c r="H1555" t="n">
         <v>151091</v>
@@ -45551,7 +45551,7 @@
         <v>21.6496601104736</v>
       </c>
       <c r="G1558" t="n">
-        <v>16.7390460968018</v>
+        <v>16.7390441894531</v>
       </c>
       <c r="H1558" t="n">
         <v>523113</v>
@@ -45609,7 +45609,7 @@
         <v>19.9368572235107</v>
       </c>
       <c r="G1560" t="n">
-        <v>15.4147424697876</v>
+        <v>15.4147415161133</v>
       </c>
       <c r="H1560" t="n">
         <v>254459</v>
@@ -45638,7 +45638,7 @@
         <v>19.5784606933594</v>
       </c>
       <c r="G1561" t="n">
-        <v>15.1376390457153</v>
+        <v>15.137638092041</v>
       </c>
       <c r="H1561" t="n">
         <v>134574</v>
@@ -45667,7 +45667,7 @@
         <v>19.1325492858887</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.7928705215454</v>
+        <v>14.7928686141968</v>
       </c>
       <c r="H1562" t="n">
         <v>328129</v>
@@ -45696,7 +45696,7 @@
         <v>19.0366992950439</v>
       </c>
       <c r="G1563" t="n">
-        <v>14.7187604904175</v>
+        <v>14.7187595367432</v>
       </c>
       <c r="H1563" t="n">
         <v>364625</v>
@@ -45725,7 +45725,7 @@
         <v>18.7741527557373</v>
       </c>
       <c r="G1564" t="n">
-        <v>14.5157642364502</v>
+        <v>14.5157632827759</v>
       </c>
       <c r="H1564" t="n">
         <v>315453</v>
@@ -45841,7 +45841,7 @@
         <v>17.1113586425781</v>
       </c>
       <c r="G1568" t="n">
-        <v>13.230128288269</v>
+        <v>13.2301292419434</v>
       </c>
       <c r="H1568" t="n">
         <v>266822</v>
@@ -45870,7 +45870,7 @@
         <v>17.5614376068115</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.5781202316284</v>
+        <v>13.5781211853027</v>
       </c>
       <c r="H1569" t="n">
         <v>306814</v>
@@ -45928,7 +45928,7 @@
         <v>15.940318107605</v>
       </c>
       <c r="G1571" t="n">
-        <v>12.3247060775757</v>
+        <v>12.3247051239014</v>
       </c>
       <c r="H1571" t="n">
         <v>242452</v>
@@ -45957,7 +45957,7 @@
         <v>16.9196586608887</v>
       </c>
       <c r="G1572" t="n">
-        <v>13.0819110870361</v>
+        <v>13.0819101333618</v>
       </c>
       <c r="H1572" t="n">
         <v>407858</v>
@@ -45986,7 +45986,7 @@
         <v>16.6237716674805</v>
       </c>
       <c r="G1573" t="n">
-        <v>12.8531370162964</v>
+        <v>12.8531379699707</v>
       </c>
       <c r="H1573" t="n">
         <v>585254</v>
@@ -46015,7 +46015,7 @@
         <v>17.807315826416</v>
       </c>
       <c r="G1574" t="n">
-        <v>13.7682285308838</v>
+        <v>13.7682275772095</v>
       </c>
       <c r="H1574" t="n">
         <v>308404</v>
@@ -46102,7 +46102,7 @@
         <v>19.4200992584229</v>
       </c>
       <c r="G1577" t="n">
-        <v>15.0151977539062</v>
+        <v>15.0151968002319</v>
       </c>
       <c r="H1577" t="n">
         <v>400947</v>
@@ -46131,7 +46131,7 @@
         <v>19.7534923553467</v>
       </c>
       <c r="G1578" t="n">
-        <v>15.2729682922363</v>
+        <v>15.272967338562</v>
       </c>
       <c r="H1578" t="n">
         <v>326853</v>
@@ -46218,7 +46218,7 @@
         <v>20.3661003112793</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.7466239929199</v>
+        <v>15.7466249465942</v>
       </c>
       <c r="H1581" t="n">
         <v>349520</v>
@@ -46276,7 +46276,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1583" t="n">
-        <v>15.9496192932129</v>
+        <v>15.9496202468872</v>
       </c>
       <c r="H1583" t="n">
         <v>228335</v>
@@ -46305,7 +46305,7 @@
         <v>20.6286468505859</v>
       </c>
       <c r="G1584" t="n">
-        <v>15.9496192932129</v>
+        <v>15.9496202468872</v>
       </c>
       <c r="H1584" t="n">
         <v>108428</v>
@@ -46334,7 +46334,7 @@
         <v>20.1077213287354</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.5468511581421</v>
+        <v>15.5468521118164</v>
       </c>
       <c r="H1585" t="n">
         <v>177619</v>
@@ -46363,7 +46363,7 @@
         <v>20.0952186584473</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.537184715271</v>
+        <v>15.5371856689453</v>
       </c>
       <c r="H1586" t="n">
         <v>198619</v>
@@ -46392,7 +46392,7 @@
         <v>20.1202239990234</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.5565195083618</v>
+        <v>15.5565176010132</v>
       </c>
       <c r="H1587" t="n">
         <v>228146</v>
@@ -46450,7 +46450,7 @@
         <v>19.9493598937988</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.424409866333</v>
+        <v>15.4244089126587</v>
       </c>
       <c r="H1589" t="n">
         <v>222730</v>
@@ -46479,7 +46479,7 @@
         <v>19.49094581604</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.069974899292</v>
+        <v>15.0699739456177</v>
       </c>
       <c r="H1590" t="n">
         <v>151523</v>
@@ -46537,7 +46537,7 @@
         <v>18.9616851806641</v>
       </c>
       <c r="G1592" t="n">
-        <v>14.6607608795166</v>
+        <v>14.6607599258423</v>
       </c>
       <c r="H1592" t="n">
         <v>276239</v>
@@ -46653,7 +46653,7 @@
         <v>18.4511775970459</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.2660484313965</v>
+        <v>14.2660474777222</v>
       </c>
       <c r="H1596" t="n">
         <v>137521</v>
@@ -46682,7 +46682,7 @@
         <v>18.1177864074707</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0082769393921</v>
+        <v>14.0082759857178</v>
       </c>
       <c r="H1597" t="n">
         <v>193042</v>
@@ -46711,7 +46711,7 @@
         <v>17.7948112487793</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.7585582733154</v>
+        <v>13.7585592269897</v>
       </c>
       <c r="H1598" t="n">
         <v>171526</v>
@@ -46740,7 +46740,7 @@
         <v>17.9927635192871</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.9116115570068</v>
+        <v>13.9116106033325</v>
       </c>
       <c r="H1599" t="n">
         <v>156203</v>
@@ -46827,7 +46827,7 @@
         <v>17.9719276428223</v>
       </c>
       <c r="G1602" t="n">
-        <v>13.8955011367798</v>
+        <v>13.8955020904541</v>
       </c>
       <c r="H1602" t="n">
         <v>168613</v>
@@ -46914,7 +46914,7 @@
         <v>17.6385345458984</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.6377296447754</v>
+        <v>13.6377305984497</v>
       </c>
       <c r="H1605" t="n">
         <v>312015</v>
@@ -47204,7 +47204,7 @@
         <v>14.2941932678223</v>
       </c>
       <c r="G1615" t="n">
-        <v>11.0519590377808</v>
+        <v>11.0519580841064</v>
       </c>
       <c r="H1615" t="n">
         <v>230061</v>
@@ -47233,7 +47233,7 @@
         <v>14.3983793258667</v>
       </c>
       <c r="G1616" t="n">
-        <v>11.1325130462646</v>
+        <v>11.1325120925903</v>
       </c>
       <c r="H1616" t="n">
         <v>191940</v>
@@ -47262,7 +47262,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.390284538269</v>
+        <v>11.3902835845947</v>
       </c>
       <c r="H1617" t="n">
         <v>109832</v>
@@ -47291,7 +47291,7 @@
         <v>14.7942819595337</v>
       </c>
       <c r="G1618" t="n">
-        <v>11.4386167526245</v>
+        <v>11.4386157989502</v>
       </c>
       <c r="H1618" t="n">
         <v>110697</v>
@@ -47349,7 +47349,7 @@
         <v>14.5442380905151</v>
       </c>
       <c r="G1620" t="n">
-        <v>11.2452878952026</v>
+        <v>11.2452869415283</v>
       </c>
       <c r="H1620" t="n">
         <v>96191</v>
@@ -47378,7 +47378,7 @@
         <v>14.7317714691162</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.390284538269</v>
+        <v>11.3902835845947</v>
       </c>
       <c r="H1621" t="n">
         <v>197863</v>
@@ -47465,7 +47465,7 @@
         <v>14.700514793396</v>
       </c>
       <c r="G1624" t="n">
-        <v>11.3661165237427</v>
+        <v>11.366117477417</v>
       </c>
       <c r="H1624" t="n">
         <v>91847</v>
@@ -47523,7 +47523,7 @@
         <v>15.5131587982178</v>
       </c>
       <c r="G1626" t="n">
-        <v>11.9944353103638</v>
+        <v>11.9944362640381</v>
       </c>
       <c r="H1626" t="n">
         <v>418987</v>
@@ -47552,7 +47552,7 @@
         <v>15.4819030761719</v>
       </c>
       <c r="G1627" t="n">
-        <v>11.9702701568604</v>
+        <v>11.970269203186</v>
       </c>
       <c r="H1627" t="n">
         <v>161789</v>
@@ -47610,7 +47610,7 @@
         <v>15.5235767364502</v>
       </c>
       <c r="G1629" t="n">
-        <v>12.0024909973145</v>
+        <v>12.0024900436401</v>
       </c>
       <c r="H1629" t="n">
         <v>65253</v>
@@ -47639,7 +47639,7 @@
         <v>16.1903629302979</v>
       </c>
       <c r="G1630" t="n">
-        <v>12.5180358886719</v>
+        <v>12.5180349349976</v>
       </c>
       <c r="H1630" t="n">
         <v>120708</v>
@@ -47784,7 +47784,7 @@
         <v>16.6591949462891</v>
       </c>
       <c r="G1635" t="n">
-        <v>12.8805255889893</v>
+        <v>12.8805265426636</v>
       </c>
       <c r="H1635" t="n">
         <v>140616</v>
@@ -47871,7 +47871,7 @@
         <v>16.0549201965332</v>
       </c>
       <c r="G1638" t="n">
-        <v>12.4133138656616</v>
+        <v>12.4133148193359</v>
       </c>
       <c r="H1638" t="n">
         <v>114953</v>
@@ -47987,7 +47987,7 @@
         <v>14.7734451293945</v>
       </c>
       <c r="G1642" t="n">
-        <v>11.4225063323975</v>
+        <v>11.4225053787231</v>
       </c>
       <c r="H1642" t="n">
         <v>170224</v>
@@ -48016,7 +48016,7 @@
         <v>14.5650749206543</v>
       </c>
       <c r="G1643" t="n">
-        <v>11.2613983154297</v>
+        <v>11.2613973617554</v>
       </c>
       <c r="H1643" t="n">
         <v>60975</v>
@@ -48161,7 +48161,7 @@
         <v>13.8566160202026</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.7136335372925</v>
+        <v>10.7136325836182</v>
       </c>
       <c r="H1648" t="n">
         <v>160860</v>
@@ -48190,7 +48190,7 @@
         <v>14.0441493988037</v>
       </c>
       <c r="G1649" t="n">
-        <v>10.8586301803589</v>
+        <v>10.8586292266846</v>
       </c>
       <c r="H1649" t="n">
         <v>111558</v>
@@ -48364,7 +48364,7 @@
         <v>10.5539493560791</v>
       </c>
       <c r="G1655" t="n">
-        <v>8.16008377075195</v>
+        <v>8.16008281707764</v>
       </c>
       <c r="H1655" t="n">
         <v>232329</v>
@@ -48393,7 +48393,7 @@
         <v>10.0017681121826</v>
       </c>
       <c r="G1656" t="n">
-        <v>7.7331485748291</v>
+        <v>7.73314952850342</v>
       </c>
       <c r="H1656" t="n">
         <v>208616</v>
@@ -48422,7 +48422,7 @@
         <v>9.64753913879395</v>
       </c>
       <c r="G1657" t="n">
-        <v>7.45926666259766</v>
+        <v>7.45926713943481</v>
       </c>
       <c r="H1657" t="n">
         <v>314217</v>
@@ -48451,7 +48451,7 @@
         <v>10.010103225708</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.73959350585938</v>
+        <v>7.73959302902222</v>
       </c>
       <c r="H1658" t="n">
         <v>359843</v>
@@ -48480,7 +48480,7 @@
         <v>11.1894779205322</v>
       </c>
       <c r="G1659" t="n">
-        <v>8.65145969390869</v>
+        <v>8.65146064758301</v>
       </c>
       <c r="H1659" t="n">
         <v>479547</v>
@@ -48567,7 +48567,7 @@
         <v>10.2226400375366</v>
       </c>
       <c r="G1662" t="n">
-        <v>7.90392208099365</v>
+        <v>7.90392255783081</v>
       </c>
       <c r="H1662" t="n">
         <v>148424</v>
@@ -48596,7 +48596,7 @@
         <v>9.50584697723389</v>
       </c>
       <c r="G1663" t="n">
-        <v>7.34971284866333</v>
+        <v>7.34971332550049</v>
       </c>
       <c r="H1663" t="n">
         <v>388404</v>
@@ -48683,7 +48683,7 @@
         <v>9.54335308074951</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.37871170043945</v>
+        <v>7.37871217727661</v>
       </c>
       <c r="H1666" t="n">
         <v>148370</v>
@@ -48712,7 +48712,7 @@
         <v>9.3766565322876</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.2498254776001</v>
+        <v>7.24982595443726</v>
       </c>
       <c r="H1667" t="n">
         <v>419862</v>
@@ -48741,7 +48741,7 @@
         <v>8.87656879425049</v>
       </c>
       <c r="G1668" t="n">
-        <v>6.86316871643066</v>
+        <v>6.86316919326782</v>
       </c>
       <c r="H1668" t="n">
         <v>393325</v>
@@ -48799,7 +48799,7 @@
         <v>8.75571441650391</v>
       </c>
       <c r="G1670" t="n">
-        <v>6.76972723007202</v>
+        <v>6.76972770690918</v>
       </c>
       <c r="H1670" t="n">
         <v>178963</v>
@@ -48828,7 +48828,7 @@
         <v>8.57234764099121</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.62795209884644</v>
+        <v>6.62795162200928</v>
       </c>
       <c r="H1671" t="n">
         <v>134394</v>
@@ -49118,7 +49118,7 @@
         <v>8.60568809509277</v>
       </c>
       <c r="G1681" t="n">
-        <v>6.65373039245605</v>
+        <v>6.65373086929321</v>
       </c>
       <c r="H1681" t="n">
         <v>83569</v>
@@ -49379,7 +49379,7 @@
         <v>7.95557308197021</v>
       </c>
       <c r="G1690" t="n">
-        <v>6.15107583999634</v>
+        <v>6.15107536315918</v>
       </c>
       <c r="H1690" t="n">
         <v>346128</v>
@@ -49408,7 +49408,7 @@
         <v>7.97640991210938</v>
       </c>
       <c r="G1691" t="n">
-        <v>6.16718626022339</v>
+        <v>6.16718578338623</v>
       </c>
       <c r="H1691" t="n">
         <v>184846</v>
@@ -49437,7 +49437,7 @@
         <v>7.7680401802063</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.00607872009277</v>
+        <v>6.00607919692993</v>
       </c>
       <c r="H1692" t="n">
         <v>226862</v>
@@ -49553,7 +49553,7 @@
         <v>6.60950088500977</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.11032199859619</v>
+        <v>5.11032152175903</v>
       </c>
       <c r="H1696" t="n">
         <v>868645</v>
@@ -49582,7 +49582,7 @@
         <v>6.32611799240112</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.89121627807617</v>
+        <v>4.89121675491333</v>
       </c>
       <c r="H1697" t="n">
         <v>323082</v>
@@ -49669,7 +49669,7 @@
         <v>6.05523681640625</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.68177652359009</v>
+        <v>4.68177700042725</v>
       </c>
       <c r="H1700" t="n">
         <v>576189</v>
@@ -49843,7 +49843,7 @@
         <v>7.44298219680786</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.75475120544434</v>
+        <v>5.75475168228149</v>
       </c>
       <c r="H1706" t="n">
         <v>683471</v>
@@ -49872,7 +49872,7 @@
         <v>7.65135192871094</v>
       </c>
       <c r="G1707" t="n">
-        <v>5.91585826873779</v>
+        <v>5.91585779190063</v>
       </c>
       <c r="H1707" t="n">
         <v>677853</v>
@@ -49901,7 +49901,7 @@
         <v>7.26378393173218</v>
       </c>
       <c r="G1708" t="n">
-        <v>5.61619901657104</v>
+        <v>5.6161994934082</v>
       </c>
       <c r="H1708" t="n">
         <v>487854</v>
@@ -50046,7 +50046,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.91699361801147</v>
+        <v>4.91699314117432</v>
       </c>
       <c r="H1713" t="n">
         <v>765955</v>
@@ -50075,7 +50075,7 @@
         <v>6.35945701599121</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.91699361801147</v>
+        <v>4.91699314117432</v>
       </c>
       <c r="H1714" t="n">
         <v>0</v>
@@ -50133,7 +50133,7 @@
         <v>6.2302680015564</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.8171067237854</v>
+        <v>4.81710720062256</v>
       </c>
       <c r="H1716" t="n">
         <v>855847</v>
@@ -50249,7 +50249,7 @@
         <v>4.99671602249146</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.86335134506226</v>
+        <v>3.86335158348083</v>
       </c>
       <c r="H1720" t="n">
         <v>478249</v>
@@ -50307,7 +50307,7 @@
         <v>4.66853284835815</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.6096076965332</v>
+        <v>3.60960793495178</v>
       </c>
       <c r="H1722" t="n">
         <v>526169</v>
@@ -50394,7 +50394,7 @@
         <v>4.84252214431763</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.74413228034973</v>
+        <v>3.74413251876831</v>
       </c>
       <c r="H1725" t="n">
         <v>619872</v>
@@ -50568,7 +50568,7 @@
         <v>2.00300002098083</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.54867589473724</v>
+        <v>1.54867601394653</v>
       </c>
       <c r="H1731" t="n">
         <v>1258018</v>
@@ -50742,7 +50742,7 @@
         <v>1.9617999792099</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.51682090759277</v>
+        <v>1.51682078838348</v>
       </c>
       <c r="H1737" t="n">
         <v>885498</v>
@@ -50771,7 +50771,7 @@
         <v>1.93019998073578</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.49238836765289</v>
+        <v>1.49238848686218</v>
       </c>
       <c r="H1738" t="n">
         <v>977946</v>
@@ -50916,7 +50916,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.2525486946106</v>
+        <v>1.25254857540131</v>
       </c>
       <c r="H1743" t="n">
         <v>32047433</v>
@@ -51090,7 +51090,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.38398885726929</v>
+        <v>1.38398897647858</v>
       </c>
       <c r="H1749" t="n">
         <v>7258460</v>
@@ -51119,7 +51119,7 @@
         <v>1.81560003757477</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.4037823677063</v>
+        <v>1.40378224849701</v>
       </c>
       <c r="H1750" t="n">
         <v>4722464</v>
@@ -51148,7 +51148,7 @@
         <v>1.76339995861053</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.36342227458954</v>
+        <v>1.36342239379883</v>
       </c>
       <c r="H1751" t="n">
         <v>3047867</v>
@@ -51206,7 +51206,7 @@
         <v>1.81299996376038</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.40177202224731</v>
+        <v>1.40177190303802</v>
       </c>
       <c r="H1753" t="n">
         <v>5951051</v>
@@ -51235,7 +51235,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.391566157341</v>
+        <v>1.39156603813171</v>
       </c>
       <c r="H1754" t="n">
         <v>2641302</v>
@@ -51293,7 +51293,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.41615307331085</v>
+        <v>1.41615319252014</v>
       </c>
       <c r="H1756" t="n">
         <v>9845377</v>
@@ -51409,7 +51409,7 @@
         <v>1.88839995861053</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.46006965637207</v>
+        <v>1.46006953716278</v>
       </c>
       <c r="H1760" t="n">
         <v>10216109</v>
@@ -51612,7 +51612,7 @@
         <v>1.80820000171661</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.39806079864502</v>
+        <v>1.39806067943573</v>
       </c>
       <c r="H1767" t="n">
         <v>5834324</v>
@@ -51641,7 +51641,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.409503698349</v>
+        <v>1.40950381755829</v>
       </c>
       <c r="H1768" t="n">
         <v>4615701</v>
@@ -51699,7 +51699,7 @@
         <v>1.94640004634857</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.50491392612457</v>
+        <v>1.50491404533386</v>
       </c>
       <c r="H1770" t="n">
         <v>8428502</v>
@@ -51844,7 +51844,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.46903860569</v>
+        <v>1.46903848648071</v>
       </c>
       <c r="H1775" t="n">
         <v>3814973</v>
@@ -51873,7 +51873,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.52702689170837</v>
+        <v>1.52702677249908</v>
       </c>
       <c r="H1776" t="n">
         <v>4241606</v>
@@ -51931,7 +51931,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.52161455154419</v>
+        <v>1.52161467075348</v>
       </c>
       <c r="H1778" t="n">
         <v>5872856</v>
@@ -51960,7 +51960,7 @@
         <v>1.94780004024506</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.50599646568298</v>
+        <v>1.50599634647369</v>
       </c>
       <c r="H1779" t="n">
         <v>7787315</v>
@@ -52221,7 +52221,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.71490931510925</v>
+        <v>1.71490919589996</v>
       </c>
       <c r="H1788" t="n">
         <v>25457401</v>
@@ -52279,7 +52279,7 @@
         <v>2.16899991035461</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.67702341079712</v>
+        <v>1.67702329158783</v>
       </c>
       <c r="H1790" t="n">
         <v>8965001</v>
@@ -52482,7 +52482,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.56800544261932</v>
+        <v>1.56800532341003</v>
       </c>
       <c r="H1797" t="n">
         <v>6304338</v>
@@ -52511,7 +52511,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.65305483341217</v>
+        <v>1.65305495262146</v>
       </c>
       <c r="H1798" t="n">
         <v>10373984</v>
@@ -52627,7 +52627,7 @@
         <v>2.18449997901917</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.68900775909424</v>
+        <v>1.68900763988495</v>
       </c>
       <c r="H1802" t="n">
         <v>7676085</v>
@@ -52743,7 +52743,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.87186431884766</v>
+        <v>1.87186455726624</v>
       </c>
       <c r="H1806" t="n">
         <v>12148200</v>
@@ -52772,7 +52772,7 @@
         <v>2.48950004577637</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.92482697963715</v>
+        <v>1.92482721805573</v>
       </c>
       <c r="H1807" t="n">
         <v>14549250</v>
@@ -52830,7 +52830,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.84789597988129</v>
+        <v>1.84789609909058</v>
       </c>
       <c r="H1809" t="n">
         <v>9933747</v>
@@ -52946,7 +52946,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.88191556930542</v>
+        <v>1.881915807724</v>
       </c>
       <c r="H1813" t="n">
         <v>7390193</v>
@@ -53033,7 +53033,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.91052317619324</v>
+        <v>1.91052305698395</v>
       </c>
       <c r="H1816" t="n">
         <v>14267354</v>
@@ -53265,7 +53265,7 @@
         <v>2.52349996566772</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.95111525058746</v>
+        <v>1.95111513137817</v>
       </c>
       <c r="H1824" t="n">
         <v>54311078</v>
@@ -53352,7 +53352,7 @@
         <v>2.46099996566772</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.90279138088226</v>
+        <v>1.90279150009155</v>
       </c>
       <c r="H1827" t="n">
         <v>7484611</v>
@@ -53410,7 +53410,7 @@
         <v>2.36700010299683</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.83011269569397</v>
+        <v>1.83011281490326</v>
       </c>
       <c r="H1829" t="n">
         <v>7991760</v>
@@ -53468,7 +53468,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.80305147171021</v>
+        <v>1.80305159091949</v>
       </c>
       <c r="H1831" t="n">
         <v>6664209</v>
@@ -53497,7 +53497,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.78256225585938</v>
+        <v>1.78256213665009</v>
       </c>
       <c r="H1832" t="n">
         <v>18578156</v>
@@ -53526,7 +53526,7 @@
         <v>2.13649988174438</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.65189492702484</v>
+        <v>1.65189504623413</v>
       </c>
       <c r="H1833" t="n">
         <v>20642011</v>
@@ -53613,7 +53613,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.48450195789337</v>
+        <v>1.48450207710266</v>
       </c>
       <c r="H1836" t="n">
         <v>20305784</v>
@@ -53903,7 +53903,7 @@
         <v>1.99520003795624</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.54264497756958</v>
+        <v>1.54264509677887</v>
       </c>
       <c r="H1846" t="n">
         <v>10952973</v>
@@ -54019,7 +54019,7 @@
         <v>1.91349995136261</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.47947633266449</v>
+        <v>1.47947645187378</v>
       </c>
       <c r="H1850" t="n">
         <v>4817935</v>
@@ -54077,7 +54077,7 @@
         <v>1.99950003623962</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.54596972465515</v>
+        <v>1.54596984386444</v>
       </c>
       <c r="H1852" t="n">
         <v>6684358</v>
@@ -54222,7 +54222,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650671005249</v>
       </c>
       <c r="H1857" t="n">
         <v>11220865</v>
@@ -54309,7 +54309,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.75666081905365</v>
+        <v>1.75666093826294</v>
       </c>
       <c r="H1860" t="n">
         <v>8508624</v>
@@ -54367,7 +54367,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1862" t="n">
-        <v>1.70872378349304</v>
+        <v>1.70872366428375</v>
       </c>
       <c r="H1862" t="n">
         <v>3381175</v>
@@ -54425,7 +54425,7 @@
         <v>2.18099999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.68630146980286</v>
+        <v>1.68630158901215</v>
       </c>
       <c r="H1864" t="n">
         <v>5899256</v>
@@ -54454,7 +54454,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.61516916751862</v>
+        <v>1.61516928672791</v>
       </c>
       <c r="H1865" t="n">
         <v>6994580</v>
@@ -54483,7 +54483,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.58037602901459</v>
+        <v>1.58037614822388</v>
       </c>
       <c r="H1866" t="n">
         <v>6951613</v>
@@ -54657,7 +54657,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.60125207901001</v>
+        <v>1.60125195980072</v>
       </c>
       <c r="H1872" t="n">
         <v>6922251</v>
@@ -54918,7 +54918,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.77444386482239</v>
+        <v>1.77444398403168</v>
       </c>
       <c r="H1881" t="n">
         <v>14803240</v>
@@ -55063,7 +55063,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.60125207901001</v>
+        <v>1.60125195980072</v>
       </c>
       <c r="H1886" t="n">
         <v>6292235</v>
@@ -55150,7 +55150,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.73037254810333</v>
+        <v>1.73037266731262</v>
       </c>
       <c r="H1889" t="n">
         <v>8200584</v>
@@ -55237,7 +55237,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.86954474449158</v>
+        <v>1.86954486370087</v>
       </c>
       <c r="H1892" t="n">
         <v>29342749</v>
@@ -55266,7 +55266,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.88346219062805</v>
+        <v>1.88346207141876</v>
       </c>
       <c r="H1893" t="n">
         <v>15431172</v>
@@ -55353,7 +55353,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.68552851676941</v>
+        <v>1.68552839756012</v>
       </c>
       <c r="H1896" t="n">
         <v>10826926</v>
@@ -55382,7 +55382,7 @@
         <v>2.23300004005432</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.72650682926178</v>
+        <v>1.72650671005249</v>
       </c>
       <c r="H1897" t="n">
         <v>13177383</v>
@@ -55527,7 +55527,7 @@
         <v>2.36299991607666</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.82702016830444</v>
+        <v>1.82702004909515</v>
       </c>
       <c r="H1902" t="n">
         <v>11298307</v>
@@ -55556,7 +55556,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.79068064689636</v>
+        <v>1.79068076610565</v>
       </c>
       <c r="H1903" t="n">
         <v>9401467</v>
@@ -55614,7 +55614,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.71645545959473</v>
+        <v>1.71645557880402</v>
       </c>
       <c r="H1905" t="n">
         <v>7081375</v>
@@ -55643,7 +55643,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.73578500747681</v>
+        <v>1.73578488826752</v>
       </c>
       <c r="H1906" t="n">
         <v>5356916</v>
@@ -55759,7 +55759,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1910" t="n">
         <v>7777212</v>
@@ -55788,7 +55788,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.77444386482239</v>
+        <v>1.77444398403168</v>
       </c>
       <c r="H1911" t="n">
         <v>8748249</v>
@@ -55904,7 +55904,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.80150508880615</v>
+        <v>1.80150496959686</v>
       </c>
       <c r="H1915" t="n">
         <v>7696382</v>
@@ -55933,7 +55933,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.81387603282928</v>
+        <v>1.81387591362</v>
       </c>
       <c r="H1916" t="n">
         <v>11063863</v>
@@ -55991,7 +55991,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.92985260486603</v>
+        <v>1.92985272407532</v>
       </c>
       <c r="H1918" t="n">
         <v>16178743</v>
@@ -56020,7 +56020,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96309924125671</v>
+        <v>1.963099360466</v>
       </c>
       <c r="H1919" t="n">
         <v>16639251</v>
@@ -56049,7 +56049,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.96000671386719</v>
+        <v>1.96000683307648</v>
       </c>
       <c r="H1920" t="n">
         <v>11600649</v>
@@ -56078,7 +56078,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.97624337673187</v>
+        <v>1.97624325752258</v>
       </c>
       <c r="H1921" t="n">
         <v>6898571</v>
@@ -56107,7 +56107,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.97160422801971</v>
+        <v>1.97160446643829</v>
       </c>
       <c r="H1922" t="n">
         <v>5995361</v>
@@ -56136,7 +56136,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.95923340320587</v>
+        <v>1.95923328399658</v>
       </c>
       <c r="H1923" t="n">
         <v>6467525</v>
@@ -56165,7 +56165,7 @@
         <v>2.52699995040894</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.95382106304169</v>
+        <v>1.95382118225098</v>
       </c>
       <c r="H1924" t="n">
         <v>4430041</v>
@@ -56194,7 +56194,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.97160422801971</v>
+        <v>1.97160446643829</v>
       </c>
       <c r="H1925" t="n">
         <v>5300597</v>
@@ -56426,7 +56426,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.90356469154358</v>
+        <v>1.90356457233429</v>
       </c>
       <c r="H1933" t="n">
         <v>13404200</v>
@@ -56455,7 +56455,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1934" t="n">
-        <v>1.95691382884979</v>
+        <v>1.95691394805908</v>
       </c>
       <c r="H1934" t="n">
         <v>24640061</v>
@@ -56513,7 +56513,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.9097501039505</v>
+        <v>1.90974998474121</v>
       </c>
       <c r="H1936" t="n">
         <v>39674896</v>
@@ -56542,7 +56542,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.95691382884979</v>
+        <v>1.95691394805908</v>
       </c>
       <c r="H1937" t="n">
         <v>24480809</v>
@@ -56571,7 +56571,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G1938" t="n">
-        <v>1.97005796432495</v>
+        <v>1.97005808353424</v>
       </c>
       <c r="H1938" t="n">
         <v>9538925</v>
@@ -56600,7 +56600,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.03191208839417</v>
+        <v>2.03191232681274</v>
       </c>
       <c r="H1939" t="n">
         <v>13224837</v>
@@ -56658,7 +56658,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.12160086631775</v>
+        <v>2.12160062789917</v>
       </c>
       <c r="H1941" t="n">
         <v>27795440</v>
@@ -56745,7 +56745,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.03500485420227</v>
+        <v>2.03500509262085</v>
       </c>
       <c r="H1944" t="n">
         <v>9682287</v>
@@ -56803,7 +56803,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.97624337673187</v>
+        <v>1.97624325752258</v>
       </c>
       <c r="H1946" t="n">
         <v>12028860</v>
@@ -56861,7 +56861,7 @@
         <v>2.50699996948242</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.93835759162903</v>
+        <v>1.93835783004761</v>
       </c>
       <c r="H1948" t="n">
         <v>8196480</v>
@@ -56890,7 +56890,7 @@
         <v>2.53900003433228</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.96309924125671</v>
+        <v>1.963099360466</v>
       </c>
       <c r="H1949" t="n">
         <v>5429828</v>
@@ -56948,7 +56948,7 @@
         <v>2.62899994850159</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.03268551826477</v>
+        <v>2.03268527984619</v>
       </c>
       <c r="H1951" t="n">
         <v>12173491</v>
@@ -56977,7 +56977,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.98088252544403</v>
+        <v>1.98088264465332</v>
       </c>
       <c r="H1952" t="n">
         <v>14258681</v>
@@ -57006,7 +57006,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.96000671386719</v>
+        <v>1.96000683307648</v>
       </c>
       <c r="H1953" t="n">
         <v>6716319</v>
@@ -57064,7 +57064,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.90511095523834</v>
+        <v>1.90511119365692</v>
       </c>
       <c r="H1955" t="n">
         <v>11937121</v>
@@ -57122,7 +57122,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.74970209598541</v>
+        <v>1.7497022151947</v>
       </c>
       <c r="H1957" t="n">
         <v>16237631</v>
@@ -57238,7 +57238,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.86645221710205</v>
+        <v>1.86645209789276</v>
       </c>
       <c r="H1961" t="n">
         <v>10420578</v>
@@ -57267,7 +57267,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.920574426651</v>
+        <v>1.92057454586029</v>
       </c>
       <c r="H1962" t="n">
         <v>17155594</v>
@@ -57296,7 +57296,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.9267600774765</v>
+        <v>1.92676019668579</v>
       </c>
       <c r="H1963" t="n">
         <v>13390725</v>
@@ -57354,7 +57354,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.09222030639648</v>
+        <v>2.09222006797791</v>
       </c>
       <c r="H1965" t="n">
         <v>37563550</v>
@@ -57383,7 +57383,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.10768389701843</v>
+        <v>2.10768365859985</v>
       </c>
       <c r="H1966" t="n">
         <v>26715391</v>
@@ -57615,7 +57615,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.89737904071808</v>
+        <v>1.89737915992737</v>
       </c>
       <c r="H1974" t="n">
         <v>15191141</v>
@@ -57876,7 +57876,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.94840896129608</v>
+        <v>1.94840908050537</v>
       </c>
       <c r="H1983" t="n">
         <v>25197954</v>
@@ -57905,7 +57905,7 @@
         <v>2.53099989891052</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.95691382884979</v>
+        <v>1.95691394805908</v>
       </c>
       <c r="H1984" t="n">
         <v>32448765</v>
@@ -57992,7 +57992,7 @@
         <v>2.47099995613098</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.91052317619324</v>
+        <v>1.91052305698395</v>
       </c>
       <c r="H1987" t="n">
         <v>16615036</v>
@@ -58050,7 +58050,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.85949349403381</v>
+        <v>1.85949337482452</v>
       </c>
       <c r="H1989" t="n">
         <v>32110096</v>
@@ -58079,7 +58079,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.85408115386963</v>
+        <v>1.85408127307892</v>
       </c>
       <c r="H1990" t="n">
         <v>14799249</v>
@@ -58108,7 +58108,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.81155633926392</v>
+        <v>1.81155645847321</v>
       </c>
       <c r="H1991" t="n">
         <v>6593039</v>
@@ -58137,7 +58137,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.85872042179108</v>
+        <v>1.85872030258179</v>
       </c>
       <c r="H1992" t="n">
         <v>17881971</v>
@@ -58195,7 +58195,7 @@
         <v>2.49699997901917</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.93062567710876</v>
+        <v>1.93062579631805</v>
       </c>
       <c r="H1994" t="n">
         <v>10863078</v>
@@ -58253,7 +58253,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.99866545200348</v>
+        <v>1.99866569042206</v>
       </c>
       <c r="H1996" t="n">
         <v>13386081</v>
@@ -58311,7 +58311,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.05510759353638</v>
+        <v>2.0551073551178</v>
       </c>
       <c r="H1998" t="n">
         <v>14855596</v>
@@ -58340,7 +58340,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1999" t="n">
-        <v>2.03191208839417</v>
+        <v>2.03191232681274</v>
       </c>
       <c r="H1999" t="n">
         <v>11141976</v>
@@ -58601,7 +58601,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.35819339752197</v>
+        <v>2.35819315910339</v>
       </c>
       <c r="H2008" t="n">
         <v>14964188</v>
@@ -58717,7 +58717,7 @@
         <v>2.92899990081787</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.26463890075684</v>
+        <v>2.26463866233826</v>
       </c>
       <c r="H2012" t="n">
         <v>40936353</v>
@@ -58746,7 +58746,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.30716371536255</v>
+        <v>2.30716347694397</v>
       </c>
       <c r="H2013" t="n">
         <v>31624933</v>
@@ -58775,7 +58775,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.28551459312439</v>
+        <v>2.28551483154297</v>
       </c>
       <c r="H2014" t="n">
         <v>26182103</v>
@@ -59007,7 +59007,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G2022" t="n">
-        <v>2.55458068847656</v>
+        <v>2.55458045005798</v>
       </c>
       <c r="H2022" t="n">
         <v>35842230</v>
@@ -59065,7 +59065,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.60329103469849</v>
+        <v>2.60329079627991</v>
       </c>
       <c r="H2024" t="n">
         <v>39561081</v>
@@ -59326,7 +59326,7 @@
         <v>3.07100009918213</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.37443017959595</v>
+        <v>2.37443041801453</v>
       </c>
       <c r="H2033" t="n">
         <v>6292252</v>
@@ -59355,7 +59355,7 @@
         <v>3.11899995803833</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.41154289245605</v>
+        <v>2.41154265403748</v>
       </c>
       <c r="H2034" t="n">
         <v>8906628</v>
@@ -59384,7 +59384,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.3875744342804</v>
+        <v>2.38757419586182</v>
       </c>
       <c r="H2035" t="n">
         <v>9119120</v>
@@ -59413,7 +59413,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.35510087013245</v>
+        <v>2.35510063171387</v>
       </c>
       <c r="H2036" t="n">
         <v>10336670</v>
@@ -59587,7 +59587,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.52597284317017</v>
+        <v>2.52597308158875</v>
       </c>
       <c r="H2042" t="n">
         <v>27175102</v>
@@ -59732,7 +59732,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G2047" t="n">
-        <v>2.41076946258545</v>
+        <v>2.41076970100403</v>
       </c>
       <c r="H2047" t="n">
         <v>12400838</v>
@@ -59790,7 +59790,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.46798467636108</v>
+        <v>2.46798491477966</v>
       </c>
       <c r="H2049" t="n">
         <v>16737351</v>
@@ -59819,7 +59819,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2050" t="n">
-        <v>2.50509738922119</v>
+        <v>2.50509715080261</v>
       </c>
       <c r="H2050" t="n">
         <v>12837166</v>
@@ -59848,7 +59848,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G2051" t="n">
-        <v>2.49891185760498</v>
+        <v>2.49891209602356</v>
       </c>
       <c r="H2051" t="n">
         <v>12882380</v>
@@ -59906,7 +59906,7 @@
         <v>3.38899993896484</v>
       </c>
       <c r="G2053" t="n">
-        <v>2.62030053138733</v>
+        <v>2.62030076980591</v>
       </c>
       <c r="H2053" t="n">
         <v>38395558</v>
@@ -59935,7 +59935,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.59169340133667</v>
+        <v>2.59169316291809</v>
       </c>
       <c r="H2054" t="n">
         <v>26331357</v>
@@ -60167,7 +60167,7 @@
         <v>3.37299990653992</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.60792970657349</v>
+        <v>2.60792994499207</v>
       </c>
       <c r="H2062" t="n">
         <v>29705979</v>
@@ -60283,7 +60283,7 @@
         <v>3.53900003433228</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.73627781867981</v>
+        <v>2.73627758026123</v>
       </c>
       <c r="H2066" t="n">
         <v>30033671</v>
@@ -60312,7 +60312,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.74323606491089</v>
+        <v>2.74323630332947</v>
       </c>
       <c r="H2067" t="n">
         <v>44075315</v>
@@ -60399,7 +60399,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.72467994689941</v>
+        <v>2.72467970848083</v>
       </c>
       <c r="H2070" t="n">
         <v>14759944</v>
@@ -60515,7 +60515,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.83137822151184</v>
+        <v>2.83137845993042</v>
       </c>
       <c r="H2074" t="n">
         <v>31284132</v>
@@ -60544,7 +60544,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.89245939254761</v>
+        <v>2.89245963096619</v>
       </c>
       <c r="H2075" t="n">
         <v>28364901</v>
@@ -60631,7 +60631,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G2078" t="n">
-        <v>2.89245939254761</v>
+        <v>2.89245963096619</v>
       </c>
       <c r="H2078" t="n">
         <v>15255947</v>
@@ -60834,7 +60834,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2085" t="n">
-        <v>2.98292136192322</v>
+        <v>2.9829216003418</v>
       </c>
       <c r="H2085" t="n">
         <v>15537029</v>
@@ -60892,7 +60892,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2087" t="n">
-        <v>3.14219641685486</v>
+        <v>3.14219617843628</v>
       </c>
       <c r="H2087" t="n">
         <v>30756951</v>
@@ -61037,7 +61037,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G2092" t="n">
-        <v>3.33085155487061</v>
+        <v>3.33085179328918</v>
       </c>
       <c r="H2092" t="n">
         <v>20564055</v>
@@ -61066,7 +61066,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2093" t="n">
-        <v>3.36487126350403</v>
+        <v>3.36487150192261</v>
       </c>
       <c r="H2093" t="n">
         <v>20421753</v>
@@ -61240,7 +61240,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2099" t="n">
-        <v>3.24734807014465</v>
+        <v>3.24734830856323</v>
       </c>
       <c r="H2099" t="n">
         <v>35140784</v>
@@ -61298,7 +61298,7 @@
         <v>4.1710000038147</v>
       </c>
       <c r="G2101" t="n">
-        <v>3.22492599487305</v>
+        <v>3.22492623329163</v>
       </c>
       <c r="H2101" t="n">
         <v>15860905</v>
@@ -61356,7 +61356,7 @@
         <v>4.05100011825562</v>
       </c>
       <c r="G2103" t="n">
-        <v>3.13214492797852</v>
+        <v>3.13214468955994</v>
       </c>
       <c r="H2103" t="n">
         <v>26905943</v>
@@ -61385,7 +61385,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G2104" t="n">
-        <v>3.15843272209167</v>
+        <v>3.15843296051025</v>
       </c>
       <c r="H2104" t="n">
         <v>12108834</v>
@@ -61443,7 +61443,7 @@
         <v>4.16699981689453</v>
       </c>
       <c r="G2106" t="n">
-        <v>3.22183322906494</v>
+        <v>3.22183346748352</v>
       </c>
       <c r="H2106" t="n">
         <v>31396325</v>
@@ -61472,7 +61472,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2107" t="n">
-        <v>3.10972237586975</v>
+        <v>3.10972261428833</v>
       </c>
       <c r="H2107" t="n">
         <v>24633782</v>
@@ -61617,7 +61617,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2112" t="n">
-        <v>3.24734807014465</v>
+        <v>3.24734830856323</v>
       </c>
       <c r="H2112" t="n">
         <v>29517947</v>
@@ -61675,7 +61675,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>3.31693458557129</v>
+        <v>3.31693434715271</v>
       </c>
       <c r="H2114" t="n">
         <v>22785909</v>
@@ -61733,7 +61733,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G2116" t="n">
-        <v>3.33085155487061</v>
+        <v>3.33085179328918</v>
       </c>
       <c r="H2116" t="n">
         <v>23312184</v>
@@ -61907,7 +61907,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.51409506797791</v>
+        <v>3.51409482955933</v>
       </c>
       <c r="H2122" t="n">
         <v>36014819</v>
@@ -61965,7 +61965,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2124" t="n">
-        <v>3.6030101776123</v>
+        <v>3.60300993919373</v>
       </c>
       <c r="H2124" t="n">
         <v>34298846</v>
@@ -61994,7 +61994,7 @@
         <v>4.64900016784668</v>
       </c>
       <c r="G2125" t="n">
-        <v>3.59450531005859</v>
+        <v>3.59450507164001</v>
       </c>
       <c r="H2125" t="n">
         <v>25660150</v>
@@ -62023,7 +62023,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2126" t="n">
-        <v>3.62002038955688</v>
+        <v>3.62002015113831</v>
       </c>
       <c r="H2126" t="n">
         <v>19618847</v>
@@ -62052,7 +62052,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.66022539138794</v>
+        <v>3.66022562980652</v>
       </c>
       <c r="H2127" t="n">
         <v>18548351</v>
@@ -62081,7 +62081,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G2128" t="n">
-        <v>3.66873025894165</v>
+        <v>3.66873049736023</v>
       </c>
       <c r="H2128" t="n">
         <v>13092351</v>
@@ -62110,7 +62110,7 @@
         <v>4.8730001449585</v>
       </c>
       <c r="G2129" t="n">
-        <v>3.76769733428955</v>
+        <v>3.76769709587097</v>
       </c>
       <c r="H2129" t="n">
         <v>26746590</v>
@@ -62197,7 +62197,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G2132" t="n">
-        <v>4.09320545196533</v>
+        <v>4.09320497512817</v>
       </c>
       <c r="H2132" t="n">
         <v>33248614</v>
@@ -62255,7 +62255,7 @@
         <v>4.98099994659424</v>
       </c>
       <c r="G2134" t="n">
-        <v>4.04208087921143</v>
+        <v>4.04208040237427</v>
       </c>
       <c r="H2134" t="n">
         <v>12971734</v>
@@ -62458,7 +62458,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2141" t="n">
-        <v>3.99257922172546</v>
+        <v>3.99257898330688</v>
       </c>
       <c r="H2141" t="n">
         <v>26160718</v>
@@ -62516,7 +62516,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G2143" t="n">
-        <v>3.99907112121582</v>
+        <v>3.9990713596344</v>
       </c>
       <c r="H2143" t="n">
         <v>11607781</v>
@@ -62690,7 +62690,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2149" t="n">
-        <v>3.75724411010742</v>
+        <v>3.757244348526</v>
       </c>
       <c r="H2149" t="n">
         <v>21711731</v>
@@ -62719,7 +62719,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2150" t="n">
-        <v>3.78970408439636</v>
+        <v>3.78970456123352</v>
       </c>
       <c r="H2150" t="n">
         <v>15083376</v>
@@ -62748,7 +62748,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G2151" t="n">
-        <v>3.6420111656189</v>
+        <v>3.64201140403748</v>
       </c>
       <c r="H2151" t="n">
         <v>19374406</v>
@@ -62835,7 +62835,7 @@
         <v>4.53200006484985</v>
       </c>
       <c r="G2154" t="n">
-        <v>3.67771744728088</v>
+        <v>3.6777172088623</v>
       </c>
       <c r="H2154" t="n">
         <v>20881847</v>
@@ -62864,7 +62864,7 @@
         <v>4.56699991226196</v>
       </c>
       <c r="G2155" t="n">
-        <v>3.70611977577209</v>
+        <v>3.70611953735352</v>
       </c>
       <c r="H2155" t="n">
         <v>13574114</v>
@@ -62951,7 +62951,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2158" t="n">
-        <v>3.7499406337738</v>
+        <v>3.74994039535522</v>
       </c>
       <c r="H2158" t="n">
         <v>19858583</v>
@@ -63009,7 +63009,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2160" t="n">
-        <v>3.6030592918396</v>
+        <v>3.60305953025818</v>
       </c>
       <c r="H2160" t="n">
         <v>12604005</v>
@@ -63096,7 +63096,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G2163" t="n">
-        <v>3.79700756072998</v>
+        <v>3.79700779914856</v>
       </c>
       <c r="H2163" t="n">
         <v>21436986</v>
@@ -63125,7 +63125,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G2164" t="n">
-        <v>3.7499406337738</v>
+        <v>3.74994039535522</v>
       </c>
       <c r="H2164" t="n">
         <v>10077225</v>
@@ -63154,7 +63154,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G2165" t="n">
-        <v>3.96417689323425</v>
+        <v>3.96417713165283</v>
       </c>
       <c r="H2165" t="n">
         <v>30567140</v>
@@ -63212,7 +63212,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G2167" t="n">
-        <v>3.9252245426178</v>
+        <v>3.92522478103638</v>
       </c>
       <c r="H2167" t="n">
         <v>13060115</v>
@@ -63444,7 +63444,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G2175" t="n">
-        <v>3.99501371383667</v>
+        <v>3.99501347541809</v>
       </c>
       <c r="H2175" t="n">
         <v>11662675</v>
@@ -63676,7 +63676,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G2183" t="n">
-        <v>3.99420213699341</v>
+        <v>3.99420237541199</v>
       </c>
       <c r="H2183" t="n">
         <v>8046997</v>
@@ -63763,7 +63763,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2186" t="n">
-        <v>3.81404900550842</v>
+        <v>3.814049243927</v>
       </c>
       <c r="H2186" t="n">
         <v>21749998</v>
@@ -63792,7 +63792,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G2187" t="n">
-        <v>3.63470768928528</v>
+        <v>3.63470792770386</v>
       </c>
       <c r="H2187" t="n">
         <v>19583127</v>
@@ -63821,7 +63821,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G2188" t="n">
-        <v>3.52028608322144</v>
+        <v>3.52028632164001</v>
       </c>
       <c r="H2188" t="n">
         <v>25013968</v>
@@ -63908,7 +63908,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G2191" t="n">
-        <v>4.07859802246094</v>
+        <v>4.0785984992981</v>
       </c>
       <c r="H2191" t="n">
         <v>19208194</v>
@@ -64111,7 +64111,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2198" t="n">
-        <v>4.22629117965698</v>
+        <v>4.22629165649414</v>
       </c>
       <c r="H2198" t="n">
         <v>10355970</v>
@@ -64140,7 +64140,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G2199" t="n">
-        <v>4.23440647125244</v>
+        <v>4.23440599441528</v>
       </c>
       <c r="H2199" t="n">
         <v>8128461</v>
@@ -64227,7 +64227,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G2202" t="n">
-        <v>4.24089813232422</v>
+        <v>4.24089765548706</v>
       </c>
       <c r="H2202" t="n">
         <v>3987011</v>
@@ -64256,7 +64256,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2203" t="n">
-        <v>4.24414396286011</v>
+        <v>4.24414443969727</v>
       </c>
       <c r="H2203" t="n">
         <v>5969529</v>
@@ -64314,7 +64314,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G2205" t="n">
-        <v>4.23278284072876</v>
+        <v>4.23278331756592</v>
       </c>
       <c r="H2205" t="n">
         <v>7947589</v>
@@ -64372,7 +64372,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G2207" t="n">
-        <v>4.21006107330322</v>
+        <v>4.21006155014038</v>
       </c>
       <c r="H2207" t="n">
         <v>10026352</v>
@@ -64459,7 +64459,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2210" t="n">
-        <v>4.09807395935059</v>
+        <v>4.09807443618774</v>
       </c>
       <c r="H2210" t="n">
         <v>9610643</v>
@@ -64488,7 +64488,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G2211" t="n">
-        <v>3.98608756065369</v>
+        <v>3.98608732223511</v>
       </c>
       <c r="H2211" t="n">
         <v>13196853</v>
@@ -64575,7 +64575,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G2214" t="n">
-        <v>3.96904540061951</v>
+        <v>3.96904563903809</v>
       </c>
       <c r="H2214" t="n">
         <v>12020355</v>
@@ -64691,7 +64691,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G2218" t="n">
-        <v>3.99582529067993</v>
+        <v>3.99582505226135</v>
       </c>
       <c r="H2218" t="n">
         <v>10120832</v>
@@ -64749,7 +64749,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2220" t="n">
-        <v>4.0558762550354</v>
+        <v>4.05587673187256</v>
       </c>
       <c r="H2220" t="n">
         <v>12990332</v>
@@ -64778,7 +64778,7 @@
         <v>4.97100019454956</v>
       </c>
       <c r="G2221" t="n">
-        <v>4.03396558761597</v>
+        <v>4.03396606445312</v>
       </c>
       <c r="H2221" t="n">
         <v>14888759</v>
@@ -64836,7 +64836,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G2223" t="n">
-        <v>4.06074571609497</v>
+        <v>4.06074523925781</v>
       </c>
       <c r="H2223" t="n">
         <v>11996497</v>
@@ -64952,7 +64952,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G2227" t="n">
-        <v>4.20519208908081</v>
+        <v>4.20519256591797</v>
       </c>
       <c r="H2227" t="n">
         <v>12886962</v>
@@ -65039,7 +65039,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G2230" t="n">
-        <v>3.88870716094971</v>
+        <v>3.88870739936829</v>
       </c>
       <c r="H2230" t="n">
         <v>16144924</v>
@@ -65097,7 +65097,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G2232" t="n">
-        <v>4.0558762550354</v>
+        <v>4.05587673187256</v>
       </c>
       <c r="H2232" t="n">
         <v>10452631</v>
@@ -65126,7 +65126,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G2233" t="n">
-        <v>4.1532564163208</v>
+        <v>4.15325593948364</v>
       </c>
       <c r="H2233" t="n">
         <v>16873513</v>
@@ -65155,7 +65155,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G2234" t="n">
-        <v>4.16137075424194</v>
+        <v>4.1613712310791</v>
       </c>
       <c r="H2234" t="n">
         <v>7535202</v>
@@ -65271,7 +65271,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G2238" t="n">
-        <v>4.25712823867798</v>
+        <v>4.25712776184082</v>
       </c>
       <c r="H2238" t="n">
         <v>12216723</v>
@@ -65416,7 +65416,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G2243" t="n">
-        <v>4.2587513923645</v>
+        <v>4.25875091552734</v>
       </c>
       <c r="H2243" t="n">
         <v>8824041</v>
@@ -65445,7 +65445,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G2244" t="n">
-        <v>4.12566566467285</v>
+        <v>4.12566518783569</v>
       </c>
       <c r="H2244" t="n">
         <v>14098523</v>
@@ -65503,7 +65503,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G2246" t="n">
-        <v>4.09645080566406</v>
+        <v>4.09645128250122</v>
       </c>
       <c r="H2246" t="n">
         <v>9115898</v>
@@ -65561,7 +65561,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G2248" t="n">
-        <v>4.14838743209839</v>
+        <v>4.14838695526123</v>
       </c>
       <c r="H2248" t="n">
         <v>9089883</v>
@@ -65677,7 +65677,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G2252" t="n">
-        <v>4.13702630996704</v>
+        <v>4.13702583312988</v>
       </c>
       <c r="H2252" t="n">
         <v>8443415</v>
@@ -65764,7 +65764,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G2255" t="n">
-        <v>4.22629117965698</v>
+        <v>4.22629165649414</v>
       </c>
       <c r="H2255" t="n">
         <v>19992634</v>
@@ -65880,7 +65880,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G2259" t="n">
-        <v>4.47623252868652</v>
+        <v>4.47623300552368</v>
       </c>
       <c r="H2259" t="n">
         <v>24618281</v>
@@ -65938,7 +65938,7 @@
         <v>6.01800012588501</v>
       </c>
       <c r="G2261" t="n">
-        <v>4.88360643386841</v>
+        <v>4.88360595703125</v>
       </c>
       <c r="H2261" t="n">
         <v>15163406</v>
@@ -66083,7 +66083,7 @@
         <v>5.93200016021729</v>
       </c>
       <c r="G2266" t="n">
-        <v>4.81381750106812</v>
+        <v>4.81381702423096</v>
       </c>
       <c r="H2266" t="n">
         <v>14209848</v>
@@ -66373,7 +66373,7 @@
         <v>6.37200021743774</v>
       </c>
       <c r="G2276" t="n">
-        <v>5.17087745666504</v>
+        <v>5.17087697982788</v>
       </c>
       <c r="H2276" t="n">
         <v>8697069</v>
@@ -66402,7 +66402,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2277" t="n">
-        <v>5.1286792755127</v>
+        <v>5.12867879867554</v>
       </c>
       <c r="H2277" t="n">
         <v>9776574</v>
@@ -66721,7 +66721,7 @@
         <v>6.65199995040894</v>
       </c>
       <c r="G2288" t="n">
-        <v>5.39809703826904</v>
+        <v>5.39809656143188</v>
       </c>
       <c r="H2288" t="n">
         <v>5442007</v>
@@ -66779,7 +66779,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2290" t="n">
-        <v>5.44516372680664</v>
+        <v>5.4451642036438</v>
       </c>
       <c r="H2290" t="n">
         <v>13302467</v>
@@ -66837,7 +66837,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2292" t="n">
-        <v>5.52631425857544</v>
+        <v>5.52631378173828</v>
       </c>
       <c r="H2292" t="n">
         <v>8534256</v>
@@ -66924,7 +66924,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2295" t="n">
-        <v>5.71133613586426</v>
+        <v>5.7113356590271</v>
       </c>
       <c r="H2295" t="n">
         <v>13899191</v>
@@ -67011,7 +67011,7 @@
         <v>7.03800010681152</v>
       </c>
       <c r="G2298" t="n">
-        <v>5.71133613586426</v>
+        <v>5.7113356590271</v>
       </c>
       <c r="H2298" t="n">
         <v>10737504</v>
@@ -67040,7 +67040,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2299" t="n">
-        <v>5.7421727180481</v>
+        <v>5.74217319488525</v>
       </c>
       <c r="H2299" t="n">
         <v>12020301</v>
@@ -67069,7 +67069,7 @@
         <v>7.07600021362305</v>
       </c>
       <c r="G2300" t="n">
-        <v>5.7421727180481</v>
+        <v>5.74217319488525</v>
       </c>
       <c r="H2300" t="n">
         <v>10188937</v>
@@ -67098,7 +67098,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G2301" t="n">
-        <v>5.7194504737854</v>
+        <v>5.71945095062256</v>
       </c>
       <c r="H2301" t="n">
         <v>9495869</v>
@@ -67272,7 +67272,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G2307" t="n">
-        <v>5.16276168823242</v>
+        <v>5.16276216506958</v>
       </c>
       <c r="H2307" t="n">
         <v>34036799</v>
@@ -67359,7 +67359,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G2310" t="n">
-        <v>5.05402088165283</v>
+        <v>5.05402135848999</v>
       </c>
       <c r="H2310" t="n">
         <v>20549379</v>
@@ -67417,7 +67417,7 @@
         <v>6.30200004577637</v>
       </c>
       <c r="G2312" t="n">
-        <v>5.1140718460083</v>
+        <v>5.11407232284546</v>
       </c>
       <c r="H2312" t="n">
         <v>15019935</v>
@@ -67620,7 +67620,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2319" t="n">
-        <v>5.1286792755127</v>
+        <v>5.12867879867554</v>
       </c>
       <c r="H2319" t="n">
         <v>15133688</v>
@@ -67852,7 +67852,7 @@
         <v>6.60799980163574</v>
       </c>
       <c r="G2327" t="n">
-        <v>5.36239051818848</v>
+        <v>5.36239099502563</v>
       </c>
       <c r="H2327" t="n">
         <v>26555901</v>
@@ -67910,7 +67910,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G2329" t="n">
-        <v>5.69835138320923</v>
+        <v>5.69835186004639</v>
       </c>
       <c r="H2329" t="n">
         <v>30197117</v>
@@ -67939,7 +67939,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G2330" t="n">
-        <v>5.69348239898682</v>
+        <v>5.69348287582397</v>
       </c>
       <c r="H2330" t="n">
         <v>20333854</v>
@@ -67997,7 +67997,7 @@
         <v>7.11800003051758</v>
       </c>
       <c r="G2332" t="n">
-        <v>5.77625608444214</v>
+        <v>5.77625560760498</v>
       </c>
       <c r="H2332" t="n">
         <v>25105102</v>
@@ -68142,7 +68142,7 @@
         <v>6.88800001144409</v>
       </c>
       <c r="G2337" t="n">
-        <v>5.5896110534668</v>
+        <v>5.58961057662964</v>
       </c>
       <c r="H2337" t="n">
         <v>31043675</v>
@@ -68229,7 +68229,7 @@
         <v>7.09600019454956</v>
       </c>
       <c r="G2340" t="n">
-        <v>5.75840282440186</v>
+        <v>5.75840330123901</v>
       </c>
       <c r="H2340" t="n">
         <v>18107631</v>
@@ -68345,7 +68345,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2344" t="n">
-        <v>6.34592866897583</v>
+        <v>6.34592914581299</v>
       </c>
       <c r="H2344" t="n">
         <v>26774763</v>
@@ -68403,7 +68403,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G2346" t="n">
-        <v>6.17064523696899</v>
+        <v>6.17064476013184</v>
       </c>
       <c r="H2346" t="n">
         <v>35553613</v>
@@ -68780,7 +68780,7 @@
         <v>5.89300012588501</v>
       </c>
       <c r="G2359" t="n">
-        <v>4.7821683883667</v>
+        <v>4.78216886520386</v>
       </c>
       <c r="H2359" t="n">
         <v>19388932</v>
@@ -68809,7 +68809,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G2360" t="n">
-        <v>5.01019954681396</v>
+        <v>5.01020002365112</v>
       </c>
       <c r="H2360" t="n">
         <v>25575508</v>
@@ -68896,7 +68896,7 @@
         <v>6.67799997329712</v>
       </c>
       <c r="G2363" t="n">
-        <v>5.41919612884521</v>
+        <v>5.41919565200806</v>
       </c>
       <c r="H2363" t="n">
         <v>16423481</v>
@@ -68954,7 +68954,7 @@
         <v>6.53200006484985</v>
       </c>
       <c r="G2365" t="n">
-        <v>5.30071687698364</v>
+        <v>5.3007173538208</v>
       </c>
       <c r="H2365" t="n">
         <v>10138487</v>
@@ -68983,7 +68983,7 @@
         <v>6.50899982452393</v>
       </c>
       <c r="G2366" t="n">
-        <v>5.28205251693726</v>
+        <v>5.2820520401001</v>
       </c>
       <c r="H2366" t="n">
         <v>11026759</v>
@@ -69273,7 +69273,7 @@
         <v>7.48899984359741</v>
       </c>
       <c r="G2376" t="n">
-        <v>6.07732200622559</v>
+        <v>6.07732248306274</v>
       </c>
       <c r="H2376" t="n">
         <v>12569452</v>
@@ -69302,7 +69302,7 @@
         <v>7.68400001525879</v>
       </c>
       <c r="G2377" t="n">
-        <v>6.23556518554688</v>
+        <v>6.23556470870972</v>
       </c>
       <c r="H2377" t="n">
         <v>20468675</v>
@@ -69418,7 +69418,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G2381" t="n">
-        <v>6.72733402252197</v>
+        <v>6.72733354568481</v>
       </c>
       <c r="H2381" t="n">
         <v>21907312</v>
@@ -69447,7 +69447,7 @@
         <v>8.14200019836426</v>
       </c>
       <c r="G2382" t="n">
-        <v>6.60723161697388</v>
+        <v>6.60723209381104</v>
       </c>
       <c r="H2382" t="n">
         <v>27889420</v>
@@ -69476,7 +69476,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G2383" t="n">
-        <v>6.55286121368408</v>
+        <v>6.55286073684692</v>
       </c>
       <c r="H2383" t="n">
         <v>25770231</v>
@@ -80180,9 +80180,38 @@
         <v>10.8760004043579</v>
       </c>
       <c r="H2752" t="n">
-        <v>5545530</v>
+        <v>5549422</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>10.8280000686646</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>10.9739999771118</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>10.7760000228882</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>10.9020004272461</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>10.9020004272461</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>8127528</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BMPS.MI.xlsx
+++ b/data/BMPS.MI.xlsx
@@ -601,7 +601,7 @@
         <v>1933.67529296875</v>
       </c>
       <c r="G8" t="n">
-        <v>1495.07556152344</v>
+        <v>1495.07543945312</v>
       </c>
       <c r="H8" t="n">
         <v>53763</v>
@@ -978,7 +978,7 @@
         <v>1381.49438476562</v>
       </c>
       <c r="G21" t="n">
-        <v>1068.14135742188</v>
+        <v>1068.14123535156</v>
       </c>
       <c r="H21" t="n">
         <v>67666</v>
@@ -1094,7 +1094,7 @@
         <v>1187.71008300781</v>
       </c>
       <c r="G25" t="n">
-        <v>918.3115234375</v>
+        <v>918.311462402344</v>
       </c>
       <c r="H25" t="n">
         <v>64565</v>
@@ -1239,7 +1239,7 @@
         <v>1009.34521484375</v>
       </c>
       <c r="G30" t="n">
-        <v>780.403625488281</v>
+        <v>780.403686523438</v>
       </c>
       <c r="H30" t="n">
         <v>46957</v>
@@ -1297,7 +1297,7 @@
         <v>1044.97644042969</v>
       </c>
       <c r="G32" t="n">
-        <v>807.952941894531</v>
+        <v>807.953002929688</v>
       </c>
       <c r="H32" t="n">
         <v>67475</v>
@@ -1355,7 +1355,7 @@
         <v>1198.12854003906</v>
       </c>
       <c r="G34" t="n">
-        <v>926.366760253906</v>
+        <v>926.366882324219</v>
       </c>
       <c r="H34" t="n">
         <v>65735</v>
@@ -1442,7 +1442,7 @@
         <v>1115.82238769531</v>
       </c>
       <c r="G37" t="n">
-        <v>862.729553222656</v>
+        <v>862.7294921875</v>
       </c>
       <c r="H37" t="n">
         <v>36987</v>
@@ -1500,7 +1500,7 @@
         <v>1073.1064453125</v>
       </c>
       <c r="G39" t="n">
-        <v>829.702453613281</v>
+        <v>829.702514648438</v>
       </c>
       <c r="H39" t="n">
         <v>36745</v>
@@ -1616,7 +1616,7 @@
         <v>1076.23205566406</v>
       </c>
       <c r="G43" t="n">
-        <v>832.119079589844</v>
+        <v>832.119140625</v>
       </c>
       <c r="H43" t="n">
         <v>62505</v>
@@ -1703,7 +1703,7 @@
         <v>1167.91491699219</v>
       </c>
       <c r="G46" t="n">
-        <v>903.00634765625</v>
+        <v>903.006286621094</v>
       </c>
       <c r="H46" t="n">
         <v>46525</v>
@@ -2022,7 +2022,7 @@
         <v>1289.8115234375</v>
       </c>
       <c r="G57" t="n">
-        <v>997.254150390625</v>
+        <v>997.254089355469</v>
       </c>
       <c r="H57" t="n">
         <v>46915</v>
@@ -2109,7 +2109,7 @@
         <v>1177.29162597656</v>
       </c>
       <c r="G60" t="n">
-        <v>910.256164550781</v>
+        <v>910.256225585938</v>
       </c>
       <c r="H60" t="n">
         <v>37028</v>
@@ -2138,7 +2138,7 @@
         <v>1121.03161621094</v>
       </c>
       <c r="G61" t="n">
-        <v>866.757202148438</v>
+        <v>866.757141113281</v>
       </c>
       <c r="H61" t="n">
         <v>44323</v>
@@ -2225,7 +2225,7 @@
         <v>1040.18395996094</v>
       </c>
       <c r="G64" t="n">
-        <v>804.247497558594</v>
+        <v>804.24755859375</v>
       </c>
       <c r="H64" t="n">
         <v>34669</v>
@@ -2254,7 +2254,7 @@
         <v>1000.80200195312</v>
       </c>
       <c r="G65" t="n">
-        <v>773.798217773438</v>
+        <v>773.798278808594</v>
       </c>
       <c r="H65" t="n">
         <v>36991</v>
@@ -2341,7 +2341,7 @@
         <v>908.702392578125</v>
       </c>
       <c r="G68" t="n">
-        <v>702.588806152344</v>
+        <v>702.5888671875</v>
       </c>
       <c r="H68" t="n">
         <v>37316</v>
@@ -2399,7 +2399,7 @@
         <v>1076.23205566406</v>
       </c>
       <c r="G70" t="n">
-        <v>832.119079589844</v>
+        <v>832.119140625</v>
       </c>
       <c r="H70" t="n">
         <v>65174</v>
@@ -2602,7 +2602,7 @@
         <v>1404.4150390625</v>
       </c>
       <c r="G77" t="n">
-        <v>1085.86315917969</v>
+        <v>1085.86303710938</v>
       </c>
       <c r="H77" t="n">
         <v>60062</v>
@@ -2747,7 +2747,7 @@
         <v>1470.05163574219</v>
       </c>
       <c r="G82" t="n">
-        <v>1136.61181640625</v>
+        <v>1136.61193847656</v>
       </c>
       <c r="H82" t="n">
         <v>43127</v>
@@ -2805,7 +2805,7 @@
         <v>1472.13537597656</v>
       </c>
       <c r="G84" t="n">
-        <v>1138.22302246094</v>
+        <v>1138.22290039062</v>
       </c>
       <c r="H84" t="n">
         <v>42537</v>
@@ -2834,7 +2834,7 @@
         <v>1390.87097167969</v>
       </c>
       <c r="G85" t="n">
-        <v>1075.39099121094</v>
+        <v>1075.39111328125</v>
       </c>
       <c r="H85" t="n">
         <v>43075</v>
@@ -2863,7 +2863,7 @@
         <v>1285.64404296875</v>
       </c>
       <c r="G86" t="n">
-        <v>994.031921386719</v>
+        <v>994.031799316406</v>
       </c>
       <c r="H86" t="n">
         <v>50926</v>
@@ -3095,7 +3095,7 @@
         <v>1168.95678710938</v>
       </c>
       <c r="G94" t="n">
-        <v>903.811950683594</v>
+        <v>903.811889648438</v>
       </c>
       <c r="H94" t="n">
         <v>30176</v>
@@ -3124,7 +3124,7 @@
         <v>1163.74755859375</v>
       </c>
       <c r="G95" t="n">
-        <v>899.784240722656</v>
+        <v>899.7841796875</v>
       </c>
       <c r="H95" t="n">
         <v>21832</v>
@@ -3240,7 +3240,7 @@
         <v>1174.166015625</v>
       </c>
       <c r="G99" t="n">
-        <v>907.839477539062</v>
+        <v>907.839538574219</v>
       </c>
       <c r="H99" t="n">
         <v>19584</v>
@@ -3269,7 +3269,7 @@
         <v>1159.580078125</v>
       </c>
       <c r="G100" t="n">
-        <v>896.56201171875</v>
+        <v>896.561950683594</v>
       </c>
       <c r="H100" t="n">
         <v>16345</v>
@@ -3298,7 +3298,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G101" t="n">
-        <v>990.809814453125</v>
+        <v>990.809692382812</v>
       </c>
       <c r="H101" t="n">
         <v>46314</v>
@@ -3530,7 +3530,7 @@
         <v>1214.79821777344</v>
       </c>
       <c r="G109" t="n">
-        <v>939.255554199219</v>
+        <v>939.255432128906</v>
       </c>
       <c r="H109" t="n">
         <v>27462</v>
@@ -3588,7 +3588,7 @@
         <v>1281.47668457031</v>
       </c>
       <c r="G111" t="n">
-        <v>990.809814453125</v>
+        <v>990.809692382812</v>
       </c>
       <c r="H111" t="n">
         <v>28141</v>
@@ -3849,7 +3849,7 @@
         <v>1123.11535644531</v>
       </c>
       <c r="G120" t="n">
-        <v>868.368225097656</v>
+        <v>868.368286132812</v>
       </c>
       <c r="H120" t="n">
         <v>32561</v>
@@ -3965,7 +3965,7 @@
         <v>946.417419433594</v>
       </c>
       <c r="G124" t="n">
-        <v>731.749328613281</v>
+        <v>731.749267578125</v>
       </c>
       <c r="H124" t="n">
         <v>64325</v>
@@ -3994,7 +3994,7 @@
         <v>820.145080566406</v>
       </c>
       <c r="G125" t="n">
-        <v>634.118286132812</v>
+        <v>634.118225097656</v>
       </c>
       <c r="H125" t="n">
         <v>71078</v>
@@ -4139,7 +4139,7 @@
         <v>685.537902832031</v>
       </c>
       <c r="G130" t="n">
-        <v>530.042907714844</v>
+        <v>530.04296875</v>
       </c>
       <c r="H130" t="n">
         <v>79855</v>
@@ -4168,7 +4168,7 @@
         <v>552.597717285156</v>
       </c>
       <c r="G131" t="n">
-        <v>427.256500244141</v>
+        <v>427.256469726562</v>
       </c>
       <c r="H131" t="n">
         <v>109680</v>
@@ -4197,7 +4197,7 @@
         <v>586.145324707031</v>
       </c>
       <c r="G132" t="n">
-        <v>453.194763183594</v>
+        <v>453.194793701172</v>
       </c>
       <c r="H132" t="n">
         <v>69237</v>
@@ -4255,7 +4255,7 @@
         <v>582.394653320312</v>
       </c>
       <c r="G134" t="n">
-        <v>450.294860839844</v>
+        <v>450.294830322266</v>
       </c>
       <c r="H134" t="n">
         <v>57016</v>
@@ -4313,7 +4313,7 @@
         <v>645.947570800781</v>
       </c>
       <c r="G136" t="n">
-        <v>499.432525634766</v>
+        <v>499.432556152344</v>
       </c>
       <c r="H136" t="n">
         <v>59299</v>
@@ -4400,7 +4400,7 @@
         <v>709.083740234375</v>
       </c>
       <c r="G139" t="n">
-        <v>548.248107910156</v>
+        <v>548.248046875</v>
       </c>
       <c r="H139" t="n">
         <v>39413</v>
@@ -4458,7 +4458,7 @@
         <v>673.244079589844</v>
       </c>
       <c r="G141" t="n">
-        <v>520.53759765625</v>
+        <v>520.537658691406</v>
       </c>
       <c r="H141" t="n">
         <v>36777</v>
@@ -4487,7 +4487,7 @@
         <v>660.533508300781</v>
       </c>
       <c r="G142" t="n">
-        <v>510.710083007812</v>
+        <v>510.710052490234</v>
       </c>
       <c r="H142" t="n">
         <v>34841</v>
@@ -4719,7 +4719,7 @@
         <v>645.947570800781</v>
       </c>
       <c r="G150" t="n">
-        <v>499.432525634766</v>
+        <v>499.432556152344</v>
       </c>
       <c r="H150" t="n">
         <v>48364</v>
@@ -4777,7 +4777,7 @@
         <v>551.764282226562</v>
       </c>
       <c r="G152" t="n">
-        <v>426.612121582031</v>
+        <v>426.612091064453</v>
       </c>
       <c r="H152" t="n">
         <v>35494</v>
@@ -4893,7 +4893,7 @@
         <v>512.799011230469</v>
       </c>
       <c r="G156" t="n">
-        <v>396.485015869141</v>
+        <v>396.484985351562</v>
       </c>
       <c r="H156" t="n">
         <v>51516</v>
@@ -4922,7 +4922,7 @@
         <v>515.299499511719</v>
       </c>
       <c r="G157" t="n">
-        <v>398.418304443359</v>
+        <v>398.418334960938</v>
       </c>
       <c r="H157" t="n">
         <v>17072</v>
@@ -5154,7 +5154,7 @@
         <v>494.879211425781</v>
       </c>
       <c r="G165" t="n">
-        <v>382.629791259766</v>
+        <v>382.629821777344</v>
       </c>
       <c r="H165" t="n">
         <v>15915</v>
@@ -5299,7 +5299,7 @@
         <v>503.630737304688</v>
       </c>
       <c r="G170" t="n">
-        <v>389.396301269531</v>
+        <v>389.396270751953</v>
       </c>
       <c r="H170" t="n">
         <v>13936</v>
@@ -5415,7 +5415,7 @@
         <v>497.588012695312</v>
       </c>
       <c r="G174" t="n">
-        <v>384.724182128906</v>
+        <v>384.724212646484</v>
       </c>
       <c r="H174" t="n">
         <v>11728</v>
@@ -5473,7 +5473,7 @@
         <v>491.545288085938</v>
       </c>
       <c r="G176" t="n">
-        <v>380.052093505859</v>
+        <v>380.052062988281</v>
       </c>
       <c r="H176" t="n">
         <v>10221</v>
@@ -5560,7 +5560,7 @@
         <v>481.126770019531</v>
       </c>
       <c r="G179" t="n">
-        <v>371.996734619141</v>
+        <v>371.996704101562</v>
       </c>
       <c r="H179" t="n">
         <v>19101</v>
@@ -5589,7 +5589,7 @@
         <v>476.125885009766</v>
       </c>
       <c r="G180" t="n">
-        <v>368.130126953125</v>
+        <v>368.130157470703</v>
       </c>
       <c r="H180" t="n">
         <v>18405</v>
@@ -5647,7 +5647,7 @@
         <v>464.248779296875</v>
       </c>
       <c r="G182" t="n">
-        <v>358.947021484375</v>
+        <v>358.947052001953</v>
       </c>
       <c r="H182" t="n">
         <v>28648</v>
@@ -5734,7 +5734,7 @@
         <v>390.069000244141</v>
       </c>
       <c r="G185" t="n">
-        <v>301.592864990234</v>
+        <v>301.592834472656</v>
       </c>
       <c r="H185" t="n">
         <v>38113</v>
@@ -5763,7 +5763,7 @@
         <v>399.654022216797</v>
       </c>
       <c r="G186" t="n">
-        <v>309.003784179688</v>
+        <v>309.003753662109</v>
       </c>
       <c r="H186" t="n">
         <v>27102</v>
@@ -5850,7 +5850,7 @@
         <v>398.195434570312</v>
       </c>
       <c r="G189" t="n">
-        <v>307.876037597656</v>
+        <v>307.876007080078</v>
       </c>
       <c r="H189" t="n">
         <v>25724</v>
@@ -5908,7 +5908,7 @@
         <v>403.196319580078</v>
       </c>
       <c r="G191" t="n">
-        <v>311.742584228516</v>
+        <v>311.742614746094</v>
       </c>
       <c r="H191" t="n">
         <v>13716</v>
@@ -5937,7 +5937,7 @@
         <v>392.361053466797</v>
       </c>
       <c r="G192" t="n">
-        <v>303.365020751953</v>
+        <v>303.364990234375</v>
       </c>
       <c r="H192" t="n">
         <v>11171</v>
@@ -6053,7 +6053,7 @@
         <v>361.939025878906</v>
       </c>
       <c r="G196" t="n">
-        <v>279.843322753906</v>
+        <v>279.843353271484</v>
       </c>
       <c r="H196" t="n">
         <v>54804</v>
@@ -6488,7 +6488,7 @@
         <v>561.557678222656</v>
       </c>
       <c r="G211" t="n">
-        <v>434.184112548828</v>
+        <v>434.184143066406</v>
       </c>
       <c r="H211" t="n">
         <v>136414</v>
@@ -6575,7 +6575,7 @@
         <v>506.547943115234</v>
       </c>
       <c r="G214" t="n">
-        <v>391.651824951172</v>
+        <v>391.651794433594</v>
       </c>
       <c r="H214" t="n">
         <v>68364</v>
@@ -6807,7 +6807,7 @@
         <v>537.595092773438</v>
       </c>
       <c r="G222" t="n">
-        <v>415.656768798828</v>
+        <v>415.656799316406</v>
       </c>
       <c r="H222" t="n">
         <v>116257</v>
@@ -6894,7 +6894,7 @@
         <v>524.884521484375</v>
       </c>
       <c r="G225" t="n">
-        <v>405.829223632812</v>
+        <v>405.829254150391</v>
       </c>
       <c r="H225" t="n">
         <v>74636</v>
@@ -6981,7 +6981,7 @@
         <v>492.587127685547</v>
       </c>
       <c r="G228" t="n">
-        <v>380.857635498047</v>
+        <v>380.857604980469</v>
       </c>
       <c r="H228" t="n">
         <v>55438</v>
@@ -7068,7 +7068,7 @@
         <v>464.040405273438</v>
       </c>
       <c r="G231" t="n">
-        <v>358.785888671875</v>
+        <v>358.785919189453</v>
       </c>
       <c r="H231" t="n">
         <v>44014</v>
@@ -7271,7 +7271,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G238" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H238" t="n">
         <v>56464</v>
@@ -7300,7 +7300,7 @@
         <v>389.235473632812</v>
       </c>
       <c r="G239" t="n">
-        <v>300.948364257812</v>
+        <v>300.948394775391</v>
       </c>
       <c r="H239" t="n">
         <v>60863</v>
@@ -7416,7 +7416,7 @@
         <v>406.321838378906</v>
       </c>
       <c r="G243" t="n">
-        <v>314.1591796875</v>
+        <v>314.159149169922</v>
       </c>
       <c r="H243" t="n">
         <v>108228</v>
@@ -7474,7 +7474,7 @@
         <v>426.742126464844</v>
       </c>
       <c r="G245" t="n">
-        <v>329.947692871094</v>
+        <v>329.947723388672</v>
       </c>
       <c r="H245" t="n">
         <v>45235</v>
@@ -7648,7 +7648,7 @@
         <v>339.643371582031</v>
       </c>
       <c r="G251" t="n">
-        <v>262.604858398438</v>
+        <v>262.604827880859</v>
       </c>
       <c r="H251" t="n">
         <v>159767</v>
@@ -14028,7 +14028,7 @@
         <v>97.5172424316406</v>
       </c>
       <c r="G471" t="n">
-        <v>75.3982086181641</v>
+        <v>75.3982009887695</v>
       </c>
       <c r="H471" t="n">
         <v>60497</v>
@@ -14057,7 +14057,7 @@
         <v>97.0588302612305</v>
       </c>
       <c r="G472" t="n">
-        <v>75.0437698364258</v>
+        <v>75.0437622070312</v>
       </c>
       <c r="H472" t="n">
         <v>68056</v>
@@ -14115,7 +14115,7 @@
         <v>93.7249069213867</v>
       </c>
       <c r="G474" t="n">
-        <v>72.4660568237305</v>
+        <v>72.4660491943359</v>
       </c>
       <c r="H474" t="n">
         <v>152747</v>
@@ -14231,7 +14231,7 @@
         <v>85.4734420776367</v>
       </c>
       <c r="G478" t="n">
-        <v>66.0861968994141</v>
+        <v>66.0862045288086</v>
       </c>
       <c r="H478" t="n">
         <v>120033</v>
@@ -14260,7 +14260,7 @@
         <v>81.6394348144531</v>
       </c>
       <c r="G479" t="n">
-        <v>63.1218338012695</v>
+        <v>63.121826171875</v>
       </c>
       <c r="H479" t="n">
         <v>202691</v>
@@ -14318,7 +14318,7 @@
         <v>72.72119140625</v>
       </c>
       <c r="G481" t="n">
-        <v>56.226432800293</v>
+        <v>56.2264366149902</v>
       </c>
       <c r="H481" t="n">
         <v>308433</v>
@@ -14347,7 +14347,7 @@
         <v>69.7206573486328</v>
       </c>
       <c r="G482" t="n">
-        <v>53.906494140625</v>
+        <v>53.9064903259277</v>
       </c>
       <c r="H482" t="n">
         <v>255815</v>
@@ -14579,7 +14579,7 @@
         <v>84.056526184082</v>
       </c>
       <c r="G490" t="n">
-        <v>64.9906768798828</v>
+        <v>64.9906692504883</v>
       </c>
       <c r="H490" t="n">
         <v>123807</v>
@@ -14724,7 +14724,7 @@
         <v>82.3062210083008</v>
       </c>
       <c r="G495" t="n">
-        <v>63.6373710632324</v>
+        <v>63.637378692627</v>
       </c>
       <c r="H495" t="n">
         <v>41220</v>
@@ -14753,7 +14753,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G496" t="n">
-        <v>62.8318328857422</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H496" t="n">
         <v>50947</v>
@@ -14811,7 +14811,7 @@
         <v>80.6392593383789</v>
       </c>
       <c r="G498" t="n">
-        <v>62.3485107421875</v>
+        <v>62.3485145568848</v>
       </c>
       <c r="H498" t="n">
         <v>58360</v>
@@ -14898,7 +14898,7 @@
         <v>79.0973205566406</v>
       </c>
       <c r="G501" t="n">
-        <v>61.1563186645508</v>
+        <v>61.156322479248</v>
       </c>
       <c r="H501" t="n">
         <v>62771</v>
@@ -14927,7 +14927,7 @@
         <v>78.430534362793</v>
       </c>
       <c r="G502" t="n">
-        <v>60.6407775878906</v>
+        <v>60.6407737731934</v>
       </c>
       <c r="H502" t="n">
         <v>45614</v>
@@ -15246,7 +15246,7 @@
         <v>80.7226028442383</v>
       </c>
       <c r="G513" t="n">
-        <v>62.4129486083984</v>
+        <v>62.412956237793</v>
       </c>
       <c r="H513" t="n">
         <v>27484</v>
@@ -15275,7 +15275,7 @@
         <v>81.5977630615234</v>
       </c>
       <c r="G514" t="n">
-        <v>63.0896110534668</v>
+        <v>63.0896034240723</v>
       </c>
       <c r="H514" t="n">
         <v>53122</v>
@@ -15362,7 +15362,7 @@
         <v>80.0141448974609</v>
       </c>
       <c r="G517" t="n">
-        <v>61.8651962280273</v>
+        <v>61.8651885986328</v>
       </c>
       <c r="H517" t="n">
         <v>45464</v>
@@ -15420,7 +15420,7 @@
         <v>81.8894805908203</v>
       </c>
       <c r="G519" t="n">
-        <v>63.3151588439941</v>
+        <v>63.3151512145996</v>
       </c>
       <c r="H519" t="n">
         <v>98758</v>
@@ -15565,7 +15565,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G524" t="n">
-        <v>62.8318328857422</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H524" t="n">
         <v>49745</v>
@@ -15623,7 +15623,7 @@
         <v>81.7644577026367</v>
       </c>
       <c r="G526" t="n">
-        <v>63.2184982299805</v>
+        <v>63.2184906005859</v>
       </c>
       <c r="H526" t="n">
         <v>61036</v>
@@ -15681,7 +15681,7 @@
         <v>81.2643661499023</v>
       </c>
       <c r="G528" t="n">
-        <v>62.8318328857422</v>
+        <v>62.8318367004395</v>
       </c>
       <c r="H528" t="n">
         <v>57552</v>
@@ -15884,7 +15884,7 @@
         <v>75.9717636108398</v>
       </c>
       <c r="G535" t="n">
-        <v>58.7397079467773</v>
+        <v>58.7397041320801</v>
       </c>
       <c r="H535" t="n">
         <v>102598</v>
@@ -15913,7 +15913,7 @@
         <v>75.1591186523438</v>
       </c>
       <c r="G536" t="n">
-        <v>58.111385345459</v>
+        <v>58.1113929748535</v>
       </c>
       <c r="H536" t="n">
         <v>86581</v>
@@ -16145,7 +16145,7 @@
         <v>71.8877105712891</v>
       </c>
       <c r="G544" t="n">
-        <v>55.5820083618164</v>
+        <v>55.5820121765137</v>
       </c>
       <c r="H544" t="n">
         <v>70492</v>
@@ -16174,7 +16174,7 @@
         <v>72.1377563476562</v>
       </c>
       <c r="G545" t="n">
-        <v>55.7753410339355</v>
+        <v>55.7753372192383</v>
       </c>
       <c r="H545" t="n">
         <v>35747</v>
@@ -16232,7 +16232,7 @@
         <v>71.075065612793</v>
       </c>
       <c r="G547" t="n">
-        <v>54.953685760498</v>
+        <v>54.9536895751953</v>
       </c>
       <c r="H547" t="n">
         <v>43186</v>
@@ -16377,7 +16377,7 @@
         <v>67.3035659790039</v>
       </c>
       <c r="G552" t="n">
-        <v>52.0376510620117</v>
+        <v>52.0376472473145</v>
       </c>
       <c r="H552" t="n">
         <v>75893</v>
@@ -16406,7 +16406,7 @@
         <v>66.9910125732422</v>
       </c>
       <c r="G553" t="n">
-        <v>51.7959899902344</v>
+        <v>51.7959861755371</v>
       </c>
       <c r="H553" t="n">
         <v>50170</v>
@@ -16522,7 +16522,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G557" t="n">
-        <v>51.2321166992188</v>
+        <v>51.2321128845215</v>
       </c>
       <c r="H557" t="n">
         <v>73571</v>
@@ -16551,7 +16551,7 @@
         <v>66.26171875</v>
       </c>
       <c r="G558" t="n">
-        <v>51.2321166992188</v>
+        <v>51.2321128845215</v>
       </c>
       <c r="H558" t="n">
         <v>20722</v>
@@ -16609,7 +16609,7 @@
         <v>65.4282302856445</v>
       </c>
       <c r="G560" t="n">
-        <v>50.5876808166504</v>
+        <v>50.5876770019531</v>
       </c>
       <c r="H560" t="n">
         <v>38087</v>
@@ -16638,7 +16638,7 @@
         <v>65.0114974975586</v>
       </c>
       <c r="G561" t="n">
-        <v>50.2654685974121</v>
+        <v>50.2654724121094</v>
       </c>
       <c r="H561" t="n">
         <v>34140</v>
@@ -16986,7 +16986,7 @@
         <v>51.6758041381836</v>
       </c>
       <c r="G573" t="n">
-        <v>39.9546012878418</v>
+        <v>39.9546051025391</v>
       </c>
       <c r="H573" t="n">
         <v>230355</v>
@@ -17015,7 +17015,7 @@
         <v>53.5928077697754</v>
       </c>
       <c r="G574" t="n">
-        <v>41.4367904663086</v>
+        <v>41.4367866516113</v>
       </c>
       <c r="H574" t="n">
         <v>153152</v>
@@ -17131,7 +17131,7 @@
         <v>61.0524597167969</v>
       </c>
       <c r="G578" t="n">
-        <v>47.2044258117676</v>
+        <v>47.2044296264648</v>
       </c>
       <c r="H578" t="n">
         <v>397440</v>
@@ -17247,7 +17247,7 @@
         <v>56.2391090393066</v>
       </c>
       <c r="G582" t="n">
-        <v>43.482852935791</v>
+        <v>43.4828491210938</v>
       </c>
       <c r="H582" t="n">
         <v>113949</v>
@@ -17276,7 +17276,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G583" t="n">
-        <v>43.1767425537109</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H583" t="n">
         <v>160680</v>
@@ -17363,7 +17363,7 @@
         <v>56.8850555419922</v>
       </c>
       <c r="G586" t="n">
-        <v>43.9822807312012</v>
+        <v>43.9822845458984</v>
       </c>
       <c r="H586" t="n">
         <v>88984</v>
@@ -17421,7 +17421,7 @@
         <v>56.5933380126953</v>
       </c>
       <c r="G588" t="n">
-        <v>43.7567329406738</v>
+        <v>43.7567367553711</v>
       </c>
       <c r="H588" t="n">
         <v>57313</v>
@@ -17479,7 +17479,7 @@
         <v>56.4683151245117</v>
       </c>
       <c r="G590" t="n">
-        <v>43.6600685119629</v>
+        <v>43.6600646972656</v>
       </c>
       <c r="H590" t="n">
         <v>38834</v>
@@ -17885,7 +17885,7 @@
         <v>67.3035659790039</v>
       </c>
       <c r="G604" t="n">
-        <v>52.0376510620117</v>
+        <v>52.0376472473145</v>
       </c>
       <c r="H604" t="n">
         <v>379106</v>
@@ -18001,7 +18001,7 @@
         <v>59.0312690734863</v>
       </c>
       <c r="G608" t="n">
-        <v>45.6416854858398</v>
+        <v>45.6416893005371</v>
       </c>
       <c r="H608" t="n">
         <v>166866</v>
@@ -18233,7 +18233,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G616" t="n">
-        <v>43.1767425537109</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H616" t="n">
         <v>281053</v>
@@ -18436,7 +18436,7 @@
         <v>57.9269065856934</v>
       </c>
       <c r="G623" t="n">
-        <v>44.7878227233887</v>
+        <v>44.7878189086914</v>
       </c>
       <c r="H623" t="n">
         <v>250852</v>
@@ -18639,7 +18639,7 @@
         <v>56.6975250244141</v>
       </c>
       <c r="G630" t="n">
-        <v>43.8372917175293</v>
+        <v>43.837287902832</v>
       </c>
       <c r="H630" t="n">
         <v>35877</v>
@@ -18668,7 +18668,7 @@
         <v>55.843204498291</v>
       </c>
       <c r="G631" t="n">
-        <v>43.1767425537109</v>
+        <v>43.1767463684082</v>
       </c>
       <c r="H631" t="n">
         <v>46391</v>
@@ -18900,7 +18900,7 @@
         <v>51.6758041381836</v>
       </c>
       <c r="G639" t="n">
-        <v>39.9546012878418</v>
+        <v>39.9546051025391</v>
       </c>
       <c r="H639" t="n">
         <v>54533</v>
@@ -18987,7 +18987,7 @@
         <v>51.0715293884277</v>
       </c>
       <c r="G642" t="n">
-        <v>39.4873886108398</v>
+        <v>39.4873924255371</v>
       </c>
       <c r="H642" t="n">
         <v>48431</v>
@@ -19016,7 +19016,7 @@
         <v>51.4465942382812</v>
       </c>
       <c r="G643" t="n">
-        <v>39.7773818969727</v>
+        <v>39.7773857116699</v>
       </c>
       <c r="H643" t="n">
         <v>34432</v>
@@ -19306,7 +19306,7 @@
         <v>49.4879150390625</v>
       </c>
       <c r="G653" t="n">
-        <v>38.2629737854004</v>
+        <v>38.2629776000977</v>
       </c>
       <c r="H653" t="n">
         <v>58634</v>
@@ -19364,7 +19364,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G655" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374221801758</v>
       </c>
       <c r="H655" t="n">
         <v>34543</v>
@@ -19422,7 +19422,7 @@
         <v>52.071704864502</v>
       </c>
       <c r="G657" t="n">
-        <v>40.2607078552246</v>
+        <v>40.2607040405273</v>
       </c>
       <c r="H657" t="n">
         <v>248665</v>
@@ -19741,7 +19741,7 @@
         <v>46.3415260314941</v>
       </c>
       <c r="G668" t="n">
-        <v>35.8302536010742</v>
+        <v>35.8302574157715</v>
       </c>
       <c r="H668" t="n">
         <v>138277</v>
@@ -19944,7 +19944,7 @@
         <v>45.570556640625</v>
       </c>
       <c r="G675" t="n">
-        <v>35.2341613769531</v>
+        <v>35.2341575622559</v>
       </c>
       <c r="H675" t="n">
         <v>20036</v>
@@ -19973,7 +19973,7 @@
         <v>45.5288848876953</v>
       </c>
       <c r="G676" t="n">
-        <v>35.2019386291504</v>
+        <v>35.2019424438477</v>
       </c>
       <c r="H676" t="n">
         <v>28978</v>
@@ -20060,7 +20060,7 @@
         <v>45.4038581848145</v>
       </c>
       <c r="G679" t="n">
-        <v>35.1052703857422</v>
+        <v>35.1052742004395</v>
       </c>
       <c r="H679" t="n">
         <v>107371</v>
@@ -20089,7 +20089,7 @@
         <v>44.0494537353516</v>
       </c>
       <c r="G680" t="n">
-        <v>34.0580749511719</v>
+        <v>34.0580711364746</v>
       </c>
       <c r="H680" t="n">
         <v>49600</v>
@@ -20321,7 +20321,7 @@
         <v>49.1961975097656</v>
       </c>
       <c r="G688" t="n">
-        <v>38.037425994873</v>
+        <v>38.0374221801758</v>
       </c>
       <c r="H688" t="n">
         <v>118566</v>
@@ -20408,7 +20408,7 @@
         <v>46.6124076843262</v>
       </c>
       <c r="G691" t="n">
-        <v>36.0396957397461</v>
+        <v>36.0396995544434</v>
       </c>
       <c r="H691" t="n">
         <v>87887</v>
@@ -20727,7 +20727,7 @@
         <v>44.8412628173828</v>
       </c>
       <c r="G702" t="n">
-        <v>34.6702880859375</v>
+        <v>34.6702842712402</v>
       </c>
       <c r="H702" t="n">
         <v>58496</v>
@@ -20872,7 +20872,7 @@
         <v>40.1008377075195</v>
       </c>
       <c r="G707" t="n">
-        <v>31.005090713501</v>
+        <v>31.0050945281982</v>
       </c>
       <c r="H707" t="n">
         <v>128220</v>
@@ -21075,7 +21075,7 @@
         <v>35.7875785827637</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6701755523682</v>
+        <v>27.6701736450195</v>
       </c>
       <c r="H714" t="n">
         <v>86668</v>
@@ -21104,7 +21104,7 @@
         <v>34.8603286743164</v>
       </c>
       <c r="G715" t="n">
-        <v>26.9532470703125</v>
+        <v>26.9532451629639</v>
       </c>
       <c r="H715" t="n">
         <v>100245</v>
@@ -21162,7 +21162,7 @@
         <v>31.3805484771729</v>
       </c>
       <c r="G717" t="n">
-        <v>24.2627563476562</v>
+        <v>24.2627544403076</v>
       </c>
       <c r="H717" t="n">
         <v>177943</v>
@@ -21191,7 +21191,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G718" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H718" t="n">
         <v>180004</v>
@@ -21278,7 +21278,7 @@
         <v>29.5260524749756</v>
       </c>
       <c r="G721" t="n">
-        <v>22.8288974761963</v>
+        <v>22.8288993835449</v>
       </c>
       <c r="H721" t="n">
         <v>167797</v>
@@ -21452,7 +21452,7 @@
         <v>32.3598861694336</v>
       </c>
       <c r="G727" t="n">
-        <v>25.0199584960938</v>
+        <v>25.0199565887451</v>
       </c>
       <c r="H727" t="n">
         <v>103399</v>
@@ -21481,7 +21481,7 @@
         <v>31.6201725006104</v>
       </c>
       <c r="G728" t="n">
-        <v>24.4480285644531</v>
+        <v>24.4480266571045</v>
       </c>
       <c r="H728" t="n">
         <v>59503</v>
@@ -21510,7 +21510,7 @@
         <v>30.7137622833252</v>
       </c>
       <c r="G729" t="n">
-        <v>23.7472095489502</v>
+        <v>23.7472114562988</v>
       </c>
       <c r="H729" t="n">
         <v>111085</v>
@@ -21597,7 +21597,7 @@
         <v>31.1930141448975</v>
       </c>
       <c r="G732" t="n">
-        <v>24.1177577972412</v>
+        <v>24.1177558898926</v>
       </c>
       <c r="H732" t="n">
         <v>82427</v>
@@ -21829,7 +21829,7 @@
         <v>28.8071765899658</v>
       </c>
       <c r="G740" t="n">
-        <v>22.2730808258057</v>
+        <v>22.273078918457</v>
       </c>
       <c r="H740" t="n">
         <v>68762</v>
@@ -21858,7 +21858,7 @@
         <v>29.7031688690186</v>
       </c>
       <c r="G741" t="n">
-        <v>22.965841293335</v>
+        <v>22.9658432006836</v>
       </c>
       <c r="H741" t="n">
         <v>64021</v>
@@ -21887,7 +21887,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G742" t="n">
-        <v>24.8105163574219</v>
+        <v>24.8105182647705</v>
       </c>
       <c r="H742" t="n">
         <v>190080</v>
@@ -21916,7 +21916,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H743" t="n">
         <v>69577</v>
@@ -22032,7 +22032,7 @@
         <v>36.7564964294434</v>
       </c>
       <c r="G747" t="n">
-        <v>28.419319152832</v>
+        <v>28.4193210601807</v>
       </c>
       <c r="H747" t="n">
         <v>286148</v>
@@ -22061,7 +22061,7 @@
         <v>36.048038482666</v>
       </c>
       <c r="G748" t="n">
-        <v>27.8715572357178</v>
+        <v>27.8715553283691</v>
       </c>
       <c r="H748" t="n">
         <v>89948</v>
@@ -22090,7 +22090,7 @@
         <v>35.7979965209961</v>
       </c>
       <c r="G749" t="n">
-        <v>27.6782283782959</v>
+        <v>27.6782302856445</v>
       </c>
       <c r="H749" t="n">
         <v>99834</v>
@@ -22177,7 +22177,7 @@
         <v>33.2037887573242</v>
       </c>
       <c r="G752" t="n">
-        <v>25.6724452972412</v>
+        <v>25.6724433898926</v>
       </c>
       <c r="H752" t="n">
         <v>107022</v>
@@ -22293,7 +22293,7 @@
         <v>32.0890045166016</v>
       </c>
       <c r="G756" t="n">
-        <v>24.8105163574219</v>
+        <v>24.8105182647705</v>
       </c>
       <c r="H756" t="n">
         <v>41000</v>
@@ -22322,7 +22322,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G757" t="n">
-        <v>24.4077529907227</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H757" t="n">
         <v>41825</v>
@@ -22380,7 +22380,7 @@
         <v>31.5055694580078</v>
       </c>
       <c r="G759" t="n">
-        <v>24.3594169616699</v>
+        <v>24.3594188690186</v>
       </c>
       <c r="H759" t="n">
         <v>65014</v>
@@ -22467,7 +22467,7 @@
         <v>30.9325523376465</v>
       </c>
       <c r="G762" t="n">
-        <v>23.916374206543</v>
+        <v>23.9163722991943</v>
       </c>
       <c r="H762" t="n">
         <v>60399</v>
@@ -22496,7 +22496,7 @@
         <v>31.1617584228516</v>
       </c>
       <c r="G763" t="n">
-        <v>24.0935916900635</v>
+        <v>24.0935897827148</v>
       </c>
       <c r="H763" t="n">
         <v>61156</v>
@@ -22612,7 +22612,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G767" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H767" t="n">
         <v>49945</v>
@@ -22641,7 +22641,7 @@
         <v>31.9744033813477</v>
       </c>
       <c r="G768" t="n">
-        <v>24.7219104766846</v>
+        <v>24.7219123840332</v>
       </c>
       <c r="H768" t="n">
         <v>89969</v>
@@ -22728,7 +22728,7 @@
         <v>31.4013843536377</v>
       </c>
       <c r="G771" t="n">
-        <v>24.2788639068604</v>
+        <v>24.278865814209</v>
       </c>
       <c r="H771" t="n">
         <v>59036</v>
@@ -22757,7 +22757,7 @@
         <v>28.2029037475586</v>
       </c>
       <c r="G772" t="n">
-        <v>21.8058700561523</v>
+        <v>21.8058681488037</v>
       </c>
       <c r="H772" t="n">
         <v>398596</v>
@@ -22931,7 +22931,7 @@
         <v>25.2336273193359</v>
       </c>
       <c r="G778" t="n">
-        <v>19.5100898742676</v>
+        <v>19.5100917816162</v>
       </c>
       <c r="H778" t="n">
         <v>81516</v>
@@ -22989,7 +22989,7 @@
         <v>25.598274230957</v>
       </c>
       <c r="G780" t="n">
-        <v>19.792028427124</v>
+        <v>19.7920265197754</v>
       </c>
       <c r="H780" t="n">
         <v>186608</v>
@@ -23366,7 +23366,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G793" t="n">
-        <v>21.5883712768555</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H793" t="n">
         <v>765447</v>
@@ -23511,7 +23511,7 @@
         <v>27.1714706420898</v>
       </c>
       <c r="G798" t="n">
-        <v>21.0083885192871</v>
+        <v>21.0083866119385</v>
       </c>
       <c r="H798" t="n">
         <v>100025</v>
@@ -23540,7 +23540,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G799" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H799" t="n">
         <v>101229</v>
@@ -23743,7 +23743,7 @@
         <v>27.9841136932373</v>
       </c>
       <c r="G806" t="n">
-        <v>21.6367073059082</v>
+        <v>21.6367053985596</v>
       </c>
       <c r="H806" t="n">
         <v>111838</v>
@@ -23801,7 +23801,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G808" t="n">
-        <v>21.5883712768555</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H808" t="n">
         <v>86623</v>
@@ -23888,7 +23888,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G811" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H811" t="n">
         <v>85007</v>
@@ -23917,7 +23917,7 @@
         <v>27.1297950744629</v>
       </c>
       <c r="G812" t="n">
-        <v>20.9761638641357</v>
+        <v>20.9761657714844</v>
       </c>
       <c r="H812" t="n">
         <v>42335</v>
@@ -24004,7 +24004,7 @@
         <v>26.4630126953125</v>
       </c>
       <c r="G815" t="n">
-        <v>20.4606246948242</v>
+        <v>20.4606227874756</v>
       </c>
       <c r="H815" t="n">
         <v>66042</v>
@@ -24062,7 +24062,7 @@
         <v>26.8901691436768</v>
       </c>
       <c r="G817" t="n">
-        <v>20.7908897399902</v>
+        <v>20.7908916473389</v>
       </c>
       <c r="H817" t="n">
         <v>135708</v>
@@ -24120,7 +24120,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G819" t="n">
-        <v>21.4917106628418</v>
+        <v>21.4917087554932</v>
       </c>
       <c r="H819" t="n">
         <v>111493</v>
@@ -24178,7 +24178,7 @@
         <v>26.5151042938232</v>
       </c>
       <c r="G821" t="n">
-        <v>20.5008983612061</v>
+        <v>20.5009002685547</v>
       </c>
       <c r="H821" t="n">
         <v>75021</v>
@@ -24323,7 +24323,7 @@
         <v>25.9420852661133</v>
       </c>
       <c r="G826" t="n">
-        <v>20.0578517913818</v>
+        <v>20.0578536987305</v>
       </c>
       <c r="H826" t="n">
         <v>46026</v>
@@ -24468,7 +24468,7 @@
         <v>26.5671977996826</v>
       </c>
       <c r="G831" t="n">
-        <v>20.5411777496338</v>
+        <v>20.5411758422852</v>
       </c>
       <c r="H831" t="n">
         <v>63160</v>
@@ -24613,7 +24613,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G836" t="n">
-        <v>21.5883712768555</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H836" t="n">
         <v>263799</v>
@@ -24729,7 +24729,7 @@
         <v>29.0884761810303</v>
       </c>
       <c r="G840" t="n">
-        <v>22.4905738830566</v>
+        <v>22.4905757904053</v>
       </c>
       <c r="H840" t="n">
         <v>136313</v>
@@ -24816,7 +24816,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G843" t="n">
-        <v>21.1856060028076</v>
+        <v>21.185604095459</v>
       </c>
       <c r="H843" t="n">
         <v>56383</v>
@@ -24874,7 +24874,7 @@
         <v>28.2341575622559</v>
       </c>
       <c r="G845" t="n">
-        <v>21.8300342559814</v>
+        <v>21.8300323486328</v>
       </c>
       <c r="H845" t="n">
         <v>92713</v>
@@ -24932,7 +24932,7 @@
         <v>27.9841136932373</v>
       </c>
       <c r="G847" t="n">
-        <v>21.6367073059082</v>
+        <v>21.6367053985596</v>
       </c>
       <c r="H847" t="n">
         <v>78060</v>
@@ -24990,7 +24990,7 @@
         <v>27.5882110595703</v>
       </c>
       <c r="G849" t="n">
-        <v>21.330602645874</v>
+        <v>21.3306007385254</v>
       </c>
       <c r="H849" t="n">
         <v>65057</v>
@@ -25019,7 +25019,7 @@
         <v>26.9214267730713</v>
       </c>
       <c r="G850" t="n">
-        <v>20.8150577545166</v>
+        <v>20.8150596618652</v>
       </c>
       <c r="H850" t="n">
         <v>79359</v>
@@ -25048,7 +25048,7 @@
         <v>26.5671977996826</v>
       </c>
       <c r="G851" t="n">
-        <v>20.5411777496338</v>
+        <v>20.5411758422852</v>
       </c>
       <c r="H851" t="n">
         <v>87555</v>
@@ -25193,7 +25193,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G856" t="n">
-        <v>18.6723308563232</v>
+        <v>18.6723327636719</v>
       </c>
       <c r="H856" t="n">
         <v>103442</v>
@@ -25367,7 +25367,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G862" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H862" t="n">
         <v>131429</v>
@@ -25454,7 +25454,7 @@
         <v>22.2747707366943</v>
       </c>
       <c r="G865" t="n">
-        <v>17.2223663330078</v>
+        <v>17.2223682403564</v>
       </c>
       <c r="H865" t="n">
         <v>109629</v>
@@ -25541,7 +25541,7 @@
         <v>21.7538452148438</v>
       </c>
       <c r="G868" t="n">
-        <v>16.8195972442627</v>
+        <v>16.8195991516113</v>
       </c>
       <c r="H868" t="n">
         <v>75682</v>
@@ -25570,7 +25570,7 @@
         <v>21.4829635620117</v>
       </c>
       <c r="G869" t="n">
-        <v>16.6101570129395</v>
+        <v>16.6101589202881</v>
       </c>
       <c r="H869" t="n">
         <v>57928</v>
@@ -25657,7 +25657,7 @@
         <v>20.9828758239746</v>
       </c>
       <c r="G872" t="n">
-        <v>16.223503112793</v>
+        <v>16.2235012054443</v>
       </c>
       <c r="H872" t="n">
         <v>64631</v>
@@ -25947,7 +25947,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G882" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H882" t="n">
         <v>129721</v>
@@ -26063,7 +26063,7 @@
         <v>22.0247268676758</v>
       </c>
       <c r="G886" t="n">
-        <v>17.0290374755859</v>
+        <v>17.0290355682373</v>
       </c>
       <c r="H886" t="n">
         <v>60342</v>
@@ -26353,7 +26353,7 @@
         <v>35.1520462036133</v>
       </c>
       <c r="G896" t="n">
-        <v>27.1787929534912</v>
+        <v>27.1787948608398</v>
       </c>
       <c r="H896" t="n">
         <v>688052</v>
@@ -26382,7 +26382,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G897" t="n">
-        <v>27.5493431091309</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H897" t="n">
         <v>754780</v>
@@ -26469,7 +26469,7 @@
         <v>34.4435882568359</v>
       </c>
       <c r="G900" t="n">
-        <v>26.631031036377</v>
+        <v>26.6310291290283</v>
       </c>
       <c r="H900" t="n">
         <v>494613</v>
@@ -26701,7 +26701,7 @@
         <v>29.9427947998047</v>
       </c>
       <c r="G908" t="n">
-        <v>23.1511173248291</v>
+        <v>23.1511154174805</v>
       </c>
       <c r="H908" t="n">
         <v>158585</v>
@@ -26904,7 +26904,7 @@
         <v>26.7547302246094</v>
       </c>
       <c r="G915" t="n">
-        <v>20.6861743927002</v>
+        <v>20.6861724853516</v>
       </c>
       <c r="H915" t="n">
         <v>108233</v>
@@ -26933,7 +26933,7 @@
         <v>26.4630126953125</v>
       </c>
       <c r="G916" t="n">
-        <v>20.4606246948242</v>
+        <v>20.4606227874756</v>
       </c>
       <c r="H916" t="n">
         <v>120821</v>
@@ -27078,7 +27078,7 @@
         <v>27.1506328582764</v>
       </c>
       <c r="G921" t="n">
-        <v>20.9922771453857</v>
+        <v>20.9922752380371</v>
       </c>
       <c r="H921" t="n">
         <v>265131</v>
@@ -27194,7 +27194,7 @@
         <v>27.5882110595703</v>
       </c>
       <c r="G925" t="n">
-        <v>21.330602645874</v>
+        <v>21.3306007385254</v>
       </c>
       <c r="H925" t="n">
         <v>85266</v>
@@ -27310,7 +27310,7 @@
         <v>28.0466251373291</v>
       </c>
       <c r="G929" t="n">
-        <v>21.685037612915</v>
+        <v>21.6850357055664</v>
       </c>
       <c r="H929" t="n">
         <v>97800</v>
@@ -27397,7 +27397,7 @@
         <v>30.2136745452881</v>
       </c>
       <c r="G932" t="n">
-        <v>23.3605537414551</v>
+        <v>23.3605518341064</v>
       </c>
       <c r="H932" t="n">
         <v>674039</v>
@@ -27600,7 +27600,7 @@
         <v>33.4850845336914</v>
       </c>
       <c r="G939" t="n">
-        <v>25.8899345397949</v>
+        <v>25.8899364471436</v>
       </c>
       <c r="H939" t="n">
         <v>202392</v>
@@ -27658,7 +27658,7 @@
         <v>33.651782989502</v>
       </c>
       <c r="G941" t="n">
-        <v>26.0188255310059</v>
+        <v>26.0188236236572</v>
       </c>
       <c r="H941" t="n">
         <v>233460</v>
@@ -27687,7 +27687,7 @@
         <v>34.0268478393555</v>
       </c>
       <c r="G942" t="n">
-        <v>26.30881690979</v>
+        <v>26.3088150024414</v>
       </c>
       <c r="H942" t="n">
         <v>282982</v>
@@ -27890,7 +27890,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G949" t="n">
-        <v>25.1327342987061</v>
+        <v>25.1327362060547</v>
       </c>
       <c r="H949" t="n">
         <v>164909</v>
@@ -27919,7 +27919,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G950" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H950" t="n">
         <v>295808</v>
@@ -28006,7 +28006,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G953" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H953" t="n">
         <v>64598</v>
@@ -28035,7 +28035,7 @@
         <v>31.2138519287109</v>
       </c>
       <c r="G954" t="n">
-        <v>24.1338672637939</v>
+        <v>24.1338691711426</v>
       </c>
       <c r="H954" t="n">
         <v>110938</v>
@@ -28093,7 +28093,7 @@
         <v>30.5262298583984</v>
       </c>
       <c r="G956" t="n">
-        <v>23.6022129058838</v>
+        <v>23.6022148132324</v>
       </c>
       <c r="H956" t="n">
         <v>76872</v>
@@ -28209,7 +28209,7 @@
         <v>29.9427947998047</v>
       </c>
       <c r="G960" t="n">
-        <v>23.1511173248291</v>
+        <v>23.1511154174805</v>
       </c>
       <c r="H960" t="n">
         <v>82455</v>
@@ -28412,7 +28412,7 @@
         <v>31.5055694580078</v>
       </c>
       <c r="G967" t="n">
-        <v>24.3594169616699</v>
+        <v>24.3594188690186</v>
       </c>
       <c r="H967" t="n">
         <v>130230</v>
@@ -28441,7 +28441,7 @@
         <v>31.9431476593018</v>
       </c>
       <c r="G968" t="n">
-        <v>24.6977443695068</v>
+        <v>24.6977424621582</v>
       </c>
       <c r="H968" t="n">
         <v>117112</v>
@@ -28615,7 +28615,7 @@
         <v>30.5470676422119</v>
       </c>
       <c r="G974" t="n">
-        <v>23.6183261871338</v>
+        <v>23.6183242797852</v>
       </c>
       <c r="H974" t="n">
         <v>118306</v>
@@ -28789,7 +28789,7 @@
         <v>31.6722660064697</v>
       </c>
       <c r="G980" t="n">
-        <v>24.4883041381836</v>
+        <v>24.4883060455322</v>
       </c>
       <c r="H980" t="n">
         <v>552266</v>
@@ -28818,7 +28818,7 @@
         <v>31.5680809020996</v>
       </c>
       <c r="G981" t="n">
-        <v>24.4077529907227</v>
+        <v>24.407751083374</v>
       </c>
       <c r="H981" t="n">
         <v>162326</v>
@@ -28905,7 +28905,7 @@
         <v>31.2138519287109</v>
       </c>
       <c r="G984" t="n">
-        <v>24.1338672637939</v>
+        <v>24.1338691711426</v>
       </c>
       <c r="H984" t="n">
         <v>84349</v>
@@ -28992,7 +28992,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G987" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H987" t="n">
         <v>52930</v>
@@ -29079,7 +29079,7 @@
         <v>30.4012088775635</v>
       </c>
       <c r="G990" t="n">
-        <v>23.5055522918701</v>
+        <v>23.5055503845215</v>
       </c>
       <c r="H990" t="n">
         <v>90326</v>
@@ -29108,7 +29108,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G991" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H991" t="n">
         <v>68666</v>
@@ -29282,7 +29282,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G997" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H997" t="n">
         <v>75104</v>
@@ -29340,7 +29340,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G999" t="n">
-        <v>22.7483463287354</v>
+        <v>22.7483444213867</v>
       </c>
       <c r="H999" t="n">
         <v>85330</v>
@@ -29456,7 +29456,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1003" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1003" t="n">
         <v>96029</v>
@@ -29543,7 +29543,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1006" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1006" t="n">
         <v>86215</v>
@@ -29659,7 +29659,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1010" t="n">
-        <v>21.9911403656006</v>
+        <v>21.9911422729492</v>
       </c>
       <c r="H1010" t="n">
         <v>116651</v>
@@ -29833,7 +29833,7 @@
         <v>29.4218673706055</v>
       </c>
       <c r="G1016" t="n">
-        <v>22.7483463287354</v>
+        <v>22.7483444213867</v>
       </c>
       <c r="H1016" t="n">
         <v>115421</v>
@@ -29978,7 +29978,7 @@
         <v>29.9427947998047</v>
       </c>
       <c r="G1021" t="n">
-        <v>23.1511173248291</v>
+        <v>23.1511154174805</v>
       </c>
       <c r="H1021" t="n">
         <v>110137</v>
@@ -30036,7 +30036,7 @@
         <v>33.9643363952637</v>
       </c>
       <c r="G1023" t="n">
-        <v>26.2604827880859</v>
+        <v>26.2604846954346</v>
       </c>
       <c r="H1023" t="n">
         <v>837731</v>
@@ -30065,7 +30065,7 @@
         <v>35.6312980651855</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.5493431091309</v>
+        <v>27.5493412017822</v>
       </c>
       <c r="H1024" t="n">
         <v>809390</v>
@@ -30123,7 +30123,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1026" t="n">
-        <v>27.3076839447021</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1026" t="n">
         <v>378731</v>
@@ -30152,7 +30152,7 @@
         <v>35.5687866210938</v>
       </c>
       <c r="G1027" t="n">
-        <v>27.5010070800781</v>
+        <v>27.5010089874268</v>
       </c>
       <c r="H1027" t="n">
         <v>242772</v>
@@ -30239,7 +30239,7 @@
         <v>38.9652214050293</v>
       </c>
       <c r="G1030" t="n">
-        <v>30.1270561218262</v>
+        <v>30.1270599365234</v>
       </c>
       <c r="H1030" t="n">
         <v>657786</v>
@@ -30268,7 +30268,7 @@
         <v>37.9650459289551</v>
       </c>
       <c r="G1031" t="n">
-        <v>29.3537425994873</v>
+        <v>29.3537464141846</v>
       </c>
       <c r="H1031" t="n">
         <v>257810</v>
@@ -30442,7 +30442,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1037" t="n">
-        <v>27.3076839447021</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1037" t="n">
         <v>256721</v>
@@ -30471,7 +30471,7 @@
         <v>35.3187446594238</v>
       </c>
       <c r="G1038" t="n">
-        <v>27.3076839447021</v>
+        <v>27.3076801300049</v>
       </c>
       <c r="H1038" t="n">
         <v>147337</v>
@@ -30616,7 +30616,7 @@
         <v>36.1105499267578</v>
       </c>
       <c r="G1043" t="n">
-        <v>27.9198894500732</v>
+        <v>27.919885635376</v>
       </c>
       <c r="H1043" t="n">
         <v>263584</v>
@@ -30819,7 +30819,7 @@
         <v>43.9661064147949</v>
       </c>
       <c r="G1050" t="n">
-        <v>33.9936370849609</v>
+        <v>33.9936332702637</v>
       </c>
       <c r="H1050" t="n">
         <v>1453453</v>
@@ -31109,7 +31109,7 @@
         <v>33.3183898925781</v>
       </c>
       <c r="G1060" t="n">
-        <v>25.7610530853271</v>
+        <v>25.7610511779785</v>
       </c>
       <c r="H1060" t="n">
         <v>600964</v>
@@ -31312,7 +31312,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1067" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1067" t="n">
         <v>602051</v>
@@ -31370,7 +31370,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1069" t="n">
-        <v>17.0773696899414</v>
+        <v>17.07737159729</v>
       </c>
       <c r="H1069" t="n">
         <v>307976</v>
@@ -31486,7 +31486,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1073" t="n">
-        <v>16.5618267059326</v>
+        <v>16.561824798584</v>
       </c>
       <c r="H1073" t="n">
         <v>191571</v>
@@ -31544,7 +31544,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1075" t="n">
-        <v>18.0440120697021</v>
+        <v>18.0440139770508</v>
       </c>
       <c r="H1075" t="n">
         <v>380243</v>
@@ -31660,7 +31660,7 @@
         <v>23.6083393096924</v>
       </c>
       <c r="G1079" t="n">
-        <v>18.2534523010254</v>
+        <v>18.253454208374</v>
       </c>
       <c r="H1079" t="n">
         <v>119826</v>
@@ -31747,7 +31747,7 @@
         <v>23.7750358581543</v>
       </c>
       <c r="G1082" t="n">
-        <v>18.3823394775391</v>
+        <v>18.3823375701904</v>
       </c>
       <c r="H1082" t="n">
         <v>65084</v>
@@ -31776,7 +31776,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1083" t="n">
-        <v>18.849552154541</v>
+        <v>18.8495502471924</v>
       </c>
       <c r="H1083" t="n">
         <v>133398</v>
@@ -31863,7 +31863,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1086" t="n">
-        <v>19.203987121582</v>
+        <v>19.2039852142334</v>
       </c>
       <c r="H1086" t="n">
         <v>126056</v>
@@ -31892,7 +31892,7 @@
         <v>24.5668430328369</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.9945487976074</v>
+        <v>18.9945468902588</v>
       </c>
       <c r="H1087" t="n">
         <v>102725</v>
@@ -32095,7 +32095,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1094" t="n">
-        <v>17.6734676361084</v>
+        <v>17.6734657287598</v>
       </c>
       <c r="H1094" t="n">
         <v>86867</v>
@@ -32153,7 +32153,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1096" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1096" t="n">
         <v>91309</v>
@@ -32182,7 +32182,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1097" t="n">
         <v>181346</v>
@@ -32269,7 +32269,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1100" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1100" t="n">
         <v>53003</v>
@@ -32298,7 +32298,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1101" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1101" t="n">
         <v>70876</v>
@@ -32501,7 +32501,7 @@
         <v>23.2332744598389</v>
       </c>
       <c r="G1108" t="n">
-        <v>17.9634609222412</v>
+        <v>17.9634590148926</v>
       </c>
       <c r="H1108" t="n">
         <v>76222</v>
@@ -32617,7 +32617,7 @@
         <v>21.4204521179199</v>
       </c>
       <c r="G1112" t="n">
-        <v>16.5618267059326</v>
+        <v>16.561824798584</v>
       </c>
       <c r="H1112" t="n">
         <v>116319</v>
@@ -32675,7 +32675,7 @@
         <v>21.3371047973633</v>
       </c>
       <c r="G1114" t="n">
-        <v>16.4973831176758</v>
+        <v>16.4973850250244</v>
       </c>
       <c r="H1114" t="n">
         <v>115150</v>
@@ -32733,7 +32733,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1116" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H1116" t="n">
         <v>88021</v>
@@ -32820,7 +32820,7 @@
         <v>27.4006767272949</v>
       </c>
       <c r="G1119" t="n">
-        <v>21.1856060028076</v>
+        <v>21.185604095459</v>
       </c>
       <c r="H1119" t="n">
         <v>1322864</v>
@@ -32878,7 +32878,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1121" t="n">
-        <v>21.5883712768555</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1121" t="n">
         <v>244265</v>
@@ -33023,7 +33023,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1126" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1126" t="n">
         <v>401649</v>
@@ -33110,7 +33110,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1129" t="n">
-        <v>22.861120223999</v>
+        <v>22.8611183166504</v>
       </c>
       <c r="H1129" t="n">
         <v>230255</v>
@@ -33168,7 +33168,7 @@
         <v>30.5470676422119</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.6183261871338</v>
+        <v>23.6183242797852</v>
       </c>
       <c r="H1131" t="n">
         <v>259143</v>
@@ -33197,7 +33197,7 @@
         <v>30.7346000671387</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.7633228302002</v>
+        <v>23.7633209228516</v>
       </c>
       <c r="H1132" t="n">
         <v>117120</v>
@@ -33371,7 +33371,7 @@
         <v>34.2768936157227</v>
       </c>
       <c r="G1138" t="n">
-        <v>26.5021438598633</v>
+        <v>26.5021457672119</v>
       </c>
       <c r="H1138" t="n">
         <v>299299</v>
@@ -33400,7 +33400,7 @@
         <v>32.6307678222656</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.2293968200684</v>
+        <v>25.2293949127197</v>
       </c>
       <c r="H1139" t="n">
         <v>249320</v>
@@ -33661,7 +33661,7 @@
         <v>31.8389625549316</v>
       </c>
       <c r="G1148" t="n">
-        <v>24.6171913146973</v>
+        <v>24.6171894073486</v>
       </c>
       <c r="H1148" t="n">
         <v>124950</v>
@@ -33690,7 +33690,7 @@
         <v>32.5057487487793</v>
       </c>
       <c r="G1149" t="n">
-        <v>25.1327342987061</v>
+        <v>25.1327362060547</v>
       </c>
       <c r="H1149" t="n">
         <v>67331</v>
@@ -33777,7 +33777,7 @@
         <v>31.8597984313965</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.6332988739014</v>
+        <v>24.63330078125</v>
       </c>
       <c r="H1152" t="n">
         <v>144542</v>
@@ -33980,7 +33980,7 @@
         <v>36.4856185913086</v>
       </c>
       <c r="G1159" t="n">
-        <v>28.2098846435547</v>
+        <v>28.2098827362061</v>
       </c>
       <c r="H1159" t="n">
         <v>462214</v>
@@ -34125,7 +34125,7 @@
         <v>31.9014720916748</v>
       </c>
       <c r="G1164" t="n">
-        <v>24.6655216217041</v>
+        <v>24.6655235290527</v>
       </c>
       <c r="H1164" t="n">
         <v>153075</v>
@@ -34328,7 +34328,7 @@
         <v>31.2555255889893</v>
       </c>
       <c r="G1171" t="n">
-        <v>24.1660900115967</v>
+        <v>24.1660919189453</v>
       </c>
       <c r="H1171" t="n">
         <v>144072</v>
@@ -34357,7 +34357,7 @@
         <v>30.8804588317871</v>
       </c>
       <c r="G1172" t="n">
-        <v>23.8760948181152</v>
+        <v>23.8760967254639</v>
       </c>
       <c r="H1172" t="n">
         <v>225571</v>
@@ -34473,7 +34473,7 @@
         <v>28.88010597229</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.3294677734375</v>
+        <v>22.3294658660889</v>
       </c>
       <c r="H1176" t="n">
         <v>108064</v>
@@ -34618,7 +34618,7 @@
         <v>30.2345123291016</v>
       </c>
       <c r="G1181" t="n">
-        <v>23.3766632080078</v>
+        <v>23.3766651153564</v>
       </c>
       <c r="H1181" t="n">
         <v>179328</v>
@@ -34647,7 +34647,7 @@
         <v>30.0469799041748</v>
       </c>
       <c r="G1182" t="n">
-        <v>23.23166847229</v>
+        <v>23.2316703796387</v>
       </c>
       <c r="H1182" t="n">
         <v>79634</v>
@@ -34821,7 +34821,7 @@
         <v>29.5677261352539</v>
       </c>
       <c r="G1188" t="n">
-        <v>22.861120223999</v>
+        <v>22.8611183166504</v>
       </c>
       <c r="H1188" t="n">
         <v>181360</v>
@@ -34850,7 +34850,7 @@
         <v>29.8802814483643</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.1027793884277</v>
+        <v>23.1027812957764</v>
       </c>
       <c r="H1189" t="n">
         <v>102070</v>
@@ -34879,7 +34879,7 @@
         <v>29.6302375793457</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.9094524383545</v>
+        <v>22.9094543457031</v>
       </c>
       <c r="H1190" t="n">
         <v>71944</v>
@@ -34995,7 +34995,7 @@
         <v>29.671911239624</v>
       </c>
       <c r="G1194" t="n">
-        <v>22.9416732788086</v>
+        <v>22.94167137146</v>
       </c>
       <c r="H1194" t="n">
         <v>35197</v>
@@ -35024,7 +35024,7 @@
         <v>29.7552604675293</v>
       </c>
       <c r="G1195" t="n">
-        <v>23.0061187744141</v>
+        <v>23.0061168670654</v>
       </c>
       <c r="H1195" t="n">
         <v>37758</v>
@@ -35111,7 +35111,7 @@
         <v>28.4425277709961</v>
       </c>
       <c r="G1198" t="n">
-        <v>21.9911403656006</v>
+        <v>21.9911422729492</v>
       </c>
       <c r="H1198" t="n">
         <v>75589</v>
@@ -35198,7 +35198,7 @@
         <v>27.9216022491455</v>
       </c>
       <c r="G1201" t="n">
-        <v>21.5883712768555</v>
+        <v>21.5883731842041</v>
       </c>
       <c r="H1201" t="n">
         <v>213623</v>
@@ -35401,7 +35401,7 @@
         <v>27.7965812683105</v>
       </c>
       <c r="G1208" t="n">
-        <v>21.4917106628418</v>
+        <v>21.4917087554932</v>
       </c>
       <c r="H1208" t="n">
         <v>131767</v>
@@ -35691,7 +35691,7 @@
         <v>24.8585605621338</v>
       </c>
       <c r="G1218" t="n">
-        <v>19.2200946807861</v>
+        <v>19.2200965881348</v>
       </c>
       <c r="H1218" t="n">
         <v>227042</v>
@@ -35778,7 +35778,7 @@
         <v>24.0459175109863</v>
       </c>
       <c r="G1221" t="n">
-        <v>18.5917797088623</v>
+        <v>18.5917778015137</v>
       </c>
       <c r="H1221" t="n">
         <v>382349</v>
@@ -35807,7 +35807,7 @@
         <v>24.5460052490234</v>
       </c>
       <c r="G1222" t="n">
-        <v>18.9784336090088</v>
+        <v>18.9784355163574</v>
       </c>
       <c r="H1222" t="n">
         <v>166257</v>
@@ -35865,7 +35865,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1224" t="n">
-        <v>18.849552154541</v>
+        <v>18.8495502471924</v>
       </c>
       <c r="H1224" t="n">
         <v>77151</v>
@@ -35952,7 +35952,7 @@
         <v>21.295431137085</v>
       </c>
       <c r="G1227" t="n">
-        <v>16.4651622772217</v>
+        <v>16.4651641845703</v>
       </c>
       <c r="H1227" t="n">
         <v>140219</v>
@@ -36039,7 +36039,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1230" t="n">
-        <v>18.0440120697021</v>
+        <v>18.0440139770508</v>
       </c>
       <c r="H1230" t="n">
         <v>356714</v>
@@ -36068,7 +36068,7 @@
         <v>22.7748603820801</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.6090240478516</v>
+        <v>17.6090259552002</v>
       </c>
       <c r="H1231" t="n">
         <v>366850</v>
@@ -36213,7 +36213,7 @@
         <v>23.6500148773193</v>
       </c>
       <c r="G1236" t="n">
-        <v>18.2856750488281</v>
+        <v>18.2856731414795</v>
       </c>
       <c r="H1236" t="n">
         <v>245630</v>
@@ -36271,7 +36271,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1238" t="n">
-        <v>18.3662261962891</v>
+        <v>18.3662281036377</v>
       </c>
       <c r="H1238" t="n">
         <v>189606</v>
@@ -36590,7 +36590,7 @@
         <v>23.5041542053223</v>
       </c>
       <c r="G1249" t="n">
-        <v>18.1728992462158</v>
+        <v>18.1728973388672</v>
       </c>
       <c r="H1249" t="n">
         <v>265701</v>
@@ -36677,7 +36677,7 @@
         <v>24.3793106079102</v>
       </c>
       <c r="G1252" t="n">
-        <v>18.849552154541</v>
+        <v>18.8495502471924</v>
       </c>
       <c r="H1252" t="n">
         <v>159678</v>
@@ -36764,7 +36764,7 @@
         <v>23.337459564209</v>
       </c>
       <c r="G1255" t="n">
-        <v>18.0440120697021</v>
+        <v>18.0440139770508</v>
       </c>
       <c r="H1255" t="n">
         <v>260189</v>
@@ -36822,7 +36822,7 @@
         <v>22.8165340423584</v>
       </c>
       <c r="G1257" t="n">
-        <v>17.6412467956543</v>
+        <v>17.6412448883057</v>
       </c>
       <c r="H1257" t="n">
         <v>258497</v>
@@ -36967,7 +36967,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1262" t="n">
         <v>79845</v>
@@ -37025,7 +37025,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.4318046569824</v>
+        <v>17.4318065643311</v>
       </c>
       <c r="H1264" t="n">
         <v>328679</v>
@@ -37083,7 +37083,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1266" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H1266" t="n">
         <v>116876</v>
@@ -37112,7 +37112,7 @@
         <v>21.8788681030273</v>
       </c>
       <c r="G1267" t="n">
-        <v>16.9162635803223</v>
+        <v>16.9162616729736</v>
       </c>
       <c r="H1267" t="n">
         <v>88925</v>
@@ -37199,7 +37199,7 @@
         <v>21.7330093383789</v>
       </c>
       <c r="G1270" t="n">
-        <v>16.80348777771</v>
+        <v>16.8034896850586</v>
       </c>
       <c r="H1270" t="n">
         <v>111326</v>
@@ -37257,7 +37257,7 @@
         <v>22.8582077026367</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.6734676361084</v>
+        <v>17.6734657287598</v>
       </c>
       <c r="H1272" t="n">
         <v>374152</v>
@@ -37344,7 +37344,7 @@
         <v>23.7541980743408</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.3662261962891</v>
+        <v>18.3662281036377</v>
       </c>
       <c r="H1275" t="n">
         <v>170011</v>
@@ -37402,7 +37402,7 @@
         <v>23.3582954406738</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.0601234436035</v>
+        <v>18.0601253509521</v>
       </c>
       <c r="H1277" t="n">
         <v>133192</v>
@@ -37489,7 +37489,7 @@
         <v>22.3997936248779</v>
       </c>
       <c r="G1280" t="n">
-        <v>17.3190326690674</v>
+        <v>17.3190307617188</v>
       </c>
       <c r="H1280" t="n">
         <v>107216</v>
@@ -37518,7 +37518,7 @@
         <v>22.5456523895264</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.4318046569824</v>
+        <v>17.4318065643311</v>
       </c>
       <c r="H1281" t="n">
         <v>82476</v>
@@ -37576,7 +37576,7 @@
         <v>22.7331848144531</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.5768013000488</v>
+        <v>17.5768032073975</v>
       </c>
       <c r="H1283" t="n">
         <v>188315</v>
@@ -37750,7 +37750,7 @@
         <v>22.0872383117676</v>
       </c>
       <c r="G1289" t="n">
-        <v>17.0773696899414</v>
+        <v>17.07737159729</v>
       </c>
       <c r="H1289" t="n">
         <v>72279</v>
@@ -37866,7 +37866,7 @@
         <v>22.6081638336182</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.4801406860352</v>
+        <v>17.4801387786865</v>
       </c>
       <c r="H1293" t="n">
         <v>213107</v>
@@ -37924,7 +37924,7 @@
         <v>24.1501026153564</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.6723308563232</v>
+        <v>18.6723327636719</v>
       </c>
       <c r="H1295" t="n">
         <v>825878</v>
@@ -38214,7 +38214,7 @@
         <v>26.6088714599609</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5733985900879</v>
+        <v>20.5733966827393</v>
       </c>
       <c r="H1305" t="n">
         <v>187199</v>
@@ -38272,7 +38272,7 @@
         <v>26.0045967102051</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.1061878204346</v>
+        <v>20.1061859130859</v>
       </c>
       <c r="H1307" t="n">
         <v>173167</v>
@@ -38301,7 +38301,7 @@
         <v>25.9629230499268</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.0739650726318</v>
+        <v>20.0739631652832</v>
       </c>
       <c r="H1308" t="n">
         <v>139323</v>
@@ -38359,7 +38359,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1310" t="n">
         <v>220708</v>
@@ -38388,7 +38388,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1311" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1311" t="n">
         <v>192874</v>
@@ -38504,7 +38504,7 @@
         <v>25.0460948944092</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.3650932312012</v>
+        <v>19.3650951385498</v>
       </c>
       <c r="H1315" t="n">
         <v>145650</v>
@@ -38562,7 +38562,7 @@
         <v>25.3794860839844</v>
       </c>
       <c r="G1317" t="n">
-        <v>19.6228656768799</v>
+        <v>19.6228637695312</v>
       </c>
       <c r="H1317" t="n">
         <v>206937</v>
@@ -38591,7 +38591,7 @@
         <v>25.1711177825928</v>
       </c>
       <c r="G1318" t="n">
-        <v>19.4617595672607</v>
+        <v>19.4617576599121</v>
       </c>
       <c r="H1318" t="n">
         <v>140324</v>
@@ -38620,7 +38620,7 @@
         <v>24.8377246856689</v>
       </c>
       <c r="G1319" t="n">
-        <v>19.203987121582</v>
+